--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -544,7 +544,7 @@
     <x:t>DELBENE, SUZAN K</x:t>
   </x:si>
   <x:si>
-    <x:t>DEMINGS, VAL</x:t>
+    <x:t>DEMINGS, VALDEZ 'VAL'</x:t>
   </x:si>
   <x:si>
     <x:t>DESANTIS, RON</x:t>
@@ -694,7 +694,7 @@
     <x:t>GILLEN, LAURA</x:t>
   </x:si>
   <x:si>
-    <x:t>GILLIBRAND, KIRSTEN</x:t>
+    <x:t>GILLIBRAND, KIRSTEN ELIZABETH MRS.</x:t>
   </x:si>
   <x:si>
     <x:t>GLUESENKAMP PEREZ, MARIE</x:t>
@@ -1072,7 +1072,7 @@
     <x:t>LUCAS, FRANK D.</x:t>
   </x:si>
   <x:si>
-    <x:t>LUJAN, BEN R MR.</x:t>
+    <x:t>LUJAN, BEN RAY</x:t>
   </x:si>
   <x:si>
     <x:t>LUMMIS, CYNTHIA MARIE</x:t>
@@ -1625,6 +1625,9 @@
   </x:si>
   <x:si>
     <x:t>TITUS, DINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOOMEY, PATRICK J</x:t>
   </x:si>
   <x:si>
     <x:t>TOOMEY, PATRICK JOSEPH</x:t>
@@ -1824,8 +1827,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G526" totalsRowShown="0">
-  <x:autoFilter ref="A1:G526"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G527" totalsRowShown="0">
+  <x:autoFilter ref="A1:G527"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2127,7 +2130,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G526"/>
+  <x:dimension ref="A1:G527"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2588,7 +2591,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>557012</x:v>
+        <x:v>1072531</x:v>
       </x:c>
       <x:c r="E20" s="1">
         <x:v>0</x:v>
@@ -2597,7 +2600,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="G20" s="1">
-        <x:v>564012</x:v>
+        <x:v>1079531</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
@@ -3324,7 +3327,7 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>666234</x:v>
+        <x:v>750094</x:v>
       </x:c>
       <x:c r="E52" s="1">
         <x:v>0</x:v>
@@ -3333,7 +3336,7 @@
         <x:v>22900</x:v>
       </x:c>
       <x:c r="G52" s="1">
-        <x:v>692134</x:v>
+        <x:v>775994</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
@@ -5765,7 +5768,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E158" s="1">
-        <x:v>2475788</x:v>
+        <x:v>4279482</x:v>
       </x:c>
       <x:c r="F158" s="1">
         <x:v>0</x:v>
@@ -6199,7 +6202,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D177" s="1">
-        <x:v>91656</x:v>
+        <x:v>183312</x:v>
       </x:c>
       <x:c r="E177" s="1">
         <x:v>0</x:v>
@@ -6208,7 +6211,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G177" s="1">
-        <x:v>91656</x:v>
+        <x:v>183312</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:7">
@@ -7119,7 +7122,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="D217" s="1">
-        <x:v>2099792</x:v>
+        <x:v>3772024</x:v>
       </x:c>
       <x:c r="E217" s="1">
         <x:v>0</x:v>
@@ -7128,7 +7131,7 @@
         <x:v>159500</x:v>
       </x:c>
       <x:c r="G217" s="1">
-        <x:v>2260792</x:v>
+        <x:v>3933024</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:7">
@@ -7263,10 +7266,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F223" s="1">
-        <x:v>2020</x:v>
+        <x:v>47241</x:v>
       </x:c>
       <x:c r="G223" s="1">
-        <x:v>2020</x:v>
+        <x:v>47241</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:7">
@@ -7286,10 +7289,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F224" s="1">
-        <x:v>47241</x:v>
+        <x:v>2020</x:v>
       </x:c>
       <x:c r="G224" s="1">
-        <x:v>47241</x:v>
+        <x:v>2020</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:7">
@@ -8988,10 +8991,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F298" s="1">
-        <x:v>94035</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G298" s="1">
-        <x:v>100435</x:v>
+        <x:v>6400</x:v>
       </x:c>
     </x:row>
     <x:row r="299" spans="1:7">
@@ -9011,10 +9014,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F299" s="1">
-        <x:v>0</x:v>
+        <x:v>94035</x:v>
       </x:c>
       <x:c r="G299" s="1">
-        <x:v>6400</x:v>
+        <x:v>100435</x:v>
       </x:c>
     </x:row>
     <x:row r="300" spans="1:7">
@@ -9764,7 +9767,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D332" s="1">
-        <x:v>1564215</x:v>
+        <x:v>3128430</x:v>
       </x:c>
       <x:c r="E332" s="1">
         <x:v>0</x:v>
@@ -9773,7 +9776,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G332" s="1">
-        <x:v>1564215</x:v>
+        <x:v>3128430</x:v>
       </x:c>
     </x:row>
     <x:row r="333" spans="1:7">
@@ -10017,7 +10020,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D343" s="1">
-        <x:v>5031161</x:v>
+        <x:v>10049014</x:v>
       </x:c>
       <x:c r="E343" s="1">
         <x:v>0</x:v>
@@ -10026,7 +10029,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G343" s="1">
-        <x:v>5031161</x:v>
+        <x:v>10049014</x:v>
       </x:c>
     </x:row>
     <x:row r="344" spans="1:7">
@@ -10063,7 +10066,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D345" s="1">
-        <x:v>587501</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="E345" s="1">
         <x:v>0</x:v>
@@ -10072,7 +10075,7 @@
         <x:v>7600</x:v>
       </x:c>
       <x:c r="G345" s="1">
-        <x:v>595101</x:v>
+        <x:v>676049</x:v>
       </x:c>
     </x:row>
     <x:row r="346" spans="1:7">
@@ -10339,7 +10342,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D357" s="1">
-        <x:v>141263</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E357" s="1">
         <x:v>0</x:v>
@@ -10348,7 +10351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G357" s="1">
-        <x:v>141263</x:v>
+        <x:v>282526</x:v>
       </x:c>
     </x:row>
     <x:row r="358" spans="1:7">
@@ -11032,7 +11035,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E387" s="1">
-        <x:v>817065</x:v>
+        <x:v>1634131</x:v>
       </x:c>
       <x:c r="F387" s="1">
         <x:v>0</x:v>
@@ -12662,7 +12665,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D458" s="1">
-        <x:v>771658</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E458" s="1">
         <x:v>0</x:v>
@@ -12671,7 +12674,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G458" s="1">
-        <x:v>771658</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="459" spans="1:7">
@@ -12734,7 +12737,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E461" s="1">
-        <x:v>9985740</x:v>
+        <x:v>15154476</x:v>
       </x:c>
       <x:c r="F461" s="1">
         <x:v>0</x:v>
@@ -13243,10 +13246,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F483" s="1">
-        <x:v>8300</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G483" s="1">
-        <x:v>8300</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="484" spans="1:7">
@@ -13254,22 +13257,22 @@
         <x:v>538</x:v>
       </x:c>
       <x:c r="B484" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C484" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D484" s="1">
-        <x:v>173232</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E484" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F484" s="1">
-        <x:v>164830</x:v>
+        <x:v>6300</x:v>
       </x:c>
       <x:c r="G484" s="1">
-        <x:v>342062</x:v>
+        <x:v>6300</x:v>
       </x:c>
     </x:row>
     <x:row r="485" spans="1:7">
@@ -13277,22 +13280,22 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="B485" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C485" s="1">
-        <x:v>2000</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D485" s="1">
-        <x:v>0</x:v>
+        <x:v>173232</x:v>
       </x:c>
       <x:c r="E485" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F485" s="1">
-        <x:v>1500</x:v>
+        <x:v>164830</x:v>
       </x:c>
       <x:c r="G485" s="1">
-        <x:v>3500</x:v>
+        <x:v>342062</x:v>
       </x:c>
     </x:row>
     <x:row r="486" spans="1:7">
@@ -13300,10 +13303,10 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C486" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D486" s="1">
         <x:v>0</x:v>
@@ -13312,10 +13315,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F486" s="1">
-        <x:v>83885</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G486" s="1">
-        <x:v>83885</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="487" spans="1:7">
@@ -13323,7 +13326,7 @@
         <x:v>541</x:v>
       </x:c>
       <x:c r="B487" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C487" s="1">
         <x:v>0</x:v>
@@ -13335,10 +13338,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F487" s="1">
-        <x:v>17300</x:v>
+        <x:v>83885</x:v>
       </x:c>
       <x:c r="G487" s="1">
-        <x:v>17300</x:v>
+        <x:v>83885</x:v>
       </x:c>
     </x:row>
     <x:row r="488" spans="1:7">
@@ -13346,7 +13349,7 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="B488" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C488" s="1">
         <x:v>0</x:v>
@@ -13358,10 +13361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F488" s="1">
-        <x:v>7800</x:v>
+        <x:v>17300</x:v>
       </x:c>
       <x:c r="G488" s="1">
-        <x:v>7800</x:v>
+        <x:v>17300</x:v>
       </x:c>
     </x:row>
     <x:row r="489" spans="1:7">
@@ -13369,7 +13372,7 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="B489" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C489" s="1">
         <x:v>0</x:v>
@@ -13381,10 +13384,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F489" s="1">
-        <x:v>5800</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="G489" s="1">
-        <x:v>5800</x:v>
+        <x:v>7800</x:v>
       </x:c>
     </x:row>
     <x:row r="490" spans="1:7">
@@ -13392,7 +13395,7 @@
         <x:v>544</x:v>
       </x:c>
       <x:c r="B490" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C490" s="1">
         <x:v>0</x:v>
@@ -13404,10 +13407,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F490" s="1">
-        <x:v>5000</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G490" s="1">
-        <x:v>5000</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="491" spans="1:7">
@@ -13415,22 +13418,22 @@
         <x:v>545</x:v>
       </x:c>
       <x:c r="B491" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C491" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D491" s="1">
-        <x:v>11761767</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E491" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F491" s="1">
-        <x:v>6933</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G491" s="1">
-        <x:v>11768700</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="492" spans="1:7">
@@ -13438,22 +13441,22 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="B492" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C492" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D492" s="1">
-        <x:v>0</x:v>
+        <x:v>11761767</x:v>
       </x:c>
       <x:c r="E492" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F492" s="1">
-        <x:v>2000</x:v>
+        <x:v>6933</x:v>
       </x:c>
       <x:c r="G492" s="1">
-        <x:v>2000</x:v>
+        <x:v>11768700</x:v>
       </x:c>
     </x:row>
     <x:row r="493" spans="1:7">
@@ -13461,10 +13464,10 @@
         <x:v>547</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C493" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D493" s="1">
         <x:v>0</x:v>
@@ -13473,10 +13476,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F493" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G493" s="1">
-        <x:v>1000</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="494" spans="1:7">
@@ -13484,10 +13487,10 @@
         <x:v>548</x:v>
       </x:c>
       <x:c r="B494" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C494" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D494" s="1">
         <x:v>0</x:v>
@@ -13496,10 +13499,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F494" s="1">
-        <x:v>8500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G494" s="1">
-        <x:v>8500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="495" spans="1:7">
@@ -13507,7 +13510,7 @@
         <x:v>549</x:v>
       </x:c>
       <x:c r="B495" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C495" s="1">
         <x:v>0</x:v>
@@ -13519,10 +13522,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F495" s="1">
-        <x:v>14533</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G495" s="1">
-        <x:v>14533</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="496" spans="1:7">
@@ -13530,7 +13533,7 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C496" s="1">
         <x:v>0</x:v>
@@ -13542,10 +13545,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F496" s="1">
-        <x:v>6600</x:v>
+        <x:v>14533</x:v>
       </x:c>
       <x:c r="G496" s="1">
-        <x:v>6600</x:v>
+        <x:v>14533</x:v>
       </x:c>
     </x:row>
     <x:row r="497" spans="1:7">
@@ -13553,7 +13556,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B497" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C497" s="1">
         <x:v>0</x:v>
@@ -13565,10 +13568,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F497" s="1">
-        <x:v>36100</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G497" s="1">
-        <x:v>36100</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="498" spans="1:7">
@@ -13576,7 +13579,7 @@
         <x:v>552</x:v>
       </x:c>
       <x:c r="B498" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C498" s="1">
         <x:v>0</x:v>
@@ -13588,10 +13591,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F498" s="1">
-        <x:v>1000</x:v>
+        <x:v>36100</x:v>
       </x:c>
       <x:c r="G498" s="1">
-        <x:v>1000</x:v>
+        <x:v>36100</x:v>
       </x:c>
     </x:row>
     <x:row r="499" spans="1:7">
@@ -13599,10 +13602,10 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B499" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C499" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D499" s="1">
         <x:v>0</x:v>
@@ -13611,10 +13614,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F499" s="1">
-        <x:v>7500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G499" s="1">
-        <x:v>10500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="500" spans="1:7">
@@ -13622,10 +13625,10 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="B500" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C500" s="1">
-        <x:v>1000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D500" s="1">
         <x:v>0</x:v>
@@ -13634,10 +13637,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F500" s="1">
-        <x:v>6632</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="G500" s="1">
-        <x:v>7632</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="501" spans="1:7">
@@ -13645,10 +13648,10 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B501" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C501" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D501" s="1">
         <x:v>0</x:v>
@@ -13657,10 +13660,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F501" s="1">
-        <x:v>5800</x:v>
+        <x:v>6632</x:v>
       </x:c>
       <x:c r="G501" s="1">
-        <x:v>5800</x:v>
+        <x:v>7632</x:v>
       </x:c>
     </x:row>
     <x:row r="502" spans="1:7">
@@ -13668,7 +13671,7 @@
         <x:v>556</x:v>
       </x:c>
       <x:c r="B502" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C502" s="1">
         <x:v>0</x:v>
@@ -13680,10 +13683,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F502" s="1">
-        <x:v>1000</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G502" s="1">
-        <x:v>1000</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="503" spans="1:7">
@@ -13691,22 +13694,22 @@
         <x:v>557</x:v>
       </x:c>
       <x:c r="B503" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C503" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D503" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E503" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F503" s="1">
-        <x:v>8600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G503" s="1">
-        <x:v>901452</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="504" spans="1:7">
@@ -13714,22 +13717,22 @@
         <x:v>558</x:v>
       </x:c>
       <x:c r="B504" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C504" s="1">
-        <x:v>1000</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D504" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E504" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F504" s="1">
-        <x:v>16700</x:v>
+        <x:v>8600</x:v>
       </x:c>
       <x:c r="G504" s="1">
-        <x:v>17700</x:v>
+        <x:v>901452</x:v>
       </x:c>
     </x:row>
     <x:row r="505" spans="1:7">
@@ -13737,22 +13740,22 @@
         <x:v>559</x:v>
       </x:c>
       <x:c r="B505" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C505" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D505" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E505" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F505" s="1">
-        <x:v>0</x:v>
+        <x:v>16700</x:v>
       </x:c>
       <x:c r="G505" s="1">
-        <x:v>1012792</x:v>
+        <x:v>17700</x:v>
       </x:c>
     </x:row>
     <x:row r="506" spans="1:7">
@@ -13760,22 +13763,22 @@
         <x:v>560</x:v>
       </x:c>
       <x:c r="B506" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C506" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D506" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E506" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F506" s="1">
-        <x:v>5600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G506" s="1">
-        <x:v>5600</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="507" spans="1:7">
@@ -13783,7 +13786,7 @@
         <x:v>561</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C507" s="1">
         <x:v>0</x:v>
@@ -13795,10 +13798,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F507" s="1">
-        <x:v>32600</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G507" s="1">
-        <x:v>32600</x:v>
+        <x:v>5600</x:v>
       </x:c>
     </x:row>
     <x:row r="508" spans="1:7">
@@ -13806,7 +13809,7 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B508" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C508" s="1">
         <x:v>0</x:v>
@@ -13818,10 +13821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F508" s="1">
-        <x:v>1000</x:v>
+        <x:v>32600</x:v>
       </x:c>
       <x:c r="G508" s="1">
-        <x:v>1000</x:v>
+        <x:v>32600</x:v>
       </x:c>
     </x:row>
     <x:row r="509" spans="1:7">
@@ -13829,10 +13832,10 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C509" s="1">
-        <x:v>9000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D509" s="1">
         <x:v>0</x:v>
@@ -13841,10 +13844,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F509" s="1">
-        <x:v>35900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G509" s="1">
-        <x:v>44900</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="510" spans="1:7">
@@ -13852,10 +13855,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="B510" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C510" s="1">
-        <x:v>0</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="D510" s="1">
         <x:v>0</x:v>
@@ -13864,10 +13867,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F510" s="1">
-        <x:v>1012</x:v>
+        <x:v>35900</x:v>
       </x:c>
       <x:c r="G510" s="1">
-        <x:v>1012</x:v>
+        <x:v>44900</x:v>
       </x:c>
     </x:row>
     <x:row r="511" spans="1:7">
@@ -13875,7 +13878,7 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C511" s="1">
         <x:v>0</x:v>
@@ -13887,18 +13890,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F511" s="1">
-        <x:v>485</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="G511" s="1">
-        <x:v>485</x:v>
+        <x:v>1012</x:v>
       </x:c>
     </x:row>
     <x:row r="512" spans="1:7">
       <x:c r="A512" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B512" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C512" s="1">
         <x:v>0</x:v>
@@ -13907,13 +13910,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E512" s="1">
-        <x:v>6119745</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F512" s="1">
-        <x:v>0</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="G512" s="1">
-        <x:v>0</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="513" spans="1:7">
@@ -13921,22 +13924,22 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C513" s="1">
-        <x:v>2900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D513" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E513" s="1">
-        <x:v>0</x:v>
+        <x:v>6119745</x:v>
       </x:c>
       <x:c r="F513" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G513" s="1">
-        <x:v>6200</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="514" spans="1:7">
@@ -13947,7 +13950,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C514" s="1">
-        <x:v>0</x:v>
+        <x:v>2900</x:v>
       </x:c>
       <x:c r="D514" s="1">
         <x:v>0</x:v>
@@ -13956,10 +13959,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F514" s="1">
-        <x:v>13200</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G514" s="1">
-        <x:v>13200</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="515" spans="1:7">
@@ -13967,7 +13970,7 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="B515" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C515" s="1">
         <x:v>0</x:v>
@@ -13979,10 +13982,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F515" s="1">
-        <x:v>18000</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G515" s="1">
-        <x:v>18000</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="516" spans="1:7">
@@ -13990,7 +13993,7 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B516" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C516" s="1">
         <x:v>0</x:v>
@@ -14002,10 +14005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F516" s="1">
-        <x:v>14000</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="G516" s="1">
-        <x:v>14000</x:v>
+        <x:v>18000</x:v>
       </x:c>
     </x:row>
     <x:row r="517" spans="1:7">
@@ -14013,10 +14016,10 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="B517" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C517" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D517" s="1">
         <x:v>0</x:v>
@@ -14025,10 +14028,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F517" s="1">
-        <x:v>750</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G517" s="1">
-        <x:v>1750</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="518" spans="1:7">
@@ -14036,10 +14039,10 @@
         <x:v>571</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C518" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D518" s="1">
         <x:v>0</x:v>
@@ -14048,10 +14051,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F518" s="1">
-        <x:v>9900</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G518" s="1">
-        <x:v>9900</x:v>
+        <x:v>1750</x:v>
       </x:c>
     </x:row>
     <x:row r="519" spans="1:7">
@@ -14059,7 +14062,7 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="B519" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C519" s="1">
         <x:v>0</x:v>
@@ -14071,10 +14074,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F519" s="1">
-        <x:v>11799</x:v>
+        <x:v>9900</x:v>
       </x:c>
       <x:c r="G519" s="1">
-        <x:v>11799</x:v>
+        <x:v>9900</x:v>
       </x:c>
     </x:row>
     <x:row r="520" spans="1:7">
@@ -14082,7 +14085,7 @@
         <x:v>573</x:v>
       </x:c>
       <x:c r="B520" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C520" s="1">
         <x:v>0</x:v>
@@ -14094,10 +14097,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F520" s="1">
-        <x:v>16500</x:v>
+        <x:v>11799</x:v>
       </x:c>
       <x:c r="G520" s="1">
-        <x:v>16500</x:v>
+        <x:v>11799</x:v>
       </x:c>
     </x:row>
     <x:row r="521" spans="1:7">
@@ -14105,7 +14108,7 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="B521" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C521" s="1">
         <x:v>0</x:v>
@@ -14117,10 +14120,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F521" s="1">
-        <x:v>200</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G521" s="1">
-        <x:v>200</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="522" spans="1:7">
@@ -14128,10 +14131,10 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C522" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D522" s="1">
         <x:v>0</x:v>
@@ -14140,10 +14143,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F522" s="1">
-        <x:v>116400</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G522" s="1">
-        <x:v>122200</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="523" spans="1:7">
@@ -14151,10 +14154,10 @@
         <x:v>576</x:v>
       </x:c>
       <x:c r="B523" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C523" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="D523" s="1">
         <x:v>0</x:v>
@@ -14163,10 +14166,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F523" s="1">
-        <x:v>218</x:v>
+        <x:v>116400</x:v>
       </x:c>
       <x:c r="G523" s="1">
-        <x:v>218</x:v>
+        <x:v>122200</x:v>
       </x:c>
     </x:row>
     <x:row r="524" spans="1:7">
@@ -14174,7 +14177,7 @@
         <x:v>577</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C524" s="1">
         <x:v>0</x:v>
@@ -14186,10 +14189,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F524" s="1">
-        <x:v>35800</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>35800</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -14197,7 +14200,7 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C525" s="1">
         <x:v>0</x:v>
@@ -14209,10 +14212,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F525" s="1">
-        <x:v>3200</x:v>
+        <x:v>35800</x:v>
       </x:c>
       <x:c r="G525" s="1">
-        <x:v>3200</x:v>
+        <x:v>35800</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:7">
@@ -14220,21 +14223,44 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C526" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D526" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E526" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F526" s="1">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="G526" s="1">
+        <x:v>3200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" spans="1:7">
+      <x:c r="A527" s="1" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="B527" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="C526" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D526" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E526" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F526" s="1">
+      <x:c r="C527" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D527" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E527" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F527" s="1">
         <x:v>14333</x:v>
       </x:c>
-      <x:c r="G526" s="1">
+      <x:c r="G527" s="1">
         <x:v>14333</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -2925,8 +2925,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G888" totalsRowShown="0">
-  <x:autoFilter ref="A1:G888"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G889" totalsRowShown="0">
+  <x:autoFilter ref="A1:G889"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -3228,7 +3228,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G888"/>
+  <x:dimension ref="A1:G889"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3856,10 +3856,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>0</x:v>
+        <x:v>58155</x:v>
       </x:c>
       <x:c r="G27" s="1">
-        <x:v>1050</x:v>
+        <x:v>59205</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
@@ -3879,10 +3879,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>58155</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G28" s="1">
-        <x:v>6078139</x:v>
+        <x:v>6019984</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
@@ -5190,10 +5190,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>0</x:v>
+        <x:v>11850</x:v>
       </x:c>
       <x:c r="G85" s="1">
-        <x:v>2050</x:v>
+        <x:v>13900</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
@@ -5213,10 +5213,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>11850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G86" s="1">
-        <x:v>13900</x:v>
+        <x:v>2050</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
@@ -9882,10 +9882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F289" s="1">
-        <x:v>140900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G289" s="1">
-        <x:v>150950</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="290" spans="1:7">
@@ -9905,10 +9905,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F290" s="1">
-        <x:v>0</x:v>
+        <x:v>140900</x:v>
       </x:c>
       <x:c r="G290" s="1">
-        <x:v>10050</x:v>
+        <x:v>150950</x:v>
       </x:c>
     </x:row>
     <x:row r="291" spans="1:7">
@@ -14758,10 +14758,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F501" s="1">
-        <x:v>0</x:v>
+        <x:v>32950</x:v>
       </x:c>
       <x:c r="G501" s="1">
-        <x:v>50</x:v>
+        <x:v>33000</x:v>
       </x:c>
     </x:row>
     <x:row r="502" spans="1:7">
@@ -14781,10 +14781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F502" s="1">
-        <x:v>32950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G502" s="1">
-        <x:v>33000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="503" spans="1:7">
@@ -15126,10 +15126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F517" s="1">
-        <x:v>0</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="G517" s="1">
-        <x:v>50</x:v>
+        <x:v>1765</x:v>
       </x:c>
     </x:row>
     <x:row r="518" spans="1:7">
@@ -15149,10 +15149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F518" s="1">
-        <x:v>1715</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G518" s="1">
-        <x:v>1765</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="519" spans="1:7">
@@ -19358,21 +19358,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>12250</x:v>
+        <x:v>8550</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>12300</x:v>
+        <x:v>8600</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
       <x:c r="A702" s="1" t="s">
-        <x:v>761</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C702" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D702" s="1">
         <x:v>0</x:v>
@@ -19381,21 +19381,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F702" s="1">
-        <x:v>0</x:v>
+        <x:v>3700</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>50</x:v>
+        <x:v>3700</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
       <x:c r="A703" s="1" t="s">
-        <x:v>762</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C703" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D703" s="1">
         <x:v>0</x:v>
@@ -19404,21 +19404,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F703" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
       <x:c r="A704" s="1" t="s">
-        <x:v>763</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C704" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D704" s="1">
         <x:v>0</x:v>
@@ -19427,18 +19427,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
       <x:c r="A705" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C705" s="1">
         <x:v>50</x:v>
@@ -19458,10 +19458,10 @@
     </x:row>
     <x:row r="706" spans="1:7">
       <x:c r="A706" s="1" t="s">
-        <x:v>765</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C706" s="1">
         <x:v>50</x:v>
@@ -19481,59 +19481,59 @@
     </x:row>
     <x:row r="707" spans="1:7">
       <x:c r="A707" s="1" t="s">
-        <x:v>766</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D707" s="1">
-        <x:v>5962980</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E707" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>18200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>5982180</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
       <x:c r="A708" s="1" t="s">
-        <x:v>767</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D708" s="1">
-        <x:v>0</x:v>
+        <x:v>5962980</x:v>
       </x:c>
       <x:c r="E708" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>163800</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>163800</x:v>
+        <x:v>5982180</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
       <x:c r="A709" s="1" t="s">
-        <x:v>768</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D709" s="1">
         <x:v>0</x:v>
@@ -19542,18 +19542,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>24200</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>24250</x:v>
+        <x:v>163800</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
       <x:c r="A710" s="1" t="s">
-        <x:v>769</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>770</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C710" s="1">
         <x:v>50</x:v>
@@ -19565,21 +19565,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>0</x:v>
+        <x:v>24200</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>50</x:v>
+        <x:v>24250</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
       <x:c r="A711" s="1" t="s">
-        <x:v>771</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="C711" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D711" s="1">
         <x:v>0</x:v>
@@ -19588,18 +19588,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F711" s="1">
-        <x:v>14900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>14900</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
       <x:c r="A712" s="1" t="s">
-        <x:v>772</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C712" s="1">
         <x:v>0</x:v>
@@ -19611,18 +19611,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>1000</x:v>
+        <x:v>14900</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>1000</x:v>
+        <x:v>14900</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
       <x:c r="A713" s="1" t="s">
-        <x:v>773</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C713" s="1">
         <x:v>0</x:v>
@@ -19642,13 +19642,13 @@
     </x:row>
     <x:row r="714" spans="1:7">
       <x:c r="A714" s="1" t="s">
-        <x:v>774</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>775</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D714" s="1">
         <x:v>0</x:v>
@@ -19657,18 +19657,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
       <x:c r="A715" s="1" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C715" s="1">
         <x:v>50</x:v>
@@ -19688,10 +19688,10 @@
     </x:row>
     <x:row r="716" spans="1:7">
       <x:c r="A716" s="1" t="s">
-        <x:v>777</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>531</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C716" s="1">
         <x:v>50</x:v>
@@ -19703,10 +19703,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>510</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>560</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19714,10 +19714,10 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D717" s="1">
         <x:v>0</x:v>
@@ -19726,21 +19726,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>2079</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>2079</x:v>
+        <x:v>560</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
       <x:c r="A718" s="1" t="s">
-        <x:v>778</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C718" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D718" s="1">
         <x:v>0</x:v>
@@ -19749,18 +19749,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F718" s="1">
-        <x:v>0</x:v>
+        <x:v>2079</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>50</x:v>
+        <x:v>2079</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
       <x:c r="A719" s="1" t="s">
-        <x:v>779</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C719" s="1">
         <x:v>50</x:v>
@@ -19780,13 +19780,13 @@
     </x:row>
     <x:row r="720" spans="1:7">
       <x:c r="A720" s="1" t="s">
-        <x:v>780</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D720" s="1">
         <x:v>0</x:v>
@@ -19795,21 +19795,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F720" s="1">
-        <x:v>130400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>132950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
       <x:c r="A721" s="1" t="s">
-        <x:v>781</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C721" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D721" s="1">
         <x:v>0</x:v>
@@ -19818,18 +19818,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F721" s="1">
-        <x:v>0</x:v>
+        <x:v>130400</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>50</x:v>
+        <x:v>132950</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
       <x:c r="A722" s="1" t="s">
-        <x:v>782</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C722" s="1">
         <x:v>50</x:v>
@@ -19849,13 +19849,13 @@
     </x:row>
     <x:row r="723" spans="1:7">
       <x:c r="A723" s="1" t="s">
-        <x:v>783</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D723" s="1">
         <x:v>0</x:v>
@@ -19864,21 +19864,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F723" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
       <x:c r="A724" s="1" t="s">
-        <x:v>784</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C724" s="1">
-        <x:v>100</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D724" s="1">
         <x:v>0</x:v>
@@ -19887,21 +19887,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F724" s="1">
-        <x:v>92500</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>92600</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
       <x:c r="A725" s="1" t="s">
-        <x:v>785</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D725" s="1">
         <x:v>0</x:v>
@@ -19910,21 +19910,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F725" s="1">
-        <x:v>1000</x:v>
+        <x:v>92500</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>1000</x:v>
+        <x:v>92600</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
       <x:c r="A726" s="1" t="s">
-        <x:v>786</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="C726" s="1">
-        <x:v>2050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D726" s="1">
         <x:v>0</x:v>
@@ -19933,21 +19933,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F726" s="1">
-        <x:v>8500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>10550</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
       <x:c r="A727" s="1" t="s">
-        <x:v>787</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D727" s="1">
         <x:v>0</x:v>
@@ -19956,18 +19956,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F727" s="1">
-        <x:v>25600</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>25600</x:v>
+        <x:v>10550</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
       <x:c r="A728" s="1" t="s">
-        <x:v>788</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C728" s="1">
         <x:v>0</x:v>
@@ -19979,18 +19979,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>6634</x:v>
+        <x:v>25600</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>6634</x:v>
+        <x:v>25600</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
       <x:c r="A729" s="1" t="s">
-        <x:v>789</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C729" s="1">
         <x:v>0</x:v>
@@ -20002,21 +20002,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F729" s="1">
-        <x:v>77</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>77</x:v>
+        <x:v>6634</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">
       <x:c r="A730" s="1" t="s">
-        <x:v>790</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C730" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D730" s="1">
         <x:v>0</x:v>
@@ -20025,18 +20025,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F730" s="1">
-        <x:v>0</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>50</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
       <x:c r="A731" s="1" t="s">
-        <x:v>791</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C731" s="1">
         <x:v>50</x:v>
@@ -20048,21 +20048,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F731" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
       <x:c r="A732" s="1" t="s">
-        <x:v>792</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C732" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D732" s="1">
         <x:v>0</x:v>
@@ -20071,21 +20071,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F732" s="1">
-        <x:v>52400</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>55350</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
       <x:c r="A733" s="1" t="s">
-        <x:v>793</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C733" s="1">
-        <x:v>2550</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D733" s="1">
         <x:v>0</x:v>
@@ -20094,21 +20094,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F733" s="1">
-        <x:v>333</x:v>
+        <x:v>52400</x:v>
       </x:c>
       <x:c r="G733" s="1">
-        <x:v>2883</x:v>
+        <x:v>55350</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:7">
       <x:c r="A734" s="1" t="s">
-        <x:v>794</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C734" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D734" s="1">
         <x:v>0</x:v>
@@ -20117,15 +20117,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F734" s="1">
-        <x:v>0</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G734" s="1">
-        <x:v>50</x:v>
+        <x:v>2883</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:7">
       <x:c r="A735" s="1" t="s">
-        <x:v>795</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
         <x:v>18</x:v>
@@ -20148,13 +20148,13 @@
     </x:row>
     <x:row r="736" spans="1:7">
       <x:c r="A736" s="1" t="s">
-        <x:v>796</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -20163,21 +20163,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>31800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>34350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
       <x:c r="A737" s="1" t="s">
-        <x:v>797</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C737" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D737" s="1">
         <x:v>0</x:v>
@@ -20186,21 +20186,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F737" s="1">
-        <x:v>0</x:v>
+        <x:v>31800</x:v>
       </x:c>
       <x:c r="G737" s="1">
-        <x:v>50</x:v>
+        <x:v>34350</x:v>
       </x:c>
     </x:row>
     <x:row r="738" spans="1:7">
       <x:c r="A738" s="1" t="s">
-        <x:v>798</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C738" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D738" s="1">
         <x:v>0</x:v>
@@ -20209,21 +20209,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F738" s="1">
-        <x:v>84000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>88550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
       <x:c r="A739" s="1" t="s">
-        <x:v>799</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C739" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D739" s="1">
         <x:v>0</x:v>
@@ -20232,21 +20232,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F739" s="1">
-        <x:v>2600</x:v>
+        <x:v>84000</x:v>
       </x:c>
       <x:c r="G739" s="1">
-        <x:v>2600</x:v>
+        <x:v>88550</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:7">
       <x:c r="A740" s="1" t="s">
-        <x:v>800</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D740" s="1">
         <x:v>0</x:v>
@@ -20255,18 +20255,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F740" s="1">
-        <x:v>0</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>50</x:v>
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
       <x:c r="A741" s="1" t="s">
-        <x:v>801</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C741" s="1">
         <x:v>50</x:v>
@@ -20286,10 +20286,10 @@
     </x:row>
     <x:row r="742" spans="1:7">
       <x:c r="A742" s="1" t="s">
-        <x:v>802</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C742" s="1">
         <x:v>50</x:v>
@@ -20309,10 +20309,10 @@
     </x:row>
     <x:row r="743" spans="1:7">
       <x:c r="A743" s="1" t="s">
-        <x:v>803</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C743" s="1">
         <x:v>50</x:v>
@@ -20332,10 +20332,10 @@
     </x:row>
     <x:row r="744" spans="1:7">
       <x:c r="A744" s="1" t="s">
-        <x:v>804</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C744" s="1">
         <x:v>50</x:v>
@@ -20355,13 +20355,13 @@
     </x:row>
     <x:row r="745" spans="1:7">
       <x:c r="A745" s="1" t="s">
-        <x:v>805</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C745" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D745" s="1">
         <x:v>0</x:v>
@@ -20370,21 +20370,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F745" s="1">
-        <x:v>29420</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G745" s="1">
-        <x:v>34420</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:7">
       <x:c r="A746" s="1" t="s">
-        <x:v>806</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D746" s="1">
         <x:v>0</x:v>
@@ -20393,21 +20393,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>0</x:v>
+        <x:v>29420</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>50</x:v>
+        <x:v>34420</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
       <x:c r="A747" s="1" t="s">
-        <x:v>807</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D747" s="1">
         <x:v>0</x:v>
@@ -20419,18 +20419,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">
       <x:c r="A748" s="1" t="s">
-        <x:v>808</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>1050</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D748" s="1">
         <x:v>0</x:v>
@@ -20439,21 +20439,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F748" s="1">
-        <x:v>10800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>11850</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
       <x:c r="A749" s="1" t="s">
-        <x:v>809</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C749" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D749" s="1">
         <x:v>0</x:v>
@@ -20462,21 +20462,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F749" s="1">
-        <x:v>2700</x:v>
+        <x:v>10800</x:v>
       </x:c>
       <x:c r="G749" s="1">
-        <x:v>2750</x:v>
+        <x:v>11850</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:7">
       <x:c r="A750" s="1" t="s">
-        <x:v>810</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20485,21 +20485,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F750" s="1">
-        <x:v>3300</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>3300</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
       <x:c r="A751" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20508,21 +20508,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F751" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>50</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
       <x:c r="A752" s="1" t="s">
-        <x:v>812</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20531,22 +20531,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>39500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>39600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
       <x:c r="A753" s="1" t="s">
-        <x:v>813</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C753" s="1">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C753" s="1">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
       </x:c>
@@ -20554,64 +20554,64 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>0</x:v>
+        <x:v>39500</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>50</x:v>
+        <x:v>39600</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
       <x:c r="A754" s="1" t="s">
-        <x:v>814</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C754" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D754" s="1">
-        <x:v>10046680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E754" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F754" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>10048730</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
       <x:c r="A755" s="1" t="s">
-        <x:v>815</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C755" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D755" s="1">
-        <x:v>0</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E755" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F755" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>50</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
       <x:c r="A756" s="1" t="s">
-        <x:v>816</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C756" s="1">
         <x:v>50</x:v>
@@ -20631,13 +20631,13 @@
     </x:row>
     <x:row r="757" spans="1:7">
       <x:c r="A757" s="1" t="s">
-        <x:v>817</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20646,21 +20646,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
       <x:c r="A758" s="1" t="s">
-        <x:v>818</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20669,21 +20669,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>5000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>5050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
       <x:c r="A759" s="1" t="s">
-        <x:v>819</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C759" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D759" s="1">
         <x:v>0</x:v>
@@ -20692,21 +20692,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F759" s="1">
-        <x:v>90966</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>97016</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
       <x:c r="A760" s="1" t="s">
-        <x:v>820</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C760" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D760" s="1">
         <x:v>0</x:v>
@@ -20715,18 +20715,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F760" s="1">
-        <x:v>0</x:v>
+        <x:v>90966</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>50</x:v>
+        <x:v>97016</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
       <x:c r="A761" s="1" t="s">
-        <x:v>821</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C761" s="1">
         <x:v>50</x:v>
@@ -20746,13 +20746,13 @@
     </x:row>
     <x:row r="762" spans="1:7">
       <x:c r="A762" s="1" t="s">
-        <x:v>822</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C762" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D762" s="1">
         <x:v>0</x:v>
@@ -20761,67 +20761,67 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F762" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">
       <x:c r="A763" s="1" t="s">
-        <x:v>823</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C763" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D763" s="1">
-        <x:v>817169</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E763" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F763" s="1">
-        <x:v>13234</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G763" s="1">
-        <x:v>832403</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="764" spans="1:7">
       <x:c r="A764" s="1" t="s">
-        <x:v>824</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C764" s="1">
-        <x:v>11050</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D764" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E764" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F764" s="1">
-        <x:v>45434</x:v>
+        <x:v>13234</x:v>
       </x:c>
       <x:c r="G764" s="1">
-        <x:v>56484</x:v>
+        <x:v>832403</x:v>
       </x:c>
     </x:row>
     <x:row r="765" spans="1:7">
       <x:c r="A765" s="1" t="s">
-        <x:v>825</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C765" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D765" s="1">
         <x:v>0</x:v>
@@ -20830,18 +20830,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F765" s="1">
-        <x:v>5800</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="G765" s="1">
-        <x:v>5850</x:v>
+        <x:v>56484</x:v>
       </x:c>
     </x:row>
     <x:row r="766" spans="1:7">
       <x:c r="A766" s="1" t="s">
-        <x:v>826</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C766" s="1">
         <x:v>50</x:v>
@@ -20853,18 +20853,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
       <x:c r="A767" s="1" t="s">
-        <x:v>827</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C767" s="1">
         <x:v>50</x:v>
@@ -20876,18 +20876,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F767" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G767" s="1">
-        <x:v>25050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:7">
       <x:c r="A768" s="1" t="s">
-        <x:v>828</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C768" s="1">
         <x:v>50</x:v>
@@ -20899,64 +20899,64 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>5800</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>5850</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
       <x:c r="A769" s="1" t="s">
-        <x:v>829</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C769" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D769" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E769" s="1">
-        <x:v>1531015</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F769" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G769" s="1">
-        <x:v>0</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:7">
       <x:c r="A770" s="1" t="s">
-        <x:v>830</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C770" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D770" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E770" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F770" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G770" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="771" spans="1:7">
       <x:c r="A771" s="1" t="s">
-        <x:v>831</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C771" s="1">
         <x:v>50</x:v>
@@ -20976,148 +20976,148 @@
     </x:row>
     <x:row r="772" spans="1:7">
       <x:c r="A772" s="1" t="s">
-        <x:v>832</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C772" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D772" s="1">
-        <x:v>5583432</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E772" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F772" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G772" s="1">
-        <x:v>5591032</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="773" spans="1:7">
       <x:c r="A773" s="1" t="s">
-        <x:v>833</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C773" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D773" s="1">
-        <x:v>0</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E773" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F773" s="1">
-        <x:v>27300</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G773" s="1">
-        <x:v>27350</x:v>
+        <x:v>5591032</x:v>
       </x:c>
     </x:row>
     <x:row r="774" spans="1:7">
       <x:c r="A774" s="1" t="s">
-        <x:v>834</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C774" s="1">
-        <x:v>18050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D774" s="1">
-        <x:v>764206</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E774" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F774" s="1">
-        <x:v>81382</x:v>
+        <x:v>27300</x:v>
       </x:c>
       <x:c r="G774" s="1">
-        <x:v>863638</x:v>
+        <x:v>27350</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:7">
       <x:c r="A775" s="1" t="s">
-        <x:v>835</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C775" s="1">
-        <x:v>0</x:v>
+        <x:v>18050</x:v>
       </x:c>
       <x:c r="D775" s="1">
-        <x:v>0</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="E775" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>2700</x:v>
+        <x:v>81382</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>2700</x:v>
+        <x:v>863638</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
       <x:c r="A776" s="1" t="s">
-        <x:v>836</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C776" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D776" s="1">
-        <x:v>1543316</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E776" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
       <x:c r="A777" s="1" t="s">
-        <x:v>837</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C777" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D777" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E777" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F777" s="1">
-        <x:v>14500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G777" s="1">
-        <x:v>14550</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="778" spans="1:7">
       <x:c r="A778" s="1" t="s">
-        <x:v>838</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C778" s="1">
         <x:v>50</x:v>
@@ -21129,18 +21129,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F778" s="1">
-        <x:v>5800</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>5850</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
       <x:c r="A779" s="1" t="s">
-        <x:v>839</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C779" s="1">
         <x:v>50</x:v>
@@ -21152,18 +21152,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F779" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G779" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="780" spans="1:7">
       <x:c r="A780" s="1" t="s">
-        <x:v>840</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C780" s="1">
         <x:v>50</x:v>
@@ -21183,33 +21183,33 @@
     </x:row>
     <x:row r="781" spans="1:7">
       <x:c r="A781" s="1" t="s">
-        <x:v>841</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C781" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D781" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E781" s="1">
-        <x:v>15154476</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F781" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
       <x:c r="A782" s="1" t="s">
-        <x:v>842</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="B782" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C782" s="1">
         <x:v>0</x:v>
@@ -21218,21 +21218,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E782" s="1">
-        <x:v>0</x:v>
+        <x:v>15154476</x:v>
       </x:c>
       <x:c r="F782" s="1">
-        <x:v>16800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G782" s="1">
-        <x:v>16800</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="783" spans="1:7">
       <x:c r="A783" s="1" t="s">
-        <x:v>843</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="B783" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C783" s="1">
         <x:v>0</x:v>
@@ -21244,102 +21244,102 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F783" s="1">
-        <x:v>2700</x:v>
+        <x:v>16800</x:v>
       </x:c>
       <x:c r="G783" s="1">
-        <x:v>2700</x:v>
+        <x:v>16800</x:v>
       </x:c>
     </x:row>
     <x:row r="784" spans="1:7">
       <x:c r="A784" s="1" t="s">
-        <x:v>844</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="B784" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C784" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D784" s="1">
-        <x:v>106947</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E784" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F784" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G784" s="1">
-        <x:v>106947</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="785" spans="1:7">
       <x:c r="A785" s="1" t="s">
-        <x:v>845</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="B785" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C785" s="1">
-        <x:v>10050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D785" s="1">
-        <x:v>0</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="E785" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F785" s="1">
-        <x:v>1945889</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G785" s="1">
-        <x:v>1955939</x:v>
+        <x:v>106947</x:v>
       </x:c>
     </x:row>
     <x:row r="786" spans="1:7">
       <x:c r="A786" s="1" t="s">
-        <x:v>846</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="B786" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C786" s="1">
-        <x:v>1050</x:v>
+        <x:v>10050</x:v>
       </x:c>
       <x:c r="D786" s="1">
-        <x:v>902176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E786" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F786" s="1">
-        <x:v>26650</x:v>
+        <x:v>1945889</x:v>
       </x:c>
       <x:c r="G786" s="1">
-        <x:v>929876</x:v>
+        <x:v>1955939</x:v>
       </x:c>
     </x:row>
     <x:row r="787" spans="1:7">
       <x:c r="A787" s="1" t="s">
-        <x:v>847</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="B787" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C787" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D787" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E787" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F787" s="1">
-        <x:v>26500</x:v>
+        <x:v>26650</x:v>
       </x:c>
       <x:c r="G787" s="1">
-        <x:v>26550</x:v>
+        <x:v>929876</x:v>
       </x:c>
     </x:row>
     <x:row r="788" spans="1:7">
@@ -21347,10 +21347,10 @@
         <x:v>847</x:v>
       </x:c>
       <x:c r="B788" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C788" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D788" s="1">
         <x:v>0</x:v>
@@ -21359,18 +21359,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F788" s="1">
-        <x:v>1800</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G788" s="1">
-        <x:v>1800</x:v>
+        <x:v>26550</x:v>
       </x:c>
     </x:row>
     <x:row r="789" spans="1:7">
       <x:c r="A789" s="1" t="s">
-        <x:v>848</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="B789" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C789" s="1">
         <x:v>0</x:v>
@@ -21382,21 +21382,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F789" s="1">
-        <x:v>1000</x:v>
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="G789" s="1">
-        <x:v>1000</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="790" spans="1:7">
       <x:c r="A790" s="1" t="s">
-        <x:v>849</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="B790" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C790" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D790" s="1">
         <x:v>0</x:v>
@@ -21405,21 +21405,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F790" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G790" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="791" spans="1:7">
       <x:c r="A791" s="1" t="s">
-        <x:v>850</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="B791" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C791" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D791" s="1">
         <x:v>0</x:v>
@@ -21428,18 +21428,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F791" s="1">
-        <x:v>10500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G791" s="1">
-        <x:v>10500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="792" spans="1:7">
       <x:c r="A792" s="1" t="s">
-        <x:v>851</x:v>
+        <x:v>850</x:v>
       </x:c>
       <x:c r="B792" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C792" s="1">
         <x:v>0</x:v>
@@ -21451,21 +21451,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F792" s="1">
-        <x:v>13200</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G792" s="1">
-        <x:v>13200</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="793" spans="1:7">
       <x:c r="A793" s="1" t="s">
-        <x:v>852</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="B793" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C793" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D793" s="1">
         <x:v>0</x:v>
@@ -21474,21 +21474,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F793" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G793" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="794" spans="1:7">
       <x:c r="A794" s="1" t="s">
-        <x:v>853</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="B794" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C794" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D794" s="1">
         <x:v>0</x:v>
@@ -21497,21 +21497,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F794" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G794" s="1">
-        <x:v>4300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="795" spans="1:7">
       <x:c r="A795" s="1" t="s">
-        <x:v>854</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="B795" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C795" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D795" s="1">
         <x:v>0</x:v>
@@ -21520,67 +21520,67 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F795" s="1">
-        <x:v>6600</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G795" s="1">
-        <x:v>6650</x:v>
+        <x:v>4300</x:v>
       </x:c>
     </x:row>
     <x:row r="796" spans="1:7">
       <x:c r="A796" s="1" t="s">
-        <x:v>855</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="B796" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C796" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D796" s="1">
-        <x:v>1010142</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E796" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F796" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G796" s="1">
-        <x:v>1010142</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="797" spans="1:7">
       <x:c r="A797" s="1" t="s">
-        <x:v>856</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="B797" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C797" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D797" s="1">
-        <x:v>0</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="E797" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F797" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G797" s="1">
-        <x:v>5000</x:v>
+        <x:v>1010142</x:v>
       </x:c>
     </x:row>
     <x:row r="798" spans="1:7">
       <x:c r="A798" s="1" t="s">
-        <x:v>857</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="B798" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C798" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D798" s="1">
         <x:v>0</x:v>
@@ -21589,21 +21589,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F798" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G798" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="799" spans="1:7">
       <x:c r="A799" s="1" t="s">
-        <x:v>858</x:v>
+        <x:v>857</x:v>
       </x:c>
       <x:c r="B799" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="C799" s="1">
-        <x:v>6550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D799" s="1">
         <x:v>0</x:v>
@@ -21612,21 +21612,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F799" s="1">
-        <x:v>39400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G799" s="1">
-        <x:v>45950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="800" spans="1:7">
       <x:c r="A800" s="1" t="s">
-        <x:v>859</x:v>
+        <x:v>858</x:v>
       </x:c>
       <x:c r="B800" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C800" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D800" s="1">
         <x:v>0</x:v>
@@ -21635,18 +21635,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F800" s="1">
-        <x:v>0</x:v>
+        <x:v>39400</x:v>
       </x:c>
       <x:c r="G800" s="1">
-        <x:v>50</x:v>
+        <x:v>45950</x:v>
       </x:c>
     </x:row>
     <x:row r="801" spans="1:7">
       <x:c r="A801" s="1" t="s">
-        <x:v>860</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="B801" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C801" s="1">
         <x:v>50</x:v>
@@ -21666,13 +21666,13 @@
     </x:row>
     <x:row r="802" spans="1:7">
       <x:c r="A802" s="1" t="s">
-        <x:v>861</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="B802" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C802" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D802" s="1">
         <x:v>0</x:v>
@@ -21681,21 +21681,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F802" s="1">
-        <x:v>20900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G802" s="1">
-        <x:v>24450</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="803" spans="1:7">
       <x:c r="A803" s="1" t="s">
-        <x:v>862</x:v>
+        <x:v>861</x:v>
       </x:c>
       <x:c r="B803" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C803" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D803" s="1">
         <x:v>0</x:v>
@@ -21704,21 +21704,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F803" s="1">
-        <x:v>5400</x:v>
+        <x:v>20900</x:v>
       </x:c>
       <x:c r="G803" s="1">
-        <x:v>5400</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="804" spans="1:7">
       <x:c r="A804" s="1" t="s">
-        <x:v>863</x:v>
+        <x:v>862</x:v>
       </x:c>
       <x:c r="B804" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C804" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D804" s="1">
         <x:v>0</x:v>
@@ -21727,21 +21727,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F804" s="1">
-        <x:v>0</x:v>
+        <x:v>5400</x:v>
       </x:c>
       <x:c r="G804" s="1">
-        <x:v>50</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="805" spans="1:7">
       <x:c r="A805" s="1" t="s">
-        <x:v>864</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="B805" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C805" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D805" s="1">
         <x:v>0</x:v>
@@ -21750,64 +21750,64 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F805" s="1">
-        <x:v>21433</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G805" s="1">
-        <x:v>24983</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="806" spans="1:7">
       <x:c r="A806" s="1" t="s">
-        <x:v>865</x:v>
+        <x:v>864</x:v>
       </x:c>
       <x:c r="B806" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C806" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D806" s="1">
-        <x:v>1860445</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E806" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F806" s="1">
-        <x:v>11600</x:v>
+        <x:v>21433</x:v>
       </x:c>
       <x:c r="G806" s="1">
-        <x:v>1872095</x:v>
+        <x:v>24983</x:v>
       </x:c>
     </x:row>
     <x:row r="807" spans="1:7">
       <x:c r="A807" s="1" t="s">
-        <x:v>866</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="B807" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C807" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D807" s="1">
-        <x:v>0</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="E807" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F807" s="1">
-        <x:v>0</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G807" s="1">
-        <x:v>50</x:v>
+        <x:v>1872095</x:v>
       </x:c>
     </x:row>
     <x:row r="808" spans="1:7">
       <x:c r="A808" s="1" t="s">
-        <x:v>867</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="B808" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C808" s="1">
         <x:v>50</x:v>
@@ -21819,18 +21819,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F808" s="1">
-        <x:v>16484</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G808" s="1">
-        <x:v>16534</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="809" spans="1:7">
       <x:c r="A809" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>867</x:v>
       </x:c>
       <x:c r="B809" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C809" s="1">
         <x:v>50</x:v>
@@ -21842,21 +21842,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F809" s="1">
-        <x:v>0</x:v>
+        <x:v>16484</x:v>
       </x:c>
       <x:c r="G809" s="1">
-        <x:v>50</x:v>
+        <x:v>16534</x:v>
       </x:c>
     </x:row>
     <x:row r="810" spans="1:7">
       <x:c r="A810" s="1" t="s">
-        <x:v>869</x:v>
+        <x:v>868</x:v>
       </x:c>
       <x:c r="B810" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C810" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D810" s="1">
         <x:v>0</x:v>
@@ -21865,21 +21865,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F810" s="1">
-        <x:v>6300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G810" s="1">
-        <x:v>6300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="811" spans="1:7">
       <x:c r="A811" s="1" t="s">
-        <x:v>870</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="B811" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C811" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D811" s="1">
         <x:v>0</x:v>
@@ -21888,18 +21888,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F811" s="1">
-        <x:v>0</x:v>
+        <x:v>6300</x:v>
       </x:c>
       <x:c r="G811" s="1">
-        <x:v>50</x:v>
+        <x:v>6300</x:v>
       </x:c>
     </x:row>
     <x:row r="812" spans="1:7">
       <x:c r="A812" s="1" t="s">
-        <x:v>871</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="B812" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C812" s="1">
         <x:v>50</x:v>
@@ -21911,18 +21911,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F812" s="1">
-        <x:v>11000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G812" s="1">
-        <x:v>11050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="813" spans="1:7">
       <x:c r="A813" s="1" t="s">
-        <x:v>872</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="B813" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C813" s="1">
         <x:v>50</x:v>
@@ -21934,18 +21934,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F813" s="1">
-        <x:v>0</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="G813" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
     </x:row>
     <x:row r="814" spans="1:7">
       <x:c r="A814" s="1" t="s">
-        <x:v>873</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="B814" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C814" s="1">
         <x:v>50</x:v>
@@ -21965,59 +21965,59 @@
     </x:row>
     <x:row r="815" spans="1:7">
       <x:c r="A815" s="1" t="s">
-        <x:v>874</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="B815" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C815" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D815" s="1">
-        <x:v>173232</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E815" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F815" s="1">
-        <x:v>167130</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G815" s="1">
-        <x:v>356862</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="816" spans="1:7">
       <x:c r="A816" s="1" t="s">
-        <x:v>875</x:v>
+        <x:v>874</x:v>
       </x:c>
       <x:c r="B816" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C816" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D816" s="1">
-        <x:v>0</x:v>
+        <x:v>173232</x:v>
       </x:c>
       <x:c r="E816" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F816" s="1">
-        <x:v>1000</x:v>
+        <x:v>167130</x:v>
       </x:c>
       <x:c r="G816" s="1">
-        <x:v>1000</x:v>
+        <x:v>356862</x:v>
       </x:c>
     </x:row>
     <x:row r="817" spans="1:7">
       <x:c r="A817" s="1" t="s">
-        <x:v>876</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="B817" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C817" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D817" s="1">
         <x:v>0</x:v>
@@ -22026,21 +22026,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F817" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G817" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="818" spans="1:7">
       <x:c r="A818" s="1" t="s">
-        <x:v>877</x:v>
+        <x:v>876</x:v>
       </x:c>
       <x:c r="B818" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C818" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D818" s="1">
         <x:v>0</x:v>
@@ -22049,21 +22049,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F818" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G818" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="819" spans="1:7">
       <x:c r="A819" s="1" t="s">
-        <x:v>878</x:v>
+        <x:v>877</x:v>
       </x:c>
       <x:c r="B819" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C819" s="1">
-        <x:v>100</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D819" s="1">
         <x:v>0</x:v>
@@ -22072,67 +22072,67 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F819" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G819" s="1">
-        <x:v>100</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="820" spans="1:7">
       <x:c r="A820" s="1" t="s">
-        <x:v>879</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="B820" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C820" s="1">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D820" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E820" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F820" s="1">
-        <x:v>65132</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G820" s="1">
-        <x:v>105132</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="821" spans="1:7">
       <x:c r="A821" s="1" t="s">
-        <x:v>880</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="B821" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C821" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D821" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E821" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F821" s="1">
-        <x:v>13800</x:v>
+        <x:v>65132</x:v>
       </x:c>
       <x:c r="G821" s="1">
-        <x:v>14800</x:v>
+        <x:v>105132</x:v>
       </x:c>
     </x:row>
     <x:row r="822" spans="1:7">
       <x:c r="A822" s="1" t="s">
-        <x:v>881</x:v>
+        <x:v>880</x:v>
       </x:c>
       <x:c r="B822" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C822" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D822" s="1">
         <x:v>0</x:v>
@@ -22141,21 +22141,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F822" s="1">
-        <x:v>0</x:v>
+        <x:v>13800</x:v>
       </x:c>
       <x:c r="G822" s="1">
-        <x:v>50</x:v>
+        <x:v>14800</x:v>
       </x:c>
     </x:row>
     <x:row r="823" spans="1:7">
       <x:c r="A823" s="1" t="s">
-        <x:v>882</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="B823" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C823" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D823" s="1">
         <x:v>0</x:v>
@@ -22164,21 +22164,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F823" s="1">
-        <x:v>7800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G823" s="1">
-        <x:v>7800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="824" spans="1:7">
       <x:c r="A824" s="1" t="s">
-        <x:v>883</x:v>
+        <x:v>882</x:v>
       </x:c>
       <x:c r="B824" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C824" s="1">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D824" s="1">
         <x:v>0</x:v>
@@ -22187,21 +22187,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F824" s="1">
-        <x:v>0</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="G824" s="1">
-        <x:v>100</x:v>
+        <x:v>7800</x:v>
       </x:c>
     </x:row>
     <x:row r="825" spans="1:7">
       <x:c r="A825" s="1" t="s">
-        <x:v>884</x:v>
+        <x:v>883</x:v>
       </x:c>
       <x:c r="B825" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C825" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D825" s="1">
         <x:v>0</x:v>
@@ -22210,18 +22210,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F825" s="1">
-        <x:v>6300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G825" s="1">
-        <x:v>6350</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="826" spans="1:7">
       <x:c r="A826" s="1" t="s">
-        <x:v>885</x:v>
+        <x:v>884</x:v>
       </x:c>
       <x:c r="B826" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C826" s="1">
         <x:v>50</x:v>
@@ -22233,67 +22233,67 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F826" s="1">
-        <x:v>5000</x:v>
+        <x:v>6300</x:v>
       </x:c>
       <x:c r="G826" s="1">
-        <x:v>5050</x:v>
+        <x:v>6350</x:v>
       </x:c>
     </x:row>
     <x:row r="827" spans="1:7">
       <x:c r="A827" s="1" t="s">
-        <x:v>886</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="B827" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C827" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D827" s="1">
-        <x:v>11761767</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E827" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F827" s="1">
-        <x:v>6933</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G827" s="1">
-        <x:v>11768700</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="828" spans="1:7">
       <x:c r="A828" s="1" t="s">
-        <x:v>887</x:v>
+        <x:v>886</x:v>
       </x:c>
       <x:c r="B828" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C828" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D828" s="1">
-        <x:v>0</x:v>
+        <x:v>11761767</x:v>
       </x:c>
       <x:c r="E828" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F828" s="1">
-        <x:v>2000</x:v>
+        <x:v>6933</x:v>
       </x:c>
       <x:c r="G828" s="1">
-        <x:v>2050</x:v>
+        <x:v>11768700</x:v>
       </x:c>
     </x:row>
     <x:row r="829" spans="1:7">
       <x:c r="A829" s="1" t="s">
-        <x:v>888</x:v>
+        <x:v>887</x:v>
       </x:c>
       <x:c r="B829" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C829" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D829" s="1">
         <x:v>0</x:v>
@@ -22302,21 +22302,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F829" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G829" s="1">
-        <x:v>1000</x:v>
+        <x:v>2050</x:v>
       </x:c>
     </x:row>
     <x:row r="830" spans="1:7">
       <x:c r="A830" s="1" t="s">
-        <x:v>889</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="B830" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C830" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D830" s="1">
         <x:v>0</x:v>
@@ -22325,21 +22325,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F830" s="1">
-        <x:v>8500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G830" s="1">
-        <x:v>8550</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="831" spans="1:7">
       <x:c r="A831" s="1" t="s">
-        <x:v>890</x:v>
+        <x:v>889</x:v>
       </x:c>
       <x:c r="B831" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C831" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D831" s="1">
         <x:v>0</x:v>
@@ -22348,18 +22348,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F831" s="1">
-        <x:v>14533</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G831" s="1">
-        <x:v>14533</x:v>
+        <x:v>8550</x:v>
       </x:c>
     </x:row>
     <x:row r="832" spans="1:7">
       <x:c r="A832" s="1" t="s">
-        <x:v>891</x:v>
+        <x:v>890</x:v>
       </x:c>
       <x:c r="B832" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C832" s="1">
         <x:v>0</x:v>
@@ -22371,18 +22371,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F832" s="1">
-        <x:v>6600</x:v>
+        <x:v>14533</x:v>
       </x:c>
       <x:c r="G832" s="1">
-        <x:v>6600</x:v>
+        <x:v>14533</x:v>
       </x:c>
     </x:row>
     <x:row r="833" spans="1:7">
       <x:c r="A833" s="1" t="s">
-        <x:v>892</x:v>
+        <x:v>891</x:v>
       </x:c>
       <x:c r="B833" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C833" s="1">
         <x:v>0</x:v>
@@ -22394,18 +22394,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F833" s="1">
-        <x:v>37000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G833" s="1">
-        <x:v>37000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="834" spans="1:7">
       <x:c r="A834" s="1" t="s">
-        <x:v>893</x:v>
+        <x:v>892</x:v>
       </x:c>
       <x:c r="B834" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C834" s="1">
         <x:v>0</x:v>
@@ -22417,21 +22417,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F834" s="1">
-        <x:v>1000</x:v>
+        <x:v>37000</x:v>
       </x:c>
       <x:c r="G834" s="1">
-        <x:v>1000</x:v>
+        <x:v>37000</x:v>
       </x:c>
     </x:row>
     <x:row r="835" spans="1:7">
       <x:c r="A835" s="1" t="s">
-        <x:v>894</x:v>
+        <x:v>893</x:v>
       </x:c>
       <x:c r="B835" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C835" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D835" s="1">
         <x:v>0</x:v>
@@ -22440,21 +22440,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F835" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G835" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="836" spans="1:7">
       <x:c r="A836" s="1" t="s">
-        <x:v>895</x:v>
+        <x:v>894</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D836" s="1">
         <x:v>0</x:v>
@@ -22463,21 +22463,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>7500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>10500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
       <x:c r="A837" s="1" t="s">
-        <x:v>896</x:v>
+        <x:v>895</x:v>
       </x:c>
       <x:c r="B837" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C837" s="1">
-        <x:v>1050</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D837" s="1">
         <x:v>0</x:v>
@@ -22486,21 +22486,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F837" s="1">
-        <x:v>6632</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="G837" s="1">
-        <x:v>7682</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="838" spans="1:7">
       <x:c r="A838" s="1" t="s">
-        <x:v>897</x:v>
+        <x:v>896</x:v>
       </x:c>
       <x:c r="B838" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C838" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D838" s="1">
         <x:v>0</x:v>
@@ -22509,18 +22509,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F838" s="1">
-        <x:v>0</x:v>
+        <x:v>6632</x:v>
       </x:c>
       <x:c r="G838" s="1">
-        <x:v>50</x:v>
+        <x:v>7682</x:v>
       </x:c>
     </x:row>
     <x:row r="839" spans="1:7">
       <x:c r="A839" s="1" t="s">
-        <x:v>898</x:v>
+        <x:v>897</x:v>
       </x:c>
       <x:c r="B839" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C839" s="1">
         <x:v>50</x:v>
@@ -22540,13 +22540,13 @@
     </x:row>
     <x:row r="840" spans="1:7">
       <x:c r="A840" s="1" t="s">
-        <x:v>899</x:v>
+        <x:v>898</x:v>
       </x:c>
       <x:c r="B840" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C840" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D840" s="1">
         <x:v>0</x:v>
@@ -22555,18 +22555,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F840" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G840" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="841" spans="1:7">
       <x:c r="A841" s="1" t="s">
-        <x:v>900</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="B841" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C841" s="1">
         <x:v>0</x:v>
@@ -22578,67 +22578,67 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F841" s="1">
-        <x:v>1000</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G841" s="1">
-        <x:v>1000</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="842" spans="1:7">
       <x:c r="A842" s="1" t="s">
-        <x:v>901</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="B842" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C842" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D842" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E842" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F842" s="1">
-        <x:v>8600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G842" s="1">
-        <x:v>901452</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="843" spans="1:7">
       <x:c r="A843" s="1" t="s">
-        <x:v>902</x:v>
+        <x:v>901</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>50</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D843" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E843" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>0</x:v>
+        <x:v>8600</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>50</x:v>
+        <x:v>901452</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
       <x:c r="A844" s="1" t="s">
-        <x:v>903</x:v>
+        <x:v>902</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>14600</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -22647,21 +22647,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>30905</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>45505</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
       <x:c r="A845" s="1" t="s">
-        <x:v>904</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="B845" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C845" s="1">
-        <x:v>50</x:v>
+        <x:v>14600</x:v>
       </x:c>
       <x:c r="D845" s="1">
         <x:v>0</x:v>
@@ -22670,18 +22670,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F845" s="1">
-        <x:v>0</x:v>
+        <x:v>30905</x:v>
       </x:c>
       <x:c r="G845" s="1">
-        <x:v>50</x:v>
+        <x:v>45505</x:v>
       </x:c>
     </x:row>
     <x:row r="846" spans="1:7">
       <x:c r="A846" s="1" t="s">
-        <x:v>905</x:v>
+        <x:v>904</x:v>
       </x:c>
       <x:c r="B846" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C846" s="1">
         <x:v>50</x:v>
@@ -22701,13 +22701,13 @@
     </x:row>
     <x:row r="847" spans="1:7">
       <x:c r="A847" s="1" t="s">
-        <x:v>906</x:v>
+        <x:v>905</x:v>
       </x:c>
       <x:c r="B847" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C847" s="1">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D847" s="1">
         <x:v>0</x:v>
@@ -22719,18 +22719,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G847" s="1">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="848" spans="1:7">
       <x:c r="A848" s="1" t="s">
-        <x:v>907</x:v>
+        <x:v>906</x:v>
       </x:c>
       <x:c r="B848" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C848" s="1">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D848" s="1">
         <x:v>0</x:v>
@@ -22739,47 +22739,47 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F848" s="1">
-        <x:v>2900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G848" s="1">
-        <x:v>2900</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="849" spans="1:7">
       <x:c r="A849" s="1" t="s">
-        <x:v>908</x:v>
+        <x:v>907</x:v>
       </x:c>
       <x:c r="B849" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C849" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D849" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E849" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F849" s="1">
-        <x:v>0</x:v>
+        <x:v>2900</x:v>
       </x:c>
       <x:c r="G849" s="1">
-        <x:v>1012792</x:v>
+        <x:v>2900</x:v>
       </x:c>
     </x:row>
     <x:row r="850" spans="1:7">
       <x:c r="A850" s="1" t="s">
-        <x:v>909</x:v>
+        <x:v>908</x:v>
       </x:c>
       <x:c r="B850" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C850" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D850" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E850" s="1">
         <x:v>0</x:v>
@@ -22788,18 +22788,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G850" s="1">
-        <x:v>50</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="851" spans="1:7">
       <x:c r="A851" s="1" t="s">
-        <x:v>910</x:v>
+        <x:v>909</x:v>
       </x:c>
       <x:c r="B851" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C851" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D851" s="1">
         <x:v>0</x:v>
@@ -22808,21 +22808,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F851" s="1">
-        <x:v>32600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G851" s="1">
-        <x:v>32600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="852" spans="1:7">
       <x:c r="A852" s="1" t="s">
-        <x:v>911</x:v>
+        <x:v>910</x:v>
       </x:c>
       <x:c r="B852" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C852" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D852" s="1">
         <x:v>0</x:v>
@@ -22831,21 +22831,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F852" s="1">
-        <x:v>0</x:v>
+        <x:v>32600</x:v>
       </x:c>
       <x:c r="G852" s="1">
-        <x:v>50</x:v>
+        <x:v>32600</x:v>
       </x:c>
     </x:row>
     <x:row r="853" spans="1:7">
       <x:c r="A853" s="1" t="s">
-        <x:v>912</x:v>
+        <x:v>911</x:v>
       </x:c>
       <x:c r="B853" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C853" s="1">
-        <x:v>19050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D853" s="1">
         <x:v>0</x:v>
@@ -22854,21 +22854,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F853" s="1">
-        <x:v>40900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G853" s="1">
-        <x:v>59950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="854" spans="1:7">
       <x:c r="A854" s="1" t="s">
-        <x:v>913</x:v>
+        <x:v>912</x:v>
       </x:c>
       <x:c r="B854" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C854" s="1">
-        <x:v>3500</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D854" s="1">
         <x:v>0</x:v>
@@ -22877,21 +22877,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F854" s="1">
-        <x:v>1162</x:v>
+        <x:v>40900</x:v>
       </x:c>
       <x:c r="G854" s="1">
-        <x:v>4662</x:v>
+        <x:v>59950</x:v>
       </x:c>
     </x:row>
     <x:row r="855" spans="1:7">
       <x:c r="A855" s="1" t="s">
-        <x:v>914</x:v>
+        <x:v>913</x:v>
       </x:c>
       <x:c r="B855" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C855" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D855" s="1">
         <x:v>0</x:v>
@@ -22900,10 +22900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F855" s="1">
-        <x:v>0</x:v>
+        <x:v>1162</x:v>
       </x:c>
       <x:c r="G855" s="1">
-        <x:v>50</x:v>
+        <x:v>4662</x:v>
       </x:c>
     </x:row>
     <x:row r="856" spans="1:7">
@@ -22911,10 +22911,10 @@
         <x:v>914</x:v>
       </x:c>
       <x:c r="B856" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C856" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D856" s="1">
         <x:v>0</x:v>
@@ -22923,21 +22923,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F856" s="1">
-        <x:v>485</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G856" s="1">
-        <x:v>485</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="857" spans="1:7">
       <x:c r="A857" s="1" t="s">
-        <x:v>915</x:v>
+        <x:v>914</x:v>
       </x:c>
       <x:c r="B857" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C857" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D857" s="1">
         <x:v>0</x:v>
@@ -22946,21 +22946,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F857" s="1">
-        <x:v>0</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="G857" s="1">
-        <x:v>50</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="858" spans="1:7">
       <x:c r="A858" s="1" t="s">
-        <x:v>916</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="B858" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C858" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D858" s="1">
         <x:v>0</x:v>
@@ -22969,21 +22969,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F858" s="1">
-        <x:v>1200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G858" s="1">
-        <x:v>7650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="859" spans="1:7">
       <x:c r="A859" s="1" t="s">
-        <x:v>917</x:v>
+        <x:v>916</x:v>
       </x:c>
       <x:c r="B859" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C859" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D859" s="1">
         <x:v>0</x:v>
@@ -22992,21 +22992,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F859" s="1">
-        <x:v>0</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="G859" s="1">
-        <x:v>50</x:v>
+        <x:v>7650</x:v>
       </x:c>
     </x:row>
     <x:row r="860" spans="1:7">
       <x:c r="A860" s="1" t="s">
-        <x:v>918</x:v>
+        <x:v>917</x:v>
       </x:c>
       <x:c r="B860" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C860" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D860" s="1">
         <x:v>0</x:v>
@@ -23015,21 +23015,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F860" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G860" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="861" spans="1:7">
       <x:c r="A861" s="1" t="s">
-        <x:v>919</x:v>
+        <x:v>918</x:v>
       </x:c>
       <x:c r="B861" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C861" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D861" s="1">
         <x:v>0</x:v>
@@ -23038,18 +23038,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F861" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G861" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="862" spans="1:7">
       <x:c r="A862" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>919</x:v>
       </x:c>
       <x:c r="B862" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C862" s="1">
         <x:v>50</x:v>
@@ -23069,13 +23069,13 @@
     </x:row>
     <x:row r="863" spans="1:7">
       <x:c r="A863" s="1" t="s">
-        <x:v>921</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="B863" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C863" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D863" s="1">
         <x:v>0</x:v>
@@ -23084,21 +23084,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F863" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G863" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="864" spans="1:7">
       <x:c r="A864" s="1" t="s">
-        <x:v>922</x:v>
+        <x:v>921</x:v>
       </x:c>
       <x:c r="B864" s="1" t="s">
-        <x:v>531</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C864" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D864" s="1">
         <x:v>0</x:v>
@@ -23107,18 +23107,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F864" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G864" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="865" spans="1:7">
       <x:c r="A865" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>922</x:v>
       </x:c>
       <x:c r="B865" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="C865" s="1">
         <x:v>50</x:v>
@@ -23138,13 +23138,13 @@
     </x:row>
     <x:row r="866" spans="1:7">
       <x:c r="A866" s="1" t="s">
-        <x:v>924</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="B866" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C866" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D866" s="1">
         <x:v>0</x:v>
@@ -23153,21 +23153,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F866" s="1">
-        <x:v>16000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G866" s="1">
-        <x:v>16000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="867" spans="1:7">
       <x:c r="A867" s="1" t="s">
-        <x:v>925</x:v>
+        <x:v>924</x:v>
       </x:c>
       <x:c r="B867" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C867" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D867" s="1">
         <x:v>0</x:v>
@@ -23176,18 +23176,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F867" s="1">
-        <x:v>0</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="G867" s="1">
-        <x:v>50</x:v>
+        <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="868" spans="1:7">
       <x:c r="A868" s="1" t="s">
-        <x:v>926</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="B868" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C868" s="1">
         <x:v>50</x:v>
@@ -23207,13 +23207,13 @@
     </x:row>
     <x:row r="869" spans="1:7">
       <x:c r="A869" s="1" t="s">
-        <x:v>927</x:v>
+        <x:v>926</x:v>
       </x:c>
       <x:c r="B869" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C869" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D869" s="1">
         <x:v>0</x:v>
@@ -23222,21 +23222,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F869" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G869" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="870" spans="1:7">
       <x:c r="A870" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="B870" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C870" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D870" s="1">
         <x:v>0</x:v>
@@ -23245,21 +23245,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F870" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G870" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="871" spans="1:7">
       <x:c r="A871" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="B871" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C871" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D871" s="1">
         <x:v>0</x:v>
@@ -23268,21 +23268,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F871" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G871" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="872" spans="1:7">
       <x:c r="A872" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="B872" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C872" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D872" s="1">
         <x:v>0</x:v>
@@ -23291,18 +23291,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F872" s="1">
-        <x:v>9900</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G872" s="1">
-        <x:v>9950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="873" spans="1:7">
       <x:c r="A873" s="1" t="s">
-        <x:v>931</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="B873" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="C873" s="1">
         <x:v>50</x:v>
@@ -23314,21 +23314,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F873" s="1">
-        <x:v>11799</x:v>
+        <x:v>9900</x:v>
       </x:c>
       <x:c r="G873" s="1">
-        <x:v>11849</x:v>
+        <x:v>9950</x:v>
       </x:c>
     </x:row>
     <x:row r="874" spans="1:7">
       <x:c r="A874" s="1" t="s">
-        <x:v>932</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="B874" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C874" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D874" s="1">
         <x:v>0</x:v>
@@ -23337,21 +23337,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F874" s="1">
-        <x:v>16500</x:v>
+        <x:v>11799</x:v>
       </x:c>
       <x:c r="G874" s="1">
-        <x:v>16500</x:v>
+        <x:v>11849</x:v>
       </x:c>
     </x:row>
     <x:row r="875" spans="1:7">
       <x:c r="A875" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>932</x:v>
       </x:c>
       <x:c r="B875" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C875" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D875" s="1">
         <x:v>0</x:v>
@@ -23360,18 +23360,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F875" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G875" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="876" spans="1:7">
       <x:c r="A876" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>933</x:v>
       </x:c>
       <x:c r="B876" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C876" s="1">
         <x:v>50</x:v>
@@ -23391,10 +23391,10 @@
     </x:row>
     <x:row r="877" spans="1:7">
       <x:c r="A877" s="1" t="s">
-        <x:v>935</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="B877" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C877" s="1">
         <x:v>50</x:v>
@@ -23414,10 +23414,10 @@
     </x:row>
     <x:row r="878" spans="1:7">
       <x:c r="A878" s="1" t="s">
-        <x:v>936</x:v>
+        <x:v>935</x:v>
       </x:c>
       <x:c r="B878" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C878" s="1">
         <x:v>50</x:v>
@@ -23429,18 +23429,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F878" s="1">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G878" s="1">
-        <x:v>250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="879" spans="1:7">
       <x:c r="A879" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>936</x:v>
       </x:c>
       <x:c r="B879" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C879" s="1">
         <x:v>50</x:v>
@@ -23452,18 +23452,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F879" s="1">
-        <x:v>0</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G879" s="1">
-        <x:v>50</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="880" spans="1:7">
       <x:c r="A880" s="1" t="s">
-        <x:v>938</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="B880" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C880" s="1">
         <x:v>50</x:v>
@@ -23483,13 +23483,13 @@
     </x:row>
     <x:row r="881" spans="1:7">
       <x:c r="A881" s="1" t="s">
-        <x:v>939</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="B881" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C881" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D881" s="1">
         <x:v>0</x:v>
@@ -23498,21 +23498,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F881" s="1">
-        <x:v>114400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G881" s="1">
-        <x:v>125250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="882" spans="1:7">
       <x:c r="A882" s="1" t="s">
-        <x:v>940</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="B882" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C882" s="1">
-        <x:v>0</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D882" s="1">
         <x:v>0</x:v>
@@ -23521,21 +23521,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F882" s="1">
-        <x:v>218</x:v>
+        <x:v>114400</x:v>
       </x:c>
       <x:c r="G882" s="1">
-        <x:v>218</x:v>
+        <x:v>125250</x:v>
       </x:c>
     </x:row>
     <x:row r="883" spans="1:7">
       <x:c r="A883" s="1" t="s">
-        <x:v>941</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="B883" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C883" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D883" s="1">
         <x:v>0</x:v>
@@ -23544,18 +23544,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F883" s="1">
-        <x:v>0</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G883" s="1">
-        <x:v>50</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="884" spans="1:7">
       <x:c r="A884" s="1" t="s">
-        <x:v>942</x:v>
+        <x:v>941</x:v>
       </x:c>
       <x:c r="B884" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C884" s="1">
         <x:v>50</x:v>
@@ -23575,10 +23575,10 @@
     </x:row>
     <x:row r="885" spans="1:7">
       <x:c r="A885" s="1" t="s">
-        <x:v>943</x:v>
+        <x:v>942</x:v>
       </x:c>
       <x:c r="B885" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C885" s="1">
         <x:v>50</x:v>
@@ -23598,13 +23598,13 @@
     </x:row>
     <x:row r="886" spans="1:7">
       <x:c r="A886" s="1" t="s">
-        <x:v>944</x:v>
+        <x:v>943</x:v>
       </x:c>
       <x:c r="B886" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C886" s="1">
-        <x:v>3100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D886" s="1">
         <x:v>0</x:v>
@@ -23613,21 +23613,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F886" s="1">
-        <x:v>35800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G886" s="1">
-        <x:v>38900</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="887" spans="1:7">
       <x:c r="A887" s="1" t="s">
-        <x:v>945</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="B887" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C887" s="1">
-        <x:v>50</x:v>
+        <x:v>3100</x:v>
       </x:c>
       <x:c r="D887" s="1">
         <x:v>0</x:v>
@@ -23636,32 +23636,55 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F887" s="1">
-        <x:v>278</x:v>
+        <x:v>35800</x:v>
       </x:c>
       <x:c r="G887" s="1">
-        <x:v>328</x:v>
+        <x:v>38900</x:v>
       </x:c>
     </x:row>
     <x:row r="888" spans="1:7">
       <x:c r="A888" s="1" t="s">
+        <x:v>945</x:v>
+      </x:c>
+      <x:c r="B888" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C888" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D888" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E888" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F888" s="1">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G888" s="1">
+        <x:v>328</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="889" spans="1:7">
+      <x:c r="A889" s="1" t="s">
         <x:v>946</x:v>
       </x:c>
-      <x:c r="B888" s="1" t="s">
+      <x:c r="B889" s="1" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="C888" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D888" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E888" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F888" s="1">
+      <x:c r="C889" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D889" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E889" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F889" s="1">
         <x:v>14333</x:v>
       </x:c>
-      <x:c r="G888" s="1">
+      <x:c r="G889" s="1">
         <x:v>14333</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -22940,10 +22940,10 @@
         <x:v>916</x:v>
       </x:c>
       <x:c r="B857" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C857" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D857" s="1">
         <x:v>0</x:v>
@@ -22952,10 +22952,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F857" s="1">
-        <x:v>0</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="G857" s="1">
-        <x:v>50</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="858" spans="1:7">
@@ -22963,10 +22963,10 @@
         <x:v>916</x:v>
       </x:c>
       <x:c r="B858" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C858" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D858" s="1">
         <x:v>0</x:v>
@@ -22975,10 +22975,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F858" s="1">
-        <x:v>485</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G858" s="1">
-        <x:v>485</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="859" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -250,6 +250,12 @@
     <x:t>BEYER, DONALD STERNOFF JR.</x:t>
   </x:si>
   <x:si>
+    <x:t>BIDEN, JOSEPH R JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
     <x:t>BIGGS, ANDY</x:t>
   </x:si>
   <x:si>
@@ -313,9 +319,6 @@
     <x:t>BOOKER, CORY A.</x:t>
   </x:si>
   <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
     <x:t>NJ</x:t>
   </x:si>
   <x:si>
@@ -643,9 +646,6 @@
     <x:t>COOPER, JAMES</x:t>
   </x:si>
   <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
     <x:t>CORNYN, JOHN SEN</x:t>
   </x:si>
   <x:si>
@@ -1729,7 +1729,7 @@
     <x:t>MANCHIN, JOE III</x:t>
   </x:si>
   <x:si>
-    <x:t>MANDEL, JOSHUA A.</x:t>
+    <x:t>MANDEL, JOSHUA A</x:t>
   </x:si>
   <x:si>
     <x:t>MANSHARAMANI, VIKRAM</x:t>
@@ -2627,6 +2627,9 @@
   </x:si>
   <x:si>
     <x:t>TONKO, PAUL DAVID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TOOMEY, PATRICK J</x:t>
   </x:si>
   <x:si>
     <x:t>TOOMEY, PATRICK JOSEPH</x:t>
@@ -4281,10 +4284,10 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>0</x:v>
@@ -4293,18 +4296,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>0</x:v>
+        <x:v>25449</x:v>
       </x:c>
       <x:c r="G46" s="1">
-        <x:v>50</x:v>
+        <x:v>25449</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>50</x:v>
@@ -4327,7 +4330,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>50</x:v>
@@ -4347,10 +4350,10 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>50</x:v>
@@ -4373,7 +4376,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>50</x:v>
@@ -4385,21 +4388,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>12600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G50" s="1">
-        <x:v>12650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C51" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>0</x:v>
@@ -4408,21 +4411,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>0</x:v>
+        <x:v>12600</x:v>
       </x:c>
       <x:c r="G51" s="1">
-        <x:v>1000</x:v>
+        <x:v>12650</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C52" s="1">
-        <x:v>2100</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>0</x:v>
@@ -4431,21 +4434,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>30100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G52" s="1">
-        <x:v>32200</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C53" s="1">
-        <x:v>0</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>0</x:v>
@@ -4454,21 +4457,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>1250</x:v>
+        <x:v>30100</x:v>
       </x:c>
       <x:c r="G53" s="1">
-        <x:v>1250</x:v>
+        <x:v>32200</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C54" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>0</x:v>
@@ -4477,10 +4480,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>0</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="G54" s="1">
-        <x:v>50</x:v>
+        <x:v>1250</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
@@ -4500,10 +4503,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>5400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G55" s="1">
-        <x:v>5450</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
@@ -4514,7 +4517,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="C56" s="1">
-        <x:v>3050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>0</x:v>
@@ -4523,10 +4526,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>11600</x:v>
+        <x:v>5400</x:v>
       </x:c>
       <x:c r="G56" s="1">
-        <x:v>14650</x:v>
+        <x:v>5450</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
@@ -4534,10 +4537,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C57" s="1">
-        <x:v>100</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>0</x:v>
@@ -4546,21 +4549,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>0</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G57" s="1">
-        <x:v>100</x:v>
+        <x:v>14650</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C58" s="1">
-        <x:v>0</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>0</x:v>
@@ -4569,21 +4572,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>71000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G58" s="1">
-        <x:v>71000</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C59" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>0</x:v>
@@ -4592,21 +4595,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>0</x:v>
+        <x:v>71000</x:v>
       </x:c>
       <x:c r="G59" s="1">
-        <x:v>50</x:v>
+        <x:v>71000</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C60" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>0</x:v>
@@ -4615,18 +4618,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>13600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G60" s="1">
-        <x:v>13600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>0</x:v>
@@ -4638,21 +4641,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>2800</x:v>
+        <x:v>13600</x:v>
       </x:c>
       <x:c r="G61" s="1">
-        <x:v>2800</x:v>
+        <x:v>13600</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C62" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>0</x:v>
@@ -4661,21 +4664,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>85000</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G62" s="1">
-        <x:v>85050</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B63" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="B63" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="C63" s="1">
-        <x:v>5450</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>0</x:v>
@@ -4684,21 +4687,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>36300</x:v>
+        <x:v>85000</x:v>
       </x:c>
       <x:c r="G63" s="1">
-        <x:v>41750</x:v>
+        <x:v>85050</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B64" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B64" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="C64" s="1">
-        <x:v>50</x:v>
+        <x:v>5450</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>0</x:v>
@@ -4707,10 +4710,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>28700</x:v>
+        <x:v>36300</x:v>
       </x:c>
       <x:c r="G64" s="1">
-        <x:v>28750</x:v>
+        <x:v>41750</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
@@ -4718,10 +4721,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C65" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>0</x:v>
@@ -4730,10 +4733,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>2500</x:v>
+        <x:v>28700</x:v>
       </x:c>
       <x:c r="G65" s="1">
-        <x:v>2500</x:v>
+        <x:v>28750</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
@@ -4741,7 +4744,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>0</x:v>
@@ -4750,13 +4753,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E66" s="1">
-        <x:v>2078023</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G66" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
@@ -4764,7 +4767,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>0</x:v>
@@ -4773,13 +4776,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E67" s="1">
-        <x:v>0</x:v>
+        <x:v>2078023</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>2400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G67" s="1">
-        <x:v>2400</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
@@ -4787,10 +4790,10 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C68" s="1">
-        <x:v>1050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>0</x:v>
@@ -4799,33 +4802,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>8300</x:v>
+        <x:v>2400</x:v>
       </x:c>
       <x:c r="G68" s="1">
-        <x:v>9350</x:v>
+        <x:v>2400</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B69" s="1" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B69" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="C69" s="1">
-        <x:v>0</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D69" s="1">
-        <x:v>530840</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E69" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>0</x:v>
+        <x:v>8300</x:v>
       </x:c>
       <x:c r="G69" s="1">
-        <x:v>530840</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
@@ -4833,22 +4836,22 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C70" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D70" s="1">
-        <x:v>0</x:v>
+        <x:v>530840</x:v>
       </x:c>
       <x:c r="E70" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G70" s="1">
-        <x:v>2750</x:v>
+        <x:v>530840</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
@@ -4856,10 +4859,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C71" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>0</x:v>
@@ -4868,21 +4871,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>500</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G71" s="1">
-        <x:v>500</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B72" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="B72" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="C72" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>0</x:v>
@@ -4891,10 +4894,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G72" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
@@ -4902,10 +4905,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C73" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>0</x:v>
@@ -4914,10 +4917,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>14333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G73" s="1">
-        <x:v>14333</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
@@ -4925,10 +4928,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C74" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>0</x:v>
@@ -4937,10 +4940,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>0</x:v>
+        <x:v>14333</x:v>
       </x:c>
       <x:c r="G74" s="1">
-        <x:v>50</x:v>
+        <x:v>14333</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
@@ -4948,10 +4951,10 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C75" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>0</x:v>
@@ -4960,10 +4963,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>12400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G75" s="1">
-        <x:v>12400</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
@@ -4974,7 +4977,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C76" s="1">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D76" s="1">
         <x:v>0</x:v>
@@ -4983,10 +4986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>0</x:v>
+        <x:v>12400</x:v>
       </x:c>
       <x:c r="G76" s="1">
-        <x:v>100</x:v>
+        <x:v>12400</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
@@ -4994,10 +4997,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C77" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D77" s="1">
         <x:v>0</x:v>
@@ -5009,7 +5012,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G77" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
@@ -5017,7 +5020,7 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C78" s="1">
         <x:v>50</x:v>
@@ -5040,10 +5043,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C79" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D79" s="1">
         <x:v>0</x:v>
@@ -5052,10 +5055,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>78670</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G79" s="1">
-        <x:v>78670</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
@@ -5063,10 +5066,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C80" s="1">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D80" s="1">
         <x:v>0</x:v>
@@ -5075,10 +5078,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>35450</x:v>
+        <x:v>78670</x:v>
       </x:c>
       <x:c r="G80" s="1">
-        <x:v>35550</x:v>
+        <x:v>78670</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
@@ -5086,10 +5089,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C81" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D81" s="1">
         <x:v>0</x:v>
@@ -5098,10 +5101,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>0</x:v>
+        <x:v>35450</x:v>
       </x:c>
       <x:c r="G81" s="1">
-        <x:v>50</x:v>
+        <x:v>35550</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
@@ -5109,7 +5112,7 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C82" s="1">
         <x:v>50</x:v>
@@ -5132,7 +5135,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C83" s="1">
         <x:v>50</x:v>
@@ -5155,7 +5158,7 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C84" s="1">
         <x:v>50</x:v>
@@ -5178,10 +5181,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C85" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D85" s="1">
         <x:v>0</x:v>
@@ -5190,10 +5193,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>11850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G85" s="1">
-        <x:v>13900</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
@@ -5224,22 +5227,22 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C87" s="1">
-        <x:v>3000</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D87" s="1">
-        <x:v>750094</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E87" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>19400</x:v>
+        <x:v>11850</x:v>
       </x:c>
       <x:c r="G87" s="1">
-        <x:v>772494</x:v>
+        <x:v>13900</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
@@ -5247,33 +5250,33 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C88" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D88" s="1">
-        <x:v>0</x:v>
+        <x:v>750094</x:v>
       </x:c>
       <x:c r="E88" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>6100</x:v>
+        <x:v>19400</x:v>
       </x:c>
       <x:c r="G88" s="1">
-        <x:v>6100</x:v>
+        <x:v>772494</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B89" s="1" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="B89" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="C89" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D89" s="1">
         <x:v>0</x:v>
@@ -5282,10 +5285,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>0</x:v>
+        <x:v>6100</x:v>
       </x:c>
       <x:c r="G89" s="1">
-        <x:v>50</x:v>
+        <x:v>6100</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
@@ -5293,7 +5296,7 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C90" s="1">
         <x:v>50</x:v>
@@ -5316,10 +5319,10 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C91" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D91" s="1">
         <x:v>0</x:v>
@@ -5328,10 +5331,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>2900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G91" s="1">
-        <x:v>2900</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
@@ -5339,7 +5342,7 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C92" s="1">
         <x:v>0</x:v>
@@ -5351,10 +5354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>500</x:v>
+        <x:v>2900</x:v>
       </x:c>
       <x:c r="G92" s="1">
-        <x:v>500</x:v>
+        <x:v>2900</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
@@ -5362,10 +5365,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C93" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D93" s="1">
         <x:v>0</x:v>
@@ -5374,10 +5377,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>1000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G93" s="1">
-        <x:v>1050</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
@@ -5385,22 +5388,22 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C94" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D94" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E94" s="1">
-        <x:v>2813046</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G94" s="1">
-        <x:v>0</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
@@ -5408,22 +5411,22 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C95" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D95" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E95" s="1">
-        <x:v>0</x:v>
+        <x:v>2813046</x:v>
       </x:c>
       <x:c r="F95" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G95" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
@@ -5431,7 +5434,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C96" s="1">
         <x:v>50</x:v>
@@ -5454,10 +5457,10 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C97" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D97" s="1">
         <x:v>0</x:v>
@@ -5466,10 +5469,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>3350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G97" s="1">
-        <x:v>3350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
@@ -5477,10 +5480,10 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C98" s="1">
-        <x:v>9500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D98" s="1">
         <x:v>0</x:v>
@@ -5489,10 +5492,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>8231</x:v>
+        <x:v>3350</x:v>
       </x:c>
       <x:c r="G98" s="1">
-        <x:v>17731</x:v>
+        <x:v>3350</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
@@ -5500,10 +5503,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C99" s="1">
-        <x:v>0</x:v>
+        <x:v>9500</x:v>
       </x:c>
       <x:c r="D99" s="1">
         <x:v>0</x:v>
@@ -5512,10 +5515,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>7776</x:v>
+        <x:v>8231</x:v>
       </x:c>
       <x:c r="G99" s="1">
-        <x:v>7776</x:v>
+        <x:v>17731</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
@@ -5523,10 +5526,10 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C100" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D100" s="1">
         <x:v>0</x:v>
@@ -5535,10 +5538,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>20933</x:v>
+        <x:v>7776</x:v>
       </x:c>
       <x:c r="G100" s="1">
-        <x:v>20983</x:v>
+        <x:v>7776</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
@@ -5546,10 +5549,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C101" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D101" s="1">
         <x:v>0</x:v>
@@ -5558,10 +5561,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>25300</x:v>
+        <x:v>20933</x:v>
       </x:c>
       <x:c r="G101" s="1">
-        <x:v>25800</x:v>
+        <x:v>20983</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
@@ -5569,10 +5572,10 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C102" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D102" s="1">
         <x:v>0</x:v>
@@ -5581,10 +5584,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>25000</x:v>
+        <x:v>25300</x:v>
       </x:c>
       <x:c r="G102" s="1">
-        <x:v>25000</x:v>
+        <x:v>25800</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
@@ -5592,10 +5595,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C103" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D103" s="1">
         <x:v>0</x:v>
@@ -5604,21 +5607,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>25100</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G103" s="1">
-        <x:v>25150</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B104" s="1" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="B104" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="C104" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D104" s="1">
         <x:v>0</x:v>
@@ -5627,10 +5630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>2000</x:v>
+        <x:v>25100</x:v>
       </x:c>
       <x:c r="G104" s="1">
-        <x:v>2000</x:v>
+        <x:v>25150</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
@@ -5638,10 +5641,10 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -5650,33 +5653,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B106" s="1" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B106" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="C106" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D106" s="1">
-        <x:v>2270929</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E106" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>33350</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2304779</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -5684,22 +5687,22 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C107" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D107" s="1">
-        <x:v>0</x:v>
+        <x:v>2270929</x:v>
       </x:c>
       <x:c r="E107" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>0</x:v>
+        <x:v>33350</x:v>
       </x:c>
       <x:c r="G107" s="1">
-        <x:v>50</x:v>
+        <x:v>2304779</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
@@ -5730,7 +5733,7 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C109" s="1">
         <x:v>50</x:v>
@@ -5753,10 +5756,10 @@
         <x:v>154</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C110" s="1">
-        <x:v>8000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D110" s="1">
         <x:v>0</x:v>
@@ -5765,10 +5768,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>4500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G110" s="1">
-        <x:v>12500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
@@ -5776,10 +5779,10 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C111" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D111" s="1">
         <x:v>0</x:v>
@@ -5788,10 +5791,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>5000</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G111" s="1">
-        <x:v>5000</x:v>
+        <x:v>12500</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
@@ -5799,10 +5802,10 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C112" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D112" s="1">
         <x:v>0</x:v>
@@ -5811,10 +5814,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>2500</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G112" s="1">
-        <x:v>2550</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
@@ -5822,7 +5825,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C113" s="1">
         <x:v>50</x:v>
@@ -5834,10 +5837,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G113" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:7">
@@ -5845,10 +5848,10 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C114" s="1">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D114" s="1">
         <x:v>0</x:v>
@@ -5860,7 +5863,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G114" s="1">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7">
@@ -5868,10 +5871,10 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="B115" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C115" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D115" s="1">
         <x:v>0</x:v>
@@ -5883,7 +5886,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G115" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
@@ -5891,10 +5894,10 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B116" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C116" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D116" s="1">
         <x:v>0</x:v>
@@ -5903,21 +5906,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F116" s="1">
-        <x:v>3332</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G116" s="1">
-        <x:v>5332</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7">
       <x:c r="A117" s="1" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B117" s="1" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="B117" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
       <x:c r="C117" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D117" s="1">
         <x:v>0</x:v>
@@ -5926,10 +5929,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F117" s="1">
-        <x:v>0</x:v>
+        <x:v>3332</x:v>
       </x:c>
       <x:c r="G117" s="1">
-        <x:v>50</x:v>
+        <x:v>5332</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7">
@@ -5937,7 +5940,7 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B118" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C118" s="1">
         <x:v>50</x:v>
@@ -5960,7 +5963,7 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="B119" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C119" s="1">
         <x:v>50</x:v>
@@ -5972,10 +5975,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F119" s="1">
-        <x:v>21900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G119" s="1">
-        <x:v>21950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:7">
@@ -5983,7 +5986,7 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B120" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C120" s="1">
         <x:v>50</x:v>
@@ -5995,10 +5998,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F120" s="1">
-        <x:v>29700</x:v>
+        <x:v>21900</x:v>
       </x:c>
       <x:c r="G120" s="1">
-        <x:v>29750</x:v>
+        <x:v>21950</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7">
@@ -6006,10 +6009,10 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C121" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D121" s="1">
         <x:v>0</x:v>
@@ -6018,10 +6021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F121" s="1">
-        <x:v>2900</x:v>
+        <x:v>29700</x:v>
       </x:c>
       <x:c r="G121" s="1">
-        <x:v>2900</x:v>
+        <x:v>29750</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:7">
@@ -6029,10 +6032,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B122" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C122" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D122" s="1">
         <x:v>0</x:v>
@@ -6041,10 +6044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F122" s="1">
-        <x:v>0</x:v>
+        <x:v>2900</x:v>
       </x:c>
       <x:c r="G122" s="1">
-        <x:v>50</x:v>
+        <x:v>2900</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:7">
@@ -6052,10 +6055,10 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B123" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C123" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D123" s="1">
         <x:v>0</x:v>
@@ -6064,10 +6067,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F123" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G123" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:7">
@@ -6075,10 +6078,10 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="B124" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C124" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D124" s="1">
         <x:v>0</x:v>
@@ -6087,10 +6090,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F124" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G124" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:7">
@@ -6098,7 +6101,7 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="B125" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C125" s="1">
         <x:v>50</x:v>
@@ -6121,7 +6124,7 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C126" s="1">
         <x:v>50</x:v>
@@ -6144,10 +6147,10 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B127" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C127" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D127" s="1">
         <x:v>0</x:v>
@@ -6156,10 +6159,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F127" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G127" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:7">
@@ -6167,22 +6170,22 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B128" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C128" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D128" s="1">
-        <x:v>3028740</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E128" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F128" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G128" s="1">
-        <x:v>3035340</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:7">
@@ -6190,22 +6193,22 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C129" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D129" s="1">
-        <x:v>0</x:v>
+        <x:v>3028740</x:v>
       </x:c>
       <x:c r="E129" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F129" s="1">
-        <x:v>5800</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G129" s="1">
-        <x:v>5800</x:v>
+        <x:v>3035340</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
@@ -6213,10 +6216,10 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B130" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C130" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D130" s="1">
         <x:v>0</x:v>
@@ -6225,10 +6228,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F130" s="1">
-        <x:v>11000</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G130" s="1">
-        <x:v>11050</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
@@ -6236,22 +6239,22 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="B131" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C131" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D131" s="1">
-        <x:v>415283</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E131" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F131" s="1">
-        <x:v>0</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="G131" s="1">
-        <x:v>415283</x:v>
+        <x:v>11050</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7">
@@ -6259,22 +6262,22 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B132" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C132" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D132" s="1">
-        <x:v>0</x:v>
+        <x:v>415283</x:v>
       </x:c>
       <x:c r="E132" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F132" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G132" s="1">
-        <x:v>500</x:v>
+        <x:v>415283</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:7">
@@ -6282,7 +6285,7 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B133" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C133" s="1">
         <x:v>0</x:v>
@@ -6294,10 +6297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F133" s="1">
-        <x:v>2700</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G133" s="1">
-        <x:v>2700</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:7">
@@ -6305,10 +6308,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C134" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D134" s="1">
         <x:v>0</x:v>
@@ -6317,10 +6320,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F134" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G134" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:7">
@@ -6328,7 +6331,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="B135" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C135" s="1">
         <x:v>50</x:v>
@@ -6351,22 +6354,22 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B136" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C136" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D136" s="1">
-        <x:v>3250594</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E136" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F136" s="1">
-        <x:v>20933</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G136" s="1">
-        <x:v>3271527</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:7">
@@ -6374,22 +6377,22 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="B137" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C137" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D137" s="1">
-        <x:v>0</x:v>
+        <x:v>3250594</x:v>
       </x:c>
       <x:c r="E137" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F137" s="1">
-        <x:v>0</x:v>
+        <x:v>20933</x:v>
       </x:c>
       <x:c r="G137" s="1">
-        <x:v>50</x:v>
+        <x:v>3271527</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">
@@ -6397,10 +6400,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B138" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C138" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D138" s="1">
         <x:v>0</x:v>
@@ -6409,10 +6412,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F138" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G138" s="1">
-        <x:v>3300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:7">
@@ -6420,7 +6423,7 @@
         <x:v>184</x:v>
       </x:c>
       <x:c r="B139" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C139" s="1">
         <x:v>0</x:v>
@@ -6432,10 +6435,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F139" s="1">
-        <x:v>7000</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G139" s="1">
-        <x:v>7000</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:7">
@@ -6443,10 +6446,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B140" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C140" s="1">
-        <x:v>6050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D140" s="1">
         <x:v>0</x:v>
@@ -6455,10 +6458,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F140" s="1">
-        <x:v>37900</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G140" s="1">
-        <x:v>43950</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:7">
@@ -6466,10 +6469,10 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="B141" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C141" s="1">
-        <x:v>0</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D141" s="1">
         <x:v>0</x:v>
@@ -6478,10 +6481,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F141" s="1">
-        <x:v>2000</x:v>
+        <x:v>37900</x:v>
       </x:c>
       <x:c r="G141" s="1">
-        <x:v>2000</x:v>
+        <x:v>43950</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:7">
@@ -6489,10 +6492,10 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B142" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C142" s="1">
-        <x:v>2550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D142" s="1">
         <x:v>0</x:v>
@@ -6501,10 +6504,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F142" s="1">
-        <x:v>5000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G142" s="1">
-        <x:v>7550</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:7">
@@ -6512,10 +6515,10 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="B143" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C143" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D143" s="1">
         <x:v>0</x:v>
@@ -6524,10 +6527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F143" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G143" s="1">
-        <x:v>50</x:v>
+        <x:v>7550</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:7">
@@ -6558,7 +6561,7 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="B145" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C145" s="1">
         <x:v>50</x:v>
@@ -6581,10 +6584,10 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="B146" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C146" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D146" s="1">
         <x:v>0</x:v>
@@ -6593,10 +6596,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F146" s="1">
-        <x:v>7358</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G146" s="1">
-        <x:v>7358</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:7">
@@ -6604,10 +6607,10 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="B147" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C147" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D147" s="1">
         <x:v>0</x:v>
@@ -6616,10 +6619,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F147" s="1">
-        <x:v>0</x:v>
+        <x:v>7358</x:v>
       </x:c>
       <x:c r="G147" s="1">
-        <x:v>50</x:v>
+        <x:v>7358</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:7">
@@ -6627,7 +6630,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="B148" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C148" s="1">
         <x:v>50</x:v>
@@ -6639,19 +6642,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F148" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G148" s="1">
-        <x:v>5850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
       <x:c r="A149" s="1" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B149" s="1" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="B149" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="C149" s="1">
         <x:v>50</x:v>
       </x:c>
@@ -6662,10 +6665,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F149" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G149" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:7">
@@ -6673,13 +6676,13 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="B150" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C150" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D150" s="1">
-        <x:v>845124</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E150" s="1">
         <x:v>0</x:v>
@@ -6688,21 +6691,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G150" s="1">
-        <x:v>845174</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:7">
       <x:c r="A151" s="1" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B151" s="1" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="B151" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="C151" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D151" s="1">
-        <x:v>0</x:v>
+        <x:v>845124</x:v>
       </x:c>
       <x:c r="E151" s="1">
         <x:v>0</x:v>
@@ -6711,7 +6714,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G151" s="1">
-        <x:v>50</x:v>
+        <x:v>845174</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:7">
@@ -6719,7 +6722,7 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="B152" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C152" s="1">
         <x:v>50</x:v>
@@ -6731,10 +6734,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G152" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:7">
@@ -6745,7 +6748,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C153" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D153" s="1">
         <x:v>0</x:v>
@@ -6754,10 +6757,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F153" s="1">
-        <x:v>14000</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G153" s="1">
-        <x:v>14000</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:7">
@@ -6765,10 +6768,10 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="B154" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C154" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D154" s="1">
         <x:v>0</x:v>
@@ -6777,19 +6780,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F154" s="1">
-        <x:v>9200</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G154" s="1">
-        <x:v>9250</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:7">
       <x:c r="A155" s="1" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B155" s="1" t="s">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="B155" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="C155" s="1">
         <x:v>50</x:v>
       </x:c>
@@ -6800,10 +6803,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F155" s="1">
-        <x:v>0</x:v>
+        <x:v>9200</x:v>
       </x:c>
       <x:c r="G155" s="1">
-        <x:v>50</x:v>
+        <x:v>9250</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:7">
@@ -6811,10 +6814,10 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="B156" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C156" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D156" s="1">
         <x:v>0</x:v>
@@ -6823,10 +6826,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F156" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G156" s="1">
-        <x:v>4050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:7">
@@ -6834,10 +6837,10 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B157" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C157" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D157" s="1">
         <x:v>0</x:v>
@@ -6846,10 +6849,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F157" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="G157" s="1">
-        <x:v>50</x:v>
+        <x:v>4050</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:7">
@@ -6857,7 +6860,7 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="B158" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C158" s="1">
         <x:v>50</x:v>
@@ -6880,10 +6883,10 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="B159" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C159" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D159" s="1">
         <x:v>0</x:v>
@@ -6895,7 +6898,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G159" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:7">
@@ -6903,10 +6906,10 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B160" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C160" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D160" s="1">
         <x:v>0</x:v>
@@ -6918,7 +6921,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G160" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:7">
@@ -6926,10 +6929,10 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B161" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C161" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D161" s="1">
         <x:v>0</x:v>
@@ -6938,10 +6941,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F161" s="1">
-        <x:v>7000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G161" s="1">
-        <x:v>7000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:7">
@@ -7041,7 +7044,7 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B166" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C166" s="1">
         <x:v>100</x:v>
@@ -7064,7 +7067,7 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B167" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C167" s="1">
         <x:v>50</x:v>
@@ -7225,7 +7228,7 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B174" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C174" s="1">
         <x:v>50</x:v>
@@ -7271,7 +7274,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="B176" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C176" s="1">
         <x:v>50</x:v>
@@ -7363,7 +7366,7 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="B180" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C180" s="1">
         <x:v>0</x:v>
@@ -7432,7 +7435,7 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="B183" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C183" s="1">
         <x:v>50</x:v>
@@ -7455,7 +7458,7 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="B184" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C184" s="1">
         <x:v>100</x:v>
@@ -7478,7 +7481,7 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="B185" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C185" s="1">
         <x:v>5350</x:v>
@@ -7501,7 +7504,7 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B186" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C186" s="1">
         <x:v>5350</x:v>
@@ -7616,7 +7619,7 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="B191" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C191" s="1">
         <x:v>0</x:v>
@@ -7777,7 +7780,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="B198" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C198" s="1">
         <x:v>50</x:v>
@@ -7823,7 +7826,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B200" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C200" s="1">
         <x:v>0</x:v>
@@ -7869,7 +7872,7 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="B202" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C202" s="1">
         <x:v>50</x:v>
@@ -7915,7 +7918,7 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="B204" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C204" s="1">
         <x:v>50</x:v>
@@ -7938,7 +7941,7 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="B205" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C205" s="1">
         <x:v>6050</x:v>
@@ -7984,7 +7987,7 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="B207" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C207" s="1">
         <x:v>0</x:v>
@@ -8007,7 +8010,7 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="B208" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C208" s="1">
         <x:v>50</x:v>
@@ -8030,7 +8033,7 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B209" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C209" s="1">
         <x:v>50</x:v>
@@ -8053,7 +8056,7 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="B210" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C210" s="1">
         <x:v>0</x:v>
@@ -8122,7 +8125,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B213" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C213" s="1">
         <x:v>50</x:v>
@@ -8145,7 +8148,7 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="B214" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C214" s="1">
         <x:v>50</x:v>
@@ -8191,7 +8194,7 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="B216" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C216" s="1">
         <x:v>0</x:v>
@@ -8283,7 +8286,7 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="B220" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C220" s="1">
         <x:v>8000</x:v>
@@ -8306,7 +8309,7 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="B221" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C221" s="1">
         <x:v>1500</x:v>
@@ -8329,7 +8332,7 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="B222" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C222" s="1">
         <x:v>50</x:v>
@@ -8398,7 +8401,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B225" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C225" s="1">
         <x:v>50</x:v>
@@ -8421,7 +8424,7 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="B226" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C226" s="1">
         <x:v>50</x:v>
@@ -8513,7 +8516,7 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="B230" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C230" s="1">
         <x:v>0</x:v>
@@ -8766,7 +8769,7 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="B241" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C241" s="1">
         <x:v>50</x:v>
@@ -8904,7 +8907,7 @@
         <x:v>299</x:v>
       </x:c>
       <x:c r="B247" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C247" s="1">
         <x:v>0</x:v>
@@ -9042,7 +9045,7 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="B253" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C253" s="1">
         <x:v>50</x:v>
@@ -9272,7 +9275,7 @@
         <x:v>315</x:v>
       </x:c>
       <x:c r="B263" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C263" s="1">
         <x:v>50</x:v>
@@ -9433,7 +9436,7 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="B270" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C270" s="1">
         <x:v>50</x:v>
@@ -9456,7 +9459,7 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B271" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C271" s="1">
         <x:v>50</x:v>
@@ -9548,7 +9551,7 @@
         <x:v>327</x:v>
       </x:c>
       <x:c r="B275" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C275" s="1">
         <x:v>0</x:v>
@@ -9709,7 +9712,7 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="B282" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C282" s="1">
         <x:v>0</x:v>
@@ -9755,7 +9758,7 @@
         <x:v>336</x:v>
       </x:c>
       <x:c r="B284" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C284" s="1">
         <x:v>50</x:v>
@@ -9801,7 +9804,7 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="B286" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C286" s="1">
         <x:v>0</x:v>
@@ -9916,7 +9919,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="B291" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C291" s="1">
         <x:v>0</x:v>
@@ -9985,7 +9988,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="B294" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C294" s="1">
         <x:v>50</x:v>
@@ -10284,7 +10287,7 @@
         <x:v>361</x:v>
       </x:c>
       <x:c r="B307" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C307" s="1">
         <x:v>4550</x:v>
@@ -10307,7 +10310,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B308" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C308" s="1">
         <x:v>50</x:v>
@@ -10376,7 +10379,7 @@
         <x:v>365</x:v>
       </x:c>
       <x:c r="B311" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C311" s="1">
         <x:v>50</x:v>
@@ -10836,7 +10839,7 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="B331" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C331" s="1">
         <x:v>0</x:v>
@@ -10928,7 +10931,7 @@
         <x:v>391</x:v>
       </x:c>
       <x:c r="B335" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C335" s="1">
         <x:v>1500</x:v>
@@ -11020,7 +11023,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="B339" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C339" s="1">
         <x:v>0</x:v>
@@ -11032,10 +11035,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F339" s="1">
-        <x:v>28249</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G339" s="1">
-        <x:v>28249</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="340" spans="1:7">
@@ -11158,7 +11161,7 @@
         <x:v>401</x:v>
       </x:c>
       <x:c r="B345" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C345" s="1">
         <x:v>50</x:v>
@@ -11181,7 +11184,7 @@
         <x:v>402</x:v>
       </x:c>
       <x:c r="B346" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C346" s="1">
         <x:v>0</x:v>
@@ -11227,7 +11230,7 @@
         <x:v>404</x:v>
       </x:c>
       <x:c r="B348" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C348" s="1">
         <x:v>50</x:v>
@@ -11250,7 +11253,7 @@
         <x:v>405</x:v>
       </x:c>
       <x:c r="B349" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C349" s="1">
         <x:v>50</x:v>
@@ -11342,7 +11345,7 @@
         <x:v>409</x:v>
       </x:c>
       <x:c r="B353" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C353" s="1">
         <x:v>50</x:v>
@@ -11365,7 +11368,7 @@
         <x:v>410</x:v>
       </x:c>
       <x:c r="B354" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C354" s="1">
         <x:v>50</x:v>
@@ -11457,7 +11460,7 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C358" s="1">
         <x:v>50</x:v>
@@ -11480,7 +11483,7 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C359" s="1">
         <x:v>11050</x:v>
@@ -11549,7 +11552,7 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B362" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C362" s="1">
         <x:v>3550</x:v>
@@ -11595,7 +11598,7 @@
         <x:v>420</x:v>
       </x:c>
       <x:c r="B364" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C364" s="1">
         <x:v>50</x:v>
@@ -11618,7 +11621,7 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="B365" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C365" s="1">
         <x:v>50</x:v>
@@ -11756,7 +11759,7 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="B371" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C371" s="1">
         <x:v>100</x:v>
@@ -11825,7 +11828,7 @@
         <x:v>430</x:v>
       </x:c>
       <x:c r="B374" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C374" s="1">
         <x:v>50</x:v>
@@ -11917,7 +11920,7 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B378" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C378" s="1">
         <x:v>0</x:v>
@@ -12055,7 +12058,7 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B384" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C384" s="1">
         <x:v>0</x:v>
@@ -12170,7 +12173,7 @@
         <x:v>445</x:v>
       </x:c>
       <x:c r="B389" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C389" s="1">
         <x:v>50</x:v>
@@ -12377,7 +12380,7 @@
         <x:v>454</x:v>
       </x:c>
       <x:c r="B398" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C398" s="1">
         <x:v>50</x:v>
@@ -12423,7 +12426,7 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B400" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C400" s="1">
         <x:v>0</x:v>
@@ -12538,7 +12541,7 @@
         <x:v>461</x:v>
       </x:c>
       <x:c r="B405" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C405" s="1">
         <x:v>50</x:v>
@@ -12722,7 +12725,7 @@
         <x:v>469</x:v>
       </x:c>
       <x:c r="B413" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C413" s="1">
         <x:v>50</x:v>
@@ -12768,7 +12771,7 @@
         <x:v>471</x:v>
       </x:c>
       <x:c r="B415" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C415" s="1">
         <x:v>1000</x:v>
@@ -12883,7 +12886,7 @@
         <x:v>476</x:v>
       </x:c>
       <x:c r="B420" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C420" s="1">
         <x:v>0</x:v>
@@ -12929,7 +12932,7 @@
         <x:v>478</x:v>
       </x:c>
       <x:c r="B422" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C422" s="1">
         <x:v>0</x:v>
@@ -12952,7 +12955,7 @@
         <x:v>479</x:v>
       </x:c>
       <x:c r="B423" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C423" s="1">
         <x:v>0</x:v>
@@ -12998,7 +13001,7 @@
         <x:v>481</x:v>
       </x:c>
       <x:c r="B425" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C425" s="1">
         <x:v>50</x:v>
@@ -13021,7 +13024,7 @@
         <x:v>482</x:v>
       </x:c>
       <x:c r="B426" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C426" s="1">
         <x:v>50</x:v>
@@ -13113,7 +13116,7 @@
         <x:v>486</x:v>
       </x:c>
       <x:c r="B430" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C430" s="1">
         <x:v>50</x:v>
@@ -13159,7 +13162,7 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B432" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C432" s="1">
         <x:v>0</x:v>
@@ -13228,7 +13231,7 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B435" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C435" s="1">
         <x:v>0</x:v>
@@ -13320,7 +13323,7 @@
         <x:v>495</x:v>
       </x:c>
       <x:c r="B439" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C439" s="1">
         <x:v>50</x:v>
@@ -13343,7 +13346,7 @@
         <x:v>496</x:v>
       </x:c>
       <x:c r="B440" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C440" s="1">
         <x:v>100</x:v>
@@ -13412,7 +13415,7 @@
         <x:v>499</x:v>
       </x:c>
       <x:c r="B443" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C443" s="1">
         <x:v>50</x:v>
@@ -13458,7 +13461,7 @@
         <x:v>501</x:v>
       </x:c>
       <x:c r="B445" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C445" s="1">
         <x:v>0</x:v>
@@ -13803,7 +13806,7 @@
         <x:v>516</x:v>
       </x:c>
       <x:c r="B460" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C460" s="1">
         <x:v>100</x:v>
@@ -13872,7 +13875,7 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="B463" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C463" s="1">
         <x:v>50</x:v>
@@ -13895,7 +13898,7 @@
         <x:v>520</x:v>
       </x:c>
       <x:c r="B464" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C464" s="1">
         <x:v>50</x:v>
@@ -13941,7 +13944,7 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B466" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C466" s="1">
         <x:v>50</x:v>
@@ -13964,7 +13967,7 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B467" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C467" s="1">
         <x:v>5050</x:v>
@@ -14079,7 +14082,7 @@
         <x:v>528</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C472" s="1">
         <x:v>1550</x:v>
@@ -14194,7 +14197,7 @@
         <x:v>534</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C477" s="1">
         <x:v>50</x:v>
@@ -14309,7 +14312,7 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="B482" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C482" s="1">
         <x:v>0</x:v>
@@ -14700,7 +14703,7 @@
         <x:v>556</x:v>
       </x:c>
       <x:c r="B499" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C499" s="1">
         <x:v>50</x:v>
@@ -14884,7 +14887,7 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C507" s="1">
         <x:v>0</x:v>
@@ -14930,7 +14933,7 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C509" s="1">
         <x:v>50</x:v>
@@ -15022,7 +15025,7 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C513" s="1">
         <x:v>50</x:v>
@@ -15126,10 +15129,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F517" s="1">
-        <x:v>1715</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G517" s="1">
-        <x:v>1765</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="518" spans="1:7">
@@ -15149,10 +15152,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F518" s="1">
-        <x:v>0</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="G518" s="1">
-        <x:v>50</x:v>
+        <x:v>1765</x:v>
       </x:c>
     </x:row>
     <x:row r="519" spans="1:7">
@@ -15206,7 +15209,7 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B521" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C521" s="1">
         <x:v>50</x:v>
@@ -15275,7 +15278,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C524" s="1">
         <x:v>50</x:v>
@@ -15321,7 +15324,7 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C526" s="1">
         <x:v>0</x:v>
@@ -15367,7 +15370,7 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="B528" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C528" s="1">
         <x:v>0</x:v>
@@ -15551,7 +15554,7 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C536" s="1">
         <x:v>8300</x:v>
@@ -15689,7 +15692,7 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B542" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C542" s="1">
         <x:v>0</x:v>
@@ -15804,7 +15807,7 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C547" s="1">
         <x:v>50</x:v>
@@ -15827,7 +15830,7 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="B548" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C548" s="1">
         <x:v>50</x:v>
@@ -15850,7 +15853,7 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C549" s="1">
         <x:v>0</x:v>
@@ -15965,7 +15968,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C554" s="1">
         <x:v>3100</x:v>
@@ -16011,7 +16014,7 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C556" s="1">
         <x:v>50</x:v>
@@ -16057,7 +16060,7 @@
         <x:v>615</x:v>
       </x:c>
       <x:c r="B558" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C558" s="1">
         <x:v>1550</x:v>
@@ -16103,7 +16106,7 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C560" s="1">
         <x:v>50</x:v>
@@ -16172,7 +16175,7 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B563" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C563" s="1">
         <x:v>0</x:v>
@@ -16264,7 +16267,7 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B567" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C567" s="1">
         <x:v>0</x:v>
@@ -16310,7 +16313,7 @@
         <x:v>626</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C569" s="1">
         <x:v>50</x:v>
@@ -16333,7 +16336,7 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>1000</x:v>
@@ -16402,7 +16405,7 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C573" s="1">
         <x:v>0</x:v>
@@ -16448,7 +16451,7 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B575" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C575" s="1">
         <x:v>1000</x:v>
@@ -16563,7 +16566,7 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C580" s="1">
         <x:v>1000</x:v>
@@ -16609,7 +16612,7 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C582" s="1">
         <x:v>50</x:v>
@@ -16655,7 +16658,7 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="B584" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C584" s="1">
         <x:v>50</x:v>
@@ -16678,7 +16681,7 @@
         <x:v>642</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C585" s="1">
         <x:v>50</x:v>
@@ -16701,7 +16704,7 @@
         <x:v>643</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>2700</x:v>
@@ -16747,7 +16750,7 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C588" s="1">
         <x:v>50</x:v>
@@ -16793,7 +16796,7 @@
         <x:v>647</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C590" s="1">
         <x:v>0</x:v>
@@ -16839,7 +16842,7 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C592" s="1">
         <x:v>50</x:v>
@@ -16862,7 +16865,7 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="B593" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C593" s="1">
         <x:v>50</x:v>
@@ -17046,7 +17049,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C601" s="1">
         <x:v>0</x:v>
@@ -17069,7 +17072,7 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C602" s="1">
         <x:v>50</x:v>
@@ -17138,7 +17141,7 @@
         <x:v>662</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>50</x:v>
@@ -17184,7 +17187,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>50</x:v>
@@ -17299,7 +17302,7 @@
         <x:v>670</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>0</x:v>
@@ -17368,7 +17371,7 @@
         <x:v>673</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C615" s="1">
         <x:v>0</x:v>
@@ -17506,7 +17509,7 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C621" s="1">
         <x:v>0</x:v>
@@ -17575,7 +17578,7 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C624" s="1">
         <x:v>50</x:v>
@@ -17644,7 +17647,7 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C627" s="1">
         <x:v>50</x:v>
@@ -17667,7 +17670,7 @@
         <x:v>686</x:v>
       </x:c>
       <x:c r="B628" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C628" s="1">
         <x:v>0</x:v>
@@ -17713,7 +17716,7 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C630" s="1">
         <x:v>0</x:v>
@@ -17736,7 +17739,7 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C631" s="1">
         <x:v>50</x:v>
@@ -17851,7 +17854,7 @@
         <x:v>694</x:v>
       </x:c>
       <x:c r="B636" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C636" s="1">
         <x:v>0</x:v>
@@ -17943,7 +17946,7 @@
         <x:v>698</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C640" s="1">
         <x:v>0</x:v>
@@ -17966,7 +17969,7 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="B641" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C641" s="1">
         <x:v>50</x:v>
@@ -18127,7 +18130,7 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B648" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C648" s="1">
         <x:v>50</x:v>
@@ -18265,7 +18268,7 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C654" s="1">
         <x:v>50</x:v>
@@ -18288,7 +18291,7 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C655" s="1">
         <x:v>1000</x:v>
@@ -18403,7 +18406,7 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C660" s="1">
         <x:v>0</x:v>
@@ -18426,7 +18429,7 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C661" s="1">
         <x:v>0</x:v>
@@ -18587,7 +18590,7 @@
         <x:v>727</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C668" s="1">
         <x:v>0</x:v>
@@ -18633,7 +18636,7 @@
         <x:v>729</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C670" s="1">
         <x:v>50</x:v>
@@ -18725,7 +18728,7 @@
         <x:v>733</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C674" s="1">
         <x:v>50</x:v>
@@ -18748,7 +18751,7 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C675" s="1">
         <x:v>50</x:v>
@@ -19024,7 +19027,7 @@
         <x:v>746</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -19047,7 +19050,7 @@
         <x:v>747</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C688" s="1">
         <x:v>50</x:v>
@@ -19070,7 +19073,7 @@
         <x:v>748</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C689" s="1">
         <x:v>50</x:v>
@@ -19208,7 +19211,7 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C695" s="1">
         <x:v>0</x:v>
@@ -19346,10 +19349,10 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C701" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D701" s="1">
         <x:v>0</x:v>
@@ -19358,18 +19361,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>3700</x:v>
+        <x:v>12250</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>3700</x:v>
+        <x:v>12300</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
       <x:c r="A702" s="1" t="s">
-        <x:v>760</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C702" s="1">
         <x:v>50</x:v>
@@ -19381,21 +19384,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F702" s="1">
-        <x:v>8550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>8600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
       <x:c r="A703" s="1" t="s">
-        <x:v>761</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C703" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D703" s="1">
         <x:v>0</x:v>
@@ -19404,21 +19407,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F703" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
       <x:c r="A704" s="1" t="s">
-        <x:v>762</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C704" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D704" s="1">
         <x:v>0</x:v>
@@ -19427,18 +19430,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
       <x:c r="A705" s="1" t="s">
-        <x:v>763</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C705" s="1">
         <x:v>50</x:v>
@@ -19458,10 +19461,10 @@
     </x:row>
     <x:row r="706" spans="1:7">
       <x:c r="A706" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C706" s="1">
         <x:v>50</x:v>
@@ -19481,59 +19484,59 @@
     </x:row>
     <x:row r="707" spans="1:7">
       <x:c r="A707" s="1" t="s">
-        <x:v>765</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D707" s="1">
-        <x:v>0</x:v>
+        <x:v>5962980</x:v>
       </x:c>
       <x:c r="E707" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>0</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>50</x:v>
+        <x:v>5982180</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
       <x:c r="A708" s="1" t="s">
-        <x:v>766</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D708" s="1">
-        <x:v>5962980</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E708" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>18200</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>5982180</x:v>
+        <x:v>163800</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
       <x:c r="A709" s="1" t="s">
-        <x:v>767</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D709" s="1">
         <x:v>0</x:v>
@@ -19542,18 +19545,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>163800</x:v>
+        <x:v>24200</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>163800</x:v>
+        <x:v>24250</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
       <x:c r="A710" s="1" t="s">
-        <x:v>768</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="C710" s="1">
         <x:v>50</x:v>
@@ -19565,21 +19568,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>24200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>24250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
       <x:c r="A711" s="1" t="s">
-        <x:v>769</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>770</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C711" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D711" s="1">
         <x:v>0</x:v>
@@ -19588,18 +19591,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F711" s="1">
-        <x:v>0</x:v>
+        <x:v>14900</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>50</x:v>
+        <x:v>14900</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
       <x:c r="A712" s="1" t="s">
-        <x:v>771</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C712" s="1">
         <x:v>0</x:v>
@@ -19611,18 +19614,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>14900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>14900</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
       <x:c r="A713" s="1" t="s">
-        <x:v>772</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C713" s="1">
         <x:v>0</x:v>
@@ -19642,13 +19645,13 @@
     </x:row>
     <x:row r="714" spans="1:7">
       <x:c r="A714" s="1" t="s">
-        <x:v>773</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D714" s="1">
         <x:v>0</x:v>
@@ -19657,18 +19660,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
       <x:c r="A715" s="1" t="s">
-        <x:v>774</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>775</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C715" s="1">
         <x:v>50</x:v>
@@ -19688,10 +19691,10 @@
     </x:row>
     <x:row r="716" spans="1:7">
       <x:c r="A716" s="1" t="s">
-        <x:v>776</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="C716" s="1">
         <x:v>50</x:v>
@@ -19703,10 +19706,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>0</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>50</x:v>
+        <x:v>560</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19714,10 +19717,10 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>531</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D717" s="1">
         <x:v>0</x:v>
@@ -19726,21 +19729,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>510</x:v>
+        <x:v>2079</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>560</x:v>
+        <x:v>2079</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
       <x:c r="A718" s="1" t="s">
-        <x:v>777</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C718" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D718" s="1">
         <x:v>0</x:v>
@@ -19749,18 +19752,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F718" s="1">
-        <x:v>2079</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>2079</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
       <x:c r="A719" s="1" t="s">
-        <x:v>778</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C719" s="1">
         <x:v>50</x:v>
@@ -19780,13 +19783,13 @@
     </x:row>
     <x:row r="720" spans="1:7">
       <x:c r="A720" s="1" t="s">
-        <x:v>779</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D720" s="1">
         <x:v>0</x:v>
@@ -19795,21 +19798,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F720" s="1">
-        <x:v>0</x:v>
+        <x:v>130400</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>50</x:v>
+        <x:v>132950</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
       <x:c r="A721" s="1" t="s">
-        <x:v>780</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C721" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D721" s="1">
         <x:v>0</x:v>
@@ -19818,18 +19821,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F721" s="1">
-        <x:v>130400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>132950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
       <x:c r="A722" s="1" t="s">
-        <x:v>781</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C722" s="1">
         <x:v>50</x:v>
@@ -19849,13 +19852,13 @@
     </x:row>
     <x:row r="723" spans="1:7">
       <x:c r="A723" s="1" t="s">
-        <x:v>782</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D723" s="1">
         <x:v>0</x:v>
@@ -19864,21 +19867,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F723" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
       <x:c r="A724" s="1" t="s">
-        <x:v>783</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C724" s="1">
-        <x:v>1550</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D724" s="1">
         <x:v>0</x:v>
@@ -19887,21 +19890,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F724" s="1">
-        <x:v>3500</x:v>
+        <x:v>92500</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>5050</x:v>
+        <x:v>92600</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
       <x:c r="A725" s="1" t="s">
-        <x:v>784</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D725" s="1">
         <x:v>0</x:v>
@@ -19910,21 +19913,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F725" s="1">
-        <x:v>92500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>92600</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
       <x:c r="A726" s="1" t="s">
-        <x:v>785</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="C726" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D726" s="1">
         <x:v>0</x:v>
@@ -19933,21 +19936,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F726" s="1">
-        <x:v>1000</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>1000</x:v>
+        <x:v>10550</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
       <x:c r="A727" s="1" t="s">
-        <x:v>786</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>2050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D727" s="1">
         <x:v>0</x:v>
@@ -19956,18 +19959,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F727" s="1">
-        <x:v>8500</x:v>
+        <x:v>25600</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>10550</x:v>
+        <x:v>25600</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
       <x:c r="A728" s="1" t="s">
-        <x:v>787</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C728" s="1">
         <x:v>0</x:v>
@@ -19979,18 +19982,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>25600</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>25600</x:v>
+        <x:v>6634</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
       <x:c r="A729" s="1" t="s">
-        <x:v>788</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C729" s="1">
         <x:v>0</x:v>
@@ -20002,21 +20005,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F729" s="1">
-        <x:v>6634</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>6634</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">
       <x:c r="A730" s="1" t="s">
-        <x:v>789</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C730" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D730" s="1">
         <x:v>0</x:v>
@@ -20025,18 +20028,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F730" s="1">
-        <x:v>77</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>77</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
       <x:c r="A731" s="1" t="s">
-        <x:v>790</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C731" s="1">
         <x:v>50</x:v>
@@ -20048,21 +20051,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F731" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
       <x:c r="A732" s="1" t="s">
-        <x:v>791</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C732" s="1">
-        <x:v>50</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D732" s="1">
         <x:v>0</x:v>
@@ -20071,21 +20074,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F732" s="1">
-        <x:v>1000</x:v>
+        <x:v>52400</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>1050</x:v>
+        <x:v>55350</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
       <x:c r="A733" s="1" t="s">
-        <x:v>792</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C733" s="1">
-        <x:v>2950</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D733" s="1">
         <x:v>0</x:v>
@@ -20094,21 +20097,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F733" s="1">
-        <x:v>52400</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G733" s="1">
-        <x:v>55350</x:v>
+        <x:v>2883</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:7">
       <x:c r="A734" s="1" t="s">
-        <x:v>793</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C734" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D734" s="1">
         <x:v>0</x:v>
@@ -20117,15 +20120,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F734" s="1">
-        <x:v>333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G734" s="1">
-        <x:v>2883</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:7">
       <x:c r="A735" s="1" t="s">
-        <x:v>794</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
         <x:v>18</x:v>
@@ -20148,13 +20151,13 @@
     </x:row>
     <x:row r="736" spans="1:7">
       <x:c r="A736" s="1" t="s">
-        <x:v>795</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -20163,21 +20166,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>0</x:v>
+        <x:v>31800</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>50</x:v>
+        <x:v>34350</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
       <x:c r="A737" s="1" t="s">
-        <x:v>796</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C737" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D737" s="1">
         <x:v>0</x:v>
@@ -20186,21 +20189,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F737" s="1">
-        <x:v>31800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G737" s="1">
-        <x:v>34350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="738" spans="1:7">
       <x:c r="A738" s="1" t="s">
-        <x:v>797</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C738" s="1">
-        <x:v>50</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D738" s="1">
         <x:v>0</x:v>
@@ -20209,21 +20212,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F738" s="1">
-        <x:v>0</x:v>
+        <x:v>84000</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>50</x:v>
+        <x:v>88550</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
       <x:c r="A739" s="1" t="s">
-        <x:v>798</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C739" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D739" s="1">
         <x:v>0</x:v>
@@ -20232,21 +20235,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F739" s="1">
-        <x:v>84000</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G739" s="1">
-        <x:v>88550</x:v>
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:7">
       <x:c r="A740" s="1" t="s">
-        <x:v>799</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D740" s="1">
         <x:v>0</x:v>
@@ -20255,18 +20258,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F740" s="1">
-        <x:v>2600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>2600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
       <x:c r="A741" s="1" t="s">
-        <x:v>800</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C741" s="1">
         <x:v>50</x:v>
@@ -20286,10 +20289,10 @@
     </x:row>
     <x:row r="742" spans="1:7">
       <x:c r="A742" s="1" t="s">
-        <x:v>801</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C742" s="1">
         <x:v>50</x:v>
@@ -20309,10 +20312,10 @@
     </x:row>
     <x:row r="743" spans="1:7">
       <x:c r="A743" s="1" t="s">
-        <x:v>802</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C743" s="1">
         <x:v>50</x:v>
@@ -20332,10 +20335,10 @@
     </x:row>
     <x:row r="744" spans="1:7">
       <x:c r="A744" s="1" t="s">
-        <x:v>803</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C744" s="1">
         <x:v>50</x:v>
@@ -20355,13 +20358,13 @@
     </x:row>
     <x:row r="745" spans="1:7">
       <x:c r="A745" s="1" t="s">
-        <x:v>804</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C745" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D745" s="1">
         <x:v>0</x:v>
@@ -20370,21 +20373,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F745" s="1">
-        <x:v>0</x:v>
+        <x:v>29420</x:v>
       </x:c>
       <x:c r="G745" s="1">
-        <x:v>50</x:v>
+        <x:v>34420</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:7">
       <x:c r="A746" s="1" t="s">
-        <x:v>805</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D746" s="1">
         <x:v>0</x:v>
@@ -20393,21 +20396,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>29420</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>34420</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
       <x:c r="A747" s="1" t="s">
-        <x:v>806</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D747" s="1">
         <x:v>0</x:v>
@@ -20419,18 +20422,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">
       <x:c r="A748" s="1" t="s">
-        <x:v>807</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>5050</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D748" s="1">
         <x:v>0</x:v>
@@ -20439,21 +20442,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F748" s="1">
-        <x:v>0</x:v>
+        <x:v>10800</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>5050</x:v>
+        <x:v>11850</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
       <x:c r="A749" s="1" t="s">
-        <x:v>808</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C749" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D749" s="1">
         <x:v>0</x:v>
@@ -20462,21 +20465,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F749" s="1">
-        <x:v>10800</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G749" s="1">
-        <x:v>11850</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:7">
       <x:c r="A750" s="1" t="s">
-        <x:v>809</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20485,21 +20488,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F750" s="1">
-        <x:v>2700</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>2750</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
       <x:c r="A751" s="1" t="s">
-        <x:v>810</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20508,21 +20511,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F751" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>3300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
       <x:c r="A752" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20531,21 +20534,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>0</x:v>
+        <x:v>39500</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>50</x:v>
+        <x:v>39600</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
       <x:c r="A753" s="1" t="s">
-        <x:v>812</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20554,64 +20557,64 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>39500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>39600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
       <x:c r="A754" s="1" t="s">
-        <x:v>813</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C754" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D754" s="1">
-        <x:v>0</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E754" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F754" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>50</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
       <x:c r="A755" s="1" t="s">
-        <x:v>814</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C755" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D755" s="1">
-        <x:v>10046680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E755" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F755" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>10048730</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
       <x:c r="A756" s="1" t="s">
-        <x:v>815</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C756" s="1">
         <x:v>50</x:v>
@@ -20631,13 +20634,13 @@
     </x:row>
     <x:row r="757" spans="1:7">
       <x:c r="A757" s="1" t="s">
-        <x:v>816</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20646,21 +20649,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
       <x:c r="A758" s="1" t="s">
-        <x:v>817</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20669,21 +20672,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>1000</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>1000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
       <x:c r="A759" s="1" t="s">
-        <x:v>818</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C759" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D759" s="1">
         <x:v>0</x:v>
@@ -20692,21 +20695,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F759" s="1">
-        <x:v>5000</x:v>
+        <x:v>90966</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>5050</x:v>
+        <x:v>97016</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
       <x:c r="A760" s="1" t="s">
-        <x:v>819</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C760" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D760" s="1">
         <x:v>0</x:v>
@@ -20715,18 +20718,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F760" s="1">
-        <x:v>90966</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>97016</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
       <x:c r="A761" s="1" t="s">
-        <x:v>820</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C761" s="1">
         <x:v>50</x:v>
@@ -20746,13 +20749,13 @@
     </x:row>
     <x:row r="762" spans="1:7">
       <x:c r="A762" s="1" t="s">
-        <x:v>821</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C762" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D762" s="1">
         <x:v>0</x:v>
@@ -20761,67 +20764,67 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F762" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">
       <x:c r="A763" s="1" t="s">
-        <x:v>822</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C763" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D763" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E763" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F763" s="1">
-        <x:v>1000</x:v>
+        <x:v>13234</x:v>
       </x:c>
       <x:c r="G763" s="1">
-        <x:v>1000</x:v>
+        <x:v>832403</x:v>
       </x:c>
     </x:row>
     <x:row r="764" spans="1:7">
       <x:c r="A764" s="1" t="s">
-        <x:v>823</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C764" s="1">
-        <x:v>2000</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D764" s="1">
-        <x:v>817169</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E764" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F764" s="1">
-        <x:v>13234</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="G764" s="1">
-        <x:v>832403</x:v>
+        <x:v>56484</x:v>
       </x:c>
     </x:row>
     <x:row r="765" spans="1:7">
       <x:c r="A765" s="1" t="s">
-        <x:v>824</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C765" s="1">
-        <x:v>11050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D765" s="1">
         <x:v>0</x:v>
@@ -20830,18 +20833,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F765" s="1">
-        <x:v>45434</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G765" s="1">
-        <x:v>56484</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="766" spans="1:7">
       <x:c r="A766" s="1" t="s">
-        <x:v>825</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C766" s="1">
         <x:v>50</x:v>
@@ -20853,18 +20856,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>5850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
       <x:c r="A767" s="1" t="s">
-        <x:v>826</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C767" s="1">
         <x:v>50</x:v>
@@ -20876,18 +20879,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F767" s="1">
-        <x:v>0</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G767" s="1">
-        <x:v>50</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:7">
       <x:c r="A768" s="1" t="s">
-        <x:v>827</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C768" s="1">
         <x:v>50</x:v>
@@ -20899,64 +20902,64 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>25000</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>25050</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
       <x:c r="A769" s="1" t="s">
-        <x:v>828</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C769" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D769" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E769" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F769" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G769" s="1">
-        <x:v>5850</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:7">
       <x:c r="A770" s="1" t="s">
-        <x:v>829</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C770" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D770" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E770" s="1">
-        <x:v>1531015</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F770" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G770" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="771" spans="1:7">
       <x:c r="A771" s="1" t="s">
-        <x:v>830</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C771" s="1">
         <x:v>50</x:v>
@@ -20976,148 +20979,148 @@
     </x:row>
     <x:row r="772" spans="1:7">
       <x:c r="A772" s="1" t="s">
-        <x:v>831</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C772" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D772" s="1">
-        <x:v>0</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E772" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F772" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G772" s="1">
-        <x:v>50</x:v>
+        <x:v>5591032</x:v>
       </x:c>
     </x:row>
     <x:row r="773" spans="1:7">
       <x:c r="A773" s="1" t="s">
-        <x:v>832</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C773" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D773" s="1">
-        <x:v>5583432</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E773" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F773" s="1">
-        <x:v>6600</x:v>
+        <x:v>27300</x:v>
       </x:c>
       <x:c r="G773" s="1">
-        <x:v>5591032</x:v>
+        <x:v>27350</x:v>
       </x:c>
     </x:row>
     <x:row r="774" spans="1:7">
       <x:c r="A774" s="1" t="s">
-        <x:v>833</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C774" s="1">
-        <x:v>50</x:v>
+        <x:v>18050</x:v>
       </x:c>
       <x:c r="D774" s="1">
-        <x:v>0</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="E774" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F774" s="1">
-        <x:v>27300</x:v>
+        <x:v>81382</x:v>
       </x:c>
       <x:c r="G774" s="1">
-        <x:v>27350</x:v>
+        <x:v>863638</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:7">
       <x:c r="A775" s="1" t="s">
-        <x:v>834</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C775" s="1">
-        <x:v>18050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D775" s="1">
-        <x:v>764206</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E775" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>81382</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>863638</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
       <x:c r="A776" s="1" t="s">
-        <x:v>835</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C776" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D776" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E776" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>2700</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
       <x:c r="A777" s="1" t="s">
-        <x:v>836</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C777" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D777" s="1">
-        <x:v>1543316</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E777" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F777" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G777" s="1">
-        <x:v>1543316</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="778" spans="1:7">
       <x:c r="A778" s="1" t="s">
-        <x:v>837</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C778" s="1">
         <x:v>50</x:v>
@@ -21129,18 +21132,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F778" s="1">
-        <x:v>14500</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>14550</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
       <x:c r="A779" s="1" t="s">
-        <x:v>838</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C779" s="1">
         <x:v>50</x:v>
@@ -21152,18 +21155,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F779" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G779" s="1">
-        <x:v>5850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="780" spans="1:7">
       <x:c r="A780" s="1" t="s">
-        <x:v>839</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C780" s="1">
         <x:v>50</x:v>
@@ -21183,33 +21186,33 @@
     </x:row>
     <x:row r="781" spans="1:7">
       <x:c r="A781" s="1" t="s">
-        <x:v>840</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C781" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D781" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E781" s="1">
-        <x:v>0</x:v>
+        <x:v>15154476</x:v>
       </x:c>
       <x:c r="F781" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
       <x:c r="A782" s="1" t="s">
-        <x:v>841</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="B782" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C782" s="1">
         <x:v>0</x:v>
@@ -21218,21 +21221,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E782" s="1">
-        <x:v>15154476</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F782" s="1">
-        <x:v>0</x:v>
+        <x:v>16800</x:v>
       </x:c>
       <x:c r="G782" s="1">
-        <x:v>0</x:v>
+        <x:v>16800</x:v>
       </x:c>
     </x:row>
     <x:row r="783" spans="1:7">
       <x:c r="A783" s="1" t="s">
-        <x:v>842</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="B783" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C783" s="1">
         <x:v>0</x:v>
@@ -21244,102 +21247,102 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F783" s="1">
-        <x:v>16800</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G783" s="1">
-        <x:v>16800</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="784" spans="1:7">
       <x:c r="A784" s="1" t="s">
-        <x:v>843</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="B784" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C784" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D784" s="1">
-        <x:v>0</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="E784" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F784" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G784" s="1">
-        <x:v>2700</x:v>
+        <x:v>106947</x:v>
       </x:c>
     </x:row>
     <x:row r="785" spans="1:7">
       <x:c r="A785" s="1" t="s">
-        <x:v>844</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="B785" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C785" s="1">
-        <x:v>0</x:v>
+        <x:v>10050</x:v>
       </x:c>
       <x:c r="D785" s="1">
-        <x:v>106947</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E785" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F785" s="1">
-        <x:v>0</x:v>
+        <x:v>1945889</x:v>
       </x:c>
       <x:c r="G785" s="1">
-        <x:v>106947</x:v>
+        <x:v>1955939</x:v>
       </x:c>
     </x:row>
     <x:row r="786" spans="1:7">
       <x:c r="A786" s="1" t="s">
-        <x:v>845</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="B786" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C786" s="1">
-        <x:v>10050</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D786" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E786" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F786" s="1">
-        <x:v>1945889</x:v>
+        <x:v>26650</x:v>
       </x:c>
       <x:c r="G786" s="1">
-        <x:v>1955939</x:v>
+        <x:v>929876</x:v>
       </x:c>
     </x:row>
     <x:row r="787" spans="1:7">
       <x:c r="A787" s="1" t="s">
-        <x:v>846</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="B787" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C787" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D787" s="1">
-        <x:v>902176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E787" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F787" s="1">
-        <x:v>26650</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G787" s="1">
-        <x:v>929876</x:v>
+        <x:v>26550</x:v>
       </x:c>
     </x:row>
     <x:row r="788" spans="1:7">
@@ -21347,10 +21350,10 @@
         <x:v>847</x:v>
       </x:c>
       <x:c r="B788" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C788" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D788" s="1">
         <x:v>0</x:v>
@@ -21359,18 +21362,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F788" s="1">
-        <x:v>26500</x:v>
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="G788" s="1">
-        <x:v>26550</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="789" spans="1:7">
       <x:c r="A789" s="1" t="s">
-        <x:v>847</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="B789" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C789" s="1">
         <x:v>0</x:v>
@@ -21382,21 +21385,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F789" s="1">
-        <x:v>1800</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G789" s="1">
-        <x:v>1800</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="790" spans="1:7">
       <x:c r="A790" s="1" t="s">
-        <x:v>848</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="B790" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C790" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D790" s="1">
         <x:v>0</x:v>
@@ -21405,21 +21408,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F790" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G790" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="791" spans="1:7">
       <x:c r="A791" s="1" t="s">
-        <x:v>849</x:v>
+        <x:v>850</x:v>
       </x:c>
       <x:c r="B791" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C791" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D791" s="1">
         <x:v>0</x:v>
@@ -21428,18 +21431,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F791" s="1">
-        <x:v>0</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G791" s="1">
-        <x:v>50</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="792" spans="1:7">
       <x:c r="A792" s="1" t="s">
-        <x:v>850</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="B792" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C792" s="1">
         <x:v>0</x:v>
@@ -21451,21 +21454,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F792" s="1">
-        <x:v>10500</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G792" s="1">
-        <x:v>10500</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="793" spans="1:7">
       <x:c r="A793" s="1" t="s">
-        <x:v>851</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="B793" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C793" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D793" s="1">
         <x:v>0</x:v>
@@ -21474,21 +21477,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F793" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G793" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="794" spans="1:7">
       <x:c r="A794" s="1" t="s">
-        <x:v>852</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="B794" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C794" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D794" s="1">
         <x:v>0</x:v>
@@ -21497,21 +21500,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F794" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G794" s="1">
-        <x:v>50</x:v>
+        <x:v>4300</x:v>
       </x:c>
     </x:row>
     <x:row r="795" spans="1:7">
       <x:c r="A795" s="1" t="s">
-        <x:v>853</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="B795" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C795" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D795" s="1">
         <x:v>0</x:v>
@@ -21520,67 +21523,67 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F795" s="1">
-        <x:v>3300</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G795" s="1">
-        <x:v>4300</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="796" spans="1:7">
       <x:c r="A796" s="1" t="s">
-        <x:v>854</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="B796" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C796" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D796" s="1">
-        <x:v>0</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="E796" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F796" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G796" s="1">
-        <x:v>6650</x:v>
+        <x:v>1010142</x:v>
       </x:c>
     </x:row>
     <x:row r="797" spans="1:7">
       <x:c r="A797" s="1" t="s">
-        <x:v>855</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="B797" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C797" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D797" s="1">
-        <x:v>1010142</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E797" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F797" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G797" s="1">
-        <x:v>1010142</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="798" spans="1:7">
       <x:c r="A798" s="1" t="s">
-        <x:v>856</x:v>
+        <x:v>857</x:v>
       </x:c>
       <x:c r="B798" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="C798" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D798" s="1">
         <x:v>0</x:v>
@@ -21589,21 +21592,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F798" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G798" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="799" spans="1:7">
       <x:c r="A799" s="1" t="s">
-        <x:v>857</x:v>
+        <x:v>858</x:v>
       </x:c>
       <x:c r="B799" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C799" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D799" s="1">
         <x:v>0</x:v>
@@ -21612,21 +21615,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F799" s="1">
-        <x:v>0</x:v>
+        <x:v>39400</x:v>
       </x:c>
       <x:c r="G799" s="1">
-        <x:v>50</x:v>
+        <x:v>45950</x:v>
       </x:c>
     </x:row>
     <x:row r="800" spans="1:7">
       <x:c r="A800" s="1" t="s">
-        <x:v>858</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="B800" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C800" s="1">
-        <x:v>6550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D800" s="1">
         <x:v>0</x:v>
@@ -21635,18 +21638,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F800" s="1">
-        <x:v>39400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G800" s="1">
-        <x:v>45950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="801" spans="1:7">
       <x:c r="A801" s="1" t="s">
-        <x:v>859</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="B801" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C801" s="1">
         <x:v>50</x:v>
@@ -21666,13 +21669,13 @@
     </x:row>
     <x:row r="802" spans="1:7">
       <x:c r="A802" s="1" t="s">
-        <x:v>860</x:v>
+        <x:v>861</x:v>
       </x:c>
       <x:c r="B802" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C802" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D802" s="1">
         <x:v>0</x:v>
@@ -21681,21 +21684,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F802" s="1">
-        <x:v>0</x:v>
+        <x:v>20900</x:v>
       </x:c>
       <x:c r="G802" s="1">
-        <x:v>50</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="803" spans="1:7">
       <x:c r="A803" s="1" t="s">
-        <x:v>861</x:v>
+        <x:v>862</x:v>
       </x:c>
       <x:c r="B803" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C803" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D803" s="1">
         <x:v>0</x:v>
@@ -21704,21 +21707,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F803" s="1">
-        <x:v>20900</x:v>
+        <x:v>5400</x:v>
       </x:c>
       <x:c r="G803" s="1">
-        <x:v>24450</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="804" spans="1:7">
       <x:c r="A804" s="1" t="s">
-        <x:v>862</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="B804" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C804" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D804" s="1">
         <x:v>0</x:v>
@@ -21727,21 +21730,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F804" s="1">
-        <x:v>5400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G804" s="1">
-        <x:v>5400</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="805" spans="1:7">
       <x:c r="A805" s="1" t="s">
-        <x:v>863</x:v>
+        <x:v>864</x:v>
       </x:c>
       <x:c r="B805" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C805" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D805" s="1">
         <x:v>0</x:v>
@@ -21750,64 +21753,64 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F805" s="1">
-        <x:v>0</x:v>
+        <x:v>21433</x:v>
       </x:c>
       <x:c r="G805" s="1">
-        <x:v>50</x:v>
+        <x:v>24983</x:v>
       </x:c>
     </x:row>
     <x:row r="806" spans="1:7">
       <x:c r="A806" s="1" t="s">
-        <x:v>864</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="B806" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C806" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D806" s="1">
-        <x:v>0</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="E806" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F806" s="1">
-        <x:v>21433</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G806" s="1">
-        <x:v>24983</x:v>
+        <x:v>1872095</x:v>
       </x:c>
     </x:row>
     <x:row r="807" spans="1:7">
       <x:c r="A807" s="1" t="s">
-        <x:v>865</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="B807" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C807" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D807" s="1">
-        <x:v>1860445</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E807" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F807" s="1">
-        <x:v>11600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G807" s="1">
-        <x:v>1872095</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="808" spans="1:7">
       <x:c r="A808" s="1" t="s">
-        <x:v>866</x:v>
+        <x:v>867</x:v>
       </x:c>
       <x:c r="B808" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C808" s="1">
         <x:v>50</x:v>
@@ -21819,18 +21822,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F808" s="1">
-        <x:v>0</x:v>
+        <x:v>16484</x:v>
       </x:c>
       <x:c r="G808" s="1">
-        <x:v>50</x:v>
+        <x:v>16534</x:v>
       </x:c>
     </x:row>
     <x:row r="809" spans="1:7">
       <x:c r="A809" s="1" t="s">
-        <x:v>867</x:v>
+        <x:v>868</x:v>
       </x:c>
       <x:c r="B809" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C809" s="1">
         <x:v>50</x:v>
@@ -21842,21 +21845,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F809" s="1">
-        <x:v>16484</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G809" s="1">
-        <x:v>16534</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="810" spans="1:7">
       <x:c r="A810" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="B810" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C810" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D810" s="1">
         <x:v>0</x:v>
@@ -21865,21 +21868,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F810" s="1">
-        <x:v>0</x:v>
+        <x:v>6300</x:v>
       </x:c>
       <x:c r="G810" s="1">
-        <x:v>50</x:v>
+        <x:v>6300</x:v>
       </x:c>
     </x:row>
     <x:row r="811" spans="1:7">
       <x:c r="A811" s="1" t="s">
-        <x:v>869</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="B811" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="C811" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D811" s="1">
         <x:v>0</x:v>
@@ -21888,21 +21891,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F811" s="1">
-        <x:v>6300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G811" s="1">
-        <x:v>6300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="812" spans="1:7">
       <x:c r="A812" s="1" t="s">
-        <x:v>870</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="B812" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C812" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D812" s="1">
         <x:v>0</x:v>
@@ -21911,18 +21914,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F812" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G812" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="813" spans="1:7">
       <x:c r="A813" s="1" t="s">
-        <x:v>871</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="B813" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C813" s="1">
         <x:v>50</x:v>
@@ -21934,15 +21937,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F813" s="1">
-        <x:v>11000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="G813" s="1">
-        <x:v>11050</x:v>
+        <x:v>9050</x:v>
       </x:c>
     </x:row>
     <x:row r="814" spans="1:7">
       <x:c r="A814" s="1" t="s">
-        <x:v>872</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="B814" s="1" t="s">
         <x:v>382</x:v>
@@ -21965,7 +21968,7 @@
     </x:row>
     <x:row r="815" spans="1:7">
       <x:c r="A815" s="1" t="s">
-        <x:v>873</x:v>
+        <x:v>874</x:v>
       </x:c>
       <x:c r="B815" s="1" t="s">
         <x:v>12</x:v>
@@ -21988,7 +21991,7 @@
     </x:row>
     <x:row r="816" spans="1:7">
       <x:c r="A816" s="1" t="s">
-        <x:v>874</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="B816" s="1" t="s">
         <x:v>43</x:v>
@@ -22011,10 +22014,10 @@
     </x:row>
     <x:row r="817" spans="1:7">
       <x:c r="A817" s="1" t="s">
-        <x:v>875</x:v>
+        <x:v>876</x:v>
       </x:c>
       <x:c r="B817" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C817" s="1">
         <x:v>0</x:v>
@@ -22034,7 +22037,7 @@
     </x:row>
     <x:row r="818" spans="1:7">
       <x:c r="A818" s="1" t="s">
-        <x:v>876</x:v>
+        <x:v>877</x:v>
       </x:c>
       <x:c r="B818" s="1" t="s">
         <x:v>41</x:v>
@@ -22057,7 +22060,7 @@
     </x:row>
     <x:row r="819" spans="1:7">
       <x:c r="A819" s="1" t="s">
-        <x:v>877</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="B819" s="1" t="s">
         <x:v>12</x:v>
@@ -22080,7 +22083,7 @@
     </x:row>
     <x:row r="820" spans="1:7">
       <x:c r="A820" s="1" t="s">
-        <x:v>878</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="B820" s="1" t="s">
         <x:v>22</x:v>
@@ -22103,10 +22106,10 @@
     </x:row>
     <x:row r="821" spans="1:7">
       <x:c r="A821" s="1" t="s">
-        <x:v>879</x:v>
+        <x:v>880</x:v>
       </x:c>
       <x:c r="B821" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C821" s="1">
         <x:v>0</x:v>
@@ -22126,7 +22129,7 @@
     </x:row>
     <x:row r="822" spans="1:7">
       <x:c r="A822" s="1" t="s">
-        <x:v>880</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="B822" s="1" t="s">
         <x:v>10</x:v>
@@ -22149,7 +22152,7 @@
     </x:row>
     <x:row r="823" spans="1:7">
       <x:c r="A823" s="1" t="s">
-        <x:v>881</x:v>
+        <x:v>882</x:v>
       </x:c>
       <x:c r="B823" s="1" t="s">
         <x:v>51</x:v>
@@ -22172,7 +22175,7 @@
     </x:row>
     <x:row r="824" spans="1:7">
       <x:c r="A824" s="1" t="s">
-        <x:v>882</x:v>
+        <x:v>883</x:v>
       </x:c>
       <x:c r="B824" s="1" t="s">
         <x:v>74</x:v>
@@ -22195,7 +22198,7 @@
     </x:row>
     <x:row r="825" spans="1:7">
       <x:c r="A825" s="1" t="s">
-        <x:v>883</x:v>
+        <x:v>884</x:v>
       </x:c>
       <x:c r="B825" s="1" t="s">
         <x:v>382</x:v>
@@ -22218,7 +22221,7 @@
     </x:row>
     <x:row r="826" spans="1:7">
       <x:c r="A826" s="1" t="s">
-        <x:v>884</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="B826" s="1" t="s">
         <x:v>65</x:v>
@@ -22241,7 +22244,7 @@
     </x:row>
     <x:row r="827" spans="1:7">
       <x:c r="A827" s="1" t="s">
-        <x:v>885</x:v>
+        <x:v>886</x:v>
       </x:c>
       <x:c r="B827" s="1" t="s">
         <x:v>24</x:v>
@@ -22264,7 +22267,7 @@
     </x:row>
     <x:row r="828" spans="1:7">
       <x:c r="A828" s="1" t="s">
-        <x:v>886</x:v>
+        <x:v>887</x:v>
       </x:c>
       <x:c r="B828" s="1" t="s">
         <x:v>12</x:v>
@@ -22287,10 +22290,10 @@
     </x:row>
     <x:row r="829" spans="1:7">
       <x:c r="A829" s="1" t="s">
-        <x:v>887</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="B829" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C829" s="1">
         <x:v>50</x:v>
@@ -22310,7 +22313,7 @@
     </x:row>
     <x:row r="830" spans="1:7">
       <x:c r="A830" s="1" t="s">
-        <x:v>888</x:v>
+        <x:v>889</x:v>
       </x:c>
       <x:c r="B830" s="1" t="s">
         <x:v>20</x:v>
@@ -22333,7 +22336,7 @@
     </x:row>
     <x:row r="831" spans="1:7">
       <x:c r="A831" s="1" t="s">
-        <x:v>889</x:v>
+        <x:v>890</x:v>
       </x:c>
       <x:c r="B831" s="1" t="s">
         <x:v>22</x:v>
@@ -22356,7 +22359,7 @@
     </x:row>
     <x:row r="832" spans="1:7">
       <x:c r="A832" s="1" t="s">
-        <x:v>890</x:v>
+        <x:v>891</x:v>
       </x:c>
       <x:c r="B832" s="1" t="s">
         <x:v>16</x:v>
@@ -22379,7 +22382,7 @@
     </x:row>
     <x:row r="833" spans="1:7">
       <x:c r="A833" s="1" t="s">
-        <x:v>891</x:v>
+        <x:v>892</x:v>
       </x:c>
       <x:c r="B833" s="1" t="s">
         <x:v>358</x:v>
@@ -22402,7 +22405,7 @@
     </x:row>
     <x:row r="834" spans="1:7">
       <x:c r="A834" s="1" t="s">
-        <x:v>892</x:v>
+        <x:v>893</x:v>
       </x:c>
       <x:c r="B834" s="1" t="s">
         <x:v>51</x:v>
@@ -22425,7 +22428,7 @@
     </x:row>
     <x:row r="835" spans="1:7">
       <x:c r="A835" s="1" t="s">
-        <x:v>893</x:v>
+        <x:v>894</x:v>
       </x:c>
       <x:c r="B835" s="1" t="s">
         <x:v>47</x:v>
@@ -22448,7 +22451,7 @@
     </x:row>
     <x:row r="836" spans="1:7">
       <x:c r="A836" s="1" t="s">
-        <x:v>894</x:v>
+        <x:v>895</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
         <x:v>12</x:v>
@@ -22471,7 +22474,7 @@
     </x:row>
     <x:row r="837" spans="1:7">
       <x:c r="A837" s="1" t="s">
-        <x:v>895</x:v>
+        <x:v>896</x:v>
       </x:c>
       <x:c r="B837" s="1" t="s">
         <x:v>382</x:v>
@@ -22494,7 +22497,7 @@
     </x:row>
     <x:row r="838" spans="1:7">
       <x:c r="A838" s="1" t="s">
-        <x:v>896</x:v>
+        <x:v>897</x:v>
       </x:c>
       <x:c r="B838" s="1" t="s">
         <x:v>20</x:v>
@@ -22517,7 +22520,7 @@
     </x:row>
     <x:row r="839" spans="1:7">
       <x:c r="A839" s="1" t="s">
-        <x:v>897</x:v>
+        <x:v>898</x:v>
       </x:c>
       <x:c r="B839" s="1" t="s">
         <x:v>20</x:v>
@@ -22540,7 +22543,7 @@
     </x:row>
     <x:row r="840" spans="1:7">
       <x:c r="A840" s="1" t="s">
-        <x:v>898</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="B840" s="1" t="s">
         <x:v>43</x:v>
@@ -22563,7 +22566,7 @@
     </x:row>
     <x:row r="841" spans="1:7">
       <x:c r="A841" s="1" t="s">
-        <x:v>899</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="B841" s="1" t="s">
         <x:v>65</x:v>
@@ -22586,7 +22589,7 @@
     </x:row>
     <x:row r="842" spans="1:7">
       <x:c r="A842" s="1" t="s">
-        <x:v>900</x:v>
+        <x:v>901</x:v>
       </x:c>
       <x:c r="B842" s="1" t="s">
         <x:v>36</x:v>
@@ -22609,7 +22612,7 @@
     </x:row>
     <x:row r="843" spans="1:7">
       <x:c r="A843" s="1" t="s">
-        <x:v>901</x:v>
+        <x:v>902</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
         <x:v>32</x:v>
@@ -22632,7 +22635,7 @@
     </x:row>
     <x:row r="844" spans="1:7">
       <x:c r="A844" s="1" t="s">
-        <x:v>902</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
         <x:v>49</x:v>
@@ -22655,7 +22658,7 @@
     </x:row>
     <x:row r="845" spans="1:7">
       <x:c r="A845" s="1" t="s">
-        <x:v>903</x:v>
+        <x:v>904</x:v>
       </x:c>
       <x:c r="B845" s="1" t="s">
         <x:v>72</x:v>
@@ -22678,7 +22681,7 @@
     </x:row>
     <x:row r="846" spans="1:7">
       <x:c r="A846" s="1" t="s">
-        <x:v>904</x:v>
+        <x:v>905</x:v>
       </x:c>
       <x:c r="B846" s="1" t="s">
         <x:v>24</x:v>
@@ -22701,10 +22704,10 @@
     </x:row>
     <x:row r="847" spans="1:7">
       <x:c r="A847" s="1" t="s">
-        <x:v>905</x:v>
+        <x:v>906</x:v>
       </x:c>
       <x:c r="B847" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C847" s="1">
         <x:v>50</x:v>
@@ -22724,7 +22727,7 @@
     </x:row>
     <x:row r="848" spans="1:7">
       <x:c r="A848" s="1" t="s">
-        <x:v>906</x:v>
+        <x:v>907</x:v>
       </x:c>
       <x:c r="B848" s="1" t="s">
         <x:v>8</x:v>
@@ -22747,7 +22750,7 @@
     </x:row>
     <x:row r="849" spans="1:7">
       <x:c r="A849" s="1" t="s">
-        <x:v>907</x:v>
+        <x:v>908</x:v>
       </x:c>
       <x:c r="B849" s="1" t="s">
         <x:v>18</x:v>
@@ -22770,7 +22773,7 @@
     </x:row>
     <x:row r="850" spans="1:7">
       <x:c r="A850" s="1" t="s">
-        <x:v>908</x:v>
+        <x:v>909</x:v>
       </x:c>
       <x:c r="B850" s="1" t="s">
         <x:v>32</x:v>
@@ -22793,7 +22796,7 @@
     </x:row>
     <x:row r="851" spans="1:7">
       <x:c r="A851" s="1" t="s">
-        <x:v>909</x:v>
+        <x:v>910</x:v>
       </x:c>
       <x:c r="B851" s="1" t="s">
         <x:v>49</x:v>
@@ -22816,10 +22819,10 @@
     </x:row>
     <x:row r="852" spans="1:7">
       <x:c r="A852" s="1" t="s">
-        <x:v>910</x:v>
+        <x:v>911</x:v>
       </x:c>
       <x:c r="B852" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C852" s="1">
         <x:v>0</x:v>
@@ -22839,10 +22842,10 @@
     </x:row>
     <x:row r="853" spans="1:7">
       <x:c r="A853" s="1" t="s">
-        <x:v>911</x:v>
+        <x:v>912</x:v>
       </x:c>
       <x:c r="B853" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C853" s="1">
         <x:v>50</x:v>
@@ -22862,7 +22865,7 @@
     </x:row>
     <x:row r="854" spans="1:7">
       <x:c r="A854" s="1" t="s">
-        <x:v>912</x:v>
+        <x:v>913</x:v>
       </x:c>
       <x:c r="B854" s="1" t="s">
         <x:v>32</x:v>
@@ -22885,7 +22888,7 @@
     </x:row>
     <x:row r="855" spans="1:7">
       <x:c r="A855" s="1" t="s">
-        <x:v>913</x:v>
+        <x:v>914</x:v>
       </x:c>
       <x:c r="B855" s="1" t="s">
         <x:v>18</x:v>
@@ -22908,7 +22911,7 @@
     </x:row>
     <x:row r="856" spans="1:7">
       <x:c r="A856" s="1" t="s">
-        <x:v>914</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="B856" s="1" t="s">
         <x:v>41</x:v>
@@ -22931,10 +22934,10 @@
     </x:row>
     <x:row r="857" spans="1:7">
       <x:c r="A857" s="1" t="s">
-        <x:v>914</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="B857" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C857" s="1">
         <x:v>0</x:v>
@@ -22954,10 +22957,10 @@
     </x:row>
     <x:row r="858" spans="1:7">
       <x:c r="A858" s="1" t="s">
-        <x:v>915</x:v>
+        <x:v>916</x:v>
       </x:c>
       <x:c r="B858" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C858" s="1">
         <x:v>50</x:v>
@@ -22977,7 +22980,7 @@
     </x:row>
     <x:row r="859" spans="1:7">
       <x:c r="A859" s="1" t="s">
-        <x:v>916</x:v>
+        <x:v>917</x:v>
       </x:c>
       <x:c r="B859" s="1" t="s">
         <x:v>12</x:v>
@@ -23000,7 +23003,7 @@
     </x:row>
     <x:row r="860" spans="1:7">
       <x:c r="A860" s="1" t="s">
-        <x:v>917</x:v>
+        <x:v>918</x:v>
       </x:c>
       <x:c r="B860" s="1" t="s">
         <x:v>241</x:v>
@@ -23023,7 +23026,7 @@
     </x:row>
     <x:row r="861" spans="1:7">
       <x:c r="A861" s="1" t="s">
-        <x:v>918</x:v>
+        <x:v>919</x:v>
       </x:c>
       <x:c r="B861" s="1" t="s">
         <x:v>32</x:v>
@@ -23046,7 +23049,7 @@
     </x:row>
     <x:row r="862" spans="1:7">
       <x:c r="A862" s="1" t="s">
-        <x:v>919</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="B862" s="1" t="s">
         <x:v>20</x:v>
@@ -23069,10 +23072,10 @@
     </x:row>
     <x:row r="863" spans="1:7">
       <x:c r="A863" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>921</x:v>
       </x:c>
       <x:c r="B863" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C863" s="1">
         <x:v>50</x:v>
@@ -23092,7 +23095,7 @@
     </x:row>
     <x:row r="864" spans="1:7">
       <x:c r="A864" s="1" t="s">
-        <x:v>921</x:v>
+        <x:v>922</x:v>
       </x:c>
       <x:c r="B864" s="1" t="s">
         <x:v>12</x:v>
@@ -23115,7 +23118,7 @@
     </x:row>
     <x:row r="865" spans="1:7">
       <x:c r="A865" s="1" t="s">
-        <x:v>922</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="B865" s="1" t="s">
         <x:v>531</x:v>
@@ -23138,7 +23141,7 @@
     </x:row>
     <x:row r="866" spans="1:7">
       <x:c r="A866" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>924</x:v>
       </x:c>
       <x:c r="B866" s="1" t="s">
         <x:v>51</x:v>
@@ -23161,10 +23164,10 @@
     </x:row>
     <x:row r="867" spans="1:7">
       <x:c r="A867" s="1" t="s">
-        <x:v>924</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="B867" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C867" s="1">
         <x:v>0</x:v>
@@ -23184,10 +23187,10 @@
     </x:row>
     <x:row r="868" spans="1:7">
       <x:c r="A868" s="1" t="s">
-        <x:v>925</x:v>
+        <x:v>926</x:v>
       </x:c>
       <x:c r="B868" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C868" s="1">
         <x:v>50</x:v>
@@ -23207,7 +23210,7 @@
     </x:row>
     <x:row r="869" spans="1:7">
       <x:c r="A869" s="1" t="s">
-        <x:v>926</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="B869" s="1" t="s">
         <x:v>32</x:v>
@@ -23230,7 +23233,7 @@
     </x:row>
     <x:row r="870" spans="1:7">
       <x:c r="A870" s="1" t="s">
-        <x:v>927</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="B870" s="1" t="s">
         <x:v>8</x:v>
@@ -23253,7 +23256,7 @@
     </x:row>
     <x:row r="871" spans="1:7">
       <x:c r="A871" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="B871" s="1" t="s">
         <x:v>28</x:v>
@@ -23276,7 +23279,7 @@
     </x:row>
     <x:row r="872" spans="1:7">
       <x:c r="A872" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="B872" s="1" t="s">
         <x:v>12</x:v>
@@ -23299,7 +23302,7 @@
     </x:row>
     <x:row r="873" spans="1:7">
       <x:c r="A873" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="B873" s="1" t="s">
         <x:v>378</x:v>
@@ -23322,10 +23325,10 @@
     </x:row>
     <x:row r="874" spans="1:7">
       <x:c r="A874" s="1" t="s">
-        <x:v>931</x:v>
+        <x:v>932</x:v>
       </x:c>
       <x:c r="B874" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C874" s="1">
         <x:v>50</x:v>
@@ -23345,7 +23348,7 @@
     </x:row>
     <x:row r="875" spans="1:7">
       <x:c r="A875" s="1" t="s">
-        <x:v>932</x:v>
+        <x:v>933</x:v>
       </x:c>
       <x:c r="B875" s="1" t="s">
         <x:v>43</x:v>
@@ -23368,7 +23371,7 @@
     </x:row>
     <x:row r="876" spans="1:7">
       <x:c r="A876" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="B876" s="1" t="s">
         <x:v>20</x:v>
@@ -23391,10 +23394,10 @@
     </x:row>
     <x:row r="877" spans="1:7">
       <x:c r="A877" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>935</x:v>
       </x:c>
       <x:c r="B877" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C877" s="1">
         <x:v>50</x:v>
@@ -23414,10 +23417,10 @@
     </x:row>
     <x:row r="878" spans="1:7">
       <x:c r="A878" s="1" t="s">
-        <x:v>935</x:v>
+        <x:v>936</x:v>
       </x:c>
       <x:c r="B878" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C878" s="1">
         <x:v>50</x:v>
@@ -23437,7 +23440,7 @@
     </x:row>
     <x:row r="879" spans="1:7">
       <x:c r="A879" s="1" t="s">
-        <x:v>936</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="B879" s="1" t="s">
         <x:v>32</x:v>
@@ -23460,10 +23463,10 @@
     </x:row>
     <x:row r="880" spans="1:7">
       <x:c r="A880" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="B880" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C880" s="1">
         <x:v>50</x:v>
@@ -23483,7 +23486,7 @@
     </x:row>
     <x:row r="881" spans="1:7">
       <x:c r="A881" s="1" t="s">
-        <x:v>938</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="B881" s="1" t="s">
         <x:v>20</x:v>
@@ -23506,10 +23509,10 @@
     </x:row>
     <x:row r="882" spans="1:7">
       <x:c r="A882" s="1" t="s">
-        <x:v>939</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="B882" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C882" s="1">
         <x:v>10850</x:v>
@@ -23529,10 +23532,10 @@
     </x:row>
     <x:row r="883" spans="1:7">
       <x:c r="A883" s="1" t="s">
-        <x:v>940</x:v>
+        <x:v>941</x:v>
       </x:c>
       <x:c r="B883" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C883" s="1">
         <x:v>0</x:v>
@@ -23552,7 +23555,7 @@
     </x:row>
     <x:row r="884" spans="1:7">
       <x:c r="A884" s="1" t="s">
-        <x:v>941</x:v>
+        <x:v>942</x:v>
       </x:c>
       <x:c r="B884" s="1" t="s">
         <x:v>57</x:v>
@@ -23575,10 +23578,10 @@
     </x:row>
     <x:row r="885" spans="1:7">
       <x:c r="A885" s="1" t="s">
-        <x:v>942</x:v>
+        <x:v>943</x:v>
       </x:c>
       <x:c r="B885" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C885" s="1">
         <x:v>50</x:v>
@@ -23598,7 +23601,7 @@
     </x:row>
     <x:row r="886" spans="1:7">
       <x:c r="A886" s="1" t="s">
-        <x:v>943</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="B886" s="1" t="s">
         <x:v>70</x:v>
@@ -23621,7 +23624,7 @@
     </x:row>
     <x:row r="887" spans="1:7">
       <x:c r="A887" s="1" t="s">
-        <x:v>944</x:v>
+        <x:v>945</x:v>
       </x:c>
       <x:c r="B887" s="1" t="s">
         <x:v>49</x:v>
@@ -23644,7 +23647,7 @@
     </x:row>
     <x:row r="888" spans="1:7">
       <x:c r="A888" s="1" t="s">
-        <x:v>945</x:v>
+        <x:v>946</x:v>
       </x:c>
       <x:c r="B888" s="1" t="s">
         <x:v>43</x:v>
@@ -23667,10 +23670,10 @@
     </x:row>
     <x:row r="889" spans="1:7">
       <x:c r="A889" s="1" t="s">
-        <x:v>946</x:v>
+        <x:v>947</x:v>
       </x:c>
       <x:c r="B889" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C889" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -18893,7 +18893,7 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C683" s="1">
         <x:v>0</x:v>
@@ -18916,7 +18916,7 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C684" s="1">
         <x:v>0</x:v>
@@ -19422,10 +19422,10 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D706" s="1">
         <x:v>0</x:v>
@@ -19434,10 +19434,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>2079</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>2079</x:v>
+        <x:v>560</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -19445,10 +19445,10 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D707" s="1">
         <x:v>0</x:v>
@@ -19457,10 +19457,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>510</x:v>
+        <x:v>2079</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>560</x:v>
+        <x:v>2079</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
@@ -22527,7 +22527,7 @@
         <x:v>897</x:v>
       </x:c>
       <x:c r="B841" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C841" s="1">
         <x:v>0</x:v>
@@ -22539,10 +22539,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F841" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G841" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="842" spans="1:7">
@@ -22550,7 +22550,7 @@
         <x:v>897</x:v>
       </x:c>
       <x:c r="B842" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C842" s="1">
         <x:v>0</x:v>
@@ -22562,10 +22562,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F842" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G842" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="843" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -22642,10 +22642,10 @@
         <x:v>901</x:v>
       </x:c>
       <x:c r="B846" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C846" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D846" s="1">
         <x:v>0</x:v>
@@ -22654,10 +22654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F846" s="1">
-        <x:v>0</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="G846" s="1">
-        <x:v>50</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="847" spans="1:7">
@@ -22665,10 +22665,10 @@
         <x:v>901</x:v>
       </x:c>
       <x:c r="B847" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C847" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D847" s="1">
         <x:v>0</x:v>
@@ -22677,10 +22677,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F847" s="1">
-        <x:v>485</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G847" s="1">
-        <x:v>485</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="848" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -21081,10 +21081,10 @@
         <x:v>835</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C778" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D778" s="1">
         <x:v>0</x:v>
@@ -21093,10 +21093,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F778" s="1">
-        <x:v>1800</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>1800</x:v>
+        <x:v>26550</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
@@ -21104,10 +21104,10 @@
         <x:v>835</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C779" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D779" s="1">
         <x:v>0</x:v>
@@ -21116,10 +21116,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F779" s="1">
-        <x:v>26500</x:v>
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="G779" s="1">
-        <x:v>26550</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="780" spans="1:7">
@@ -22553,7 +22553,7 @@
         <x:v>898</x:v>
       </x:c>
       <x:c r="B842" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C842" s="1">
         <x:v>0</x:v>
@@ -22565,10 +22565,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F842" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G842" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="843" spans="1:7">
@@ -22576,7 +22576,7 @@
         <x:v>898</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C843" s="1">
         <x:v>0</x:v>
@@ -22588,10 +22588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -22668,10 +22668,10 @@
         <x:v>902</x:v>
       </x:c>
       <x:c r="B847" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C847" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D847" s="1">
         <x:v>0</x:v>
@@ -22680,10 +22680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F847" s="1">
-        <x:v>0</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="G847" s="1">
-        <x:v>50</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="848" spans="1:7">
@@ -22691,10 +22691,10 @@
         <x:v>902</x:v>
       </x:c>
       <x:c r="B848" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C848" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D848" s="1">
         <x:v>0</x:v>
@@ -22703,10 +22703,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F848" s="1">
-        <x:v>485</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G848" s="1">
-        <x:v>485</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="849" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -18919,7 +18919,7 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C684" s="1">
         <x:v>0</x:v>
@@ -18942,7 +18942,7 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C685" s="1">
         <x:v>0</x:v>
@@ -22668,10 +22668,10 @@
         <x:v>902</x:v>
       </x:c>
       <x:c r="B847" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C847" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D847" s="1">
         <x:v>0</x:v>
@@ -22680,10 +22680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F847" s="1">
-        <x:v>485</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G847" s="1">
-        <x:v>485</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="848" spans="1:7">
@@ -22691,10 +22691,10 @@
         <x:v>902</x:v>
       </x:c>
       <x:c r="B848" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C848" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D848" s="1">
         <x:v>0</x:v>
@@ -22703,10 +22703,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F848" s="1">
-        <x:v>0</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="G848" s="1">
-        <x:v>50</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="849" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -18971,7 +18971,7 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>0</x:v>
@@ -18994,7 +18994,7 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -21133,10 +21133,10 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C780" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D780" s="1">
         <x:v>0</x:v>
@@ -21145,10 +21145,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F780" s="1">
-        <x:v>1800</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G780" s="1">
-        <x:v>1800</x:v>
+        <x:v>26550</x:v>
       </x:c>
     </x:row>
     <x:row r="781" spans="1:7">
@@ -21156,10 +21156,10 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C781" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D781" s="1">
         <x:v>0</x:v>
@@ -21168,10 +21168,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F781" s="1">
-        <x:v>26500</x:v>
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>26550</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -6350,7 +6350,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D137" s="1">
-        <x:v>102144</x:v>
+        <x:v>161489</x:v>
       </x:c>
       <x:c r="E137" s="1">
         <x:v>0</x:v>
@@ -6359,7 +6359,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="G137" s="1">
-        <x:v>109144</x:v>
+        <x:v>168489</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">
@@ -22605,7 +22605,7 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C844" s="1">
         <x:v>0</x:v>
@@ -22617,10 +22617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -22628,7 +22628,7 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="B845" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C845" s="1">
         <x:v>0</x:v>
@@ -22640,10 +22640,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F845" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G845" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="846" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -6350,7 +6350,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D137" s="1">
-        <x:v>161489</x:v>
+        <x:v>882245</x:v>
       </x:c>
       <x:c r="E137" s="1">
         <x:v>0</x:v>
@@ -6359,7 +6359,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="G137" s="1">
-        <x:v>168489</x:v>
+        <x:v>889245</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">
@@ -18971,7 +18971,7 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>0</x:v>
@@ -18994,7 +18994,7 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -6350,7 +6350,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D137" s="1">
-        <x:v>882245</x:v>
+        <x:v>996447</x:v>
       </x:c>
       <x:c r="E137" s="1">
         <x:v>0</x:v>
@@ -6359,7 +6359,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="G137" s="1">
-        <x:v>889245</x:v>
+        <x:v>1003447</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -18971,7 +18971,7 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>0</x:v>
@@ -18994,7 +18994,7 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -21133,10 +21133,10 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C780" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D780" s="1">
         <x:v>0</x:v>
@@ -21145,10 +21145,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F780" s="1">
-        <x:v>26500</x:v>
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="G780" s="1">
-        <x:v>26550</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="781" spans="1:7">
@@ -21156,10 +21156,10 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C781" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D781" s="1">
         <x:v>0</x:v>
@@ -21168,10 +21168,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F781" s="1">
-        <x:v>1800</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>1800</x:v>
+        <x:v>26550</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
@@ -22605,7 +22605,7 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C844" s="1">
         <x:v>0</x:v>
@@ -22617,10 +22617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -22628,7 +22628,7 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="B845" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C845" s="1">
         <x:v>0</x:v>
@@ -22640,10 +22640,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F845" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G845" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="846" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -6350,7 +6350,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D137" s="1">
-        <x:v>996447</x:v>
+        <x:v>1052492</x:v>
       </x:c>
       <x:c r="E137" s="1">
         <x:v>0</x:v>
@@ -6359,7 +6359,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="G137" s="1">
-        <x:v>1003447</x:v>
+        <x:v>1059492</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">
@@ -13624,10 +13624,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F453" s="1">
-        <x:v>35800</x:v>
+        <x:v>32300</x:v>
       </x:c>
       <x:c r="G453" s="1">
-        <x:v>35850</x:v>
+        <x:v>32350</x:v>
       </x:c>
     </x:row>
     <x:row r="454" spans="1:7">
@@ -13877,10 +13877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F464" s="1">
-        <x:v>22333</x:v>
+        <x:v>32833</x:v>
       </x:c>
       <x:c r="G464" s="1">
-        <x:v>26833</x:v>
+        <x:v>37333</x:v>
       </x:c>
     </x:row>
     <x:row r="465" spans="1:7">
@@ -18971,7 +18971,7 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>0</x:v>
@@ -18994,7 +18994,7 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -19213,10 +19213,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>14000</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>14000</x:v>
+        <x:v>24000</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -21133,10 +21133,10 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C780" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D780" s="1">
         <x:v>0</x:v>
@@ -21145,10 +21145,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F780" s="1">
-        <x:v>1800</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G780" s="1">
-        <x:v>1800</x:v>
+        <x:v>26550</x:v>
       </x:c>
     </x:row>
     <x:row r="781" spans="1:7">
@@ -21156,10 +21156,10 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C781" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D781" s="1">
         <x:v>0</x:v>
@@ -21168,10 +21168,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F781" s="1">
-        <x:v>26500</x:v>
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>26550</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
@@ -22605,7 +22605,7 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C844" s="1">
         <x:v>0</x:v>
@@ -22617,10 +22617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -22628,7 +22628,7 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="B845" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C845" s="1">
         <x:v>0</x:v>
@@ -22640,10 +22640,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F845" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G845" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="846" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -18971,7 +18971,7 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>0</x:v>
@@ -18994,7 +18994,7 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -19500,10 +19500,10 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D709" s="1">
         <x:v>0</x:v>
@@ -19512,10 +19512,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>510</x:v>
+        <x:v>2079</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>560</x:v>
+        <x:v>2079</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -19523,10 +19523,10 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="C710" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D710" s="1">
         <x:v>0</x:v>
@@ -19535,10 +19535,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>2079</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>2079</x:v>
+        <x:v>560</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
@@ -22605,7 +22605,7 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C844" s="1">
         <x:v>0</x:v>
@@ -22617,10 +22617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -22628,7 +22628,7 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="B845" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C845" s="1">
         <x:v>0</x:v>
@@ -22640,10 +22640,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F845" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G845" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="846" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -2048,6 +2048,9 @@
   </x:si>
   <x:si>
     <x:t>PAULINA LUNA, ANNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
   </x:si>
   <x:si>
     <x:t>PAYNE, DONALD M MR. JR</x:t>
@@ -2895,8 +2898,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G882" totalsRowShown="0">
-  <x:autoFilter ref="A1:G882"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G883" totalsRowShown="0">
+  <x:autoFilter ref="A1:G883"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -3198,7 +3201,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G882"/>
+  <x:dimension ref="A1:G883"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -14147,7 +14150,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D476" s="1">
-        <x:v>0</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E476" s="1">
         <x:v>0</x:v>
@@ -14156,7 +14159,7 @@
         <x:v>3900</x:v>
       </x:c>
       <x:c r="G476" s="1">
-        <x:v>3900</x:v>
+        <x:v>353900</x:v>
       </x:c>
     </x:row>
     <x:row r="477" spans="1:7">
@@ -17476,13 +17479,13 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C621" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D621" s="1">
-        <x:v>0</x:v>
+        <x:v>3500000</x:v>
       </x:c>
       <x:c r="E621" s="1">
         <x:v>0</x:v>
@@ -17491,7 +17494,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G621" s="1">
-        <x:v>50</x:v>
+        <x:v>3500000</x:v>
       </x:c>
     </x:row>
     <x:row r="622" spans="1:7">
@@ -17499,22 +17502,22 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C622" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D622" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E622" s="1">
-        <x:v>20483</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F622" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G622" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="623" spans="1:7">
@@ -17522,22 +17525,22 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C623" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D623" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E623" s="1">
-        <x:v>0</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="F623" s="1">
-        <x:v>803700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G623" s="1">
-        <x:v>803750</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="624" spans="1:7">
@@ -17545,22 +17548,22 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C624" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D624" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E624" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F624" s="1">
-        <x:v>9900</x:v>
+        <x:v>803700</x:v>
       </x:c>
       <x:c r="G624" s="1">
-        <x:v>1937606</x:v>
+        <x:v>803750</x:v>
       </x:c>
     </x:row>
     <x:row r="625" spans="1:7">
@@ -17568,22 +17571,22 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D625" s="1">
-        <x:v>0</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="E625" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>0</x:v>
+        <x:v>9900</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>50</x:v>
+        <x:v>1937606</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17591,10 +17594,10 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17603,10 +17606,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17614,10 +17617,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17626,10 +17629,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>7082</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>7132</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -17637,7 +17640,7 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B628" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C628" s="1">
         <x:v>50</x:v>
@@ -17649,10 +17652,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F628" s="1">
-        <x:v>0</x:v>
+        <x:v>7082</x:v>
       </x:c>
       <x:c r="G628" s="1">
-        <x:v>50</x:v>
+        <x:v>7132</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:7">
@@ -17660,10 +17663,10 @@
         <x:v>686</x:v>
       </x:c>
       <x:c r="B629" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C629" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D629" s="1">
         <x:v>0</x:v>
@@ -17672,10 +17675,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F629" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G629" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="630" spans="1:7">
@@ -17683,7 +17686,7 @@
         <x:v>687</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C630" s="1">
         <x:v>0</x:v>
@@ -17706,10 +17709,10 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D631" s="1">
         <x:v>0</x:v>
@@ -17718,10 +17721,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>533</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>583</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -17729,7 +17732,7 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C632" s="1">
         <x:v>50</x:v>
@@ -17741,10 +17744,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>15000</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>15050</x:v>
+        <x:v>583</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17752,22 +17755,22 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C633" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D633" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E633" s="1">
-        <x:v>817066</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F633" s="1">
-        <x:v>0</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="G633" s="1">
-        <x:v>0</x:v>
+        <x:v>15050</x:v>
       </x:c>
     </x:row>
     <x:row r="634" spans="1:7">
@@ -17775,22 +17778,22 @@
         <x:v>691</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C634" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D634" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E634" s="1">
-        <x:v>0</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="F634" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G634" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="635" spans="1:7">
@@ -17798,7 +17801,7 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C635" s="1">
         <x:v>50</x:v>
@@ -17821,22 +17824,22 @@
         <x:v>693</x:v>
       </x:c>
       <x:c r="B636" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C636" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D636" s="1">
-        <x:v>88256</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E636" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F636" s="1">
-        <x:v>49284</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G636" s="1">
-        <x:v>151540</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="637" spans="1:7">
@@ -17844,22 +17847,22 @@
         <x:v>694</x:v>
       </x:c>
       <x:c r="B637" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C637" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D637" s="1">
-        <x:v>0</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="E637" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F637" s="1">
-        <x:v>0</x:v>
+        <x:v>49284</x:v>
       </x:c>
       <x:c r="G637" s="1">
-        <x:v>50</x:v>
+        <x:v>151540</x:v>
       </x:c>
     </x:row>
     <x:row r="638" spans="1:7">
@@ -17867,7 +17870,7 @@
         <x:v>695</x:v>
       </x:c>
       <x:c r="B638" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C638" s="1">
         <x:v>50</x:v>
@@ -17890,7 +17893,7 @@
         <x:v>696</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>697</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C639" s="1">
         <x:v>50</x:v>
@@ -17910,10 +17913,10 @@
     </x:row>
     <x:row r="640" spans="1:7">
       <x:c r="A640" s="1" t="s">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="B640" s="1" t="s">
         <x:v>698</x:v>
-      </x:c>
-      <x:c r="B640" s="1" t="s">
-        <x:v>16</x:v>
       </x:c>
       <x:c r="C640" s="1">
         <x:v>50</x:v>
@@ -17936,10 +17939,10 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="B641" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C641" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D641" s="1">
         <x:v>0</x:v>
@@ -17948,10 +17951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F641" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G641" s="1">
-        <x:v>6000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="642" spans="1:7">
@@ -17962,19 +17965,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C642" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D642" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E642" s="1">
-        <x:v>10041119</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F642" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G642" s="1">
-        <x:v>50</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:7">
@@ -17982,7 +17985,7 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B643" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C643" s="1">
         <x:v>50</x:v>
@@ -17991,13 +17994,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E643" s="1">
-        <x:v>0</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="F643" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G643" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="644" spans="1:7">
@@ -18005,7 +18008,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C644" s="1">
         <x:v>50</x:v>
@@ -18017,10 +18020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F644" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -18028,10 +18031,10 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D645" s="1">
         <x:v>0</x:v>
@@ -18040,10 +18043,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -18051,10 +18054,10 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D646" s="1">
         <x:v>0</x:v>
@@ -18063,10 +18066,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F646" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -18074,7 +18077,7 @@
         <x:v>705</x:v>
       </x:c>
       <x:c r="B647" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C647" s="1">
         <x:v>50</x:v>
@@ -18097,7 +18100,7 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B648" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C648" s="1">
         <x:v>50</x:v>
@@ -18120,10 +18123,10 @@
         <x:v>707</x:v>
       </x:c>
       <x:c r="B649" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C649" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D649" s="1">
         <x:v>0</x:v>
@@ -18132,10 +18135,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F649" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G649" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:7">
@@ -18143,7 +18146,7 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C650" s="1">
         <x:v>0</x:v>
@@ -18155,10 +18158,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F650" s="1">
-        <x:v>71940</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G650" s="1">
-        <x:v>71940</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:7">
@@ -18166,22 +18169,22 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C651" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D651" s="1">
-        <x:v>1491280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E651" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F651" s="1">
-        <x:v>6600</x:v>
+        <x:v>71940</x:v>
       </x:c>
       <x:c r="G651" s="1">
-        <x:v>1497880</x:v>
+        <x:v>71940</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:7">
@@ -18189,22 +18192,22 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C652" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D652" s="1">
-        <x:v>0</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="E652" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F652" s="1">
-        <x:v>500</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>500</x:v>
+        <x:v>1497880</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -18212,10 +18215,10 @@
         <x:v>711</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D653" s="1">
         <x:v>0</x:v>
@@ -18224,10 +18227,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F653" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
@@ -18235,7 +18238,7 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C654" s="1">
         <x:v>50</x:v>
@@ -18247,10 +18250,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F654" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G654" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="655" spans="1:7">
@@ -18258,7 +18261,7 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C655" s="1">
         <x:v>50</x:v>
@@ -18270,10 +18273,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F655" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G655" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="656" spans="1:7">
@@ -18281,7 +18284,7 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C656" s="1">
         <x:v>50</x:v>
@@ -18293,10 +18296,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F656" s="1">
-        <x:v>1287</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>1337</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -18304,10 +18307,10 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C657" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D657" s="1">
         <x:v>0</x:v>
@@ -18316,10 +18319,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F657" s="1">
-        <x:v>6697</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G657" s="1">
-        <x:v>6697</x:v>
+        <x:v>1337</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:7">
@@ -18327,7 +18330,7 @@
         <x:v>716</x:v>
       </x:c>
       <x:c r="B658" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C658" s="1">
         <x:v>0</x:v>
@@ -18339,10 +18342,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F658" s="1">
-        <x:v>6600</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="G658" s="1">
-        <x:v>6600</x:v>
+        <x:v>6697</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:7">
@@ -18350,7 +18353,7 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C659" s="1">
         <x:v>0</x:v>
@@ -18362,10 +18365,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F659" s="1">
-        <x:v>5200</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G659" s="1">
-        <x:v>5200</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:7">
@@ -18373,10 +18376,10 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D660" s="1">
         <x:v>0</x:v>
@@ -18385,10 +18388,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F660" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18396,10 +18399,10 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
         <x:v>0</x:v>
@@ -18408,10 +18411,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F661" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18419,7 +18422,7 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C662" s="1">
         <x:v>0</x:v>
@@ -18431,10 +18434,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F662" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -18442,10 +18445,10 @@
         <x:v>721</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C663" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D663" s="1">
         <x:v>0</x:v>
@@ -18454,10 +18457,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F663" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G663" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:7">
@@ -18465,7 +18468,7 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B664" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C664" s="1">
         <x:v>50</x:v>
@@ -18488,7 +18491,7 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B665" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C665" s="1">
         <x:v>50</x:v>
@@ -18511,22 +18514,22 @@
         <x:v>724</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C666" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D666" s="1">
-        <x:v>700000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E666" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F666" s="1">
-        <x:v>50200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G666" s="1">
-        <x:v>752700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:7">
@@ -18534,22 +18537,22 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C667" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D667" s="1">
-        <x:v>0</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="E667" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F667" s="1">
-        <x:v>0</x:v>
+        <x:v>50200</x:v>
       </x:c>
       <x:c r="G667" s="1">
-        <x:v>50</x:v>
+        <x:v>752700</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:7">
@@ -18557,10 +18560,10 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C668" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D668" s="1">
         <x:v>0</x:v>
@@ -18569,10 +18572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F668" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -18580,10 +18583,10 @@
         <x:v>727</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C669" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D669" s="1">
         <x:v>0</x:v>
@@ -18592,10 +18595,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F669" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
@@ -18603,7 +18606,7 @@
         <x:v>728</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C670" s="1">
         <x:v>50</x:v>
@@ -18626,7 +18629,7 @@
         <x:v>729</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C671" s="1">
         <x:v>50</x:v>
@@ -18649,7 +18652,7 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B672" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C672" s="1">
         <x:v>50</x:v>
@@ -18672,7 +18675,7 @@
         <x:v>731</x:v>
       </x:c>
       <x:c r="B673" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C673" s="1">
         <x:v>50</x:v>
@@ -18695,7 +18698,7 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C674" s="1">
         <x:v>50</x:v>
@@ -18718,22 +18721,22 @@
         <x:v>733</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C675" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D675" s="1">
-        <x:v>183694</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E675" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F675" s="1">
-        <x:v>50346</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G675" s="1">
-        <x:v>234040</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:7">
@@ -18741,22 +18744,22 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B676" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C676" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D676" s="1">
-        <x:v>0</x:v>
+        <x:v>183694</x:v>
       </x:c>
       <x:c r="E676" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F676" s="1">
-        <x:v>1500</x:v>
+        <x:v>50346</x:v>
       </x:c>
       <x:c r="G676" s="1">
-        <x:v>1500</x:v>
+        <x:v>234040</x:v>
       </x:c>
     </x:row>
     <x:row r="677" spans="1:7">
@@ -18764,7 +18767,7 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B677" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C677" s="1">
         <x:v>0</x:v>
@@ -18776,10 +18779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F677" s="1">
-        <x:v>94400</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>94400</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
@@ -18787,10 +18790,10 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B678" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C678" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D678" s="1">
         <x:v>0</x:v>
@@ -18799,10 +18802,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F678" s="1">
-        <x:v>0</x:v>
+        <x:v>94400</x:v>
       </x:c>
       <x:c r="G678" s="1">
-        <x:v>50</x:v>
+        <x:v>94400</x:v>
       </x:c>
     </x:row>
     <x:row r="679" spans="1:7">
@@ -18810,7 +18813,7 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C679" s="1">
         <x:v>50</x:v>
@@ -18833,10 +18836,10 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D680" s="1">
         <x:v>0</x:v>
@@ -18848,7 +18851,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -18856,10 +18859,10 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D681" s="1">
         <x:v>0</x:v>
@@ -18871,7 +18874,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -18879,7 +18882,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C682" s="1">
         <x:v>50</x:v>
@@ -18891,10 +18894,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>2750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -18902,10 +18905,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -18914,10 +18917,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>10000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>10000</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -18925,7 +18928,7 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C684" s="1">
         <x:v>0</x:v>
@@ -18937,10 +18940,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>5400</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>5400</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -18948,7 +18951,7 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C685" s="1">
         <x:v>0</x:v>
@@ -18960,10 +18963,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>1000</x:v>
+        <x:v>5400</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>1000</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -18971,30 +18974,30 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D686" s="1">
-        <x:v>106708</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>106708</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
       <x:c r="A687" s="1" t="s">
-        <x:v>744</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
@@ -19017,22 +19020,22 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C688" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D688" s="1">
-        <x:v>0</x:v>
+        <x:v>106708</x:v>
       </x:c>
       <x:c r="E688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F688" s="1">
-        <x:v>5600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>5650</x:v>
+        <x:v>106708</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
@@ -19040,10 +19043,10 @@
         <x:v>746</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C689" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D689" s="1">
         <x:v>0</x:v>
@@ -19052,10 +19055,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F689" s="1">
-        <x:v>30811</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G689" s="1">
-        <x:v>42861</x:v>
+        <x:v>5650</x:v>
       </x:c>
     </x:row>
     <x:row r="690" spans="1:7">
@@ -19063,10 +19066,10 @@
         <x:v>747</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>100</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -19075,10 +19078,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>0</x:v>
+        <x:v>30811</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>100</x:v>
+        <x:v>42861</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -19086,10 +19089,10 @@
         <x:v>748</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -19098,10 +19101,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>3350</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -19109,7 +19112,7 @@
         <x:v>749</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C692" s="1">
         <x:v>50</x:v>
@@ -19121,10 +19124,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>50</x:v>
+        <x:v>3350</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -19132,7 +19135,7 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C693" s="1">
         <x:v>50</x:v>
@@ -19144,21 +19147,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F693" s="1">
-        <x:v>8550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>8600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
       <x:c r="A694" s="1" t="s">
-        <x:v>750</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C694" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D694" s="1">
         <x:v>0</x:v>
@@ -19167,10 +19170,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F694" s="1">
-        <x:v>3700</x:v>
+        <x:v>8550</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>3700</x:v>
+        <x:v>8600</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
@@ -19178,10 +19181,10 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C695" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D695" s="1">
         <x:v>0</x:v>
@@ -19190,10 +19193,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F695" s="1">
-        <x:v>0</x:v>
+        <x:v>3700</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>50</x:v>
+        <x:v>3700</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
@@ -19201,10 +19204,10 @@
         <x:v>752</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D696" s="1">
         <x:v>0</x:v>
@@ -19213,10 +19216,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>24000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -19224,10 +19227,10 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C697" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D697" s="1">
         <x:v>0</x:v>
@@ -19236,10 +19239,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F697" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>50</x:v>
+        <x:v>24000</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">
@@ -19247,7 +19250,7 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C698" s="1">
         <x:v>50</x:v>
@@ -19270,7 +19273,7 @@
         <x:v>755</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C699" s="1">
         <x:v>50</x:v>
@@ -19293,22 +19296,22 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C700" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D700" s="1">
-        <x:v>3975320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E700" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F700" s="1">
-        <x:v>18200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>3994520</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
@@ -19316,22 +19319,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C701" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D701" s="1">
-        <x:v>0</x:v>
+        <x:v>3975320</x:v>
       </x:c>
       <x:c r="E701" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>163800</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>163800</x:v>
+        <x:v>3994520</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
@@ -19339,10 +19342,10 @@
         <x:v>758</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C702" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D702" s="1">
         <x:v>0</x:v>
@@ -19351,10 +19354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F702" s="1">
-        <x:v>24200</x:v>
+        <x:v>163800</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>24250</x:v>
+        <x:v>163800</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
@@ -19362,7 +19365,7 @@
         <x:v>759</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>760</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C703" s="1">
         <x:v>50</x:v>
@@ -19374,21 +19377,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F703" s="1">
-        <x:v>0</x:v>
+        <x:v>24200</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>50</x:v>
+        <x:v>24250</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
       <x:c r="A704" s="1" t="s">
+        <x:v>760</x:v>
+      </x:c>
+      <x:c r="B704" s="1" t="s">
         <x:v>761</x:v>
       </x:c>
-      <x:c r="B704" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C704" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D704" s="1">
         <x:v>0</x:v>
@@ -19397,10 +19400,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>14900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>14900</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
@@ -19408,7 +19411,7 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C705" s="1">
         <x:v>0</x:v>
@@ -19420,10 +19423,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>1000</x:v>
+        <x:v>14900</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>1000</x:v>
+        <x:v>14900</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19431,7 +19434,7 @@
         <x:v>763</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C706" s="1">
         <x:v>0</x:v>
@@ -19454,10 +19457,10 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>765</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D707" s="1">
         <x:v>0</x:v>
@@ -19466,18 +19469,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
       <x:c r="A708" s="1" t="s">
+        <x:v>765</x:v>
+      </x:c>
+      <x:c r="B708" s="1" t="s">
         <x:v>766</x:v>
-      </x:c>
-      <x:c r="B708" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C708" s="1">
         <x:v>50</x:v>
@@ -19500,10 +19503,10 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D709" s="1">
         <x:v>0</x:v>
@@ -19512,15 +19515,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>2079</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>2079</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
       <x:c r="A710" s="1" t="s">
-        <x:v>767</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
         <x:v>524</x:v>
@@ -19546,10 +19549,10 @@
         <x:v>768</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C711" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D711" s="1">
         <x:v>0</x:v>
@@ -19558,10 +19561,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F711" s="1">
-        <x:v>0</x:v>
+        <x:v>2079</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>50</x:v>
+        <x:v>2079</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
@@ -19569,7 +19572,7 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C712" s="1">
         <x:v>50</x:v>
@@ -19592,10 +19595,10 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D713" s="1">
         <x:v>0</x:v>
@@ -19604,10 +19607,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>130400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>132950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19615,10 +19618,10 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D714" s="1">
         <x:v>0</x:v>
@@ -19627,10 +19630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>0</x:v>
+        <x:v>130400</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>50</x:v>
+        <x:v>132950</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19638,7 +19641,7 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C715" s="1">
         <x:v>50</x:v>
@@ -19661,10 +19664,10 @@
         <x:v>773</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D716" s="1">
         <x:v>0</x:v>
@@ -19673,10 +19676,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19684,10 +19687,10 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D717" s="1">
         <x:v>0</x:v>
@@ -19696,10 +19699,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>92500</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>92550</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
@@ -19707,10 +19710,10 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C718" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D718" s="1">
         <x:v>0</x:v>
@@ -19719,10 +19722,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F718" s="1">
-        <x:v>1000</x:v>
+        <x:v>92500</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>1000</x:v>
+        <x:v>92550</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
@@ -19733,7 +19736,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C719" s="1">
-        <x:v>2050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D719" s="1">
         <x:v>0</x:v>
@@ -19742,10 +19745,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F719" s="1">
-        <x:v>8500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G719" s="1">
-        <x:v>10550</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="720" spans="1:7">
@@ -19756,7 +19759,7 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D720" s="1">
         <x:v>0</x:v>
@@ -19765,10 +19768,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F720" s="1">
-        <x:v>25600</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>25600</x:v>
+        <x:v>10550</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
@@ -19776,7 +19779,7 @@
         <x:v>778</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C721" s="1">
         <x:v>0</x:v>
@@ -19788,10 +19791,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F721" s="1">
-        <x:v>6634</x:v>
+        <x:v>25600</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>6634</x:v>
+        <x:v>25600</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
@@ -19799,7 +19802,7 @@
         <x:v>779</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C722" s="1">
         <x:v>0</x:v>
@@ -19811,10 +19814,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F722" s="1">
-        <x:v>77</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>77</x:v>
+        <x:v>6634</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
@@ -19822,10 +19825,10 @@
         <x:v>780</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D723" s="1">
         <x:v>0</x:v>
@@ -19834,10 +19837,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F723" s="1">
-        <x:v>0</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>50</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
@@ -19845,7 +19848,7 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C724" s="1">
         <x:v>50</x:v>
@@ -19857,10 +19860,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F724" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
@@ -19868,10 +19871,10 @@
         <x:v>782</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D725" s="1">
         <x:v>0</x:v>
@@ -19880,10 +19883,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F725" s="1">
-        <x:v>52400</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>55350</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
@@ -19891,10 +19894,10 @@
         <x:v>783</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C726" s="1">
-        <x:v>2550</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D726" s="1">
         <x:v>0</x:v>
@@ -19903,10 +19906,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F726" s="1">
-        <x:v>333</x:v>
+        <x:v>52400</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>2883</x:v>
+        <x:v>55350</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
@@ -19914,10 +19917,10 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D727" s="1">
         <x:v>0</x:v>
@@ -19926,10 +19929,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F727" s="1">
-        <x:v>0</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>50</x:v>
+        <x:v>2883</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
@@ -19960,10 +19963,10 @@
         <x:v>786</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C729" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D729" s="1">
         <x:v>0</x:v>
@@ -19972,10 +19975,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F729" s="1">
-        <x:v>31800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>34350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">
@@ -19983,10 +19986,10 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C730" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D730" s="1">
         <x:v>0</x:v>
@@ -19995,10 +19998,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F730" s="1">
-        <x:v>0</x:v>
+        <x:v>31800</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>50</x:v>
+        <x:v>34350</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
@@ -20006,10 +20009,10 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C731" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D731" s="1">
         <x:v>0</x:v>
@@ -20018,10 +20021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F731" s="1">
-        <x:v>84000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>88550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
@@ -20029,10 +20032,10 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C732" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D732" s="1">
         <x:v>0</x:v>
@@ -20041,10 +20044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F732" s="1">
-        <x:v>2600</x:v>
+        <x:v>84000</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>2600</x:v>
+        <x:v>88550</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
@@ -20052,10 +20055,10 @@
         <x:v>790</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C733" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D733" s="1">
         <x:v>0</x:v>
@@ -20064,10 +20067,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F733" s="1">
-        <x:v>0</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G733" s="1">
-        <x:v>50</x:v>
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:7">
@@ -20075,7 +20078,7 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C734" s="1">
         <x:v>50</x:v>
@@ -20098,7 +20101,7 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C735" s="1">
         <x:v>50</x:v>
@@ -20121,7 +20124,7 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C736" s="1">
         <x:v>50</x:v>
@@ -20144,7 +20147,7 @@
         <x:v>794</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C737" s="1">
         <x:v>50</x:v>
@@ -20167,10 +20170,10 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C738" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D738" s="1">
         <x:v>0</x:v>
@@ -20179,10 +20182,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F738" s="1">
-        <x:v>29420</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>34420</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
@@ -20190,10 +20193,10 @@
         <x:v>796</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C739" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D739" s="1">
         <x:v>0</x:v>
@@ -20202,10 +20205,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F739" s="1">
-        <x:v>0</x:v>
+        <x:v>29420</x:v>
       </x:c>
       <x:c r="G739" s="1">
-        <x:v>50</x:v>
+        <x:v>34420</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:7">
@@ -20213,10 +20216,10 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D740" s="1">
         <x:v>0</x:v>
@@ -20228,7 +20231,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
@@ -20236,10 +20239,10 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C741" s="1">
-        <x:v>1050</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D741" s="1">
         <x:v>0</x:v>
@@ -20248,10 +20251,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F741" s="1">
-        <x:v>10800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>11850</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">
@@ -20259,10 +20262,10 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C742" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D742" s="1">
         <x:v>0</x:v>
@@ -20271,10 +20274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F742" s="1">
-        <x:v>2700</x:v>
+        <x:v>10800</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>2750</x:v>
+        <x:v>11850</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
@@ -20282,10 +20285,10 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C743" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D743" s="1">
         <x:v>0</x:v>
@@ -20294,10 +20297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F743" s="1">
-        <x:v>3300</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G743" s="1">
-        <x:v>3300</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="744" spans="1:7">
@@ -20305,10 +20308,10 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C744" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D744" s="1">
         <x:v>0</x:v>
@@ -20317,10 +20320,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F744" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G744" s="1">
-        <x:v>50</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:7">
@@ -20328,7 +20331,7 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C745" s="1">
         <x:v>50</x:v>
@@ -20340,10 +20343,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F745" s="1">
-        <x:v>39500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G745" s="1">
-        <x:v>39550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:7">
@@ -20351,7 +20354,7 @@
         <x:v>803</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C746" s="1">
         <x:v>50</x:v>
@@ -20363,10 +20366,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>0</x:v>
+        <x:v>39500</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>50</x:v>
+        <x:v>39550</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20374,22 +20377,22 @@
         <x:v>804</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C747" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D747" s="1">
-        <x:v>10046680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E747" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F747" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>10048730</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">
@@ -20397,22 +20400,22 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C748" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D748" s="1">
-        <x:v>0</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E748" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F748" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>50</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
@@ -20420,7 +20423,7 @@
         <x:v>806</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C749" s="1">
         <x:v>50</x:v>
@@ -20443,10 +20446,10 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20455,10 +20458,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F750" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
@@ -20466,10 +20469,10 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20478,10 +20481,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F751" s="1">
-        <x:v>5000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>5050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
@@ -20489,10 +20492,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20501,10 +20504,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>90966</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>97016</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
@@ -20512,10 +20515,10 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20524,10 +20527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>0</x:v>
+        <x:v>90966</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>50</x:v>
+        <x:v>97016</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
@@ -20535,7 +20538,7 @@
         <x:v>811</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C754" s="1">
         <x:v>50</x:v>
@@ -20558,10 +20561,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -20570,10 +20573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F755" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
@@ -20581,22 +20584,22 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C756" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D756" s="1">
-        <x:v>817169</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E756" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F756" s="1">
-        <x:v>13234</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>832403</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">
@@ -20604,22 +20607,22 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>11050</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D757" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E757" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>45434</x:v>
+        <x:v>13234</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>56484</x:v>
+        <x:v>832403</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20627,10 +20630,10 @@
         <x:v>815</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20639,10 +20642,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>5800</x:v>
+        <x:v>45434</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>5850</x:v>
+        <x:v>56484</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
@@ -20650,7 +20653,7 @@
         <x:v>816</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C759" s="1">
         <x:v>50</x:v>
@@ -20662,10 +20665,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F759" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
@@ -20673,7 +20676,7 @@
         <x:v>817</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C760" s="1">
         <x:v>50</x:v>
@@ -20685,10 +20688,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F760" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>25050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
@@ -20696,7 +20699,7 @@
         <x:v>818</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C761" s="1">
         <x:v>50</x:v>
@@ -20708,10 +20711,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F761" s="1">
-        <x:v>5800</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>5850</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">
@@ -20719,22 +20722,22 @@
         <x:v>819</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C762" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D762" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E762" s="1">
-        <x:v>1531015</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F762" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>0</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">
@@ -20742,22 +20745,22 @@
         <x:v>820</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C763" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D763" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E763" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F763" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G763" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="764" spans="1:7">
@@ -20765,7 +20768,7 @@
         <x:v>821</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C764" s="1">
         <x:v>50</x:v>
@@ -20788,22 +20791,22 @@
         <x:v>822</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C765" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D765" s="1">
-        <x:v>5583432</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E765" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F765" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G765" s="1">
-        <x:v>5591032</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="766" spans="1:7">
@@ -20811,22 +20814,22 @@
         <x:v>823</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C766" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D766" s="1">
-        <x:v>0</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E766" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>27300</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>27350</x:v>
+        <x:v>5591032</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
@@ -20834,22 +20837,22 @@
         <x:v>824</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C767" s="1">
-        <x:v>18050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D767" s="1">
-        <x:v>764206</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E767" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F767" s="1">
-        <x:v>81382</x:v>
+        <x:v>27300</x:v>
       </x:c>
       <x:c r="G767" s="1">
-        <x:v>863638</x:v>
+        <x:v>27350</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:7">
@@ -20857,22 +20860,22 @@
         <x:v>825</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C768" s="1">
-        <x:v>0</x:v>
+        <x:v>18050</x:v>
       </x:c>
       <x:c r="D768" s="1">
-        <x:v>0</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="E768" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>2700</x:v>
+        <x:v>81382</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>2700</x:v>
+        <x:v>863638</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
@@ -20880,22 +20883,22 @@
         <x:v>826</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C769" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D769" s="1">
-        <x:v>1543316</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E769" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F769" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G769" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:7">
@@ -20903,22 +20906,22 @@
         <x:v>827</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C770" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D770" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E770" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F770" s="1">
-        <x:v>14500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G770" s="1">
-        <x:v>14550</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="771" spans="1:7">
@@ -20926,7 +20929,7 @@
         <x:v>828</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C771" s="1">
         <x:v>50</x:v>
@@ -20938,10 +20941,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F771" s="1">
-        <x:v>5800</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G771" s="1">
-        <x:v>5850</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="772" spans="1:7">
@@ -20949,7 +20952,7 @@
         <x:v>829</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C772" s="1">
         <x:v>50</x:v>
@@ -20961,10 +20964,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F772" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G772" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="773" spans="1:7">
@@ -20972,13 +20975,13 @@
         <x:v>830</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C773" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D773" s="1">
-        <x:v>107353</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E773" s="1">
         <x:v>0</x:v>
@@ -20987,7 +20990,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G773" s="1">
-        <x:v>107403</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="774" spans="1:7">
@@ -20995,22 +20998,22 @@
         <x:v>831</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C774" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D774" s="1">
-        <x:v>0</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="E774" s="1">
-        <x:v>9985740</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F774" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G774" s="1">
-        <x:v>0</x:v>
+        <x:v>107403</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:7">
@@ -21018,7 +21021,7 @@
         <x:v>832</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C775" s="1">
         <x:v>0</x:v>
@@ -21027,13 +21030,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E775" s="1">
-        <x:v>0</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>16800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>16800</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
@@ -21041,7 +21044,7 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C776" s="1">
         <x:v>0</x:v>
@@ -21053,10 +21056,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>2700</x:v>
+        <x:v>16800</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>2700</x:v>
+        <x:v>16800</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
@@ -21064,22 +21067,22 @@
         <x:v>834</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C777" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D777" s="1">
-        <x:v>106947</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E777" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F777" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G777" s="1">
-        <x:v>106947</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="778" spans="1:7">
@@ -21087,22 +21090,22 @@
         <x:v>835</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C778" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D778" s="1">
-        <x:v>0</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="E778" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F778" s="1">
-        <x:v>18333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>18383</x:v>
+        <x:v>106947</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
@@ -21110,22 +21113,22 @@
         <x:v>836</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C779" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D779" s="1">
-        <x:v>902176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E779" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F779" s="1">
-        <x:v>26650</x:v>
+        <x:v>18333</x:v>
       </x:c>
       <x:c r="G779" s="1">
-        <x:v>929876</x:v>
+        <x:v>18383</x:v>
       </x:c>
     </x:row>
     <x:row r="780" spans="1:7">
@@ -21133,27 +21136,27 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C780" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D780" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E780" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F780" s="1">
-        <x:v>26500</x:v>
+        <x:v>26650</x:v>
       </x:c>
       <x:c r="G780" s="1">
-        <x:v>26550</x:v>
+        <x:v>929876</x:v>
       </x:c>
     </x:row>
     <x:row r="781" spans="1:7">
       <x:c r="A781" s="1" t="s">
-        <x:v>837</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
         <x:v>98</x:v>
@@ -21179,10 +21182,10 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="B782" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C782" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D782" s="1">
         <x:v>0</x:v>
@@ -21191,10 +21194,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F782" s="1">
-        <x:v>1000</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G782" s="1">
-        <x:v>1000</x:v>
+        <x:v>26550</x:v>
       </x:c>
     </x:row>
     <x:row r="783" spans="1:7">
@@ -21202,10 +21205,10 @@
         <x:v>839</x:v>
       </x:c>
       <x:c r="B783" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C783" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D783" s="1">
         <x:v>0</x:v>
@@ -21214,10 +21217,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F783" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G783" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="784" spans="1:7">
@@ -21225,10 +21228,10 @@
         <x:v>840</x:v>
       </x:c>
       <x:c r="B784" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C784" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D784" s="1">
         <x:v>0</x:v>
@@ -21237,10 +21240,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F784" s="1">
-        <x:v>10500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G784" s="1">
-        <x:v>10500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="785" spans="1:7">
@@ -21248,7 +21251,7 @@
         <x:v>841</x:v>
       </x:c>
       <x:c r="B785" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C785" s="1">
         <x:v>0</x:v>
@@ -21260,10 +21263,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F785" s="1">
-        <x:v>13200</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G785" s="1">
-        <x:v>13200</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="786" spans="1:7">
@@ -21271,10 +21274,10 @@
         <x:v>842</x:v>
       </x:c>
       <x:c r="B786" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C786" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D786" s="1">
         <x:v>0</x:v>
@@ -21283,10 +21286,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F786" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G786" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="787" spans="1:7">
@@ -21294,10 +21297,10 @@
         <x:v>843</x:v>
       </x:c>
       <x:c r="B787" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C787" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D787" s="1">
         <x:v>0</x:v>
@@ -21306,10 +21309,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F787" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G787" s="1">
-        <x:v>4300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="788" spans="1:7">
@@ -21317,10 +21320,10 @@
         <x:v>844</x:v>
       </x:c>
       <x:c r="B788" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C788" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D788" s="1">
         <x:v>0</x:v>
@@ -21329,10 +21332,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F788" s="1">
-        <x:v>6600</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G788" s="1">
-        <x:v>6650</x:v>
+        <x:v>4300</x:v>
       </x:c>
     </x:row>
     <x:row r="789" spans="1:7">
@@ -21340,22 +21343,22 @@
         <x:v>845</x:v>
       </x:c>
       <x:c r="B789" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C789" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D789" s="1">
-        <x:v>1010142</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E789" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F789" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G789" s="1">
-        <x:v>1010142</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="790" spans="1:7">
@@ -21363,22 +21366,22 @@
         <x:v>846</x:v>
       </x:c>
       <x:c r="B790" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C790" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D790" s="1">
-        <x:v>0</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="E790" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F790" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G790" s="1">
-        <x:v>5000</x:v>
+        <x:v>1010142</x:v>
       </x:c>
     </x:row>
     <x:row r="791" spans="1:7">
@@ -21386,10 +21389,10 @@
         <x:v>847</x:v>
       </x:c>
       <x:c r="B791" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C791" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D791" s="1">
         <x:v>0</x:v>
@@ -21398,10 +21401,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F791" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G791" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="792" spans="1:7">
@@ -21409,10 +21412,10 @@
         <x:v>848</x:v>
       </x:c>
       <x:c r="B792" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C792" s="1">
-        <x:v>6550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D792" s="1">
         <x:v>0</x:v>
@@ -21421,10 +21424,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F792" s="1">
-        <x:v>39400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G792" s="1">
-        <x:v>45950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="793" spans="1:7">
@@ -21432,10 +21435,10 @@
         <x:v>849</x:v>
       </x:c>
       <x:c r="B793" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C793" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D793" s="1">
         <x:v>0</x:v>
@@ -21444,10 +21447,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F793" s="1">
-        <x:v>0</x:v>
+        <x:v>39400</x:v>
       </x:c>
       <x:c r="G793" s="1">
-        <x:v>50</x:v>
+        <x:v>45950</x:v>
       </x:c>
     </x:row>
     <x:row r="794" spans="1:7">
@@ -21455,7 +21458,7 @@
         <x:v>850</x:v>
       </x:c>
       <x:c r="B794" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C794" s="1">
         <x:v>50</x:v>
@@ -21478,10 +21481,10 @@
         <x:v>851</x:v>
       </x:c>
       <x:c r="B795" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C795" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D795" s="1">
         <x:v>0</x:v>
@@ -21490,10 +21493,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F795" s="1">
-        <x:v>20900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G795" s="1">
-        <x:v>24450</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="796" spans="1:7">
@@ -21501,10 +21504,10 @@
         <x:v>852</x:v>
       </x:c>
       <x:c r="B796" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C796" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D796" s="1">
         <x:v>0</x:v>
@@ -21513,10 +21516,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F796" s="1">
-        <x:v>5400</x:v>
+        <x:v>20900</x:v>
       </x:c>
       <x:c r="G796" s="1">
-        <x:v>5400</x:v>
+        <x:v>24450</x:v>
       </x:c>
     </x:row>
     <x:row r="797" spans="1:7">
@@ -21524,10 +21527,10 @@
         <x:v>853</x:v>
       </x:c>
       <x:c r="B797" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C797" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D797" s="1">
         <x:v>0</x:v>
@@ -21536,10 +21539,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F797" s="1">
-        <x:v>0</x:v>
+        <x:v>5400</x:v>
       </x:c>
       <x:c r="G797" s="1">
-        <x:v>50</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="798" spans="1:7">
@@ -21547,10 +21550,10 @@
         <x:v>854</x:v>
       </x:c>
       <x:c r="B798" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C798" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D798" s="1">
         <x:v>0</x:v>
@@ -21559,10 +21562,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F798" s="1">
-        <x:v>21433</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G798" s="1">
-        <x:v>24983</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="799" spans="1:7">
@@ -21570,22 +21573,22 @@
         <x:v>855</x:v>
       </x:c>
       <x:c r="B799" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C799" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D799" s="1">
-        <x:v>1860445</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E799" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F799" s="1">
-        <x:v>11600</x:v>
+        <x:v>21433</x:v>
       </x:c>
       <x:c r="G799" s="1">
-        <x:v>1872095</x:v>
+        <x:v>24983</x:v>
       </x:c>
     </x:row>
     <x:row r="800" spans="1:7">
@@ -21593,22 +21596,22 @@
         <x:v>856</x:v>
       </x:c>
       <x:c r="B800" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C800" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D800" s="1">
-        <x:v>0</x:v>
+        <x:v>1860445</x:v>
       </x:c>
       <x:c r="E800" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F800" s="1">
-        <x:v>0</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G800" s="1">
-        <x:v>50</x:v>
+        <x:v>1872095</x:v>
       </x:c>
     </x:row>
     <x:row r="801" spans="1:7">
@@ -21616,7 +21619,7 @@
         <x:v>857</x:v>
       </x:c>
       <x:c r="B801" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C801" s="1">
         <x:v>50</x:v>
@@ -21628,10 +21631,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F801" s="1">
-        <x:v>16484</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G801" s="1">
-        <x:v>16534</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="802" spans="1:7">
@@ -21639,7 +21642,7 @@
         <x:v>858</x:v>
       </x:c>
       <x:c r="B802" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C802" s="1">
         <x:v>50</x:v>
@@ -21651,10 +21654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F802" s="1">
-        <x:v>0</x:v>
+        <x:v>16484</x:v>
       </x:c>
       <x:c r="G802" s="1">
-        <x:v>50</x:v>
+        <x:v>16534</x:v>
       </x:c>
     </x:row>
     <x:row r="803" spans="1:7">
@@ -21662,10 +21665,10 @@
         <x:v>859</x:v>
       </x:c>
       <x:c r="B803" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C803" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D803" s="1">
         <x:v>0</x:v>
@@ -21674,10 +21677,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F803" s="1">
-        <x:v>6300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G803" s="1">
-        <x:v>6300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="804" spans="1:7">
@@ -21688,7 +21691,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="C804" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D804" s="1">
         <x:v>0</x:v>
@@ -21697,10 +21700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F804" s="1">
-        <x:v>0</x:v>
+        <x:v>6300</x:v>
       </x:c>
       <x:c r="G804" s="1">
-        <x:v>50</x:v>
+        <x:v>6300</x:v>
       </x:c>
     </x:row>
     <x:row r="805" spans="1:7">
@@ -21708,7 +21711,7 @@
         <x:v>861</x:v>
       </x:c>
       <x:c r="B805" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C805" s="1">
         <x:v>50</x:v>
@@ -21720,10 +21723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F805" s="1">
-        <x:v>11000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G805" s="1">
-        <x:v>11050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="806" spans="1:7">
@@ -21731,7 +21734,7 @@
         <x:v>862</x:v>
       </x:c>
       <x:c r="B806" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C806" s="1">
         <x:v>50</x:v>
@@ -21743,10 +21746,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F806" s="1">
-        <x:v>0</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="G806" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
     </x:row>
     <x:row r="807" spans="1:7">
@@ -21754,7 +21757,7 @@
         <x:v>863</x:v>
       </x:c>
       <x:c r="B807" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C807" s="1">
         <x:v>50</x:v>
@@ -21777,22 +21780,22 @@
         <x:v>864</x:v>
       </x:c>
       <x:c r="B808" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C808" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D808" s="1">
-        <x:v>173232</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E808" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F808" s="1">
-        <x:v>167130</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G808" s="1">
-        <x:v>356862</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="809" spans="1:7">
@@ -21800,22 +21803,22 @@
         <x:v>865</x:v>
       </x:c>
       <x:c r="B809" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C809" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D809" s="1">
-        <x:v>0</x:v>
+        <x:v>173232</x:v>
       </x:c>
       <x:c r="E809" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F809" s="1">
-        <x:v>1000</x:v>
+        <x:v>167130</x:v>
       </x:c>
       <x:c r="G809" s="1">
-        <x:v>1000</x:v>
+        <x:v>356862</x:v>
       </x:c>
     </x:row>
     <x:row r="810" spans="1:7">
@@ -21823,10 +21826,10 @@
         <x:v>866</x:v>
       </x:c>
       <x:c r="B810" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C810" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D810" s="1">
         <x:v>0</x:v>
@@ -21835,10 +21838,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F810" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G810" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="811" spans="1:7">
@@ -21846,10 +21849,10 @@
         <x:v>867</x:v>
       </x:c>
       <x:c r="B811" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C811" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D811" s="1">
         <x:v>0</x:v>
@@ -21858,10 +21861,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F811" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G811" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="812" spans="1:7">
@@ -21869,10 +21872,10 @@
         <x:v>868</x:v>
       </x:c>
       <x:c r="B812" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C812" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D812" s="1">
         <x:v>0</x:v>
@@ -21881,10 +21884,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F812" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G812" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="813" spans="1:7">
@@ -21892,22 +21895,22 @@
         <x:v>869</x:v>
       </x:c>
       <x:c r="B813" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C813" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D813" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E813" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F813" s="1">
-        <x:v>65132</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G813" s="1">
-        <x:v>105132</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="814" spans="1:7">
@@ -21915,22 +21918,22 @@
         <x:v>870</x:v>
       </x:c>
       <x:c r="B814" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C814" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D814" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E814" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F814" s="1">
-        <x:v>13800</x:v>
+        <x:v>65132</x:v>
       </x:c>
       <x:c r="G814" s="1">
-        <x:v>14800</x:v>
+        <x:v>105132</x:v>
       </x:c>
     </x:row>
     <x:row r="815" spans="1:7">
@@ -21938,10 +21941,10 @@
         <x:v>871</x:v>
       </x:c>
       <x:c r="B815" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C815" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D815" s="1">
         <x:v>0</x:v>
@@ -21950,10 +21953,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F815" s="1">
-        <x:v>0</x:v>
+        <x:v>13800</x:v>
       </x:c>
       <x:c r="G815" s="1">
-        <x:v>50</x:v>
+        <x:v>14800</x:v>
       </x:c>
     </x:row>
     <x:row r="816" spans="1:7">
@@ -21961,10 +21964,10 @@
         <x:v>872</x:v>
       </x:c>
       <x:c r="B816" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C816" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D816" s="1">
         <x:v>0</x:v>
@@ -21973,10 +21976,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F816" s="1">
-        <x:v>7800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G816" s="1">
-        <x:v>7800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="817" spans="1:7">
@@ -21984,10 +21987,10 @@
         <x:v>873</x:v>
       </x:c>
       <x:c r="B817" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C817" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D817" s="1">
         <x:v>0</x:v>
@@ -21996,10 +21999,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F817" s="1">
-        <x:v>0</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="G817" s="1">
-        <x:v>50</x:v>
+        <x:v>7800</x:v>
       </x:c>
     </x:row>
     <x:row r="818" spans="1:7">
@@ -22007,7 +22010,7 @@
         <x:v>874</x:v>
       </x:c>
       <x:c r="B818" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C818" s="1">
         <x:v>50</x:v>
@@ -22019,10 +22022,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F818" s="1">
-        <x:v>6300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G818" s="1">
-        <x:v>6350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="819" spans="1:7">
@@ -22030,7 +22033,7 @@
         <x:v>875</x:v>
       </x:c>
       <x:c r="B819" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C819" s="1">
         <x:v>50</x:v>
@@ -22042,10 +22045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F819" s="1">
-        <x:v>5000</x:v>
+        <x:v>6300</x:v>
       </x:c>
       <x:c r="G819" s="1">
-        <x:v>5050</x:v>
+        <x:v>6350</x:v>
       </x:c>
     </x:row>
     <x:row r="820" spans="1:7">
@@ -22053,22 +22056,22 @@
         <x:v>876</x:v>
       </x:c>
       <x:c r="B820" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C820" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D820" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E820" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F820" s="1">
-        <x:v>6933</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G820" s="1">
-        <x:v>3927522</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="821" spans="1:7">
@@ -22076,22 +22079,22 @@
         <x:v>877</x:v>
       </x:c>
       <x:c r="B821" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C821" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D821" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E821" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F821" s="1">
-        <x:v>2000</x:v>
+        <x:v>6933</x:v>
       </x:c>
       <x:c r="G821" s="1">
-        <x:v>2050</x:v>
+        <x:v>3927522</x:v>
       </x:c>
     </x:row>
     <x:row r="822" spans="1:7">
@@ -22099,10 +22102,10 @@
         <x:v>878</x:v>
       </x:c>
       <x:c r="B822" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C822" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D822" s="1">
         <x:v>0</x:v>
@@ -22111,10 +22114,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F822" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G822" s="1">
-        <x:v>1000</x:v>
+        <x:v>2050</x:v>
       </x:c>
     </x:row>
     <x:row r="823" spans="1:7">
@@ -22122,10 +22125,10 @@
         <x:v>879</x:v>
       </x:c>
       <x:c r="B823" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C823" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D823" s="1">
         <x:v>0</x:v>
@@ -22134,10 +22137,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F823" s="1">
-        <x:v>8500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G823" s="1">
-        <x:v>8550</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="824" spans="1:7">
@@ -22145,10 +22148,10 @@
         <x:v>880</x:v>
       </x:c>
       <x:c r="B824" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C824" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D824" s="1">
         <x:v>0</x:v>
@@ -22157,10 +22160,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F824" s="1">
-        <x:v>14533</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G824" s="1">
-        <x:v>14533</x:v>
+        <x:v>8550</x:v>
       </x:c>
     </x:row>
     <x:row r="825" spans="1:7">
@@ -22168,7 +22171,7 @@
         <x:v>881</x:v>
       </x:c>
       <x:c r="B825" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C825" s="1">
         <x:v>0</x:v>
@@ -22180,10 +22183,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F825" s="1">
-        <x:v>6600</x:v>
+        <x:v>14533</x:v>
       </x:c>
       <x:c r="G825" s="1">
-        <x:v>6600</x:v>
+        <x:v>14533</x:v>
       </x:c>
     </x:row>
     <x:row r="826" spans="1:7">
@@ -22191,7 +22194,7 @@
         <x:v>882</x:v>
       </x:c>
       <x:c r="B826" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C826" s="1">
         <x:v>0</x:v>
@@ -22203,10 +22206,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F826" s="1">
-        <x:v>37000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G826" s="1">
-        <x:v>37000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="827" spans="1:7">
@@ -22214,7 +22217,7 @@
         <x:v>883</x:v>
       </x:c>
       <x:c r="B827" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C827" s="1">
         <x:v>0</x:v>
@@ -22226,10 +22229,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F827" s="1">
-        <x:v>1000</x:v>
+        <x:v>37000</x:v>
       </x:c>
       <x:c r="G827" s="1">
-        <x:v>1000</x:v>
+        <x:v>37000</x:v>
       </x:c>
     </x:row>
     <x:row r="828" spans="1:7">
@@ -22237,10 +22240,10 @@
         <x:v>884</x:v>
       </x:c>
       <x:c r="B828" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C828" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D828" s="1">
         <x:v>0</x:v>
@@ -22249,10 +22252,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F828" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G828" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="829" spans="1:7">
@@ -22260,10 +22263,10 @@
         <x:v>885</x:v>
       </x:c>
       <x:c r="B829" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C829" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D829" s="1">
         <x:v>0</x:v>
@@ -22272,10 +22275,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F829" s="1">
-        <x:v>7500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G829" s="1">
-        <x:v>10500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="830" spans="1:7">
@@ -22283,10 +22286,10 @@
         <x:v>886</x:v>
       </x:c>
       <x:c r="B830" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C830" s="1">
-        <x:v>1050</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D830" s="1">
         <x:v>0</x:v>
@@ -22295,10 +22298,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F830" s="1">
-        <x:v>6632</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="G830" s="1">
-        <x:v>7682</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="831" spans="1:7">
@@ -22309,7 +22312,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="C831" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D831" s="1">
         <x:v>0</x:v>
@@ -22318,10 +22321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F831" s="1">
-        <x:v>0</x:v>
+        <x:v>6632</x:v>
       </x:c>
       <x:c r="G831" s="1">
-        <x:v>50</x:v>
+        <x:v>7682</x:v>
       </x:c>
     </x:row>
     <x:row r="832" spans="1:7">
@@ -22329,7 +22332,7 @@
         <x:v>888</x:v>
       </x:c>
       <x:c r="B832" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C832" s="1">
         <x:v>50</x:v>
@@ -22352,10 +22355,10 @@
         <x:v>889</x:v>
       </x:c>
       <x:c r="B833" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C833" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D833" s="1">
         <x:v>0</x:v>
@@ -22364,10 +22367,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F833" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G833" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="834" spans="1:7">
@@ -22375,7 +22378,7 @@
         <x:v>890</x:v>
       </x:c>
       <x:c r="B834" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C834" s="1">
         <x:v>0</x:v>
@@ -22387,10 +22390,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F834" s="1">
-        <x:v>1000</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G834" s="1">
-        <x:v>1000</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="835" spans="1:7">
@@ -22398,22 +22401,22 @@
         <x:v>891</x:v>
       </x:c>
       <x:c r="B835" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C835" s="1">
-        <x:v>3000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D835" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E835" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F835" s="1">
-        <x:v>8600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G835" s="1">
-        <x:v>901452</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="836" spans="1:7">
@@ -22421,22 +22424,22 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B836" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C836" s="1">
-        <x:v>50</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D836" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E836" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F836" s="1">
-        <x:v>0</x:v>
+        <x:v>8600</x:v>
       </x:c>
       <x:c r="G836" s="1">
-        <x:v>50</x:v>
+        <x:v>901452</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:7">
@@ -22444,10 +22447,10 @@
         <x:v>893</x:v>
       </x:c>
       <x:c r="B837" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C837" s="1">
-        <x:v>14600</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D837" s="1">
         <x:v>0</x:v>
@@ -22456,10 +22459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F837" s="1">
-        <x:v>30905</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G837" s="1">
-        <x:v>45505</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="838" spans="1:7">
@@ -22467,10 +22470,10 @@
         <x:v>894</x:v>
       </x:c>
       <x:c r="B838" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C838" s="1">
-        <x:v>50</x:v>
+        <x:v>14600</x:v>
       </x:c>
       <x:c r="D838" s="1">
         <x:v>0</x:v>
@@ -22479,10 +22482,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F838" s="1">
-        <x:v>0</x:v>
+        <x:v>30905</x:v>
       </x:c>
       <x:c r="G838" s="1">
-        <x:v>50</x:v>
+        <x:v>45505</x:v>
       </x:c>
     </x:row>
     <x:row r="839" spans="1:7">
@@ -22490,7 +22493,7 @@
         <x:v>895</x:v>
       </x:c>
       <x:c r="B839" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C839" s="1">
         <x:v>50</x:v>
@@ -22513,7 +22516,7 @@
         <x:v>896</x:v>
       </x:c>
       <x:c r="B840" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C840" s="1">
         <x:v>50</x:v>
@@ -22536,10 +22539,10 @@
         <x:v>897</x:v>
       </x:c>
       <x:c r="B841" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C841" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D841" s="1">
         <x:v>0</x:v>
@@ -22548,10 +22551,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F841" s="1">
-        <x:v>2900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G841" s="1">
-        <x:v>2900</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="842" spans="1:7">
@@ -22559,22 +22562,22 @@
         <x:v>898</x:v>
       </x:c>
       <x:c r="B842" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C842" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D842" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E842" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F842" s="1">
-        <x:v>0</x:v>
+        <x:v>2900</x:v>
       </x:c>
       <x:c r="G842" s="1">
-        <x:v>1012792</x:v>
+        <x:v>2900</x:v>
       </x:c>
     </x:row>
     <x:row r="843" spans="1:7">
@@ -22582,13 +22585,13 @@
         <x:v>899</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D843" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E843" s="1">
         <x:v>0</x:v>
@@ -22597,7 +22600,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>50</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -22605,10 +22608,10 @@
         <x:v>900</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -22617,15 +22620,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>2600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>2600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
       <x:c r="A845" s="1" t="s">
-        <x:v>900</x:v>
+        <x:v>901</x:v>
       </x:c>
       <x:c r="B845" s="1" t="s">
         <x:v>8</x:v>
@@ -22651,10 +22654,10 @@
         <x:v>901</x:v>
       </x:c>
       <x:c r="B846" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C846" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D846" s="1">
         <x:v>0</x:v>
@@ -22663,10 +22666,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F846" s="1">
-        <x:v>0</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G846" s="1">
-        <x:v>50</x:v>
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="847" spans="1:7">
@@ -22674,10 +22677,10 @@
         <x:v>902</x:v>
       </x:c>
       <x:c r="B847" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C847" s="1">
-        <x:v>19050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D847" s="1">
         <x:v>0</x:v>
@@ -22686,10 +22689,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F847" s="1">
-        <x:v>40900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G847" s="1">
-        <x:v>59950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="848" spans="1:7">
@@ -22697,10 +22700,10 @@
         <x:v>903</x:v>
       </x:c>
       <x:c r="B848" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C848" s="1">
-        <x:v>3500</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D848" s="1">
         <x:v>0</x:v>
@@ -22709,10 +22712,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F848" s="1">
-        <x:v>1162</x:v>
+        <x:v>40900</x:v>
       </x:c>
       <x:c r="G848" s="1">
-        <x:v>4662</x:v>
+        <x:v>59950</x:v>
       </x:c>
     </x:row>
     <x:row r="849" spans="1:7">
@@ -22720,10 +22723,10 @@
         <x:v>904</x:v>
       </x:c>
       <x:c r="B849" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C849" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D849" s="1">
         <x:v>0</x:v>
@@ -22732,21 +22735,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F849" s="1">
-        <x:v>0</x:v>
+        <x:v>1162</x:v>
       </x:c>
       <x:c r="G849" s="1">
-        <x:v>50</x:v>
+        <x:v>4662</x:v>
       </x:c>
     </x:row>
     <x:row r="850" spans="1:7">
       <x:c r="A850" s="1" t="s">
-        <x:v>904</x:v>
+        <x:v>905</x:v>
       </x:c>
       <x:c r="B850" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C850" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D850" s="1">
         <x:v>0</x:v>
@@ -22755,10 +22758,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F850" s="1">
-        <x:v>485</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G850" s="1">
-        <x:v>485</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="851" spans="1:7">
@@ -22766,10 +22769,10 @@
         <x:v>905</x:v>
       </x:c>
       <x:c r="B851" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C851" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D851" s="1">
         <x:v>0</x:v>
@@ -22778,10 +22781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F851" s="1">
-        <x:v>0</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="G851" s="1">
-        <x:v>50</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="852" spans="1:7">
@@ -22789,10 +22792,10 @@
         <x:v>906</x:v>
       </x:c>
       <x:c r="B852" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C852" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D852" s="1">
         <x:v>0</x:v>
@@ -22801,10 +22804,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F852" s="1">
-        <x:v>1200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G852" s="1">
-        <x:v>7650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="853" spans="1:7">
@@ -22812,10 +22815,10 @@
         <x:v>907</x:v>
       </x:c>
       <x:c r="B853" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C853" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D853" s="1">
         <x:v>0</x:v>
@@ -22824,10 +22827,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F853" s="1">
-        <x:v>0</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="G853" s="1">
-        <x:v>50</x:v>
+        <x:v>7650</x:v>
       </x:c>
     </x:row>
     <x:row r="854" spans="1:7">
@@ -22835,10 +22838,10 @@
         <x:v>908</x:v>
       </x:c>
       <x:c r="B854" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C854" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D854" s="1">
         <x:v>0</x:v>
@@ -22847,10 +22850,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F854" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G854" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="855" spans="1:7">
@@ -22858,10 +22861,10 @@
         <x:v>909</x:v>
       </x:c>
       <x:c r="B855" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C855" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D855" s="1">
         <x:v>0</x:v>
@@ -22870,10 +22873,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F855" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G855" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="856" spans="1:7">
@@ -22881,7 +22884,7 @@
         <x:v>910</x:v>
       </x:c>
       <x:c r="B856" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C856" s="1">
         <x:v>50</x:v>
@@ -22904,10 +22907,10 @@
         <x:v>911</x:v>
       </x:c>
       <x:c r="B857" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C857" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D857" s="1">
         <x:v>0</x:v>
@@ -22916,10 +22919,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F857" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G857" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="858" spans="1:7">
@@ -22927,10 +22930,10 @@
         <x:v>912</x:v>
       </x:c>
       <x:c r="B858" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C858" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D858" s="1">
         <x:v>0</x:v>
@@ -22939,10 +22942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F858" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G858" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="859" spans="1:7">
@@ -22950,7 +22953,7 @@
         <x:v>913</x:v>
       </x:c>
       <x:c r="B859" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="C859" s="1">
         <x:v>50</x:v>
@@ -22973,10 +22976,10 @@
         <x:v>914</x:v>
       </x:c>
       <x:c r="B860" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C860" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D860" s="1">
         <x:v>0</x:v>
@@ -22985,10 +22988,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F860" s="1">
-        <x:v>16000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G860" s="1">
-        <x:v>16000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="861" spans="1:7">
@@ -22996,22 +22999,22 @@
         <x:v>915</x:v>
       </x:c>
       <x:c r="B861" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C861" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D861" s="1">
-        <x:v>943006</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E861" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F861" s="1">
-        <x:v>0</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="G861" s="1">
-        <x:v>943056</x:v>
+        <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="862" spans="1:7">
@@ -23019,13 +23022,13 @@
         <x:v>916</x:v>
       </x:c>
       <x:c r="B862" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C862" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D862" s="1">
-        <x:v>0</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="E862" s="1">
         <x:v>0</x:v>
@@ -23034,7 +23037,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G862" s="1">
-        <x:v>50</x:v>
+        <x:v>943056</x:v>
       </x:c>
     </x:row>
     <x:row r="863" spans="1:7">
@@ -23042,10 +23045,10 @@
         <x:v>917</x:v>
       </x:c>
       <x:c r="B863" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C863" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D863" s="1">
         <x:v>0</x:v>
@@ -23054,10 +23057,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F863" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G863" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="864" spans="1:7">
@@ -23065,10 +23068,10 @@
         <x:v>918</x:v>
       </x:c>
       <x:c r="B864" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C864" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D864" s="1">
         <x:v>0</x:v>
@@ -23077,10 +23080,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F864" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G864" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="865" spans="1:7">
@@ -23088,10 +23091,10 @@
         <x:v>919</x:v>
       </x:c>
       <x:c r="B865" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C865" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D865" s="1">
         <x:v>0</x:v>
@@ -23100,10 +23103,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F865" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G865" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="866" spans="1:7">
@@ -23111,10 +23114,10 @@
         <x:v>920</x:v>
       </x:c>
       <x:c r="B866" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C866" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D866" s="1">
         <x:v>0</x:v>
@@ -23123,10 +23126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F866" s="1">
-        <x:v>9900</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G866" s="1">
-        <x:v>9950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="867" spans="1:7">
@@ -23134,7 +23137,7 @@
         <x:v>921</x:v>
       </x:c>
       <x:c r="B867" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C867" s="1">
         <x:v>50</x:v>
@@ -23146,10 +23149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F867" s="1">
-        <x:v>11799</x:v>
+        <x:v>9900</x:v>
       </x:c>
       <x:c r="G867" s="1">
-        <x:v>11849</x:v>
+        <x:v>9950</x:v>
       </x:c>
     </x:row>
     <x:row r="868" spans="1:7">
@@ -23157,10 +23160,10 @@
         <x:v>922</x:v>
       </x:c>
       <x:c r="B868" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C868" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D868" s="1">
         <x:v>0</x:v>
@@ -23169,10 +23172,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F868" s="1">
-        <x:v>16500</x:v>
+        <x:v>11799</x:v>
       </x:c>
       <x:c r="G868" s="1">
-        <x:v>16500</x:v>
+        <x:v>11849</x:v>
       </x:c>
     </x:row>
     <x:row r="869" spans="1:7">
@@ -23180,10 +23183,10 @@
         <x:v>923</x:v>
       </x:c>
       <x:c r="B869" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C869" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D869" s="1">
         <x:v>0</x:v>
@@ -23192,10 +23195,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F869" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G869" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="870" spans="1:7">
@@ -23203,7 +23206,7 @@
         <x:v>924</x:v>
       </x:c>
       <x:c r="B870" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C870" s="1">
         <x:v>50</x:v>
@@ -23226,7 +23229,7 @@
         <x:v>925</x:v>
       </x:c>
       <x:c r="B871" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C871" s="1">
         <x:v>50</x:v>
@@ -23249,7 +23252,7 @@
         <x:v>926</x:v>
       </x:c>
       <x:c r="B872" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C872" s="1">
         <x:v>50</x:v>
@@ -23261,10 +23264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F872" s="1">
-        <x:v>200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G872" s="1">
-        <x:v>250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="873" spans="1:7">
@@ -23272,7 +23275,7 @@
         <x:v>927</x:v>
       </x:c>
       <x:c r="B873" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C873" s="1">
         <x:v>50</x:v>
@@ -23284,10 +23287,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F873" s="1">
-        <x:v>0</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G873" s="1">
-        <x:v>50</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="874" spans="1:7">
@@ -23295,7 +23298,7 @@
         <x:v>928</x:v>
       </x:c>
       <x:c r="B874" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C874" s="1">
         <x:v>50</x:v>
@@ -23318,10 +23321,10 @@
         <x:v>929</x:v>
       </x:c>
       <x:c r="B875" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C875" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D875" s="1">
         <x:v>0</x:v>
@@ -23330,10 +23333,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F875" s="1">
-        <x:v>114400</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G875" s="1">
-        <x:v>125250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="876" spans="1:7">
@@ -23341,10 +23344,10 @@
         <x:v>930</x:v>
       </x:c>
       <x:c r="B876" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C876" s="1">
-        <x:v>0</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D876" s="1">
         <x:v>0</x:v>
@@ -23353,10 +23356,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F876" s="1">
-        <x:v>218</x:v>
+        <x:v>114400</x:v>
       </x:c>
       <x:c r="G876" s="1">
-        <x:v>218</x:v>
+        <x:v>125250</x:v>
       </x:c>
     </x:row>
     <x:row r="877" spans="1:7">
@@ -23364,10 +23367,10 @@
         <x:v>931</x:v>
       </x:c>
       <x:c r="B877" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C877" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D877" s="1">
         <x:v>0</x:v>
@@ -23376,10 +23379,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F877" s="1">
-        <x:v>0</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="G877" s="1">
-        <x:v>50</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="878" spans="1:7">
@@ -23387,7 +23390,7 @@
         <x:v>932</x:v>
       </x:c>
       <x:c r="B878" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C878" s="1">
         <x:v>50</x:v>
@@ -23410,7 +23413,7 @@
         <x:v>933</x:v>
       </x:c>
       <x:c r="B879" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C879" s="1">
         <x:v>50</x:v>
@@ -23433,10 +23436,10 @@
         <x:v>934</x:v>
       </x:c>
       <x:c r="B880" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C880" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D880" s="1">
         <x:v>0</x:v>
@@ -23445,10 +23448,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F880" s="1">
-        <x:v>35800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G880" s="1">
-        <x:v>37350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="881" spans="1:7">
@@ -23456,10 +23459,10 @@
         <x:v>935</x:v>
       </x:c>
       <x:c r="B881" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C881" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D881" s="1">
         <x:v>0</x:v>
@@ -23468,10 +23471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F881" s="1">
-        <x:v>278</x:v>
+        <x:v>35800</x:v>
       </x:c>
       <x:c r="G881" s="1">
-        <x:v>328</x:v>
+        <x:v>37350</x:v>
       </x:c>
     </x:row>
     <x:row r="882" spans="1:7">
@@ -23479,21 +23482,44 @@
         <x:v>936</x:v>
       </x:c>
       <x:c r="B882" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C882" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D882" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E882" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F882" s="1">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G882" s="1">
+        <x:v>328</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="883" spans="1:7">
+      <x:c r="A883" s="1" t="s">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="B883" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="C882" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D882" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E882" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F882" s="1">
+      <x:c r="C883" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D883" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E883" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F883" s="1">
         <x:v>14333</x:v>
       </x:c>
-      <x:c r="G882" s="1">
+      <x:c r="G883" s="1">
         <x:v>14333</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -19949,7 +19949,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E728" s="1">
-        <x:v>0</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="F728" s="1">
         <x:v>0</x:v>
@@ -21159,10 +21159,10 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C781" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D781" s="1">
         <x:v>0</x:v>
@@ -21171,10 +21171,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F781" s="1">
-        <x:v>1800</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>1800</x:v>
+        <x:v>26550</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
@@ -21182,10 +21182,10 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="B782" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C782" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D782" s="1">
         <x:v>0</x:v>
@@ -21194,10 +21194,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F782" s="1">
-        <x:v>26500</x:v>
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="G782" s="1">
-        <x:v>26550</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="783" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -6353,7 +6353,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D137" s="1">
-        <x:v>1052492</x:v>
+        <x:v>2010471</x:v>
       </x:c>
       <x:c r="E137" s="1">
         <x:v>0</x:v>
@@ -6362,7 +6362,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="G137" s="1">
-        <x:v>1059492</x:v>
+        <x:v>2017471</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -6353,7 +6353,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D137" s="1">
-        <x:v>2010471</x:v>
+        <x:v>2067216</x:v>
       </x:c>
       <x:c r="E137" s="1">
         <x:v>0</x:v>
@@ -6362,7 +6362,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="G137" s="1">
-        <x:v>2017471</x:v>
+        <x:v>2074216</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">
@@ -22631,7 +22631,7 @@
         <x:v>901</x:v>
       </x:c>
       <x:c r="B845" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C845" s="1">
         <x:v>0</x:v>
@@ -22643,10 +22643,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F845" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G845" s="1">
-        <x:v>30000</x:v>
+        <x:v>2600</x:v>
       </x:c>
     </x:row>
     <x:row r="846" spans="1:7">
@@ -22654,7 +22654,7 @@
         <x:v>901</x:v>
       </x:c>
       <x:c r="B846" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C846" s="1">
         <x:v>0</x:v>
@@ -22666,10 +22666,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F846" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G846" s="1">
-        <x:v>2600</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="847" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16309,10 +16309,10 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C588" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D588" s="1">
         <x:v>0</x:v>
@@ -16321,10 +16321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F588" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G588" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:7">
@@ -16332,10 +16332,10 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C589" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D589" s="1">
         <x:v>0</x:v>
@@ -16344,10 +16344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F589" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G589" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:7">
@@ -19161,10 +19161,10 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D712" s="1">
         <x:v>0</x:v>
@@ -19173,10 +19173,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19184,10 +19184,10 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D713" s="1">
         <x:v>0</x:v>
@@ -19196,10 +19196,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -12011,7 +12011,7 @@
         <x:v>318</x:v>
       </x:c>
       <x:c r="C401" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D401" s="1">
         <x:v>0</x:v>
@@ -12023,7 +12023,7 @@
         <x:v>22650</x:v>
       </x:c>
       <x:c r="G401" s="1">
-        <x:v>22700</x:v>
+        <x:v>23700</x:v>
       </x:c>
     </x:row>
     <x:row r="402" spans="1:7">
@@ -12934,7 +12934,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D441" s="1">
-        <x:v>1564215</x:v>
+        <x:v>1611377</x:v>
       </x:c>
       <x:c r="E441" s="1">
         <x:v>0</x:v>
@@ -12943,7 +12943,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G441" s="1">
-        <x:v>1564215</x:v>
+        <x:v>1611377</x:v>
       </x:c>
     </x:row>
     <x:row r="442" spans="1:7">
@@ -15872,7 +15872,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C569" s="1">
         <x:v>0</x:v>
@@ -15895,7 +15895,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>0</x:v>
@@ -16309,10 +16309,10 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C588" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D588" s="1">
         <x:v>0</x:v>
@@ -16321,10 +16321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F588" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G588" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:7">
@@ -16332,10 +16332,10 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C589" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D589" s="1">
         <x:v>0</x:v>
@@ -16344,10 +16344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F589" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G589" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -19161,10 +19161,10 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D712" s="1">
         <x:v>0</x:v>
@@ -19173,10 +19173,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19184,10 +19184,10 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D713" s="1">
         <x:v>0</x:v>
@@ -19196,10 +19196,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -15872,7 +15872,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C569" s="1">
         <x:v>0</x:v>
@@ -15895,7 +15895,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>0</x:v>
@@ -19161,10 +19161,10 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D712" s="1">
         <x:v>0</x:v>
@@ -19173,10 +19173,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19184,10 +19184,10 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D713" s="1">
         <x:v>0</x:v>
@@ -19196,10 +19196,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -5436,7 +5436,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D115" s="1">
-        <x:v>2067216</x:v>
+        <x:v>2123261</x:v>
       </x:c>
       <x:c r="E115" s="1">
         <x:v>0</x:v>
@@ -5445,7 +5445,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G115" s="1">
-        <x:v>2067216</x:v>
+        <x:v>2123261</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
@@ -12934,7 +12934,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D441" s="1">
-        <x:v>1611377</x:v>
+        <x:v>1658539</x:v>
       </x:c>
       <x:c r="E441" s="1">
         <x:v>0</x:v>
@@ -12943,7 +12943,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G441" s="1">
-        <x:v>1611377</x:v>
+        <x:v>1658539</x:v>
       </x:c>
     </x:row>
     <x:row r="442" spans="1:7">
@@ -16309,10 +16309,10 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C588" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D588" s="1">
         <x:v>0</x:v>
@@ -16321,10 +16321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F588" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G588" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:7">
@@ -16332,10 +16332,10 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C589" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D589" s="1">
         <x:v>0</x:v>
@@ -16344,10 +16344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F589" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G589" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -5436,7 +5436,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D115" s="1">
-        <x:v>2123261</x:v>
+        <x:v>2648216</x:v>
       </x:c>
       <x:c r="E115" s="1">
         <x:v>0</x:v>
@@ -5445,7 +5445,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G115" s="1">
-        <x:v>2123261</x:v>
+        <x:v>2648216</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
@@ -16309,10 +16309,10 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C588" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D588" s="1">
         <x:v>0</x:v>
@@ -16321,10 +16321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F588" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G588" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:7">
@@ -16332,10 +16332,10 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>436</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C589" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D589" s="1">
         <x:v>0</x:v>
@@ -16344,10 +16344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F589" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G589" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -286,10 +286,10 @@
     <x:t>BOOKER, CORY A.</x:t>
   </x:si>
   <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
     <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
   </x:si>
   <x:si>
     <x:t>BOOZMAN, SEN. JOHN</x:t>
@@ -3984,7 +3984,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C52" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>0</x:v>
@@ -3993,10 +3993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>18200</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G52" s="1">
-        <x:v>18250</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
@@ -4007,7 +4007,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="C53" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>0</x:v>
@@ -4016,10 +4016,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>2800</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G53" s="1">
-        <x:v>2800</x:v>
+        <x:v>18250</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
@@ -4648,7 +4648,7 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C81" s="1">
         <x:v>0</x:v>
@@ -5436,7 +5436,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D115" s="1">
-        <x:v>2648216</x:v>
+        <x:v>2704261</x:v>
       </x:c>
       <x:c r="E115" s="1">
         <x:v>0</x:v>
@@ -5445,7 +5445,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G115" s="1">
-        <x:v>2648216</x:v>
+        <x:v>2704261</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
@@ -5568,7 +5568,7 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C121" s="1">
         <x:v>0</x:v>
@@ -5683,7 +5683,7 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C126" s="1">
         <x:v>50</x:v>
@@ -6787,7 +6787,7 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B174" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C174" s="1">
         <x:v>0</x:v>
@@ -8466,7 +8466,7 @@
         <x:v>299</x:v>
       </x:c>
       <x:c r="B247" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C247" s="1">
         <x:v>4550</x:v>
@@ -8926,7 +8926,7 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B267" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C267" s="1">
         <x:v>0</x:v>
@@ -9064,7 +9064,7 @@
         <x:v>327</x:v>
       </x:c>
       <x:c r="B273" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C273" s="1">
         <x:v>0</x:v>
@@ -9823,7 +9823,7 @@
         <x:v>361</x:v>
       </x:c>
       <x:c r="B306" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C306" s="1">
         <x:v>0</x:v>
@@ -10490,7 +10490,7 @@
         <x:v>391</x:v>
       </x:c>
       <x:c r="B335" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C335" s="1">
         <x:v>0</x:v>
@@ -10536,7 +10536,7 @@
         <x:v>393</x:v>
       </x:c>
       <x:c r="B337" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C337" s="1">
         <x:v>0</x:v>
@@ -10743,7 +10743,7 @@
         <x:v>402</x:v>
       </x:c>
       <x:c r="B346" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C346" s="1">
         <x:v>0</x:v>
@@ -10789,7 +10789,7 @@
         <x:v>404</x:v>
       </x:c>
       <x:c r="B348" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C348" s="1">
         <x:v>0</x:v>
@@ -10881,7 +10881,7 @@
         <x:v>408</x:v>
       </x:c>
       <x:c r="B352" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C352" s="1">
         <x:v>50</x:v>
@@ -12100,7 +12100,7 @@
         <x:v>462</x:v>
       </x:c>
       <x:c r="B405" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C405" s="1">
         <x:v>50</x:v>
@@ -12468,7 +12468,7 @@
         <x:v>478</x:v>
       </x:c>
       <x:c r="B421" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C421" s="1">
         <x:v>0</x:v>
@@ -12934,7 +12934,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D441" s="1">
-        <x:v>1658539</x:v>
+        <x:v>1705701</x:v>
       </x:c>
       <x:c r="E441" s="1">
         <x:v>0</x:v>
@@ -12943,7 +12943,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G441" s="1">
-        <x:v>1658539</x:v>
+        <x:v>1705701</x:v>
       </x:c>
     </x:row>
     <x:row r="442" spans="1:7">
@@ -12951,7 +12951,7 @@
         <x:v>499</x:v>
       </x:c>
       <x:c r="B442" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C442" s="1">
         <x:v>1550</x:v>
@@ -13963,7 +13963,7 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C486" s="1">
         <x:v>50</x:v>
@@ -14124,7 +14124,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C493" s="1">
         <x:v>0</x:v>
@@ -14193,7 +14193,7 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C496" s="1">
         <x:v>0</x:v>
@@ -14377,7 +14377,7 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B504" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C504" s="1">
         <x:v>50</x:v>
@@ -14446,7 +14446,7 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C507" s="1">
         <x:v>50</x:v>
@@ -14538,7 +14538,7 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C511" s="1">
         <x:v>50</x:v>
@@ -14699,7 +14699,7 @@
         <x:v>576</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C518" s="1">
         <x:v>0</x:v>
@@ -15044,7 +15044,7 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C533" s="1">
         <x:v>1000</x:v>
@@ -15136,7 +15136,7 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C537" s="1">
         <x:v>0</x:v>
@@ -15688,7 +15688,7 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C561" s="1">
         <x:v>0</x:v>
@@ -16332,7 +16332,7 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C589" s="1">
         <x:v>0</x:v>
@@ -16953,7 +16953,7 @@
         <x:v>675</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C616" s="1">
         <x:v>1050</x:v>
@@ -17068,7 +17068,7 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C621" s="1">
         <x:v>50</x:v>
@@ -17137,7 +17137,7 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C624" s="1">
         <x:v>50</x:v>
@@ -17551,7 +17551,7 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C642" s="1">
         <x:v>0</x:v>
@@ -18408,7 +18408,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D679" s="1">
-        <x:v>173232</x:v>
+        <x:v>224107</x:v>
       </x:c>
       <x:c r="E679" s="1">
         <x:v>0</x:v>
@@ -18417,7 +18417,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>190732</x:v>
+        <x:v>241607</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
@@ -18425,7 +18425,7 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C680" s="1">
         <x:v>0</x:v>
@@ -18517,7 +18517,7 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C684" s="1">
         <x:v>0</x:v>
@@ -18701,7 +18701,7 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C692" s="1">
         <x:v>50</x:v>
@@ -19184,7 +19184,7 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C713" s="1">
         <x:v>0</x:v>
@@ -19736,7 +19736,7 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C737" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -286,10 +286,10 @@
     <x:t>BOOKER, CORY A.</x:t>
   </x:si>
   <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
     <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
   </x:si>
   <x:si>
     <x:t>BOOZMAN, SEN. JOHN</x:t>
@@ -3274,7 +3274,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>0</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="E21" s="1">
         <x:v>0</x:v>
@@ -3283,7 +3283,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G21" s="1">
-        <x:v>50</x:v>
+        <x:v>513918</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
@@ -3984,7 +3984,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C52" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>0</x:v>
@@ -3993,10 +3993,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>2800</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G52" s="1">
-        <x:v>2800</x:v>
+        <x:v>18250</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
@@ -4007,7 +4007,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="C53" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>0</x:v>
@@ -4016,10 +4016,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>18200</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G53" s="1">
-        <x:v>18250</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
@@ -4648,7 +4648,7 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C81" s="1">
         <x:v>0</x:v>
@@ -5568,7 +5568,7 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="B121" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C121" s="1">
         <x:v>0</x:v>
@@ -5683,7 +5683,7 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B126" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C126" s="1">
         <x:v>50</x:v>
@@ -6787,7 +6787,7 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B174" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C174" s="1">
         <x:v>0</x:v>
@@ -8466,7 +8466,7 @@
         <x:v>299</x:v>
       </x:c>
       <x:c r="B247" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C247" s="1">
         <x:v>4550</x:v>
@@ -8926,7 +8926,7 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B267" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C267" s="1">
         <x:v>0</x:v>
@@ -9064,7 +9064,7 @@
         <x:v>327</x:v>
       </x:c>
       <x:c r="B273" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C273" s="1">
         <x:v>0</x:v>
@@ -9823,7 +9823,7 @@
         <x:v>361</x:v>
       </x:c>
       <x:c r="B306" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C306" s="1">
         <x:v>0</x:v>
@@ -10490,7 +10490,7 @@
         <x:v>391</x:v>
       </x:c>
       <x:c r="B335" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C335" s="1">
         <x:v>0</x:v>
@@ -10536,7 +10536,7 @@
         <x:v>393</x:v>
       </x:c>
       <x:c r="B337" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C337" s="1">
         <x:v>0</x:v>
@@ -10743,7 +10743,7 @@
         <x:v>402</x:v>
       </x:c>
       <x:c r="B346" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C346" s="1">
         <x:v>0</x:v>
@@ -10789,7 +10789,7 @@
         <x:v>404</x:v>
       </x:c>
       <x:c r="B348" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C348" s="1">
         <x:v>0</x:v>
@@ -10881,7 +10881,7 @@
         <x:v>408</x:v>
       </x:c>
       <x:c r="B352" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C352" s="1">
         <x:v>50</x:v>
@@ -12100,7 +12100,7 @@
         <x:v>462</x:v>
       </x:c>
       <x:c r="B405" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C405" s="1">
         <x:v>50</x:v>
@@ -12468,7 +12468,7 @@
         <x:v>478</x:v>
       </x:c>
       <x:c r="B421" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C421" s="1">
         <x:v>0</x:v>
@@ -12951,7 +12951,7 @@
         <x:v>499</x:v>
       </x:c>
       <x:c r="B442" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C442" s="1">
         <x:v>1550</x:v>
@@ -13963,7 +13963,7 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C486" s="1">
         <x:v>50</x:v>
@@ -14124,7 +14124,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C493" s="1">
         <x:v>0</x:v>
@@ -14193,7 +14193,7 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C496" s="1">
         <x:v>0</x:v>
@@ -14377,7 +14377,7 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B504" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C504" s="1">
         <x:v>50</x:v>
@@ -14446,7 +14446,7 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C507" s="1">
         <x:v>50</x:v>
@@ -14538,7 +14538,7 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C511" s="1">
         <x:v>50</x:v>
@@ -14699,7 +14699,7 @@
         <x:v>576</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C518" s="1">
         <x:v>0</x:v>
@@ -15044,7 +15044,7 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C533" s="1">
         <x:v>1000</x:v>
@@ -15136,7 +15136,7 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C537" s="1">
         <x:v>0</x:v>
@@ -15688,7 +15688,7 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C561" s="1">
         <x:v>0</x:v>
@@ -16332,7 +16332,7 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C589" s="1">
         <x:v>0</x:v>
@@ -16953,7 +16953,7 @@
         <x:v>675</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C616" s="1">
         <x:v>1050</x:v>
@@ -17068,7 +17068,7 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C621" s="1">
         <x:v>50</x:v>
@@ -17137,7 +17137,7 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C624" s="1">
         <x:v>50</x:v>
@@ -17551,7 +17551,7 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C642" s="1">
         <x:v>0</x:v>
@@ -18425,7 +18425,7 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C680" s="1">
         <x:v>0</x:v>
@@ -18517,7 +18517,7 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C684" s="1">
         <x:v>0</x:v>
@@ -18701,7 +18701,7 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C692" s="1">
         <x:v>50</x:v>
@@ -19184,7 +19184,7 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C713" s="1">
         <x:v>0</x:v>
@@ -19736,7 +19736,7 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C737" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -15898,7 +15898,7 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>0</x:v>
@@ -15921,7 +15921,7 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B571" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C571" s="1">
         <x:v>0</x:v>
@@ -16335,10 +16335,10 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>437</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C589" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D589" s="1">
         <x:v>0</x:v>
@@ -16347,10 +16347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F589" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G589" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:7">
@@ -16358,10 +16358,10 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C590" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D590" s="1">
         <x:v>0</x:v>
@@ -16370,10 +16370,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F590" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G590" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="591" spans="1:7">
@@ -19187,10 +19187,10 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D713" s="1">
         <x:v>0</x:v>
@@ -19199,10 +19199,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19210,10 +19210,10 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D714" s="1">
         <x:v>0</x:v>
@@ -19222,10 +19222,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3398,7 +3398,7 @@
         <x:v>14300</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>320124</x:v>
+        <x:v>11091675</x:v>
       </x:c>
       <x:c r="E26" s="1">
         <x:v>0</x:v>
@@ -3407,7 +3407,7 @@
         <x:v>17500</x:v>
       </x:c>
       <x:c r="G26" s="1">
-        <x:v>351924</x:v>
+        <x:v>11123475</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
@@ -5468,7 +5468,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D116" s="1">
-        <x:v>2761006</x:v>
+        <x:v>3343831</x:v>
       </x:c>
       <x:c r="E116" s="1">
         <x:v>0</x:v>
@@ -5477,7 +5477,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G116" s="1">
-        <x:v>2761006</x:v>
+        <x:v>3343831</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7">
@@ -10206,7 +10206,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D322" s="1">
-        <x:v>106708</x:v>
+        <x:v>3697225</x:v>
       </x:c>
       <x:c r="E322" s="1">
         <x:v>0</x:v>
@@ -10215,7 +10215,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G322" s="1">
-        <x:v>106758</x:v>
+        <x:v>3697275</x:v>
       </x:c>
     </x:row>
     <x:row r="323" spans="1:7">
@@ -13012,7 +13012,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D444" s="1">
-        <x:v>1752863</x:v>
+        <x:v>2779856</x:v>
       </x:c>
       <x:c r="E444" s="1">
         <x:v>0</x:v>
@@ -13021,7 +13021,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G444" s="1">
-        <x:v>1752863</x:v>
+        <x:v>2779856</x:v>
       </x:c>
     </x:row>
     <x:row r="445" spans="1:7">
@@ -14162,7 +14162,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D494" s="1">
-        <x:v>106708</x:v>
+        <x:v>3697225</x:v>
       </x:c>
       <x:c r="E494" s="1">
         <x:v>0</x:v>
@@ -14171,7 +14171,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G494" s="1">
-        <x:v>106708</x:v>
+        <x:v>3697225</x:v>
       </x:c>
     </x:row>
     <x:row r="495" spans="1:7">
@@ -15950,13 +15950,13 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B572" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C572" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D572" s="1">
-        <x:v>106708</x:v>
+        <x:v>3697225</x:v>
       </x:c>
       <x:c r="E572" s="1">
         <x:v>0</x:v>
@@ -15965,7 +15965,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>106708</x:v>
+        <x:v>3697225</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -15973,13 +15973,13 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C573" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D573" s="1">
-        <x:v>106708</x:v>
+        <x:v>3697225</x:v>
       </x:c>
       <x:c r="E573" s="1">
         <x:v>0</x:v>
@@ -15988,7 +15988,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G573" s="1">
-        <x:v>106708</x:v>
+        <x:v>3697225</x:v>
       </x:c>
     </x:row>
     <x:row r="574" spans="1:7">
@@ -17198,7 +17198,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
-        <x:v>0</x:v>
+        <x:v>1131900</x:v>
       </x:c>
       <x:c r="E626" s="1">
         <x:v>0</x:v>
@@ -17207,7 +17207,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>50</x:v>
+        <x:v>1131950</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -7932,7 +7932,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D223" s="1">
-        <x:v>726570</x:v>
+        <x:v>1257152</x:v>
       </x:c>
       <x:c r="E223" s="1">
         <x:v>0</x:v>
@@ -7941,7 +7941,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G223" s="1">
-        <x:v>726570</x:v>
+        <x:v>1257152</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:7">
@@ -8001,7 +8001,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D226" s="1">
-        <x:v>64338</x:v>
+        <x:v>580151</x:v>
       </x:c>
       <x:c r="E226" s="1">
         <x:v>0</x:v>
@@ -8010,7 +8010,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G226" s="1">
-        <x:v>64338</x:v>
+        <x:v>580151</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:7">
@@ -11129,7 +11129,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D362" s="1">
-        <x:v>54935</x:v>
+        <x:v>320996</x:v>
       </x:c>
       <x:c r="E362" s="1">
         <x:v>0</x:v>
@@ -11138,7 +11138,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G362" s="1">
-        <x:v>54935</x:v>
+        <x:v>320996</x:v>
       </x:c>
     </x:row>
     <x:row r="363" spans="1:7">
@@ -13038,7 +13038,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D445" s="1">
-        <x:v>2779856</x:v>
+        <x:v>2827018</x:v>
       </x:c>
       <x:c r="E445" s="1">
         <x:v>0</x:v>
@@ -13047,7 +13047,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G445" s="1">
-        <x:v>2779856</x:v>
+        <x:v>2827018</x:v>
       </x:c>
     </x:row>
     <x:row r="446" spans="1:7">
@@ -13567,7 +13567,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D468" s="1">
-        <x:v>850000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="E468" s="1">
         <x:v>0</x:v>
@@ -13576,7 +13576,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G468" s="1">
-        <x:v>850000</x:v>
+        <x:v>221403</x:v>
       </x:c>
     </x:row>
     <x:row r="469" spans="1:7">
@@ -15976,7 +15976,7 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C573" s="1">
         <x:v>0</x:v>
@@ -15999,7 +15999,7 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C574" s="1">
         <x:v>0</x:v>
@@ -18512,7 +18512,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D683" s="1">
-        <x:v>224107</x:v>
+        <x:v>274982</x:v>
       </x:c>
       <x:c r="E683" s="1">
         <x:v>0</x:v>
@@ -18521,7 +18521,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>241607</x:v>
+        <x:v>292482</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -5494,7 +5494,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D117" s="1">
-        <x:v>3399876</x:v>
+        <x:v>3455921</x:v>
       </x:c>
       <x:c r="E117" s="1">
         <x:v>0</x:v>
@@ -5503,7 +5503,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G117" s="1">
-        <x:v>3399876</x:v>
+        <x:v>3455921</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7">
@@ -13038,7 +13038,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D445" s="1">
-        <x:v>2827018</x:v>
+        <x:v>2874180</x:v>
       </x:c>
       <x:c r="E445" s="1">
         <x:v>0</x:v>
@@ -13047,7 +13047,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G445" s="1">
-        <x:v>2827018</x:v>
+        <x:v>2874180</x:v>
       </x:c>
     </x:row>
     <x:row r="446" spans="1:7">
@@ -19265,10 +19265,10 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D716" s="1">
         <x:v>0</x:v>
@@ -19277,10 +19277,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19288,10 +19288,10 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D717" s="1">
         <x:v>0</x:v>
@@ -19300,10 +19300,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -12047,7 +12047,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D410" s="1">
-        <x:v>2874180</x:v>
+        <x:v>3442924</x:v>
       </x:c>
       <x:c r="E410" s="1">
         <x:v>0</x:v>
@@ -12056,7 +12056,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G410" s="1">
-        <x:v>2874180</x:v>
+        <x:v>3442924</x:v>
       </x:c>
     </x:row>
     <x:row r="411" spans="1:7">
@@ -14663,7 +14663,7 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C524" s="1">
         <x:v>0</x:v>
@@ -14686,7 +14686,7 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C525" s="1">
         <x:v>0</x:v>
@@ -15100,10 +15100,10 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C543" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D543" s="1">
         <x:v>0</x:v>
@@ -15112,10 +15112,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F543" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15123,10 +15123,10 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="C544" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D544" s="1">
         <x:v>0</x:v>
@@ -15135,10 +15135,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4940,7 +4940,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D101" s="1">
-        <x:v>3455921</x:v>
+        <x:v>4210393</x:v>
       </x:c>
       <x:c r="E101" s="1">
         <x:v>0</x:v>
@@ -4949,7 +4949,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G101" s="1">
-        <x:v>3455921</x:v>
+        <x:v>4210393</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
@@ -7194,7 +7194,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D199" s="1">
-        <x:v>1257152</x:v>
+        <x:v>1383722</x:v>
       </x:c>
       <x:c r="E199" s="1">
         <x:v>0</x:v>
@@ -7203,7 +7203,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G199" s="1">
-        <x:v>1257152</x:v>
+        <x:v>1383722</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
@@ -7263,7 +7263,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D202" s="1">
-        <x:v>580151</x:v>
+        <x:v>644489</x:v>
       </x:c>
       <x:c r="E202" s="1">
         <x:v>0</x:v>
@@ -7272,7 +7272,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G202" s="1">
-        <x:v>580151</x:v>
+        <x:v>644489</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
@@ -10230,7 +10230,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D331" s="1">
-        <x:v>320996</x:v>
+        <x:v>375931</x:v>
       </x:c>
       <x:c r="E331" s="1">
         <x:v>0</x:v>
@@ -10239,7 +10239,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G331" s="1">
-        <x:v>320996</x:v>
+        <x:v>375931</x:v>
       </x:c>
     </x:row>
     <x:row r="332" spans="1:7">
@@ -14663,7 +14663,7 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C524" s="1">
         <x:v>0</x:v>
@@ -14686,7 +14686,7 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C525" s="1">
         <x:v>0</x:v>
@@ -15100,10 +15100,10 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="C543" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D543" s="1">
         <x:v>0</x:v>
@@ -15112,10 +15112,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F543" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15123,10 +15123,10 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C544" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D544" s="1">
         <x:v>0</x:v>
@@ -15135,10 +15135,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">
@@ -17061,7 +17061,7 @@
         <x:v>9000</x:v>
       </x:c>
       <x:c r="D628" s="1">
-        <x:v>101750</x:v>
+        <x:v>144600</x:v>
       </x:c>
       <x:c r="E628" s="1">
         <x:v>0</x:v>
@@ -17070,7 +17070,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G628" s="1">
-        <x:v>110750</x:v>
+        <x:v>153600</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3146,7 +3146,7 @@
         <x:v>11800</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>10771551</x:v>
+        <x:v>21510414</x:v>
       </x:c>
       <x:c r="E23" s="1">
         <x:v>0</x:v>
@@ -3155,7 +3155,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G23" s="1">
-        <x:v>10783351</x:v>
+        <x:v>21522214</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
@@ -3629,7 +3629,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
       <x:c r="E44" s="1">
         <x:v>0</x:v>
@@ -3638,7 +3638,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G44" s="1">
-        <x:v>303642</x:v>
+        <x:v>535135</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
@@ -7194,7 +7194,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D199" s="1">
-        <x:v>1383722</x:v>
+        <x:v>1510292</x:v>
       </x:c>
       <x:c r="E199" s="1">
         <x:v>0</x:v>
@@ -7203,7 +7203,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G199" s="1">
-        <x:v>1383722</x:v>
+        <x:v>1510292</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
@@ -7263,7 +7263,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D202" s="1">
-        <x:v>644489</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="E202" s="1">
         <x:v>0</x:v>
@@ -7272,7 +7272,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G202" s="1">
-        <x:v>644489</x:v>
+        <x:v>708827</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
@@ -9356,7 +9356,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D293" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="E293" s="1">
         <x:v>0</x:v>
@@ -9365,7 +9365,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G293" s="1">
-        <x:v>3590567</x:v>
+        <x:v>7170188</x:v>
       </x:c>
     </x:row>
     <x:row r="294" spans="1:7">
@@ -10230,7 +10230,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D331" s="1">
-        <x:v>375931</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="E331" s="1">
         <x:v>0</x:v>
@@ -10239,7 +10239,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G331" s="1">
-        <x:v>375931</x:v>
+        <x:v>430866</x:v>
       </x:c>
     </x:row>
     <x:row r="332" spans="1:7">
@@ -12047,7 +12047,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D410" s="1">
-        <x:v>3442924</x:v>
+        <x:v>3490086</x:v>
       </x:c>
       <x:c r="E410" s="1">
         <x:v>0</x:v>
@@ -12056,7 +12056,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G410" s="1">
-        <x:v>3442924</x:v>
+        <x:v>3490086</x:v>
       </x:c>
     </x:row>
     <x:row r="411" spans="1:7">
@@ -13105,7 +13105,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D456" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="E456" s="1">
         <x:v>0</x:v>
@@ -13114,7 +13114,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G456" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
     </x:row>
     <x:row r="457" spans="1:7">
@@ -14663,13 +14663,13 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C524" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D524" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="E524" s="1">
         <x:v>0</x:v>
@@ -14678,7 +14678,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -14686,13 +14686,13 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C525" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D525" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="E525" s="1">
         <x:v>0</x:v>
@@ -14701,7 +14701,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G525" s="1">
-        <x:v>3590517</x:v>
+        <x:v>7170138</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:7">
@@ -15100,10 +15100,10 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>409</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C543" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D543" s="1">
         <x:v>0</x:v>
@@ -15112,10 +15112,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F543" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15123,10 +15123,10 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="C544" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D544" s="1">
         <x:v>0</x:v>
@@ -15135,10 +15135,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16057,7 +16057,7 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B576" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C576" s="1">
         <x:v>0</x:v>
@@ -16080,7 +16080,7 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B577" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C577" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3997,7 +3997,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
       <x:c r="E51" s="1">
         <x:v>0</x:v>
@@ -4006,7 +4006,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G51" s="1">
-        <x:v>1069843</x:v>
+        <x:v>2062516</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
@@ -4066,7 +4066,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D54" s="1">
-        <x:v>85440</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="E54" s="1">
         <x:v>0</x:v>
@@ -4075,7 +4075,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G54" s="1">
-        <x:v>85440</x:v>
+        <x:v>348433</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
@@ -6688,7 +6688,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D168" s="1">
-        <x:v>70422</x:v>
+        <x:v>581175</x:v>
       </x:c>
       <x:c r="E168" s="1">
         <x:v>0</x:v>
@@ -6697,7 +6697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G168" s="1">
-        <x:v>70422</x:v>
+        <x:v>581175</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:7">
@@ -13151,7 +13151,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D449" s="1">
-        <x:v>25663</x:v>
+        <x:v>436280</x:v>
       </x:c>
       <x:c r="E449" s="1">
         <x:v>0</x:v>
@@ -13160,7 +13160,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G449" s="1">
-        <x:v>25663</x:v>
+        <x:v>436280</x:v>
       </x:c>
     </x:row>
     <x:row r="450" spans="1:7">
@@ -13197,7 +13197,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D451" s="1">
-        <x:v>5650160</x:v>
+        <x:v>5667720</x:v>
       </x:c>
       <x:c r="E451" s="1">
         <x:v>0</x:v>
@@ -13206,7 +13206,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G451" s="1">
-        <x:v>5650160</x:v>
+        <x:v>5667720</x:v>
       </x:c>
     </x:row>
     <x:row r="452" spans="1:7">
@@ -14784,7 +14784,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D520" s="1">
-        <x:v>3500000</x:v>
+        <x:v>4500000</x:v>
       </x:c>
       <x:c r="E520" s="1">
         <x:v>0</x:v>
@@ -14793,7 +14793,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G520" s="1">
-        <x:v>3500000</x:v>
+        <x:v>4500000</x:v>
       </x:c>
     </x:row>
     <x:row r="521" spans="1:7">
@@ -17061,7 +17061,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D619" s="1">
-        <x:v>108744</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="E619" s="1">
         <x:v>0</x:v>
@@ -17070,7 +17070,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G619" s="1">
-        <x:v>108744</x:v>
+        <x:v>426280</x:v>
       </x:c>
     </x:row>
     <x:row r="620" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -6044,7 +6044,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D140" s="1">
-        <x:v>0</x:v>
+        <x:v>53694</x:v>
       </x:c>
       <x:c r="E140" s="1">
         <x:v>0</x:v>
@@ -6053,7 +6053,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G140" s="1">
-        <x:v>50</x:v>
+        <x:v>53744</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:7">
@@ -6688,7 +6688,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D168" s="1">
-        <x:v>581175</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="E168" s="1">
         <x:v>0</x:v>
@@ -6697,7 +6697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G168" s="1">
-        <x:v>581175</x:v>
+        <x:v>616386</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:7">
@@ -12024,7 +12024,7 @@
         <x:v>1050</x:v>
       </x:c>
       <x:c r="D400" s="1">
-        <x:v>0</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="E400" s="1">
         <x:v>0</x:v>
@@ -12033,7 +12033,7 @@
         <x:v>10000</x:v>
       </x:c>
       <x:c r="G400" s="1">
-        <x:v>11050</x:v>
+        <x:v>117398</x:v>
       </x:c>
     </x:row>
     <x:row r="401" spans="1:7">
@@ -12093,7 +12093,7 @@
         <x:v>2050</x:v>
       </x:c>
       <x:c r="D403" s="1">
-        <x:v>0</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="E403" s="1">
         <x:v>0</x:v>
@@ -12102,7 +12102,7 @@
         <x:v>37600</x:v>
       </x:c>
       <x:c r="G403" s="1">
-        <x:v>39650</x:v>
+        <x:v>148924</x:v>
       </x:c>
     </x:row>
     <x:row r="404" spans="1:7">
@@ -13151,7 +13151,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D449" s="1">
-        <x:v>436280</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="E449" s="1">
         <x:v>0</x:v>
@@ -13160,7 +13160,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G449" s="1">
-        <x:v>436280</x:v>
+        <x:v>461943</x:v>
       </x:c>
     </x:row>
     <x:row r="450" spans="1:7">
@@ -13197,7 +13197,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D451" s="1">
-        <x:v>5667720</x:v>
+        <x:v>5714882</x:v>
       </x:c>
       <x:c r="E451" s="1">
         <x:v>0</x:v>
@@ -13206,7 +13206,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G451" s="1">
-        <x:v>5667720</x:v>
+        <x:v>5714882</x:v>
       </x:c>
     </x:row>
     <x:row r="452" spans="1:7">
@@ -13220,7 +13220,7 @@
         <x:v>1550</x:v>
       </x:c>
       <x:c r="D452" s="1">
-        <x:v>314348</x:v>
+        <x:v>378743</x:v>
       </x:c>
       <x:c r="E452" s="1">
         <x:v>0</x:v>
@@ -13229,7 +13229,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G452" s="1">
-        <x:v>315898</x:v>
+        <x:v>380293</x:v>
       </x:c>
     </x:row>
     <x:row r="453" spans="1:7">
@@ -13404,7 +13404,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="D460" s="1">
-        <x:v>0</x:v>
+        <x:v>53970</x:v>
       </x:c>
       <x:c r="E460" s="1">
         <x:v>0</x:v>
@@ -13413,7 +13413,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G460" s="1">
-        <x:v>2000</x:v>
+        <x:v>55970</x:v>
       </x:c>
     </x:row>
     <x:row r="461" spans="1:7">
@@ -16572,10 +16572,10 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C598" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D598" s="1">
         <x:v>0</x:v>
@@ -16584,10 +16584,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F598" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G598" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="599" spans="1:7">
@@ -16595,10 +16595,10 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C599" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D599" s="1">
         <x:v>0</x:v>
@@ -16607,10 +16607,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F599" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G599" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="600" spans="1:7">
@@ -17337,7 +17337,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D631" s="1">
-        <x:v>0</x:v>
+        <x:v>55799</x:v>
       </x:c>
       <x:c r="E631" s="1">
         <x:v>0</x:v>
@@ -17346,7 +17346,7 @@
         <x:v>3300</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>3300</x:v>
+        <x:v>59099</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16135,7 +16135,7 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B579" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C579" s="1">
         <x:v>0</x:v>
@@ -16158,7 +16158,7 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C580" s="1">
         <x:v>0</x:v>
@@ -16572,10 +16572,10 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C598" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D598" s="1">
         <x:v>0</x:v>
@@ -16584,10 +16584,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F598" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G598" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="599" spans="1:7">
@@ -16595,10 +16595,10 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C599" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D599" s="1">
         <x:v>0</x:v>
@@ -16607,10 +16607,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F599" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G599" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="600" spans="1:7">
@@ -18763,7 +18763,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D693" s="1">
-        <x:v>360682</x:v>
+        <x:v>404474</x:v>
       </x:c>
       <x:c r="E693" s="1">
         <x:v>0</x:v>
@@ -18772,7 +18772,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>378182</x:v>
+        <x:v>421974</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -1511,6 +1511,9 @@
   </x:si>
   <x:si>
     <x:t>MCGOVERN, JAMES P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
   </x:si>
   <x:si>
     <x:t>MCHENRY, PATRICK TIMOTHY</x:t>
@@ -2520,8 +2523,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G756" totalsRowShown="0">
-  <x:autoFilter ref="A1:G756"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G757" totalsRowShown="0">
+  <x:autoFilter ref="A1:G757"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2823,7 +2826,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G756"/>
+  <x:dimension ref="A1:G757"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3997,7 +4000,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>2062516</x:v>
+        <x:v>2122190</x:v>
       </x:c>
       <x:c r="E51" s="1">
         <x:v>0</x:v>
@@ -4006,7 +4009,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G51" s="1">
-        <x:v>2062516</x:v>
+        <x:v>2122190</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
@@ -13007,22 +13010,22 @@
         <x:v>499</x:v>
       </x:c>
       <x:c r="B443" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C443" s="1">
-        <x:v>8670</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D443" s="1">
-        <x:v>126626</x:v>
+        <x:v>55720</x:v>
       </x:c>
       <x:c r="E443" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F443" s="1">
-        <x:v>8000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G443" s="1">
-        <x:v>143296</x:v>
+        <x:v>55720</x:v>
       </x:c>
     </x:row>
     <x:row r="444" spans="1:7">
@@ -13030,22 +13033,22 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="B444" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C444" s="1">
-        <x:v>50</x:v>
+        <x:v>8670</x:v>
       </x:c>
       <x:c r="D444" s="1">
-        <x:v>0</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="E444" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F444" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G444" s="1">
-        <x:v>50</x:v>
+        <x:v>143296</x:v>
       </x:c>
     </x:row>
     <x:row r="445" spans="1:7">
@@ -13053,7 +13056,7 @@
         <x:v>501</x:v>
       </x:c>
       <x:c r="B445" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C445" s="1">
         <x:v>50</x:v>
@@ -13076,10 +13079,10 @@
         <x:v>502</x:v>
       </x:c>
       <x:c r="B446" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C446" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D446" s="1">
         <x:v>0</x:v>
@@ -13088,10 +13091,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F446" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G446" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="447" spans="1:7">
@@ -13099,10 +13102,10 @@
         <x:v>503</x:v>
       </x:c>
       <x:c r="B447" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C447" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D447" s="1">
         <x:v>0</x:v>
@@ -13111,10 +13114,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F447" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G447" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="448" spans="1:7">
@@ -13122,7 +13125,7 @@
         <x:v>504</x:v>
       </x:c>
       <x:c r="B448" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C448" s="1">
         <x:v>50</x:v>
@@ -13145,13 +13148,13 @@
         <x:v>505</x:v>
       </x:c>
       <x:c r="B449" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C449" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D449" s="1">
-        <x:v>461943</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E449" s="1">
         <x:v>0</x:v>
@@ -13160,7 +13163,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G449" s="1">
-        <x:v>461943</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="450" spans="1:7">
@@ -13168,13 +13171,13 @@
         <x:v>506</x:v>
       </x:c>
       <x:c r="B450" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C450" s="1">
-        <x:v>1050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D450" s="1">
-        <x:v>92320</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="E450" s="1">
         <x:v>0</x:v>
@@ -13183,7 +13186,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G450" s="1">
-        <x:v>93370</x:v>
+        <x:v>461943</x:v>
       </x:c>
     </x:row>
     <x:row r="451" spans="1:7">
@@ -13191,13 +13194,13 @@
         <x:v>507</x:v>
       </x:c>
       <x:c r="B451" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C451" s="1">
-        <x:v>0</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D451" s="1">
-        <x:v>5714882</x:v>
+        <x:v>92320</x:v>
       </x:c>
       <x:c r="E451" s="1">
         <x:v>0</x:v>
@@ -13206,7 +13209,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G451" s="1">
-        <x:v>5714882</x:v>
+        <x:v>93370</x:v>
       </x:c>
     </x:row>
     <x:row r="452" spans="1:7">
@@ -13214,13 +13217,13 @@
         <x:v>508</x:v>
       </x:c>
       <x:c r="B452" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C452" s="1">
-        <x:v>1550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D452" s="1">
-        <x:v>378743</x:v>
+        <x:v>5714882</x:v>
       </x:c>
       <x:c r="E452" s="1">
         <x:v>0</x:v>
@@ -13229,7 +13232,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G452" s="1">
-        <x:v>380293</x:v>
+        <x:v>5714882</x:v>
       </x:c>
     </x:row>
     <x:row r="453" spans="1:7">
@@ -13237,13 +13240,13 @@
         <x:v>509</x:v>
       </x:c>
       <x:c r="B453" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C453" s="1">
         <x:v>1550</x:v>
       </x:c>
       <x:c r="D453" s="1">
-        <x:v>0</x:v>
+        <x:v>378743</x:v>
       </x:c>
       <x:c r="E453" s="1">
         <x:v>0</x:v>
@@ -13252,7 +13255,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G453" s="1">
-        <x:v>1550</x:v>
+        <x:v>380293</x:v>
       </x:c>
     </x:row>
     <x:row r="454" spans="1:7">
@@ -13260,10 +13263,10 @@
         <x:v>510</x:v>
       </x:c>
       <x:c r="B454" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C454" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D454" s="1">
         <x:v>0</x:v>
@@ -13275,7 +13278,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G454" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="455" spans="1:7">
@@ -13283,13 +13286,13 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="B455" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C455" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D455" s="1">
-        <x:v>504020</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E455" s="1">
         <x:v>0</x:v>
@@ -13298,7 +13301,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G455" s="1">
-        <x:v>504020</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="456" spans="1:7">
@@ -13306,13 +13309,13 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="B456" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C456" s="1">
-        <x:v>1550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D456" s="1">
-        <x:v>0</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="E456" s="1">
         <x:v>0</x:v>
@@ -13321,7 +13324,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G456" s="1">
-        <x:v>1550</x:v>
+        <x:v>504020</x:v>
       </x:c>
     </x:row>
     <x:row r="457" spans="1:7">
@@ -13329,10 +13332,10 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B457" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C457" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D457" s="1">
         <x:v>0</x:v>
@@ -13344,7 +13347,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G457" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="458" spans="1:7">
@@ -13352,7 +13355,7 @@
         <x:v>514</x:v>
       </x:c>
       <x:c r="B458" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C458" s="1">
         <x:v>50</x:v>
@@ -13375,10 +13378,10 @@
         <x:v>515</x:v>
       </x:c>
       <x:c r="B459" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C459" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D459" s="1">
         <x:v>0</x:v>
@@ -13387,10 +13390,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F459" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G459" s="1">
-        <x:v>3667</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="460" spans="1:7">
@@ -13398,22 +13401,22 @@
         <x:v>516</x:v>
       </x:c>
       <x:c r="B460" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C460" s="1">
-        <x:v>500</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D460" s="1">
-        <x:v>53970</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E460" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F460" s="1">
-        <x:v>1500</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G460" s="1">
-        <x:v>55970</x:v>
+        <x:v>3667</x:v>
       </x:c>
     </x:row>
     <x:row r="461" spans="1:7">
@@ -13421,22 +13424,22 @@
         <x:v>517</x:v>
       </x:c>
       <x:c r="B461" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C461" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D461" s="1">
-        <x:v>0</x:v>
+        <x:v>53970</x:v>
       </x:c>
       <x:c r="E461" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F461" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G461" s="1">
-        <x:v>50</x:v>
+        <x:v>55970</x:v>
       </x:c>
     </x:row>
     <x:row r="462" spans="1:7">
@@ -13444,10 +13447,10 @@
         <x:v>518</x:v>
       </x:c>
       <x:c r="B462" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C462" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D462" s="1">
         <x:v>0</x:v>
@@ -13456,10 +13459,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F462" s="1">
-        <x:v>6200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G462" s="1">
-        <x:v>7200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="463" spans="1:7">
@@ -13467,10 +13470,10 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="B463" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C463" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D463" s="1">
         <x:v>0</x:v>
@@ -13479,10 +13482,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F463" s="1">
-        <x:v>2000</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G463" s="1">
-        <x:v>2000</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="464" spans="1:7">
@@ -13490,10 +13493,10 @@
         <x:v>520</x:v>
       </x:c>
       <x:c r="B464" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C464" s="1">
-        <x:v>5050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D464" s="1">
         <x:v>0</x:v>
@@ -13502,10 +13505,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F464" s="1">
-        <x:v>1000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G464" s="1">
-        <x:v>6050</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="465" spans="1:7">
@@ -13513,10 +13516,10 @@
         <x:v>521</x:v>
       </x:c>
       <x:c r="B465" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C465" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D465" s="1">
         <x:v>0</x:v>
@@ -13525,10 +13528,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F465" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G465" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
     </x:row>
     <x:row r="466" spans="1:7">
@@ -13536,10 +13539,10 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B466" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C466" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D466" s="1">
         <x:v>0</x:v>
@@ -13551,7 +13554,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G466" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="467" spans="1:7">
@@ -13559,10 +13562,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B467" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C467" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D467" s="1">
         <x:v>0</x:v>
@@ -13574,7 +13577,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G467" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="468" spans="1:7">
@@ -13582,13 +13585,13 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="B468" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C468" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D468" s="1">
-        <x:v>726377</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E468" s="1">
         <x:v>0</x:v>
@@ -13597,7 +13600,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G468" s="1">
-        <x:v>726377</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="469" spans="1:7">
@@ -13605,22 +13608,22 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C469" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="E469" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F469" s="1">
-        <x:v>7600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>676049</x:v>
+        <x:v>726377</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -13628,22 +13631,22 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D470" s="1">
-        <x:v>0</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="E470" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F470" s="1">
-        <x:v>0</x:v>
+        <x:v>7600</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>1000</x:v>
+        <x:v>676049</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -13651,10 +13654,10 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D471" s="1">
         <x:v>0</x:v>
@@ -13663,10 +13666,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F471" s="1">
-        <x:v>1250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>1300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -13674,7 +13677,7 @@
         <x:v>528</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C472" s="1">
         <x:v>50</x:v>
@@ -13686,10 +13689,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>0</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>50</x:v>
+        <x:v>1300</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -13697,13 +13700,13 @@
         <x:v>529</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D473" s="1">
-        <x:v>120404787</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E473" s="1">
         <x:v>0</x:v>
@@ -13712,7 +13715,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>120406787</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -13720,13 +13723,13 @@
         <x:v>530</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C474" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D474" s="1">
-        <x:v>221403</x:v>
+        <x:v>120404787</x:v>
       </x:c>
       <x:c r="E474" s="1">
         <x:v>0</x:v>
@@ -13735,7 +13738,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G474" s="1">
-        <x:v>221403</x:v>
+        <x:v>120406787</x:v>
       </x:c>
     </x:row>
     <x:row r="475" spans="1:7">
@@ -13743,22 +13746,22 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B475" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C475" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D475" s="1">
-        <x:v>0</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="E475" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F475" s="1">
-        <x:v>3333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G475" s="1">
-        <x:v>4333</x:v>
+        <x:v>221403</x:v>
       </x:c>
     </x:row>
     <x:row r="476" spans="1:7">
@@ -13766,10 +13769,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B476" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C476" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D476" s="1">
         <x:v>0</x:v>
@@ -13778,10 +13781,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F476" s="1">
-        <x:v>0</x:v>
+        <x:v>3333</x:v>
       </x:c>
       <x:c r="G476" s="1">
-        <x:v>50</x:v>
+        <x:v>4333</x:v>
       </x:c>
     </x:row>
     <x:row r="477" spans="1:7">
@@ -13789,7 +13792,7 @@
         <x:v>533</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C477" s="1">
         <x:v>50</x:v>
@@ -13812,10 +13815,10 @@
         <x:v>534</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -13827,7 +13830,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -13835,10 +13838,10 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -13850,7 +13853,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -13858,10 +13861,10 @@
         <x:v>536</x:v>
       </x:c>
       <x:c r="B480" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C480" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D480" s="1">
         <x:v>0</x:v>
@@ -13870,10 +13873,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F480" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G480" s="1">
-        <x:v>5400</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="481" spans="1:7">
@@ -13881,10 +13884,10 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="B481" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C481" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D481" s="1">
         <x:v>0</x:v>
@@ -13893,10 +13896,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F481" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G481" s="1">
-        <x:v>50</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="482" spans="1:7">
@@ -13904,7 +13907,7 @@
         <x:v>538</x:v>
       </x:c>
       <x:c r="B482" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C482" s="1">
         <x:v>50</x:v>
@@ -13916,10 +13919,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F482" s="1">
-        <x:v>12000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G482" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="483" spans="1:7">
@@ -13927,7 +13930,7 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="B483" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C483" s="1">
         <x:v>50</x:v>
@@ -13939,10 +13942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F483" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G483" s="1">
-        <x:v>50</x:v>
+        <x:v>12050</x:v>
       </x:c>
     </x:row>
     <x:row r="484" spans="1:7">
@@ -13950,10 +13953,10 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="B484" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C484" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D484" s="1">
         <x:v>0</x:v>
@@ -13962,10 +13965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F484" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G484" s="1">
-        <x:v>250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="485" spans="1:7">
@@ -13973,10 +13976,10 @@
         <x:v>541</x:v>
       </x:c>
       <x:c r="B485" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C485" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D485" s="1">
         <x:v>0</x:v>
@@ -13985,10 +13988,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F485" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G485" s="1">
-        <x:v>50</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="486" spans="1:7">
@@ -13996,7 +13999,7 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C486" s="1">
         <x:v>50</x:v>
@@ -14008,10 +14011,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F486" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G486" s="1">
-        <x:v>2750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="487" spans="1:7">
@@ -14019,10 +14022,10 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="B487" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C487" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D487" s="1">
         <x:v>0</x:v>
@@ -14031,10 +14034,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F487" s="1">
-        <x:v>4600</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G487" s="1">
-        <x:v>4600</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="488" spans="1:7">
@@ -14042,10 +14045,10 @@
         <x:v>544</x:v>
       </x:c>
       <x:c r="B488" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C488" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D488" s="1">
         <x:v>0</x:v>
@@ -14054,10 +14057,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F488" s="1">
-        <x:v>0</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G488" s="1">
-        <x:v>50</x:v>
+        <x:v>4600</x:v>
       </x:c>
     </x:row>
     <x:row r="489" spans="1:7">
@@ -14065,7 +14068,7 @@
         <x:v>545</x:v>
       </x:c>
       <x:c r="B489" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C489" s="1">
         <x:v>50</x:v>
@@ -14088,7 +14091,7 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="B490" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C490" s="1">
         <x:v>50</x:v>
@@ -14111,7 +14114,7 @@
         <x:v>547</x:v>
       </x:c>
       <x:c r="B491" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C491" s="1">
         <x:v>50</x:v>
@@ -14134,13 +14137,13 @@
         <x:v>548</x:v>
       </x:c>
       <x:c r="B492" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C492" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D492" s="1">
-        <x:v>282526</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E492" s="1">
         <x:v>0</x:v>
@@ -14149,7 +14152,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G492" s="1">
-        <x:v>282526</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="493" spans="1:7">
@@ -14157,22 +14160,22 @@
         <x:v>549</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C493" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D493" s="1">
-        <x:v>0</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E493" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F493" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G493" s="1">
-        <x:v>1000</x:v>
+        <x:v>282526</x:v>
       </x:c>
     </x:row>
     <x:row r="494" spans="1:7">
@@ -14180,10 +14183,10 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="B494" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C494" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D494" s="1">
         <x:v>0</x:v>
@@ -14192,10 +14195,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F494" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G494" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="495" spans="1:7">
@@ -14203,22 +14206,22 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B495" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C495" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D495" s="1">
-        <x:v>116161</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E495" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F495" s="1">
-        <x:v>4500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G495" s="1">
-        <x:v>124661</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="496" spans="1:7">
@@ -14226,22 +14229,22 @@
         <x:v>552</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C496" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D496" s="1">
-        <x:v>0</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="E496" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F496" s="1">
-        <x:v>0</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G496" s="1">
-        <x:v>50</x:v>
+        <x:v>124661</x:v>
       </x:c>
     </x:row>
     <x:row r="497" spans="1:7">
@@ -14249,7 +14252,7 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B497" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C497" s="1">
         <x:v>50</x:v>
@@ -14272,7 +14275,7 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="B498" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C498" s="1">
         <x:v>50</x:v>
@@ -14292,10 +14295,10 @@
     </x:row>
     <x:row r="499" spans="1:7">
       <x:c r="A499" s="1" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="B499" s="1" t="s">
         <x:v>556</x:v>
-      </x:c>
-      <x:c r="B499" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C499" s="1">
         <x:v>50</x:v>
@@ -14318,22 +14321,22 @@
         <x:v>557</x:v>
       </x:c>
       <x:c r="B500" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C500" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D500" s="1">
-        <x:v>2997852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E500" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F500" s="1">
-        <x:v>6800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G500" s="1">
-        <x:v>3006652</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="501" spans="1:7">
@@ -14341,22 +14344,22 @@
         <x:v>558</x:v>
       </x:c>
       <x:c r="B501" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C501" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D501" s="1">
-        <x:v>7276846</x:v>
+        <x:v>2997852</x:v>
       </x:c>
       <x:c r="E501" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F501" s="1">
-        <x:v>0</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="G501" s="1">
-        <x:v>7276846</x:v>
+        <x:v>3006652</x:v>
       </x:c>
     </x:row>
     <x:row r="502" spans="1:7">
@@ -14364,13 +14367,13 @@
         <x:v>559</x:v>
       </x:c>
       <x:c r="B502" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C502" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D502" s="1">
-        <x:v>0</x:v>
+        <x:v>7276846</x:v>
       </x:c>
       <x:c r="E502" s="1">
         <x:v>0</x:v>
@@ -14379,7 +14382,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G502" s="1">
-        <x:v>50</x:v>
+        <x:v>7276846</x:v>
       </x:c>
     </x:row>
     <x:row r="503" spans="1:7">
@@ -14387,10 +14390,10 @@
         <x:v>560</x:v>
       </x:c>
       <x:c r="B503" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C503" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D503" s="1">
         <x:v>0</x:v>
@@ -14399,10 +14402,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F503" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G503" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="504" spans="1:7">
@@ -14410,7 +14413,7 @@
         <x:v>561</x:v>
       </x:c>
       <x:c r="B504" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C504" s="1">
         <x:v>0</x:v>
@@ -14422,10 +14425,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F504" s="1">
-        <x:v>5000</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="G504" s="1">
-        <x:v>5000</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="505" spans="1:7">
@@ -14433,10 +14436,10 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B505" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C505" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D505" s="1">
         <x:v>0</x:v>
@@ -14445,10 +14448,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F505" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G505" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="506" spans="1:7">
@@ -14456,10 +14459,10 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="B506" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C506" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D506" s="1">
         <x:v>0</x:v>
@@ -14468,10 +14471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F506" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G506" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="507" spans="1:7">
@@ -14479,10 +14482,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C507" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D507" s="1">
         <x:v>0</x:v>
@@ -14491,10 +14494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F507" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G507" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="508" spans="1:7">
@@ -14502,13 +14505,13 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B508" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C508" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D508" s="1">
-        <x:v>209387</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E508" s="1">
         <x:v>0</x:v>
@@ -14517,7 +14520,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G508" s="1">
-        <x:v>209387</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="509" spans="1:7">
@@ -14525,13 +14528,13 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C509" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D509" s="1">
-        <x:v>0</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="E509" s="1">
         <x:v>0</x:v>
@@ -14540,7 +14543,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G509" s="1">
-        <x:v>50</x:v>
+        <x:v>209387</x:v>
       </x:c>
     </x:row>
     <x:row r="510" spans="1:7">
@@ -14548,13 +14551,13 @@
         <x:v>567</x:v>
       </x:c>
       <x:c r="B510" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C510" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D510" s="1">
-        <x:v>257695</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E510" s="1">
         <x:v>0</x:v>
@@ -14563,7 +14566,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G510" s="1">
-        <x:v>257695</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="511" spans="1:7">
@@ -14571,22 +14574,22 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C511" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D511" s="1">
-        <x:v>0</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="E511" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F511" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G511" s="1">
-        <x:v>3300</x:v>
+        <x:v>257695</x:v>
       </x:c>
     </x:row>
     <x:row r="512" spans="1:7">
@@ -14594,10 +14597,10 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B512" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C512" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D512" s="1">
         <x:v>0</x:v>
@@ -14606,10 +14609,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F512" s="1">
-        <x:v>29800</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G512" s="1">
-        <x:v>34800</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="513" spans="1:7">
@@ -14617,10 +14620,10 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C513" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D513" s="1">
         <x:v>0</x:v>
@@ -14629,10 +14632,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F513" s="1">
-        <x:v>0</x:v>
+        <x:v>29800</x:v>
       </x:c>
       <x:c r="G513" s="1">
-        <x:v>50</x:v>
+        <x:v>34800</x:v>
       </x:c>
     </x:row>
     <x:row r="514" spans="1:7">
@@ -14640,7 +14643,7 @@
         <x:v>571</x:v>
       </x:c>
       <x:c r="B514" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C514" s="1">
         <x:v>50</x:v>
@@ -14652,10 +14655,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F514" s="1">
-        <x:v>5600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G514" s="1">
-        <x:v>5650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="515" spans="1:7">
@@ -14663,10 +14666,10 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="B515" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C515" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D515" s="1">
         <x:v>0</x:v>
@@ -14675,10 +14678,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F515" s="1">
-        <x:v>0</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G515" s="1">
-        <x:v>2050</x:v>
+        <x:v>5650</x:v>
       </x:c>
     </x:row>
     <x:row r="516" spans="1:7">
@@ -14686,10 +14689,10 @@
         <x:v>573</x:v>
       </x:c>
       <x:c r="B516" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C516" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D516" s="1">
         <x:v>0</x:v>
@@ -14698,10 +14701,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F516" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G516" s="1">
-        <x:v>3384</x:v>
+        <x:v>2050</x:v>
       </x:c>
     </x:row>
     <x:row r="517" spans="1:7">
@@ -14709,7 +14712,7 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="B517" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C517" s="1">
         <x:v>50</x:v>
@@ -14721,10 +14724,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F517" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G517" s="1">
-        <x:v>50</x:v>
+        <x:v>3384</x:v>
       </x:c>
     </x:row>
     <x:row r="518" spans="1:7">
@@ -14732,22 +14735,22 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C518" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D518" s="1">
-        <x:v>558813</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E518" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F518" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G518" s="1">
-        <x:v>559813</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="519" spans="1:7">
@@ -14755,22 +14758,22 @@
         <x:v>576</x:v>
       </x:c>
       <x:c r="B519" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C519" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D519" s="1">
-        <x:v>0</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E519" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F519" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G519" s="1">
-        <x:v>6650</x:v>
+        <x:v>559813</x:v>
       </x:c>
     </x:row>
     <x:row r="520" spans="1:7">
@@ -14778,22 +14781,22 @@
         <x:v>577</x:v>
       </x:c>
       <x:c r="B520" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C520" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D520" s="1">
-        <x:v>4500000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E520" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F520" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G520" s="1">
-        <x:v>4500000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="521" spans="1:7">
@@ -14801,13 +14804,13 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B521" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C521" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D521" s="1">
-        <x:v>0</x:v>
+        <x:v>4500000</x:v>
       </x:c>
       <x:c r="E521" s="1">
         <x:v>0</x:v>
@@ -14816,7 +14819,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G521" s="1">
-        <x:v>50</x:v>
+        <x:v>4500000</x:v>
       </x:c>
     </x:row>
     <x:row r="522" spans="1:7">
@@ -14824,22 +14827,22 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C522" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D522" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E522" s="1">
-        <x:v>20483</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F522" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G522" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="523" spans="1:7">
@@ -14847,22 +14850,22 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B523" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C523" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D523" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E523" s="1">
-        <x:v>0</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="F523" s="1">
-        <x:v>1089100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G523" s="1">
-        <x:v>1089150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="524" spans="1:7">
@@ -14870,22 +14873,22 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C524" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D524" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E524" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F524" s="1">
-        <x:v>0</x:v>
+        <x:v>1089100</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>1927706</x:v>
+        <x:v>1089150</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -14893,13 +14896,13 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C525" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D525" s="1">
-        <x:v>0</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="E525" s="1">
         <x:v>0</x:v>
@@ -14908,7 +14911,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G525" s="1">
-        <x:v>50</x:v>
+        <x:v>1927706</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:7">
@@ -14916,7 +14919,7 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C526" s="1">
         <x:v>50</x:v>
@@ -14939,7 +14942,7 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B527" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C527" s="1">
         <x:v>50</x:v>
@@ -14962,10 +14965,10 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="B528" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C528" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D528" s="1">
         <x:v>0</x:v>
@@ -14974,10 +14977,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F528" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G528" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="529" spans="1:7">
@@ -14985,10 +14988,10 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C529" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D529" s="1">
         <x:v>0</x:v>
@@ -14997,10 +15000,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F529" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G529" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="530" spans="1:7">
@@ -15008,7 +15011,7 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="B530" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C530" s="1">
         <x:v>50</x:v>
@@ -15020,10 +15023,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F530" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G530" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="531" spans="1:7">
@@ -15031,22 +15034,22 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="B531" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C531" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D531" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E531" s="1">
-        <x:v>817066</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F531" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G531" s="1">
-        <x:v>0</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="532" spans="1:7">
@@ -15054,22 +15057,22 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C532" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D532" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E532" s="1">
-        <x:v>0</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="F532" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G532" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="533" spans="1:7">
@@ -15077,7 +15080,7 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C533" s="1">
         <x:v>50</x:v>
@@ -15100,22 +15103,22 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="B534" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C534" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D534" s="1">
-        <x:v>88256</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E534" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F534" s="1">
-        <x:v>14866</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G534" s="1">
-        <x:v>117122</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="535" spans="1:7">
@@ -15123,22 +15126,22 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B535" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C535" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D535" s="1">
-        <x:v>0</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="E535" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F535" s="1">
-        <x:v>0</x:v>
+        <x:v>14866</x:v>
       </x:c>
       <x:c r="G535" s="1">
-        <x:v>50</x:v>
+        <x:v>117122</x:v>
       </x:c>
     </x:row>
     <x:row r="536" spans="1:7">
@@ -15146,7 +15149,7 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C536" s="1">
         <x:v>50</x:v>
@@ -15169,7 +15172,7 @@
         <x:v>594</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>595</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C537" s="1">
         <x:v>50</x:v>
@@ -15189,10 +15192,10 @@
     </x:row>
     <x:row r="538" spans="1:7">
       <x:c r="A538" s="1" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="B538" s="1" t="s">
         <x:v>596</x:v>
-      </x:c>
-      <x:c r="B538" s="1" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="C538" s="1">
         <x:v>50</x:v>
@@ -15215,10 +15218,10 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C539" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D539" s="1">
         <x:v>0</x:v>
@@ -15227,10 +15230,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F539" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G539" s="1">
-        <x:v>6000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="540" spans="1:7">
@@ -15241,19 +15244,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C540" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D540" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E540" s="1">
-        <x:v>10041119</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F540" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G540" s="1">
-        <x:v>50</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:7">
@@ -15261,7 +15264,7 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B541" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C541" s="1">
         <x:v>50</x:v>
@@ -15270,13 +15273,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E541" s="1">
-        <x:v>0</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="F541" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G541" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:7">
@@ -15284,7 +15287,7 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B542" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C542" s="1">
         <x:v>50</x:v>
@@ -15296,10 +15299,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F542" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G542" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="543" spans="1:7">
@@ -15307,10 +15310,10 @@
         <x:v>601</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C543" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D543" s="1">
         <x:v>0</x:v>
@@ -15319,10 +15322,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F543" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15330,10 +15333,10 @@
         <x:v>602</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C544" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D544" s="1">
         <x:v>0</x:v>
@@ -15342,10 +15345,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">
@@ -15353,7 +15356,7 @@
         <x:v>603</x:v>
       </x:c>
       <x:c r="B545" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C545" s="1">
         <x:v>50</x:v>
@@ -15376,7 +15379,7 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B546" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C546" s="1">
         <x:v>50</x:v>
@@ -15399,10 +15402,10 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C547" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D547" s="1">
         <x:v>0</x:v>
@@ -15411,10 +15414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F547" s="1">
-        <x:v>-19405</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G547" s="1">
-        <x:v>-19405</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="548" spans="1:7">
@@ -15422,22 +15425,22 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B548" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C548" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D548" s="1">
-        <x:v>1491280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E548" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F548" s="1">
-        <x:v>0</x:v>
+        <x:v>-19405</x:v>
       </x:c>
       <x:c r="G548" s="1">
-        <x:v>1491280</x:v>
+        <x:v>-19405</x:v>
       </x:c>
     </x:row>
     <x:row r="549" spans="1:7">
@@ -15445,22 +15448,22 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C549" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D549" s="1">
-        <x:v>0</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="E549" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F549" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G549" s="1">
-        <x:v>500</x:v>
+        <x:v>1491280</x:v>
       </x:c>
     </x:row>
     <x:row r="550" spans="1:7">
@@ -15468,10 +15471,10 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C550" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D550" s="1">
         <x:v>0</x:v>
@@ -15480,10 +15483,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F550" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G550" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="551" spans="1:7">
@@ -15491,7 +15494,7 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C551" s="1">
         <x:v>50</x:v>
@@ -15503,10 +15506,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F551" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -15514,7 +15517,7 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B552" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C552" s="1">
         <x:v>50</x:v>
@@ -15526,10 +15529,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F552" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G552" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="553" spans="1:7">
@@ -15537,7 +15540,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B553" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C553" s="1">
         <x:v>50</x:v>
@@ -15549,10 +15552,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F553" s="1">
-        <x:v>1287</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G553" s="1">
-        <x:v>1337</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="554" spans="1:7">
@@ -15560,10 +15563,10 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C554" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D554" s="1">
         <x:v>0</x:v>
@@ -15572,10 +15575,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F554" s="1">
-        <x:v>6697</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G554" s="1">
-        <x:v>6697</x:v>
+        <x:v>1337</x:v>
       </x:c>
     </x:row>
     <x:row r="555" spans="1:7">
@@ -15583,10 +15586,10 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B555" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C555" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D555" s="1">
         <x:v>0</x:v>
@@ -15595,10 +15598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F555" s="1">
-        <x:v>0</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="G555" s="1">
-        <x:v>50</x:v>
+        <x:v>6697</x:v>
       </x:c>
     </x:row>
     <x:row r="556" spans="1:7">
@@ -15606,10 +15609,10 @@
         <x:v>614</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C556" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D556" s="1">
         <x:v>0</x:v>
@@ -15618,10 +15621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F556" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G556" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:7">
@@ -15629,7 +15632,7 @@
         <x:v>615</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C557" s="1">
         <x:v>0</x:v>
@@ -15641,10 +15644,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F557" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="G557" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="558" spans="1:7">
@@ -15652,10 +15655,10 @@
         <x:v>616</x:v>
       </x:c>
       <x:c r="B558" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C558" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D558" s="1">
         <x:v>0</x:v>
@@ -15664,10 +15667,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F558" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G558" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="559" spans="1:7">
@@ -15675,7 +15678,7 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C559" s="1">
         <x:v>50</x:v>
@@ -15698,7 +15701,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C560" s="1">
         <x:v>50</x:v>
@@ -15721,13 +15724,13 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C561" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D561" s="1">
-        <x:v>700000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E561" s="1">
         <x:v>0</x:v>
@@ -15736,7 +15739,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G561" s="1">
-        <x:v>702500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="562" spans="1:7">
@@ -15744,13 +15747,13 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B562" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C562" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D562" s="1">
-        <x:v>0</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="E562" s="1">
         <x:v>0</x:v>
@@ -15759,7 +15762,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G562" s="1">
-        <x:v>50</x:v>
+        <x:v>702500</x:v>
       </x:c>
     </x:row>
     <x:row r="563" spans="1:7">
@@ -15767,10 +15770,10 @@
         <x:v>621</x:v>
       </x:c>
       <x:c r="B563" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C563" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D563" s="1">
         <x:v>0</x:v>
@@ -15779,10 +15782,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F563" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G563" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="564" spans="1:7">
@@ -15790,10 +15793,10 @@
         <x:v>622</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C564" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D564" s="1">
         <x:v>0</x:v>
@@ -15802,10 +15805,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F564" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G564" s="1">
-        <x:v>50</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="565" spans="1:7">
@@ -15813,7 +15816,7 @@
         <x:v>623</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>50</x:v>
@@ -15836,7 +15839,7 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>50</x:v>
@@ -15859,7 +15862,7 @@
         <x:v>625</x:v>
       </x:c>
       <x:c r="B567" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C567" s="1">
         <x:v>50</x:v>
@@ -15882,7 +15885,7 @@
         <x:v>626</x:v>
       </x:c>
       <x:c r="B568" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C568" s="1">
         <x:v>50</x:v>
@@ -15905,7 +15908,7 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C569" s="1">
         <x:v>50</x:v>
@@ -15928,13 +15931,13 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C570" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D570" s="1">
-        <x:v>183694</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E570" s="1">
         <x:v>0</x:v>
@@ -15943,7 +15946,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G570" s="1">
-        <x:v>183694</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="571" spans="1:7">
@@ -15951,22 +15954,22 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B571" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C571" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D571" s="1">
-        <x:v>0</x:v>
+        <x:v>183694</x:v>
       </x:c>
       <x:c r="E571" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F571" s="1">
-        <x:v>81050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G571" s="1">
-        <x:v>81050</x:v>
+        <x:v>183694</x:v>
       </x:c>
     </x:row>
     <x:row r="572" spans="1:7">
@@ -15974,10 +15977,10 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="B572" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C572" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D572" s="1">
         <x:v>0</x:v>
@@ -15986,10 +15989,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F572" s="1">
-        <x:v>0</x:v>
+        <x:v>81050</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>50</x:v>
+        <x:v>81050</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -15997,7 +16000,7 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C573" s="1">
         <x:v>50</x:v>
@@ -16020,10 +16023,10 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C574" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D574" s="1">
         <x:v>0</x:v>
@@ -16035,7 +16038,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G574" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="575" spans="1:7">
@@ -16043,10 +16046,10 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="B575" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C575" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D575" s="1">
         <x:v>0</x:v>
@@ -16058,7 +16061,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G575" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
     </x:row>
     <x:row r="576" spans="1:7">
@@ -16066,7 +16069,7 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="B576" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C576" s="1">
         <x:v>50</x:v>
@@ -16078,10 +16081,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F576" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G576" s="1">
-        <x:v>14050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="577" spans="1:7">
@@ -16089,10 +16092,10 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B577" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C577" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D577" s="1">
         <x:v>0</x:v>
@@ -16101,10 +16104,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F577" s="1">
-        <x:v>2700</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G577" s="1">
-        <x:v>2700</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="578" spans="1:7">
@@ -16112,7 +16115,7 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="B578" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C578" s="1">
         <x:v>0</x:v>
@@ -16124,10 +16127,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F578" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G578" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="579" spans="1:7">
@@ -16135,30 +16138,30 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B579" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C579" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D579" s="1">
-        <x:v>7276846</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E579" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F579" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G579" s="1">
-        <x:v>7276846</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="580" spans="1:7">
       <x:c r="A580" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C580" s="1">
         <x:v>0</x:v>
@@ -16181,13 +16184,13 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B581" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C581" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D581" s="1">
-        <x:v>0</x:v>
+        <x:v>7276846</x:v>
       </x:c>
       <x:c r="E581" s="1">
         <x:v>0</x:v>
@@ -16196,7 +16199,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G581" s="1">
-        <x:v>50</x:v>
+        <x:v>7276846</x:v>
       </x:c>
     </x:row>
     <x:row r="582" spans="1:7">
@@ -16204,10 +16207,10 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C582" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D582" s="1">
         <x:v>0</x:v>
@@ -16216,10 +16219,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F582" s="1">
-        <x:v>11834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G582" s="1">
-        <x:v>23884</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="583" spans="1:7">
@@ -16227,10 +16230,10 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B583" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="C583" s="1">
-        <x:v>100</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="D583" s="1">
         <x:v>0</x:v>
@@ -16239,10 +16242,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F583" s="1">
-        <x:v>0</x:v>
+        <x:v>11834</x:v>
       </x:c>
       <x:c r="G583" s="1">
-        <x:v>100</x:v>
+        <x:v>23884</x:v>
       </x:c>
     </x:row>
     <x:row r="584" spans="1:7">
@@ -16250,10 +16253,10 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="B584" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C584" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D584" s="1">
         <x:v>0</x:v>
@@ -16265,7 +16268,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G584" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:7">
@@ -16273,7 +16276,7 @@
         <x:v>642</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C585" s="1">
         <x:v>50</x:v>
@@ -16296,7 +16299,7 @@
         <x:v>643</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>50</x:v>
@@ -16308,10 +16311,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -16319,7 +16322,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C587" s="1">
         <x:v>50</x:v>
@@ -16331,10 +16334,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F587" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G587" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="588" spans="1:7">
@@ -16342,7 +16345,7 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C588" s="1">
         <x:v>50</x:v>
@@ -16365,7 +16368,7 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C589" s="1">
         <x:v>50</x:v>
@@ -16388,7 +16391,7 @@
         <x:v>647</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C590" s="1">
         <x:v>50</x:v>
@@ -16411,22 +16414,22 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C591" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D591" s="1">
-        <x:v>3975320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E591" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F591" s="1">
-        <x:v>6634</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G591" s="1">
-        <x:v>3982954</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="592" spans="1:7">
@@ -16434,22 +16437,22 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C592" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D592" s="1">
-        <x:v>0</x:v>
+        <x:v>3975320</x:v>
       </x:c>
       <x:c r="E592" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F592" s="1">
-        <x:v>22000</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G592" s="1">
-        <x:v>22000</x:v>
+        <x:v>3982954</x:v>
       </x:c>
     </x:row>
     <x:row r="593" spans="1:7">
@@ -16457,10 +16460,10 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="B593" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C593" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D593" s="1">
         <x:v>0</x:v>
@@ -16469,10 +16472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F593" s="1">
-        <x:v>5800</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G593" s="1">
-        <x:v>5850</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="594" spans="1:7">
@@ -16480,7 +16483,7 @@
         <x:v>651</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>652</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C594" s="1">
         <x:v>50</x:v>
@@ -16492,21 +16495,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F594" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G594" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="595" spans="1:7">
       <x:c r="A595" s="1" t="s">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="B595" s="1" t="s">
         <x:v>653</x:v>
       </x:c>
-      <x:c r="B595" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C595" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D595" s="1">
         <x:v>0</x:v>
@@ -16515,10 +16518,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F595" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G595" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="596" spans="1:7">
@@ -16526,10 +16529,10 @@
         <x:v>654</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>655</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C596" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D596" s="1">
         <x:v>0</x:v>
@@ -16538,18 +16541,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F596" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G596" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="597" spans="1:7">
       <x:c r="A597" s="1" t="s">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="B597" s="1" t="s">
         <x:v>656</x:v>
-      </x:c>
-      <x:c r="B597" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C597" s="1">
         <x:v>50</x:v>
@@ -16572,7 +16575,7 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C598" s="1">
         <x:v>50</x:v>
@@ -16592,13 +16595,13 @@
     </x:row>
     <x:row r="599" spans="1:7">
       <x:c r="A599" s="1" t="s">
-        <x:v>657</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C599" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D599" s="1">
         <x:v>0</x:v>
@@ -16607,10 +16610,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F599" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G599" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="600" spans="1:7">
@@ -16618,10 +16621,10 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C600" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D600" s="1">
         <x:v>0</x:v>
@@ -16630,10 +16633,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F600" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G600" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="601" spans="1:7">
@@ -16641,7 +16644,7 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C601" s="1">
         <x:v>50</x:v>
@@ -16664,10 +16667,10 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C602" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D602" s="1">
         <x:v>0</x:v>
@@ -16676,10 +16679,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F602" s="1">
-        <x:v>68600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>71150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -16687,10 +16690,10 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C603" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D603" s="1">
         <x:v>0</x:v>
@@ -16699,10 +16702,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F603" s="1">
-        <x:v>0</x:v>
+        <x:v>68600</x:v>
       </x:c>
       <x:c r="G603" s="1">
-        <x:v>50</x:v>
+        <x:v>71150</x:v>
       </x:c>
     </x:row>
     <x:row r="604" spans="1:7">
@@ -16710,7 +16713,7 @@
         <x:v>662</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C604" s="1">
         <x:v>50</x:v>
@@ -16733,10 +16736,10 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16745,10 +16748,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16756,10 +16759,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16768,10 +16771,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>58000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>58050</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -16779,10 +16782,10 @@
         <x:v>665</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C607" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D607" s="1">
         <x:v>0</x:v>
@@ -16791,10 +16794,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F607" s="1">
-        <x:v>1666</x:v>
+        <x:v>58000</x:v>
       </x:c>
       <x:c r="G607" s="1">
-        <x:v>3716</x:v>
+        <x:v>58050</x:v>
       </x:c>
     </x:row>
     <x:row r="608" spans="1:7">
@@ -16802,10 +16805,10 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C608" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D608" s="1">
         <x:v>0</x:v>
@@ -16814,10 +16817,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F608" s="1">
-        <x:v>1668</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="G608" s="1">
-        <x:v>1668</x:v>
+        <x:v>3716</x:v>
       </x:c>
     </x:row>
     <x:row r="609" spans="1:7">
@@ -16825,10 +16828,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B609" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C609" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D609" s="1">
         <x:v>0</x:v>
@@ -16837,10 +16840,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F609" s="1">
-        <x:v>0</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G609" s="1">
-        <x:v>50</x:v>
+        <x:v>1668</x:v>
       </x:c>
     </x:row>
     <x:row r="610" spans="1:7">
@@ -16848,7 +16851,7 @@
         <x:v>668</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C610" s="1">
         <x:v>50</x:v>
@@ -16871,10 +16874,10 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C611" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D611" s="1">
         <x:v>0</x:v>
@@ -16883,10 +16886,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F611" s="1">
-        <x:v>30600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G611" s="1">
-        <x:v>33550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="612" spans="1:7">
@@ -16894,10 +16897,10 @@
         <x:v>670</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C612" s="1">
-        <x:v>2550</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D612" s="1">
         <x:v>0</x:v>
@@ -16906,10 +16909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F612" s="1">
-        <x:v>0</x:v>
+        <x:v>30600</x:v>
       </x:c>
       <x:c r="G612" s="1">
-        <x:v>2550</x:v>
+        <x:v>33550</x:v>
       </x:c>
     </x:row>
     <x:row r="613" spans="1:7">
@@ -16917,22 +16920,22 @@
         <x:v>671</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C613" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D613" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E613" s="1">
-        <x:v>56045</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F613" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G613" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:7">
@@ -16949,7 +16952,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E614" s="1">
-        <x:v>0</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="F614" s="1">
         <x:v>0</x:v>
@@ -16963,10 +16966,10 @@
         <x:v>673</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -16978,7 +16981,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -16986,10 +16989,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D616" s="1">
         <x:v>0</x:v>
@@ -17001,7 +17004,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -17009,10 +17012,10 @@
         <x:v>675</x:v>
       </x:c>
       <x:c r="B617" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C617" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D617" s="1">
         <x:v>0</x:v>
@@ -17024,21 +17027,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G617" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="618" spans="1:7">
       <x:c r="A618" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="B618" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C618" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D618" s="1">
-        <x:v>550000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E618" s="1">
         <x:v>0</x:v>
@@ -17047,7 +17050,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G618" s="1">
-        <x:v>550000</x:v>
+        <x:v>4550</x:v>
       </x:c>
     </x:row>
     <x:row r="619" spans="1:7">
@@ -17061,7 +17064,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D619" s="1">
-        <x:v>426280</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E619" s="1">
         <x:v>0</x:v>
@@ -17070,7 +17073,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G619" s="1">
-        <x:v>426280</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="620" spans="1:7">
@@ -17078,13 +17081,13 @@
         <x:v>677</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C620" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D620" s="1">
-        <x:v>0</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="E620" s="1">
         <x:v>0</x:v>
@@ -17093,7 +17096,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G620" s="1">
-        <x:v>50</x:v>
+        <x:v>426280</x:v>
       </x:c>
     </x:row>
     <x:row r="621" spans="1:7">
@@ -17101,7 +17104,7 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C621" s="1">
         <x:v>50</x:v>
@@ -17124,13 +17127,13 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C622" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D622" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E622" s="1">
         <x:v>0</x:v>
@@ -17139,7 +17142,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G622" s="1">
-        <x:v>1100000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="623" spans="1:7">
@@ -17147,13 +17150,13 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C623" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D623" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E623" s="1">
         <x:v>0</x:v>
@@ -17162,7 +17165,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G623" s="1">
-        <x:v>50</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="624" spans="1:7">
@@ -17170,7 +17173,7 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C624" s="1">
         <x:v>50</x:v>
@@ -17193,7 +17196,7 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C625" s="1">
         <x:v>50</x:v>
@@ -17216,10 +17219,10 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17231,7 +17234,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17239,10 +17242,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17254,7 +17257,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -17262,10 +17265,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B628" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C628" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D628" s="1">
         <x:v>0</x:v>
@@ -17277,7 +17280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G628" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:7">
@@ -17285,10 +17288,10 @@
         <x:v>686</x:v>
       </x:c>
       <x:c r="B629" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C629" s="1">
-        <x:v>1050</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D629" s="1">
         <x:v>0</x:v>
@@ -17297,10 +17300,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F629" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G629" s="1">
-        <x:v>2717</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="630" spans="1:7">
@@ -17308,10 +17311,10 @@
         <x:v>687</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C630" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D630" s="1">
         <x:v>0</x:v>
@@ -17320,10 +17323,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F630" s="1">
-        <x:v>0</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G630" s="1">
-        <x:v>50</x:v>
+        <x:v>2717</x:v>
       </x:c>
     </x:row>
     <x:row r="631" spans="1:7">
@@ -17331,22 +17334,22 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D631" s="1">
-        <x:v>55799</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E631" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>59099</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -17354,22 +17357,22 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D632" s="1">
-        <x:v>0</x:v>
+        <x:v>55799</x:v>
       </x:c>
       <x:c r="E632" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>50</x:v>
+        <x:v>59099</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17377,7 +17380,7 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C633" s="1">
         <x:v>50</x:v>
@@ -17400,7 +17403,7 @@
         <x:v>691</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C634" s="1">
         <x:v>50</x:v>
@@ -17423,22 +17426,22 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C635" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D635" s="1">
-        <x:v>10046680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E635" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F635" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G635" s="1">
-        <x:v>10048730</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:7">
@@ -17446,22 +17449,22 @@
         <x:v>693</x:v>
       </x:c>
       <x:c r="B636" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C636" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D636" s="1">
-        <x:v>1131900</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E636" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F636" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G636" s="1">
-        <x:v>1131950</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="637" spans="1:7">
@@ -17469,13 +17472,13 @@
         <x:v>694</x:v>
       </x:c>
       <x:c r="B637" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C637" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D637" s="1">
-        <x:v>0</x:v>
+        <x:v>1131900</x:v>
       </x:c>
       <x:c r="E637" s="1">
         <x:v>0</x:v>
@@ -17484,7 +17487,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G637" s="1">
-        <x:v>50</x:v>
+        <x:v>1131950</x:v>
       </x:c>
     </x:row>
     <x:row r="638" spans="1:7">
@@ -17492,7 +17495,7 @@
         <x:v>695</x:v>
       </x:c>
       <x:c r="B638" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C638" s="1">
         <x:v>50</x:v>
@@ -17504,10 +17507,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F638" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G638" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="639" spans="1:7">
@@ -17515,10 +17518,10 @@
         <x:v>696</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C639" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D639" s="1">
         <x:v>0</x:v>
@@ -17527,10 +17530,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F639" s="1">
-        <x:v>52333</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>58383</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -17538,10 +17541,10 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C640" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D640" s="1">
         <x:v>0</x:v>
@@ -17550,10 +17553,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F640" s="1">
-        <x:v>0</x:v>
+        <x:v>52333</x:v>
       </x:c>
       <x:c r="G640" s="1">
-        <x:v>50</x:v>
+        <x:v>58383</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:7">
@@ -17561,7 +17564,7 @@
         <x:v>698</x:v>
       </x:c>
       <x:c r="B641" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C641" s="1">
         <x:v>50</x:v>
@@ -17584,10 +17587,10 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C642" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D642" s="1">
         <x:v>0</x:v>
@@ -17596,10 +17599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F642" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G642" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:7">
@@ -17607,22 +17610,22 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="B643" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C643" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D643" s="1">
-        <x:v>817169</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E643" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F643" s="1">
-        <x:v>1668</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G643" s="1">
-        <x:v>820837</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="644" spans="1:7">
@@ -17630,22 +17633,22 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>11050</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F644" s="1">
-        <x:v>6242</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>17292</x:v>
+        <x:v>820837</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17653,10 +17656,10 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D645" s="1">
         <x:v>0</x:v>
@@ -17665,10 +17668,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>0</x:v>
+        <x:v>6242</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>50</x:v>
+        <x:v>17292</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17676,7 +17679,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C646" s="1">
         <x:v>50</x:v>
@@ -17699,7 +17702,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="B647" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C647" s="1">
         <x:v>50</x:v>
@@ -17711,10 +17714,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F647" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G647" s="1">
-        <x:v>25050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="648" spans="1:7">
@@ -17722,7 +17725,7 @@
         <x:v>705</x:v>
       </x:c>
       <x:c r="B648" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C648" s="1">
         <x:v>50</x:v>
@@ -17734,10 +17737,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F648" s="1">
-        <x:v>0</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G648" s="1">
-        <x:v>50</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="649" spans="1:7">
@@ -17745,22 +17748,22 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B649" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C649" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D649" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E649" s="1">
-        <x:v>1531015</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F649" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G649" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:7">
@@ -17768,22 +17771,22 @@
         <x:v>707</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C650" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D650" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E650" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F650" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G650" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:7">
@@ -17791,7 +17794,7 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C651" s="1">
         <x:v>50</x:v>
@@ -17814,13 +17817,13 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C652" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D652" s="1">
-        <x:v>5583432</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E652" s="1">
         <x:v>0</x:v>
@@ -17829,7 +17832,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>5584432</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -17837,13 +17840,13 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D653" s="1">
-        <x:v>0</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E653" s="1">
         <x:v>0</x:v>
@@ -17852,7 +17855,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>50</x:v>
+        <x:v>5584432</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
@@ -17860,13 +17863,13 @@
         <x:v>711</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C654" s="1">
-        <x:v>18050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D654" s="1">
-        <x:v>764206</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E654" s="1">
         <x:v>0</x:v>
@@ -17875,7 +17878,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G654" s="1">
-        <x:v>782256</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="655" spans="1:7">
@@ -17883,22 +17886,22 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C655" s="1">
-        <x:v>0</x:v>
+        <x:v>18050</x:v>
       </x:c>
       <x:c r="D655" s="1">
-        <x:v>0</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="E655" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F655" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G655" s="1">
-        <x:v>2700</x:v>
+        <x:v>782256</x:v>
       </x:c>
     </x:row>
     <x:row r="656" spans="1:7">
@@ -17906,22 +17909,22 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C656" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>1543316</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F656" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -17929,22 +17932,22 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C657" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D657" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E657" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F657" s="1">
-        <x:v>14500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G657" s="1">
-        <x:v>14550</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:7">
@@ -17952,7 +17955,7 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B658" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C658" s="1">
         <x:v>50</x:v>
@@ -17964,10 +17967,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F658" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G658" s="1">
-        <x:v>50</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:7">
@@ -17975,7 +17978,7 @@
         <x:v>716</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C659" s="1">
         <x:v>50</x:v>
@@ -17998,13 +18001,13 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C660" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D660" s="1">
-        <x:v>107353</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E660" s="1">
         <x:v>0</x:v>
@@ -18013,7 +18016,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>107403</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18021,22 +18024,22 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>0</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="E661" s="1">
-        <x:v>9985740</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F661" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>0</x:v>
+        <x:v>107403</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18044,7 +18047,7 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C662" s="1">
         <x:v>0</x:v>
@@ -18053,13 +18056,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E662" s="1">
-        <x:v>0</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="F662" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -18067,22 +18070,22 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C663" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D663" s="1">
-        <x:v>106947</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E663" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F663" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G663" s="1">
-        <x:v>106947</x:v>
+        <x:v>3334</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:7">
@@ -18090,22 +18093,22 @@
         <x:v>721</x:v>
       </x:c>
       <x:c r="B664" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C664" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D664" s="1">
-        <x:v>0</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="E664" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F664" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G664" s="1">
-        <x:v>25050</x:v>
+        <x:v>106947</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:7">
@@ -18113,22 +18116,22 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B665" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C665" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D665" s="1">
-        <x:v>902176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E665" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F665" s="1">
-        <x:v>7000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G665" s="1">
-        <x:v>910226</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:7">
@@ -18136,22 +18139,22 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C666" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D666" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E666" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F666" s="1">
-        <x:v>25500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G666" s="1">
-        <x:v>25550</x:v>
+        <x:v>910226</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:7">
@@ -18171,10 +18174,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F667" s="1">
-        <x:v>0</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="G667" s="1">
-        <x:v>50</x:v>
+        <x:v>25550</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:7">
@@ -18182,10 +18185,10 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C668" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D668" s="1">
         <x:v>0</x:v>
@@ -18194,10 +18197,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F668" s="1">
-        <x:v>10500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>10500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -18205,7 +18208,7 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C669" s="1">
         <x:v>0</x:v>
@@ -18217,10 +18220,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F669" s="1">
-        <x:v>6200</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>6200</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
@@ -18228,10 +18231,10 @@
         <x:v>727</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C670" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D670" s="1">
         <x:v>0</x:v>
@@ -18240,10 +18243,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F670" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G670" s="1">
-        <x:v>50</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="671" spans="1:7">
@@ -18251,10 +18254,10 @@
         <x:v>728</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C671" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D671" s="1">
         <x:v>0</x:v>
@@ -18266,7 +18269,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">
@@ -18274,10 +18277,10 @@
         <x:v>729</x:v>
       </x:c>
       <x:c r="B672" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C672" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D672" s="1">
         <x:v>0</x:v>
@@ -18286,10 +18289,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F672" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G672" s="1">
-        <x:v>6650</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="673" spans="1:7">
@@ -18297,22 +18300,22 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B673" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C673" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D673" s="1">
-        <x:v>1010142</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E673" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F673" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G673" s="1">
-        <x:v>1010142</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="674" spans="1:7">
@@ -18320,22 +18323,22 @@
         <x:v>731</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C674" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D674" s="1">
-        <x:v>0</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="E674" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F674" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G674" s="1">
-        <x:v>5000</x:v>
+        <x:v>1010142</x:v>
       </x:c>
     </x:row>
     <x:row r="675" spans="1:7">
@@ -18343,10 +18346,10 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C675" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D675" s="1">
         <x:v>0</x:v>
@@ -18355,10 +18358,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F675" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G675" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:7">
@@ -18366,10 +18369,10 @@
         <x:v>733</x:v>
       </x:c>
       <x:c r="B676" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C676" s="1">
-        <x:v>6550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D676" s="1">
         <x:v>0</x:v>
@@ -18378,10 +18381,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F676" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G676" s="1">
-        <x:v>9850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="677" spans="1:7">
@@ -18389,10 +18392,10 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B677" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C677" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D677" s="1">
         <x:v>0</x:v>
@@ -18401,10 +18404,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F677" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>50</x:v>
+        <x:v>9850</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
@@ -18412,7 +18415,7 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B678" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C678" s="1">
         <x:v>50</x:v>
@@ -18435,10 +18438,10 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C679" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D679" s="1">
         <x:v>0</x:v>
@@ -18447,10 +18450,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F679" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>9550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
@@ -18458,10 +18461,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D680" s="1">
         <x:v>0</x:v>
@@ -18470,10 +18473,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>2700</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>2700</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -18481,10 +18484,10 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D681" s="1">
         <x:v>0</x:v>
@@ -18493,10 +18496,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -18504,10 +18507,10 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
@@ -18516,33 +18519,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>4300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>7850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
       <x:c r="A683" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D683" s="1">
-        <x:v>550000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E683" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>0</x:v>
+        <x:v>4300</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>550000</x:v>
+        <x:v>7850</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -18550,22 +18553,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D684" s="1">
-        <x:v>1916563</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E684" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>1921613</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -18573,22 +18576,22 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C685" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D685" s="1">
-        <x:v>0</x:v>
+        <x:v>1916563</x:v>
       </x:c>
       <x:c r="E685" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>50</x:v>
+        <x:v>1921613</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -18596,7 +18599,7 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>50</x:v>
@@ -18608,10 +18611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -18619,7 +18622,7 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>50</x:v>
@@ -18631,10 +18634,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F687" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
@@ -18642,10 +18645,10 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C688" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D688" s="1">
         <x:v>0</x:v>
@@ -18654,10 +18657,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F688" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>3300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
@@ -18668,7 +18671,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C689" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D689" s="1">
         <x:v>0</x:v>
@@ -18677,10 +18680,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F689" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G689" s="1">
-        <x:v>50</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="690" spans="1:7">
@@ -18688,7 +18691,7 @@
         <x:v>746</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C690" s="1">
         <x:v>50</x:v>
@@ -18700,10 +18703,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>3700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>3750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -18711,7 +18714,7 @@
         <x:v>747</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C691" s="1">
         <x:v>50</x:v>
@@ -18723,10 +18726,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>3700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>50</x:v>
+        <x:v>3750</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -18734,7 +18737,7 @@
         <x:v>748</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C692" s="1">
         <x:v>50</x:v>
@@ -18757,22 +18760,22 @@
         <x:v>749</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C693" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D693" s="1">
-        <x:v>404474</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E693" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F693" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>421974</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
@@ -18780,13 +18783,13 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C694" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D694" s="1">
-        <x:v>0</x:v>
+        <x:v>404474</x:v>
       </x:c>
       <x:c r="E694" s="1">
         <x:v>0</x:v>
@@ -18795,7 +18798,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>1000</x:v>
+        <x:v>421974</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
@@ -18803,10 +18806,10 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C695" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D695" s="1">
         <x:v>0</x:v>
@@ -18815,10 +18818,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F695" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
@@ -18826,10 +18829,10 @@
         <x:v>752</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D696" s="1">
         <x:v>0</x:v>
@@ -18838,10 +18841,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -18849,10 +18852,10 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C697" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D697" s="1">
         <x:v>0</x:v>
@@ -18861,10 +18864,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F697" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">
@@ -18872,13 +18875,13 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C698" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D698" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E698" s="1">
         <x:v>0</x:v>
@@ -18887,7 +18890,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>40000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
@@ -18895,13 +18898,13 @@
         <x:v>755</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C699" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D699" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E699" s="1">
         <x:v>0</x:v>
@@ -18910,7 +18913,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G699" s="1">
-        <x:v>1000</x:v>
+        <x:v>40000</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:7">
@@ -18918,10 +18921,10 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C700" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D700" s="1">
         <x:v>0</x:v>
@@ -18933,7 +18936,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
@@ -18941,10 +18944,10 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C701" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D701" s="1">
         <x:v>0</x:v>
@@ -18953,10 +18956,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>5200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
@@ -18964,10 +18967,10 @@
         <x:v>758</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C702" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D702" s="1">
         <x:v>0</x:v>
@@ -18976,10 +18979,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F702" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
@@ -18987,7 +18990,7 @@
         <x:v>759</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C703" s="1">
         <x:v>50</x:v>
@@ -19010,7 +19013,7 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C704" s="1">
         <x:v>50</x:v>
@@ -19022,10 +19025,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
@@ -19033,22 +19036,22 @@
         <x:v>761</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>3920589</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19056,13 +19059,13 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D706" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E706" s="1">
         <x:v>0</x:v>
@@ -19071,7 +19074,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>50</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -19079,10 +19082,10 @@
         <x:v>763</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D707" s="1">
         <x:v>0</x:v>
@@ -19094,7 +19097,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
@@ -19102,10 +19105,10 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D708" s="1">
         <x:v>0</x:v>
@@ -19117,7 +19120,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
@@ -19125,7 +19128,7 @@
         <x:v>765</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C709" s="1">
         <x:v>50</x:v>
@@ -19148,10 +19151,10 @@
         <x:v>766</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C710" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D710" s="1">
         <x:v>0</x:v>
@@ -19160,10 +19163,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>7834</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
@@ -19171,10 +19174,10 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C711" s="1">
-        <x:v>1050</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D711" s="1">
         <x:v>0</x:v>
@@ -19183,10 +19186,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F711" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>1050</x:v>
+        <x:v>7834</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
@@ -19197,7 +19200,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D712" s="1">
         <x:v>0</x:v>
@@ -19209,7 +19212,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19217,7 +19220,7 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C713" s="1">
         <x:v>50</x:v>
@@ -19240,13 +19243,13 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D714" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E714" s="1">
         <x:v>0</x:v>
@@ -19255,7 +19258,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19263,13 +19266,13 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>50</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D715" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E715" s="1">
         <x:v>0</x:v>
@@ -19278,7 +19281,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>50</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
@@ -19286,10 +19289,10 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>14600</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D716" s="1">
         <x:v>0</x:v>
@@ -19298,10 +19301,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>31600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19309,10 +19312,10 @@
         <x:v>773</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>50</x:v>
+        <x:v>14600</x:v>
       </x:c>
       <x:c r="D717" s="1">
         <x:v>0</x:v>
@@ -19321,10 +19324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>50</x:v>
+        <x:v>31600</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
@@ -19332,7 +19335,7 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C718" s="1">
         <x:v>50</x:v>
@@ -19355,7 +19358,7 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C719" s="1">
         <x:v>50</x:v>
@@ -19378,13 +19381,13 @@
         <x:v>776</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D720" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E720" s="1">
         <x:v>0</x:v>
@@ -19393,7 +19396,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
@@ -19401,13 +19404,13 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C721" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D721" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E721" s="1">
         <x:v>0</x:v>
@@ -19416,7 +19419,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>50</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
@@ -19424,10 +19427,10 @@
         <x:v>778</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C722" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D722" s="1">
         <x:v>0</x:v>
@@ -19436,10 +19439,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F722" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>30000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
@@ -19447,10 +19450,10 @@
         <x:v>779</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D723" s="1">
         <x:v>0</x:v>
@@ -19459,10 +19462,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F723" s="1">
-        <x:v>0</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>50</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
@@ -19470,10 +19473,10 @@
         <x:v>780</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C724" s="1">
-        <x:v>19050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D724" s="1">
         <x:v>0</x:v>
@@ -19482,10 +19485,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F724" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>21550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
@@ -19493,10 +19496,10 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>3500</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D725" s="1">
         <x:v>0</x:v>
@@ -19505,10 +19508,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F725" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>3500</x:v>
+        <x:v>21550</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
@@ -19516,10 +19519,10 @@
         <x:v>782</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C726" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D726" s="1">
         <x:v>0</x:v>
@@ -19531,18 +19534,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
       <x:c r="A727" s="1" t="s">
-        <x:v>782</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D727" s="1">
         <x:v>0</x:v>
@@ -19551,10 +19554,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F727" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
@@ -19562,10 +19565,10 @@
         <x:v>783</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C728" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D728" s="1">
         <x:v>0</x:v>
@@ -19574,10 +19577,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
@@ -19585,10 +19588,10 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C729" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D729" s="1">
         <x:v>0</x:v>
@@ -19600,7 +19603,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">
@@ -19608,10 +19611,10 @@
         <x:v>785</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C730" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D730" s="1">
         <x:v>0</x:v>
@@ -19623,7 +19626,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
@@ -19631,10 +19634,10 @@
         <x:v>786</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C731" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D731" s="1">
         <x:v>0</x:v>
@@ -19643,10 +19646,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F731" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
@@ -19654,10 +19657,10 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C732" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D732" s="1">
         <x:v>0</x:v>
@@ -19666,10 +19669,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F732" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
@@ -19677,7 +19680,7 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C733" s="1">
         <x:v>50</x:v>
@@ -19700,10 +19703,10 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C734" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D734" s="1">
         <x:v>0</x:v>
@@ -19712,10 +19715,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F734" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G734" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:7">
@@ -19723,10 +19726,10 @@
         <x:v>790</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19735,10 +19738,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19746,7 +19749,7 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C736" s="1">
         <x:v>50</x:v>
@@ -19769,13 +19772,13 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C737" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D737" s="1">
-        <x:v>943006</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E737" s="1">
         <x:v>0</x:v>
@@ -19784,7 +19787,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G737" s="1">
-        <x:v>943056</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="738" spans="1:7">
@@ -19792,13 +19795,13 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C738" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D738" s="1">
-        <x:v>0</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="E738" s="1">
         <x:v>0</x:v>
@@ -19807,7 +19810,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>50</x:v>
+        <x:v>943056</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
@@ -19815,7 +19818,7 @@
         <x:v>794</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C739" s="1">
         <x:v>50</x:v>
@@ -19838,10 +19841,10 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D740" s="1">
         <x:v>0</x:v>
@@ -19850,10 +19853,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F740" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
@@ -19861,10 +19864,10 @@
         <x:v>796</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C741" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D741" s="1">
         <x:v>0</x:v>
@@ -19873,10 +19876,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F741" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">
@@ -19884,7 +19887,7 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C742" s="1">
         <x:v>50</x:v>
@@ -19896,10 +19899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F742" s="1">
-        <x:v>4999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>5049</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
@@ -19907,10 +19910,10 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C743" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D743" s="1">
         <x:v>0</x:v>
@@ -19919,10 +19922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F743" s="1">
-        <x:v>16500</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G743" s="1">
-        <x:v>16500</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="744" spans="1:7">
@@ -19930,10 +19933,10 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C744" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D744" s="1">
         <x:v>0</x:v>
@@ -19942,10 +19945,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F744" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G744" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:7">
@@ -19953,7 +19956,7 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C745" s="1">
         <x:v>50</x:v>
@@ -19976,7 +19979,7 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C746" s="1">
         <x:v>50</x:v>
@@ -19999,7 +20002,7 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C747" s="1">
         <x:v>50</x:v>
@@ -20022,7 +20025,7 @@
         <x:v>803</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C748" s="1">
         <x:v>50</x:v>
@@ -20045,7 +20048,7 @@
         <x:v>804</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C749" s="1">
         <x:v>50</x:v>
@@ -20068,10 +20071,10 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20080,10 +20083,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F750" s="1">
-        <x:v>37300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>48150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
@@ -20091,10 +20094,10 @@
         <x:v>806</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>0</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20103,10 +20106,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F751" s="1">
-        <x:v>83</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>83</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
@@ -20114,10 +20117,10 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20126,10 +20129,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
@@ -20137,7 +20140,7 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C753" s="1">
         <x:v>50</x:v>
@@ -20160,7 +20163,7 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C754" s="1">
         <x:v>50</x:v>
@@ -20183,10 +20186,10 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -20195,10 +20198,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F755" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
@@ -20206,21 +20209,44 @@
         <x:v>811</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C756" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D756" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E756" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F756" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G756" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="757" spans="1:7">
+      <x:c r="A757" s="1" t="s">
+        <x:v>812</x:v>
+      </x:c>
+      <x:c r="B757" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C756" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D756" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E756" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F756" s="1">
+      <x:c r="C757" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D757" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E757" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F757" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G756" s="1">
+      <x:c r="G757" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -8689,13 +8689,13 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="B255" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C255" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D255" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850000</x:v>
       </x:c>
       <x:c r="E255" s="1">
         <x:v>0</x:v>
@@ -8704,7 +8704,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G255" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850050</x:v>
       </x:c>
     </x:row>
     <x:row r="256" spans="1:7">
@@ -8712,13 +8712,13 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="B256" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C256" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D256" s="1">
-        <x:v>3850000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E256" s="1">
         <x:v>0</x:v>
@@ -8727,7 +8727,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G256" s="1">
-        <x:v>3850050</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="257" spans="1:7">
@@ -16187,7 +16187,7 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B581" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C581" s="1">
         <x:v>0</x:v>
@@ -16210,7 +16210,7 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C582" s="1">
         <x:v>0</x:v>
@@ -19568,10 +19568,10 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C728" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D728" s="1">
         <x:v>0</x:v>
@@ -19580,10 +19580,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
@@ -19591,10 +19591,10 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C729" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D729" s="1">
         <x:v>0</x:v>
@@ -19603,10 +19603,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F729" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -1135,6 +1135,9 @@
     <x:t>INHOFE, JAMES M. SEN.</x:t>
   </x:si>
   <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
     <x:t>ISAKSON, JOHN HARDY</x:t>
   </x:si>
   <x:si>
@@ -2120,6 +2123,9 @@
   </x:si>
   <x:si>
     <x:t>SNOWE, OLYMPIA J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
   </x:si>
   <x:si>
     <x:t>SORENSEN, ERIC</x:t>
@@ -2526,8 +2532,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G758" totalsRowShown="0">
-  <x:autoFilter ref="A1:G758"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G760" totalsRowShown="0">
+  <x:autoFilter ref="A1:G760"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2829,7 +2835,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G758"/>
+  <x:dimension ref="A1:G760"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4003,7 +4009,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>2122190</x:v>
+        <x:v>3114863</x:v>
       </x:c>
       <x:c r="E51" s="1">
         <x:v>0</x:v>
@@ -4012,7 +4018,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G51" s="1">
-        <x:v>2122190</x:v>
+        <x:v>3114863</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
@@ -6050,7 +6056,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D140" s="1">
-        <x:v>53694</x:v>
+        <x:v>107388</x:v>
       </x:c>
       <x:c r="E140" s="1">
         <x:v>0</x:v>
@@ -6059,7 +6065,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G140" s="1">
-        <x:v>53744</x:v>
+        <x:v>107438</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:7">
@@ -10161,13 +10167,13 @@
         <x:v>373</x:v>
       </x:c>
       <x:c r="B319" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C319" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D319" s="1">
-        <x:v>0</x:v>
+        <x:v>54932</x:v>
       </x:c>
       <x:c r="E319" s="1">
         <x:v>0</x:v>
@@ -10176,7 +10182,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G319" s="1">
-        <x:v>50</x:v>
+        <x:v>54932</x:v>
       </x:c>
     </x:row>
     <x:row r="320" spans="1:7">
@@ -10184,10 +10190,10 @@
         <x:v>374</x:v>
       </x:c>
       <x:c r="B320" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C320" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D320" s="1">
         <x:v>0</x:v>
@@ -10196,10 +10202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F320" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G320" s="1">
-        <x:v>30000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="321" spans="1:7">
@@ -10207,10 +10213,10 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="B321" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C321" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D321" s="1">
         <x:v>0</x:v>
@@ -10219,10 +10225,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F321" s="1">
-        <x:v>6668</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G321" s="1">
-        <x:v>7668</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="322" spans="1:7">
@@ -10230,22 +10236,22 @@
         <x:v>376</x:v>
       </x:c>
       <x:c r="B322" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C322" s="1">
-        <x:v>2500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D322" s="1">
-        <x:v>1308901</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E322" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F322" s="1">
-        <x:v>0</x:v>
+        <x:v>6668</x:v>
       </x:c>
       <x:c r="G322" s="1">
-        <x:v>1311401</x:v>
+        <x:v>7668</x:v>
       </x:c>
     </x:row>
     <x:row r="323" spans="1:7">
@@ -10253,13 +10259,13 @@
         <x:v>377</x:v>
       </x:c>
       <x:c r="B323" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C323" s="1">
         <x:v>2500</x:v>
       </x:c>
       <x:c r="D323" s="1">
-        <x:v>0</x:v>
+        <x:v>1308901</x:v>
       </x:c>
       <x:c r="E323" s="1">
         <x:v>0</x:v>
@@ -10268,7 +10274,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G323" s="1">
-        <x:v>2500</x:v>
+        <x:v>1311401</x:v>
       </x:c>
     </x:row>
     <x:row r="324" spans="1:7">
@@ -10276,10 +10282,10 @@
         <x:v>378</x:v>
       </x:c>
       <x:c r="B324" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C324" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D324" s="1">
         <x:v>0</x:v>
@@ -10291,7 +10297,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G324" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="325" spans="1:7">
@@ -10299,10 +10305,10 @@
         <x:v>379</x:v>
       </x:c>
       <x:c r="B325" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C325" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D325" s="1">
         <x:v>0</x:v>
@@ -10311,10 +10317,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F325" s="1">
-        <x:v>2900</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G325" s="1">
-        <x:v>2900</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="326" spans="1:7">
@@ -10322,10 +10328,10 @@
         <x:v>380</x:v>
       </x:c>
       <x:c r="B326" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C326" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D326" s="1">
         <x:v>0</x:v>
@@ -10334,10 +10340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F326" s="1">
-        <x:v>0</x:v>
+        <x:v>2900</x:v>
       </x:c>
       <x:c r="G326" s="1">
-        <x:v>50</x:v>
+        <x:v>2900</x:v>
       </x:c>
     </x:row>
     <x:row r="327" spans="1:7">
@@ -10345,7 +10351,7 @@
         <x:v>381</x:v>
       </x:c>
       <x:c r="B327" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C327" s="1">
         <x:v>50</x:v>
@@ -10368,13 +10374,13 @@
         <x:v>382</x:v>
       </x:c>
       <x:c r="B328" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C328" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D328" s="1">
-        <x:v>7276846</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E328" s="1">
         <x:v>0</x:v>
@@ -10383,7 +10389,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G328" s="1">
-        <x:v>7276896</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="329" spans="1:7">
@@ -10391,45 +10397,45 @@
         <x:v>383</x:v>
       </x:c>
       <x:c r="B329" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C329" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D329" s="1">
-        <x:v>124736</x:v>
+        <x:v>7276846</x:v>
       </x:c>
       <x:c r="E329" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F329" s="1">
-        <x:v>17167</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G329" s="1">
-        <x:v>145453</x:v>
+        <x:v>7276896</x:v>
       </x:c>
     </x:row>
     <x:row r="330" spans="1:7">
       <x:c r="A330" s="1" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="B330" s="1" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="B330" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="C330" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D330" s="1">
-        <x:v>0</x:v>
+        <x:v>124736</x:v>
       </x:c>
       <x:c r="E330" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F330" s="1">
-        <x:v>0</x:v>
+        <x:v>17167</x:v>
       </x:c>
       <x:c r="G330" s="1">
-        <x:v>50</x:v>
+        <x:v>145453</x:v>
       </x:c>
     </x:row>
     <x:row r="331" spans="1:7">
@@ -10437,7 +10443,7 @@
         <x:v>386</x:v>
       </x:c>
       <x:c r="B331" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C331" s="1">
         <x:v>50</x:v>
@@ -10460,7 +10466,7 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="B332" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C332" s="1">
         <x:v>50</x:v>
@@ -10472,10 +10478,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F332" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G332" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="333" spans="1:7">
@@ -10483,22 +10489,22 @@
         <x:v>388</x:v>
       </x:c>
       <x:c r="B333" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C333" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D333" s="1">
-        <x:v>961273</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E333" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F333" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G333" s="1">
-        <x:v>961273</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="334" spans="1:7">
@@ -10506,13 +10512,13 @@
         <x:v>389</x:v>
       </x:c>
       <x:c r="B334" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C334" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D334" s="1">
-        <x:v>0</x:v>
+        <x:v>961273</x:v>
       </x:c>
       <x:c r="E334" s="1">
         <x:v>0</x:v>
@@ -10521,7 +10527,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G334" s="1">
-        <x:v>50</x:v>
+        <x:v>961273</x:v>
       </x:c>
     </x:row>
     <x:row r="335" spans="1:7">
@@ -10529,10 +10535,10 @@
         <x:v>390</x:v>
       </x:c>
       <x:c r="B335" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C335" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D335" s="1">
         <x:v>0</x:v>
@@ -10541,10 +10547,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F335" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G335" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="336" spans="1:7">
@@ -10552,10 +10558,10 @@
         <x:v>391</x:v>
       </x:c>
       <x:c r="B336" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C336" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D336" s="1">
         <x:v>0</x:v>
@@ -10564,10 +10570,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F336" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G336" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="337" spans="1:7">
@@ -10575,7 +10581,7 @@
         <x:v>392</x:v>
       </x:c>
       <x:c r="B337" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C337" s="1">
         <x:v>50</x:v>
@@ -10601,7 +10607,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C338" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D338" s="1">
         <x:v>0</x:v>
@@ -10613,7 +10619,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G338" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="339" spans="1:7">
@@ -10621,10 +10627,10 @@
         <x:v>394</x:v>
       </x:c>
       <x:c r="B339" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C339" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D339" s="1">
         <x:v>0</x:v>
@@ -10633,10 +10639,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F339" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G339" s="1">
-        <x:v>10050</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="340" spans="1:7">
@@ -10644,22 +10650,22 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="B340" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C340" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D340" s="1">
-        <x:v>6051088</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E340" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F340" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G340" s="1">
-        <x:v>6052088</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="341" spans="1:7">
@@ -10667,13 +10673,13 @@
         <x:v>396</x:v>
       </x:c>
       <x:c r="B341" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C341" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D341" s="1">
-        <x:v>0</x:v>
+        <x:v>6051088</x:v>
       </x:c>
       <x:c r="E341" s="1">
         <x:v>0</x:v>
@@ -10682,7 +10688,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G341" s="1">
-        <x:v>50</x:v>
+        <x:v>6052088</x:v>
       </x:c>
     </x:row>
     <x:row r="342" spans="1:7">
@@ -10690,7 +10696,7 @@
         <x:v>397</x:v>
       </x:c>
       <x:c r="B342" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C342" s="1">
         <x:v>50</x:v>
@@ -10713,10 +10719,10 @@
         <x:v>398</x:v>
       </x:c>
       <x:c r="B343" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C343" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D343" s="1">
         <x:v>0</x:v>
@@ -10725,10 +10731,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F343" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G343" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="344" spans="1:7">
@@ -10736,10 +10742,10 @@
         <x:v>399</x:v>
       </x:c>
       <x:c r="B344" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C344" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D344" s="1">
         <x:v>0</x:v>
@@ -10748,10 +10754,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F344" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G344" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="345" spans="1:7">
@@ -10759,10 +10765,10 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="B345" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C345" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D345" s="1">
         <x:v>0</x:v>
@@ -10771,10 +10777,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F345" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G345" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="346" spans="1:7">
@@ -10782,10 +10788,10 @@
         <x:v>401</x:v>
       </x:c>
       <x:c r="B346" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C346" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D346" s="1">
         <x:v>0</x:v>
@@ -10794,10 +10800,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F346" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G346" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="347" spans="1:7">
@@ -10805,7 +10811,7 @@
         <x:v>402</x:v>
       </x:c>
       <x:c r="B347" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C347" s="1">
         <x:v>50</x:v>
@@ -10851,7 +10857,7 @@
         <x:v>404</x:v>
       </x:c>
       <x:c r="B349" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C349" s="1">
         <x:v>50</x:v>
@@ -10874,10 +10880,10 @@
         <x:v>405</x:v>
       </x:c>
       <x:c r="B350" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C350" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D350" s="1">
         <x:v>0</x:v>
@@ -10886,10 +10892,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F350" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G350" s="1">
-        <x:v>6600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="351" spans="1:7">
@@ -10897,22 +10903,22 @@
         <x:v>406</x:v>
       </x:c>
       <x:c r="B351" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C351" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D351" s="1">
-        <x:v>285008</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E351" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F351" s="1">
-        <x:v>5000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G351" s="1">
-        <x:v>290058</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="352" spans="1:7">
@@ -10920,22 +10926,22 @@
         <x:v>407</x:v>
       </x:c>
       <x:c r="B352" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C352" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D352" s="1">
-        <x:v>0</x:v>
+        <x:v>285008</x:v>
       </x:c>
       <x:c r="E352" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F352" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G352" s="1">
-        <x:v>50</x:v>
+        <x:v>290058</x:v>
       </x:c>
     </x:row>
     <x:row r="353" spans="1:7">
@@ -10943,7 +10949,7 @@
         <x:v>408</x:v>
       </x:c>
       <x:c r="B353" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C353" s="1">
         <x:v>50</x:v>
@@ -10955,10 +10961,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F353" s="1">
-        <x:v>8200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G353" s="1">
-        <x:v>8250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="354" spans="1:7">
@@ -10966,10 +10972,10 @@
         <x:v>409</x:v>
       </x:c>
       <x:c r="B354" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C354" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D354" s="1">
         <x:v>0</x:v>
@@ -10978,10 +10984,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F354" s="1">
-        <x:v>17400</x:v>
+        <x:v>8200</x:v>
       </x:c>
       <x:c r="G354" s="1">
-        <x:v>17400</x:v>
+        <x:v>8250</x:v>
       </x:c>
     </x:row>
     <x:row r="355" spans="1:7">
@@ -10989,22 +10995,22 @@
         <x:v>410</x:v>
       </x:c>
       <x:c r="B355" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C355" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D355" s="1">
-        <x:v>68985</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E355" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F355" s="1">
-        <x:v>1668</x:v>
+        <x:v>17400</x:v>
       </x:c>
       <x:c r="G355" s="1">
-        <x:v>71653</x:v>
+        <x:v>17400</x:v>
       </x:c>
     </x:row>
     <x:row r="356" spans="1:7">
@@ -11012,22 +11018,22 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="B356" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C356" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D356" s="1">
-        <x:v>0</x:v>
+        <x:v>68985</x:v>
       </x:c>
       <x:c r="E356" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F356" s="1">
-        <x:v>1000</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G356" s="1">
-        <x:v>1000</x:v>
+        <x:v>71653</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:7">
@@ -11035,22 +11041,22 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B357" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C357" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D357" s="1">
-        <x:v>217092</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E357" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F357" s="1">
-        <x:v>238150</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G357" s="1">
-        <x:v>455292</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="358" spans="1:7">
@@ -11058,22 +11064,22 @@
         <x:v>413</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C358" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D358" s="1">
-        <x:v>0</x:v>
+        <x:v>217092</x:v>
       </x:c>
       <x:c r="E358" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F358" s="1">
-        <x:v>0</x:v>
+        <x:v>238150</x:v>
       </x:c>
       <x:c r="G358" s="1">
-        <x:v>50</x:v>
+        <x:v>455292</x:v>
       </x:c>
     </x:row>
     <x:row r="359" spans="1:7">
@@ -11081,7 +11087,7 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C359" s="1">
         <x:v>50</x:v>
@@ -11104,7 +11110,7 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="B360" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C360" s="1">
         <x:v>50</x:v>
@@ -11127,22 +11133,22 @@
         <x:v>416</x:v>
       </x:c>
       <x:c r="B361" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C361" s="1">
-        <x:v>12200</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D361" s="1">
-        <x:v>3848426</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E361" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F361" s="1">
-        <x:v>15700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G361" s="1">
-        <x:v>3876326</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="362" spans="1:7">
@@ -11150,22 +11156,22 @@
         <x:v>417</x:v>
       </x:c>
       <x:c r="B362" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C362" s="1">
-        <x:v>50</x:v>
+        <x:v>12200</x:v>
       </x:c>
       <x:c r="D362" s="1">
-        <x:v>0</x:v>
+        <x:v>3848426</x:v>
       </x:c>
       <x:c r="E362" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F362" s="1">
-        <x:v>0</x:v>
+        <x:v>15700</x:v>
       </x:c>
       <x:c r="G362" s="1">
-        <x:v>50</x:v>
+        <x:v>3876326</x:v>
       </x:c>
     </x:row>
     <x:row r="363" spans="1:7">
@@ -11173,7 +11179,7 @@
         <x:v>418</x:v>
       </x:c>
       <x:c r="B363" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C363" s="1">
         <x:v>50</x:v>
@@ -11196,10 +11202,10 @@
         <x:v>419</x:v>
       </x:c>
       <x:c r="B364" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C364" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D364" s="1">
         <x:v>0</x:v>
@@ -11208,10 +11214,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F364" s="1">
-        <x:v>77</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G364" s="1">
-        <x:v>77</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="365" spans="1:7">
@@ -11219,10 +11225,10 @@
         <x:v>420</x:v>
       </x:c>
       <x:c r="B365" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C365" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D365" s="1">
         <x:v>0</x:v>
@@ -11231,10 +11237,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F365" s="1">
-        <x:v>0</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G365" s="1">
-        <x:v>50</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="366" spans="1:7">
@@ -11242,7 +11248,7 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="B366" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C366" s="1">
         <x:v>50</x:v>
@@ -11265,13 +11271,13 @@
         <x:v>422</x:v>
       </x:c>
       <x:c r="B367" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C367" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D367" s="1">
-        <x:v>430866</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E367" s="1">
         <x:v>0</x:v>
@@ -11280,7 +11286,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G367" s="1">
-        <x:v>430866</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="368" spans="1:7">
@@ -11311,13 +11317,13 @@
         <x:v>424</x:v>
       </x:c>
       <x:c r="B369" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C369" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D369" s="1">
-        <x:v>0</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="E369" s="1">
         <x:v>0</x:v>
@@ -11326,7 +11332,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G369" s="1">
-        <x:v>50</x:v>
+        <x:v>430866</x:v>
       </x:c>
     </x:row>
     <x:row r="370" spans="1:7">
@@ -11334,7 +11340,7 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B370" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C370" s="1">
         <x:v>50</x:v>
@@ -11357,7 +11363,7 @@
         <x:v>426</x:v>
       </x:c>
       <x:c r="B371" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C371" s="1">
         <x:v>50</x:v>
@@ -11380,22 +11386,22 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="B372" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C372" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D372" s="1">
-        <x:v>30183</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E372" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F372" s="1">
-        <x:v>7500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G372" s="1">
-        <x:v>37683</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="373" spans="1:7">
@@ -11406,19 +11412,19 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C373" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D373" s="1">
-        <x:v>0</x:v>
+        <x:v>30183</x:v>
       </x:c>
       <x:c r="E373" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F373" s="1">
-        <x:v>1667</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="G373" s="1">
-        <x:v>1717</x:v>
+        <x:v>37683</x:v>
       </x:c>
     </x:row>
     <x:row r="374" spans="1:7">
@@ -11426,7 +11432,7 @@
         <x:v>429</x:v>
       </x:c>
       <x:c r="B374" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C374" s="1">
         <x:v>50</x:v>
@@ -11438,10 +11444,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F374" s="1">
-        <x:v>0</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G374" s="1">
-        <x:v>50</x:v>
+        <x:v>1717</x:v>
       </x:c>
     </x:row>
     <x:row r="375" spans="1:7">
@@ -11449,7 +11455,7 @@
         <x:v>430</x:v>
       </x:c>
       <x:c r="B375" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C375" s="1">
         <x:v>50</x:v>
@@ -11472,7 +11478,7 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="B376" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C376" s="1">
         <x:v>50</x:v>
@@ -11495,7 +11501,7 @@
         <x:v>432</x:v>
       </x:c>
       <x:c r="B377" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C377" s="1">
         <x:v>50</x:v>
@@ -11518,7 +11524,7 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="B378" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C378" s="1">
         <x:v>50</x:v>
@@ -11541,7 +11547,7 @@
         <x:v>434</x:v>
       </x:c>
       <x:c r="B379" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C379" s="1">
         <x:v>50</x:v>
@@ -11564,7 +11570,7 @@
         <x:v>435</x:v>
       </x:c>
       <x:c r="B380" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C380" s="1">
         <x:v>50</x:v>
@@ -11587,7 +11593,7 @@
         <x:v>436</x:v>
       </x:c>
       <x:c r="B381" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C381" s="1">
         <x:v>50</x:v>
@@ -11610,7 +11616,7 @@
         <x:v>437</x:v>
       </x:c>
       <x:c r="B382" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C382" s="1">
         <x:v>50</x:v>
@@ -11633,10 +11639,10 @@
         <x:v>438</x:v>
       </x:c>
       <x:c r="B383" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C383" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D383" s="1">
         <x:v>0</x:v>
@@ -11648,7 +11654,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G383" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="384" spans="1:7">
@@ -11656,10 +11662,10 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="B384" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C384" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D384" s="1">
         <x:v>0</x:v>
@@ -11668,10 +11674,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F384" s="1">
-        <x:v>15000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G384" s="1">
-        <x:v>15050</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="385" spans="1:7">
@@ -11679,10 +11685,10 @@
         <x:v>440</x:v>
       </x:c>
       <x:c r="B385" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C385" s="1">
-        <x:v>4500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D385" s="1">
         <x:v>0</x:v>
@@ -11691,10 +11697,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F385" s="1">
-        <x:v>0</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="G385" s="1">
-        <x:v>4500</x:v>
+        <x:v>15050</x:v>
       </x:c>
     </x:row>
     <x:row r="386" spans="1:7">
@@ -11702,10 +11708,10 @@
         <x:v>441</x:v>
       </x:c>
       <x:c r="B386" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C386" s="1">
-        <x:v>50</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D386" s="1">
         <x:v>0</x:v>
@@ -11717,7 +11723,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G386" s="1">
-        <x:v>50</x:v>
+        <x:v>4500</x:v>
       </x:c>
     </x:row>
     <x:row r="387" spans="1:7">
@@ -11725,10 +11731,10 @@
         <x:v>442</x:v>
       </x:c>
       <x:c r="B387" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C387" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D387" s="1">
         <x:v>0</x:v>
@@ -11740,7 +11746,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G387" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="388" spans="1:7">
@@ -11748,10 +11754,10 @@
         <x:v>443</x:v>
       </x:c>
       <x:c r="B388" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C388" s="1">
-        <x:v>0</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D388" s="1">
         <x:v>0</x:v>
@@ -11760,10 +11766,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F388" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G388" s="1">
-        <x:v>5000</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="389" spans="1:7">
@@ -11771,10 +11777,10 @@
         <x:v>444</x:v>
       </x:c>
       <x:c r="B389" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C389" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D389" s="1">
         <x:v>0</x:v>
@@ -11783,18 +11789,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F389" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G389" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="390" spans="1:7">
       <x:c r="A390" s="1" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="B390" s="1" t="s">
         <x:v>446</x:v>
-      </x:c>
-      <x:c r="B390" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C390" s="1">
         <x:v>50</x:v>
@@ -11817,10 +11823,10 @@
         <x:v>447</x:v>
       </x:c>
       <x:c r="B391" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C391" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D391" s="1">
         <x:v>0</x:v>
@@ -11829,10 +11835,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F391" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G391" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="392" spans="1:7">
@@ -11840,10 +11846,10 @@
         <x:v>448</x:v>
       </x:c>
       <x:c r="B392" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C392" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D392" s="1">
         <x:v>0</x:v>
@@ -11852,10 +11858,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F392" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G392" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="393" spans="1:7">
@@ -11863,7 +11869,7 @@
         <x:v>449</x:v>
       </x:c>
       <x:c r="B393" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C393" s="1">
         <x:v>50</x:v>
@@ -11886,10 +11892,10 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="B394" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C394" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D394" s="1">
         <x:v>0</x:v>
@@ -11898,10 +11904,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F394" s="1">
-        <x:v>3168</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G394" s="1">
-        <x:v>5218</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="395" spans="1:7">
@@ -11909,10 +11915,10 @@
         <x:v>451</x:v>
       </x:c>
       <x:c r="B395" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C395" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D395" s="1">
         <x:v>0</x:v>
@@ -11921,10 +11927,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F395" s="1">
-        <x:v>0</x:v>
+        <x:v>3168</x:v>
       </x:c>
       <x:c r="G395" s="1">
-        <x:v>50</x:v>
+        <x:v>5218</x:v>
       </x:c>
     </x:row>
     <x:row r="396" spans="1:7">
@@ -11932,22 +11938,22 @@
         <x:v>452</x:v>
       </x:c>
       <x:c r="B396" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C396" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D396" s="1">
-        <x:v>350000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E396" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F396" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G396" s="1">
-        <x:v>351000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="397" spans="1:7">
@@ -11955,22 +11961,22 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="B397" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C397" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D397" s="1">
-        <x:v>0</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="E397" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F397" s="1">
-        <x:v>5400</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G397" s="1">
-        <x:v>5450</x:v>
+        <x:v>351000</x:v>
       </x:c>
     </x:row>
     <x:row r="398" spans="1:7">
@@ -11978,7 +11984,7 @@
         <x:v>454</x:v>
       </x:c>
       <x:c r="B398" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C398" s="1">
         <x:v>50</x:v>
@@ -11990,10 +11996,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F398" s="1">
-        <x:v>0</x:v>
+        <x:v>5400</x:v>
       </x:c>
       <x:c r="G398" s="1">
-        <x:v>50</x:v>
+        <x:v>5450</x:v>
       </x:c>
     </x:row>
     <x:row r="399" spans="1:7">
@@ -12001,7 +12007,7 @@
         <x:v>455</x:v>
       </x:c>
       <x:c r="B399" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C399" s="1">
         <x:v>50</x:v>
@@ -12024,10 +12030,10 @@
         <x:v>456</x:v>
       </x:c>
       <x:c r="B400" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C400" s="1">
-        <x:v>12750</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D400" s="1">
         <x:v>0</x:v>
@@ -12036,10 +12042,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F400" s="1">
-        <x:v>25450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G400" s="1">
-        <x:v>38200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="401" spans="1:7">
@@ -12050,19 +12056,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C401" s="1">
-        <x:v>1050</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="D401" s="1">
-        <x:v>106348</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E401" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F401" s="1">
-        <x:v>10000</x:v>
+        <x:v>25450</x:v>
       </x:c>
       <x:c r="G401" s="1">
-        <x:v>117398</x:v>
+        <x:v>38200</x:v>
       </x:c>
     </x:row>
     <x:row r="402" spans="1:7">
@@ -12070,22 +12076,22 @@
         <x:v>458</x:v>
       </x:c>
       <x:c r="B402" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C402" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D402" s="1">
-        <x:v>0</x:v>
+        <x:v>212696</x:v>
       </x:c>
       <x:c r="E402" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F402" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G402" s="1">
-        <x:v>50</x:v>
+        <x:v>223746</x:v>
       </x:c>
     </x:row>
     <x:row r="403" spans="1:7">
@@ -12093,7 +12099,7 @@
         <x:v>459</x:v>
       </x:c>
       <x:c r="B403" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C403" s="1">
         <x:v>50</x:v>
@@ -12116,22 +12122,22 @@
         <x:v>460</x:v>
       </x:c>
       <x:c r="B404" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C404" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D404" s="1">
-        <x:v>109274</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E404" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F404" s="1">
-        <x:v>37600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G404" s="1">
-        <x:v>148924</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="405" spans="1:7">
@@ -12139,22 +12145,22 @@
         <x:v>461</x:v>
       </x:c>
       <x:c r="B405" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C405" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D405" s="1">
-        <x:v>0</x:v>
+        <x:v>218548</x:v>
       </x:c>
       <x:c r="E405" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F405" s="1">
-        <x:v>0</x:v>
+        <x:v>37600</x:v>
       </x:c>
       <x:c r="G405" s="1">
-        <x:v>50</x:v>
+        <x:v>258198</x:v>
       </x:c>
     </x:row>
     <x:row r="406" spans="1:7">
@@ -12162,7 +12168,7 @@
         <x:v>462</x:v>
       </x:c>
       <x:c r="B406" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C406" s="1">
         <x:v>50</x:v>
@@ -12174,10 +12180,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F406" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G406" s="1">
-        <x:v>550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="407" spans="1:7">
@@ -12185,7 +12191,7 @@
         <x:v>463</x:v>
       </x:c>
       <x:c r="B407" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C407" s="1">
         <x:v>50</x:v>
@@ -12197,10 +12203,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F407" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G407" s="1">
-        <x:v>50</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="408" spans="1:7">
@@ -12208,7 +12214,7 @@
         <x:v>464</x:v>
       </x:c>
       <x:c r="B408" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C408" s="1">
         <x:v>50</x:v>
@@ -12231,7 +12237,7 @@
         <x:v>465</x:v>
       </x:c>
       <x:c r="B409" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C409" s="1">
         <x:v>50</x:v>
@@ -12243,10 +12249,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F409" s="1">
-        <x:v>31100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G409" s="1">
-        <x:v>31150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="410" spans="1:7">
@@ -12254,7 +12260,7 @@
         <x:v>466</x:v>
       </x:c>
       <x:c r="B410" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C410" s="1">
         <x:v>50</x:v>
@@ -12266,10 +12272,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F410" s="1">
-        <x:v>0</x:v>
+        <x:v>31100</x:v>
       </x:c>
       <x:c r="G410" s="1">
-        <x:v>50</x:v>
+        <x:v>31150</x:v>
       </x:c>
     </x:row>
     <x:row r="411" spans="1:7">
@@ -12277,10 +12283,10 @@
         <x:v>467</x:v>
       </x:c>
       <x:c r="B411" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C411" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D411" s="1">
         <x:v>0</x:v>
@@ -12289,10 +12295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F411" s="1">
-        <x:v>22650</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G411" s="1">
-        <x:v>23700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="412" spans="1:7">
@@ -12300,10 +12306,10 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="B412" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C412" s="1">
-        <x:v>19400</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D412" s="1">
         <x:v>0</x:v>
@@ -12312,10 +12318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F412" s="1">
-        <x:v>11600</x:v>
+        <x:v>22650</x:v>
       </x:c>
       <x:c r="G412" s="1">
-        <x:v>31000</x:v>
+        <x:v>23700</x:v>
       </x:c>
     </x:row>
     <x:row r="413" spans="1:7">
@@ -12323,10 +12329,10 @@
         <x:v>469</x:v>
       </x:c>
       <x:c r="B413" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C413" s="1">
-        <x:v>50</x:v>
+        <x:v>19400</x:v>
       </x:c>
       <x:c r="D413" s="1">
         <x:v>0</x:v>
@@ -12335,10 +12341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F413" s="1">
-        <x:v>0</x:v>
+        <x:v>11600</x:v>
       </x:c>
       <x:c r="G413" s="1">
-        <x:v>50</x:v>
+        <x:v>31000</x:v>
       </x:c>
     </x:row>
     <x:row r="414" spans="1:7">
@@ -12346,7 +12352,7 @@
         <x:v>470</x:v>
       </x:c>
       <x:c r="B414" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C414" s="1">
         <x:v>50</x:v>
@@ -12369,7 +12375,7 @@
         <x:v>471</x:v>
       </x:c>
       <x:c r="B415" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C415" s="1">
         <x:v>50</x:v>
@@ -12392,7 +12398,7 @@
         <x:v>472</x:v>
       </x:c>
       <x:c r="B416" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C416" s="1">
         <x:v>50</x:v>
@@ -12418,7 +12424,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C417" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D417" s="1">
         <x:v>0</x:v>
@@ -12430,7 +12436,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G417" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="418" spans="1:7">
@@ -12438,10 +12444,10 @@
         <x:v>474</x:v>
       </x:c>
       <x:c r="B418" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C418" s="1">
-        <x:v>50</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D418" s="1">
         <x:v>0</x:v>
@@ -12450,10 +12456,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F418" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G418" s="1">
-        <x:v>5850</x:v>
+        <x:v>2950</x:v>
       </x:c>
     </x:row>
     <x:row r="419" spans="1:7">
@@ -12461,10 +12467,10 @@
         <x:v>475</x:v>
       </x:c>
       <x:c r="B419" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C419" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D419" s="1">
         <x:v>0</x:v>
@@ -12473,10 +12479,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F419" s="1">
-        <x:v>1000</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G419" s="1">
-        <x:v>1000</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="420" spans="1:7">
@@ -12484,10 +12490,10 @@
         <x:v>476</x:v>
       </x:c>
       <x:c r="B420" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C420" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D420" s="1">
         <x:v>0</x:v>
@@ -12496,10 +12502,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F420" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G420" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="421" spans="1:7">
@@ -12507,7 +12513,7 @@
         <x:v>477</x:v>
       </x:c>
       <x:c r="B421" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C421" s="1">
         <x:v>50</x:v>
@@ -12519,10 +12525,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F421" s="1">
-        <x:v>1715</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G421" s="1">
-        <x:v>1765</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="422" spans="1:7">
@@ -12530,10 +12536,10 @@
         <x:v>478</x:v>
       </x:c>
       <x:c r="B422" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C422" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D422" s="1">
         <x:v>0</x:v>
@@ -12542,10 +12548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F422" s="1">
-        <x:v>14000</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="G422" s="1">
-        <x:v>15050</x:v>
+        <x:v>1765</x:v>
       </x:c>
     </x:row>
     <x:row r="423" spans="1:7">
@@ -12553,10 +12559,10 @@
         <x:v>479</x:v>
       </x:c>
       <x:c r="B423" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C423" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D423" s="1">
         <x:v>0</x:v>
@@ -12565,10 +12571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F423" s="1">
-        <x:v>6600</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G423" s="1">
-        <x:v>6650</x:v>
+        <x:v>15050</x:v>
       </x:c>
     </x:row>
     <x:row r="424" spans="1:7">
@@ -12576,7 +12582,7 @@
         <x:v>480</x:v>
       </x:c>
       <x:c r="B424" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C424" s="1">
         <x:v>50</x:v>
@@ -12588,10 +12594,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F424" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G424" s="1">
-        <x:v>50</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="425" spans="1:7">
@@ -12599,22 +12605,22 @@
         <x:v>481</x:v>
       </x:c>
       <x:c r="B425" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C425" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D425" s="1">
-        <x:v>582915</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E425" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F425" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G425" s="1">
-        <x:v>591215</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="426" spans="1:7">
@@ -12622,22 +12628,22 @@
         <x:v>482</x:v>
       </x:c>
       <x:c r="B426" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C426" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D426" s="1">
-        <x:v>0</x:v>
+        <x:v>582915</x:v>
       </x:c>
       <x:c r="E426" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F426" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G426" s="1">
-        <x:v>50</x:v>
+        <x:v>591215</x:v>
       </x:c>
     </x:row>
     <x:row r="427" spans="1:7">
@@ -12645,7 +12651,7 @@
         <x:v>483</x:v>
       </x:c>
       <x:c r="B427" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C427" s="1">
         <x:v>50</x:v>
@@ -12668,10 +12674,10 @@
         <x:v>484</x:v>
       </x:c>
       <x:c r="B428" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C428" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D428" s="1">
         <x:v>0</x:v>
@@ -12683,7 +12689,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G428" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="429" spans="1:7">
@@ -12691,13 +12697,13 @@
         <x:v>485</x:v>
       </x:c>
       <x:c r="B429" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C429" s="1">
-        <x:v>0</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D429" s="1">
-        <x:v>112913</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E429" s="1">
         <x:v>0</x:v>
@@ -12706,7 +12712,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G429" s="1">
-        <x:v>112913</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="430" spans="1:7">
@@ -12714,22 +12720,22 @@
         <x:v>486</x:v>
       </x:c>
       <x:c r="B430" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C430" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D430" s="1">
-        <x:v>0</x:v>
+        <x:v>112913</x:v>
       </x:c>
       <x:c r="E430" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F430" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G430" s="1">
-        <x:v>250</x:v>
+        <x:v>112913</x:v>
       </x:c>
     </x:row>
     <x:row r="431" spans="1:7">
@@ -12737,7 +12743,7 @@
         <x:v>487</x:v>
       </x:c>
       <x:c r="B431" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C431" s="1">
         <x:v>0</x:v>
@@ -12749,10 +12755,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F431" s="1">
-        <x:v>2000</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G431" s="1">
-        <x:v>2000</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="432" spans="1:7">
@@ -12760,10 +12766,10 @@
         <x:v>488</x:v>
       </x:c>
       <x:c r="B432" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C432" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D432" s="1">
         <x:v>0</x:v>
@@ -12772,10 +12778,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F432" s="1">
-        <x:v>36300</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G432" s="1">
-        <x:v>36350</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="433" spans="1:7">
@@ -12783,7 +12789,7 @@
         <x:v>489</x:v>
       </x:c>
       <x:c r="B433" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C433" s="1">
         <x:v>50</x:v>
@@ -12795,10 +12801,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F433" s="1">
-        <x:v>0</x:v>
+        <x:v>36300</x:v>
       </x:c>
       <x:c r="G433" s="1">
-        <x:v>50</x:v>
+        <x:v>36350</x:v>
       </x:c>
     </x:row>
     <x:row r="434" spans="1:7">
@@ -12806,10 +12812,10 @@
         <x:v>490</x:v>
       </x:c>
       <x:c r="B434" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C434" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D434" s="1">
         <x:v>0</x:v>
@@ -12821,7 +12827,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G434" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="435" spans="1:7">
@@ -12829,10 +12835,10 @@
         <x:v>491</x:v>
       </x:c>
       <x:c r="B435" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C435" s="1">
-        <x:v>50</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="D435" s="1">
         <x:v>0</x:v>
@@ -12844,7 +12850,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G435" s="1">
-        <x:v>50</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="436" spans="1:7">
@@ -12852,7 +12858,7 @@
         <x:v>492</x:v>
       </x:c>
       <x:c r="B436" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C436" s="1">
         <x:v>50</x:v>
@@ -12875,7 +12881,7 @@
         <x:v>493</x:v>
       </x:c>
       <x:c r="B437" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C437" s="1">
         <x:v>50</x:v>
@@ -12887,10 +12893,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F437" s="1">
-        <x:v>2600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G437" s="1">
-        <x:v>2650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="438" spans="1:7">
@@ -12898,22 +12904,22 @@
         <x:v>494</x:v>
       </x:c>
       <x:c r="B438" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C438" s="1">
-        <x:v>8300</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D438" s="1">
-        <x:v>104910</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E438" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F438" s="1">
-        <x:v>16300</x:v>
+        <x:v>2600</x:v>
       </x:c>
       <x:c r="G438" s="1">
-        <x:v>129510</x:v>
+        <x:v>2650</x:v>
       </x:c>
     </x:row>
     <x:row r="439" spans="1:7">
@@ -12921,22 +12927,22 @@
         <x:v>495</x:v>
       </x:c>
       <x:c r="B439" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C439" s="1">
-        <x:v>0</x:v>
+        <x:v>8300</x:v>
       </x:c>
       <x:c r="D439" s="1">
-        <x:v>0</x:v>
+        <x:v>104910</x:v>
       </x:c>
       <x:c r="E439" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F439" s="1">
-        <x:v>250</x:v>
+        <x:v>16300</x:v>
       </x:c>
       <x:c r="G439" s="1">
-        <x:v>250</x:v>
+        <x:v>129510</x:v>
       </x:c>
     </x:row>
     <x:row r="440" spans="1:7">
@@ -12944,10 +12950,10 @@
         <x:v>496</x:v>
       </x:c>
       <x:c r="B440" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C440" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D440" s="1">
         <x:v>0</x:v>
@@ -12956,10 +12962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F440" s="1">
-        <x:v>1500</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G440" s="1">
-        <x:v>4000</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="441" spans="1:7">
@@ -12967,10 +12973,10 @@
         <x:v>497</x:v>
       </x:c>
       <x:c r="B441" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C441" s="1">
-        <x:v>1000</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D441" s="1">
         <x:v>0</x:v>
@@ -12979,10 +12985,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F441" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G441" s="1">
-        <x:v>1000</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="442" spans="1:7">
@@ -12990,10 +12996,10 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="B442" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C442" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D442" s="1">
         <x:v>0</x:v>
@@ -13005,7 +13011,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G442" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="443" spans="1:7">
@@ -13013,7 +13019,7 @@
         <x:v>499</x:v>
       </x:c>
       <x:c r="B443" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C443" s="1">
         <x:v>50</x:v>
@@ -13036,13 +13042,13 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="B444" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C444" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D444" s="1">
-        <x:v>55720</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E444" s="1">
         <x:v>0</x:v>
@@ -13051,7 +13057,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G444" s="1">
-        <x:v>55720</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="445" spans="1:7">
@@ -13059,22 +13065,22 @@
         <x:v>501</x:v>
       </x:c>
       <x:c r="B445" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C445" s="1">
-        <x:v>8670</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D445" s="1">
-        <x:v>126626</x:v>
+        <x:v>111440</x:v>
       </x:c>
       <x:c r="E445" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F445" s="1">
-        <x:v>8000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G445" s="1">
-        <x:v>143296</x:v>
+        <x:v>111440</x:v>
       </x:c>
     </x:row>
     <x:row r="446" spans="1:7">
@@ -13082,22 +13088,22 @@
         <x:v>502</x:v>
       </x:c>
       <x:c r="B446" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C446" s="1">
-        <x:v>50</x:v>
+        <x:v>8670</x:v>
       </x:c>
       <x:c r="D446" s="1">
-        <x:v>0</x:v>
+        <x:v>126626</x:v>
       </x:c>
       <x:c r="E446" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F446" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G446" s="1">
-        <x:v>50</x:v>
+        <x:v>143296</x:v>
       </x:c>
     </x:row>
     <x:row r="447" spans="1:7">
@@ -13105,7 +13111,7 @@
         <x:v>503</x:v>
       </x:c>
       <x:c r="B447" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C447" s="1">
         <x:v>50</x:v>
@@ -13128,10 +13134,10 @@
         <x:v>504</x:v>
       </x:c>
       <x:c r="B448" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C448" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D448" s="1">
         <x:v>0</x:v>
@@ -13140,10 +13146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F448" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G448" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="449" spans="1:7">
@@ -13151,10 +13157,10 @@
         <x:v>505</x:v>
       </x:c>
       <x:c r="B449" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C449" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D449" s="1">
         <x:v>0</x:v>
@@ -13163,10 +13169,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F449" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G449" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="450" spans="1:7">
@@ -13174,7 +13180,7 @@
         <x:v>506</x:v>
       </x:c>
       <x:c r="B450" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C450" s="1">
         <x:v>50</x:v>
@@ -13197,13 +13203,13 @@
         <x:v>507</x:v>
       </x:c>
       <x:c r="B451" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C451" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D451" s="1">
-        <x:v>461943</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E451" s="1">
         <x:v>0</x:v>
@@ -13212,7 +13218,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G451" s="1">
-        <x:v>461943</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="452" spans="1:7">
@@ -13220,13 +13226,13 @@
         <x:v>508</x:v>
       </x:c>
       <x:c r="B452" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C452" s="1">
-        <x:v>1050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D452" s="1">
-        <x:v>92320</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="E452" s="1">
         <x:v>0</x:v>
@@ -13235,7 +13241,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G452" s="1">
-        <x:v>93370</x:v>
+        <x:v>461943</x:v>
       </x:c>
     </x:row>
     <x:row r="453" spans="1:7">
@@ -13243,13 +13249,13 @@
         <x:v>509</x:v>
       </x:c>
       <x:c r="B453" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C453" s="1">
-        <x:v>0</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D453" s="1">
-        <x:v>6468074</x:v>
+        <x:v>92320</x:v>
       </x:c>
       <x:c r="E453" s="1">
         <x:v>0</x:v>
@@ -13258,7 +13264,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G453" s="1">
-        <x:v>6468074</x:v>
+        <x:v>93370</x:v>
       </x:c>
     </x:row>
     <x:row r="454" spans="1:7">
@@ -13266,13 +13272,13 @@
         <x:v>510</x:v>
       </x:c>
       <x:c r="B454" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C454" s="1">
-        <x:v>1550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D454" s="1">
-        <x:v>378743</x:v>
+        <x:v>6468074</x:v>
       </x:c>
       <x:c r="E454" s="1">
         <x:v>0</x:v>
@@ -13281,7 +13287,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G454" s="1">
-        <x:v>380293</x:v>
+        <x:v>6468074</x:v>
       </x:c>
     </x:row>
     <x:row r="455" spans="1:7">
@@ -13289,13 +13295,13 @@
         <x:v>511</x:v>
       </x:c>
       <x:c r="B455" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C455" s="1">
         <x:v>1550</x:v>
       </x:c>
       <x:c r="D455" s="1">
-        <x:v>0</x:v>
+        <x:v>413633</x:v>
       </x:c>
       <x:c r="E455" s="1">
         <x:v>0</x:v>
@@ -13304,7 +13310,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G455" s="1">
-        <x:v>1550</x:v>
+        <x:v>415183</x:v>
       </x:c>
     </x:row>
     <x:row r="456" spans="1:7">
@@ -13312,10 +13318,10 @@
         <x:v>512</x:v>
       </x:c>
       <x:c r="B456" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C456" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D456" s="1">
         <x:v>0</x:v>
@@ -13327,7 +13333,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G456" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="457" spans="1:7">
@@ -13335,13 +13341,13 @@
         <x:v>513</x:v>
       </x:c>
       <x:c r="B457" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C457" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D457" s="1">
-        <x:v>504020</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E457" s="1">
         <x:v>0</x:v>
@@ -13350,7 +13356,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G457" s="1">
-        <x:v>504020</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="458" spans="1:7">
@@ -13358,13 +13364,13 @@
         <x:v>514</x:v>
       </x:c>
       <x:c r="B458" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C458" s="1">
-        <x:v>1550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D458" s="1">
-        <x:v>0</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="E458" s="1">
         <x:v>0</x:v>
@@ -13373,7 +13379,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G458" s="1">
-        <x:v>1550</x:v>
+        <x:v>504020</x:v>
       </x:c>
     </x:row>
     <x:row r="459" spans="1:7">
@@ -13381,10 +13387,10 @@
         <x:v>515</x:v>
       </x:c>
       <x:c r="B459" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C459" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D459" s="1">
         <x:v>0</x:v>
@@ -13396,7 +13402,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G459" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="460" spans="1:7">
@@ -13404,7 +13410,7 @@
         <x:v>516</x:v>
       </x:c>
       <x:c r="B460" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C460" s="1">
         <x:v>50</x:v>
@@ -13427,10 +13433,10 @@
         <x:v>517</x:v>
       </x:c>
       <x:c r="B461" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C461" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D461" s="1">
         <x:v>0</x:v>
@@ -13439,10 +13445,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F461" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G461" s="1">
-        <x:v>3667</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="462" spans="1:7">
@@ -13450,22 +13456,22 @@
         <x:v>518</x:v>
       </x:c>
       <x:c r="B462" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C462" s="1">
-        <x:v>500</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D462" s="1">
-        <x:v>53970</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E462" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F462" s="1">
-        <x:v>1500</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G462" s="1">
-        <x:v>55970</x:v>
+        <x:v>3667</x:v>
       </x:c>
     </x:row>
     <x:row r="463" spans="1:7">
@@ -13473,22 +13479,22 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="B463" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C463" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D463" s="1">
-        <x:v>0</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="E463" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F463" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G463" s="1">
-        <x:v>50</x:v>
+        <x:v>109940</x:v>
       </x:c>
     </x:row>
     <x:row r="464" spans="1:7">
@@ -13496,10 +13502,10 @@
         <x:v>520</x:v>
       </x:c>
       <x:c r="B464" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C464" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D464" s="1">
         <x:v>0</x:v>
@@ -13508,10 +13514,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F464" s="1">
-        <x:v>6200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G464" s="1">
-        <x:v>7200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="465" spans="1:7">
@@ -13519,10 +13525,10 @@
         <x:v>521</x:v>
       </x:c>
       <x:c r="B465" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C465" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D465" s="1">
         <x:v>0</x:v>
@@ -13531,10 +13537,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F465" s="1">
-        <x:v>2000</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G465" s="1">
-        <x:v>2000</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="466" spans="1:7">
@@ -13542,10 +13548,10 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B466" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C466" s="1">
-        <x:v>5050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D466" s="1">
         <x:v>0</x:v>
@@ -13554,10 +13560,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F466" s="1">
-        <x:v>1000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G466" s="1">
-        <x:v>6050</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="467" spans="1:7">
@@ -13565,10 +13571,10 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B467" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C467" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D467" s="1">
         <x:v>0</x:v>
@@ -13577,10 +13583,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F467" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G467" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
     </x:row>
     <x:row r="468" spans="1:7">
@@ -13588,10 +13594,10 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="B468" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C468" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D468" s="1">
         <x:v>0</x:v>
@@ -13603,7 +13609,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G468" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="469" spans="1:7">
@@ -13611,10 +13617,10 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D469" s="1">
         <x:v>0</x:v>
@@ -13626,7 +13632,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -13634,13 +13640,13 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D470" s="1">
-        <x:v>726377</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E470" s="1">
         <x:v>0</x:v>
@@ -13649,7 +13655,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>726377</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -13657,22 +13663,22 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C471" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D471" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="E471" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F471" s="1">
-        <x:v>7600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>676049</x:v>
+        <x:v>726377</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -13680,22 +13686,22 @@
         <x:v>528</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
-        <x:v>0</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="E472" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F472" s="1">
-        <x:v>0</x:v>
+        <x:v>7600</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>1000</x:v>
+        <x:v>676049</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -13703,10 +13709,10 @@
         <x:v>529</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -13715,10 +13721,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F473" s="1">
-        <x:v>1250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>1300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -13726,7 +13732,7 @@
         <x:v>530</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C474" s="1">
         <x:v>50</x:v>
@@ -13738,10 +13744,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F474" s="1">
-        <x:v>0</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="G474" s="1">
-        <x:v>50</x:v>
+        <x:v>1300</x:v>
       </x:c>
     </x:row>
     <x:row r="475" spans="1:7">
@@ -13749,13 +13755,13 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B475" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C475" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D475" s="1">
-        <x:v>120404787</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E475" s="1">
         <x:v>0</x:v>
@@ -13764,7 +13770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G475" s="1">
-        <x:v>120406787</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="476" spans="1:7">
@@ -13772,13 +13778,13 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B476" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C476" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D476" s="1">
-        <x:v>221403</x:v>
+        <x:v>120404787</x:v>
       </x:c>
       <x:c r="E476" s="1">
         <x:v>0</x:v>
@@ -13787,7 +13793,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G476" s="1">
-        <x:v>221403</x:v>
+        <x:v>120406787</x:v>
       </x:c>
     </x:row>
     <x:row r="477" spans="1:7">
@@ -13795,22 +13801,22 @@
         <x:v>533</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D477" s="1">
-        <x:v>0</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="E477" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>3333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>4333</x:v>
+        <x:v>221403</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -13818,10 +13824,10 @@
         <x:v>534</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -13830,10 +13836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>0</x:v>
+        <x:v>3333</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>50</x:v>
+        <x:v>4333</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -13841,7 +13847,7 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C479" s="1">
         <x:v>50</x:v>
@@ -13864,10 +13870,10 @@
         <x:v>536</x:v>
       </x:c>
       <x:c r="B480" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C480" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D480" s="1">
         <x:v>0</x:v>
@@ -13879,7 +13885,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G480" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="481" spans="1:7">
@@ -13887,10 +13893,10 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="B481" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C481" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D481" s="1">
         <x:v>0</x:v>
@@ -13902,7 +13908,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G481" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="482" spans="1:7">
@@ -13910,10 +13916,10 @@
         <x:v>538</x:v>
       </x:c>
       <x:c r="B482" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C482" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D482" s="1">
         <x:v>0</x:v>
@@ -13922,10 +13928,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F482" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G482" s="1">
-        <x:v>5400</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="483" spans="1:7">
@@ -13933,10 +13939,10 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="B483" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C483" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D483" s="1">
         <x:v>0</x:v>
@@ -13945,10 +13951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F483" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G483" s="1">
-        <x:v>50</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="484" spans="1:7">
@@ -13956,7 +13962,7 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="B484" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C484" s="1">
         <x:v>50</x:v>
@@ -13968,10 +13974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F484" s="1">
-        <x:v>12000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G484" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="485" spans="1:7">
@@ -13979,7 +13985,7 @@
         <x:v>541</x:v>
       </x:c>
       <x:c r="B485" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C485" s="1">
         <x:v>50</x:v>
@@ -13991,10 +13997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F485" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G485" s="1">
-        <x:v>50</x:v>
+        <x:v>12050</x:v>
       </x:c>
     </x:row>
     <x:row r="486" spans="1:7">
@@ -14002,10 +14008,10 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C486" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D486" s="1">
         <x:v>0</x:v>
@@ -14014,10 +14020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F486" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G486" s="1">
-        <x:v>250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="487" spans="1:7">
@@ -14025,10 +14031,10 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="B487" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C487" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D487" s="1">
         <x:v>0</x:v>
@@ -14037,10 +14043,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F487" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G487" s="1">
-        <x:v>50</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="488" spans="1:7">
@@ -14048,7 +14054,7 @@
         <x:v>544</x:v>
       </x:c>
       <x:c r="B488" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C488" s="1">
         <x:v>50</x:v>
@@ -14060,10 +14066,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F488" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G488" s="1">
-        <x:v>2750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="489" spans="1:7">
@@ -14071,10 +14077,10 @@
         <x:v>545</x:v>
       </x:c>
       <x:c r="B489" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C489" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D489" s="1">
         <x:v>0</x:v>
@@ -14083,10 +14089,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F489" s="1">
-        <x:v>4600</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G489" s="1">
-        <x:v>4600</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="490" spans="1:7">
@@ -14094,10 +14100,10 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="B490" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C490" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D490" s="1">
         <x:v>0</x:v>
@@ -14106,10 +14112,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F490" s="1">
-        <x:v>0</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G490" s="1">
-        <x:v>50</x:v>
+        <x:v>4600</x:v>
       </x:c>
     </x:row>
     <x:row r="491" spans="1:7">
@@ -14117,7 +14123,7 @@
         <x:v>547</x:v>
       </x:c>
       <x:c r="B491" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C491" s="1">
         <x:v>50</x:v>
@@ -14140,7 +14146,7 @@
         <x:v>548</x:v>
       </x:c>
       <x:c r="B492" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C492" s="1">
         <x:v>50</x:v>
@@ -14163,7 +14169,7 @@
         <x:v>549</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C493" s="1">
         <x:v>50</x:v>
@@ -14186,13 +14192,13 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="B494" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C494" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D494" s="1">
-        <x:v>282526</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E494" s="1">
         <x:v>0</x:v>
@@ -14201,7 +14207,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G494" s="1">
-        <x:v>282526</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="495" spans="1:7">
@@ -14209,22 +14215,22 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B495" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C495" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D495" s="1">
-        <x:v>0</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E495" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F495" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G495" s="1">
-        <x:v>1000</x:v>
+        <x:v>282526</x:v>
       </x:c>
     </x:row>
     <x:row r="496" spans="1:7">
@@ -14232,10 +14238,10 @@
         <x:v>552</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C496" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D496" s="1">
         <x:v>0</x:v>
@@ -14244,10 +14250,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F496" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G496" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="497" spans="1:7">
@@ -14255,22 +14261,22 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B497" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C497" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D497" s="1">
-        <x:v>116161</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E497" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F497" s="1">
-        <x:v>4500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G497" s="1">
-        <x:v>124661</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="498" spans="1:7">
@@ -14278,22 +14284,22 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="B498" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C498" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D498" s="1">
-        <x:v>0</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="E498" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F498" s="1">
-        <x:v>0</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G498" s="1">
-        <x:v>50</x:v>
+        <x:v>124661</x:v>
       </x:c>
     </x:row>
     <x:row r="499" spans="1:7">
@@ -14301,7 +14307,7 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B499" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C499" s="1">
         <x:v>50</x:v>
@@ -14324,7 +14330,7 @@
         <x:v>556</x:v>
       </x:c>
       <x:c r="B500" s="1" t="s">
-        <x:v>557</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C500" s="1">
         <x:v>50</x:v>
@@ -14344,10 +14350,10 @@
     </x:row>
     <x:row r="501" spans="1:7">
       <x:c r="A501" s="1" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="B501" s="1" t="s">
         <x:v>558</x:v>
-      </x:c>
-      <x:c r="B501" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C501" s="1">
         <x:v>50</x:v>
@@ -14370,22 +14376,22 @@
         <x:v>559</x:v>
       </x:c>
       <x:c r="B502" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C502" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D502" s="1">
-        <x:v>2997852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E502" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F502" s="1">
-        <x:v>6800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G502" s="1">
-        <x:v>3006652</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="503" spans="1:7">
@@ -14393,22 +14399,22 @@
         <x:v>560</x:v>
       </x:c>
       <x:c r="B503" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C503" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D503" s="1">
-        <x:v>7276846</x:v>
+        <x:v>2997852</x:v>
       </x:c>
       <x:c r="E503" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F503" s="1">
-        <x:v>0</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="G503" s="1">
-        <x:v>7276846</x:v>
+        <x:v>3006652</x:v>
       </x:c>
     </x:row>
     <x:row r="504" spans="1:7">
@@ -14416,13 +14422,13 @@
         <x:v>561</x:v>
       </x:c>
       <x:c r="B504" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C504" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D504" s="1">
-        <x:v>0</x:v>
+        <x:v>7276846</x:v>
       </x:c>
       <x:c r="E504" s="1">
         <x:v>0</x:v>
@@ -14431,7 +14437,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G504" s="1">
-        <x:v>50</x:v>
+        <x:v>7276846</x:v>
       </x:c>
     </x:row>
     <x:row r="505" spans="1:7">
@@ -14439,10 +14445,10 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B505" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C505" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D505" s="1">
         <x:v>0</x:v>
@@ -14451,10 +14457,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F505" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G505" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="506" spans="1:7">
@@ -14462,7 +14468,7 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="B506" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C506" s="1">
         <x:v>0</x:v>
@@ -14474,10 +14480,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F506" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="G506" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="507" spans="1:7">
@@ -14485,10 +14491,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C507" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D507" s="1">
         <x:v>0</x:v>
@@ -14497,10 +14503,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F507" s="1">
-        <x:v>0</x:v>
+        <x:v>22334</x:v>
       </x:c>
       <x:c r="G507" s="1">
-        <x:v>50</x:v>
+        <x:v>22334</x:v>
       </x:c>
     </x:row>
     <x:row r="508" spans="1:7">
@@ -14508,10 +14514,10 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B508" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C508" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D508" s="1">
         <x:v>0</x:v>
@@ -14520,10 +14526,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F508" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G508" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="509" spans="1:7">
@@ -14531,10 +14537,10 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C509" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D509" s="1">
         <x:v>0</x:v>
@@ -14543,10 +14549,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F509" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G509" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="510" spans="1:7">
@@ -14554,13 +14560,13 @@
         <x:v>567</x:v>
       </x:c>
       <x:c r="B510" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C510" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D510" s="1">
-        <x:v>209387</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E510" s="1">
         <x:v>0</x:v>
@@ -14569,7 +14575,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G510" s="1">
-        <x:v>209387</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="511" spans="1:7">
@@ -14577,13 +14583,13 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C511" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D511" s="1">
-        <x:v>0</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="E511" s="1">
         <x:v>0</x:v>
@@ -14592,7 +14598,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G511" s="1">
-        <x:v>50</x:v>
+        <x:v>209387</x:v>
       </x:c>
     </x:row>
     <x:row r="512" spans="1:7">
@@ -14600,13 +14606,13 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B512" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C512" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D512" s="1">
-        <x:v>257695</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E512" s="1">
         <x:v>0</x:v>
@@ -14615,7 +14621,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G512" s="1">
-        <x:v>257695</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="513" spans="1:7">
@@ -14623,22 +14629,22 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C513" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D513" s="1">
-        <x:v>0</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="E513" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F513" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G513" s="1">
-        <x:v>3300</x:v>
+        <x:v>257695</x:v>
       </x:c>
     </x:row>
     <x:row r="514" spans="1:7">
@@ -14646,10 +14652,10 @@
         <x:v>571</x:v>
       </x:c>
       <x:c r="B514" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C514" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D514" s="1">
         <x:v>0</x:v>
@@ -14658,10 +14664,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F514" s="1">
-        <x:v>29800</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G514" s="1">
-        <x:v>34800</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="515" spans="1:7">
@@ -14669,10 +14675,10 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="B515" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C515" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D515" s="1">
         <x:v>0</x:v>
@@ -14681,10 +14687,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F515" s="1">
-        <x:v>0</x:v>
+        <x:v>29800</x:v>
       </x:c>
       <x:c r="G515" s="1">
-        <x:v>50</x:v>
+        <x:v>34800</x:v>
       </x:c>
     </x:row>
     <x:row r="516" spans="1:7">
@@ -14692,7 +14698,7 @@
         <x:v>573</x:v>
       </x:c>
       <x:c r="B516" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C516" s="1">
         <x:v>50</x:v>
@@ -14704,10 +14710,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F516" s="1">
-        <x:v>5600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G516" s="1">
-        <x:v>5650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="517" spans="1:7">
@@ -14715,10 +14721,10 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="B517" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C517" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D517" s="1">
         <x:v>0</x:v>
@@ -14727,10 +14733,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F517" s="1">
-        <x:v>0</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G517" s="1">
-        <x:v>2050</x:v>
+        <x:v>5650</x:v>
       </x:c>
     </x:row>
     <x:row r="518" spans="1:7">
@@ -14738,10 +14744,10 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C518" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D518" s="1">
         <x:v>0</x:v>
@@ -14750,10 +14756,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F518" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G518" s="1">
-        <x:v>3384</x:v>
+        <x:v>2050</x:v>
       </x:c>
     </x:row>
     <x:row r="519" spans="1:7">
@@ -14761,7 +14767,7 @@
         <x:v>576</x:v>
       </x:c>
       <x:c r="B519" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C519" s="1">
         <x:v>50</x:v>
@@ -14773,10 +14779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F519" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G519" s="1">
-        <x:v>50</x:v>
+        <x:v>3384</x:v>
       </x:c>
     </x:row>
     <x:row r="520" spans="1:7">
@@ -14784,22 +14790,22 @@
         <x:v>577</x:v>
       </x:c>
       <x:c r="B520" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C520" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D520" s="1">
-        <x:v>558813</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E520" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F520" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G520" s="1">
-        <x:v>559813</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="521" spans="1:7">
@@ -14807,22 +14813,22 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B521" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C521" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D521" s="1">
-        <x:v>0</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E521" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F521" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G521" s="1">
-        <x:v>6650</x:v>
+        <x:v>559813</x:v>
       </x:c>
     </x:row>
     <x:row r="522" spans="1:7">
@@ -14830,22 +14836,22 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C522" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D522" s="1">
-        <x:v>4500000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E522" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F522" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G522" s="1">
-        <x:v>4500000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="523" spans="1:7">
@@ -14853,13 +14859,13 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B523" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C523" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D523" s="1">
-        <x:v>0</x:v>
+        <x:v>4500000</x:v>
       </x:c>
       <x:c r="E523" s="1">
         <x:v>0</x:v>
@@ -14868,7 +14874,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G523" s="1">
-        <x:v>50</x:v>
+        <x:v>4500000</x:v>
       </x:c>
     </x:row>
     <x:row r="524" spans="1:7">
@@ -14876,22 +14882,22 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C524" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D524" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E524" s="1">
-        <x:v>20483</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F524" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -14899,22 +14905,22 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C525" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D525" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E525" s="1">
-        <x:v>0</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="F525" s="1">
-        <x:v>1089100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G525" s="1">
-        <x:v>1089150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:7">
@@ -14922,22 +14928,22 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C526" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D526" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E526" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F526" s="1">
-        <x:v>0</x:v>
+        <x:v>1089100</x:v>
       </x:c>
       <x:c r="G526" s="1">
-        <x:v>1927706</x:v>
+        <x:v>1089150</x:v>
       </x:c>
     </x:row>
     <x:row r="527" spans="1:7">
@@ -14945,13 +14951,13 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B527" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C527" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D527" s="1">
-        <x:v>0</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="E527" s="1">
         <x:v>0</x:v>
@@ -14960,7 +14966,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G527" s="1">
-        <x:v>50</x:v>
+        <x:v>1927706</x:v>
       </x:c>
     </x:row>
     <x:row r="528" spans="1:7">
@@ -14968,7 +14974,7 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="B528" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C528" s="1">
         <x:v>50</x:v>
@@ -14991,7 +14997,7 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C529" s="1">
         <x:v>50</x:v>
@@ -15014,10 +15020,10 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="B530" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C530" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D530" s="1">
         <x:v>0</x:v>
@@ -15026,10 +15032,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F530" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G530" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="531" spans="1:7">
@@ -15037,10 +15043,10 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="B531" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C531" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D531" s="1">
         <x:v>0</x:v>
@@ -15049,10 +15055,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F531" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G531" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="532" spans="1:7">
@@ -15060,7 +15066,7 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C532" s="1">
         <x:v>50</x:v>
@@ -15072,10 +15078,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F532" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G532" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="533" spans="1:7">
@@ -15083,22 +15089,22 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C533" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D533" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E533" s="1">
-        <x:v>817066</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F533" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G533" s="1">
-        <x:v>0</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="534" spans="1:7">
@@ -15106,22 +15112,22 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="B534" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C534" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D534" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E534" s="1">
-        <x:v>0</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="F534" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G534" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="535" spans="1:7">
@@ -15129,7 +15135,7 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B535" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C535" s="1">
         <x:v>50</x:v>
@@ -15152,22 +15158,22 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C536" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D536" s="1">
-        <x:v>88256</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E536" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F536" s="1">
-        <x:v>14866</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G536" s="1">
-        <x:v>117122</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="537" spans="1:7">
@@ -15175,22 +15181,22 @@
         <x:v>594</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C537" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D537" s="1">
-        <x:v>0</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="E537" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F537" s="1">
-        <x:v>0</x:v>
+        <x:v>14866</x:v>
       </x:c>
       <x:c r="G537" s="1">
-        <x:v>50</x:v>
+        <x:v>117122</x:v>
       </x:c>
     </x:row>
     <x:row r="538" spans="1:7">
@@ -15198,7 +15204,7 @@
         <x:v>595</x:v>
       </x:c>
       <x:c r="B538" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C538" s="1">
         <x:v>50</x:v>
@@ -15221,7 +15227,7 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C539" s="1">
         <x:v>50</x:v>
@@ -15241,10 +15247,10 @@
     </x:row>
     <x:row r="540" spans="1:7">
       <x:c r="A540" s="1" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B540" s="1" t="s">
         <x:v>598</x:v>
-      </x:c>
-      <x:c r="B540" s="1" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="C540" s="1">
         <x:v>50</x:v>
@@ -15267,10 +15273,10 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B541" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C541" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D541" s="1">
         <x:v>0</x:v>
@@ -15279,10 +15285,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F541" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G541" s="1">
-        <x:v>6000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:7">
@@ -15293,19 +15299,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C542" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D542" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E542" s="1">
-        <x:v>10041119</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F542" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G542" s="1">
-        <x:v>50</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="543" spans="1:7">
@@ -15313,7 +15319,7 @@
         <x:v>601</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C543" s="1">
         <x:v>50</x:v>
@@ -15322,13 +15328,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E543" s="1">
-        <x:v>0</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="F543" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15336,7 +15342,7 @@
         <x:v>602</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C544" s="1">
         <x:v>50</x:v>
@@ -15348,10 +15354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">
@@ -15359,10 +15365,10 @@
         <x:v>603</x:v>
       </x:c>
       <x:c r="B545" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C545" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D545" s="1">
         <x:v>0</x:v>
@@ -15371,10 +15377,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F545" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G545" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="546" spans="1:7">
@@ -15382,10 +15388,10 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B546" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C546" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D546" s="1">
         <x:v>0</x:v>
@@ -15394,10 +15400,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F546" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G546" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="547" spans="1:7">
@@ -15405,7 +15411,7 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C547" s="1">
         <x:v>50</x:v>
@@ -15428,7 +15434,7 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B548" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C548" s="1">
         <x:v>50</x:v>
@@ -15451,10 +15457,10 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C549" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D549" s="1">
         <x:v>0</x:v>
@@ -15463,10 +15469,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F549" s="1">
-        <x:v>-19405</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G549" s="1">
-        <x:v>-19405</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="550" spans="1:7">
@@ -15474,22 +15480,22 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C550" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D550" s="1">
-        <x:v>1491280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E550" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F550" s="1">
-        <x:v>0</x:v>
+        <x:v>-19405</x:v>
       </x:c>
       <x:c r="G550" s="1">
-        <x:v>1491280</x:v>
+        <x:v>-19405</x:v>
       </x:c>
     </x:row>
     <x:row r="551" spans="1:7">
@@ -15497,22 +15503,22 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C551" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D551" s="1">
-        <x:v>0</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="E551" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F551" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>500</x:v>
+        <x:v>1491280</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -15520,10 +15526,10 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B552" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C552" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D552" s="1">
         <x:v>0</x:v>
@@ -15532,10 +15538,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F552" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G552" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="553" spans="1:7">
@@ -15543,7 +15549,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B553" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C553" s="1">
         <x:v>50</x:v>
@@ -15555,10 +15561,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F553" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G553" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="554" spans="1:7">
@@ -15566,7 +15572,7 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C554" s="1">
         <x:v>50</x:v>
@@ -15578,10 +15584,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F554" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G554" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="555" spans="1:7">
@@ -15589,7 +15595,7 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B555" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C555" s="1">
         <x:v>50</x:v>
@@ -15601,10 +15607,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F555" s="1">
-        <x:v>1287</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G555" s="1">
-        <x:v>1337</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="556" spans="1:7">
@@ -15612,10 +15618,10 @@
         <x:v>614</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C556" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D556" s="1">
         <x:v>0</x:v>
@@ -15624,10 +15630,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F556" s="1">
-        <x:v>6697</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G556" s="1">
-        <x:v>6697</x:v>
+        <x:v>1337</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:7">
@@ -15635,10 +15641,10 @@
         <x:v>615</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C557" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D557" s="1">
         <x:v>0</x:v>
@@ -15647,10 +15653,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F557" s="1">
-        <x:v>0</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="G557" s="1">
-        <x:v>50</x:v>
+        <x:v>6697</x:v>
       </x:c>
     </x:row>
     <x:row r="558" spans="1:7">
@@ -15658,10 +15664,10 @@
         <x:v>616</x:v>
       </x:c>
       <x:c r="B558" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C558" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D558" s="1">
         <x:v>0</x:v>
@@ -15670,10 +15676,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F558" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G558" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="559" spans="1:7">
@@ -15681,7 +15687,7 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C559" s="1">
         <x:v>0</x:v>
@@ -15693,10 +15699,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -15704,10 +15710,10 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C560" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D560" s="1">
         <x:v>0</x:v>
@@ -15716,10 +15722,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F560" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G560" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="561" spans="1:7">
@@ -15727,7 +15733,7 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C561" s="1">
         <x:v>50</x:v>
@@ -15750,7 +15756,7 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B562" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C562" s="1">
         <x:v>50</x:v>
@@ -15773,22 +15779,22 @@
         <x:v>621</x:v>
       </x:c>
       <x:c r="B563" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C563" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D563" s="1">
-        <x:v>700000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E563" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F563" s="1">
-        <x:v>7000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G563" s="1">
-        <x:v>709500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="564" spans="1:7">
@@ -15796,22 +15802,22 @@
         <x:v>622</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C564" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D564" s="1">
-        <x:v>0</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="E564" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F564" s="1">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G564" s="1">
-        <x:v>50</x:v>
+        <x:v>709500</x:v>
       </x:c>
     </x:row>
     <x:row r="565" spans="1:7">
@@ -15819,10 +15825,10 @@
         <x:v>623</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C565" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D565" s="1">
         <x:v>0</x:v>
@@ -15831,10 +15837,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -15842,10 +15848,10 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C566" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D566" s="1">
         <x:v>0</x:v>
@@ -15854,10 +15860,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F566" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>50</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -15865,7 +15871,7 @@
         <x:v>625</x:v>
       </x:c>
       <x:c r="B567" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C567" s="1">
         <x:v>50</x:v>
@@ -15888,7 +15894,7 @@
         <x:v>626</x:v>
       </x:c>
       <x:c r="B568" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C568" s="1">
         <x:v>50</x:v>
@@ -15911,7 +15917,7 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C569" s="1">
         <x:v>50</x:v>
@@ -15934,7 +15940,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>50</x:v>
@@ -15957,7 +15963,7 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B571" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C571" s="1">
         <x:v>50</x:v>
@@ -15980,13 +15986,13 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="B572" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C572" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D572" s="1">
-        <x:v>183694</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E572" s="1">
         <x:v>0</x:v>
@@ -15995,7 +16001,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>183694</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -16003,22 +16009,22 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C573" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D573" s="1">
-        <x:v>0</x:v>
+        <x:v>183694</x:v>
       </x:c>
       <x:c r="E573" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F573" s="1">
-        <x:v>81050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G573" s="1">
-        <x:v>81050</x:v>
+        <x:v>183694</x:v>
       </x:c>
     </x:row>
     <x:row r="574" spans="1:7">
@@ -16026,10 +16032,10 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C574" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D574" s="1">
         <x:v>0</x:v>
@@ -16038,10 +16044,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F574" s="1">
-        <x:v>0</x:v>
+        <x:v>81050</x:v>
       </x:c>
       <x:c r="G574" s="1">
-        <x:v>50</x:v>
+        <x:v>81050</x:v>
       </x:c>
     </x:row>
     <x:row r="575" spans="1:7">
@@ -16049,7 +16055,7 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="B575" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C575" s="1">
         <x:v>50</x:v>
@@ -16072,10 +16078,10 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="B576" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C576" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D576" s="1">
         <x:v>0</x:v>
@@ -16087,7 +16093,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G576" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="577" spans="1:7">
@@ -16095,10 +16101,10 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B577" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C577" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D577" s="1">
         <x:v>0</x:v>
@@ -16110,7 +16116,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G577" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
     </x:row>
     <x:row r="578" spans="1:7">
@@ -16118,7 +16124,7 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="B578" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C578" s="1">
         <x:v>50</x:v>
@@ -16130,10 +16136,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F578" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G578" s="1">
-        <x:v>14050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="579" spans="1:7">
@@ -16141,10 +16147,10 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B579" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C579" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D579" s="1">
         <x:v>0</x:v>
@@ -16153,10 +16159,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F579" s="1">
-        <x:v>2700</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G579" s="1">
-        <x:v>2700</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="580" spans="1:7">
@@ -16164,7 +16170,7 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C580" s="1">
         <x:v>0</x:v>
@@ -16176,10 +16182,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F580" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G580" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="581" spans="1:7">
@@ -16187,27 +16193,27 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B581" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C581" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D581" s="1">
-        <x:v>7276846</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E581" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F581" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G581" s="1">
-        <x:v>7276846</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="582" spans="1:7">
       <x:c r="A582" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
         <x:v>102</x:v>
@@ -16233,13 +16239,13 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B583" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C583" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D583" s="1">
-        <x:v>0</x:v>
+        <x:v>7276846</x:v>
       </x:c>
       <x:c r="E583" s="1">
         <x:v>0</x:v>
@@ -16248,7 +16254,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G583" s="1">
-        <x:v>50</x:v>
+        <x:v>7276846</x:v>
       </x:c>
     </x:row>
     <x:row r="584" spans="1:7">
@@ -16256,10 +16262,10 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="B584" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C584" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D584" s="1">
         <x:v>0</x:v>
@@ -16268,10 +16274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F584" s="1">
-        <x:v>11834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G584" s="1">
-        <x:v>23884</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:7">
@@ -16279,10 +16285,10 @@
         <x:v>642</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>100</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -16291,10 +16297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>0</x:v>
+        <x:v>11834</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>100</x:v>
+        <x:v>23884</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -16302,10 +16308,10 @@
         <x:v>643</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D586" s="1">
         <x:v>0</x:v>
@@ -16317,7 +16323,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -16325,7 +16331,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C587" s="1">
         <x:v>50</x:v>
@@ -16348,7 +16354,7 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C588" s="1">
         <x:v>50</x:v>
@@ -16360,10 +16366,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F588" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G588" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:7">
@@ -16371,7 +16377,7 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C589" s="1">
         <x:v>50</x:v>
@@ -16383,10 +16389,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F589" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G589" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:7">
@@ -16394,7 +16400,7 @@
         <x:v>647</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C590" s="1">
         <x:v>50</x:v>
@@ -16417,7 +16423,7 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C591" s="1">
         <x:v>50</x:v>
@@ -16440,7 +16446,7 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C592" s="1">
         <x:v>50</x:v>
@@ -16463,22 +16469,22 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="B593" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C593" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D593" s="1">
-        <x:v>3975320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E593" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F593" s="1">
-        <x:v>6634</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G593" s="1">
-        <x:v>3982954</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="594" spans="1:7">
@@ -16486,22 +16492,22 @@
         <x:v>651</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C594" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D594" s="1">
-        <x:v>0</x:v>
+        <x:v>3975320</x:v>
       </x:c>
       <x:c r="E594" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F594" s="1">
-        <x:v>22000</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G594" s="1">
-        <x:v>22000</x:v>
+        <x:v>3982954</x:v>
       </x:c>
     </x:row>
     <x:row r="595" spans="1:7">
@@ -16509,10 +16515,10 @@
         <x:v>652</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C595" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D595" s="1">
         <x:v>0</x:v>
@@ -16521,10 +16527,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F595" s="1">
-        <x:v>5800</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G595" s="1">
-        <x:v>5850</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="596" spans="1:7">
@@ -16532,7 +16538,7 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>654</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C596" s="1">
         <x:v>50</x:v>
@@ -16544,21 +16550,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F596" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G596" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="597" spans="1:7">
       <x:c r="A597" s="1" t="s">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="B597" s="1" t="s">
         <x:v>655</x:v>
       </x:c>
-      <x:c r="B597" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C597" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D597" s="1">
         <x:v>0</x:v>
@@ -16567,10 +16573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F597" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G597" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="598" spans="1:7">
@@ -16578,10 +16584,10 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>657</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C598" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D598" s="1">
         <x:v>0</x:v>
@@ -16590,18 +16596,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F598" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G598" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="599" spans="1:7">
       <x:c r="A599" s="1" t="s">
+        <x:v>657</x:v>
+      </x:c>
+      <x:c r="B599" s="1" t="s">
         <x:v>658</x:v>
-      </x:c>
-      <x:c r="B599" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C599" s="1">
         <x:v>50</x:v>
@@ -16624,7 +16630,7 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C600" s="1">
         <x:v>50</x:v>
@@ -16644,7 +16650,7 @@
     </x:row>
     <x:row r="601" spans="1:7">
       <x:c r="A601" s="1" t="s">
-        <x:v>659</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
         <x:v>93</x:v>
@@ -16670,7 +16676,7 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="C602" s="1">
         <x:v>50</x:v>
@@ -16693,7 +16699,7 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C603" s="1">
         <x:v>50</x:v>
@@ -16716,10 +16722,10 @@
         <x:v>662</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C604" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D604" s="1">
         <x:v>0</x:v>
@@ -16728,10 +16734,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F604" s="1">
-        <x:v>68600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G604" s="1">
-        <x:v>71150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="605" spans="1:7">
@@ -16739,10 +16745,10 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16751,10 +16757,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>0</x:v>
+        <x:v>68600</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>50</x:v>
+        <x:v>71150</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16762,7 +16768,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>50</x:v>
@@ -16785,10 +16791,10 @@
         <x:v>665</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C607" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D607" s="1">
         <x:v>0</x:v>
@@ -16797,10 +16803,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F607" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G607" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="608" spans="1:7">
@@ -16808,10 +16814,10 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C608" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D608" s="1">
         <x:v>0</x:v>
@@ -16820,10 +16826,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F608" s="1">
-        <x:v>58000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G608" s="1">
-        <x:v>58050</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="609" spans="1:7">
@@ -16831,10 +16837,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B609" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C609" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D609" s="1">
         <x:v>0</x:v>
@@ -16843,10 +16849,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F609" s="1">
-        <x:v>1666</x:v>
+        <x:v>58000</x:v>
       </x:c>
       <x:c r="G609" s="1">
-        <x:v>3716</x:v>
+        <x:v>58050</x:v>
       </x:c>
     </x:row>
     <x:row r="610" spans="1:7">
@@ -16854,10 +16860,10 @@
         <x:v>668</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C610" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D610" s="1">
         <x:v>0</x:v>
@@ -16866,10 +16872,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F610" s="1">
-        <x:v>1668</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="G610" s="1">
-        <x:v>1668</x:v>
+        <x:v>3716</x:v>
       </x:c>
     </x:row>
     <x:row r="611" spans="1:7">
@@ -16877,10 +16883,10 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C611" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D611" s="1">
         <x:v>0</x:v>
@@ -16889,10 +16895,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F611" s="1">
-        <x:v>0</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G611" s="1">
-        <x:v>50</x:v>
+        <x:v>1668</x:v>
       </x:c>
     </x:row>
     <x:row r="612" spans="1:7">
@@ -16900,7 +16906,7 @@
         <x:v>670</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>50</x:v>
@@ -16923,10 +16929,10 @@
         <x:v>671</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C613" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D613" s="1">
         <x:v>0</x:v>
@@ -16935,10 +16941,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F613" s="1">
-        <x:v>30600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G613" s="1">
-        <x:v>33550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:7">
@@ -16946,10 +16952,10 @@
         <x:v>672</x:v>
       </x:c>
       <x:c r="B614" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C614" s="1">
-        <x:v>2550</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D614" s="1">
         <x:v>0</x:v>
@@ -16958,10 +16964,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F614" s="1">
-        <x:v>0</x:v>
+        <x:v>30600</x:v>
       </x:c>
       <x:c r="G614" s="1">
-        <x:v>2550</x:v>
+        <x:v>33550</x:v>
       </x:c>
     </x:row>
     <x:row r="615" spans="1:7">
@@ -16969,22 +16975,22 @@
         <x:v>673</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E615" s="1">
-        <x:v>56045</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -17001,7 +17007,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E616" s="1">
-        <x:v>0</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="F616" s="1">
         <x:v>0</x:v>
@@ -17015,10 +17021,10 @@
         <x:v>675</x:v>
       </x:c>
       <x:c r="B617" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C617" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D617" s="1">
         <x:v>0</x:v>
@@ -17030,7 +17036,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G617" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="618" spans="1:7">
@@ -17038,10 +17044,10 @@
         <x:v>676</x:v>
       </x:c>
       <x:c r="B618" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C618" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D618" s="1">
         <x:v>0</x:v>
@@ -17053,7 +17059,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G618" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="619" spans="1:7">
@@ -17061,10 +17067,10 @@
         <x:v>677</x:v>
       </x:c>
       <x:c r="B619" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C619" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D619" s="1">
         <x:v>0</x:v>
@@ -17076,21 +17082,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G619" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="620" spans="1:7">
       <x:c r="A620" s="1" t="s">
-        <x:v>677</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C620" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D620" s="1">
-        <x:v>550000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E620" s="1">
         <x:v>0</x:v>
@@ -17099,7 +17105,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G620" s="1">
-        <x:v>550000</x:v>
+        <x:v>4550</x:v>
       </x:c>
     </x:row>
     <x:row r="621" spans="1:7">
@@ -17113,7 +17119,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D621" s="1">
-        <x:v>426280</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E621" s="1">
         <x:v>0</x:v>
@@ -17122,7 +17128,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G621" s="1">
-        <x:v>426280</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="622" spans="1:7">
@@ -17130,13 +17136,13 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C622" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D622" s="1">
-        <x:v>0</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="E622" s="1">
         <x:v>0</x:v>
@@ -17145,7 +17151,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G622" s="1">
-        <x:v>50</x:v>
+        <x:v>426280</x:v>
       </x:c>
     </x:row>
     <x:row r="623" spans="1:7">
@@ -17153,7 +17159,7 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C623" s="1">
         <x:v>50</x:v>
@@ -17176,13 +17182,13 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C624" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D624" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E624" s="1">
         <x:v>0</x:v>
@@ -17191,7 +17197,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G624" s="1">
-        <x:v>1100000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="625" spans="1:7">
@@ -17199,13 +17205,13 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D625" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E625" s="1">
         <x:v>0</x:v>
@@ -17214,7 +17220,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>50</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17222,7 +17228,7 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C626" s="1">
         <x:v>50</x:v>
@@ -17245,7 +17251,7 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C627" s="1">
         <x:v>50</x:v>
@@ -17268,10 +17274,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B628" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C628" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D628" s="1">
         <x:v>0</x:v>
@@ -17283,7 +17289,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G628" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:7">
@@ -17291,10 +17297,10 @@
         <x:v>686</x:v>
       </x:c>
       <x:c r="B629" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C629" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D629" s="1">
         <x:v>0</x:v>
@@ -17306,7 +17312,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G629" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="630" spans="1:7">
@@ -17314,10 +17320,10 @@
         <x:v>687</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C630" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D630" s="1">
         <x:v>0</x:v>
@@ -17329,7 +17335,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G630" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="631" spans="1:7">
@@ -17337,10 +17343,10 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>1050</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D631" s="1">
         <x:v>0</x:v>
@@ -17349,10 +17355,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>2717</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -17360,10 +17366,10 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
@@ -17372,10 +17378,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>0</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>50</x:v>
+        <x:v>2717</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17383,22 +17389,22 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C633" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D633" s="1">
-        <x:v>55799</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E633" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F633" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G633" s="1">
-        <x:v>59099</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="634" spans="1:7">
@@ -17406,22 +17412,22 @@
         <x:v>691</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C634" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D634" s="1">
-        <x:v>0</x:v>
+        <x:v>111598</x:v>
       </x:c>
       <x:c r="E634" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F634" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G634" s="1">
-        <x:v>50</x:v>
+        <x:v>114898</x:v>
       </x:c>
     </x:row>
     <x:row r="635" spans="1:7">
@@ -17429,7 +17435,7 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C635" s="1">
         <x:v>50</x:v>
@@ -17452,7 +17458,7 @@
         <x:v>693</x:v>
       </x:c>
       <x:c r="B636" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C636" s="1">
         <x:v>50</x:v>
@@ -17475,22 +17481,22 @@
         <x:v>694</x:v>
       </x:c>
       <x:c r="B637" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C637" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D637" s="1">
-        <x:v>10046680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E637" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F637" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G637" s="1">
-        <x:v>10048730</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="638" spans="1:7">
@@ -17498,22 +17504,22 @@
         <x:v>695</x:v>
       </x:c>
       <x:c r="B638" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C638" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D638" s="1">
-        <x:v>1131900</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E638" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F638" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G638" s="1">
-        <x:v>1131950</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="639" spans="1:7">
@@ -17521,13 +17527,13 @@
         <x:v>696</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C639" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D639" s="1">
-        <x:v>0</x:v>
+        <x:v>1131900</x:v>
       </x:c>
       <x:c r="E639" s="1">
         <x:v>0</x:v>
@@ -17536,7 +17542,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>50</x:v>
+        <x:v>1131950</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -17544,7 +17550,7 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C640" s="1">
         <x:v>50</x:v>
@@ -17556,10 +17562,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F640" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G640" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:7">
@@ -17567,10 +17573,10 @@
         <x:v>698</x:v>
       </x:c>
       <x:c r="B641" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C641" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D641" s="1">
         <x:v>0</x:v>
@@ -17579,10 +17585,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F641" s="1">
-        <x:v>52333</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G641" s="1">
-        <x:v>58383</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="642" spans="1:7">
@@ -17590,10 +17596,10 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C642" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D642" s="1">
         <x:v>0</x:v>
@@ -17602,10 +17608,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F642" s="1">
-        <x:v>0</x:v>
+        <x:v>52333</x:v>
       </x:c>
       <x:c r="G642" s="1">
-        <x:v>50</x:v>
+        <x:v>58383</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:7">
@@ -17613,7 +17619,7 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="B643" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C643" s="1">
         <x:v>50</x:v>
@@ -17636,10 +17642,10 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D644" s="1">
         <x:v>0</x:v>
@@ -17648,10 +17654,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F644" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17659,22 +17665,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>817169</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>1668</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>820837</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17682,22 +17688,22 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>11050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D646" s="1">
-        <x:v>0</x:v>
+        <x:v>54685</x:v>
       </x:c>
       <x:c r="E646" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F646" s="1">
-        <x:v>6242</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>17292</x:v>
+        <x:v>54685</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -17705,22 +17711,22 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="B647" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C647" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D647" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E647" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F647" s="1">
-        <x:v>0</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G647" s="1">
-        <x:v>50</x:v>
+        <x:v>820837</x:v>
       </x:c>
     </x:row>
     <x:row r="648" spans="1:7">
@@ -17731,7 +17737,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C648" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D648" s="1">
         <x:v>0</x:v>
@@ -17740,10 +17746,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F648" s="1">
-        <x:v>0</x:v>
+        <x:v>6242</x:v>
       </x:c>
       <x:c r="G648" s="1">
-        <x:v>50</x:v>
+        <x:v>17292</x:v>
       </x:c>
     </x:row>
     <x:row r="649" spans="1:7">
@@ -17751,7 +17757,7 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B649" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C649" s="1">
         <x:v>50</x:v>
@@ -17763,10 +17769,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F649" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G649" s="1">
-        <x:v>25050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:7">
@@ -17774,7 +17780,7 @@
         <x:v>707</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C650" s="1">
         <x:v>50</x:v>
@@ -17797,22 +17803,22 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C651" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D651" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E651" s="1">
-        <x:v>1531015</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F651" s="1">
-        <x:v>0</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G651" s="1">
-        <x:v>0</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:7">
@@ -17820,7 +17826,7 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C652" s="1">
         <x:v>50</x:v>
@@ -17843,22 +17849,22 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D653" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E653" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F653" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
@@ -17866,13 +17872,13 @@
         <x:v>711</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C654" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D654" s="1">
-        <x:v>5583432</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E654" s="1">
         <x:v>0</x:v>
@@ -17881,7 +17887,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G654" s="1">
-        <x:v>5584432</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="655" spans="1:7">
@@ -17889,7 +17895,7 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C655" s="1">
         <x:v>50</x:v>
@@ -17912,13 +17918,13 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C656" s="1">
-        <x:v>18050</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>764206</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
@@ -17927,7 +17933,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>782256</x:v>
+        <x:v>5584432</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -17935,10 +17941,10 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C657" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D657" s="1">
         <x:v>0</x:v>
@@ -17947,10 +17953,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F657" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G657" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:7">
@@ -17958,13 +17964,13 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B658" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C658" s="1">
-        <x:v>0</x:v>
+        <x:v>18050</x:v>
       </x:c>
       <x:c r="D658" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="E658" s="1">
         <x:v>0</x:v>
@@ -17973,7 +17979,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G658" s="1">
-        <x:v>1543316</x:v>
+        <x:v>782256</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:7">
@@ -17981,10 +17987,10 @@
         <x:v>716</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C659" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D659" s="1">
         <x:v>0</x:v>
@@ -17993,10 +17999,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F659" s="1">
-        <x:v>14500</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G659" s="1">
-        <x:v>14550</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:7">
@@ -18004,13 +18010,13 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D660" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E660" s="1">
         <x:v>0</x:v>
@@ -18019,7 +18025,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>50</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18027,7 +18033,7 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C661" s="1">
         <x:v>50</x:v>
@@ -18039,10 +18045,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F661" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>50</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18050,13 +18056,13 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C662" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D662" s="1">
-        <x:v>107353</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E662" s="1">
         <x:v>0</x:v>
@@ -18065,7 +18071,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>107403</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -18073,22 +18079,22 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C663" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D663" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E663" s="1">
-        <x:v>9985740</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F663" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G663" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:7">
@@ -18096,22 +18102,22 @@
         <x:v>721</x:v>
       </x:c>
       <x:c r="B664" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C664" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D664" s="1">
-        <x:v>0</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="E664" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F664" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G664" s="1">
-        <x:v>3334</x:v>
+        <x:v>107403</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:7">
@@ -18119,22 +18125,22 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B665" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C665" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D665" s="1">
-        <x:v>106947</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E665" s="1">
-        <x:v>0</x:v>
+        <x:v>9985740</x:v>
       </x:c>
       <x:c r="F665" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G665" s="1">
-        <x:v>106947</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:7">
@@ -18142,10 +18148,10 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C666" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D666" s="1">
         <x:v>0</x:v>
@@ -18154,10 +18160,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F666" s="1">
-        <x:v>25000</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G666" s="1">
-        <x:v>25050</x:v>
+        <x:v>3334</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:7">
@@ -18165,22 +18171,22 @@
         <x:v>724</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C667" s="1">
-        <x:v>1050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D667" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="E667" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F667" s="1">
-        <x:v>7000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G667" s="1">
-        <x:v>910226</x:v>
+        <x:v>106947</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:7">
@@ -18188,7 +18194,7 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C668" s="1">
         <x:v>50</x:v>
@@ -18200,10 +18206,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F668" s="1">
-        <x:v>25500</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>25550</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -18211,22 +18217,22 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C669" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D669" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E669" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F669" s="1">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>50</x:v>
+        <x:v>910226</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
@@ -18234,10 +18240,10 @@
         <x:v>727</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C670" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D670" s="1">
         <x:v>0</x:v>
@@ -18246,10 +18252,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F670" s="1">
-        <x:v>10500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="G670" s="1">
-        <x:v>10500</x:v>
+        <x:v>25550</x:v>
       </x:c>
     </x:row>
     <x:row r="671" spans="1:7">
@@ -18257,10 +18263,10 @@
         <x:v>728</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C671" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D671" s="1">
         <x:v>0</x:v>
@@ -18269,10 +18275,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F671" s="1">
-        <x:v>6200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>6200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">
@@ -18283,7 +18289,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C672" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D672" s="1">
         <x:v>0</x:v>
@@ -18292,10 +18298,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F672" s="1">
-        <x:v>0</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G672" s="1">
-        <x:v>50</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="673" spans="1:7">
@@ -18303,10 +18309,10 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B673" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C673" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D673" s="1">
         <x:v>0</x:v>
@@ -18315,10 +18321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F673" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G673" s="1">
-        <x:v>1000</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="674" spans="1:7">
@@ -18326,7 +18332,7 @@
         <x:v>731</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C674" s="1">
         <x:v>50</x:v>
@@ -18338,10 +18344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F674" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G674" s="1">
-        <x:v>6650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="675" spans="1:7">
@@ -18349,13 +18355,13 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C675" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D675" s="1">
-        <x:v>1010142</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E675" s="1">
         <x:v>0</x:v>
@@ -18364,7 +18370,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G675" s="1">
-        <x:v>1010142</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:7">
@@ -18372,10 +18378,10 @@
         <x:v>733</x:v>
       </x:c>
       <x:c r="B676" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C676" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D676" s="1">
         <x:v>0</x:v>
@@ -18384,10 +18390,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F676" s="1">
-        <x:v>5000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G676" s="1">
-        <x:v>5000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="677" spans="1:7">
@@ -18395,13 +18401,13 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B677" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C677" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D677" s="1">
-        <x:v>0</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="E677" s="1">
         <x:v>0</x:v>
@@ -18410,7 +18416,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>50</x:v>
+        <x:v>1010142</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
@@ -18418,10 +18424,10 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B678" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C678" s="1">
-        <x:v>6550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D678" s="1">
         <x:v>0</x:v>
@@ -18430,10 +18436,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F678" s="1">
-        <x:v>3300</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G678" s="1">
-        <x:v>9850</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="679" spans="1:7">
@@ -18441,7 +18447,7 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C679" s="1">
         <x:v>50</x:v>
@@ -18464,10 +18470,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D680" s="1">
         <x:v>0</x:v>
@@ -18476,10 +18482,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>50</x:v>
+        <x:v>9850</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -18487,10 +18493,10 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D681" s="1">
         <x:v>0</x:v>
@@ -18499,10 +18505,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>9550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -18510,10 +18516,10 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
@@ -18522,10 +18528,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -18533,10 +18539,10 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D683" s="1">
         <x:v>0</x:v>
@@ -18545,10 +18551,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>50</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -18556,10 +18562,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D684" s="1">
         <x:v>0</x:v>
@@ -18568,24 +18574,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>4300</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>7850</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
       <x:c r="A685" s="1" t="s">
-        <x:v>741</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D685" s="1">
-        <x:v>550000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E685" s="1">
         <x:v>0</x:v>
@@ -18594,30 +18600,30 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>550000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
       <x:c r="A686" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D686" s="1">
-        <x:v>1916563</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>5000</x:v>
+        <x:v>4300</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>1921613</x:v>
+        <x:v>7850</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -18625,13 +18631,13 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C687" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D687" s="1">
-        <x:v>0</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E687" s="1">
         <x:v>0</x:v>
@@ -18640,7 +18646,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>50</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
@@ -18648,22 +18654,22 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C688" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D688" s="1">
-        <x:v>0</x:v>
+        <x:v>1916563</x:v>
       </x:c>
       <x:c r="E688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F688" s="1">
-        <x:v>5750</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>5800</x:v>
+        <x:v>1921613</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
@@ -18671,7 +18677,7 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C689" s="1">
         <x:v>50</x:v>
@@ -18694,10 +18700,10 @@
         <x:v>746</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -18706,10 +18712,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>3300</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>3300</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -18717,7 +18723,7 @@
         <x:v>747</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C691" s="1">
         <x:v>50</x:v>
@@ -18740,10 +18746,10 @@
         <x:v>748</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -18752,10 +18758,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>3700</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>3750</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -18763,7 +18769,7 @@
         <x:v>749</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C693" s="1">
         <x:v>50</x:v>
@@ -18786,7 +18792,7 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C694" s="1">
         <x:v>50</x:v>
@@ -18798,10 +18804,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F694" s="1">
-        <x:v>0</x:v>
+        <x:v>3700</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>50</x:v>
+        <x:v>3750</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
@@ -18809,22 +18815,22 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C695" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D695" s="1">
-        <x:v>404474</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E695" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F695" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>421974</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
@@ -18832,10 +18838,10 @@
         <x:v>752</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D696" s="1">
         <x:v>0</x:v>
@@ -18844,10 +18850,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -18855,22 +18861,22 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C697" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D697" s="1">
-        <x:v>0</x:v>
+        <x:v>448266</x:v>
       </x:c>
       <x:c r="E697" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F697" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>50</x:v>
+        <x:v>465766</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">
@@ -18878,10 +18884,10 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C698" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D698" s="1">
         <x:v>0</x:v>
@@ -18890,10 +18896,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F698" s="1">
-        <x:v>1500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>3500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
@@ -18901,7 +18907,7 @@
         <x:v>755</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C699" s="1">
         <x:v>50</x:v>
@@ -18924,22 +18930,22 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C700" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D700" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E700" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F700" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>40000</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
@@ -18947,10 +18953,10 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C701" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D701" s="1">
         <x:v>0</x:v>
@@ -18962,7 +18968,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
@@ -18970,13 +18976,13 @@
         <x:v>758</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C702" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
@@ -18985,7 +18991,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>50</x:v>
+        <x:v>40000</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
@@ -18993,10 +18999,10 @@
         <x:v>759</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C703" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D703" s="1">
         <x:v>0</x:v>
@@ -19005,10 +19011,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F703" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>5200</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
@@ -19016,7 +19022,7 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C704" s="1">
         <x:v>50</x:v>
@@ -19039,10 +19045,10 @@
         <x:v>761</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D705" s="1">
         <x:v>0</x:v>
@@ -19051,10 +19057,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19062,7 +19068,7 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C706" s="1">
         <x:v>50</x:v>
@@ -19074,10 +19080,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -19085,13 +19091,13 @@
         <x:v>763</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D707" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E707" s="1">
         <x:v>0</x:v>
@@ -19100,7 +19106,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>3920589</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
@@ -19108,7 +19114,7 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C708" s="1">
         <x:v>50</x:v>
@@ -19120,10 +19126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
@@ -19131,13 +19137,13 @@
         <x:v>765</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D709" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E709" s="1">
         <x:v>0</x:v>
@@ -19146,7 +19152,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>1000</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -19154,7 +19160,7 @@
         <x:v>766</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C710" s="1">
         <x:v>50</x:v>
@@ -19177,10 +19183,10 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C711" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D711" s="1">
         <x:v>0</x:v>
@@ -19192,7 +19198,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
@@ -19200,10 +19206,10 @@
         <x:v>768</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D712" s="1">
         <x:v>0</x:v>
@@ -19212,10 +19218,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>7834</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19223,10 +19229,10 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D713" s="1">
         <x:v>0</x:v>
@@ -19238,7 +19244,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19246,10 +19252,10 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>50</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D714" s="1">
         <x:v>0</x:v>
@@ -19258,10 +19264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>50</x:v>
+        <x:v>7834</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19269,10 +19275,10 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D715" s="1">
         <x:v>0</x:v>
@@ -19284,7 +19290,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
@@ -19292,13 +19298,13 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D716" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E716" s="1">
         <x:v>0</x:v>
@@ -19307,7 +19313,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19315,7 +19321,7 @@
         <x:v>773</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C717" s="1">
         <x:v>50</x:v>
@@ -19338,22 +19344,22 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C718" s="1">
-        <x:v>14600</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D718" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E718" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F718" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>31600</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
@@ -19361,7 +19367,7 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C719" s="1">
         <x:v>50</x:v>
@@ -19384,10 +19390,10 @@
         <x:v>776</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>50</x:v>
+        <x:v>14600</x:v>
       </x:c>
       <x:c r="D720" s="1">
         <x:v>0</x:v>
@@ -19396,10 +19402,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F720" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>50</x:v>
+        <x:v>31600</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
@@ -19407,7 +19413,7 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C721" s="1">
         <x:v>50</x:v>
@@ -19430,13 +19436,13 @@
         <x:v>778</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C722" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D722" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E722" s="1">
         <x:v>0</x:v>
@@ -19445,7 +19451,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
@@ -19453,7 +19459,7 @@
         <x:v>779</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C723" s="1">
         <x:v>50</x:v>
@@ -19476,22 +19482,22 @@
         <x:v>780</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C724" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D724" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E724" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F724" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>30000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
@@ -19499,7 +19505,7 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C725" s="1">
         <x:v>50</x:v>
@@ -19522,10 +19528,10 @@
         <x:v>782</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C726" s="1">
-        <x:v>19050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D726" s="1">
         <x:v>0</x:v>
@@ -19534,10 +19540,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F726" s="1">
-        <x:v>2500</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>21550</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
@@ -19545,10 +19551,10 @@
         <x:v>783</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D727" s="1">
         <x:v>0</x:v>
@@ -19560,7 +19566,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
@@ -19568,10 +19574,10 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C728" s="1">
-        <x:v>50</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D728" s="1">
         <x:v>0</x:v>
@@ -19580,21 +19586,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>50</x:v>
+        <x:v>21550</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
       <x:c r="A729" s="1" t="s">
-        <x:v>784</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C729" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D729" s="1">
         <x:v>0</x:v>
@@ -19603,18 +19609,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F729" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>35</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">
       <x:c r="A730" s="1" t="s">
-        <x:v>785</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C730" s="1">
         <x:v>50</x:v>
@@ -19637,10 +19643,10 @@
         <x:v>786</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C731" s="1">
-        <x:v>6450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D731" s="1">
         <x:v>0</x:v>
@@ -19649,10 +19655,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F731" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>6450</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
@@ -19660,7 +19666,7 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C732" s="1">
         <x:v>50</x:v>
@@ -19683,10 +19689,10 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C733" s="1">
-        <x:v>0</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D733" s="1">
         <x:v>0</x:v>
@@ -19695,10 +19701,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F733" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G733" s="1">
-        <x:v>1000</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:7">
@@ -19706,7 +19712,7 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C734" s="1">
         <x:v>50</x:v>
@@ -19729,10 +19735,10 @@
         <x:v>790</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19741,10 +19747,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19752,10 +19758,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19764,10 +19770,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
@@ -19775,7 +19781,7 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C737" s="1">
         <x:v>50</x:v>
@@ -19798,10 +19804,10 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C738" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D738" s="1">
         <x:v>0</x:v>
@@ -19810,10 +19816,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F738" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
@@ -19821,13 +19827,13 @@
         <x:v>794</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="C739" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D739" s="1">
-        <x:v>943006</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E739" s="1">
         <x:v>0</x:v>
@@ -19836,7 +19842,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G739" s="1">
-        <x:v>943056</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:7">
@@ -19844,7 +19850,7 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C740" s="1">
         <x:v>50</x:v>
@@ -19867,13 +19873,13 @@
         <x:v>796</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C741" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D741" s="1">
-        <x:v>0</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="E741" s="1">
         <x:v>0</x:v>
@@ -19882,7 +19888,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>50</x:v>
+        <x:v>943056</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">
@@ -19890,10 +19896,10 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C742" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D742" s="1">
         <x:v>0</x:v>
@@ -19902,10 +19908,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F742" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
@@ -19913,7 +19919,7 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C743" s="1">
         <x:v>50</x:v>
@@ -19936,10 +19942,10 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C744" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D744" s="1">
         <x:v>0</x:v>
@@ -19948,10 +19954,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F744" s="1">
-        <x:v>4999</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G744" s="1">
-        <x:v>5049</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:7">
@@ -19959,10 +19965,10 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C745" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D745" s="1">
         <x:v>0</x:v>
@@ -19971,10 +19977,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F745" s="1">
-        <x:v>16500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G745" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:7">
@@ -19982,7 +19988,7 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C746" s="1">
         <x:v>50</x:v>
@@ -19994,10 +20000,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>0</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>50</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20005,10 +20011,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D747" s="1">
         <x:v>0</x:v>
@@ -20017,10 +20023,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F747" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">
@@ -20028,7 +20034,7 @@
         <x:v>803</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C748" s="1">
         <x:v>50</x:v>
@@ -20051,7 +20057,7 @@
         <x:v>804</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C749" s="1">
         <x:v>50</x:v>
@@ -20074,7 +20080,7 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C750" s="1">
         <x:v>50</x:v>
@@ -20097,7 +20103,7 @@
         <x:v>806</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C751" s="1">
         <x:v>50</x:v>
@@ -20120,10 +20126,10 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20132,10 +20138,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>37300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>48150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
@@ -20143,10 +20149,10 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20155,10 +20161,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>83</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
@@ -20166,10 +20172,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C754" s="1">
-        <x:v>50</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D754" s="1">
         <x:v>0</x:v>
@@ -20178,10 +20184,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F754" s="1">
-        <x:v>0</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>50</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
@@ -20189,10 +20195,10 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -20201,10 +20207,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F755" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
@@ -20212,7 +20218,7 @@
         <x:v>811</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C756" s="1">
         <x:v>50</x:v>
@@ -20235,10 +20241,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20247,10 +20253,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20258,21 +20264,67 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C758" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D758" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E758" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F758" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G758" s="1">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="759" spans="1:7">
+      <x:c r="A759" s="1" t="s">
+        <x:v>814</x:v>
+      </x:c>
+      <x:c r="B759" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C759" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D759" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E759" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F759" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G759" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="760" spans="1:7">
+      <x:c r="A760" s="1" t="s">
+        <x:v>815</x:v>
+      </x:c>
+      <x:c r="B760" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C758" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D758" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E758" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F758" s="1">
+      <x:c r="C760" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D760" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E760" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F760" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G758" s="1">
+      <x:c r="G760" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -10173,7 +10173,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D319" s="1">
-        <x:v>54932</x:v>
+        <x:v>366028</x:v>
       </x:c>
       <x:c r="E319" s="1">
         <x:v>0</x:v>
@@ -10182,7 +10182,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G319" s="1">
-        <x:v>54932</x:v>
+        <x:v>366028</x:v>
       </x:c>
     </x:row>
     <x:row r="320" spans="1:7">
@@ -13071,7 +13071,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D445" s="1">
-        <x:v>111440</x:v>
+        <x:v>372060</x:v>
       </x:c>
       <x:c r="E445" s="1">
         <x:v>0</x:v>
@@ -13080,7 +13080,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G445" s="1">
-        <x:v>111440</x:v>
+        <x:v>372060</x:v>
       </x:c>
     </x:row>
     <x:row r="446" spans="1:7">
@@ -13301,7 +13301,7 @@
         <x:v>1550</x:v>
       </x:c>
       <x:c r="D455" s="1">
-        <x:v>413633</x:v>
+        <x:v>478028</x:v>
       </x:c>
       <x:c r="E455" s="1">
         <x:v>0</x:v>
@@ -13310,7 +13310,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G455" s="1">
-        <x:v>415183</x:v>
+        <x:v>479578</x:v>
       </x:c>
     </x:row>
     <x:row r="456" spans="1:7">
@@ -16653,10 +16653,10 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="C601" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D601" s="1">
         <x:v>0</x:v>
@@ -16665,10 +16665,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F601" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G601" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:7">
@@ -16676,10 +16676,10 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C602" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D602" s="1">
         <x:v>0</x:v>
@@ -16688,10 +16688,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F602" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -17694,7 +17694,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D646" s="1">
-        <x:v>54685</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="E646" s="1">
         <x:v>0</x:v>
@@ -17703,7 +17703,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>54685</x:v>
+        <x:v>367531</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -18608,22 +18608,22 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D686" s="1">
-        <x:v>0</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>4300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>7850</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -18631,22 +18631,22 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C687" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D687" s="1">
-        <x:v>550000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E687" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F687" s="1">
-        <x:v>0</x:v>
+        <x:v>4300</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>550000</x:v>
+        <x:v>7850</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
@@ -19948,7 +19948,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="D744" s="1">
-        <x:v>0</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="E744" s="1">
         <x:v>0</x:v>
@@ -19957,7 +19957,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G744" s="1">
-        <x:v>2500</x:v>
+        <x:v>478754</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16216,7 +16216,7 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C582" s="1">
         <x:v>0</x:v>
@@ -16239,7 +16239,7 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B583" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C583" s="1">
         <x:v>0</x:v>
@@ -16291,7 +16291,7 @@
         <x:v>12050</x:v>
       </x:c>
       <x:c r="D585" s="1">
-        <x:v>0</x:v>
+        <x:v>1235244</x:v>
       </x:c>
       <x:c r="E585" s="1">
         <x:v>0</x:v>
@@ -16300,7 +16300,7 @@
         <x:v>11834</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>23884</x:v>
+        <x:v>1259128</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -18608,22 +18608,22 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D686" s="1">
-        <x:v>550000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>0</x:v>
+        <x:v>4300</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>550000</x:v>
+        <x:v>7850</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -18631,22 +18631,22 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C687" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D687" s="1">
-        <x:v>0</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E687" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F687" s="1">
-        <x:v>4300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>7850</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4009,7 +4009,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>3114863</x:v>
+        <x:v>3174537</x:v>
       </x:c>
       <x:c r="E51" s="1">
         <x:v>0</x:v>
@@ -4018,7 +4018,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G51" s="1">
-        <x:v>3114863</x:v>
+        <x:v>3174537</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
@@ -16653,10 +16653,10 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C601" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D601" s="1">
         <x:v>0</x:v>
@@ -16665,10 +16665,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F601" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G601" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:7">
@@ -16676,10 +16676,10 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="C602" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D602" s="1">
         <x:v>0</x:v>
@@ -16688,10 +16688,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F602" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -18660,7 +18660,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D688" s="1">
-        <x:v>1916563</x:v>
+        <x:v>1972681</x:v>
       </x:c>
       <x:c r="E688" s="1">
         <x:v>0</x:v>
@@ -18669,7 +18669,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>1921613</x:v>
+        <x:v>1977731</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
@@ -18867,7 +18867,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D697" s="1">
-        <x:v>448266</x:v>
+        <x:v>492058</x:v>
       </x:c>
       <x:c r="E697" s="1">
         <x:v>0</x:v>
@@ -18876,7 +18876,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>465766</x:v>
+        <x:v>509558</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16323,7 +16323,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>0</x:v>
@@ -16346,7 +16346,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C587" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -18790,7 +18790,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D693" s="1">
-        <x:v>1972681</x:v>
+        <x:v>2028799</x:v>
       </x:c>
       <x:c r="E693" s="1">
         <x:v>0</x:v>
@@ -18799,7 +18799,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>1977731</x:v>
+        <x:v>2033849</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4047,7 +4047,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>3174537</x:v>
+        <x:v>3234211</x:v>
       </x:c>
       <x:c r="E52" s="1">
         <x:v>0</x:v>
@@ -4056,7 +4056,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G52" s="1">
-        <x:v>3174537</x:v>
+        <x:v>3234211</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
@@ -8802,13 +8802,13 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="B259" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C259" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D259" s="1">
-        <x:v>3850000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E259" s="1">
         <x:v>0</x:v>
@@ -8817,7 +8817,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G259" s="1">
-        <x:v>3850050</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="260" spans="1:7">
@@ -8825,13 +8825,13 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="B260" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C260" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D260" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850000</x:v>
       </x:c>
       <x:c r="E260" s="1">
         <x:v>0</x:v>
@@ -8840,7 +8840,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G260" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850050</x:v>
       </x:c>
     </x:row>
     <x:row r="261" spans="1:7">
@@ -18790,7 +18790,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D693" s="1">
-        <x:v>2028799</x:v>
+        <x:v>2347762</x:v>
       </x:c>
       <x:c r="E693" s="1">
         <x:v>0</x:v>
@@ -18799,7 +18799,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>2033849</x:v>
+        <x:v>2352812</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
@@ -18997,7 +18997,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>492058</x:v>
+        <x:v>535850</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
@@ -19006,7 +19006,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>509558</x:v>
+        <x:v>553350</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
@@ -19750,10 +19750,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19762,10 +19762,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19773,10 +19773,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19785,10 +19785,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -8802,13 +8802,13 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="B259" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C259" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D259" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850000</x:v>
       </x:c>
       <x:c r="E259" s="1">
         <x:v>0</x:v>
@@ -8817,7 +8817,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G259" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850050</x:v>
       </x:c>
     </x:row>
     <x:row r="260" spans="1:7">
@@ -8825,13 +8825,13 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="B260" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C260" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D260" s="1">
-        <x:v>3850000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E260" s="1">
         <x:v>0</x:v>
@@ -8840,7 +8840,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G260" s="1">
-        <x:v>3850050</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="261" spans="1:7">
@@ -16760,10 +16760,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16772,10 +16772,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16783,10 +16783,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16795,10 +16795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -18997,7 +18997,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>535850</x:v>
+        <x:v>558161</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
@@ -19006,7 +19006,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>553350</x:v>
+        <x:v>575661</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4047,7 +4047,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>3234211</x:v>
+        <x:v>3293885</x:v>
       </x:c>
       <x:c r="E52" s="1">
         <x:v>0</x:v>
@@ -4056,7 +4056,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G52" s="1">
-        <x:v>3234211</x:v>
+        <x:v>3293885</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
@@ -16323,7 +16323,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>0</x:v>
@@ -16346,7 +16346,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C587" s="1">
         <x:v>0</x:v>
@@ -16760,10 +16760,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16772,10 +16772,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16783,10 +16783,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16795,10 +16795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -18997,7 +18997,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>558161</x:v>
+        <x:v>601953</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
@@ -19006,7 +19006,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>575661</x:v>
+        <x:v>619453</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
@@ -19750,10 +19750,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19762,10 +19762,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19773,10 +19773,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19785,10 +19785,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -6252,7 +6252,7 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="C148" s="1">
-        <x:v>5000</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="D148" s="1">
         <x:v>0</x:v>
@@ -6264,7 +6264,7 @@
         <x:v>10000</x:v>
       </x:c>
       <x:c r="G148" s="1">
-        <x:v>15000</x:v>
+        <x:v>16000</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
@@ -7664,10 +7664,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F209" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G209" s="1">
-        <x:v>2411933</x:v>
+        <x:v>2421933</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:7">
@@ -7891,7 +7891,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E219" s="1">
-        <x:v>2475786</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="F219" s="1">
         <x:v>0</x:v>
@@ -11039,7 +11039,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D356" s="1">
-        <x:v>285008</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="E356" s="1">
         <x:v>0</x:v>
@@ -11048,7 +11048,7 @@
         <x:v>5000</x:v>
       </x:c>
       <x:c r="G356" s="1">
-        <x:v>290058</x:v>
+        <x:v>290059</x:v>
       </x:c>
     </x:row>
     <x:row r="357" spans="1:7">
@@ -11266,7 +11266,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C366" s="1">
-        <x:v>12200</x:v>
+        <x:v>14700</x:v>
       </x:c>
       <x:c r="D366" s="1">
         <x:v>3848426</x:v>
@@ -11278,7 +11278,7 @@
         <x:v>15700</x:v>
       </x:c>
       <x:c r="G366" s="1">
-        <x:v>3876326</x:v>
+        <x:v>3878826</x:v>
       </x:c>
     </x:row>
     <x:row r="367" spans="1:7">
@@ -11522,7 +11522,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D377" s="1">
-        <x:v>30183</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="E377" s="1">
         <x:v>0</x:v>
@@ -11531,7 +11531,7 @@
         <x:v>7500</x:v>
       </x:c>
       <x:c r="G377" s="1">
-        <x:v>37683</x:v>
+        <x:v>37720</x:v>
       </x:c>
     </x:row>
     <x:row r="378" spans="1:7">
@@ -13385,7 +13385,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D458" s="1">
-        <x:v>6468074</x:v>
+        <x:v>6471277</x:v>
       </x:c>
       <x:c r="E458" s="1">
         <x:v>0</x:v>
@@ -13394,7 +13394,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G458" s="1">
-        <x:v>6468074</x:v>
+        <x:v>6471277</x:v>
       </x:c>
     </x:row>
     <x:row r="459" spans="1:7">
@@ -13497,7 +13497,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="C463" s="1">
-        <x:v>1550</x:v>
+        <x:v>4050</x:v>
       </x:c>
       <x:c r="D463" s="1">
         <x:v>0</x:v>
@@ -13509,7 +13509,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G463" s="1">
-        <x:v>1550</x:v>
+        <x:v>4050</x:v>
       </x:c>
     </x:row>
     <x:row r="464" spans="1:7">
@@ -13796,7 +13796,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C476" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D476" s="1">
         <x:v>668449</x:v>
@@ -13808,7 +13808,7 @@
         <x:v>7600</x:v>
       </x:c>
       <x:c r="G476" s="1">
-        <x:v>676049</x:v>
+        <x:v>678549</x:v>
       </x:c>
     </x:row>
     <x:row r="477" spans="1:7">
@@ -16122,7 +16122,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D577" s="1">
-        <x:v>183694</x:v>
+        <x:v>275541</x:v>
       </x:c>
       <x:c r="E577" s="1">
         <x:v>0</x:v>
@@ -16131,7 +16131,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G577" s="1">
-        <x:v>183694</x:v>
+        <x:v>275541</x:v>
       </x:c>
     </x:row>
     <x:row r="578" spans="1:7">
@@ -16760,10 +16760,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16772,10 +16772,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16783,10 +16783,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16795,10 +16795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -18097,7 +18097,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="C663" s="1">
-        <x:v>18050</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D663" s="1">
         <x:v>764206</x:v>
@@ -18106,10 +18106,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F663" s="1">
-        <x:v>0</x:v>
+        <x:v>20001</x:v>
       </x:c>
       <x:c r="G663" s="1">
-        <x:v>782256</x:v>
+        <x:v>803257</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:7">
@@ -18264,7 +18264,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E670" s="1">
-        <x:v>9985740</x:v>
+        <x:v>10135449</x:v>
       </x:c>
       <x:c r="F670" s="1">
         <x:v>0</x:v>
@@ -19900,10 +19900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F741" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -8802,13 +8802,13 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="B259" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C259" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D259" s="1">
-        <x:v>3850000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E259" s="1">
         <x:v>0</x:v>
@@ -8817,7 +8817,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G259" s="1">
-        <x:v>3850050</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="260" spans="1:7">
@@ -8825,13 +8825,13 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="B260" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C260" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D260" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850000</x:v>
       </x:c>
       <x:c r="E260" s="1">
         <x:v>0</x:v>
@@ -8840,7 +8840,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G260" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850050</x:v>
       </x:c>
     </x:row>
     <x:row r="261" spans="1:7">
@@ -16760,10 +16760,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16772,10 +16772,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16783,10 +16783,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16795,10 +16795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -19750,10 +19750,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19762,10 +19762,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19773,10 +19773,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19785,10 +19785,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4047,7 +4047,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>3293885</x:v>
+        <x:v>3353559</x:v>
       </x:c>
       <x:c r="E52" s="1">
         <x:v>0</x:v>
@@ -4056,7 +4056,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G52" s="1">
-        <x:v>3293885</x:v>
+        <x:v>3353559</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
@@ -8802,13 +8802,13 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="B259" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C259" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D259" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850000</x:v>
       </x:c>
       <x:c r="E259" s="1">
         <x:v>0</x:v>
@@ -8817,7 +8817,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G259" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850050</x:v>
       </x:c>
     </x:row>
     <x:row r="260" spans="1:7">
@@ -8825,13 +8825,13 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="B260" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C260" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D260" s="1">
-        <x:v>3850000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E260" s="1">
         <x:v>0</x:v>
@@ -8840,7 +8840,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G260" s="1">
-        <x:v>3850050</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="261" spans="1:7">
@@ -9659,7 +9659,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D296" s="1">
-        <x:v>0</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="E296" s="1">
         <x:v>0</x:v>
@@ -9668,7 +9668,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G296" s="1">
-        <x:v>50</x:v>
+        <x:v>300050</x:v>
       </x:c>
     </x:row>
     <x:row r="297" spans="1:7">
@@ -16323,7 +16323,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>0</x:v>
@@ -16346,7 +16346,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C587" s="1">
         <x:v>0</x:v>
@@ -18997,7 +18997,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>601953</x:v>
+        <x:v>659202</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
@@ -19006,7 +19006,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>619453</x:v>
+        <x:v>676702</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
@@ -19750,10 +19750,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19762,10 +19762,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19773,10 +19773,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19785,10 +19785,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -9659,7 +9659,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D296" s="1">
-        <x:v>300000</x:v>
+        <x:v>1035613</x:v>
       </x:c>
       <x:c r="E296" s="1">
         <x:v>0</x:v>
@@ -9668,7 +9668,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G296" s="1">
-        <x:v>300050</x:v>
+        <x:v>1035663</x:v>
       </x:c>
     </x:row>
     <x:row r="297" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4047,7 +4047,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>3353559</x:v>
+        <x:v>4868351</x:v>
       </x:c>
       <x:c r="E52" s="1">
         <x:v>0</x:v>
@@ -4056,7 +4056,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G52" s="1">
-        <x:v>3353559</x:v>
+        <x:v>4868351</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
@@ -16323,7 +16323,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>0</x:v>
@@ -16346,7 +16346,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C587" s="1">
         <x:v>0</x:v>
@@ -16760,10 +16760,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16772,10 +16772,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16783,10 +16783,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16795,10 +16795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -18997,7 +18997,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>659202</x:v>
+        <x:v>681513</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
@@ -19006,7 +19006,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>676702</x:v>
+        <x:v>699013</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -4047,7 +4047,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>4868351</x:v>
+        <x:v>4928025</x:v>
       </x:c>
       <x:c r="E52" s="1">
         <x:v>0</x:v>
@@ -4056,7 +4056,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G52" s="1">
-        <x:v>4868351</x:v>
+        <x:v>4928025</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
@@ -16323,7 +16323,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>0</x:v>
@@ -16346,7 +16346,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C587" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -18997,7 +18997,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>681513</x:v>
+        <x:v>738762</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
@@ -19006,7 +19006,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>699013</x:v>
+        <x:v>756262</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3380,7 +3380,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>513868</x:v>
+        <x:v>1027736</x:v>
       </x:c>
       <x:c r="E23" s="1">
         <x:v>0</x:v>
@@ -3389,7 +3389,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G23" s="1">
-        <x:v>513918</x:v>
+        <x:v>1027786</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
@@ -3495,7 +3495,7 @@
         <x:v>14300</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>22459135</x:v>
+        <x:v>23087732</x:v>
       </x:c>
       <x:c r="E28" s="1">
         <x:v>0</x:v>
@@ -3504,7 +3504,7 @@
         <x:v>17500</x:v>
       </x:c>
       <x:c r="G28" s="1">
-        <x:v>22490935</x:v>
+        <x:v>23119532</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
@@ -5611,7 +5611,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D120" s="1">
-        <x:v>4210393</x:v>
+        <x:v>4212649</x:v>
       </x:c>
       <x:c r="E120" s="1">
         <x:v>0</x:v>
@@ -5620,7 +5620,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G120" s="1">
-        <x:v>4210393</x:v>
+        <x:v>4212649</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7">
@@ -8141,7 +8141,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D230" s="1">
-        <x:v>1510292</x:v>
+        <x:v>1636862</x:v>
       </x:c>
       <x:c r="E230" s="1">
         <x:v>0</x:v>
@@ -8150,7 +8150,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G230" s="1">
-        <x:v>1510292</x:v>
+        <x:v>1636862</x:v>
       </x:c>
     </x:row>
     <x:row r="231" spans="1:7">
@@ -8210,7 +8210,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D233" s="1">
-        <x:v>708827</x:v>
+        <x:v>773165</x:v>
       </x:c>
       <x:c r="E233" s="1">
         <x:v>0</x:v>
@@ -8219,7 +8219,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G233" s="1">
-        <x:v>708827</x:v>
+        <x:v>773165</x:v>
       </x:c>
     </x:row>
     <x:row r="234" spans="1:7">
@@ -8791,10 +8791,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F258" s="1">
-        <x:v>88800</x:v>
+        <x:v>127300</x:v>
       </x:c>
       <x:c r="G258" s="1">
-        <x:v>336141</x:v>
+        <x:v>374641</x:v>
       </x:c>
     </x:row>
     <x:row r="259" spans="1:7">
@@ -11430,7 +11430,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D373" s="1">
-        <x:v>430866</x:v>
+        <x:v>485801</x:v>
       </x:c>
       <x:c r="E373" s="1">
         <x:v>0</x:v>
@@ -11439,7 +11439,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G373" s="1">
-        <x:v>430866</x:v>
+        <x:v>485801</x:v>
       </x:c>
     </x:row>
     <x:row r="374" spans="1:7">
@@ -12074,7 +12074,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D401" s="1">
-        <x:v>350000</x:v>
+        <x:v>700000</x:v>
       </x:c>
       <x:c r="E401" s="1">
         <x:v>0</x:v>
@@ -12083,7 +12083,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G401" s="1">
-        <x:v>351500</x:v>
+        <x:v>701500</x:v>
       </x:c>
     </x:row>
     <x:row r="402" spans="1:7">
@@ -12264,10 +12264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F409" s="1">
-        <x:v>37600</x:v>
+        <x:v>58600</x:v>
       </x:c>
       <x:c r="G409" s="1">
-        <x:v>258198</x:v>
+        <x:v>279198</x:v>
       </x:c>
     </x:row>
     <x:row r="410" spans="1:7">
@@ -13385,7 +13385,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D458" s="1">
-        <x:v>6471277</x:v>
+        <x:v>6471278</x:v>
       </x:c>
       <x:c r="E458" s="1">
         <x:v>0</x:v>
@@ -13394,7 +13394,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G458" s="1">
-        <x:v>6471277</x:v>
+        <x:v>6471278</x:v>
       </x:c>
     </x:row>
     <x:row r="459" spans="1:7">
@@ -13914,7 +13914,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D481" s="1">
-        <x:v>221403</x:v>
+        <x:v>442806</x:v>
       </x:c>
       <x:c r="E481" s="1">
         <x:v>0</x:v>
@@ -13923,7 +13923,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G481" s="1">
-        <x:v>221403</x:v>
+        <x:v>442806</x:v>
       </x:c>
     </x:row>
     <x:row r="482" spans="1:7">
@@ -14972,7 +14972,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D527" s="1">
-        <x:v>6750000</x:v>
+        <x:v>8250000</x:v>
       </x:c>
       <x:c r="E527" s="1">
         <x:v>0</x:v>
@@ -14981,7 +14981,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G527" s="1">
-        <x:v>6750000</x:v>
+        <x:v>8250000</x:v>
       </x:c>
     </x:row>
     <x:row r="528" spans="1:7">
@@ -15915,7 +15915,7 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="D568" s="1">
-        <x:v>700000</x:v>
+        <x:v>1400000</x:v>
       </x:c>
       <x:c r="E568" s="1">
         <x:v>0</x:v>
@@ -15924,7 +15924,7 @@
         <x:v>7000</x:v>
       </x:c>
       <x:c r="G568" s="1">
-        <x:v>709500</x:v>
+        <x:v>1409500</x:v>
       </x:c>
     </x:row>
     <x:row r="569" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16760,10 +16760,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16772,10 +16772,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16783,10 +16783,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16795,10 +16795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -18997,7 +18997,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>738762</x:v>
+        <x:v>1038762</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
@@ -19006,7 +19006,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>756262</x:v>
+        <x:v>1056262</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3504,7 +3504,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E28" s="1">
-        <x:v>73841</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="F28" s="1">
         <x:v>0</x:v>
@@ -4076,7 +4076,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D53" s="1">
-        <x:v>5175229</x:v>
+        <x:v>5259517</x:v>
       </x:c>
       <x:c r="E53" s="1">
         <x:v>0</x:v>
@@ -4085,7 +4085,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G53" s="1">
-        <x:v>5175229</x:v>
+        <x:v>5259517</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
@@ -7322,7 +7322,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E194" s="1">
-        <x:v>147682</x:v>
+        <x:v>344592</x:v>
       </x:c>
       <x:c r="F194" s="1">
         <x:v>0</x:v>
@@ -16375,7 +16375,7 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C588" s="1">
         <x:v>0</x:v>
@@ -16398,7 +16398,7 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C589" s="1">
         <x:v>0</x:v>
@@ -19049,7 +19049,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D704" s="1">
-        <x:v>1835021</x:v>
+        <x:v>1892270</x:v>
       </x:c>
       <x:c r="E704" s="1">
         <x:v>0</x:v>
@@ -19058,7 +19058,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>1852521</x:v>
+        <x:v>1909770</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17327,13 +17327,13 @@
         <x:v>687</x:v>
       </x:c>
       <x:c r="B629" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C629" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D629" s="1">
-        <x:v>550000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E629" s="1">
         <x:v>0</x:v>
@@ -17342,7 +17342,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G629" s="1">
-        <x:v>550000</x:v>
+        <x:v>4550</x:v>
       </x:c>
     </x:row>
     <x:row r="630" spans="1:7">
@@ -17350,13 +17350,13 @@
         <x:v>687</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C630" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D630" s="1">
-        <x:v>0</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E630" s="1">
         <x:v>0</x:v>
@@ -17365,7 +17365,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G630" s="1">
-        <x:v>4550</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="631" spans="1:7">
@@ -18868,22 +18868,22 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D696" s="1">
-        <x:v>0</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E696" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>9350</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -18891,22 +18891,22 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C697" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D697" s="1">
-        <x:v>550000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E697" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F697" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>550000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16453,7 +16453,7 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C591" s="1">
         <x:v>0</x:v>
@@ -16476,7 +16476,7 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C592" s="1">
         <x:v>0</x:v>
@@ -16890,10 +16890,10 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C610" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D610" s="1">
         <x:v>0</x:v>
@@ -16902,10 +16902,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F610" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G610" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="611" spans="1:7">
@@ -16913,10 +16913,10 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C611" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D611" s="1">
         <x:v>0</x:v>
@@ -16925,10 +16925,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F611" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G611" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="612" spans="1:7">
@@ -18868,22 +18868,22 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D696" s="1">
-        <x:v>550000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E696" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>550000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -18891,22 +18891,22 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C697" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D697" s="1">
-        <x:v>0</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E697" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F697" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>9350</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16453,7 +16453,7 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C591" s="1">
         <x:v>0</x:v>
@@ -16476,7 +16476,7 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C592" s="1">
         <x:v>0</x:v>
@@ -16890,10 +16890,10 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C610" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D610" s="1">
         <x:v>0</x:v>
@@ -16902,10 +16902,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F610" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G610" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="611" spans="1:7">
@@ -16913,10 +16913,10 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C611" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D611" s="1">
         <x:v>0</x:v>
@@ -16925,10 +16925,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F611" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G611" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="612" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16563,7 +16563,7 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C595" s="1">
         <x:v>0</x:v>
@@ -16586,7 +16586,7 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C596" s="1">
         <x:v>0</x:v>
@@ -20036,10 +20036,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D746" s="1">
         <x:v>0</x:v>
@@ -20048,10 +20048,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20059,10 +20059,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D747" s="1">
         <x:v>0</x:v>
@@ -20071,10 +20071,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F747" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16563,7 +16563,7 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C595" s="1">
         <x:v>0</x:v>
@@ -16586,7 +16586,7 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C596" s="1">
         <x:v>0</x:v>
@@ -17460,22 +17460,22 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C634" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D634" s="1">
-        <x:v>0</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E634" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F634" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G634" s="1">
-        <x:v>5050</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="635" spans="1:7">
@@ -17483,22 +17483,22 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C635" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D635" s="1">
-        <x:v>550000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E635" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F635" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G635" s="1">
-        <x:v>550000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:7">
@@ -20036,10 +20036,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D746" s="1">
         <x:v>0</x:v>
@@ -20048,10 +20048,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20059,10 +20059,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D747" s="1">
         <x:v>0</x:v>
@@ -20071,10 +20071,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F747" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17460,22 +17460,22 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C634" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D634" s="1">
-        <x:v>550000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E634" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F634" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G634" s="1">
-        <x:v>550000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="635" spans="1:7">
@@ -17483,22 +17483,22 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C635" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D635" s="1">
-        <x:v>0</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E635" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F635" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G635" s="1">
-        <x:v>5050</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -8950,13 +8950,13 @@
         <x:v>316</x:v>
       </x:c>
       <x:c r="B264" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C264" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D264" s="1">
-        <x:v>3850000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="E264" s="1">
         <x:v>0</x:v>
@@ -8965,7 +8965,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G264" s="1">
-        <x:v>3850050</x:v>
+        <x:v>550000</x:v>
       </x:c>
     </x:row>
     <x:row r="265" spans="1:7">
@@ -8973,13 +8973,13 @@
         <x:v>316</x:v>
       </x:c>
       <x:c r="B265" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C265" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D265" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850000</x:v>
       </x:c>
       <x:c r="E265" s="1">
         <x:v>0</x:v>
@@ -8988,7 +8988,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G265" s="1">
-        <x:v>550000</x:v>
+        <x:v>3850050</x:v>
       </x:c>
     </x:row>
     <x:row r="266" spans="1:7">
@@ -20036,10 +20036,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D746" s="1">
         <x:v>0</x:v>
@@ -20048,10 +20048,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20059,10 +20059,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D747" s="1">
         <x:v>0</x:v>
@@ -20071,10 +20071,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F747" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -8950,13 +8950,13 @@
         <x:v>316</x:v>
       </x:c>
       <x:c r="B264" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C264" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D264" s="1">
-        <x:v>550000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E264" s="1">
         <x:v>0</x:v>
@@ -8965,7 +8965,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G264" s="1">
-        <x:v>550000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="265" spans="1:7">
@@ -8973,13 +8973,13 @@
         <x:v>316</x:v>
       </x:c>
       <x:c r="B265" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C265" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D265" s="1">
-        <x:v>3850000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E265" s="1">
         <x:v>0</x:v>
@@ -8988,7 +8988,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G265" s="1">
-        <x:v>3850050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="266" spans="1:7">
@@ -9830,7 +9830,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D302" s="1">
-        <x:v>1035613</x:v>
+        <x:v>1335613</x:v>
       </x:c>
       <x:c r="E302" s="1">
         <x:v>0</x:v>
@@ -9839,7 +9839,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G302" s="1">
-        <x:v>1035663</x:v>
+        <x:v>1335663</x:v>
       </x:c>
     </x:row>
     <x:row r="303" spans="1:7">
@@ -12274,10 +12274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F408" s="1">
-        <x:v>1500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="G408" s="1">
-        <x:v>701500</x:v>
+        <x:v>708500</x:v>
       </x:c>
     </x:row>
     <x:row r="409" spans="1:7">
@@ -13947,7 +13947,7 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="D481" s="1">
-        <x:v>17947569</x:v>
+        <x:v>35895138</x:v>
       </x:c>
       <x:c r="E481" s="1">
         <x:v>0</x:v>
@@ -13956,7 +13956,7 @@
         <x:v>8000</x:v>
       </x:c>
       <x:c r="G481" s="1">
-        <x:v>17959069</x:v>
+        <x:v>35906638</x:v>
       </x:c>
     </x:row>
     <x:row r="482" spans="1:7">
@@ -17023,10 +17023,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -17035,10 +17035,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -17046,10 +17046,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D616" s="1">
         <x:v>0</x:v>
@@ -17058,10 +17058,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -17489,7 +17489,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D635" s="1">
-        <x:v>550000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E635" s="1">
         <x:v>0</x:v>
@@ -17498,7 +17498,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G635" s="1">
-        <x:v>550000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:7">
@@ -17581,7 +17581,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D639" s="1">
-        <x:v>1100000</x:v>
+        <x:v>2200000</x:v>
       </x:c>
       <x:c r="E639" s="1">
         <x:v>0</x:v>
@@ -17590,7 +17590,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>1100000</x:v>
+        <x:v>2200000</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -19053,7 +19053,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D703" s="1">
-        <x:v>550000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E703" s="1">
         <x:v>0</x:v>
@@ -19062,7 +19062,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>550000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
@@ -20036,10 +20036,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D746" s="1">
         <x:v>0</x:v>
@@ -20048,10 +20048,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20059,10 +20059,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D747" s="1">
         <x:v>0</x:v>
@@ -20071,10 +20071,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F747" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16563,7 +16563,7 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C595" s="1">
         <x:v>0</x:v>
@@ -16586,7 +16586,7 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C596" s="1">
         <x:v>0</x:v>
@@ -17023,10 +17023,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -17035,10 +17035,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -17046,10 +17046,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D616" s="1">
         <x:v>0</x:v>
@@ -17058,10 +17058,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16563,7 +16563,7 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C595" s="1">
         <x:v>0</x:v>
@@ -16586,7 +16586,7 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C596" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17023,10 +17023,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -17035,10 +17035,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -17046,10 +17046,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D616" s="1">
         <x:v>0</x:v>
@@ -17058,10 +17058,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -18271,7 +18271,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D669" s="1">
-        <x:v>0</x:v>
+        <x:v>52520</x:v>
       </x:c>
       <x:c r="E669" s="1">
         <x:v>0</x:v>
@@ -18280,7 +18280,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>50</x:v>
+        <x:v>52570</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17023,10 +17023,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -17035,10 +17035,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -17046,10 +17046,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>457</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D616" s="1">
         <x:v>0</x:v>
@@ -17058,10 +17058,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16615,7 +16615,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B597" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C597" s="1">
         <x:v>0</x:v>
@@ -16638,7 +16638,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C598" s="1">
         <x:v>0</x:v>
@@ -17075,10 +17075,10 @@
         <x:v>676</x:v>
       </x:c>
       <x:c r="B617" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C617" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D617" s="1">
         <x:v>0</x:v>
@@ -17087,10 +17087,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F617" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G617" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="618" spans="1:7">
@@ -17098,10 +17098,10 @@
         <x:v>676</x:v>
       </x:c>
       <x:c r="B618" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C618" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D618" s="1">
         <x:v>0</x:v>
@@ -17110,10 +17110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F618" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G618" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="619" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16615,7 +16615,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B597" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C597" s="1">
         <x:v>0</x:v>
@@ -16638,7 +16638,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C598" s="1">
         <x:v>0</x:v>
@@ -18323,7 +18323,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D671" s="1">
-        <x:v>52520</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="E671" s="1">
         <x:v>0</x:v>
@@ -18332,7 +18332,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>52570</x:v>
+        <x:v>105090</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -1565,6 +1565,9 @@
   </x:si>
   <x:si>
     <x:t>MCKINLEY, DAVID B. MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, AMANDA</x:t>
   </x:si>
   <x:si>
     <x:t>MCMORRIS RODGERS, CATHY</x:t>
@@ -2586,8 +2589,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G778" totalsRowShown="0">
-  <x:autoFilter ref="A1:G778"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G780" totalsRowShown="0">
+  <x:autoFilter ref="A1:G780"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2889,7 +2892,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G778"/>
+  <x:dimension ref="A1:G780"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -7053,7 +7056,7 @@
         <x:v>6050</x:v>
       </x:c>
       <x:c r="D181" s="1">
-        <x:v>0</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="E181" s="1">
         <x:v>0</x:v>
@@ -7062,7 +7065,7 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="G181" s="1">
-        <x:v>9382</x:v>
+        <x:v>122502</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:7">
@@ -8979,13 +8982,13 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="B265" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C265" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D265" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E265" s="1">
         <x:v>0</x:v>
@@ -8994,7 +8997,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G265" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="266" spans="1:7">
@@ -9002,13 +9005,13 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="B266" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C266" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D266" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E266" s="1">
         <x:v>0</x:v>
@@ -9017,7 +9020,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G266" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="267" spans="1:7">
@@ -13490,10 +13493,10 @@
         <x:v>135</x:v>
       </x:c>
       <x:c r="C461" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D461" s="1">
-        <x:v>0</x:v>
+        <x:v>65340</x:v>
       </x:c>
       <x:c r="E461" s="1">
         <x:v>0</x:v>
@@ -13502,7 +13505,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G461" s="1">
-        <x:v>50</x:v>
+        <x:v>65340</x:v>
       </x:c>
     </x:row>
     <x:row r="462" spans="1:7">
@@ -13510,10 +13513,10 @@
         <x:v>518</x:v>
       </x:c>
       <x:c r="B462" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C462" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D462" s="1">
         <x:v>0</x:v>
@@ -13522,10 +13525,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F462" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G462" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="463" spans="1:7">
@@ -13533,10 +13536,10 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="B463" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C463" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D463" s="1">
         <x:v>0</x:v>
@@ -13545,10 +13548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F463" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G463" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="464" spans="1:7">
@@ -13556,7 +13559,7 @@
         <x:v>520</x:v>
       </x:c>
       <x:c r="B464" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C464" s="1">
         <x:v>50</x:v>
@@ -13568,10 +13571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F464" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G464" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="465" spans="1:7">
@@ -13579,22 +13582,22 @@
         <x:v>521</x:v>
       </x:c>
       <x:c r="B465" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C465" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D465" s="1">
-        <x:v>923885</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E465" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F465" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G465" s="1">
-        <x:v>923885</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="466" spans="1:7">
@@ -13602,13 +13605,13 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B466" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C466" s="1">
-        <x:v>1050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D466" s="1">
-        <x:v>92320</x:v>
+        <x:v>923885</x:v>
       </x:c>
       <x:c r="E466" s="1">
         <x:v>0</x:v>
@@ -13617,7 +13620,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G466" s="1">
-        <x:v>93370</x:v>
+        <x:v>923885</x:v>
       </x:c>
     </x:row>
     <x:row r="467" spans="1:7">
@@ -13625,13 +13628,13 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B467" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C467" s="1">
-        <x:v>0</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D467" s="1">
-        <x:v>6471279</x:v>
+        <x:v>92320</x:v>
       </x:c>
       <x:c r="E467" s="1">
         <x:v>0</x:v>
@@ -13640,7 +13643,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G467" s="1">
-        <x:v>6471279</x:v>
+        <x:v>93370</x:v>
       </x:c>
     </x:row>
     <x:row r="468" spans="1:7">
@@ -13648,13 +13651,13 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="B468" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C468" s="1">
-        <x:v>1550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D468" s="1">
-        <x:v>512918</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="E468" s="1">
         <x:v>0</x:v>
@@ -13663,7 +13666,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G468" s="1">
-        <x:v>514468</x:v>
+        <x:v>6471279</x:v>
       </x:c>
     </x:row>
     <x:row r="469" spans="1:7">
@@ -13671,13 +13674,13 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C469" s="1">
         <x:v>1550</x:v>
       </x:c>
       <x:c r="D469" s="1">
-        <x:v>0</x:v>
+        <x:v>512918</x:v>
       </x:c>
       <x:c r="E469" s="1">
         <x:v>0</x:v>
@@ -13686,7 +13689,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>1550</x:v>
+        <x:v>514468</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -13694,10 +13697,10 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C470" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D470" s="1">
         <x:v>0</x:v>
@@ -13709,7 +13712,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -13717,13 +13720,13 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D471" s="1">
-        <x:v>504020</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E471" s="1">
         <x:v>0</x:v>
@@ -13732,7 +13735,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>504020</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -13740,13 +13743,13 @@
         <x:v>528</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>4050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D472" s="1">
-        <x:v>0</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="E472" s="1">
         <x:v>0</x:v>
@@ -13755,7 +13758,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>4050</x:v>
+        <x:v>504020</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -13763,10 +13766,10 @@
         <x:v>529</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>50</x:v>
+        <x:v>4050</x:v>
       </x:c>
       <x:c r="D473" s="1">
         <x:v>0</x:v>
@@ -13778,7 +13781,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>50</x:v>
+        <x:v>4050</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -13786,7 +13789,7 @@
         <x:v>530</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C474" s="1">
         <x:v>50</x:v>
@@ -13809,10 +13812,10 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B475" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C475" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D475" s="1">
         <x:v>0</x:v>
@@ -13821,10 +13824,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F475" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G475" s="1">
-        <x:v>3667</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="476" spans="1:7">
@@ -13832,22 +13835,22 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B476" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C476" s="1">
-        <x:v>500</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D476" s="1">
-        <x:v>107940</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E476" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F476" s="1">
-        <x:v>1500</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G476" s="1">
-        <x:v>109940</x:v>
+        <x:v>3667</x:v>
       </x:c>
     </x:row>
     <x:row r="477" spans="1:7">
@@ -13855,22 +13858,22 @@
         <x:v>533</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D477" s="1">
-        <x:v>0</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="E477" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>50</x:v>
+        <x:v>109940</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -13878,10 +13881,10 @@
         <x:v>534</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -13890,10 +13893,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>7200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -13901,10 +13904,10 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -13913,10 +13916,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>2000</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>2000</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -13924,10 +13927,10 @@
         <x:v>536</x:v>
       </x:c>
       <x:c r="B480" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C480" s="1">
-        <x:v>5050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D480" s="1">
         <x:v>0</x:v>
@@ -13936,10 +13939,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F480" s="1">
-        <x:v>1000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G480" s="1">
-        <x:v>6050</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="481" spans="1:7">
@@ -13947,10 +13950,10 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="B481" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C481" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D481" s="1">
         <x:v>0</x:v>
@@ -13959,10 +13962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F481" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G481" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
     </x:row>
     <x:row r="482" spans="1:7">
@@ -13970,13 +13973,13 @@
         <x:v>538</x:v>
       </x:c>
       <x:c r="B482" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C482" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D482" s="1">
-        <x:v>400022</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E482" s="1">
         <x:v>0</x:v>
@@ -13985,7 +13988,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G482" s="1">
-        <x:v>401022</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="483" spans="1:7">
@@ -13993,22 +13996,22 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="B483" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C483" s="1">
-        <x:v>3500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D483" s="1">
-        <x:v>44693946</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="E483" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F483" s="1">
-        <x:v>8000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G483" s="1">
-        <x:v>44705446</x:v>
+        <x:v>401022</x:v>
       </x:c>
     </x:row>
     <x:row r="484" spans="1:7">
@@ -14016,22 +14019,22 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="B484" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C484" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D484" s="1">
-        <x:v>0</x:v>
+        <x:v>44693946</x:v>
       </x:c>
       <x:c r="E484" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F484" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G484" s="1">
-        <x:v>50</x:v>
+        <x:v>44705446</x:v>
       </x:c>
     </x:row>
     <x:row r="485" spans="1:7">
@@ -14039,13 +14042,13 @@
         <x:v>541</x:v>
       </x:c>
       <x:c r="B485" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C485" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D485" s="1">
-        <x:v>726377</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E485" s="1">
         <x:v>0</x:v>
@@ -14054,7 +14057,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G485" s="1">
-        <x:v>726377</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="486" spans="1:7">
@@ -14062,22 +14065,22 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C486" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D486" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="E486" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F486" s="1">
-        <x:v>7600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G486" s="1">
-        <x:v>678549</x:v>
+        <x:v>726377</x:v>
       </x:c>
     </x:row>
     <x:row r="487" spans="1:7">
@@ -14085,22 +14088,22 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="B487" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C487" s="1">
-        <x:v>1000</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D487" s="1">
-        <x:v>0</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="E487" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F487" s="1">
-        <x:v>0</x:v>
+        <x:v>7600</x:v>
       </x:c>
       <x:c r="G487" s="1">
-        <x:v>1000</x:v>
+        <x:v>678549</x:v>
       </x:c>
     </x:row>
     <x:row r="488" spans="1:7">
@@ -14108,10 +14111,10 @@
         <x:v>544</x:v>
       </x:c>
       <x:c r="B488" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C488" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D488" s="1">
         <x:v>0</x:v>
@@ -14120,10 +14123,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F488" s="1">
-        <x:v>1250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G488" s="1">
-        <x:v>1300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="489" spans="1:7">
@@ -14131,7 +14134,7 @@
         <x:v>545</x:v>
       </x:c>
       <x:c r="B489" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C489" s="1">
         <x:v>50</x:v>
@@ -14143,10 +14146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F489" s="1">
-        <x:v>0</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="G489" s="1">
-        <x:v>50</x:v>
+        <x:v>1300</x:v>
       </x:c>
     </x:row>
     <x:row r="490" spans="1:7">
@@ -14154,13 +14157,13 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="B490" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C490" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D490" s="1">
-        <x:v>120404787</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E490" s="1">
         <x:v>0</x:v>
@@ -14169,7 +14172,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G490" s="1">
-        <x:v>120406787</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="491" spans="1:7">
@@ -14177,13 +14180,13 @@
         <x:v>547</x:v>
       </x:c>
       <x:c r="B491" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C491" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D491" s="1">
-        <x:v>442806</x:v>
+        <x:v>120404787</x:v>
       </x:c>
       <x:c r="E491" s="1">
         <x:v>0</x:v>
@@ -14192,7 +14195,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G491" s="1">
-        <x:v>442806</x:v>
+        <x:v>120406787</x:v>
       </x:c>
     </x:row>
     <x:row r="492" spans="1:7">
@@ -14200,22 +14203,22 @@
         <x:v>548</x:v>
       </x:c>
       <x:c r="B492" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C492" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D492" s="1">
-        <x:v>0</x:v>
+        <x:v>442806</x:v>
       </x:c>
       <x:c r="E492" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F492" s="1">
-        <x:v>3333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G492" s="1">
-        <x:v>4333</x:v>
+        <x:v>442806</x:v>
       </x:c>
     </x:row>
     <x:row r="493" spans="1:7">
@@ -14223,10 +14226,10 @@
         <x:v>549</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C493" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D493" s="1">
         <x:v>0</x:v>
@@ -14235,10 +14238,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F493" s="1">
-        <x:v>0</x:v>
+        <x:v>3333</x:v>
       </x:c>
       <x:c r="G493" s="1">
-        <x:v>50</x:v>
+        <x:v>4333</x:v>
       </x:c>
     </x:row>
     <x:row r="494" spans="1:7">
@@ -14246,7 +14249,7 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="B494" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C494" s="1">
         <x:v>50</x:v>
@@ -14269,10 +14272,10 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B495" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C495" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D495" s="1">
         <x:v>0</x:v>
@@ -14284,7 +14287,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G495" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="496" spans="1:7">
@@ -14292,10 +14295,10 @@
         <x:v>552</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C496" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D496" s="1">
         <x:v>0</x:v>
@@ -14304,10 +14307,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F496" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G496" s="1">
-        <x:v>1050</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="497" spans="1:7">
@@ -14315,10 +14318,10 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B497" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C497" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D497" s="1">
         <x:v>0</x:v>
@@ -14327,10 +14330,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F497" s="1">
-        <x:v>2700</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G497" s="1">
-        <x:v>5400</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="498" spans="1:7">
@@ -14338,10 +14341,10 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="B498" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C498" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D498" s="1">
         <x:v>0</x:v>
@@ -14350,10 +14353,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F498" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G498" s="1">
-        <x:v>50</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="499" spans="1:7">
@@ -14361,7 +14364,7 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B499" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C499" s="1">
         <x:v>50</x:v>
@@ -14373,10 +14376,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F499" s="1">
-        <x:v>12000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G499" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="500" spans="1:7">
@@ -14384,7 +14387,7 @@
         <x:v>556</x:v>
       </x:c>
       <x:c r="B500" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C500" s="1">
         <x:v>50</x:v>
@@ -14396,10 +14399,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F500" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G500" s="1">
-        <x:v>50</x:v>
+        <x:v>12050</x:v>
       </x:c>
     </x:row>
     <x:row r="501" spans="1:7">
@@ -14407,10 +14410,10 @@
         <x:v>557</x:v>
       </x:c>
       <x:c r="B501" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C501" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D501" s="1">
         <x:v>0</x:v>
@@ -14419,10 +14422,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F501" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G501" s="1">
-        <x:v>250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="502" spans="1:7">
@@ -14430,10 +14433,10 @@
         <x:v>558</x:v>
       </x:c>
       <x:c r="B502" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C502" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D502" s="1">
         <x:v>0</x:v>
@@ -14442,10 +14445,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F502" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G502" s="1">
-        <x:v>50</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="503" spans="1:7">
@@ -14453,7 +14456,7 @@
         <x:v>559</x:v>
       </x:c>
       <x:c r="B503" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C503" s="1">
         <x:v>50</x:v>
@@ -14465,10 +14468,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F503" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G503" s="1">
-        <x:v>2750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="504" spans="1:7">
@@ -14476,10 +14479,10 @@
         <x:v>560</x:v>
       </x:c>
       <x:c r="B504" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C504" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D504" s="1">
         <x:v>0</x:v>
@@ -14488,10 +14491,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F504" s="1">
-        <x:v>4600</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G504" s="1">
-        <x:v>4600</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="505" spans="1:7">
@@ -14499,10 +14502,10 @@
         <x:v>561</x:v>
       </x:c>
       <x:c r="B505" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C505" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D505" s="1">
         <x:v>0</x:v>
@@ -14511,10 +14514,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F505" s="1">
-        <x:v>0</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G505" s="1">
-        <x:v>50</x:v>
+        <x:v>4600</x:v>
       </x:c>
     </x:row>
     <x:row r="506" spans="1:7">
@@ -14522,7 +14525,7 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B506" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C506" s="1">
         <x:v>50</x:v>
@@ -14545,7 +14548,7 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C507" s="1">
         <x:v>50</x:v>
@@ -14568,7 +14571,7 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="B508" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C508" s="1">
         <x:v>50</x:v>
@@ -14591,13 +14594,13 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C509" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D509" s="1">
-        <x:v>282526</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E509" s="1">
         <x:v>0</x:v>
@@ -14606,7 +14609,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G509" s="1">
-        <x:v>282526</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="510" spans="1:7">
@@ -14614,22 +14617,22 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="B510" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C510" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D510" s="1">
-        <x:v>0</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E510" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F510" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G510" s="1">
-        <x:v>1000</x:v>
+        <x:v>282526</x:v>
       </x:c>
     </x:row>
     <x:row r="511" spans="1:7">
@@ -14637,10 +14640,10 @@
         <x:v>567</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C511" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D511" s="1">
         <x:v>0</x:v>
@@ -14649,10 +14652,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F511" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G511" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="512" spans="1:7">
@@ -14660,22 +14663,22 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="B512" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C512" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D512" s="1">
-        <x:v>116161</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E512" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F512" s="1">
-        <x:v>4500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G512" s="1">
-        <x:v>124661</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="513" spans="1:7">
@@ -14683,22 +14686,22 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C513" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D513" s="1">
-        <x:v>0</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="E513" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F513" s="1">
-        <x:v>0</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G513" s="1">
-        <x:v>50</x:v>
+        <x:v>124661</x:v>
       </x:c>
     </x:row>
     <x:row r="514" spans="1:7">
@@ -14706,7 +14709,7 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="B514" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C514" s="1">
         <x:v>50</x:v>
@@ -14729,7 +14732,7 @@
         <x:v>571</x:v>
       </x:c>
       <x:c r="B515" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C515" s="1">
         <x:v>50</x:v>
@@ -14749,10 +14752,10 @@
     </x:row>
     <x:row r="516" spans="1:7">
       <x:c r="A516" s="1" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="B516" s="1" t="s">
         <x:v>573</x:v>
-      </x:c>
-      <x:c r="B516" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C516" s="1">
         <x:v>50</x:v>
@@ -14775,22 +14778,22 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="B517" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C517" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D517" s="1">
-        <x:v>2997852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E517" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F517" s="1">
-        <x:v>6800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G517" s="1">
-        <x:v>3006652</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="518" spans="1:7">
@@ -14798,22 +14801,22 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C518" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D518" s="1">
-        <x:v>14446984</x:v>
+        <x:v>2997852</x:v>
       </x:c>
       <x:c r="E518" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F518" s="1">
-        <x:v>0</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="G518" s="1">
-        <x:v>14446984</x:v>
+        <x:v>3006652</x:v>
       </x:c>
     </x:row>
     <x:row r="519" spans="1:7">
@@ -14821,13 +14824,13 @@
         <x:v>576</x:v>
       </x:c>
       <x:c r="B519" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C519" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D519" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E519" s="1">
         <x:v>0</x:v>
@@ -14836,7 +14839,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G519" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="520" spans="1:7">
@@ -14844,10 +14847,10 @@
         <x:v>577</x:v>
       </x:c>
       <x:c r="B520" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C520" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D520" s="1">
         <x:v>0</x:v>
@@ -14856,10 +14859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F520" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G520" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="521" spans="1:7">
@@ -14867,7 +14870,7 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B521" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C521" s="1">
         <x:v>0</x:v>
@@ -14879,10 +14882,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F521" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="G521" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="522" spans="1:7">
@@ -14890,10 +14893,10 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C522" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D522" s="1">
         <x:v>0</x:v>
@@ -14902,10 +14905,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F522" s="1">
-        <x:v>0</x:v>
+        <x:v>22334</x:v>
       </x:c>
       <x:c r="G522" s="1">
-        <x:v>50</x:v>
+        <x:v>22334</x:v>
       </x:c>
     </x:row>
     <x:row r="523" spans="1:7">
@@ -14913,10 +14916,10 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B523" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C523" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D523" s="1">
         <x:v>0</x:v>
@@ -14925,10 +14928,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F523" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G523" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="524" spans="1:7">
@@ -14936,10 +14939,10 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C524" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D524" s="1">
         <x:v>0</x:v>
@@ -14948,10 +14951,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F524" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -14959,13 +14962,13 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C525" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D525" s="1">
-        <x:v>209387</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E525" s="1">
         <x:v>0</x:v>
@@ -14974,7 +14977,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G525" s="1">
-        <x:v>209387</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:7">
@@ -14982,13 +14985,13 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C526" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D526" s="1">
-        <x:v>0</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="E526" s="1">
         <x:v>0</x:v>
@@ -14997,7 +15000,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G526" s="1">
-        <x:v>50</x:v>
+        <x:v>209387</x:v>
       </x:c>
     </x:row>
     <x:row r="527" spans="1:7">
@@ -15005,13 +15008,13 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B527" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C527" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D527" s="1">
-        <x:v>257695</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E527" s="1">
         <x:v>0</x:v>
@@ -15020,7 +15023,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G527" s="1">
-        <x:v>257695</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="528" spans="1:7">
@@ -15028,22 +15031,22 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="B528" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C528" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D528" s="1">
-        <x:v>0</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="E528" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F528" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G528" s="1">
-        <x:v>3300</x:v>
+        <x:v>257695</x:v>
       </x:c>
     </x:row>
     <x:row r="529" spans="1:7">
@@ -15051,10 +15054,10 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C529" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D529" s="1">
         <x:v>0</x:v>
@@ -15063,10 +15066,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F529" s="1">
-        <x:v>29800</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G529" s="1">
-        <x:v>34800</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="530" spans="1:7">
@@ -15074,10 +15077,10 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="B530" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C530" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D530" s="1">
         <x:v>0</x:v>
@@ -15086,10 +15089,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F530" s="1">
-        <x:v>0</x:v>
+        <x:v>29800</x:v>
       </x:c>
       <x:c r="G530" s="1">
-        <x:v>50</x:v>
+        <x:v>34800</x:v>
       </x:c>
     </x:row>
     <x:row r="531" spans="1:7">
@@ -15097,7 +15100,7 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="B531" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C531" s="1">
         <x:v>50</x:v>
@@ -15109,10 +15112,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F531" s="1">
-        <x:v>5600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G531" s="1">
-        <x:v>5650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="532" spans="1:7">
@@ -15120,10 +15123,10 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C532" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D532" s="1">
         <x:v>0</x:v>
@@ -15132,10 +15135,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F532" s="1">
-        <x:v>0</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G532" s="1">
-        <x:v>2050</x:v>
+        <x:v>5650</x:v>
       </x:c>
     </x:row>
     <x:row r="533" spans="1:7">
@@ -15143,10 +15146,10 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C533" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D533" s="1">
         <x:v>0</x:v>
@@ -15155,10 +15158,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F533" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G533" s="1">
-        <x:v>3384</x:v>
+        <x:v>2050</x:v>
       </x:c>
     </x:row>
     <x:row r="534" spans="1:7">
@@ -15166,7 +15169,7 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="B534" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C534" s="1">
         <x:v>50</x:v>
@@ -15178,10 +15181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F534" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G534" s="1">
-        <x:v>50</x:v>
+        <x:v>3384</x:v>
       </x:c>
     </x:row>
     <x:row r="535" spans="1:7">
@@ -15189,22 +15192,22 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B535" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C535" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D535" s="1">
-        <x:v>558813</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E535" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F535" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G535" s="1">
-        <x:v>559813</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="536" spans="1:7">
@@ -15212,22 +15215,22 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C536" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D536" s="1">
-        <x:v>0</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E536" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F536" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G536" s="1">
-        <x:v>6650</x:v>
+        <x:v>559813</x:v>
       </x:c>
     </x:row>
     <x:row r="537" spans="1:7">
@@ -15235,22 +15238,22 @@
         <x:v>594</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C537" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D537" s="1">
-        <x:v>8250000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E537" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F537" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G537" s="1">
-        <x:v>8250000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="538" spans="1:7">
@@ -15258,13 +15261,13 @@
         <x:v>595</x:v>
       </x:c>
       <x:c r="B538" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C538" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D538" s="1">
-        <x:v>0</x:v>
+        <x:v>8250000</x:v>
       </x:c>
       <x:c r="E538" s="1">
         <x:v>0</x:v>
@@ -15273,7 +15276,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G538" s="1">
-        <x:v>50</x:v>
+        <x:v>8250000</x:v>
       </x:c>
     </x:row>
     <x:row r="539" spans="1:7">
@@ -15281,22 +15284,22 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C539" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D539" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E539" s="1">
-        <x:v>20483</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F539" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G539" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="540" spans="1:7">
@@ -15304,22 +15307,22 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C540" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D540" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E540" s="1">
-        <x:v>0</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="F540" s="1">
-        <x:v>1089100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G540" s="1">
-        <x:v>1089150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:7">
@@ -15327,22 +15330,22 @@
         <x:v>598</x:v>
       </x:c>
       <x:c r="B541" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C541" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D541" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E541" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F541" s="1">
-        <x:v>0</x:v>
+        <x:v>1089100</x:v>
       </x:c>
       <x:c r="G541" s="1">
-        <x:v>1927706</x:v>
+        <x:v>1089150</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:7">
@@ -15350,13 +15353,13 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B542" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C542" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D542" s="1">
-        <x:v>0</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="E542" s="1">
         <x:v>0</x:v>
@@ -15365,7 +15368,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G542" s="1">
-        <x:v>50</x:v>
+        <x:v>1927706</x:v>
       </x:c>
     </x:row>
     <x:row r="543" spans="1:7">
@@ -15373,7 +15376,7 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C543" s="1">
         <x:v>50</x:v>
@@ -15385,10 +15388,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F543" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15396,7 +15399,7 @@
         <x:v>601</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C544" s="1">
         <x:v>50</x:v>
@@ -15408,10 +15411,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">
@@ -15419,10 +15422,10 @@
         <x:v>602</x:v>
       </x:c>
       <x:c r="B545" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C545" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D545" s="1">
         <x:v>0</x:v>
@@ -15431,10 +15434,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F545" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G545" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="546" spans="1:7">
@@ -15442,10 +15445,10 @@
         <x:v>603</x:v>
       </x:c>
       <x:c r="B546" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C546" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D546" s="1">
         <x:v>0</x:v>
@@ -15454,10 +15457,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F546" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G546" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="547" spans="1:7">
@@ -15465,7 +15468,7 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C547" s="1">
         <x:v>50</x:v>
@@ -15477,10 +15480,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F547" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G547" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="548" spans="1:7">
@@ -15488,22 +15491,22 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="B548" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C548" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D548" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E548" s="1">
-        <x:v>817066</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F548" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G548" s="1">
-        <x:v>0</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="549" spans="1:7">
@@ -15511,22 +15514,22 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C549" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D549" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E549" s="1">
-        <x:v>0</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="F549" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G549" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="550" spans="1:7">
@@ -15534,7 +15537,7 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C550" s="1">
         <x:v>50</x:v>
@@ -15557,22 +15560,22 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C551" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D551" s="1">
-        <x:v>88256</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E551" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F551" s="1">
-        <x:v>14866</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>117122</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -15580,22 +15583,22 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B552" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C552" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D552" s="1">
-        <x:v>0</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="E552" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F552" s="1">
-        <x:v>0</x:v>
+        <x:v>14866</x:v>
       </x:c>
       <x:c r="G552" s="1">
-        <x:v>50</x:v>
+        <x:v>117122</x:v>
       </x:c>
     </x:row>
     <x:row r="553" spans="1:7">
@@ -15603,7 +15606,7 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B553" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C553" s="1">
         <x:v>50</x:v>
@@ -15626,7 +15629,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>612</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C554" s="1">
         <x:v>50</x:v>
@@ -15646,10 +15649,10 @@
     </x:row>
     <x:row r="555" spans="1:7">
       <x:c r="A555" s="1" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B555" s="1" t="s">
         <x:v>613</x:v>
-      </x:c>
-      <x:c r="B555" s="1" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="C555" s="1">
         <x:v>50</x:v>
@@ -15672,10 +15675,10 @@
         <x:v>614</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C556" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D556" s="1">
         <x:v>0</x:v>
@@ -15684,10 +15687,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F556" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G556" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:7">
@@ -15695,7 +15698,7 @@
         <x:v>615</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C557" s="1">
         <x:v>0</x:v>
@@ -15707,10 +15710,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F557" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G557" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="558" spans="1:7">
@@ -15721,19 +15724,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C558" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D558" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E558" s="1">
-        <x:v>10041119</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F558" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G558" s="1">
-        <x:v>50</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="559" spans="1:7">
@@ -15741,7 +15744,7 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C559" s="1">
         <x:v>50</x:v>
@@ -15750,13 +15753,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E559" s="1">
-        <x:v>0</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -15764,7 +15767,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C560" s="1">
         <x:v>50</x:v>
@@ -15776,10 +15779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F560" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G560" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="561" spans="1:7">
@@ -15787,10 +15790,10 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C561" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D561" s="1">
         <x:v>0</x:v>
@@ -15799,10 +15802,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F561" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G561" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="562" spans="1:7">
@@ -15810,10 +15813,10 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B562" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C562" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D562" s="1">
         <x:v>0</x:v>
@@ -15822,10 +15825,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F562" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G562" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="563" spans="1:7">
@@ -15833,7 +15836,7 @@
         <x:v>621</x:v>
       </x:c>
       <x:c r="B563" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C563" s="1">
         <x:v>50</x:v>
@@ -15856,7 +15859,7 @@
         <x:v>622</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C564" s="1">
         <x:v>50</x:v>
@@ -15879,10 +15882,10 @@
         <x:v>623</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C565" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D565" s="1">
         <x:v>0</x:v>
@@ -15891,10 +15894,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>-19405</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>-19405</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -15902,22 +15905,22 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D566" s="1">
-        <x:v>1491280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E566" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F566" s="1">
-        <x:v>0</x:v>
+        <x:v>-19405</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>1491280</x:v>
+        <x:v>-19405</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -15925,22 +15928,22 @@
         <x:v>625</x:v>
       </x:c>
       <x:c r="B567" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C567" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D567" s="1">
-        <x:v>0</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="E567" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F567" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G567" s="1">
-        <x:v>500</x:v>
+        <x:v>1491280</x:v>
       </x:c>
     </x:row>
     <x:row r="568" spans="1:7">
@@ -15948,10 +15951,10 @@
         <x:v>626</x:v>
       </x:c>
       <x:c r="B568" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C568" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D568" s="1">
         <x:v>0</x:v>
@@ -15960,10 +15963,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F568" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G568" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="569" spans="1:7">
@@ -15971,7 +15974,7 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C569" s="1">
         <x:v>50</x:v>
@@ -15983,10 +15986,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F569" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G569" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="570" spans="1:7">
@@ -15994,7 +15997,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>50</x:v>
@@ -16006,10 +16009,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F570" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G570" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="571" spans="1:7">
@@ -16017,7 +16020,7 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B571" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C571" s="1">
         <x:v>50</x:v>
@@ -16029,10 +16032,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F571" s="1">
-        <x:v>1287</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G571" s="1">
-        <x:v>1337</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="572" spans="1:7">
@@ -16040,10 +16043,10 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="B572" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C572" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D572" s="1">
         <x:v>0</x:v>
@@ -16052,10 +16055,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F572" s="1">
-        <x:v>6697</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>6697</x:v>
+        <x:v>1337</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -16063,10 +16066,10 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C573" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D573" s="1">
         <x:v>0</x:v>
@@ -16075,10 +16078,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F573" s="1">
-        <x:v>0</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="G573" s="1">
-        <x:v>50</x:v>
+        <x:v>6697</x:v>
       </x:c>
     </x:row>
     <x:row r="574" spans="1:7">
@@ -16086,10 +16089,10 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C574" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D574" s="1">
         <x:v>0</x:v>
@@ -16098,10 +16101,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F574" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G574" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="575" spans="1:7">
@@ -16109,7 +16112,7 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="B575" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C575" s="1">
         <x:v>0</x:v>
@@ -16121,10 +16124,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F575" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="G575" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="576" spans="1:7">
@@ -16132,10 +16135,10 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="B576" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C576" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D576" s="1">
         <x:v>0</x:v>
@@ -16144,10 +16147,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F576" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G576" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="577" spans="1:7">
@@ -16155,7 +16158,7 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B577" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C577" s="1">
         <x:v>50</x:v>
@@ -16178,7 +16181,7 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="B578" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C578" s="1">
         <x:v>50</x:v>
@@ -16201,22 +16204,22 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B579" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C579" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D579" s="1">
-        <x:v>1400000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E579" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F579" s="1">
-        <x:v>7000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G579" s="1">
-        <x:v>1409500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="580" spans="1:7">
@@ -16224,22 +16227,22 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C580" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D580" s="1">
-        <x:v>0</x:v>
+        <x:v>1400000</x:v>
       </x:c>
       <x:c r="E580" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F580" s="1">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G580" s="1">
-        <x:v>50</x:v>
+        <x:v>1409500</x:v>
       </x:c>
     </x:row>
     <x:row r="581" spans="1:7">
@@ -16247,10 +16250,10 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B581" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C581" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D581" s="1">
         <x:v>0</x:v>
@@ -16259,10 +16262,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F581" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G581" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="582" spans="1:7">
@@ -16270,10 +16273,10 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C582" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D582" s="1">
         <x:v>0</x:v>
@@ -16285,7 +16288,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G582" s="1">
-        <x:v>1550</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="583" spans="1:7">
@@ -16293,7 +16296,7 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="B583" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C583" s="1">
         <x:v>50</x:v>
@@ -16305,10 +16308,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F583" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G583" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="584" spans="1:7">
@@ -16316,7 +16319,7 @@
         <x:v>642</x:v>
       </x:c>
       <x:c r="B584" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C584" s="1">
         <x:v>50</x:v>
@@ -16339,7 +16342,7 @@
         <x:v>643</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C585" s="1">
         <x:v>50</x:v>
@@ -16362,7 +16365,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>50</x:v>
@@ -16385,7 +16388,7 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C587" s="1">
         <x:v>50</x:v>
@@ -16408,13 +16411,13 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C588" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D588" s="1">
-        <x:v>275541</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E588" s="1">
         <x:v>0</x:v>
@@ -16423,7 +16426,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G588" s="1">
-        <x:v>275541</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:7">
@@ -16431,22 +16434,22 @@
         <x:v>647</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C589" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D589" s="1">
-        <x:v>0</x:v>
+        <x:v>275541</x:v>
       </x:c>
       <x:c r="E589" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F589" s="1">
-        <x:v>81050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G589" s="1">
-        <x:v>81050</x:v>
+        <x:v>275541</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:7">
@@ -16454,10 +16457,10 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C590" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D590" s="1">
         <x:v>0</x:v>
@@ -16466,10 +16469,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F590" s="1">
-        <x:v>0</x:v>
+        <x:v>81050</x:v>
       </x:c>
       <x:c r="G590" s="1">
-        <x:v>50</x:v>
+        <x:v>81050</x:v>
       </x:c>
     </x:row>
     <x:row r="591" spans="1:7">
@@ -16477,7 +16480,7 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C591" s="1">
         <x:v>50</x:v>
@@ -16500,10 +16503,10 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C592" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D592" s="1">
         <x:v>0</x:v>
@@ -16515,7 +16518,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G592" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="593" spans="1:7">
@@ -16523,10 +16526,10 @@
         <x:v>651</x:v>
       </x:c>
       <x:c r="B593" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C593" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D593" s="1">
         <x:v>0</x:v>
@@ -16538,7 +16541,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G593" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
     </x:row>
     <x:row r="594" spans="1:7">
@@ -16546,7 +16549,7 @@
         <x:v>652</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C594" s="1">
         <x:v>50</x:v>
@@ -16558,10 +16561,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F594" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G594" s="1">
-        <x:v>14050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="595" spans="1:7">
@@ -16569,10 +16572,10 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C595" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D595" s="1">
         <x:v>0</x:v>
@@ -16581,10 +16584,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F595" s="1">
-        <x:v>2700</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G595" s="1">
-        <x:v>2700</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="596" spans="1:7">
@@ -16592,7 +16595,7 @@
         <x:v>654</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C596" s="1">
         <x:v>0</x:v>
@@ -16604,10 +16607,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F596" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G596" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="597" spans="1:7">
@@ -16615,30 +16618,30 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B597" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C597" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D597" s="1">
-        <x:v>14446984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E597" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F597" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G597" s="1">
-        <x:v>14446984</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="598" spans="1:7">
       <x:c r="A598" s="1" t="s">
-        <x:v>655</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C598" s="1">
         <x:v>0</x:v>
@@ -16661,13 +16664,13 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C599" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D599" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E599" s="1">
         <x:v>0</x:v>
@@ -16676,7 +16679,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G599" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="600" spans="1:7">
@@ -16684,22 +16687,22 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C600" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D600" s="1">
-        <x:v>2470488</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E600" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F600" s="1">
-        <x:v>11834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G600" s="1">
-        <x:v>2494372</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="601" spans="1:7">
@@ -16707,22 +16710,22 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C601" s="1">
-        <x:v>100</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="D601" s="1">
-        <x:v>0</x:v>
+        <x:v>2470488</x:v>
       </x:c>
       <x:c r="E601" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F601" s="1">
-        <x:v>0</x:v>
+        <x:v>11834</x:v>
       </x:c>
       <x:c r="G601" s="1">
-        <x:v>100</x:v>
+        <x:v>2494372</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:7">
@@ -16730,10 +16733,10 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C602" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D602" s="1">
         <x:v>0</x:v>
@@ -16745,7 +16748,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -16753,7 +16756,7 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C603" s="1">
         <x:v>50</x:v>
@@ -16779,7 +16782,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C604" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D604" s="1">
         <x:v>0</x:v>
@@ -16788,10 +16791,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F604" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G604" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="605" spans="1:7">
@@ -16799,10 +16802,10 @@
         <x:v>662</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16811,10 +16814,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>2550</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16822,7 +16825,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>50</x:v>
@@ -16834,10 +16837,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -16845,7 +16848,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>50</x:v>
@@ -16868,7 +16871,7 @@
         <x:v>665</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C608" s="1">
         <x:v>50</x:v>
@@ -16891,7 +16894,7 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B609" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C609" s="1">
         <x:v>50</x:v>
@@ -16914,22 +16917,22 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C610" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D610" s="1">
-        <x:v>3975320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E610" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F610" s="1">
-        <x:v>6634</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G610" s="1">
-        <x:v>3982954</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="611" spans="1:7">
@@ -16937,22 +16940,22 @@
         <x:v>668</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C611" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D611" s="1">
-        <x:v>0</x:v>
+        <x:v>3975320</x:v>
       </x:c>
       <x:c r="E611" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F611" s="1">
-        <x:v>22000</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G611" s="1">
-        <x:v>22000</x:v>
+        <x:v>3982954</x:v>
       </x:c>
     </x:row>
     <x:row r="612" spans="1:7">
@@ -16960,10 +16963,10 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C612" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D612" s="1">
         <x:v>0</x:v>
@@ -16972,10 +16975,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F612" s="1">
-        <x:v>5800</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G612" s="1">
-        <x:v>5850</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="613" spans="1:7">
@@ -16983,7 +16986,7 @@
         <x:v>670</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>671</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C613" s="1">
         <x:v>50</x:v>
@@ -16995,21 +16998,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F613" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G613" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:7">
       <x:c r="A614" s="1" t="s">
+        <x:v>671</x:v>
+      </x:c>
+      <x:c r="B614" s="1" t="s">
         <x:v>672</x:v>
       </x:c>
-      <x:c r="B614" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C614" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D614" s="1">
         <x:v>0</x:v>
@@ -17018,10 +17021,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F614" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G614" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="615" spans="1:7">
@@ -17029,10 +17032,10 @@
         <x:v>673</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>674</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -17041,18 +17044,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
       <x:c r="A616" s="1" t="s">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="B616" s="1" t="s">
         <x:v>675</x:v>
-      </x:c>
-      <x:c r="B616" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C616" s="1">
         <x:v>50</x:v>
@@ -17075,7 +17078,7 @@
         <x:v>676</x:v>
       </x:c>
       <x:c r="B617" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C617" s="1">
         <x:v>50</x:v>
@@ -17095,13 +17098,13 @@
     </x:row>
     <x:row r="618" spans="1:7">
       <x:c r="A618" s="1" t="s">
-        <x:v>676</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="B618" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C618" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D618" s="1">
         <x:v>0</x:v>
@@ -17110,10 +17113,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F618" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G618" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="619" spans="1:7">
@@ -17121,10 +17124,10 @@
         <x:v>677</x:v>
       </x:c>
       <x:c r="B619" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C619" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D619" s="1">
         <x:v>0</x:v>
@@ -17133,10 +17136,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F619" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G619" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="620" spans="1:7">
@@ -17144,7 +17147,7 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C620" s="1">
         <x:v>50</x:v>
@@ -17167,10 +17170,10 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C621" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D621" s="1">
         <x:v>0</x:v>
@@ -17179,10 +17182,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F621" s="1">
-        <x:v>68600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G621" s="1">
-        <x:v>71150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="622" spans="1:7">
@@ -17190,10 +17193,10 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C622" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D622" s="1">
         <x:v>0</x:v>
@@ -17202,10 +17205,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F622" s="1">
-        <x:v>0</x:v>
+        <x:v>68600</x:v>
       </x:c>
       <x:c r="G622" s="1">
-        <x:v>50</x:v>
+        <x:v>71150</x:v>
       </x:c>
     </x:row>
     <x:row r="623" spans="1:7">
@@ -17213,7 +17216,7 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C623" s="1">
         <x:v>50</x:v>
@@ -17236,10 +17239,10 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C624" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D624" s="1">
         <x:v>0</x:v>
@@ -17248,10 +17251,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F624" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G624" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="625" spans="1:7">
@@ -17259,10 +17262,10 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D625" s="1">
         <x:v>0</x:v>
@@ -17271,10 +17274,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>58000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>58050</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17282,10 +17285,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17294,10 +17297,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>1666</x:v>
+        <x:v>58000</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>3716</x:v>
+        <x:v>58050</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17305,10 +17308,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17317,10 +17320,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>1668</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>1668</x:v>
+        <x:v>3716</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -17328,10 +17331,10 @@
         <x:v>686</x:v>
       </x:c>
       <x:c r="B628" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C628" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D628" s="1">
         <x:v>0</x:v>
@@ -17340,10 +17343,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F628" s="1">
-        <x:v>0</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G628" s="1">
-        <x:v>50</x:v>
+        <x:v>1668</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:7">
@@ -17351,7 +17354,7 @@
         <x:v>687</x:v>
       </x:c>
       <x:c r="B629" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C629" s="1">
         <x:v>50</x:v>
@@ -17374,22 +17377,22 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C630" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D630" s="1">
-        <x:v>0</x:v>
+        <x:v>52520</x:v>
       </x:c>
       <x:c r="E630" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F630" s="1">
-        <x:v>30600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G630" s="1">
-        <x:v>33550</x:v>
+        <x:v>52570</x:v>
       </x:c>
     </x:row>
     <x:row r="631" spans="1:7">
@@ -17397,10 +17400,10 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>2550</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D631" s="1">
         <x:v>0</x:v>
@@ -17409,10 +17412,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>0</x:v>
+        <x:v>30600</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>2550</x:v>
+        <x:v>33550</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -17420,22 +17423,22 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E632" s="1">
-        <x:v>56045</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17452,7 +17455,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E633" s="1">
-        <x:v>0</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="F633" s="1">
         <x:v>0</x:v>
@@ -17466,10 +17469,10 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C634" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D634" s="1">
         <x:v>0</x:v>
@@ -17481,7 +17484,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G634" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="635" spans="1:7">
@@ -17489,10 +17492,10 @@
         <x:v>693</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C635" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D635" s="1">
         <x:v>0</x:v>
@@ -17504,7 +17507,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G635" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:7">
@@ -17512,10 +17515,10 @@
         <x:v>694</x:v>
       </x:c>
       <x:c r="B636" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C636" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D636" s="1">
         <x:v>0</x:v>
@@ -17524,33 +17527,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F636" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G636" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="637" spans="1:7">
       <x:c r="A637" s="1" t="s">
-        <x:v>694</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="B637" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C637" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D637" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E637" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F637" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G637" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="638" spans="1:7">
@@ -17564,7 +17567,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D638" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E638" s="1">
         <x:v>0</x:v>
@@ -17573,7 +17576,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G638" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="639" spans="1:7">
@@ -17581,13 +17584,13 @@
         <x:v>696</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C639" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D639" s="1">
-        <x:v>0</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="E639" s="1">
         <x:v>0</x:v>
@@ -17596,7 +17599,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>50</x:v>
+        <x:v>852561</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -17604,7 +17607,7 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C640" s="1">
         <x:v>50</x:v>
@@ -17627,13 +17630,13 @@
         <x:v>698</x:v>
       </x:c>
       <x:c r="B641" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C641" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D641" s="1">
-        <x:v>2200000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E641" s="1">
         <x:v>0</x:v>
@@ -17642,7 +17645,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G641" s="1">
-        <x:v>2200000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="642" spans="1:7">
@@ -17650,13 +17653,13 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C642" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D642" s="1">
-        <x:v>0</x:v>
+        <x:v>2200000</x:v>
       </x:c>
       <x:c r="E642" s="1">
         <x:v>0</x:v>
@@ -17665,7 +17668,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G642" s="1">
-        <x:v>50</x:v>
+        <x:v>2200000</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:7">
@@ -17673,7 +17676,7 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="B643" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C643" s="1">
         <x:v>50</x:v>
@@ -17696,7 +17699,7 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C644" s="1">
         <x:v>50</x:v>
@@ -17719,10 +17722,10 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D645" s="1">
         <x:v>0</x:v>
@@ -17734,7 +17737,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17742,10 +17745,10 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D646" s="1">
         <x:v>0</x:v>
@@ -17757,7 +17760,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -17765,10 +17768,10 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="B647" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C647" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D647" s="1">
         <x:v>0</x:v>
@@ -17780,7 +17783,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G647" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="648" spans="1:7">
@@ -17788,10 +17791,10 @@
         <x:v>705</x:v>
       </x:c>
       <x:c r="B648" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C648" s="1">
-        <x:v>1050</x:v>
+        <x:v>10050</x:v>
       </x:c>
       <x:c r="D648" s="1">
         <x:v>0</x:v>
@@ -17800,10 +17803,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F648" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G648" s="1">
-        <x:v>2717</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="649" spans="1:7">
@@ -17811,10 +17814,10 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B649" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C649" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D649" s="1">
         <x:v>0</x:v>
@@ -17823,10 +17826,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F649" s="1">
-        <x:v>0</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G649" s="1">
-        <x:v>50</x:v>
+        <x:v>2717</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:7">
@@ -17834,22 +17837,22 @@
         <x:v>707</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C650" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D650" s="1">
-        <x:v>111599</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E650" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F650" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G650" s="1">
-        <x:v>114899</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:7">
@@ -17857,22 +17860,22 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C651" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D651" s="1">
-        <x:v>0</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="E651" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F651" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G651" s="1">
-        <x:v>50</x:v>
+        <x:v>114899</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:7">
@@ -17880,7 +17883,7 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C652" s="1">
         <x:v>50</x:v>
@@ -17903,7 +17906,7 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C653" s="1">
         <x:v>50</x:v>
@@ -17923,39 +17926,39 @@
     </x:row>
     <x:row r="654" spans="1:7">
       <x:c r="A654" s="1" t="s">
-        <x:v>711</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C654" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D654" s="1">
-        <x:v>10046680</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="E654" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F654" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G654" s="1">
-        <x:v>10048730</x:v>
+        <x:v>113120</x:v>
       </x:c>
     </x:row>
     <x:row r="655" spans="1:7">
       <x:c r="A655" s="1" t="s">
-        <x:v>712</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C655" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D655" s="1">
-        <x:v>2263800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E655" s="1">
         <x:v>0</x:v>
@@ -17964,64 +17967,64 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G655" s="1">
-        <x:v>2263850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="656" spans="1:7">
       <x:c r="A656" s="1" t="s">
-        <x:v>713</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C656" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>0</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F656" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>50</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
       <x:c r="A657" s="1" t="s">
-        <x:v>714</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C657" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D657" s="1">
-        <x:v>0</x:v>
+        <x:v>2263800</x:v>
       </x:c>
       <x:c r="E657" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F657" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G657" s="1">
-        <x:v>5050</x:v>
+        <x:v>2263850</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:7">
       <x:c r="A658" s="1" t="s">
-        <x:v>715</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="B658" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C658" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D658" s="1">
         <x:v>0</x:v>
@@ -18030,18 +18033,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F658" s="1">
-        <x:v>52333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G658" s="1">
-        <x:v>58383</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:7">
       <x:c r="A659" s="1" t="s">
-        <x:v>716</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C659" s="1">
         <x:v>50</x:v>
@@ -18053,21 +18056,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F659" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G659" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:7">
       <x:c r="A660" s="1" t="s">
-        <x:v>717</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D660" s="1">
         <x:v>0</x:v>
@@ -18076,21 +18079,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F660" s="1">
-        <x:v>0</x:v>
+        <x:v>52333</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>50</x:v>
+        <x:v>58383</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
       <x:c r="A661" s="1" t="s">
-        <x:v>718</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
         <x:v>0</x:v>
@@ -18099,24 +18102,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F661" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
       <x:c r="A662" s="1" t="s">
-        <x:v>719</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D662" s="1">
-        <x:v>367531</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E662" s="1">
         <x:v>0</x:v>
@@ -18125,87 +18128,87 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>367531</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
       <x:c r="A663" s="1" t="s">
-        <x:v>720</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C663" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D663" s="1">
-        <x:v>817169</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E663" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F663" s="1">
-        <x:v>1668</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G663" s="1">
-        <x:v>820837</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:7">
       <x:c r="A664" s="1" t="s">
-        <x:v>721</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="B664" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C664" s="1">
-        <x:v>11050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D664" s="1">
-        <x:v>0</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="E664" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F664" s="1">
-        <x:v>6242</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G664" s="1">
-        <x:v>17292</x:v>
+        <x:v>367531</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:7">
       <x:c r="A665" s="1" t="s">
-        <x:v>722</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="B665" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C665" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D665" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E665" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F665" s="1">
-        <x:v>0</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G665" s="1">
-        <x:v>50</x:v>
+        <x:v>820837</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:7">
       <x:c r="A666" s="1" t="s">
-        <x:v>723</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="C666" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D666" s="1">
         <x:v>0</x:v>
@@ -18214,21 +18217,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F666" s="1">
-        <x:v>0</x:v>
+        <x:v>6242</x:v>
       </x:c>
       <x:c r="G666" s="1">
-        <x:v>50</x:v>
+        <x:v>17292</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:7">
       <x:c r="A667" s="1" t="s">
-        <x:v>724</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C667" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D667" s="1">
         <x:v>0</x:v>
@@ -18237,18 +18240,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F667" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G667" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:7">
       <x:c r="A668" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C668" s="1">
         <x:v>50</x:v>
@@ -18260,21 +18263,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F668" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>25050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
       <x:c r="A669" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C669" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D669" s="1">
         <x:v>0</x:v>
@@ -18283,47 +18286,47 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F669" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
       <x:c r="A670" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C670" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D670" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E670" s="1">
-        <x:v>1531015</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F670" s="1">
-        <x:v>0</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G670" s="1">
-        <x:v>0</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="671" spans="1:7">
       <x:c r="A671" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C671" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D671" s="1">
-        <x:v>105040</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E671" s="1">
         <x:v>0</x:v>
@@ -18332,44 +18335,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>105090</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">
       <x:c r="A672" s="1" t="s">
-        <x:v>729</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="B672" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C672" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D672" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E672" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F672" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G672" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="673" spans="1:7">
       <x:c r="A673" s="1" t="s">
-        <x:v>730</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="B673" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C673" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D673" s="1">
-        <x:v>5583432</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="E673" s="1">
         <x:v>0</x:v>
@@ -18378,15 +18381,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G673" s="1">
-        <x:v>5584432</x:v>
+        <x:v>157610</x:v>
       </x:c>
     </x:row>
     <x:row r="674" spans="1:7">
       <x:c r="A674" s="1" t="s">
-        <x:v>731</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C674" s="1">
         <x:v>50</x:v>
@@ -18406,36 +18409,36 @@
     </x:row>
     <x:row r="675" spans="1:7">
       <x:c r="A675" s="1" t="s">
-        <x:v>732</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C675" s="1">
-        <x:v>24050</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D675" s="1">
-        <x:v>764206</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E675" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F675" s="1">
-        <x:v>20501</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G675" s="1">
-        <x:v>808757</x:v>
+        <x:v>5584432</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:7">
       <x:c r="A676" s="1" t="s">
-        <x:v>733</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="B676" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C676" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D676" s="1">
         <x:v>0</x:v>
@@ -18444,44 +18447,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F676" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G676" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="677" spans="1:7">
       <x:c r="A677" s="1" t="s">
-        <x:v>734</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="B677" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C677" s="1">
-        <x:v>0</x:v>
+        <x:v>24050</x:v>
       </x:c>
       <x:c r="D677" s="1">
-        <x:v>1543316</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="E677" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F677" s="1">
-        <x:v>0</x:v>
+        <x:v>20501</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>1543316</x:v>
+        <x:v>808757</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
       <x:c r="A678" s="1" t="s">
-        <x:v>735</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="B678" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C678" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D678" s="1">
         <x:v>0</x:v>
@@ -18490,24 +18493,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F678" s="1">
-        <x:v>14500</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G678" s="1">
-        <x:v>14550</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="679" spans="1:7">
       <x:c r="A679" s="1" t="s">
-        <x:v>736</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C679" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D679" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E679" s="1">
         <x:v>0</x:v>
@@ -18516,15 +18519,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>50</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
       <x:c r="A680" s="1" t="s">
-        <x:v>737</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C680" s="1">
         <x:v>50</x:v>
@@ -18536,24 +18539,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>50</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
       <x:c r="A681" s="1" t="s">
-        <x:v>738</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C681" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D681" s="1">
-        <x:v>107353</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E681" s="1">
         <x:v>0</x:v>
@@ -18562,110 +18565,110 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>107403</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
       <x:c r="A682" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D682" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E682" s="1">
-        <x:v>10135449</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
       <x:c r="A683" s="1" t="s">
-        <x:v>740</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C683" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D683" s="1">
-        <x:v>0</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="E683" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>3334</x:v>
+        <x:v>107403</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
       <x:c r="A684" s="1" t="s">
-        <x:v>741</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D684" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E684" s="1">
-        <x:v>0</x:v>
+        <x:v>10135449</x:v>
       </x:c>
       <x:c r="F684" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
       <x:c r="A685" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C685" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D685" s="1">
-        <x:v>106947</x:v>
+        <x:v>51510</x:v>
       </x:c>
       <x:c r="E685" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>106947</x:v>
+        <x:v>54844</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
       <x:c r="A686" s="1" t="s">
-        <x:v>743</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D686" s="1">
         <x:v>0</x:v>
@@ -18674,41 +18677,41 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>25050</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
       <x:c r="A687" s="1" t="s">
-        <x:v>744</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C687" s="1">
-        <x:v>1050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D687" s="1">
-        <x:v>902176</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="E687" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F687" s="1">
-        <x:v>7000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>910226</x:v>
+        <x:v>106947</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
       <x:c r="A688" s="1" t="s">
-        <x:v>745</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C688" s="1">
         <x:v>50</x:v>
@@ -18720,44 +18723,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F688" s="1">
-        <x:v>25500</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>25550</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
       <x:c r="A689" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C689" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D689" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E689" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F689" s="1">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G689" s="1">
-        <x:v>50</x:v>
+        <x:v>910226</x:v>
       </x:c>
     </x:row>
     <x:row r="690" spans="1:7">
       <x:c r="A690" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D690" s="1">
         <x:v>0</x:v>
@@ -18766,21 +18769,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>10500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>10500</x:v>
+        <x:v>25550</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
       <x:c r="A691" s="1" t="s">
-        <x:v>748</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -18789,21 +18792,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>6200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>6200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
       <x:c r="A692" s="1" t="s">
-        <x:v>749</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -18812,21 +18815,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>0</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>50</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
       <x:c r="A693" s="1" t="s">
-        <x:v>750</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C693" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D693" s="1">
         <x:v>0</x:v>
@@ -18835,18 +18838,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F693" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>1000</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
       <x:c r="A694" s="1" t="s">
-        <x:v>751</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C694" s="1">
         <x:v>50</x:v>
@@ -18858,24 +18861,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F694" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>6650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
       <x:c r="A695" s="1" t="s">
-        <x:v>752</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C695" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D695" s="1">
-        <x:v>1010142</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E695" s="1">
         <x:v>0</x:v>
@@ -18884,18 +18887,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>1010142</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
       <x:c r="A696" s="1" t="s">
-        <x:v>753</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D696" s="1">
         <x:v>0</x:v>
@@ -18904,24 +18907,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>5000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>5000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
       <x:c r="A697" s="1" t="s">
-        <x:v>754</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C697" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D697" s="1">
-        <x:v>0</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="E697" s="1">
         <x:v>0</x:v>
@@ -18930,18 +18933,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>50</x:v>
+        <x:v>1010142</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">
       <x:c r="A698" s="1" t="s">
-        <x:v>755</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C698" s="1">
-        <x:v>6550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D698" s="1">
         <x:v>0</x:v>
@@ -18950,18 +18953,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F698" s="1">
-        <x:v>3300</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>9850</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
       <x:c r="A699" s="1" t="s">
-        <x:v>756</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C699" s="1">
         <x:v>50</x:v>
@@ -18981,13 +18984,13 @@
     </x:row>
     <x:row r="700" spans="1:7">
       <x:c r="A700" s="1" t="s">
-        <x:v>757</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C700" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D700" s="1">
         <x:v>0</x:v>
@@ -18996,21 +18999,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F700" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>50</x:v>
+        <x:v>9850</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
       <x:c r="A701" s="1" t="s">
-        <x:v>758</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C701" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D701" s="1">
         <x:v>0</x:v>
@@ -19019,21 +19022,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>9550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
       <x:c r="A702" s="1" t="s">
-        <x:v>759</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C702" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D702" s="1">
         <x:v>0</x:v>
@@ -19042,21 +19045,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F702" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
       <x:c r="A703" s="1" t="s">
-        <x:v>760</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C703" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D703" s="1">
         <x:v>0</x:v>
@@ -19065,21 +19068,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F703" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>50</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
       <x:c r="A704" s="1" t="s">
-        <x:v>761</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C704" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D704" s="1">
         <x:v>0</x:v>
@@ -19088,10 +19091,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>5800</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>9350</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
@@ -19099,13 +19102,13 @@
         <x:v>761</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D705" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E705" s="1">
         <x:v>0</x:v>
@@ -19114,7 +19117,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>1100000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19122,33 +19125,33 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D706" s="1">
-        <x:v>2572233</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E706" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>5500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>2577783</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
       <x:c r="A707" s="1" t="s">
-        <x:v>763</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D707" s="1">
         <x:v>0</x:v>
@@ -19157,41 +19160,41 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>50</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
       <x:c r="A708" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C708" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D708" s="1">
-        <x:v>0</x:v>
+        <x:v>2572233</x:v>
       </x:c>
       <x:c r="E708" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>5750</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>5800</x:v>
+        <x:v>2577783</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
       <x:c r="A709" s="1" t="s">
-        <x:v>765</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C709" s="1">
         <x:v>50</x:v>
@@ -19211,13 +19214,13 @@
     </x:row>
     <x:row r="710" spans="1:7">
       <x:c r="A710" s="1" t="s">
-        <x:v>766</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C710" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D710" s="1">
         <x:v>0</x:v>
@@ -19226,18 +19229,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>3300</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>3300</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
       <x:c r="A711" s="1" t="s">
-        <x:v>767</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C711" s="1">
         <x:v>50</x:v>
@@ -19257,13 +19260,13 @@
     </x:row>
     <x:row r="712" spans="1:7">
       <x:c r="A712" s="1" t="s">
-        <x:v>768</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D712" s="1">
         <x:v>0</x:v>
@@ -19272,18 +19275,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>5700</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>5750</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
       <x:c r="A713" s="1" t="s">
-        <x:v>769</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C713" s="1">
         <x:v>50</x:v>
@@ -19303,10 +19306,10 @@
     </x:row>
     <x:row r="714" spans="1:7">
       <x:c r="A714" s="1" t="s">
-        <x:v>770</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C714" s="1">
         <x:v>50</x:v>
@@ -19318,44 +19321,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>0</x:v>
+        <x:v>5700</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
       <x:c r="A715" s="1" t="s">
-        <x:v>771</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D715" s="1">
-        <x:v>1892270</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E715" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>1909770</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
       <x:c r="A716" s="1" t="s">
-        <x:v>772</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D716" s="1">
         <x:v>0</x:v>
@@ -19364,44 +19367,44 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
       <x:c r="A717" s="1" t="s">
-        <x:v>773</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D717" s="1">
-        <x:v>0</x:v>
+        <x:v>1892270</x:v>
       </x:c>
       <x:c r="E717" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>50</x:v>
+        <x:v>1909770</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
       <x:c r="A718" s="1" t="s">
-        <x:v>774</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C718" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D718" s="1">
         <x:v>0</x:v>
@@ -19410,18 +19413,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F718" s="1">
-        <x:v>1500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>3500</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
       <x:c r="A719" s="1" t="s">
-        <x:v>775</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C719" s="1">
         <x:v>50</x:v>
@@ -19441,36 +19444,36 @@
     </x:row>
     <x:row r="720" spans="1:7">
       <x:c r="A720" s="1" t="s">
-        <x:v>776</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D720" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E720" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F720" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>40000</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
       <x:c r="A721" s="1" t="s">
-        <x:v>777</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C721" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D721" s="1">
         <x:v>0</x:v>
@@ -19482,21 +19485,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
       <x:c r="A722" s="1" t="s">
-        <x:v>778</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C722" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D722" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E722" s="1">
         <x:v>0</x:v>
@@ -19505,18 +19508,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>50</x:v>
+        <x:v>40000</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
       <x:c r="A723" s="1" t="s">
-        <x:v>779</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D723" s="1">
         <x:v>0</x:v>
@@ -19525,18 +19528,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F723" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>5200</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
       <x:c r="A724" s="1" t="s">
-        <x:v>780</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C724" s="1">
         <x:v>50</x:v>
@@ -19556,13 +19559,13 @@
     </x:row>
     <x:row r="725" spans="1:7">
       <x:c r="A725" s="1" t="s">
-        <x:v>781</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D725" s="1">
         <x:v>0</x:v>
@@ -19571,18 +19574,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F725" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
       <x:c r="A726" s="1" t="s">
-        <x:v>782</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C726" s="1">
         <x:v>50</x:v>
@@ -19594,24 +19597,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F726" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
       <x:c r="A727" s="1" t="s">
-        <x:v>783</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D727" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E727" s="1">
         <x:v>0</x:v>
@@ -19620,15 +19623,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>3920589</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
       <x:c r="A728" s="1" t="s">
-        <x:v>784</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C728" s="1">
         <x:v>50</x:v>
@@ -19640,24 +19643,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
       <x:c r="A729" s="1" t="s">
-        <x:v>785</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C729" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D729" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E729" s="1">
         <x:v>0</x:v>
@@ -19666,15 +19669,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>1000</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">
       <x:c r="A730" s="1" t="s">
-        <x:v>786</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C730" s="1">
         <x:v>50</x:v>
@@ -19694,13 +19697,13 @@
     </x:row>
     <x:row r="731" spans="1:7">
       <x:c r="A731" s="1" t="s">
-        <x:v>787</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C731" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D731" s="1">
         <x:v>0</x:v>
@@ -19712,18 +19715,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
       <x:c r="A732" s="1" t="s">
-        <x:v>788</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C732" s="1">
-        <x:v>4500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D732" s="1">
         <x:v>0</x:v>
@@ -19732,21 +19735,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F732" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>9334</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
       <x:c r="A733" s="1" t="s">
-        <x:v>789</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C733" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D733" s="1">
         <x:v>0</x:v>
@@ -19758,18 +19761,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G733" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:7">
       <x:c r="A734" s="1" t="s">
-        <x:v>790</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C734" s="1">
-        <x:v>50</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D734" s="1">
         <x:v>0</x:v>
@@ -19778,21 +19781,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F734" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G734" s="1">
-        <x:v>50</x:v>
+        <x:v>9334</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:7">
       <x:c r="A735" s="1" t="s">
-        <x:v>791</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19804,21 +19807,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
       <x:c r="A736" s="1" t="s">
-        <x:v>792</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D736" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E736" s="1">
         <x:v>0</x:v>
@@ -19827,15 +19830,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
       <x:c r="A737" s="1" t="s">
-        <x:v>793</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C737" s="1">
         <x:v>50</x:v>
@@ -19855,33 +19858,33 @@
     </x:row>
     <x:row r="738" spans="1:7">
       <x:c r="A738" s="1" t="s">
-        <x:v>794</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C738" s="1">
-        <x:v>19600</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D738" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E738" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F738" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>36600</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
       <x:c r="A739" s="1" t="s">
-        <x:v>795</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C739" s="1">
         <x:v>50</x:v>
@@ -19901,13 +19904,13 @@
     </x:row>
     <x:row r="740" spans="1:7">
       <x:c r="A740" s="1" t="s">
-        <x:v>796</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>50</x:v>
+        <x:v>19600</x:v>
       </x:c>
       <x:c r="D740" s="1">
         <x:v>0</x:v>
@@ -19916,18 +19919,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F740" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>50</x:v>
+        <x:v>36600</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
       <x:c r="A741" s="1" t="s">
-        <x:v>797</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C741" s="1">
         <x:v>50</x:v>
@@ -19947,16 +19950,16 @@
     </x:row>
     <x:row r="742" spans="1:7">
       <x:c r="A742" s="1" t="s">
-        <x:v>798</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C742" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D742" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E742" s="1">
         <x:v>0</x:v>
@@ -19965,15 +19968,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
       <x:c r="A743" s="1" t="s">
-        <x:v>799</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C743" s="1">
         <x:v>50</x:v>
@@ -19993,33 +19996,33 @@
     </x:row>
     <x:row r="744" spans="1:7">
       <x:c r="A744" s="1" t="s">
-        <x:v>800</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C744" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D744" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E744" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F744" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G744" s="1">
-        <x:v>30000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:7">
       <x:c r="A745" s="1" t="s">
-        <x:v>801</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C745" s="1">
         <x:v>50</x:v>
@@ -20039,13 +20042,13 @@
     </x:row>
     <x:row r="746" spans="1:7">
       <x:c r="A746" s="1" t="s">
-        <x:v>802</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>19050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D746" s="1">
         <x:v>0</x:v>
@@ -20054,21 +20057,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>2500</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>21550</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
       <x:c r="A747" s="1" t="s">
-        <x:v>803</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D747" s="1">
         <x:v>0</x:v>
@@ -20080,18 +20083,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">
       <x:c r="A748" s="1" t="s">
-        <x:v>804</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>50</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D748" s="1">
         <x:v>0</x:v>
@@ -20100,10 +20103,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F748" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>50</x:v>
+        <x:v>21550</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
@@ -20111,10 +20114,10 @@
         <x:v>804</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C749" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D749" s="1">
         <x:v>0</x:v>
@@ -20123,10 +20126,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F749" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G749" s="1">
-        <x:v>35</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:7">
@@ -20134,10 +20137,10 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20146,21 +20149,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F750" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
       <x:c r="A751" s="1" t="s">
-        <x:v>806</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20172,15 +20175,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
       <x:c r="A752" s="1" t="s">
-        <x:v>807</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C752" s="1">
         <x:v>50</x:v>
@@ -20200,13 +20203,13 @@
     </x:row>
     <x:row r="753" spans="1:7">
       <x:c r="A753" s="1" t="s">
-        <x:v>808</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>0</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20215,18 +20218,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>1000</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
       <x:c r="A754" s="1" t="s">
-        <x:v>809</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C754" s="1">
         <x:v>50</x:v>
@@ -20238,21 +20241,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F754" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
       <x:c r="A755" s="1" t="s">
-        <x:v>810</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -20261,21 +20264,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F755" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
       <x:c r="A756" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C756" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D756" s="1">
         <x:v>0</x:v>
@@ -20284,18 +20287,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F756" s="1">
-        <x:v>13200</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>13200</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">
       <x:c r="A757" s="1" t="s">
-        <x:v>812</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C757" s="1">
         <x:v>50</x:v>
@@ -20315,13 +20318,13 @@
     </x:row>
     <x:row r="758" spans="1:7">
       <x:c r="A758" s="1" t="s">
-        <x:v>813</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20330,24 +20333,24 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
       <x:c r="A759" s="1" t="s">
-        <x:v>814</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C759" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D759" s="1">
-        <x:v>943006</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E759" s="1">
         <x:v>0</x:v>
@@ -20356,15 +20359,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>943056</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
       <x:c r="A760" s="1" t="s">
-        <x:v>815</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C760" s="1">
         <x:v>50</x:v>
@@ -20384,16 +20387,16 @@
     </x:row>
     <x:row r="761" spans="1:7">
       <x:c r="A761" s="1" t="s">
-        <x:v>816</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C761" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D761" s="1">
-        <x:v>0</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="E761" s="1">
         <x:v>0</x:v>
@@ -20402,38 +20405,38 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>50</x:v>
+        <x:v>943056</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">
       <x:c r="A762" s="1" t="s">
-        <x:v>817</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C762" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D762" s="1">
-        <x:v>476254</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E762" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F762" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>478754</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">
       <x:c r="A763" s="1" t="s">
-        <x:v>818</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C763" s="1">
         <x:v>50</x:v>
@@ -20453,36 +20456,36 @@
     </x:row>
     <x:row r="764" spans="1:7">
       <x:c r="A764" s="1" t="s">
-        <x:v>819</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C764" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D764" s="1">
-        <x:v>0</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="E764" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F764" s="1">
-        <x:v>4999</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G764" s="1">
-        <x:v>5049</x:v>
+        <x:v>478754</x:v>
       </x:c>
     </x:row>
     <x:row r="765" spans="1:7">
       <x:c r="A765" s="1" t="s">
-        <x:v>820</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C765" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D765" s="1">
         <x:v>0</x:v>
@@ -20491,18 +20494,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F765" s="1">
-        <x:v>16500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G765" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="766" spans="1:7">
       <x:c r="A766" s="1" t="s">
-        <x:v>821</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C766" s="1">
         <x:v>50</x:v>
@@ -20514,21 +20517,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>0</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>50</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
       <x:c r="A767" s="1" t="s">
-        <x:v>822</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C767" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D767" s="1">
         <x:v>0</x:v>
@@ -20537,18 +20540,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F767" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G767" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:7">
       <x:c r="A768" s="1" t="s">
-        <x:v>823</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C768" s="1">
         <x:v>50</x:v>
@@ -20568,10 +20571,10 @@
     </x:row>
     <x:row r="769" spans="1:7">
       <x:c r="A769" s="1" t="s">
-        <x:v>824</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C769" s="1">
         <x:v>50</x:v>
@@ -20591,10 +20594,10 @@
     </x:row>
     <x:row r="770" spans="1:7">
       <x:c r="A770" s="1" t="s">
-        <x:v>825</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C770" s="1">
         <x:v>50</x:v>
@@ -20606,18 +20609,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F770" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G770" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="771" spans="1:7">
       <x:c r="A771" s="1" t="s">
-        <x:v>826</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C771" s="1">
         <x:v>50</x:v>
@@ -20637,13 +20640,13 @@
     </x:row>
     <x:row r="772" spans="1:7">
       <x:c r="A772" s="1" t="s">
-        <x:v>827</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C772" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D772" s="1">
         <x:v>0</x:v>
@@ -20652,21 +20655,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F772" s="1">
-        <x:v>37300</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G772" s="1">
-        <x:v>48150</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="773" spans="1:7">
       <x:c r="A773" s="1" t="s">
-        <x:v>828</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C773" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D773" s="1">
         <x:v>0</x:v>
@@ -20675,21 +20678,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F773" s="1">
-        <x:v>83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G773" s="1">
-        <x:v>83</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="774" spans="1:7">
       <x:c r="A774" s="1" t="s">
-        <x:v>829</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C774" s="1">
-        <x:v>50</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D774" s="1">
         <x:v>0</x:v>
@@ -20698,21 +20701,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F774" s="1">
-        <x:v>0</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G774" s="1">
-        <x:v>50</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:7">
       <x:c r="A775" s="1" t="s">
-        <x:v>830</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C775" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D775" s="1">
         <x:v>0</x:v>
@@ -20721,18 +20724,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
       <x:c r="A776" s="1" t="s">
-        <x:v>831</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C776" s="1">
         <x:v>50</x:v>
@@ -20752,13 +20755,13 @@
     </x:row>
     <x:row r="777" spans="1:7">
       <x:c r="A777" s="1" t="s">
-        <x:v>832</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C777" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D777" s="1">
         <x:v>0</x:v>
@@ -20767,32 +20770,78 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F777" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G777" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="778" spans="1:7">
       <x:c r="A778" s="1" t="s">
+        <x:v>832</x:v>
+      </x:c>
+      <x:c r="B778" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C778" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D778" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E778" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F778" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G778" s="1">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="779" spans="1:7">
+      <x:c r="A779" s="1" t="s">
         <x:v>833</x:v>
       </x:c>
-      <x:c r="B778" s="1" t="s">
+      <x:c r="B779" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C779" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D779" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E779" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F779" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G779" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="780" spans="1:7">
+      <x:c r="A780" s="1" t="s">
+        <x:v>834</x:v>
+      </x:c>
+      <x:c r="B780" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C778" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D778" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E778" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F778" s="1">
+      <x:c r="C780" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D780" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E780" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F780" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G778" s="1">
+      <x:c r="G780" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -8982,13 +8982,13 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="B265" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C265" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D265" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E265" s="1">
         <x:v>0</x:v>
@@ -8997,7 +8997,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G265" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="266" spans="1:7">
@@ -9005,13 +9005,13 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="B266" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C266" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D266" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E266" s="1">
         <x:v>0</x:v>
@@ -9020,7 +9020,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G266" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="267" spans="1:7">
@@ -16641,7 +16641,7 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C598" s="1">
         <x:v>0</x:v>
@@ -16664,7 +16664,7 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C599" s="1">
         <x:v>0</x:v>
@@ -19125,22 +19125,22 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D706" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E706" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -19148,22 +19148,22 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D707" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E707" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>9350</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
@@ -20137,10 +20137,10 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20149,10 +20149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F750" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
@@ -20160,10 +20160,10 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20172,10 +20172,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F751" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -1568,6 +1568,9 @@
   </x:si>
   <x:si>
     <x:t>MCKINNEY, AMANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, DONAVAN</x:t>
   </x:si>
   <x:si>
     <x:t>MCMORRIS RODGERS, CATHY</x:t>
@@ -2589,8 +2592,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G780" totalsRowShown="0">
-  <x:autoFilter ref="A1:G780"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G781" totalsRowShown="0">
+  <x:autoFilter ref="A1:G781"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2892,7 +2895,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G780"/>
+  <x:dimension ref="A1:G781"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -13513,22 +13516,22 @@
         <x:v>518</x:v>
       </x:c>
       <x:c r="B462" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C462" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D462" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E462" s="1">
-        <x:v>0</x:v>
+        <x:v>54570</x:v>
       </x:c>
       <x:c r="F462" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G462" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="463" spans="1:7">
@@ -13536,10 +13539,10 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="B463" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C463" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D463" s="1">
         <x:v>0</x:v>
@@ -13548,10 +13551,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F463" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G463" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="464" spans="1:7">
@@ -13559,10 +13562,10 @@
         <x:v>520</x:v>
       </x:c>
       <x:c r="B464" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C464" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D464" s="1">
         <x:v>0</x:v>
@@ -13571,10 +13574,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F464" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G464" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="465" spans="1:7">
@@ -13582,7 +13585,7 @@
         <x:v>521</x:v>
       </x:c>
       <x:c r="B465" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C465" s="1">
         <x:v>50</x:v>
@@ -13594,10 +13597,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F465" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G465" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="466" spans="1:7">
@@ -13605,22 +13608,22 @@
         <x:v>522</x:v>
       </x:c>
       <x:c r="B466" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C466" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D466" s="1">
-        <x:v>923885</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E466" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F466" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G466" s="1">
-        <x:v>923885</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="467" spans="1:7">
@@ -13628,13 +13631,13 @@
         <x:v>523</x:v>
       </x:c>
       <x:c r="B467" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C467" s="1">
-        <x:v>1050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D467" s="1">
-        <x:v>92320</x:v>
+        <x:v>923885</x:v>
       </x:c>
       <x:c r="E467" s="1">
         <x:v>0</x:v>
@@ -13643,7 +13646,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G467" s="1">
-        <x:v>93370</x:v>
+        <x:v>923885</x:v>
       </x:c>
     </x:row>
     <x:row r="468" spans="1:7">
@@ -13651,13 +13654,13 @@
         <x:v>524</x:v>
       </x:c>
       <x:c r="B468" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C468" s="1">
-        <x:v>0</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D468" s="1">
-        <x:v>6471279</x:v>
+        <x:v>92320</x:v>
       </x:c>
       <x:c r="E468" s="1">
         <x:v>0</x:v>
@@ -13666,7 +13669,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G468" s="1">
-        <x:v>6471279</x:v>
+        <x:v>93370</x:v>
       </x:c>
     </x:row>
     <x:row r="469" spans="1:7">
@@ -13674,13 +13677,13 @@
         <x:v>525</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C469" s="1">
-        <x:v>1550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D469" s="1">
-        <x:v>512918</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="E469" s="1">
         <x:v>0</x:v>
@@ -13689,7 +13692,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G469" s="1">
-        <x:v>514468</x:v>
+        <x:v>6471279</x:v>
       </x:c>
     </x:row>
     <x:row r="470" spans="1:7">
@@ -13697,13 +13700,13 @@
         <x:v>526</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C470" s="1">
         <x:v>1550</x:v>
       </x:c>
       <x:c r="D470" s="1">
-        <x:v>0</x:v>
+        <x:v>512918</x:v>
       </x:c>
       <x:c r="E470" s="1">
         <x:v>0</x:v>
@@ -13712,7 +13715,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G470" s="1">
-        <x:v>1550</x:v>
+        <x:v>514468</x:v>
       </x:c>
     </x:row>
     <x:row r="471" spans="1:7">
@@ -13720,10 +13723,10 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C471" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D471" s="1">
         <x:v>0</x:v>
@@ -13735,7 +13738,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G471" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="472" spans="1:7">
@@ -13743,13 +13746,13 @@
         <x:v>528</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C472" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D472" s="1">
-        <x:v>504020</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E472" s="1">
         <x:v>0</x:v>
@@ -13758,7 +13761,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G472" s="1">
-        <x:v>504020</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="473" spans="1:7">
@@ -13766,13 +13769,13 @@
         <x:v>529</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C473" s="1">
-        <x:v>4050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D473" s="1">
-        <x:v>0</x:v>
+        <x:v>504020</x:v>
       </x:c>
       <x:c r="E473" s="1">
         <x:v>0</x:v>
@@ -13781,7 +13784,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G473" s="1">
-        <x:v>4050</x:v>
+        <x:v>504020</x:v>
       </x:c>
     </x:row>
     <x:row r="474" spans="1:7">
@@ -13789,10 +13792,10 @@
         <x:v>530</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C474" s="1">
-        <x:v>50</x:v>
+        <x:v>4050</x:v>
       </x:c>
       <x:c r="D474" s="1">
         <x:v>0</x:v>
@@ -13804,7 +13807,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G474" s="1">
-        <x:v>50</x:v>
+        <x:v>4050</x:v>
       </x:c>
     </x:row>
     <x:row r="475" spans="1:7">
@@ -13812,7 +13815,7 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B475" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C475" s="1">
         <x:v>50</x:v>
@@ -13835,10 +13838,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B476" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C476" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D476" s="1">
         <x:v>0</x:v>
@@ -13847,10 +13850,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F476" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G476" s="1">
-        <x:v>3667</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="477" spans="1:7">
@@ -13858,22 +13861,22 @@
         <x:v>533</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C477" s="1">
-        <x:v>500</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D477" s="1">
-        <x:v>107940</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E477" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F477" s="1">
-        <x:v>1500</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G477" s="1">
-        <x:v>109940</x:v>
+        <x:v>3667</x:v>
       </x:c>
     </x:row>
     <x:row r="478" spans="1:7">
@@ -13881,22 +13884,22 @@
         <x:v>534</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D478" s="1">
-        <x:v>0</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="E478" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>50</x:v>
+        <x:v>109940</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -13904,10 +13907,10 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -13916,10 +13919,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>6200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>7200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -13927,10 +13930,10 @@
         <x:v>536</x:v>
       </x:c>
       <x:c r="B480" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C480" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D480" s="1">
         <x:v>0</x:v>
@@ -13939,10 +13942,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F480" s="1">
-        <x:v>2000</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G480" s="1">
-        <x:v>2000</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="481" spans="1:7">
@@ -13950,10 +13953,10 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="B481" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C481" s="1">
-        <x:v>5050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D481" s="1">
         <x:v>0</x:v>
@@ -13962,10 +13965,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F481" s="1">
-        <x:v>1000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G481" s="1">
-        <x:v>6050</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="482" spans="1:7">
@@ -13973,10 +13976,10 @@
         <x:v>538</x:v>
       </x:c>
       <x:c r="B482" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C482" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D482" s="1">
         <x:v>0</x:v>
@@ -13985,10 +13988,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F482" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G482" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
     </x:row>
     <x:row r="483" spans="1:7">
@@ -13996,13 +13999,13 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="B483" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C483" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D483" s="1">
-        <x:v>400022</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E483" s="1">
         <x:v>0</x:v>
@@ -14011,7 +14014,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G483" s="1">
-        <x:v>401022</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="484" spans="1:7">
@@ -14019,22 +14022,22 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="B484" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C484" s="1">
-        <x:v>3500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D484" s="1">
-        <x:v>44693946</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="E484" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F484" s="1">
-        <x:v>8000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G484" s="1">
-        <x:v>44705446</x:v>
+        <x:v>401022</x:v>
       </x:c>
     </x:row>
     <x:row r="485" spans="1:7">
@@ -14042,22 +14045,22 @@
         <x:v>541</x:v>
       </x:c>
       <x:c r="B485" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C485" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D485" s="1">
-        <x:v>0</x:v>
+        <x:v>44693946</x:v>
       </x:c>
       <x:c r="E485" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F485" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G485" s="1">
-        <x:v>50</x:v>
+        <x:v>44705446</x:v>
       </x:c>
     </x:row>
     <x:row r="486" spans="1:7">
@@ -14065,13 +14068,13 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C486" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D486" s="1">
-        <x:v>726377</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E486" s="1">
         <x:v>0</x:v>
@@ -14080,7 +14083,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G486" s="1">
-        <x:v>726377</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="487" spans="1:7">
@@ -14088,22 +14091,22 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="B487" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C487" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D487" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="E487" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F487" s="1">
-        <x:v>7600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G487" s="1">
-        <x:v>678549</x:v>
+        <x:v>726377</x:v>
       </x:c>
     </x:row>
     <x:row r="488" spans="1:7">
@@ -14111,22 +14114,22 @@
         <x:v>544</x:v>
       </x:c>
       <x:c r="B488" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C488" s="1">
-        <x:v>1000</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D488" s="1">
-        <x:v>0</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="E488" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F488" s="1">
-        <x:v>0</x:v>
+        <x:v>7600</x:v>
       </x:c>
       <x:c r="G488" s="1">
-        <x:v>1000</x:v>
+        <x:v>678549</x:v>
       </x:c>
     </x:row>
     <x:row r="489" spans="1:7">
@@ -14134,10 +14137,10 @@
         <x:v>545</x:v>
       </x:c>
       <x:c r="B489" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C489" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D489" s="1">
         <x:v>0</x:v>
@@ -14146,10 +14149,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F489" s="1">
-        <x:v>1250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G489" s="1">
-        <x:v>1300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="490" spans="1:7">
@@ -14157,7 +14160,7 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="B490" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C490" s="1">
         <x:v>50</x:v>
@@ -14169,10 +14172,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F490" s="1">
-        <x:v>0</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="G490" s="1">
-        <x:v>50</x:v>
+        <x:v>1300</x:v>
       </x:c>
     </x:row>
     <x:row r="491" spans="1:7">
@@ -14180,13 +14183,13 @@
         <x:v>547</x:v>
       </x:c>
       <x:c r="B491" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C491" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D491" s="1">
-        <x:v>120404787</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E491" s="1">
         <x:v>0</x:v>
@@ -14195,7 +14198,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G491" s="1">
-        <x:v>120406787</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="492" spans="1:7">
@@ -14203,13 +14206,13 @@
         <x:v>548</x:v>
       </x:c>
       <x:c r="B492" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C492" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D492" s="1">
-        <x:v>442806</x:v>
+        <x:v>120404787</x:v>
       </x:c>
       <x:c r="E492" s="1">
         <x:v>0</x:v>
@@ -14218,7 +14221,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G492" s="1">
-        <x:v>442806</x:v>
+        <x:v>120406787</x:v>
       </x:c>
     </x:row>
     <x:row r="493" spans="1:7">
@@ -14226,22 +14229,22 @@
         <x:v>549</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C493" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D493" s="1">
-        <x:v>0</x:v>
+        <x:v>442806</x:v>
       </x:c>
       <x:c r="E493" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F493" s="1">
-        <x:v>3333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G493" s="1">
-        <x:v>4333</x:v>
+        <x:v>442806</x:v>
       </x:c>
     </x:row>
     <x:row r="494" spans="1:7">
@@ -14249,10 +14252,10 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="B494" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C494" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D494" s="1">
         <x:v>0</x:v>
@@ -14261,10 +14264,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F494" s="1">
-        <x:v>0</x:v>
+        <x:v>3333</x:v>
       </x:c>
       <x:c r="G494" s="1">
-        <x:v>50</x:v>
+        <x:v>4333</x:v>
       </x:c>
     </x:row>
     <x:row r="495" spans="1:7">
@@ -14272,7 +14275,7 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B495" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C495" s="1">
         <x:v>50</x:v>
@@ -14295,10 +14298,10 @@
         <x:v>552</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C496" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D496" s="1">
         <x:v>0</x:v>
@@ -14310,7 +14313,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G496" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="497" spans="1:7">
@@ -14318,10 +14321,10 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B497" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C497" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D497" s="1">
         <x:v>0</x:v>
@@ -14330,10 +14333,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F497" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G497" s="1">
-        <x:v>1050</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="498" spans="1:7">
@@ -14341,10 +14344,10 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="B498" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C498" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D498" s="1">
         <x:v>0</x:v>
@@ -14353,10 +14356,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F498" s="1">
-        <x:v>2700</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G498" s="1">
-        <x:v>5400</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="499" spans="1:7">
@@ -14364,10 +14367,10 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B499" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C499" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D499" s="1">
         <x:v>0</x:v>
@@ -14376,10 +14379,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F499" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G499" s="1">
-        <x:v>50</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="500" spans="1:7">
@@ -14387,7 +14390,7 @@
         <x:v>556</x:v>
       </x:c>
       <x:c r="B500" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C500" s="1">
         <x:v>50</x:v>
@@ -14399,10 +14402,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F500" s="1">
-        <x:v>12000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G500" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="501" spans="1:7">
@@ -14410,7 +14413,7 @@
         <x:v>557</x:v>
       </x:c>
       <x:c r="B501" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C501" s="1">
         <x:v>50</x:v>
@@ -14422,10 +14425,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F501" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G501" s="1">
-        <x:v>50</x:v>
+        <x:v>12050</x:v>
       </x:c>
     </x:row>
     <x:row r="502" spans="1:7">
@@ -14433,10 +14436,10 @@
         <x:v>558</x:v>
       </x:c>
       <x:c r="B502" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C502" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D502" s="1">
         <x:v>0</x:v>
@@ -14445,10 +14448,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F502" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G502" s="1">
-        <x:v>250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="503" spans="1:7">
@@ -14456,10 +14459,10 @@
         <x:v>559</x:v>
       </x:c>
       <x:c r="B503" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C503" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D503" s="1">
         <x:v>0</x:v>
@@ -14468,10 +14471,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F503" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G503" s="1">
-        <x:v>50</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="504" spans="1:7">
@@ -14479,7 +14482,7 @@
         <x:v>560</x:v>
       </x:c>
       <x:c r="B504" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C504" s="1">
         <x:v>50</x:v>
@@ -14491,10 +14494,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F504" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G504" s="1">
-        <x:v>2750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="505" spans="1:7">
@@ -14502,10 +14505,10 @@
         <x:v>561</x:v>
       </x:c>
       <x:c r="B505" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C505" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D505" s="1">
         <x:v>0</x:v>
@@ -14514,10 +14517,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F505" s="1">
-        <x:v>4600</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G505" s="1">
-        <x:v>4600</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="506" spans="1:7">
@@ -14525,10 +14528,10 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B506" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C506" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D506" s="1">
         <x:v>0</x:v>
@@ -14537,10 +14540,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F506" s="1">
-        <x:v>0</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G506" s="1">
-        <x:v>50</x:v>
+        <x:v>4600</x:v>
       </x:c>
     </x:row>
     <x:row r="507" spans="1:7">
@@ -14548,7 +14551,7 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C507" s="1">
         <x:v>50</x:v>
@@ -14571,7 +14574,7 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="B508" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C508" s="1">
         <x:v>50</x:v>
@@ -14594,7 +14597,7 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C509" s="1">
         <x:v>50</x:v>
@@ -14617,13 +14620,13 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="B510" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C510" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D510" s="1">
-        <x:v>282526</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E510" s="1">
         <x:v>0</x:v>
@@ -14632,7 +14635,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G510" s="1">
-        <x:v>282526</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="511" spans="1:7">
@@ -14640,22 +14643,22 @@
         <x:v>567</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C511" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D511" s="1">
-        <x:v>0</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E511" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F511" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G511" s="1">
-        <x:v>1000</x:v>
+        <x:v>282526</x:v>
       </x:c>
     </x:row>
     <x:row r="512" spans="1:7">
@@ -14663,10 +14666,10 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="B512" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C512" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D512" s="1">
         <x:v>0</x:v>
@@ -14675,10 +14678,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F512" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G512" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="513" spans="1:7">
@@ -14686,22 +14689,22 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C513" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D513" s="1">
-        <x:v>116161</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E513" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F513" s="1">
-        <x:v>4500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G513" s="1">
-        <x:v>124661</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="514" spans="1:7">
@@ -14709,22 +14712,22 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="B514" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C514" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D514" s="1">
-        <x:v>0</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="E514" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F514" s="1">
-        <x:v>0</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G514" s="1">
-        <x:v>50</x:v>
+        <x:v>124661</x:v>
       </x:c>
     </x:row>
     <x:row r="515" spans="1:7">
@@ -14732,7 +14735,7 @@
         <x:v>571</x:v>
       </x:c>
       <x:c r="B515" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C515" s="1">
         <x:v>50</x:v>
@@ -14755,7 +14758,7 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="B516" s="1" t="s">
-        <x:v>573</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C516" s="1">
         <x:v>50</x:v>
@@ -14775,10 +14778,10 @@
     </x:row>
     <x:row r="517" spans="1:7">
       <x:c r="A517" s="1" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="B517" s="1" t="s">
         <x:v>574</x:v>
-      </x:c>
-      <x:c r="B517" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C517" s="1">
         <x:v>50</x:v>
@@ -14801,22 +14804,22 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C518" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D518" s="1">
-        <x:v>2997852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E518" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F518" s="1">
-        <x:v>6800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G518" s="1">
-        <x:v>3006652</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="519" spans="1:7">
@@ -14824,22 +14827,22 @@
         <x:v>576</x:v>
       </x:c>
       <x:c r="B519" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C519" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D519" s="1">
-        <x:v>14446984</x:v>
+        <x:v>2997852</x:v>
       </x:c>
       <x:c r="E519" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F519" s="1">
-        <x:v>0</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="G519" s="1">
-        <x:v>14446984</x:v>
+        <x:v>3006652</x:v>
       </x:c>
     </x:row>
     <x:row r="520" spans="1:7">
@@ -14847,13 +14850,13 @@
         <x:v>577</x:v>
       </x:c>
       <x:c r="B520" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C520" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D520" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E520" s="1">
         <x:v>0</x:v>
@@ -14862,7 +14865,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G520" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="521" spans="1:7">
@@ -14870,10 +14873,10 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B521" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C521" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D521" s="1">
         <x:v>0</x:v>
@@ -14882,10 +14885,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F521" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G521" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="522" spans="1:7">
@@ -14893,7 +14896,7 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C522" s="1">
         <x:v>0</x:v>
@@ -14905,10 +14908,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F522" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="G522" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="523" spans="1:7">
@@ -14916,10 +14919,10 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B523" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C523" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D523" s="1">
         <x:v>0</x:v>
@@ -14928,10 +14931,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F523" s="1">
-        <x:v>0</x:v>
+        <x:v>22334</x:v>
       </x:c>
       <x:c r="G523" s="1">
-        <x:v>50</x:v>
+        <x:v>22334</x:v>
       </x:c>
     </x:row>
     <x:row r="524" spans="1:7">
@@ -14939,10 +14942,10 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C524" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D524" s="1">
         <x:v>0</x:v>
@@ -14951,10 +14954,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F524" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -14962,10 +14965,10 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C525" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D525" s="1">
         <x:v>0</x:v>
@@ -14974,10 +14977,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F525" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G525" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:7">
@@ -14985,13 +14988,13 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C526" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D526" s="1">
-        <x:v>209387</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E526" s="1">
         <x:v>0</x:v>
@@ -15000,7 +15003,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G526" s="1">
-        <x:v>209387</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="527" spans="1:7">
@@ -15008,13 +15011,13 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B527" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C527" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D527" s="1">
-        <x:v>0</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="E527" s="1">
         <x:v>0</x:v>
@@ -15023,7 +15026,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G527" s="1">
-        <x:v>50</x:v>
+        <x:v>209387</x:v>
       </x:c>
     </x:row>
     <x:row r="528" spans="1:7">
@@ -15031,13 +15034,13 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="B528" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C528" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D528" s="1">
-        <x:v>257695</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E528" s="1">
         <x:v>0</x:v>
@@ -15046,7 +15049,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G528" s="1">
-        <x:v>257695</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="529" spans="1:7">
@@ -15054,22 +15057,22 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C529" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D529" s="1">
-        <x:v>0</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="E529" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F529" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G529" s="1">
-        <x:v>3300</x:v>
+        <x:v>257695</x:v>
       </x:c>
     </x:row>
     <x:row r="530" spans="1:7">
@@ -15077,10 +15080,10 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="B530" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C530" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D530" s="1">
         <x:v>0</x:v>
@@ -15089,10 +15092,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F530" s="1">
-        <x:v>29800</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G530" s="1">
-        <x:v>34800</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="531" spans="1:7">
@@ -15100,10 +15103,10 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="B531" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C531" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D531" s="1">
         <x:v>0</x:v>
@@ -15112,10 +15115,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F531" s="1">
-        <x:v>0</x:v>
+        <x:v>29800</x:v>
       </x:c>
       <x:c r="G531" s="1">
-        <x:v>50</x:v>
+        <x:v>34800</x:v>
       </x:c>
     </x:row>
     <x:row r="532" spans="1:7">
@@ -15123,7 +15126,7 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C532" s="1">
         <x:v>50</x:v>
@@ -15135,10 +15138,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F532" s="1">
-        <x:v>5600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G532" s="1">
-        <x:v>5650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="533" spans="1:7">
@@ -15146,10 +15149,10 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C533" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D533" s="1">
         <x:v>0</x:v>
@@ -15158,10 +15161,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F533" s="1">
-        <x:v>0</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G533" s="1">
-        <x:v>2050</x:v>
+        <x:v>5650</x:v>
       </x:c>
     </x:row>
     <x:row r="534" spans="1:7">
@@ -15169,10 +15172,10 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="B534" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C534" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D534" s="1">
         <x:v>0</x:v>
@@ -15181,10 +15184,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F534" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G534" s="1">
-        <x:v>3384</x:v>
+        <x:v>2050</x:v>
       </x:c>
     </x:row>
     <x:row r="535" spans="1:7">
@@ -15192,7 +15195,7 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B535" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C535" s="1">
         <x:v>50</x:v>
@@ -15204,10 +15207,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F535" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G535" s="1">
-        <x:v>50</x:v>
+        <x:v>3384</x:v>
       </x:c>
     </x:row>
     <x:row r="536" spans="1:7">
@@ -15215,22 +15218,22 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C536" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D536" s="1">
-        <x:v>558813</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E536" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F536" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G536" s="1">
-        <x:v>559813</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="537" spans="1:7">
@@ -15238,22 +15241,22 @@
         <x:v>594</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C537" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D537" s="1">
-        <x:v>0</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E537" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F537" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G537" s="1">
-        <x:v>6650</x:v>
+        <x:v>559813</x:v>
       </x:c>
     </x:row>
     <x:row r="538" spans="1:7">
@@ -15261,22 +15264,22 @@
         <x:v>595</x:v>
       </x:c>
       <x:c r="B538" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C538" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D538" s="1">
-        <x:v>8250000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E538" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F538" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G538" s="1">
-        <x:v>8250000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="539" spans="1:7">
@@ -15284,13 +15287,13 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C539" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D539" s="1">
-        <x:v>0</x:v>
+        <x:v>8250000</x:v>
       </x:c>
       <x:c r="E539" s="1">
         <x:v>0</x:v>
@@ -15299,7 +15302,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G539" s="1">
-        <x:v>50</x:v>
+        <x:v>8250000</x:v>
       </x:c>
     </x:row>
     <x:row r="540" spans="1:7">
@@ -15307,22 +15310,22 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C540" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D540" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E540" s="1">
-        <x:v>20483</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F540" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G540" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:7">
@@ -15330,22 +15333,22 @@
         <x:v>598</x:v>
       </x:c>
       <x:c r="B541" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C541" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D541" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E541" s="1">
-        <x:v>0</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="F541" s="1">
-        <x:v>1089100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G541" s="1">
-        <x:v>1089150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:7">
@@ -15353,22 +15356,22 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B542" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C542" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D542" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E542" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F542" s="1">
-        <x:v>0</x:v>
+        <x:v>1089100</x:v>
       </x:c>
       <x:c r="G542" s="1">
-        <x:v>1927706</x:v>
+        <x:v>1089150</x:v>
       </x:c>
     </x:row>
     <x:row r="543" spans="1:7">
@@ -15376,13 +15379,13 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C543" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D543" s="1">
-        <x:v>0</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="E543" s="1">
         <x:v>0</x:v>
@@ -15391,7 +15394,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>50</x:v>
+        <x:v>1927706</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15399,7 +15402,7 @@
         <x:v>601</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C544" s="1">
         <x:v>50</x:v>
@@ -15411,10 +15414,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">
@@ -15422,7 +15425,7 @@
         <x:v>602</x:v>
       </x:c>
       <x:c r="B545" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C545" s="1">
         <x:v>50</x:v>
@@ -15434,10 +15437,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F545" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G545" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="546" spans="1:7">
@@ -15445,10 +15448,10 @@
         <x:v>603</x:v>
       </x:c>
       <x:c r="B546" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C546" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D546" s="1">
         <x:v>0</x:v>
@@ -15457,10 +15460,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F546" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G546" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="547" spans="1:7">
@@ -15468,10 +15471,10 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C547" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D547" s="1">
         <x:v>0</x:v>
@@ -15480,10 +15483,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F547" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G547" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="548" spans="1:7">
@@ -15491,7 +15494,7 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="B548" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C548" s="1">
         <x:v>50</x:v>
@@ -15503,10 +15506,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F548" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G548" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="549" spans="1:7">
@@ -15514,22 +15517,22 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C549" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D549" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E549" s="1">
-        <x:v>817066</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F549" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G549" s="1">
-        <x:v>0</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="550" spans="1:7">
@@ -15537,22 +15540,22 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C550" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D550" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E550" s="1">
-        <x:v>0</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="F550" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G550" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="551" spans="1:7">
@@ -15560,7 +15563,7 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C551" s="1">
         <x:v>50</x:v>
@@ -15583,22 +15586,22 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B552" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C552" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D552" s="1">
-        <x:v>88256</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E552" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F552" s="1">
-        <x:v>14866</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G552" s="1">
-        <x:v>117122</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="553" spans="1:7">
@@ -15606,22 +15609,22 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B553" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C553" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D553" s="1">
-        <x:v>0</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="E553" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F553" s="1">
-        <x:v>0</x:v>
+        <x:v>14866</x:v>
       </x:c>
       <x:c r="G553" s="1">
-        <x:v>50</x:v>
+        <x:v>117122</x:v>
       </x:c>
     </x:row>
     <x:row r="554" spans="1:7">
@@ -15629,7 +15632,7 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C554" s="1">
         <x:v>50</x:v>
@@ -15652,7 +15655,7 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B555" s="1" t="s">
-        <x:v>613</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C555" s="1">
         <x:v>50</x:v>
@@ -15672,10 +15675,10 @@
     </x:row>
     <x:row r="556" spans="1:7">
       <x:c r="A556" s="1" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="B556" s="1" t="s">
         <x:v>614</x:v>
-      </x:c>
-      <x:c r="B556" s="1" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="C556" s="1">
         <x:v>50</x:v>
@@ -15698,10 +15701,10 @@
         <x:v>615</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C557" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D557" s="1">
         <x:v>0</x:v>
@@ -15710,10 +15713,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F557" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G557" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="558" spans="1:7">
@@ -15721,7 +15724,7 @@
         <x:v>616</x:v>
       </x:c>
       <x:c r="B558" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C558" s="1">
         <x:v>0</x:v>
@@ -15733,10 +15736,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F558" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G558" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="559" spans="1:7">
@@ -15747,19 +15750,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C559" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D559" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E559" s="1">
-        <x:v>10041119</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>50</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -15767,7 +15770,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C560" s="1">
         <x:v>50</x:v>
@@ -15776,13 +15779,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E560" s="1">
-        <x:v>0</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="F560" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G560" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="561" spans="1:7">
@@ -15790,7 +15793,7 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C561" s="1">
         <x:v>50</x:v>
@@ -15802,10 +15805,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F561" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G561" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="562" spans="1:7">
@@ -15813,10 +15816,10 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B562" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C562" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D562" s="1">
         <x:v>0</x:v>
@@ -15825,10 +15828,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F562" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G562" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="563" spans="1:7">
@@ -15836,10 +15839,10 @@
         <x:v>621</x:v>
       </x:c>
       <x:c r="B563" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C563" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D563" s="1">
         <x:v>0</x:v>
@@ -15848,10 +15851,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F563" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G563" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="564" spans="1:7">
@@ -15859,7 +15862,7 @@
         <x:v>622</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C564" s="1">
         <x:v>50</x:v>
@@ -15882,7 +15885,7 @@
         <x:v>623</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>50</x:v>
@@ -15905,10 +15908,10 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C566" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D566" s="1">
         <x:v>0</x:v>
@@ -15917,10 +15920,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F566" s="1">
-        <x:v>-19405</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>-19405</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -15928,22 +15931,22 @@
         <x:v>625</x:v>
       </x:c>
       <x:c r="B567" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C567" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D567" s="1">
-        <x:v>1491280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E567" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F567" s="1">
-        <x:v>0</x:v>
+        <x:v>-19405</x:v>
       </x:c>
       <x:c r="G567" s="1">
-        <x:v>1491280</x:v>
+        <x:v>-19405</x:v>
       </x:c>
     </x:row>
     <x:row r="568" spans="1:7">
@@ -15951,22 +15954,22 @@
         <x:v>626</x:v>
       </x:c>
       <x:c r="B568" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C568" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D568" s="1">
-        <x:v>0</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="E568" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F568" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G568" s="1">
-        <x:v>500</x:v>
+        <x:v>1491280</x:v>
       </x:c>
     </x:row>
     <x:row r="569" spans="1:7">
@@ -15974,10 +15977,10 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C569" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D569" s="1">
         <x:v>0</x:v>
@@ -15986,10 +15989,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F569" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G569" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="570" spans="1:7">
@@ -15997,7 +16000,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>50</x:v>
@@ -16009,10 +16012,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F570" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G570" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="571" spans="1:7">
@@ -16020,7 +16023,7 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B571" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C571" s="1">
         <x:v>50</x:v>
@@ -16032,10 +16035,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F571" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G571" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="572" spans="1:7">
@@ -16043,7 +16046,7 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="B572" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C572" s="1">
         <x:v>50</x:v>
@@ -16055,10 +16058,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F572" s="1">
-        <x:v>1287</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>1337</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -16066,10 +16069,10 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C573" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D573" s="1">
         <x:v>0</x:v>
@@ -16078,10 +16081,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F573" s="1">
-        <x:v>6697</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G573" s="1">
-        <x:v>6697</x:v>
+        <x:v>1337</x:v>
       </x:c>
     </x:row>
     <x:row r="574" spans="1:7">
@@ -16089,10 +16092,10 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C574" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D574" s="1">
         <x:v>0</x:v>
@@ -16101,10 +16104,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F574" s="1">
-        <x:v>0</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="G574" s="1">
-        <x:v>50</x:v>
+        <x:v>6697</x:v>
       </x:c>
     </x:row>
     <x:row r="575" spans="1:7">
@@ -16112,10 +16115,10 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="B575" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C575" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D575" s="1">
         <x:v>0</x:v>
@@ -16124,10 +16127,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F575" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G575" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="576" spans="1:7">
@@ -16135,7 +16138,7 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="B576" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C576" s="1">
         <x:v>0</x:v>
@@ -16147,10 +16150,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F576" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="G576" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="577" spans="1:7">
@@ -16158,10 +16161,10 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B577" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C577" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D577" s="1">
         <x:v>0</x:v>
@@ -16170,10 +16173,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F577" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G577" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="578" spans="1:7">
@@ -16181,7 +16184,7 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="B578" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C578" s="1">
         <x:v>50</x:v>
@@ -16204,7 +16207,7 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B579" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C579" s="1">
         <x:v>50</x:v>
@@ -16227,22 +16230,22 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C580" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D580" s="1">
-        <x:v>1400000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E580" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F580" s="1">
-        <x:v>7000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G580" s="1">
-        <x:v>1409500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="581" spans="1:7">
@@ -16250,22 +16253,22 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B581" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C581" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D581" s="1">
-        <x:v>0</x:v>
+        <x:v>1400000</x:v>
       </x:c>
       <x:c r="E581" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F581" s="1">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G581" s="1">
-        <x:v>50</x:v>
+        <x:v>1409500</x:v>
       </x:c>
     </x:row>
     <x:row r="582" spans="1:7">
@@ -16273,10 +16276,10 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C582" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D582" s="1">
         <x:v>0</x:v>
@@ -16285,10 +16288,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F582" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G582" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="583" spans="1:7">
@@ -16296,10 +16299,10 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="B583" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C583" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D583" s="1">
         <x:v>0</x:v>
@@ -16311,7 +16314,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G583" s="1">
-        <x:v>1550</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="584" spans="1:7">
@@ -16319,7 +16322,7 @@
         <x:v>642</x:v>
       </x:c>
       <x:c r="B584" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C584" s="1">
         <x:v>50</x:v>
@@ -16331,10 +16334,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F584" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G584" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:7">
@@ -16342,7 +16345,7 @@
         <x:v>643</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C585" s="1">
         <x:v>50</x:v>
@@ -16365,7 +16368,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>50</x:v>
@@ -16388,7 +16391,7 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C587" s="1">
         <x:v>50</x:v>
@@ -16411,7 +16414,7 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C588" s="1">
         <x:v>50</x:v>
@@ -16434,13 +16437,13 @@
         <x:v>647</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C589" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D589" s="1">
-        <x:v>275541</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E589" s="1">
         <x:v>0</x:v>
@@ -16449,7 +16452,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G589" s="1">
-        <x:v>275541</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:7">
@@ -16457,22 +16460,22 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C590" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D590" s="1">
-        <x:v>0</x:v>
+        <x:v>275541</x:v>
       </x:c>
       <x:c r="E590" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F590" s="1">
-        <x:v>81050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G590" s="1">
-        <x:v>81050</x:v>
+        <x:v>275541</x:v>
       </x:c>
     </x:row>
     <x:row r="591" spans="1:7">
@@ -16480,10 +16483,10 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C591" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D591" s="1">
         <x:v>0</x:v>
@@ -16492,10 +16495,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F591" s="1">
-        <x:v>0</x:v>
+        <x:v>81050</x:v>
       </x:c>
       <x:c r="G591" s="1">
-        <x:v>50</x:v>
+        <x:v>81050</x:v>
       </x:c>
     </x:row>
     <x:row r="592" spans="1:7">
@@ -16503,7 +16506,7 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C592" s="1">
         <x:v>50</x:v>
@@ -16526,10 +16529,10 @@
         <x:v>651</x:v>
       </x:c>
       <x:c r="B593" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C593" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D593" s="1">
         <x:v>0</x:v>
@@ -16541,7 +16544,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G593" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="594" spans="1:7">
@@ -16549,10 +16552,10 @@
         <x:v>652</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C594" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D594" s="1">
         <x:v>0</x:v>
@@ -16564,7 +16567,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G594" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
     </x:row>
     <x:row r="595" spans="1:7">
@@ -16572,7 +16575,7 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C595" s="1">
         <x:v>50</x:v>
@@ -16584,10 +16587,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F595" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G595" s="1">
-        <x:v>14050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="596" spans="1:7">
@@ -16595,10 +16598,10 @@
         <x:v>654</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C596" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D596" s="1">
         <x:v>0</x:v>
@@ -16607,10 +16610,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F596" s="1">
-        <x:v>2700</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G596" s="1">
-        <x:v>2700</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="597" spans="1:7">
@@ -16618,7 +16621,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B597" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C597" s="1">
         <x:v>0</x:v>
@@ -16630,10 +16633,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F597" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G597" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="598" spans="1:7">
@@ -16641,30 +16644,30 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C598" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D598" s="1">
-        <x:v>14446984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E598" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F598" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G598" s="1">
-        <x:v>14446984</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="599" spans="1:7">
       <x:c r="A599" s="1" t="s">
-        <x:v>656</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C599" s="1">
         <x:v>0</x:v>
@@ -16687,13 +16690,13 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C600" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D600" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E600" s="1">
         <x:v>0</x:v>
@@ -16702,7 +16705,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G600" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="601" spans="1:7">
@@ -16710,22 +16713,22 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C601" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D601" s="1">
-        <x:v>2470488</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E601" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F601" s="1">
-        <x:v>11834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G601" s="1">
-        <x:v>2494372</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:7">
@@ -16733,22 +16736,22 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C602" s="1">
-        <x:v>100</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="D602" s="1">
-        <x:v>0</x:v>
+        <x:v>2470488</x:v>
       </x:c>
       <x:c r="E602" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F602" s="1">
-        <x:v>0</x:v>
+        <x:v>11834</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>100</x:v>
+        <x:v>2494372</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -16756,10 +16759,10 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C603" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D603" s="1">
         <x:v>0</x:v>
@@ -16771,7 +16774,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G603" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="604" spans="1:7">
@@ -16779,7 +16782,7 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C604" s="1">
         <x:v>50</x:v>
@@ -16805,7 +16808,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16814,10 +16817,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16825,10 +16828,10 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16837,10 +16840,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>2550</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -16848,7 +16851,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>50</x:v>
@@ -16860,10 +16863,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F607" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G607" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="608" spans="1:7">
@@ -16871,7 +16874,7 @@
         <x:v>665</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C608" s="1">
         <x:v>50</x:v>
@@ -16894,7 +16897,7 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B609" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C609" s="1">
         <x:v>50</x:v>
@@ -16917,7 +16920,7 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C610" s="1">
         <x:v>50</x:v>
@@ -16940,22 +16943,22 @@
         <x:v>668</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C611" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D611" s="1">
-        <x:v>3975320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E611" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F611" s="1">
-        <x:v>6634</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G611" s="1">
-        <x:v>3982954</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="612" spans="1:7">
@@ -16963,22 +16966,22 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C612" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D612" s="1">
-        <x:v>0</x:v>
+        <x:v>3975320</x:v>
       </x:c>
       <x:c r="E612" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F612" s="1">
-        <x:v>22000</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G612" s="1">
-        <x:v>22000</x:v>
+        <x:v>3982954</x:v>
       </x:c>
     </x:row>
     <x:row r="613" spans="1:7">
@@ -16986,10 +16989,10 @@
         <x:v>670</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C613" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D613" s="1">
         <x:v>0</x:v>
@@ -16998,10 +17001,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F613" s="1">
-        <x:v>5800</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G613" s="1">
-        <x:v>5850</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:7">
@@ -17009,7 +17012,7 @@
         <x:v>671</x:v>
       </x:c>
       <x:c r="B614" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C614" s="1">
         <x:v>50</x:v>
@@ -17021,21 +17024,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F614" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G614" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="615" spans="1:7">
       <x:c r="A615" s="1" t="s">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="B615" s="1" t="s">
         <x:v>673</x:v>
       </x:c>
-      <x:c r="B615" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C615" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -17044,10 +17047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -17055,10 +17058,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D616" s="1">
         <x:v>0</x:v>
@@ -17067,18 +17070,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
       <x:c r="A617" s="1" t="s">
+        <x:v>675</x:v>
+      </x:c>
+      <x:c r="B617" s="1" t="s">
         <x:v>676</x:v>
-      </x:c>
-      <x:c r="B617" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C617" s="1">
         <x:v>50</x:v>
@@ -17101,7 +17104,7 @@
         <x:v>677</x:v>
       </x:c>
       <x:c r="B618" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C618" s="1">
         <x:v>50</x:v>
@@ -17121,13 +17124,13 @@
     </x:row>
     <x:row r="619" spans="1:7">
       <x:c r="A619" s="1" t="s">
-        <x:v>677</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="B619" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C619" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D619" s="1">
         <x:v>0</x:v>
@@ -17136,10 +17139,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F619" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G619" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="620" spans="1:7">
@@ -17147,10 +17150,10 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C620" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D620" s="1">
         <x:v>0</x:v>
@@ -17159,10 +17162,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F620" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G620" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="621" spans="1:7">
@@ -17170,7 +17173,7 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C621" s="1">
         <x:v>50</x:v>
@@ -17193,10 +17196,10 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C622" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D622" s="1">
         <x:v>0</x:v>
@@ -17205,10 +17208,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F622" s="1">
-        <x:v>68600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G622" s="1">
-        <x:v>71150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="623" spans="1:7">
@@ -17216,10 +17219,10 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C623" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D623" s="1">
         <x:v>0</x:v>
@@ -17228,10 +17231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F623" s="1">
-        <x:v>0</x:v>
+        <x:v>68600</x:v>
       </x:c>
       <x:c r="G623" s="1">
-        <x:v>50</x:v>
+        <x:v>71150</x:v>
       </x:c>
     </x:row>
     <x:row r="624" spans="1:7">
@@ -17239,7 +17242,7 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C624" s="1">
         <x:v>50</x:v>
@@ -17262,10 +17265,10 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D625" s="1">
         <x:v>0</x:v>
@@ -17274,10 +17277,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17285,10 +17288,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17297,10 +17300,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>58000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>58050</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17308,10 +17311,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17320,10 +17323,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>1666</x:v>
+        <x:v>58000</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>3716</x:v>
+        <x:v>58050</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -17331,10 +17334,10 @@
         <x:v>686</x:v>
       </x:c>
       <x:c r="B628" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C628" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D628" s="1">
         <x:v>0</x:v>
@@ -17343,10 +17346,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F628" s="1">
-        <x:v>1668</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="G628" s="1">
-        <x:v>1668</x:v>
+        <x:v>3716</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:7">
@@ -17354,10 +17357,10 @@
         <x:v>687</x:v>
       </x:c>
       <x:c r="B629" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C629" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D629" s="1">
         <x:v>0</x:v>
@@ -17366,10 +17369,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F629" s="1">
-        <x:v>0</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G629" s="1">
-        <x:v>50</x:v>
+        <x:v>1668</x:v>
       </x:c>
     </x:row>
     <x:row r="630" spans="1:7">
@@ -17377,13 +17380,13 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C630" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D630" s="1">
-        <x:v>52520</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E630" s="1">
         <x:v>0</x:v>
@@ -17392,7 +17395,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G630" s="1">
-        <x:v>52570</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="631" spans="1:7">
@@ -17400,22 +17403,22 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D631" s="1">
-        <x:v>0</x:v>
+        <x:v>52520</x:v>
       </x:c>
       <x:c r="E631" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>30600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>33550</x:v>
+        <x:v>52570</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -17423,10 +17426,10 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>2550</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
@@ -17435,10 +17438,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>0</x:v>
+        <x:v>30600</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>2550</x:v>
+        <x:v>33550</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17446,22 +17449,22 @@
         <x:v>691</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C633" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D633" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E633" s="1">
-        <x:v>56045</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F633" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G633" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="634" spans="1:7">
@@ -17478,7 +17481,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E634" s="1">
-        <x:v>0</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="F634" s="1">
         <x:v>0</x:v>
@@ -17492,10 +17495,10 @@
         <x:v>693</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C635" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D635" s="1">
         <x:v>0</x:v>
@@ -17507,7 +17510,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G635" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:7">
@@ -17515,10 +17518,10 @@
         <x:v>694</x:v>
       </x:c>
       <x:c r="B636" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C636" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D636" s="1">
         <x:v>0</x:v>
@@ -17530,7 +17533,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G636" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="637" spans="1:7">
@@ -17538,10 +17541,10 @@
         <x:v>695</x:v>
       </x:c>
       <x:c r="B637" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C637" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D637" s="1">
         <x:v>0</x:v>
@@ -17550,33 +17553,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F637" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G637" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="638" spans="1:7">
       <x:c r="A638" s="1" t="s">
-        <x:v>695</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="B638" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C638" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D638" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E638" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F638" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G638" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="639" spans="1:7">
@@ -17590,7 +17593,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D639" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E639" s="1">
         <x:v>0</x:v>
@@ -17599,7 +17602,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -17607,13 +17610,13 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C640" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D640" s="1">
-        <x:v>0</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="E640" s="1">
         <x:v>0</x:v>
@@ -17622,7 +17625,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G640" s="1">
-        <x:v>50</x:v>
+        <x:v>852561</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:7">
@@ -17630,7 +17633,7 @@
         <x:v>698</x:v>
       </x:c>
       <x:c r="B641" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C641" s="1">
         <x:v>50</x:v>
@@ -17653,13 +17656,13 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C642" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D642" s="1">
-        <x:v>2200000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E642" s="1">
         <x:v>0</x:v>
@@ -17668,7 +17671,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G642" s="1">
-        <x:v>2200000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:7">
@@ -17676,13 +17679,13 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="B643" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C643" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D643" s="1">
-        <x:v>0</x:v>
+        <x:v>2200000</x:v>
       </x:c>
       <x:c r="E643" s="1">
         <x:v>0</x:v>
@@ -17691,7 +17694,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G643" s="1">
-        <x:v>50</x:v>
+        <x:v>2200000</x:v>
       </x:c>
     </x:row>
     <x:row r="644" spans="1:7">
@@ -17699,7 +17702,7 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C644" s="1">
         <x:v>50</x:v>
@@ -17722,7 +17725,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C645" s="1">
         <x:v>50</x:v>
@@ -17745,10 +17748,10 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D646" s="1">
         <x:v>0</x:v>
@@ -17760,7 +17763,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -17768,10 +17771,10 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="B647" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C647" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D647" s="1">
         <x:v>0</x:v>
@@ -17783,7 +17786,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G647" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="648" spans="1:7">
@@ -17791,10 +17794,10 @@
         <x:v>705</x:v>
       </x:c>
       <x:c r="B648" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C648" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D648" s="1">
         <x:v>0</x:v>
@@ -17806,7 +17809,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G648" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="649" spans="1:7">
@@ -17814,10 +17817,10 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B649" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C649" s="1">
-        <x:v>1050</x:v>
+        <x:v>10050</x:v>
       </x:c>
       <x:c r="D649" s="1">
         <x:v>0</x:v>
@@ -17826,10 +17829,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F649" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G649" s="1">
-        <x:v>2717</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:7">
@@ -17837,10 +17840,10 @@
         <x:v>707</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C650" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D650" s="1">
         <x:v>0</x:v>
@@ -17849,10 +17852,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F650" s="1">
-        <x:v>0</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G650" s="1">
-        <x:v>50</x:v>
+        <x:v>2717</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:7">
@@ -17860,22 +17863,22 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C651" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D651" s="1">
-        <x:v>111599</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E651" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F651" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G651" s="1">
-        <x:v>114899</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:7">
@@ -17883,22 +17886,22 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C652" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D652" s="1">
-        <x:v>0</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="E652" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F652" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>50</x:v>
+        <x:v>114899</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -17906,7 +17909,7 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C653" s="1">
         <x:v>50</x:v>
@@ -17926,16 +17929,16 @@
     </x:row>
     <x:row r="654" spans="1:7">
       <x:c r="A654" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C654" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D654" s="1">
-        <x:v>113120</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E654" s="1">
         <x:v>0</x:v>
@@ -17944,7 +17947,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G654" s="1">
-        <x:v>113120</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="655" spans="1:7">
@@ -17952,13 +17955,13 @@
         <x:v>711</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C655" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D655" s="1">
-        <x:v>0</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="E655" s="1">
         <x:v>0</x:v>
@@ -17967,7 +17970,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G655" s="1">
-        <x:v>50</x:v>
+        <x:v>113120</x:v>
       </x:c>
     </x:row>
     <x:row r="656" spans="1:7">
@@ -17975,22 +17978,22 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C656" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>10046680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F656" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>10048730</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -17998,22 +18001,22 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C657" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D657" s="1">
-        <x:v>2263800</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E657" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F657" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G657" s="1">
-        <x:v>2263850</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:7">
@@ -18021,13 +18024,13 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B658" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C658" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D658" s="1">
-        <x:v>0</x:v>
+        <x:v>2263800</x:v>
       </x:c>
       <x:c r="E658" s="1">
         <x:v>0</x:v>
@@ -18036,7 +18039,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G658" s="1">
-        <x:v>50</x:v>
+        <x:v>2263850</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:7">
@@ -18044,7 +18047,7 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C659" s="1">
         <x:v>50</x:v>
@@ -18056,10 +18059,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F659" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G659" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:7">
@@ -18067,10 +18070,10 @@
         <x:v>716</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D660" s="1">
         <x:v>0</x:v>
@@ -18079,10 +18082,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F660" s="1">
-        <x:v>52333</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>58383</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18090,10 +18093,10 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D661" s="1">
         <x:v>0</x:v>
@@ -18102,10 +18105,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F661" s="1">
-        <x:v>0</x:v>
+        <x:v>52333</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>50</x:v>
+        <x:v>58383</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18113,7 +18116,7 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C662" s="1">
         <x:v>50</x:v>
@@ -18136,10 +18139,10 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C663" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D663" s="1">
         <x:v>0</x:v>
@@ -18148,10 +18151,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F663" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G663" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:7">
@@ -18159,22 +18162,22 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="B664" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C664" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D664" s="1">
-        <x:v>367531</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E664" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F664" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G664" s="1">
-        <x:v>367531</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:7">
@@ -18182,22 +18185,22 @@
         <x:v>721</x:v>
       </x:c>
       <x:c r="B665" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C665" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D665" s="1">
-        <x:v>817169</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="E665" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F665" s="1">
-        <x:v>1668</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G665" s="1">
-        <x:v>820837</x:v>
+        <x:v>367531</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:7">
@@ -18205,22 +18208,22 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C666" s="1">
-        <x:v>11050</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D666" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E666" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F666" s="1">
-        <x:v>6242</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G666" s="1">
-        <x:v>17292</x:v>
+        <x:v>820837</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:7">
@@ -18228,10 +18231,10 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C667" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D667" s="1">
         <x:v>0</x:v>
@@ -18240,10 +18243,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F667" s="1">
-        <x:v>0</x:v>
+        <x:v>6242</x:v>
       </x:c>
       <x:c r="G667" s="1">
-        <x:v>50</x:v>
+        <x:v>17292</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:7">
@@ -18251,7 +18254,7 @@
         <x:v>724</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C668" s="1">
         <x:v>50</x:v>
@@ -18274,10 +18277,10 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C669" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D669" s="1">
         <x:v>0</x:v>
@@ -18286,10 +18289,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F669" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
@@ -18297,10 +18300,10 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C670" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D670" s="1">
         <x:v>0</x:v>
@@ -18309,10 +18312,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F670" s="1">
-        <x:v>25000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G670" s="1">
-        <x:v>25050</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="671" spans="1:7">
@@ -18320,7 +18323,7 @@
         <x:v>727</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C671" s="1">
         <x:v>50</x:v>
@@ -18332,10 +18335,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F671" s="1">
-        <x:v>0</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>50</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">
@@ -18343,22 +18346,22 @@
         <x:v>728</x:v>
       </x:c>
       <x:c r="B672" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C672" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D672" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E672" s="1">
-        <x:v>1531015</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F672" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G672" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="673" spans="1:7">
@@ -18366,22 +18369,22 @@
         <x:v>729</x:v>
       </x:c>
       <x:c r="B673" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C673" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D673" s="1">
-        <x:v>157560</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E673" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F673" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G673" s="1">
-        <x:v>157610</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="674" spans="1:7">
@@ -18389,13 +18392,13 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C674" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D674" s="1">
-        <x:v>0</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="E674" s="1">
         <x:v>0</x:v>
@@ -18404,7 +18407,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G674" s="1">
-        <x:v>50</x:v>
+        <x:v>157610</x:v>
       </x:c>
     </x:row>
     <x:row r="675" spans="1:7">
@@ -18412,13 +18415,13 @@
         <x:v>731</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C675" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D675" s="1">
-        <x:v>5583432</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E675" s="1">
         <x:v>0</x:v>
@@ -18427,7 +18430,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G675" s="1">
-        <x:v>5584432</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:7">
@@ -18435,13 +18438,13 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B676" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C676" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D676" s="1">
-        <x:v>0</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E676" s="1">
         <x:v>0</x:v>
@@ -18450,7 +18453,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G676" s="1">
-        <x:v>50</x:v>
+        <x:v>5584432</x:v>
       </x:c>
     </x:row>
     <x:row r="677" spans="1:7">
@@ -18458,22 +18461,22 @@
         <x:v>733</x:v>
       </x:c>
       <x:c r="B677" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C677" s="1">
-        <x:v>24050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D677" s="1">
-        <x:v>764206</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E677" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F677" s="1">
-        <x:v>20501</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>808757</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
@@ -18481,22 +18484,22 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B678" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C678" s="1">
-        <x:v>0</x:v>
+        <x:v>24050</x:v>
       </x:c>
       <x:c r="D678" s="1">
-        <x:v>0</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="E678" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F678" s="1">
-        <x:v>2700</x:v>
+        <x:v>20501</x:v>
       </x:c>
       <x:c r="G678" s="1">
-        <x:v>2700</x:v>
+        <x:v>808757</x:v>
       </x:c>
     </x:row>
     <x:row r="679" spans="1:7">
@@ -18504,22 +18507,22 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C679" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D679" s="1">
-        <x:v>1543316</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E679" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F679" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
@@ -18527,22 +18530,22 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D680" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E680" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>14500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>14550</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -18550,7 +18553,7 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C681" s="1">
         <x:v>50</x:v>
@@ -18562,10 +18565,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>50</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -18573,7 +18576,7 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C682" s="1">
         <x:v>50</x:v>
@@ -18596,13 +18599,13 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C683" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D683" s="1">
-        <x:v>107353</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E683" s="1">
         <x:v>0</x:v>
@@ -18611,7 +18614,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>107403</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -18619,22 +18622,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D684" s="1">
-        <x:v>0</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="E684" s="1">
-        <x:v>10135449</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>0</x:v>
+        <x:v>107403</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -18642,22 +18645,22 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C685" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D685" s="1">
-        <x:v>51510</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E685" s="1">
-        <x:v>0</x:v>
+        <x:v>10135449</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>54844</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -18665,22 +18668,22 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D686" s="1">
-        <x:v>0</x:v>
+        <x:v>51510</x:v>
       </x:c>
       <x:c r="E686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>2500</x:v>
+        <x:v>54844</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -18688,13 +18691,13 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C687" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D687" s="1">
-        <x:v>106947</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E687" s="1">
         <x:v>0</x:v>
@@ -18703,7 +18706,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>106947</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
@@ -18711,22 +18714,22 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C688" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D688" s="1">
-        <x:v>0</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="E688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F688" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>25050</x:v>
+        <x:v>106947</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
@@ -18734,22 +18737,22 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C689" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D689" s="1">
-        <x:v>902176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E689" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F689" s="1">
-        <x:v>7000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G689" s="1">
-        <x:v>910226</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="690" spans="1:7">
@@ -18757,22 +18760,22 @@
         <x:v>746</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D690" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E690" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>25500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>25550</x:v>
+        <x:v>910226</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -18792,10 +18795,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>50</x:v>
+        <x:v>25550</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -18803,10 +18806,10 @@
         <x:v>748</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -18815,10 +18818,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>10500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>10500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -18826,7 +18829,7 @@
         <x:v>749</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C693" s="1">
         <x:v>0</x:v>
@@ -18838,10 +18841,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F693" s="1">
-        <x:v>6200</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>6200</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
@@ -18849,10 +18852,10 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C694" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D694" s="1">
         <x:v>0</x:v>
@@ -18861,10 +18864,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F694" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>50</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
@@ -18872,10 +18875,10 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C695" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D695" s="1">
         <x:v>0</x:v>
@@ -18887,7 +18890,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
@@ -18895,10 +18898,10 @@
         <x:v>752</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D696" s="1">
         <x:v>0</x:v>
@@ -18907,10 +18910,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>6650</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -18918,22 +18921,22 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C697" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D697" s="1">
-        <x:v>1010142</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E697" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F697" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>1010142</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">
@@ -18941,22 +18944,22 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C698" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D698" s="1">
-        <x:v>0</x:v>
+        <x:v>1010142</x:v>
       </x:c>
       <x:c r="E698" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F698" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>5000</x:v>
+        <x:v>1010142</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
@@ -18964,10 +18967,10 @@
         <x:v>755</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C699" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D699" s="1">
         <x:v>0</x:v>
@@ -18976,10 +18979,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F699" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G699" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:7">
@@ -18987,10 +18990,10 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C700" s="1">
-        <x:v>6550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D700" s="1">
         <x:v>0</x:v>
@@ -18999,10 +19002,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F700" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>9850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
@@ -19010,10 +19013,10 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C701" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D701" s="1">
         <x:v>0</x:v>
@@ -19022,10 +19025,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>50</x:v>
+        <x:v>9850</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
@@ -19033,7 +19036,7 @@
         <x:v>758</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C702" s="1">
         <x:v>50</x:v>
@@ -19056,10 +19059,10 @@
         <x:v>759</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C703" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D703" s="1">
         <x:v>0</x:v>
@@ -19068,10 +19071,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F703" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>9550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
@@ -19079,10 +19082,10 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C704" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D704" s="1">
         <x:v>0</x:v>
@@ -19091,10 +19094,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>2700</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>2700</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
@@ -19102,10 +19105,10 @@
         <x:v>761</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D705" s="1">
         <x:v>0</x:v>
@@ -19114,10 +19117,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19125,10 +19128,10 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D706" s="1">
         <x:v>0</x:v>
@@ -19137,33 +19140,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>9350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
       <x:c r="A707" s="1" t="s">
-        <x:v>762</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D707" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E707" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
@@ -19171,22 +19174,22 @@
         <x:v>763</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D708" s="1">
-        <x:v>2572233</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E708" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>5500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>2577783</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
@@ -19194,22 +19197,22 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C709" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D709" s="1">
-        <x:v>0</x:v>
+        <x:v>2572233</x:v>
       </x:c>
       <x:c r="E709" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>0</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>50</x:v>
+        <x:v>2577783</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -19217,7 +19220,7 @@
         <x:v>765</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C710" s="1">
         <x:v>50</x:v>
@@ -19229,10 +19232,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
@@ -19240,7 +19243,7 @@
         <x:v>766</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C711" s="1">
         <x:v>50</x:v>
@@ -19252,10 +19255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F711" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
@@ -19263,10 +19266,10 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D712" s="1">
         <x:v>0</x:v>
@@ -19275,10 +19278,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>3300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19289,7 +19292,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D713" s="1">
         <x:v>0</x:v>
@@ -19298,10 +19301,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>50</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19309,7 +19312,7 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C714" s="1">
         <x:v>50</x:v>
@@ -19321,10 +19324,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>5700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19332,7 +19335,7 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C715" s="1">
         <x:v>50</x:v>
@@ -19344,10 +19347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>0</x:v>
+        <x:v>5700</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
@@ -19355,7 +19358,7 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C716" s="1">
         <x:v>50</x:v>
@@ -19378,22 +19381,22 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D717" s="1">
-        <x:v>1892270</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E717" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>1909770</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
@@ -19401,13 +19404,13 @@
         <x:v>773</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C718" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D718" s="1">
-        <x:v>0</x:v>
+        <x:v>1892270</x:v>
       </x:c>
       <x:c r="E718" s="1">
         <x:v>0</x:v>
@@ -19416,7 +19419,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>1000</x:v>
+        <x:v>1909770</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
@@ -19424,10 +19427,10 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C719" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D719" s="1">
         <x:v>0</x:v>
@@ -19436,10 +19439,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F719" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G719" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="720" spans="1:7">
@@ -19447,10 +19450,10 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D720" s="1">
         <x:v>0</x:v>
@@ -19459,10 +19462,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F720" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
@@ -19470,10 +19473,10 @@
         <x:v>776</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C721" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D721" s="1">
         <x:v>0</x:v>
@@ -19482,10 +19485,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F721" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
@@ -19493,13 +19496,13 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C722" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D722" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E722" s="1">
         <x:v>0</x:v>
@@ -19508,7 +19511,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>40000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
@@ -19516,13 +19519,13 @@
         <x:v>778</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D723" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E723" s="1">
         <x:v>0</x:v>
@@ -19531,7 +19534,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>1000</x:v>
+        <x:v>40000</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
@@ -19539,10 +19542,10 @@
         <x:v>779</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C724" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D724" s="1">
         <x:v>0</x:v>
@@ -19554,7 +19557,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
@@ -19562,10 +19565,10 @@
         <x:v>780</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D725" s="1">
         <x:v>0</x:v>
@@ -19574,10 +19577,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F725" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>5200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
@@ -19585,10 +19588,10 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C726" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D726" s="1">
         <x:v>0</x:v>
@@ -19597,10 +19600,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F726" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
@@ -19608,7 +19611,7 @@
         <x:v>782</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C727" s="1">
         <x:v>50</x:v>
@@ -19631,7 +19634,7 @@
         <x:v>783</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C728" s="1">
         <x:v>50</x:v>
@@ -19643,10 +19646,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
@@ -19654,22 +19657,22 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C729" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D729" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E729" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F729" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>3920589</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">
@@ -19677,13 +19680,13 @@
         <x:v>785</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C730" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D730" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E730" s="1">
         <x:v>0</x:v>
@@ -19692,7 +19695,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>50</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
@@ -19700,10 +19703,10 @@
         <x:v>786</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C731" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D731" s="1">
         <x:v>0</x:v>
@@ -19715,7 +19718,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
@@ -19723,10 +19726,10 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C732" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D732" s="1">
         <x:v>0</x:v>
@@ -19738,7 +19741,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
@@ -19746,7 +19749,7 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C733" s="1">
         <x:v>50</x:v>
@@ -19769,10 +19772,10 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C734" s="1">
-        <x:v>4500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D734" s="1">
         <x:v>0</x:v>
@@ -19781,10 +19784,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F734" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G734" s="1">
-        <x:v>9334</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:7">
@@ -19792,10 +19795,10 @@
         <x:v>790</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>1050</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19804,10 +19807,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>1050</x:v>
+        <x:v>9334</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19818,7 +19821,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19830,7 +19833,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
@@ -19838,7 +19841,7 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C737" s="1">
         <x:v>50</x:v>
@@ -19861,13 +19864,13 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C738" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D738" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E738" s="1">
         <x:v>0</x:v>
@@ -19876,7 +19879,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
@@ -19884,13 +19887,13 @@
         <x:v>794</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C739" s="1">
-        <x:v>50</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D739" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E739" s="1">
         <x:v>0</x:v>
@@ -19899,7 +19902,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G739" s="1">
-        <x:v>50</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:7">
@@ -19907,10 +19910,10 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>19600</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D740" s="1">
         <x:v>0</x:v>
@@ -19919,10 +19922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F740" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>36600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
@@ -19930,10 +19933,10 @@
         <x:v>796</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C741" s="1">
-        <x:v>50</x:v>
+        <x:v>19600</x:v>
       </x:c>
       <x:c r="D741" s="1">
         <x:v>0</x:v>
@@ -19942,10 +19945,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F741" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>50</x:v>
+        <x:v>36600</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">
@@ -19953,7 +19956,7 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C742" s="1">
         <x:v>50</x:v>
@@ -19976,7 +19979,7 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C743" s="1">
         <x:v>50</x:v>
@@ -19999,13 +20002,13 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C744" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D744" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E744" s="1">
         <x:v>0</x:v>
@@ -20014,7 +20017,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G744" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:7">
@@ -20022,13 +20025,13 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C745" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D745" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E745" s="1">
         <x:v>0</x:v>
@@ -20037,7 +20040,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G745" s="1">
-        <x:v>50</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:7">
@@ -20045,10 +20048,10 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D746" s="1">
         <x:v>0</x:v>
@@ -20057,10 +20060,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F746" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>30000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20068,10 +20071,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D747" s="1">
         <x:v>0</x:v>
@@ -20080,10 +20083,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F747" s="1">
-        <x:v>0</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>50</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">
@@ -20091,10 +20094,10 @@
         <x:v>803</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>19050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D748" s="1">
         <x:v>0</x:v>
@@ -20103,10 +20106,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F748" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>21550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
@@ -20114,10 +20117,10 @@
         <x:v>804</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C749" s="1">
-        <x:v>3500</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D749" s="1">
         <x:v>0</x:v>
@@ -20126,10 +20129,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F749" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G749" s="1">
-        <x:v>3500</x:v>
+        <x:v>21550</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:7">
@@ -20137,10 +20140,10 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20152,18 +20155,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
       <x:c r="A751" s="1" t="s">
-        <x:v>805</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20172,10 +20175,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F751" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
@@ -20183,10 +20186,10 @@
         <x:v>806</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20195,10 +20198,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
@@ -20206,10 +20209,10 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20221,7 +20224,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
@@ -20229,10 +20232,10 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C754" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D754" s="1">
         <x:v>0</x:v>
@@ -20244,7 +20247,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
@@ -20252,10 +20255,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -20264,10 +20267,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F755" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
@@ -20275,10 +20278,10 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C756" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D756" s="1">
         <x:v>0</x:v>
@@ -20287,10 +20290,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F756" s="1">
-        <x:v>5000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>5050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">
@@ -20298,7 +20301,7 @@
         <x:v>811</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C757" s="1">
         <x:v>50</x:v>
@@ -20310,10 +20313,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20321,10 +20324,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20333,10 +20336,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
@@ -20344,10 +20347,10 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C759" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D759" s="1">
         <x:v>0</x:v>
@@ -20356,10 +20359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F759" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
@@ -20367,7 +20370,7 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C760" s="1">
         <x:v>50</x:v>
@@ -20390,13 +20393,13 @@
         <x:v>815</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C761" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D761" s="1">
-        <x:v>943006</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E761" s="1">
         <x:v>0</x:v>
@@ -20405,7 +20408,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>943056</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">
@@ -20413,13 +20416,13 @@
         <x:v>816</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C762" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D762" s="1">
-        <x:v>0</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="E762" s="1">
         <x:v>0</x:v>
@@ -20428,7 +20431,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>50</x:v>
+        <x:v>943056</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">
@@ -20436,7 +20439,7 @@
         <x:v>817</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C763" s="1">
         <x:v>50</x:v>
@@ -20459,22 +20462,22 @@
         <x:v>818</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C764" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D764" s="1">
-        <x:v>476254</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E764" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F764" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G764" s="1">
-        <x:v>478754</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="765" spans="1:7">
@@ -20482,22 +20485,22 @@
         <x:v>819</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C765" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D765" s="1">
-        <x:v>0</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="E765" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F765" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G765" s="1">
-        <x:v>50</x:v>
+        <x:v>478754</x:v>
       </x:c>
     </x:row>
     <x:row r="766" spans="1:7">
@@ -20505,7 +20508,7 @@
         <x:v>820</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C766" s="1">
         <x:v>50</x:v>
@@ -20517,10 +20520,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>4999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>5049</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
@@ -20528,10 +20531,10 @@
         <x:v>821</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C767" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D767" s="1">
         <x:v>0</x:v>
@@ -20540,10 +20543,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F767" s="1">
-        <x:v>16500</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G767" s="1">
-        <x:v>16500</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:7">
@@ -20551,10 +20554,10 @@
         <x:v>822</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C768" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D768" s="1">
         <x:v>0</x:v>
@@ -20563,10 +20566,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
@@ -20574,7 +20577,7 @@
         <x:v>823</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C769" s="1">
         <x:v>50</x:v>
@@ -20597,7 +20600,7 @@
         <x:v>824</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C770" s="1">
         <x:v>50</x:v>
@@ -20620,7 +20623,7 @@
         <x:v>825</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C771" s="1">
         <x:v>50</x:v>
@@ -20643,7 +20646,7 @@
         <x:v>826</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C772" s="1">
         <x:v>50</x:v>
@@ -20655,10 +20658,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F772" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G772" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="773" spans="1:7">
@@ -20666,7 +20669,7 @@
         <x:v>827</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C773" s="1">
         <x:v>50</x:v>
@@ -20678,10 +20681,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F773" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G773" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="774" spans="1:7">
@@ -20689,10 +20692,10 @@
         <x:v>828</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C774" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D774" s="1">
         <x:v>0</x:v>
@@ -20701,10 +20704,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F774" s="1">
-        <x:v>37300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G774" s="1">
-        <x:v>48150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:7">
@@ -20712,10 +20715,10 @@
         <x:v>829</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C775" s="1">
-        <x:v>0</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D775" s="1">
         <x:v>0</x:v>
@@ -20724,10 +20727,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>83</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>83</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
@@ -20735,10 +20738,10 @@
         <x:v>830</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C776" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D776" s="1">
         <x:v>0</x:v>
@@ -20747,10 +20750,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
@@ -20758,7 +20761,7 @@
         <x:v>831</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C777" s="1">
         <x:v>50</x:v>
@@ -20781,7 +20784,7 @@
         <x:v>832</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C778" s="1">
         <x:v>50</x:v>
@@ -20804,10 +20807,10 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C779" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D779" s="1">
         <x:v>0</x:v>
@@ -20816,10 +20819,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F779" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G779" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="780" spans="1:7">
@@ -20827,21 +20830,44 @@
         <x:v>834</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C780" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D780" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E780" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F780" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G780" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="781" spans="1:7">
+      <x:c r="A781" s="1" t="s">
+        <x:v>835</x:v>
+      </x:c>
+      <x:c r="B781" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C780" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D780" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E780" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F780" s="1">
+      <x:c r="C781" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D781" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E781" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F781" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G780" s="1">
+      <x:c r="G781" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -1616,6 +1616,9 @@
   </x:si>
   <x:si>
     <x:t>MILLER, MAX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER-MEEKS, MARIANNETTE JANE</x:t>
   </x:si>
   <x:si>
     <x:t>MIN, DAVE</x:t>
@@ -2592,8 +2595,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G781" totalsRowShown="0">
-  <x:autoFilter ref="A1:G781"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G782" totalsRowShown="0">
+  <x:autoFilter ref="A1:G782"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2895,7 +2898,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G781"/>
+  <x:dimension ref="A1:G782"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3560,7 +3563,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>14300</x:v>
+        <x:v>19300</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>44598146</x:v>
@@ -3572,7 +3575,7 @@
         <x:v>17500</x:v>
       </x:c>
       <x:c r="G29" s="1">
-        <x:v>44629946</x:v>
+        <x:v>44634946</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
@@ -3767,7 +3770,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>1500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>0</x:v>
@@ -3779,7 +3782,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G38" s="1">
-        <x:v>1500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -4940,7 +4943,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C89" s="1">
-        <x:v>9500</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D89" s="1">
         <x:v>0</x:v>
@@ -4952,7 +4955,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G89" s="1">
-        <x:v>11000</x:v>
+        <x:v>13500</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
@@ -7999,7 +8002,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C222" s="1">
-        <x:v>14500</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="D222" s="1">
         <x:v>126740</x:v>
@@ -8011,7 +8014,7 @@
         <x:v>18500</x:v>
       </x:c>
       <x:c r="G222" s="1">
-        <x:v>159740</x:v>
+        <x:v>162240</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:7">
@@ -8482,7 +8485,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C243" s="1">
-        <x:v>2500</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="D243" s="1">
         <x:v>0</x:v>
@@ -8494,7 +8497,7 @@
         <x:v>14666</x:v>
       </x:c>
       <x:c r="G243" s="1">
-        <x:v>17166</x:v>
+        <x:v>20666</x:v>
       </x:c>
     </x:row>
     <x:row r="244" spans="1:7">
@@ -10345,7 +10348,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C324" s="1">
-        <x:v>10350</x:v>
+        <x:v>12850</x:v>
       </x:c>
       <x:c r="D324" s="1">
         <x:v>322059</x:v>
@@ -10357,7 +10360,7 @@
         <x:v>35533</x:v>
       </x:c>
       <x:c r="G324" s="1">
-        <x:v>367942</x:v>
+        <x:v>370442</x:v>
       </x:c>
     </x:row>
     <x:row r="325" spans="1:7">
@@ -12070,7 +12073,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C399" s="1">
-        <x:v>9500</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="D399" s="1">
         <x:v>0</x:v>
@@ -12082,7 +12085,7 @@
         <x:v>6666</x:v>
       </x:c>
       <x:c r="G399" s="1">
-        <x:v>16166</x:v>
+        <x:v>17166</x:v>
       </x:c>
     </x:row>
     <x:row r="400" spans="1:7">
@@ -13884,22 +13887,22 @@
         <x:v>534</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D478" s="1">
-        <x:v>107940</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E478" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>109940</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -13907,22 +13910,22 @@
         <x:v>535</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D479" s="1">
-        <x:v>0</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="E479" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>50</x:v>
+        <x:v>109940</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -13930,10 +13933,10 @@
         <x:v>536</x:v>
       </x:c>
       <x:c r="B480" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C480" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D480" s="1">
         <x:v>0</x:v>
@@ -13942,10 +13945,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F480" s="1">
-        <x:v>6200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G480" s="1">
-        <x:v>7200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="481" spans="1:7">
@@ -13953,10 +13956,10 @@
         <x:v>537</x:v>
       </x:c>
       <x:c r="B481" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C481" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D481" s="1">
         <x:v>0</x:v>
@@ -13965,10 +13968,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F481" s="1">
-        <x:v>2000</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G481" s="1">
-        <x:v>2000</x:v>
+        <x:v>7200</x:v>
       </x:c>
     </x:row>
     <x:row r="482" spans="1:7">
@@ -13976,10 +13979,10 @@
         <x:v>538</x:v>
       </x:c>
       <x:c r="B482" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C482" s="1">
-        <x:v>5050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D482" s="1">
         <x:v>0</x:v>
@@ -13988,10 +13991,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F482" s="1">
-        <x:v>1000</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G482" s="1">
-        <x:v>6050</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="483" spans="1:7">
@@ -13999,10 +14002,10 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="B483" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C483" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D483" s="1">
         <x:v>0</x:v>
@@ -14011,10 +14014,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F483" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G483" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
     </x:row>
     <x:row r="484" spans="1:7">
@@ -14022,13 +14025,13 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="B484" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C484" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D484" s="1">
-        <x:v>400022</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E484" s="1">
         <x:v>0</x:v>
@@ -14037,7 +14040,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G484" s="1">
-        <x:v>401022</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="485" spans="1:7">
@@ -14045,22 +14048,22 @@
         <x:v>541</x:v>
       </x:c>
       <x:c r="B485" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C485" s="1">
-        <x:v>3500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D485" s="1">
-        <x:v>44693946</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="E485" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F485" s="1">
-        <x:v>8000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G485" s="1">
-        <x:v>44705446</x:v>
+        <x:v>401022</x:v>
       </x:c>
     </x:row>
     <x:row r="486" spans="1:7">
@@ -14068,22 +14071,22 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C486" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D486" s="1">
-        <x:v>0</x:v>
+        <x:v>44693946</x:v>
       </x:c>
       <x:c r="E486" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F486" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G486" s="1">
-        <x:v>50</x:v>
+        <x:v>44705446</x:v>
       </x:c>
     </x:row>
     <x:row r="487" spans="1:7">
@@ -14091,13 +14094,13 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="B487" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C487" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D487" s="1">
-        <x:v>726377</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E487" s="1">
         <x:v>0</x:v>
@@ -14106,7 +14109,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G487" s="1">
-        <x:v>726377</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="488" spans="1:7">
@@ -14114,22 +14117,22 @@
         <x:v>544</x:v>
       </x:c>
       <x:c r="B488" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C488" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D488" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="E488" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F488" s="1">
-        <x:v>7600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G488" s="1">
-        <x:v>678549</x:v>
+        <x:v>726377</x:v>
       </x:c>
     </x:row>
     <x:row r="489" spans="1:7">
@@ -14137,22 +14140,22 @@
         <x:v>545</x:v>
       </x:c>
       <x:c r="B489" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C489" s="1">
-        <x:v>1000</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D489" s="1">
-        <x:v>0</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="E489" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F489" s="1">
-        <x:v>0</x:v>
+        <x:v>7600</x:v>
       </x:c>
       <x:c r="G489" s="1">
-        <x:v>1000</x:v>
+        <x:v>678549</x:v>
       </x:c>
     </x:row>
     <x:row r="490" spans="1:7">
@@ -14160,10 +14163,10 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="B490" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C490" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D490" s="1">
         <x:v>0</x:v>
@@ -14172,10 +14175,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F490" s="1">
-        <x:v>1250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G490" s="1">
-        <x:v>1300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="491" spans="1:7">
@@ -14183,7 +14186,7 @@
         <x:v>547</x:v>
       </x:c>
       <x:c r="B491" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C491" s="1">
         <x:v>50</x:v>
@@ -14195,10 +14198,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F491" s="1">
-        <x:v>0</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="G491" s="1">
-        <x:v>50</x:v>
+        <x:v>1300</x:v>
       </x:c>
     </x:row>
     <x:row r="492" spans="1:7">
@@ -14206,13 +14209,13 @@
         <x:v>548</x:v>
       </x:c>
       <x:c r="B492" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C492" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D492" s="1">
-        <x:v>120404787</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E492" s="1">
         <x:v>0</x:v>
@@ -14221,7 +14224,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G492" s="1">
-        <x:v>120406787</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="493" spans="1:7">
@@ -14229,13 +14232,13 @@
         <x:v>549</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C493" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D493" s="1">
-        <x:v>442806</x:v>
+        <x:v>120404787</x:v>
       </x:c>
       <x:c r="E493" s="1">
         <x:v>0</x:v>
@@ -14244,7 +14247,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G493" s="1">
-        <x:v>442806</x:v>
+        <x:v>120406787</x:v>
       </x:c>
     </x:row>
     <x:row r="494" spans="1:7">
@@ -14252,22 +14255,22 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="B494" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C494" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D494" s="1">
-        <x:v>0</x:v>
+        <x:v>442806</x:v>
       </x:c>
       <x:c r="E494" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F494" s="1">
-        <x:v>3333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G494" s="1">
-        <x:v>4333</x:v>
+        <x:v>442806</x:v>
       </x:c>
     </x:row>
     <x:row r="495" spans="1:7">
@@ -14275,10 +14278,10 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B495" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C495" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D495" s="1">
         <x:v>0</x:v>
@@ -14287,10 +14290,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F495" s="1">
-        <x:v>0</x:v>
+        <x:v>3333</x:v>
       </x:c>
       <x:c r="G495" s="1">
-        <x:v>50</x:v>
+        <x:v>4333</x:v>
       </x:c>
     </x:row>
     <x:row r="496" spans="1:7">
@@ -14298,7 +14301,7 @@
         <x:v>552</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C496" s="1">
         <x:v>50</x:v>
@@ -14321,10 +14324,10 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B497" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C497" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D497" s="1">
         <x:v>0</x:v>
@@ -14336,7 +14339,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G497" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="498" spans="1:7">
@@ -14344,10 +14347,10 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="B498" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C498" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D498" s="1">
         <x:v>0</x:v>
@@ -14356,10 +14359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F498" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G498" s="1">
-        <x:v>1050</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="499" spans="1:7">
@@ -14367,10 +14370,10 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B499" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C499" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D499" s="1">
         <x:v>0</x:v>
@@ -14379,10 +14382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F499" s="1">
-        <x:v>2700</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G499" s="1">
-        <x:v>5400</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="500" spans="1:7">
@@ -14390,10 +14393,10 @@
         <x:v>556</x:v>
       </x:c>
       <x:c r="B500" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C500" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D500" s="1">
         <x:v>0</x:v>
@@ -14402,10 +14405,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F500" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G500" s="1">
-        <x:v>50</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="501" spans="1:7">
@@ -14413,7 +14416,7 @@
         <x:v>557</x:v>
       </x:c>
       <x:c r="B501" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C501" s="1">
         <x:v>50</x:v>
@@ -14425,10 +14428,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F501" s="1">
-        <x:v>12000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G501" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="502" spans="1:7">
@@ -14436,7 +14439,7 @@
         <x:v>558</x:v>
       </x:c>
       <x:c r="B502" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C502" s="1">
         <x:v>50</x:v>
@@ -14448,10 +14451,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F502" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G502" s="1">
-        <x:v>50</x:v>
+        <x:v>12050</x:v>
       </x:c>
     </x:row>
     <x:row r="503" spans="1:7">
@@ -14459,10 +14462,10 @@
         <x:v>559</x:v>
       </x:c>
       <x:c r="B503" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C503" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D503" s="1">
         <x:v>0</x:v>
@@ -14471,10 +14474,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F503" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G503" s="1">
-        <x:v>250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="504" spans="1:7">
@@ -14482,10 +14485,10 @@
         <x:v>560</x:v>
       </x:c>
       <x:c r="B504" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C504" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D504" s="1">
         <x:v>0</x:v>
@@ -14494,10 +14497,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F504" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G504" s="1">
-        <x:v>50</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="505" spans="1:7">
@@ -14505,7 +14508,7 @@
         <x:v>561</x:v>
       </x:c>
       <x:c r="B505" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C505" s="1">
         <x:v>50</x:v>
@@ -14517,10 +14520,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F505" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G505" s="1">
-        <x:v>2750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="506" spans="1:7">
@@ -14528,10 +14531,10 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B506" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C506" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D506" s="1">
         <x:v>0</x:v>
@@ -14540,10 +14543,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F506" s="1">
-        <x:v>4600</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G506" s="1">
-        <x:v>4600</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="507" spans="1:7">
@@ -14551,10 +14554,10 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C507" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D507" s="1">
         <x:v>0</x:v>
@@ -14563,10 +14566,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F507" s="1">
-        <x:v>0</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G507" s="1">
-        <x:v>50</x:v>
+        <x:v>4600</x:v>
       </x:c>
     </x:row>
     <x:row r="508" spans="1:7">
@@ -14574,7 +14577,7 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="B508" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C508" s="1">
         <x:v>50</x:v>
@@ -14597,7 +14600,7 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C509" s="1">
         <x:v>50</x:v>
@@ -14620,7 +14623,7 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="B510" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C510" s="1">
         <x:v>50</x:v>
@@ -14643,13 +14646,13 @@
         <x:v>567</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C511" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D511" s="1">
-        <x:v>282526</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E511" s="1">
         <x:v>0</x:v>
@@ -14658,7 +14661,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G511" s="1">
-        <x:v>282526</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="512" spans="1:7">
@@ -14666,22 +14669,22 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="B512" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C512" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D512" s="1">
-        <x:v>0</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E512" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F512" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G512" s="1">
-        <x:v>1000</x:v>
+        <x:v>282526</x:v>
       </x:c>
     </x:row>
     <x:row r="513" spans="1:7">
@@ -14689,10 +14692,10 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C513" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D513" s="1">
         <x:v>0</x:v>
@@ -14701,10 +14704,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F513" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G513" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="514" spans="1:7">
@@ -14712,22 +14715,22 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="B514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C514" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D514" s="1">
-        <x:v>116161</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E514" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F514" s="1">
-        <x:v>4500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G514" s="1">
-        <x:v>124661</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="515" spans="1:7">
@@ -14735,22 +14738,22 @@
         <x:v>571</x:v>
       </x:c>
       <x:c r="B515" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C515" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D515" s="1">
-        <x:v>0</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="E515" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F515" s="1">
-        <x:v>0</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G515" s="1">
-        <x:v>50</x:v>
+        <x:v>124661</x:v>
       </x:c>
     </x:row>
     <x:row r="516" spans="1:7">
@@ -14758,7 +14761,7 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="B516" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C516" s="1">
         <x:v>50</x:v>
@@ -14781,7 +14784,7 @@
         <x:v>573</x:v>
       </x:c>
       <x:c r="B517" s="1" t="s">
-        <x:v>574</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C517" s="1">
         <x:v>50</x:v>
@@ -14801,10 +14804,10 @@
     </x:row>
     <x:row r="518" spans="1:7">
       <x:c r="A518" s="1" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="B518" s="1" t="s">
         <x:v>575</x:v>
-      </x:c>
-      <x:c r="B518" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C518" s="1">
         <x:v>50</x:v>
@@ -14827,22 +14830,22 @@
         <x:v>576</x:v>
       </x:c>
       <x:c r="B519" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C519" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D519" s="1">
-        <x:v>2997852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E519" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F519" s="1">
-        <x:v>6800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G519" s="1">
-        <x:v>3006652</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="520" spans="1:7">
@@ -14850,22 +14853,22 @@
         <x:v>577</x:v>
       </x:c>
       <x:c r="B520" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C520" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D520" s="1">
-        <x:v>14446984</x:v>
+        <x:v>2997852</x:v>
       </x:c>
       <x:c r="E520" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F520" s="1">
-        <x:v>0</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="G520" s="1">
-        <x:v>14446984</x:v>
+        <x:v>3007652</x:v>
       </x:c>
     </x:row>
     <x:row r="521" spans="1:7">
@@ -14873,13 +14876,13 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B521" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C521" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D521" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E521" s="1">
         <x:v>0</x:v>
@@ -14888,7 +14891,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G521" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="522" spans="1:7">
@@ -14896,10 +14899,10 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C522" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D522" s="1">
         <x:v>0</x:v>
@@ -14908,10 +14911,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F522" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G522" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="523" spans="1:7">
@@ -14919,7 +14922,7 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B523" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C523" s="1">
         <x:v>0</x:v>
@@ -14931,10 +14934,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F523" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="G523" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="524" spans="1:7">
@@ -14942,10 +14945,10 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C524" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D524" s="1">
         <x:v>0</x:v>
@@ -14954,10 +14957,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F524" s="1">
-        <x:v>0</x:v>
+        <x:v>22334</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>50</x:v>
+        <x:v>22334</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -14965,10 +14968,10 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C525" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D525" s="1">
         <x:v>0</x:v>
@@ -14977,10 +14980,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F525" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G525" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:7">
@@ -14988,10 +14991,10 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C526" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D526" s="1">
         <x:v>0</x:v>
@@ -15000,10 +15003,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F526" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G526" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="527" spans="1:7">
@@ -15011,13 +15014,13 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B527" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C527" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D527" s="1">
-        <x:v>209387</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E527" s="1">
         <x:v>0</x:v>
@@ -15026,7 +15029,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G527" s="1">
-        <x:v>209387</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="528" spans="1:7">
@@ -15034,13 +15037,13 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="B528" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C528" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D528" s="1">
-        <x:v>0</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="E528" s="1">
         <x:v>0</x:v>
@@ -15049,7 +15052,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G528" s="1">
-        <x:v>50</x:v>
+        <x:v>209387</x:v>
       </x:c>
     </x:row>
     <x:row r="529" spans="1:7">
@@ -15057,13 +15060,13 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C529" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D529" s="1">
-        <x:v>257695</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E529" s="1">
         <x:v>0</x:v>
@@ -15072,7 +15075,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G529" s="1">
-        <x:v>257695</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="530" spans="1:7">
@@ -15080,22 +15083,22 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="B530" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C530" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D530" s="1">
-        <x:v>0</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="E530" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F530" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G530" s="1">
-        <x:v>3300</x:v>
+        <x:v>257695</x:v>
       </x:c>
     </x:row>
     <x:row r="531" spans="1:7">
@@ -15103,10 +15106,10 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="B531" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C531" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D531" s="1">
         <x:v>0</x:v>
@@ -15115,10 +15118,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F531" s="1">
-        <x:v>29800</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G531" s="1">
-        <x:v>34800</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="532" spans="1:7">
@@ -15126,10 +15129,10 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C532" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D532" s="1">
         <x:v>0</x:v>
@@ -15138,10 +15141,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F532" s="1">
-        <x:v>0</x:v>
+        <x:v>29800</x:v>
       </x:c>
       <x:c r="G532" s="1">
-        <x:v>50</x:v>
+        <x:v>34800</x:v>
       </x:c>
     </x:row>
     <x:row r="533" spans="1:7">
@@ -15149,7 +15152,7 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C533" s="1">
         <x:v>50</x:v>
@@ -15161,10 +15164,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F533" s="1">
-        <x:v>5600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G533" s="1">
-        <x:v>5650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="534" spans="1:7">
@@ -15172,10 +15175,10 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="B534" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C534" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D534" s="1">
         <x:v>0</x:v>
@@ -15184,10 +15187,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F534" s="1">
-        <x:v>0</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G534" s="1">
-        <x:v>2050</x:v>
+        <x:v>5650</x:v>
       </x:c>
     </x:row>
     <x:row r="535" spans="1:7">
@@ -15195,10 +15198,10 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B535" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C535" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D535" s="1">
         <x:v>0</x:v>
@@ -15207,10 +15210,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F535" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G535" s="1">
-        <x:v>3384</x:v>
+        <x:v>2050</x:v>
       </x:c>
     </x:row>
     <x:row r="536" spans="1:7">
@@ -15218,7 +15221,7 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C536" s="1">
         <x:v>50</x:v>
@@ -15230,10 +15233,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F536" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G536" s="1">
-        <x:v>50</x:v>
+        <x:v>3384</x:v>
       </x:c>
     </x:row>
     <x:row r="537" spans="1:7">
@@ -15241,22 +15244,22 @@
         <x:v>594</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C537" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D537" s="1">
-        <x:v>558813</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E537" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F537" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G537" s="1">
-        <x:v>559813</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="538" spans="1:7">
@@ -15264,22 +15267,22 @@
         <x:v>595</x:v>
       </x:c>
       <x:c r="B538" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C538" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D538" s="1">
-        <x:v>0</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E538" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F538" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G538" s="1">
-        <x:v>6650</x:v>
+        <x:v>559813</x:v>
       </x:c>
     </x:row>
     <x:row r="539" spans="1:7">
@@ -15287,22 +15290,22 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C539" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D539" s="1">
-        <x:v>8250000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E539" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F539" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G539" s="1">
-        <x:v>8250000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="540" spans="1:7">
@@ -15310,13 +15313,13 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C540" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D540" s="1">
-        <x:v>0</x:v>
+        <x:v>8250000</x:v>
       </x:c>
       <x:c r="E540" s="1">
         <x:v>0</x:v>
@@ -15325,7 +15328,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G540" s="1">
-        <x:v>50</x:v>
+        <x:v>8250000</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:7">
@@ -15333,22 +15336,22 @@
         <x:v>598</x:v>
       </x:c>
       <x:c r="B541" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C541" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D541" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E541" s="1">
-        <x:v>20483</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F541" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G541" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:7">
@@ -15356,22 +15359,22 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B542" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C542" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D542" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E542" s="1">
-        <x:v>0</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="F542" s="1">
-        <x:v>1089100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G542" s="1">
-        <x:v>1089150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="543" spans="1:7">
@@ -15379,22 +15382,22 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C543" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D543" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E543" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F543" s="1">
-        <x:v>0</x:v>
+        <x:v>1089100</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>1927706</x:v>
+        <x:v>1089150</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15402,13 +15405,13 @@
         <x:v>601</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C544" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D544" s="1">
-        <x:v>0</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="E544" s="1">
         <x:v>0</x:v>
@@ -15417,7 +15420,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>50</x:v>
+        <x:v>1927706</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">
@@ -15425,7 +15428,7 @@
         <x:v>602</x:v>
       </x:c>
       <x:c r="B545" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C545" s="1">
         <x:v>50</x:v>
@@ -15437,10 +15440,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F545" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G545" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="546" spans="1:7">
@@ -15448,7 +15451,7 @@
         <x:v>603</x:v>
       </x:c>
       <x:c r="B546" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C546" s="1">
         <x:v>50</x:v>
@@ -15460,10 +15463,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F546" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G546" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="547" spans="1:7">
@@ -15471,10 +15474,10 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C547" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D547" s="1">
         <x:v>0</x:v>
@@ -15483,10 +15486,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F547" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G547" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="548" spans="1:7">
@@ -15494,10 +15497,10 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="B548" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C548" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D548" s="1">
         <x:v>0</x:v>
@@ -15506,10 +15509,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F548" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G548" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="549" spans="1:7">
@@ -15517,7 +15520,7 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C549" s="1">
         <x:v>50</x:v>
@@ -15529,10 +15532,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F549" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G549" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="550" spans="1:7">
@@ -15540,22 +15543,22 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C550" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D550" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E550" s="1">
-        <x:v>817066</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F550" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G550" s="1">
-        <x:v>0</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="551" spans="1:7">
@@ -15563,22 +15566,22 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C551" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D551" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E551" s="1">
-        <x:v>0</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="F551" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -15586,7 +15589,7 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B552" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C552" s="1">
         <x:v>50</x:v>
@@ -15609,22 +15612,22 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B553" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C553" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D553" s="1">
-        <x:v>88256</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E553" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F553" s="1">
-        <x:v>14866</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G553" s="1">
-        <x:v>117122</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="554" spans="1:7">
@@ -15632,22 +15635,22 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C554" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D554" s="1">
-        <x:v>0</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="E554" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F554" s="1">
-        <x:v>0</x:v>
+        <x:v>14866</x:v>
       </x:c>
       <x:c r="G554" s="1">
-        <x:v>50</x:v>
+        <x:v>117122</x:v>
       </x:c>
     </x:row>
     <x:row r="555" spans="1:7">
@@ -15655,7 +15658,7 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B555" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C555" s="1">
         <x:v>50</x:v>
@@ -15678,7 +15681,7 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>614</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C556" s="1">
         <x:v>50</x:v>
@@ -15698,10 +15701,10 @@
     </x:row>
     <x:row r="557" spans="1:7">
       <x:c r="A557" s="1" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="B557" s="1" t="s">
         <x:v>615</x:v>
-      </x:c>
-      <x:c r="B557" s="1" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="C557" s="1">
         <x:v>50</x:v>
@@ -15724,10 +15727,10 @@
         <x:v>616</x:v>
       </x:c>
       <x:c r="B558" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C558" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D558" s="1">
         <x:v>0</x:v>
@@ -15736,10 +15739,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F558" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G558" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="559" spans="1:7">
@@ -15747,7 +15750,7 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C559" s="1">
         <x:v>0</x:v>
@@ -15759,10 +15762,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -15773,19 +15776,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C560" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D560" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E560" s="1">
-        <x:v>10041119</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F560" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G560" s="1">
-        <x:v>50</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="561" spans="1:7">
@@ -15793,7 +15796,7 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C561" s="1">
         <x:v>50</x:v>
@@ -15802,13 +15805,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E561" s="1">
-        <x:v>0</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="F561" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G561" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="562" spans="1:7">
@@ -15816,7 +15819,7 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B562" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C562" s="1">
         <x:v>50</x:v>
@@ -15828,10 +15831,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F562" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G562" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="563" spans="1:7">
@@ -15839,10 +15842,10 @@
         <x:v>621</x:v>
       </x:c>
       <x:c r="B563" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C563" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D563" s="1">
         <x:v>0</x:v>
@@ -15851,10 +15854,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F563" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G563" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="564" spans="1:7">
@@ -15862,10 +15865,10 @@
         <x:v>622</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C564" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D564" s="1">
         <x:v>0</x:v>
@@ -15874,10 +15877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F564" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G564" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="565" spans="1:7">
@@ -15885,7 +15888,7 @@
         <x:v>623</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>50</x:v>
@@ -15908,7 +15911,7 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>50</x:v>
@@ -15931,10 +15934,10 @@
         <x:v>625</x:v>
       </x:c>
       <x:c r="B567" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C567" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D567" s="1">
         <x:v>0</x:v>
@@ -15943,10 +15946,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F567" s="1">
-        <x:v>-19405</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G567" s="1">
-        <x:v>-19405</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="568" spans="1:7">
@@ -15954,22 +15957,22 @@
         <x:v>626</x:v>
       </x:c>
       <x:c r="B568" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C568" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D568" s="1">
-        <x:v>1491280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E568" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F568" s="1">
-        <x:v>0</x:v>
+        <x:v>-19405</x:v>
       </x:c>
       <x:c r="G568" s="1">
-        <x:v>1491280</x:v>
+        <x:v>-19405</x:v>
       </x:c>
     </x:row>
     <x:row r="569" spans="1:7">
@@ -15977,22 +15980,22 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C569" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D569" s="1">
-        <x:v>0</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="E569" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F569" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G569" s="1">
-        <x:v>500</x:v>
+        <x:v>1491280</x:v>
       </x:c>
     </x:row>
     <x:row r="570" spans="1:7">
@@ -16000,10 +16003,10 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C570" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D570" s="1">
         <x:v>0</x:v>
@@ -16012,10 +16015,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F570" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G570" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="571" spans="1:7">
@@ -16023,7 +16026,7 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B571" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C571" s="1">
         <x:v>50</x:v>
@@ -16035,10 +16038,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F571" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G571" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="572" spans="1:7">
@@ -16046,7 +16049,7 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="B572" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C572" s="1">
         <x:v>50</x:v>
@@ -16058,10 +16061,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F572" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -16069,7 +16072,7 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C573" s="1">
         <x:v>50</x:v>
@@ -16081,10 +16084,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F573" s="1">
-        <x:v>1287</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G573" s="1">
-        <x:v>1337</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="574" spans="1:7">
@@ -16092,10 +16095,10 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C574" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D574" s="1">
         <x:v>0</x:v>
@@ -16104,10 +16107,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F574" s="1">
-        <x:v>6697</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G574" s="1">
-        <x:v>6697</x:v>
+        <x:v>1337</x:v>
       </x:c>
     </x:row>
     <x:row r="575" spans="1:7">
@@ -16115,10 +16118,10 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="B575" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C575" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D575" s="1">
         <x:v>0</x:v>
@@ -16127,10 +16130,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F575" s="1">
-        <x:v>0</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="G575" s="1">
-        <x:v>50</x:v>
+        <x:v>6697</x:v>
       </x:c>
     </x:row>
     <x:row r="576" spans="1:7">
@@ -16138,10 +16141,10 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="B576" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C576" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D576" s="1">
         <x:v>0</x:v>
@@ -16150,10 +16153,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F576" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G576" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="577" spans="1:7">
@@ -16161,7 +16164,7 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B577" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C577" s="1">
         <x:v>0</x:v>
@@ -16173,10 +16176,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F577" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="G577" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="578" spans="1:7">
@@ -16184,10 +16187,10 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="B578" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C578" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D578" s="1">
         <x:v>0</x:v>
@@ -16196,10 +16199,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F578" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G578" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="579" spans="1:7">
@@ -16207,7 +16210,7 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B579" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C579" s="1">
         <x:v>50</x:v>
@@ -16230,7 +16233,7 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C580" s="1">
         <x:v>50</x:v>
@@ -16253,22 +16256,22 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B581" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C581" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D581" s="1">
-        <x:v>1400000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E581" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F581" s="1">
-        <x:v>7000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G581" s="1">
-        <x:v>1409500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="582" spans="1:7">
@@ -16276,22 +16279,22 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C582" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D582" s="1">
-        <x:v>0</x:v>
+        <x:v>1400000</x:v>
       </x:c>
       <x:c r="E582" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F582" s="1">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G582" s="1">
-        <x:v>50</x:v>
+        <x:v>1409500</x:v>
       </x:c>
     </x:row>
     <x:row r="583" spans="1:7">
@@ -16299,10 +16302,10 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="B583" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C583" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D583" s="1">
         <x:v>0</x:v>
@@ -16311,10 +16314,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F583" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G583" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="584" spans="1:7">
@@ -16322,10 +16325,10 @@
         <x:v>642</x:v>
       </x:c>
       <x:c r="B584" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C584" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D584" s="1">
         <x:v>0</x:v>
@@ -16337,7 +16340,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G584" s="1">
-        <x:v>1550</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:7">
@@ -16345,7 +16348,7 @@
         <x:v>643</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C585" s="1">
         <x:v>50</x:v>
@@ -16357,10 +16360,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -16368,7 +16371,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>50</x:v>
@@ -16391,7 +16394,7 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C587" s="1">
         <x:v>50</x:v>
@@ -16414,7 +16417,7 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C588" s="1">
         <x:v>50</x:v>
@@ -16437,7 +16440,7 @@
         <x:v>647</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C589" s="1">
         <x:v>50</x:v>
@@ -16460,13 +16463,13 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C590" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D590" s="1">
-        <x:v>275541</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E590" s="1">
         <x:v>0</x:v>
@@ -16475,7 +16478,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G590" s="1">
-        <x:v>275541</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="591" spans="1:7">
@@ -16483,22 +16486,22 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C591" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D591" s="1">
-        <x:v>0</x:v>
+        <x:v>275541</x:v>
       </x:c>
       <x:c r="E591" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F591" s="1">
-        <x:v>81050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G591" s="1">
-        <x:v>81050</x:v>
+        <x:v>275541</x:v>
       </x:c>
     </x:row>
     <x:row r="592" spans="1:7">
@@ -16506,10 +16509,10 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C592" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D592" s="1">
         <x:v>0</x:v>
@@ -16518,10 +16521,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F592" s="1">
-        <x:v>0</x:v>
+        <x:v>81050</x:v>
       </x:c>
       <x:c r="G592" s="1">
-        <x:v>50</x:v>
+        <x:v>81050</x:v>
       </x:c>
     </x:row>
     <x:row r="593" spans="1:7">
@@ -16529,7 +16532,7 @@
         <x:v>651</x:v>
       </x:c>
       <x:c r="B593" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C593" s="1">
         <x:v>50</x:v>
@@ -16552,10 +16555,10 @@
         <x:v>652</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C594" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D594" s="1">
         <x:v>0</x:v>
@@ -16567,7 +16570,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G594" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="595" spans="1:7">
@@ -16575,10 +16578,10 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C595" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D595" s="1">
         <x:v>0</x:v>
@@ -16590,7 +16593,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G595" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
     </x:row>
     <x:row r="596" spans="1:7">
@@ -16598,7 +16601,7 @@
         <x:v>654</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C596" s="1">
         <x:v>50</x:v>
@@ -16610,10 +16613,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F596" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G596" s="1">
-        <x:v>14050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="597" spans="1:7">
@@ -16621,10 +16624,10 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B597" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C597" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D597" s="1">
         <x:v>0</x:v>
@@ -16633,10 +16636,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F597" s="1">
-        <x:v>2700</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G597" s="1">
-        <x:v>2700</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="598" spans="1:7">
@@ -16644,7 +16647,7 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C598" s="1">
         <x:v>0</x:v>
@@ -16656,10 +16659,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F598" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G598" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="599" spans="1:7">
@@ -16667,27 +16670,27 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C599" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D599" s="1">
-        <x:v>14446984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E599" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F599" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G599" s="1">
-        <x:v>14446984</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="600" spans="1:7">
       <x:c r="A600" s="1" t="s">
-        <x:v>657</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
         <x:v>106</x:v>
@@ -16713,13 +16716,13 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C601" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D601" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E601" s="1">
         <x:v>0</x:v>
@@ -16728,7 +16731,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G601" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:7">
@@ -16736,22 +16739,22 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C602" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D602" s="1">
-        <x:v>2470488</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E602" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F602" s="1">
-        <x:v>11834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>2494372</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -16759,22 +16762,22 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C603" s="1">
-        <x:v>100</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="D603" s="1">
-        <x:v>0</x:v>
+        <x:v>2470488</x:v>
       </x:c>
       <x:c r="E603" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F603" s="1">
-        <x:v>0</x:v>
+        <x:v>11834</x:v>
       </x:c>
       <x:c r="G603" s="1">
-        <x:v>100</x:v>
+        <x:v>2494372</x:v>
       </x:c>
     </x:row>
     <x:row r="604" spans="1:7">
@@ -16782,10 +16785,10 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C604" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D604" s="1">
         <x:v>0</x:v>
@@ -16797,7 +16800,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G604" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="605" spans="1:7">
@@ -16805,7 +16808,7 @@
         <x:v>662</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>50</x:v>
@@ -16831,7 +16834,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D606" s="1">
         <x:v>0</x:v>
@@ -16840,10 +16843,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -16851,10 +16854,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C607" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D607" s="1">
         <x:v>0</x:v>
@@ -16863,10 +16866,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F607" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G607" s="1">
-        <x:v>2550</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="608" spans="1:7">
@@ -16874,7 +16877,7 @@
         <x:v>665</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C608" s="1">
         <x:v>50</x:v>
@@ -16886,10 +16889,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F608" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G608" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="609" spans="1:7">
@@ -16897,7 +16900,7 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B609" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C609" s="1">
         <x:v>50</x:v>
@@ -16920,7 +16923,7 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C610" s="1">
         <x:v>50</x:v>
@@ -16943,7 +16946,7 @@
         <x:v>668</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C611" s="1">
         <x:v>50</x:v>
@@ -16966,22 +16969,22 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C612" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D612" s="1">
-        <x:v>3975320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E612" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F612" s="1">
-        <x:v>6634</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G612" s="1">
-        <x:v>3982954</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="613" spans="1:7">
@@ -16989,22 +16992,22 @@
         <x:v>670</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C613" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D613" s="1">
-        <x:v>0</x:v>
+        <x:v>3975320</x:v>
       </x:c>
       <x:c r="E613" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F613" s="1">
-        <x:v>22000</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G613" s="1">
-        <x:v>22000</x:v>
+        <x:v>3982954</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:7">
@@ -17012,10 +17015,10 @@
         <x:v>671</x:v>
       </x:c>
       <x:c r="B614" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C614" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D614" s="1">
         <x:v>0</x:v>
@@ -17024,10 +17027,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F614" s="1">
-        <x:v>5800</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G614" s="1">
-        <x:v>5850</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="615" spans="1:7">
@@ -17035,7 +17038,7 @@
         <x:v>672</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>673</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C615" s="1">
         <x:v>50</x:v>
@@ -17047,21 +17050,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
       <x:c r="A616" s="1" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="B616" s="1" t="s">
         <x:v>674</x:v>
       </x:c>
-      <x:c r="B616" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C616" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D616" s="1">
         <x:v>0</x:v>
@@ -17070,10 +17073,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -17081,10 +17084,10 @@
         <x:v>675</x:v>
       </x:c>
       <x:c r="B617" s="1" t="s">
-        <x:v>676</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C617" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D617" s="1">
         <x:v>0</x:v>
@@ -17093,18 +17096,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F617" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G617" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="618" spans="1:7">
       <x:c r="A618" s="1" t="s">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c r="B618" s="1" t="s">
         <x:v>677</x:v>
-      </x:c>
-      <x:c r="B618" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C618" s="1">
         <x:v>50</x:v>
@@ -17127,7 +17130,7 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="B619" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C619" s="1">
         <x:v>50</x:v>
@@ -17147,7 +17150,7 @@
     </x:row>
     <x:row r="620" spans="1:7">
       <x:c r="A620" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
         <x:v>97</x:v>
@@ -17173,7 +17176,7 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C621" s="1">
         <x:v>50</x:v>
@@ -17196,7 +17199,7 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C622" s="1">
         <x:v>50</x:v>
@@ -17219,10 +17222,10 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C623" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D623" s="1">
         <x:v>0</x:v>
@@ -17231,10 +17234,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F623" s="1">
-        <x:v>68600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G623" s="1">
-        <x:v>71150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="624" spans="1:7">
@@ -17242,10 +17245,10 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C624" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D624" s="1">
         <x:v>0</x:v>
@@ -17254,10 +17257,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F624" s="1">
-        <x:v>0</x:v>
+        <x:v>68600</x:v>
       </x:c>
       <x:c r="G624" s="1">
-        <x:v>50</x:v>
+        <x:v>71150</x:v>
       </x:c>
     </x:row>
     <x:row r="625" spans="1:7">
@@ -17265,7 +17268,7 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C625" s="1">
         <x:v>50</x:v>
@@ -17288,10 +17291,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17300,10 +17303,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17311,10 +17314,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17323,10 +17326,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>58000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>58050</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -17334,10 +17337,10 @@
         <x:v>686</x:v>
       </x:c>
       <x:c r="B628" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C628" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D628" s="1">
         <x:v>0</x:v>
@@ -17346,10 +17349,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F628" s="1">
-        <x:v>1666</x:v>
+        <x:v>58000</x:v>
       </x:c>
       <x:c r="G628" s="1">
-        <x:v>3716</x:v>
+        <x:v>58050</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:7">
@@ -17357,10 +17360,10 @@
         <x:v>687</x:v>
       </x:c>
       <x:c r="B629" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C629" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D629" s="1">
         <x:v>0</x:v>
@@ -17369,10 +17372,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F629" s="1">
-        <x:v>1668</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="G629" s="1">
-        <x:v>1668</x:v>
+        <x:v>3716</x:v>
       </x:c>
     </x:row>
     <x:row r="630" spans="1:7">
@@ -17380,10 +17383,10 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C630" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D630" s="1">
         <x:v>0</x:v>
@@ -17392,10 +17395,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F630" s="1">
-        <x:v>0</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G630" s="1">
-        <x:v>50</x:v>
+        <x:v>1668</x:v>
       </x:c>
     </x:row>
     <x:row r="631" spans="1:7">
@@ -17403,13 +17406,13 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C631" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D631" s="1">
-        <x:v>52520</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E631" s="1">
         <x:v>0</x:v>
@@ -17418,7 +17421,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>52570</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -17426,22 +17429,22 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D632" s="1">
-        <x:v>0</x:v>
+        <x:v>52520</x:v>
       </x:c>
       <x:c r="E632" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>30600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>33550</x:v>
+        <x:v>52570</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17449,10 +17452,10 @@
         <x:v>691</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C633" s="1">
-        <x:v>2550</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D633" s="1">
         <x:v>0</x:v>
@@ -17461,10 +17464,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F633" s="1">
-        <x:v>0</x:v>
+        <x:v>30600</x:v>
       </x:c>
       <x:c r="G633" s="1">
-        <x:v>2550</x:v>
+        <x:v>33550</x:v>
       </x:c>
     </x:row>
     <x:row r="634" spans="1:7">
@@ -17472,22 +17475,22 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C634" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D634" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E634" s="1">
-        <x:v>56045</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F634" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G634" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="635" spans="1:7">
@@ -17504,7 +17507,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E635" s="1">
-        <x:v>0</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="F635" s="1">
         <x:v>0</x:v>
@@ -17518,10 +17521,10 @@
         <x:v>694</x:v>
       </x:c>
       <x:c r="B636" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C636" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D636" s="1">
         <x:v>0</x:v>
@@ -17533,7 +17536,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G636" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="637" spans="1:7">
@@ -17541,10 +17544,10 @@
         <x:v>695</x:v>
       </x:c>
       <x:c r="B637" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C637" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D637" s="1">
         <x:v>0</x:v>
@@ -17556,7 +17559,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G637" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="638" spans="1:7">
@@ -17564,10 +17567,10 @@
         <x:v>696</x:v>
       </x:c>
       <x:c r="B638" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C638" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D638" s="1">
         <x:v>0</x:v>
@@ -17576,33 +17579,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F638" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G638" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="639" spans="1:7">
       <x:c r="A639" s="1" t="s">
-        <x:v>696</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C639" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D639" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E639" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F639" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -17616,7 +17619,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D640" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E640" s="1">
         <x:v>0</x:v>
@@ -17625,7 +17628,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G640" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:7">
@@ -17633,13 +17636,13 @@
         <x:v>698</x:v>
       </x:c>
       <x:c r="B641" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C641" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D641" s="1">
-        <x:v>0</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="E641" s="1">
         <x:v>0</x:v>
@@ -17648,7 +17651,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G641" s="1">
-        <x:v>50</x:v>
+        <x:v>852561</x:v>
       </x:c>
     </x:row>
     <x:row r="642" spans="1:7">
@@ -17656,7 +17659,7 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C642" s="1">
         <x:v>50</x:v>
@@ -17679,13 +17682,13 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="B643" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C643" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D643" s="1">
-        <x:v>2200000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E643" s="1">
         <x:v>0</x:v>
@@ -17694,7 +17697,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G643" s="1">
-        <x:v>2200000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="644" spans="1:7">
@@ -17702,13 +17705,13 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>0</x:v>
+        <x:v>2200000</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
@@ -17717,7 +17720,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>50</x:v>
+        <x:v>2200000</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17725,7 +17728,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C645" s="1">
         <x:v>50</x:v>
@@ -17748,7 +17751,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C646" s="1">
         <x:v>50</x:v>
@@ -17771,10 +17774,10 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="B647" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C647" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D647" s="1">
         <x:v>0</x:v>
@@ -17786,7 +17789,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G647" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="648" spans="1:7">
@@ -17794,10 +17797,10 @@
         <x:v>705</x:v>
       </x:c>
       <x:c r="B648" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C648" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D648" s="1">
         <x:v>0</x:v>
@@ -17809,7 +17812,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G648" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="649" spans="1:7">
@@ -17817,10 +17820,10 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B649" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C649" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D649" s="1">
         <x:v>0</x:v>
@@ -17832,7 +17835,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G649" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:7">
@@ -17840,10 +17843,10 @@
         <x:v>707</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C650" s="1">
-        <x:v>1050</x:v>
+        <x:v>10050</x:v>
       </x:c>
       <x:c r="D650" s="1">
         <x:v>0</x:v>
@@ -17852,10 +17855,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F650" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G650" s="1">
-        <x:v>2717</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:7">
@@ -17863,10 +17866,10 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C651" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D651" s="1">
         <x:v>0</x:v>
@@ -17875,10 +17878,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F651" s="1">
-        <x:v>0</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G651" s="1">
-        <x:v>50</x:v>
+        <x:v>2717</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:7">
@@ -17886,22 +17889,22 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C652" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D652" s="1">
-        <x:v>111599</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E652" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F652" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>114899</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -17909,22 +17912,22 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D653" s="1">
-        <x:v>0</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="E653" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F653" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>50</x:v>
+        <x:v>114899</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
@@ -17932,7 +17935,7 @@
         <x:v>711</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C654" s="1">
         <x:v>50</x:v>
@@ -17952,16 +17955,16 @@
     </x:row>
     <x:row r="655" spans="1:7">
       <x:c r="A655" s="1" t="s">
-        <x:v>711</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C655" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D655" s="1">
-        <x:v>113120</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E655" s="1">
         <x:v>0</x:v>
@@ -17970,7 +17973,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G655" s="1">
-        <x:v>113120</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="656" spans="1:7">
@@ -17978,13 +17981,13 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C656" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>0</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
@@ -17993,7 +17996,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>50</x:v>
+        <x:v>113120</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -18001,22 +18004,22 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C657" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D657" s="1">
-        <x:v>10046680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E657" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F657" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G657" s="1">
-        <x:v>10048730</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:7">
@@ -18024,22 +18027,22 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B658" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C658" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D658" s="1">
-        <x:v>2263800</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E658" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F658" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G658" s="1">
-        <x:v>2263850</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:7">
@@ -18047,13 +18050,13 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C659" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D659" s="1">
-        <x:v>0</x:v>
+        <x:v>2263800</x:v>
       </x:c>
       <x:c r="E659" s="1">
         <x:v>0</x:v>
@@ -18062,7 +18065,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G659" s="1">
-        <x:v>50</x:v>
+        <x:v>2263850</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:7">
@@ -18070,7 +18073,7 @@
         <x:v>716</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C660" s="1">
         <x:v>50</x:v>
@@ -18082,10 +18085,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F660" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18093,10 +18096,10 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
         <x:v>0</x:v>
@@ -18105,10 +18108,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F661" s="1">
-        <x:v>52333</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>58383</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18116,10 +18119,10 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D662" s="1">
         <x:v>0</x:v>
@@ -18128,10 +18131,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F662" s="1">
-        <x:v>0</x:v>
+        <x:v>52333</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>50</x:v>
+        <x:v>58383</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -18139,7 +18142,7 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C663" s="1">
         <x:v>50</x:v>
@@ -18162,10 +18165,10 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="B664" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C664" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D664" s="1">
         <x:v>0</x:v>
@@ -18174,10 +18177,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F664" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G664" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:7">
@@ -18185,22 +18188,22 @@
         <x:v>721</x:v>
       </x:c>
       <x:c r="B665" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C665" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D665" s="1">
-        <x:v>367531</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E665" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F665" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G665" s="1">
-        <x:v>367531</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:7">
@@ -18208,22 +18211,22 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C666" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D666" s="1">
-        <x:v>817169</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="E666" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F666" s="1">
-        <x:v>1668</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G666" s="1">
-        <x:v>820837</x:v>
+        <x:v>367531</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:7">
@@ -18231,22 +18234,22 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C667" s="1">
-        <x:v>11050</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D667" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E667" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F667" s="1">
-        <x:v>6242</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G667" s="1">
-        <x:v>17292</x:v>
+        <x:v>820837</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:7">
@@ -18254,10 +18257,10 @@
         <x:v>724</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C668" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D668" s="1">
         <x:v>0</x:v>
@@ -18266,10 +18269,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F668" s="1">
-        <x:v>0</x:v>
+        <x:v>6242</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>50</x:v>
+        <x:v>17292</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -18277,7 +18280,7 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C669" s="1">
         <x:v>50</x:v>
@@ -18300,10 +18303,10 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C670" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D670" s="1">
         <x:v>0</x:v>
@@ -18312,10 +18315,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F670" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G670" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="671" spans="1:7">
@@ -18323,10 +18326,10 @@
         <x:v>727</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C671" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D671" s="1">
         <x:v>0</x:v>
@@ -18335,10 +18338,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F671" s="1">
-        <x:v>25000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>25050</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">
@@ -18346,7 +18349,7 @@
         <x:v>728</x:v>
       </x:c>
       <x:c r="B672" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C672" s="1">
         <x:v>50</x:v>
@@ -18358,10 +18361,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F672" s="1">
-        <x:v>0</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G672" s="1">
-        <x:v>50</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="673" spans="1:7">
@@ -18369,22 +18372,22 @@
         <x:v>729</x:v>
       </x:c>
       <x:c r="B673" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C673" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D673" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E673" s="1">
-        <x:v>1531015</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F673" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G673" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="674" spans="1:7">
@@ -18392,22 +18395,22 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C674" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D674" s="1">
-        <x:v>157560</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E674" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F674" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G674" s="1">
-        <x:v>157610</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="675" spans="1:7">
@@ -18415,13 +18418,13 @@
         <x:v>731</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C675" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D675" s="1">
-        <x:v>0</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="E675" s="1">
         <x:v>0</x:v>
@@ -18430,7 +18433,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G675" s="1">
-        <x:v>50</x:v>
+        <x:v>157610</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:7">
@@ -18438,13 +18441,13 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B676" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C676" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D676" s="1">
-        <x:v>5583432</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E676" s="1">
         <x:v>0</x:v>
@@ -18453,7 +18456,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G676" s="1">
-        <x:v>5584432</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="677" spans="1:7">
@@ -18461,13 +18464,13 @@
         <x:v>733</x:v>
       </x:c>
       <x:c r="B677" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C677" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D677" s="1">
-        <x:v>0</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E677" s="1">
         <x:v>0</x:v>
@@ -18476,7 +18479,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>50</x:v>
+        <x:v>5584432</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
@@ -18484,22 +18487,22 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B678" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C678" s="1">
-        <x:v>24050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D678" s="1">
-        <x:v>764206</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E678" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F678" s="1">
-        <x:v>20501</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G678" s="1">
-        <x:v>808757</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="679" spans="1:7">
@@ -18507,22 +18510,22 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C679" s="1">
-        <x:v>0</x:v>
+        <x:v>24050</x:v>
       </x:c>
       <x:c r="D679" s="1">
-        <x:v>0</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="E679" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F679" s="1">
-        <x:v>2700</x:v>
+        <x:v>20501</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>2700</x:v>
+        <x:v>808757</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
@@ -18530,22 +18533,22 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C680" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D680" s="1">
-        <x:v>1543316</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E680" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -18553,22 +18556,22 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D681" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E681" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
-        <x:v>14500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>14550</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -18576,7 +18579,7 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C682" s="1">
         <x:v>50</x:v>
@@ -18588,10 +18591,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>50</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -18599,7 +18602,7 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C683" s="1">
         <x:v>50</x:v>
@@ -18622,13 +18625,13 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C684" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D684" s="1">
-        <x:v>107353</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E684" s="1">
         <x:v>0</x:v>
@@ -18637,7 +18640,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>107403</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -18645,22 +18648,22 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C685" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D685" s="1">
-        <x:v>0</x:v>
+        <x:v>107353</x:v>
       </x:c>
       <x:c r="E685" s="1">
-        <x:v>10135449</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>0</x:v>
+        <x:v>107403</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -18668,22 +18671,22 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D686" s="1">
-        <x:v>51510</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E686" s="1">
-        <x:v>0</x:v>
+        <x:v>10135449</x:v>
       </x:c>
       <x:c r="F686" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>54844</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -18691,22 +18694,22 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C687" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D687" s="1">
-        <x:v>0</x:v>
+        <x:v>51510</x:v>
       </x:c>
       <x:c r="E687" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F687" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>2500</x:v>
+        <x:v>54844</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
@@ -18714,13 +18717,13 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C688" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D688" s="1">
-        <x:v>106947</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E688" s="1">
         <x:v>0</x:v>
@@ -18729,7 +18732,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>106947</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
@@ -18737,22 +18740,22 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C689" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D689" s="1">
-        <x:v>0</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="E689" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F689" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G689" s="1">
-        <x:v>25050</x:v>
+        <x:v>106947</x:v>
       </x:c>
     </x:row>
     <x:row r="690" spans="1:7">
@@ -18760,22 +18763,22 @@
         <x:v>746</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>1050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D690" s="1">
-        <x:v>902176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E690" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>7000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>910226</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -18783,22 +18786,22 @@
         <x:v>747</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D691" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E691" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>25500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>25550</x:v>
+        <x:v>910226</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -18818,10 +18821,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>0</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>50</x:v>
+        <x:v>25550</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -18829,10 +18832,10 @@
         <x:v>749</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C693" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D693" s="1">
         <x:v>0</x:v>
@@ -18841,10 +18844,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F693" s="1">
-        <x:v>10500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>10500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
@@ -18852,7 +18855,7 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C694" s="1">
         <x:v>0</x:v>
@@ -18864,10 +18867,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F694" s="1">
-        <x:v>6200</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>6200</x:v>
+        <x:v>10500</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
@@ -18875,10 +18878,10 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C695" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D695" s="1">
         <x:v>0</x:v>
@@ -18887,10 +18890,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F695" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>50</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
@@ -18898,10 +18901,10 @@
         <x:v>752</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D696" s="1">
         <x:v>0</x:v>
@@ -18913,7 +18916,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -18921,10 +18924,10 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C697" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D697" s="1">
         <x:v>0</x:v>
@@ -18933,10 +18936,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F697" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>6650</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">
@@ -18944,22 +18947,22 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C698" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D698" s="1">
-        <x:v>1010142</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E698" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F698" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>1010142</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
@@ -18967,22 +18970,22 @@
         <x:v>755</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C699" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D699" s="1">
-        <x:v>0</x:v>
+        <x:v>1888055</x:v>
       </x:c>
       <x:c r="E699" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F699" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G699" s="1">
-        <x:v>5000</x:v>
+        <x:v>1888055</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:7">
@@ -18990,10 +18993,10 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C700" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D700" s="1">
         <x:v>0</x:v>
@@ -19002,10 +19005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F700" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
@@ -19013,10 +19016,10 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C701" s="1">
-        <x:v>6550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D701" s="1">
         <x:v>0</x:v>
@@ -19025,10 +19028,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>9850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
@@ -19036,10 +19039,10 @@
         <x:v>758</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C702" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D702" s="1">
         <x:v>0</x:v>
@@ -19048,10 +19051,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F702" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>50</x:v>
+        <x:v>9850</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
@@ -19059,7 +19062,7 @@
         <x:v>759</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C703" s="1">
         <x:v>50</x:v>
@@ -19082,10 +19085,10 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C704" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D704" s="1">
         <x:v>0</x:v>
@@ -19094,10 +19097,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>9550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
@@ -19105,10 +19108,10 @@
         <x:v>761</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D705" s="1">
         <x:v>0</x:v>
@@ -19117,10 +19120,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>2700</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>2700</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19128,10 +19131,10 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D706" s="1">
         <x:v>0</x:v>
@@ -19140,10 +19143,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -19151,10 +19154,10 @@
         <x:v>763</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D707" s="1">
         <x:v>0</x:v>
@@ -19163,33 +19166,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>9350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
       <x:c r="A708" s="1" t="s">
-        <x:v>763</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D708" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E708" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
@@ -19197,22 +19200,22 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D709" s="1">
-        <x:v>2572233</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E709" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>5500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>2577783</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -19220,22 +19223,22 @@
         <x:v>765</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C710" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D710" s="1">
-        <x:v>0</x:v>
+        <x:v>2572233</x:v>
       </x:c>
       <x:c r="E710" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>0</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>50</x:v>
+        <x:v>2577783</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
@@ -19243,7 +19246,7 @@
         <x:v>766</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C711" s="1">
         <x:v>50</x:v>
@@ -19255,10 +19258,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F711" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
@@ -19266,7 +19269,7 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C712" s="1">
         <x:v>50</x:v>
@@ -19278,10 +19281,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19289,10 +19292,10 @@
         <x:v>768</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D713" s="1">
         <x:v>0</x:v>
@@ -19301,10 +19304,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>3300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19315,7 +19318,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D714" s="1">
         <x:v>0</x:v>
@@ -19324,10 +19327,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>50</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19335,7 +19338,7 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C715" s="1">
         <x:v>50</x:v>
@@ -19347,10 +19350,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>5700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
@@ -19358,7 +19361,7 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C716" s="1">
         <x:v>50</x:v>
@@ -19370,10 +19373,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>0</x:v>
+        <x:v>5700</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19381,7 +19384,7 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C717" s="1">
         <x:v>50</x:v>
@@ -19404,22 +19407,22 @@
         <x:v>773</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C718" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D718" s="1">
-        <x:v>1892270</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E718" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F718" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>1909770</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
@@ -19427,13 +19430,13 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C719" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D719" s="1">
-        <x:v>0</x:v>
+        <x:v>1892270</x:v>
       </x:c>
       <x:c r="E719" s="1">
         <x:v>0</x:v>
@@ -19442,7 +19445,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G719" s="1">
-        <x:v>1000</x:v>
+        <x:v>1909770</x:v>
       </x:c>
     </x:row>
     <x:row r="720" spans="1:7">
@@ -19450,10 +19453,10 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D720" s="1">
         <x:v>0</x:v>
@@ -19462,10 +19465,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F720" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
@@ -19473,10 +19476,10 @@
         <x:v>776</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C721" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D721" s="1">
         <x:v>0</x:v>
@@ -19485,10 +19488,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F721" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
@@ -19496,10 +19499,10 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C722" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D722" s="1">
         <x:v>0</x:v>
@@ -19508,10 +19511,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F722" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
@@ -19519,13 +19522,13 @@
         <x:v>778</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D723" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E723" s="1">
         <x:v>0</x:v>
@@ -19534,7 +19537,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>40000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
@@ -19542,13 +19545,13 @@
         <x:v>779</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C724" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D724" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E724" s="1">
         <x:v>0</x:v>
@@ -19557,7 +19560,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>1000</x:v>
+        <x:v>40000</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
@@ -19565,10 +19568,10 @@
         <x:v>780</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D725" s="1">
         <x:v>0</x:v>
@@ -19580,7 +19583,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
@@ -19588,10 +19591,10 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C726" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D726" s="1">
         <x:v>0</x:v>
@@ -19600,10 +19603,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F726" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>5200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
@@ -19611,10 +19614,10 @@
         <x:v>782</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D727" s="1">
         <x:v>0</x:v>
@@ -19623,10 +19626,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F727" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
@@ -19634,7 +19637,7 @@
         <x:v>783</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C728" s="1">
         <x:v>50</x:v>
@@ -19657,7 +19660,7 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C729" s="1">
         <x:v>50</x:v>
@@ -19669,10 +19672,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F729" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">
@@ -19680,22 +19683,22 @@
         <x:v>785</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C730" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D730" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E730" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F730" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>3920589</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
@@ -19703,13 +19706,13 @@
         <x:v>786</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C731" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D731" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E731" s="1">
         <x:v>0</x:v>
@@ -19718,7 +19721,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>50</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
@@ -19726,10 +19729,10 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C732" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D732" s="1">
         <x:v>0</x:v>
@@ -19741,7 +19744,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
@@ -19749,10 +19752,10 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C733" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D733" s="1">
         <x:v>0</x:v>
@@ -19764,7 +19767,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G733" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:7">
@@ -19772,7 +19775,7 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C734" s="1">
         <x:v>50</x:v>
@@ -19795,10 +19798,10 @@
         <x:v>790</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>4500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19807,10 +19810,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F735" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>9334</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19818,10 +19821,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>1050</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19830,10 +19833,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>1050</x:v>
+        <x:v>9334</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
@@ -19844,7 +19847,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C737" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D737" s="1">
         <x:v>0</x:v>
@@ -19856,7 +19859,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G737" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="738" spans="1:7">
@@ -19864,7 +19867,7 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C738" s="1">
         <x:v>50</x:v>
@@ -19887,13 +19890,13 @@
         <x:v>794</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C739" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D739" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E739" s="1">
         <x:v>0</x:v>
@@ -19902,7 +19905,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G739" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:7">
@@ -19910,13 +19913,13 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>50</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D740" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E740" s="1">
         <x:v>0</x:v>
@@ -19925,7 +19928,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>50</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
@@ -19933,10 +19936,10 @@
         <x:v>796</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C741" s="1">
-        <x:v>19600</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D741" s="1">
         <x:v>0</x:v>
@@ -19945,10 +19948,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F741" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>36600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">
@@ -19956,10 +19959,10 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C742" s="1">
-        <x:v>50</x:v>
+        <x:v>19600</x:v>
       </x:c>
       <x:c r="D742" s="1">
         <x:v>0</x:v>
@@ -19968,10 +19971,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F742" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>50</x:v>
+        <x:v>36600</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
@@ -19979,7 +19982,7 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C743" s="1">
         <x:v>50</x:v>
@@ -20002,7 +20005,7 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C744" s="1">
         <x:v>50</x:v>
@@ -20025,13 +20028,13 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C745" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D745" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E745" s="1">
         <x:v>0</x:v>
@@ -20040,7 +20043,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G745" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:7">
@@ -20048,13 +20051,13 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D746" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E746" s="1">
         <x:v>0</x:v>
@@ -20063,7 +20066,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>50</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20071,10 +20074,10 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D747" s="1">
         <x:v>0</x:v>
@@ -20083,10 +20086,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F747" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>30000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">
@@ -20094,10 +20097,10 @@
         <x:v>803</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D748" s="1">
         <x:v>0</x:v>
@@ -20106,10 +20109,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F748" s="1">
-        <x:v>0</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>50</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
@@ -20117,10 +20120,10 @@
         <x:v>804</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C749" s="1">
-        <x:v>19050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D749" s="1">
         <x:v>0</x:v>
@@ -20129,10 +20132,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F749" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G749" s="1">
-        <x:v>21550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:7">
@@ -20140,10 +20143,10 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>3500</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20152,10 +20155,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F750" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>3500</x:v>
+        <x:v>21550</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
@@ -20163,10 +20166,10 @@
         <x:v>806</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20178,18 +20181,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
       <x:c r="A752" s="1" t="s">
-        <x:v>806</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20198,10 +20201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
@@ -20209,10 +20212,10 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20221,10 +20224,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
@@ -20232,10 +20235,10 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C754" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D754" s="1">
         <x:v>0</x:v>
@@ -20247,7 +20250,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
@@ -20255,10 +20258,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -20270,7 +20273,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
@@ -20278,10 +20281,10 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C756" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D756" s="1">
         <x:v>0</x:v>
@@ -20290,10 +20293,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F756" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">
@@ -20301,10 +20304,10 @@
         <x:v>811</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20313,10 +20316,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>5000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>5050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20324,7 +20327,7 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C758" s="1">
         <x:v>50</x:v>
@@ -20336,10 +20339,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
@@ -20347,10 +20350,10 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C759" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D759" s="1">
         <x:v>0</x:v>
@@ -20359,10 +20362,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F759" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
@@ -20370,10 +20373,10 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C760" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D760" s="1">
         <x:v>0</x:v>
@@ -20382,10 +20385,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F760" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
@@ -20393,7 +20396,7 @@
         <x:v>815</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C761" s="1">
         <x:v>50</x:v>
@@ -20416,13 +20419,13 @@
         <x:v>816</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C762" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D762" s="1">
-        <x:v>943006</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E762" s="1">
         <x:v>0</x:v>
@@ -20431,7 +20434,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>943056</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">
@@ -20439,13 +20442,13 @@
         <x:v>817</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C763" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D763" s="1">
-        <x:v>0</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="E763" s="1">
         <x:v>0</x:v>
@@ -20454,7 +20457,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G763" s="1">
-        <x:v>50</x:v>
+        <x:v>943056</x:v>
       </x:c>
     </x:row>
     <x:row r="764" spans="1:7">
@@ -20462,7 +20465,7 @@
         <x:v>818</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C764" s="1">
         <x:v>50</x:v>
@@ -20485,22 +20488,22 @@
         <x:v>819</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C765" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D765" s="1">
-        <x:v>476254</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E765" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F765" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G765" s="1">
-        <x:v>478754</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="766" spans="1:7">
@@ -20508,22 +20511,22 @@
         <x:v>820</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C766" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D766" s="1">
-        <x:v>0</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="E766" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>50</x:v>
+        <x:v>478754</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
@@ -20531,7 +20534,7 @@
         <x:v>821</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C767" s="1">
         <x:v>50</x:v>
@@ -20543,10 +20546,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F767" s="1">
-        <x:v>4999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G767" s="1">
-        <x:v>5049</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:7">
@@ -20554,10 +20557,10 @@
         <x:v>822</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C768" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D768" s="1">
         <x:v>0</x:v>
@@ -20566,10 +20569,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>16500</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>16500</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
@@ -20577,10 +20580,10 @@
         <x:v>823</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C769" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D769" s="1">
         <x:v>0</x:v>
@@ -20589,10 +20592,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F769" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G769" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:7">
@@ -20600,7 +20603,7 @@
         <x:v>824</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C770" s="1">
         <x:v>50</x:v>
@@ -20623,7 +20626,7 @@
         <x:v>825</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C771" s="1">
         <x:v>50</x:v>
@@ -20646,7 +20649,7 @@
         <x:v>826</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C772" s="1">
         <x:v>50</x:v>
@@ -20669,7 +20672,7 @@
         <x:v>827</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C773" s="1">
         <x:v>50</x:v>
@@ -20681,10 +20684,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F773" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G773" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="774" spans="1:7">
@@ -20692,7 +20695,7 @@
         <x:v>828</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C774" s="1">
         <x:v>50</x:v>
@@ -20704,10 +20707,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F774" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G774" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:7">
@@ -20715,10 +20718,10 @@
         <x:v>829</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C775" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D775" s="1">
         <x:v>0</x:v>
@@ -20727,10 +20730,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>37300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>48150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
@@ -20738,10 +20741,10 @@
         <x:v>830</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C776" s="1">
-        <x:v>0</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D776" s="1">
         <x:v>0</x:v>
@@ -20750,10 +20753,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>83</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>83</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
@@ -20761,10 +20764,10 @@
         <x:v>831</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C777" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D777" s="1">
         <x:v>0</x:v>
@@ -20773,10 +20776,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F777" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G777" s="1">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="778" spans="1:7">
@@ -20784,7 +20787,7 @@
         <x:v>832</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C778" s="1">
         <x:v>50</x:v>
@@ -20807,7 +20810,7 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C779" s="1">
         <x:v>50</x:v>
@@ -20830,10 +20833,10 @@
         <x:v>834</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C780" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D780" s="1">
         <x:v>0</x:v>
@@ -20842,10 +20845,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F780" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G780" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="781" spans="1:7">
@@ -20853,21 +20856,44 @@
         <x:v>835</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C781" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D781" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E781" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F781" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G781" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="782" spans="1:7">
+      <x:c r="A782" s="1" t="s">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c r="B782" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C781" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D781" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E781" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F781" s="1">
+      <x:c r="C782" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D782" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E782" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F782" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G781" s="1">
+      <x:c r="G782" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16693,7 +16693,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C600" s="1">
         <x:v>0</x:v>
@@ -16716,7 +16716,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C601" s="1">
         <x:v>0</x:v>
@@ -17153,10 +17153,10 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C620" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D620" s="1">
         <x:v>0</x:v>
@@ -17165,10 +17165,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F620" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G620" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="621" spans="1:7">
@@ -17176,10 +17176,10 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C621" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D621" s="1">
         <x:v>0</x:v>
@@ -17188,10 +17188,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F621" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G621" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="622" spans="1:7">
@@ -17590,22 +17590,22 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C639" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D639" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E639" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F639" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -17613,22 +17613,22 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C640" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D640" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E640" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F640" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G640" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -13528,7 +13528,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E462" s="1">
-        <x:v>54570</x:v>
+        <x:v>108100</x:v>
       </x:c>
       <x:c r="F462" s="1">
         <x:v>0</x:v>
@@ -16693,7 +16693,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C600" s="1">
         <x:v>0</x:v>
@@ -16716,7 +16716,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C601" s="1">
         <x:v>0</x:v>
@@ -17590,22 +17590,22 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C639" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D639" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E639" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F639" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -17613,22 +17613,22 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C640" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D640" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E640" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F640" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G640" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:7">
@@ -17958,13 +17958,13 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C655" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D655" s="1">
-        <x:v>0</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="E655" s="1">
         <x:v>0</x:v>
@@ -17973,7 +17973,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G655" s="1">
-        <x:v>50</x:v>
+        <x:v>113120</x:v>
       </x:c>
     </x:row>
     <x:row r="656" spans="1:7">
@@ -17981,13 +17981,13 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C656" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>113120</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
@@ -17996,7 +17996,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>113120</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -7062,7 +7062,7 @@
         <x:v>6050</x:v>
       </x:c>
       <x:c r="D181" s="1">
-        <x:v>113120</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E181" s="1">
         <x:v>0</x:v>
@@ -7071,7 +7071,7 @@
         <x:v>3332</x:v>
       </x:c>
       <x:c r="G181" s="1">
-        <x:v>122502</x:v>
+        <x:v>235622</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:7">
@@ -13502,7 +13502,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D461" s="1">
-        <x:v>65340</x:v>
+        <x:v>441577</x:v>
       </x:c>
       <x:c r="E461" s="1">
         <x:v>0</x:v>
@@ -13511,7 +13511,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G461" s="1">
-        <x:v>65340</x:v>
+        <x:v>441577</x:v>
       </x:c>
     </x:row>
     <x:row r="462" spans="1:7">
@@ -17153,10 +17153,10 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C620" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D620" s="1">
         <x:v>0</x:v>
@@ -17165,10 +17165,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F620" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G620" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="621" spans="1:7">
@@ -17176,10 +17176,10 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C621" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D621" s="1">
         <x:v>0</x:v>
@@ -17188,10 +17188,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F621" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G621" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="622" spans="1:7">
@@ -17435,7 +17435,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D632" s="1">
-        <x:v>52520</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="E632" s="1">
         <x:v>0</x:v>
@@ -17444,7 +17444,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>52570</x:v>
+        <x:v>105090</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17958,13 +17958,13 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C655" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D655" s="1">
-        <x:v>113120</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E655" s="1">
         <x:v>0</x:v>
@@ -17973,7 +17973,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G655" s="1">
-        <x:v>113120</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="656" spans="1:7">
@@ -17981,13 +17981,13 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C656" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
@@ -17996,7 +17996,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -18700,7 +18700,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D687" s="1">
-        <x:v>51510</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="E687" s="1">
         <x:v>0</x:v>
@@ -18709,7 +18709,7 @@
         <x:v>3334</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>54844</x:v>
+        <x:v>106354</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -13528,7 +13528,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E462" s="1">
-        <x:v>108100</x:v>
+        <x:v>161630</x:v>
       </x:c>
       <x:c r="F462" s="1">
         <x:v>0</x:v>
@@ -16693,7 +16693,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C600" s="1">
         <x:v>0</x:v>
@@ -16716,7 +16716,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C601" s="1">
         <x:v>0</x:v>
@@ -17153,10 +17153,10 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C620" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D620" s="1">
         <x:v>0</x:v>
@@ -17165,10 +17165,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F620" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G620" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="621" spans="1:7">
@@ -17176,10 +17176,10 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C621" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D621" s="1">
         <x:v>0</x:v>
@@ -17188,10 +17188,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F621" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G621" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="622" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -20189,10 +20189,10 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20201,10 +20201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
@@ -20212,10 +20212,10 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20224,10 +20224,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -10351,7 +10351,7 @@
         <x:v>12850</x:v>
       </x:c>
       <x:c r="D324" s="1">
-        <x:v>322059</x:v>
+        <x:v>1858047</x:v>
       </x:c>
       <x:c r="E324" s="1">
         <x:v>0</x:v>
@@ -10360,7 +10360,7 @@
         <x:v>35533</x:v>
       </x:c>
       <x:c r="G324" s="1">
-        <x:v>370442</x:v>
+        <x:v>1906430</x:v>
       </x:c>
     </x:row>
     <x:row r="325" spans="1:7">
@@ -13528,7 +13528,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E462" s="1">
-        <x:v>161630</x:v>
+        <x:v>215160</x:v>
       </x:c>
       <x:c r="F462" s="1">
         <x:v>0</x:v>
@@ -16693,7 +16693,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C600" s="1">
         <x:v>0</x:v>
@@ -16716,7 +16716,7 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C601" s="1">
         <x:v>0</x:v>
@@ -18654,7 +18654,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D685" s="1">
-        <x:v>107353</x:v>
+        <x:v>619349</x:v>
       </x:c>
       <x:c r="E685" s="1">
         <x:v>0</x:v>
@@ -18663,7 +18663,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>107403</x:v>
+        <x:v>619399</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -20189,10 +20189,10 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20201,10 +20201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
@@ -20212,10 +20212,10 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20224,10 +20224,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -1631,6 +1631,9 @@
   </x:si>
   <x:si>
     <x:t>MOLL, THOMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOODY, ASHLEY</x:t>
   </x:si>
   <x:si>
     <x:t>MOOLENAAR, JOHN MR.</x:t>
@@ -2595,8 +2598,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G782" totalsRowShown="0">
-  <x:autoFilter ref="A1:G782"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G783" totalsRowShown="0">
+  <x:autoFilter ref="A1:G783"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2898,7 +2901,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G782"/>
+  <x:dimension ref="A1:G783"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -9451,7 +9454,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C285" s="1">
-        <x:v>15300</x:v>
+        <x:v>20300</x:v>
       </x:c>
       <x:c r="D285" s="1">
         <x:v>0</x:v>
@@ -9463,7 +9466,7 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="G285" s="1">
-        <x:v>16550</x:v>
+        <x:v>21550</x:v>
       </x:c>
     </x:row>
     <x:row r="286" spans="1:7">
@@ -10440,7 +10443,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C328" s="1">
-        <x:v>2000</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D328" s="1">
         <x:v>0</x:v>
@@ -10452,7 +10455,7 @@
         <x:v>21000</x:v>
       </x:c>
       <x:c r="G328" s="1">
-        <x:v>23000</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="329" spans="1:7">
@@ -11498,7 +11501,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C374" s="1">
-        <x:v>14700</x:v>
+        <x:v>16700</x:v>
       </x:c>
       <x:c r="D374" s="1">
         <x:v>3848426</x:v>
@@ -11510,7 +11513,7 @@
         <x:v>20200</x:v>
       </x:c>
       <x:c r="G374" s="1">
-        <x:v>3883326</x:v>
+        <x:v>3885326</x:v>
       </x:c>
     </x:row>
     <x:row r="375" spans="1:7">
@@ -12418,7 +12421,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C414" s="1">
-        <x:v>17750</x:v>
+        <x:v>18750</x:v>
       </x:c>
       <x:c r="D414" s="1">
         <x:v>0</x:v>
@@ -12430,7 +12433,7 @@
         <x:v>25450</x:v>
       </x:c>
       <x:c r="G414" s="1">
-        <x:v>43200</x:v>
+        <x:v>44200</x:v>
       </x:c>
     </x:row>
     <x:row r="415" spans="1:7">
@@ -13660,7 +13663,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C468" s="1">
-        <x:v>1050</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D468" s="1">
         <x:v>92320</x:v>
@@ -13672,7 +13675,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G468" s="1">
-        <x:v>93370</x:v>
+        <x:v>95870</x:v>
       </x:c>
     </x:row>
     <x:row r="469" spans="1:7">
@@ -14002,10 +14005,10 @@
         <x:v>539</x:v>
       </x:c>
       <x:c r="B483" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C483" s="1">
-        <x:v>5050</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D483" s="1">
         <x:v>0</x:v>
@@ -14014,10 +14017,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F483" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G483" s="1">
-        <x:v>6050</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="484" spans="1:7">
@@ -14025,10 +14028,10 @@
         <x:v>540</x:v>
       </x:c>
       <x:c r="B484" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C484" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
       <x:c r="D484" s="1">
         <x:v>0</x:v>
@@ -14037,10 +14040,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F484" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G484" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
     </x:row>
     <x:row r="485" spans="1:7">
@@ -14048,13 +14051,13 @@
         <x:v>541</x:v>
       </x:c>
       <x:c r="B485" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C485" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D485" s="1">
-        <x:v>400022</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E485" s="1">
         <x:v>0</x:v>
@@ -14063,7 +14066,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G485" s="1">
-        <x:v>401022</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="486" spans="1:7">
@@ -14071,22 +14074,22 @@
         <x:v>542</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C486" s="1">
-        <x:v>3500</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D486" s="1">
-        <x:v>44693946</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="E486" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F486" s="1">
-        <x:v>8000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G486" s="1">
-        <x:v>44705446</x:v>
+        <x:v>401022</x:v>
       </x:c>
     </x:row>
     <x:row r="487" spans="1:7">
@@ -14094,22 +14097,22 @@
         <x:v>543</x:v>
       </x:c>
       <x:c r="B487" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C487" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D487" s="1">
-        <x:v>0</x:v>
+        <x:v>44693946</x:v>
       </x:c>
       <x:c r="E487" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F487" s="1">
-        <x:v>0</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="G487" s="1">
-        <x:v>50</x:v>
+        <x:v>44705446</x:v>
       </x:c>
     </x:row>
     <x:row r="488" spans="1:7">
@@ -14117,13 +14120,13 @@
         <x:v>544</x:v>
       </x:c>
       <x:c r="B488" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C488" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D488" s="1">
-        <x:v>726377</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E488" s="1">
         <x:v>0</x:v>
@@ -14132,7 +14135,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G488" s="1">
-        <x:v>726377</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="489" spans="1:7">
@@ -14140,22 +14143,22 @@
         <x:v>545</x:v>
       </x:c>
       <x:c r="B489" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C489" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D489" s="1">
-        <x:v>668449</x:v>
+        <x:v>726377</x:v>
       </x:c>
       <x:c r="E489" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F489" s="1">
-        <x:v>7600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G489" s="1">
-        <x:v>678549</x:v>
+        <x:v>726377</x:v>
       </x:c>
     </x:row>
     <x:row r="490" spans="1:7">
@@ -14163,22 +14166,22 @@
         <x:v>546</x:v>
       </x:c>
       <x:c r="B490" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C490" s="1">
-        <x:v>1000</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D490" s="1">
-        <x:v>0</x:v>
+        <x:v>668449</x:v>
       </x:c>
       <x:c r="E490" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F490" s="1">
-        <x:v>0</x:v>
+        <x:v>7600</x:v>
       </x:c>
       <x:c r="G490" s="1">
-        <x:v>1000</x:v>
+        <x:v>678549</x:v>
       </x:c>
     </x:row>
     <x:row r="491" spans="1:7">
@@ -14186,10 +14189,10 @@
         <x:v>547</x:v>
       </x:c>
       <x:c r="B491" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C491" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D491" s="1">
         <x:v>0</x:v>
@@ -14198,10 +14201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F491" s="1">
-        <x:v>1250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G491" s="1">
-        <x:v>1300</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="492" spans="1:7">
@@ -14209,7 +14212,7 @@
         <x:v>548</x:v>
       </x:c>
       <x:c r="B492" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C492" s="1">
         <x:v>50</x:v>
@@ -14221,10 +14224,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F492" s="1">
-        <x:v>0</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="G492" s="1">
-        <x:v>50</x:v>
+        <x:v>1300</x:v>
       </x:c>
     </x:row>
     <x:row r="493" spans="1:7">
@@ -14232,13 +14235,13 @@
         <x:v>549</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C493" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D493" s="1">
-        <x:v>120404787</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E493" s="1">
         <x:v>0</x:v>
@@ -14247,7 +14250,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G493" s="1">
-        <x:v>120406787</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="494" spans="1:7">
@@ -14255,13 +14258,13 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="B494" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C494" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D494" s="1">
-        <x:v>442806</x:v>
+        <x:v>120404787</x:v>
       </x:c>
       <x:c r="E494" s="1">
         <x:v>0</x:v>
@@ -14270,7 +14273,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G494" s="1">
-        <x:v>442806</x:v>
+        <x:v>120406787</x:v>
       </x:c>
     </x:row>
     <x:row r="495" spans="1:7">
@@ -14278,22 +14281,22 @@
         <x:v>551</x:v>
       </x:c>
       <x:c r="B495" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C495" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D495" s="1">
-        <x:v>0</x:v>
+        <x:v>442806</x:v>
       </x:c>
       <x:c r="E495" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F495" s="1">
-        <x:v>3333</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G495" s="1">
-        <x:v>4333</x:v>
+        <x:v>442806</x:v>
       </x:c>
     </x:row>
     <x:row r="496" spans="1:7">
@@ -14301,10 +14304,10 @@
         <x:v>552</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C496" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D496" s="1">
         <x:v>0</x:v>
@@ -14313,10 +14316,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F496" s="1">
-        <x:v>0</x:v>
+        <x:v>3333</x:v>
       </x:c>
       <x:c r="G496" s="1">
-        <x:v>50</x:v>
+        <x:v>4333</x:v>
       </x:c>
     </x:row>
     <x:row r="497" spans="1:7">
@@ -14324,7 +14327,7 @@
         <x:v>553</x:v>
       </x:c>
       <x:c r="B497" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C497" s="1">
         <x:v>50</x:v>
@@ -14347,10 +14350,10 @@
         <x:v>554</x:v>
       </x:c>
       <x:c r="B498" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C498" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D498" s="1">
         <x:v>0</x:v>
@@ -14362,7 +14365,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G498" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="499" spans="1:7">
@@ -14370,10 +14373,10 @@
         <x:v>555</x:v>
       </x:c>
       <x:c r="B499" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C499" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D499" s="1">
         <x:v>0</x:v>
@@ -14382,10 +14385,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F499" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G499" s="1">
-        <x:v>1050</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="500" spans="1:7">
@@ -14393,10 +14396,10 @@
         <x:v>556</x:v>
       </x:c>
       <x:c r="B500" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C500" s="1">
-        <x:v>2700</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D500" s="1">
         <x:v>0</x:v>
@@ -14405,10 +14408,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F500" s="1">
-        <x:v>2700</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G500" s="1">
-        <x:v>5400</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="501" spans="1:7">
@@ -14416,10 +14419,10 @@
         <x:v>557</x:v>
       </x:c>
       <x:c r="B501" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C501" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="D501" s="1">
         <x:v>0</x:v>
@@ -14428,10 +14431,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F501" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G501" s="1">
-        <x:v>50</x:v>
+        <x:v>5400</x:v>
       </x:c>
     </x:row>
     <x:row r="502" spans="1:7">
@@ -14439,7 +14442,7 @@
         <x:v>558</x:v>
       </x:c>
       <x:c r="B502" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C502" s="1">
         <x:v>50</x:v>
@@ -14451,10 +14454,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F502" s="1">
-        <x:v>12000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G502" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="503" spans="1:7">
@@ -14462,7 +14465,7 @@
         <x:v>559</x:v>
       </x:c>
       <x:c r="B503" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C503" s="1">
         <x:v>50</x:v>
@@ -14474,10 +14477,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F503" s="1">
-        <x:v>0</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="G503" s="1">
-        <x:v>50</x:v>
+        <x:v>12050</x:v>
       </x:c>
     </x:row>
     <x:row r="504" spans="1:7">
@@ -14485,10 +14488,10 @@
         <x:v>560</x:v>
       </x:c>
       <x:c r="B504" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C504" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D504" s="1">
         <x:v>0</x:v>
@@ -14497,10 +14500,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F504" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G504" s="1">
-        <x:v>250</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="505" spans="1:7">
@@ -14508,10 +14511,10 @@
         <x:v>561</x:v>
       </x:c>
       <x:c r="B505" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C505" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D505" s="1">
         <x:v>0</x:v>
@@ -14520,10 +14523,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F505" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G505" s="1">
-        <x:v>50</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="506" spans="1:7">
@@ -14531,7 +14534,7 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B506" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C506" s="1">
         <x:v>50</x:v>
@@ -14543,10 +14546,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F506" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G506" s="1">
-        <x:v>2750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="507" spans="1:7">
@@ -14554,10 +14557,10 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C507" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D507" s="1">
         <x:v>0</x:v>
@@ -14566,10 +14569,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F507" s="1">
-        <x:v>4600</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G507" s="1">
-        <x:v>4600</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="508" spans="1:7">
@@ -14577,10 +14580,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="B508" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C508" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D508" s="1">
         <x:v>0</x:v>
@@ -14589,10 +14592,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F508" s="1">
-        <x:v>0</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G508" s="1">
-        <x:v>50</x:v>
+        <x:v>4600</x:v>
       </x:c>
     </x:row>
     <x:row r="509" spans="1:7">
@@ -14600,7 +14603,7 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C509" s="1">
         <x:v>50</x:v>
@@ -14623,7 +14626,7 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="B510" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C510" s="1">
         <x:v>50</x:v>
@@ -14646,7 +14649,7 @@
         <x:v>567</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C511" s="1">
         <x:v>50</x:v>
@@ -14669,13 +14672,13 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="B512" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C512" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D512" s="1">
-        <x:v>282526</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E512" s="1">
         <x:v>0</x:v>
@@ -14684,7 +14687,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G512" s="1">
-        <x:v>282526</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="513" spans="1:7">
@@ -14692,22 +14695,22 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C513" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D513" s="1">
-        <x:v>0</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E513" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F513" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G513" s="1">
-        <x:v>1000</x:v>
+        <x:v>282526</x:v>
       </x:c>
     </x:row>
     <x:row r="514" spans="1:7">
@@ -14715,10 +14718,10 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="B514" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C514" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D514" s="1">
         <x:v>0</x:v>
@@ -14727,10 +14730,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F514" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G514" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="515" spans="1:7">
@@ -14738,22 +14741,22 @@
         <x:v>571</x:v>
       </x:c>
       <x:c r="B515" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C515" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D515" s="1">
-        <x:v>116161</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E515" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F515" s="1">
-        <x:v>4500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G515" s="1">
-        <x:v>124661</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="516" spans="1:7">
@@ -14761,22 +14764,22 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="B516" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C516" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D516" s="1">
-        <x:v>0</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="E516" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F516" s="1">
-        <x:v>0</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G516" s="1">
-        <x:v>50</x:v>
+        <x:v>124661</x:v>
       </x:c>
     </x:row>
     <x:row r="517" spans="1:7">
@@ -14784,7 +14787,7 @@
         <x:v>573</x:v>
       </x:c>
       <x:c r="B517" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C517" s="1">
         <x:v>50</x:v>
@@ -14807,7 +14810,7 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>575</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C518" s="1">
         <x:v>50</x:v>
@@ -14827,10 +14830,10 @@
     </x:row>
     <x:row r="519" spans="1:7">
       <x:c r="A519" s="1" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="B519" s="1" t="s">
         <x:v>576</x:v>
-      </x:c>
-      <x:c r="B519" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C519" s="1">
         <x:v>50</x:v>
@@ -14853,22 +14856,22 @@
         <x:v>577</x:v>
       </x:c>
       <x:c r="B520" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C520" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D520" s="1">
-        <x:v>2997852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E520" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F520" s="1">
-        <x:v>6800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G520" s="1">
-        <x:v>3007652</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="521" spans="1:7">
@@ -14876,22 +14879,22 @@
         <x:v>578</x:v>
       </x:c>
       <x:c r="B521" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C521" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D521" s="1">
-        <x:v>14446984</x:v>
+        <x:v>2997852</x:v>
       </x:c>
       <x:c r="E521" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F521" s="1">
-        <x:v>0</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="G521" s="1">
-        <x:v>14446984</x:v>
+        <x:v>3007652</x:v>
       </x:c>
     </x:row>
     <x:row r="522" spans="1:7">
@@ -14899,13 +14902,13 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C522" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D522" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E522" s="1">
         <x:v>0</x:v>
@@ -14914,7 +14917,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G522" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="523" spans="1:7">
@@ -14922,10 +14925,10 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B523" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C523" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D523" s="1">
         <x:v>0</x:v>
@@ -14934,10 +14937,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F523" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G523" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="524" spans="1:7">
@@ -14945,7 +14948,7 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C524" s="1">
         <x:v>0</x:v>
@@ -14957,10 +14960,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F524" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -14968,10 +14971,10 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C525" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D525" s="1">
         <x:v>0</x:v>
@@ -14980,10 +14983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F525" s="1">
-        <x:v>0</x:v>
+        <x:v>22334</x:v>
       </x:c>
       <x:c r="G525" s="1">
-        <x:v>50</x:v>
+        <x:v>22334</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:7">
@@ -14991,10 +14994,10 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C526" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D526" s="1">
         <x:v>0</x:v>
@@ -15003,10 +15006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F526" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G526" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="527" spans="1:7">
@@ -15014,10 +15017,10 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B527" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C527" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D527" s="1">
         <x:v>0</x:v>
@@ -15026,10 +15029,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F527" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G527" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="528" spans="1:7">
@@ -15037,13 +15040,13 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="B528" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C528" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D528" s="1">
-        <x:v>209387</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E528" s="1">
         <x:v>0</x:v>
@@ -15052,7 +15055,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G528" s="1">
-        <x:v>209387</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="529" spans="1:7">
@@ -15060,13 +15063,13 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C529" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D529" s="1">
-        <x:v>0</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="E529" s="1">
         <x:v>0</x:v>
@@ -15075,7 +15078,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G529" s="1">
-        <x:v>50</x:v>
+        <x:v>209387</x:v>
       </x:c>
     </x:row>
     <x:row r="530" spans="1:7">
@@ -15083,13 +15086,13 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="B530" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C530" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D530" s="1">
-        <x:v>257695</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E530" s="1">
         <x:v>0</x:v>
@@ -15098,7 +15101,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G530" s="1">
-        <x:v>257695</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="531" spans="1:7">
@@ -15106,22 +15109,22 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="B531" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C531" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D531" s="1">
-        <x:v>0</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="E531" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F531" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G531" s="1">
-        <x:v>3300</x:v>
+        <x:v>257695</x:v>
       </x:c>
     </x:row>
     <x:row r="532" spans="1:7">
@@ -15129,10 +15132,10 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C532" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D532" s="1">
         <x:v>0</x:v>
@@ -15141,10 +15144,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F532" s="1">
-        <x:v>29800</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G532" s="1">
-        <x:v>34800</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="533" spans="1:7">
@@ -15152,10 +15155,10 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C533" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D533" s="1">
         <x:v>0</x:v>
@@ -15164,10 +15167,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F533" s="1">
-        <x:v>0</x:v>
+        <x:v>29800</x:v>
       </x:c>
       <x:c r="G533" s="1">
-        <x:v>50</x:v>
+        <x:v>34800</x:v>
       </x:c>
     </x:row>
     <x:row r="534" spans="1:7">
@@ -15175,7 +15178,7 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="B534" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C534" s="1">
         <x:v>50</x:v>
@@ -15187,10 +15190,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F534" s="1">
-        <x:v>5600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G534" s="1">
-        <x:v>5650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="535" spans="1:7">
@@ -15198,10 +15201,10 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B535" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C535" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D535" s="1">
         <x:v>0</x:v>
@@ -15210,10 +15213,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F535" s="1">
-        <x:v>0</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G535" s="1">
-        <x:v>2050</x:v>
+        <x:v>5650</x:v>
       </x:c>
     </x:row>
     <x:row r="536" spans="1:7">
@@ -15221,10 +15224,10 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C536" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D536" s="1">
         <x:v>0</x:v>
@@ -15233,10 +15236,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F536" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G536" s="1">
-        <x:v>3384</x:v>
+        <x:v>2050</x:v>
       </x:c>
     </x:row>
     <x:row r="537" spans="1:7">
@@ -15244,7 +15247,7 @@
         <x:v>594</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C537" s="1">
         <x:v>50</x:v>
@@ -15256,10 +15259,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F537" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G537" s="1">
-        <x:v>50</x:v>
+        <x:v>3384</x:v>
       </x:c>
     </x:row>
     <x:row r="538" spans="1:7">
@@ -15267,22 +15270,22 @@
         <x:v>595</x:v>
       </x:c>
       <x:c r="B538" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C538" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D538" s="1">
-        <x:v>558813</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E538" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F538" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G538" s="1">
-        <x:v>559813</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="539" spans="1:7">
@@ -15290,22 +15293,22 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C539" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D539" s="1">
-        <x:v>0</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E539" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F539" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G539" s="1">
-        <x:v>6650</x:v>
+        <x:v>559813</x:v>
       </x:c>
     </x:row>
     <x:row r="540" spans="1:7">
@@ -15313,22 +15316,22 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C540" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D540" s="1">
-        <x:v>8250000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E540" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F540" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G540" s="1">
-        <x:v>8250000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:7">
@@ -15336,13 +15339,13 @@
         <x:v>598</x:v>
       </x:c>
       <x:c r="B541" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C541" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D541" s="1">
-        <x:v>0</x:v>
+        <x:v>8250000</x:v>
       </x:c>
       <x:c r="E541" s="1">
         <x:v>0</x:v>
@@ -15351,7 +15354,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G541" s="1">
-        <x:v>50</x:v>
+        <x:v>8250000</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:7">
@@ -15359,22 +15362,22 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B542" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C542" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D542" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E542" s="1">
-        <x:v>20483</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F542" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G542" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="543" spans="1:7">
@@ -15382,22 +15385,22 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C543" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D543" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E543" s="1">
-        <x:v>0</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="F543" s="1">
-        <x:v>1089100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>1089150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15405,22 +15408,22 @@
         <x:v>601</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C544" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D544" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E544" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
-        <x:v>0</x:v>
+        <x:v>1089100</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>1927706</x:v>
+        <x:v>1089150</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">
@@ -15428,13 +15431,13 @@
         <x:v>602</x:v>
       </x:c>
       <x:c r="B545" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C545" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D545" s="1">
-        <x:v>0</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="E545" s="1">
         <x:v>0</x:v>
@@ -15443,7 +15446,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G545" s="1">
-        <x:v>50</x:v>
+        <x:v>1927706</x:v>
       </x:c>
     </x:row>
     <x:row r="546" spans="1:7">
@@ -15451,7 +15454,7 @@
         <x:v>603</x:v>
       </x:c>
       <x:c r="B546" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C546" s="1">
         <x:v>50</x:v>
@@ -15463,10 +15466,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F546" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G546" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="547" spans="1:7">
@@ -15474,7 +15477,7 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C547" s="1">
         <x:v>50</x:v>
@@ -15486,10 +15489,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F547" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G547" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="548" spans="1:7">
@@ -15497,10 +15500,10 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="B548" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C548" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D548" s="1">
         <x:v>0</x:v>
@@ -15509,10 +15512,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F548" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G548" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="549" spans="1:7">
@@ -15520,10 +15523,10 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C549" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D549" s="1">
         <x:v>0</x:v>
@@ -15532,10 +15535,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F549" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G549" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="550" spans="1:7">
@@ -15543,7 +15546,7 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C550" s="1">
         <x:v>50</x:v>
@@ -15555,10 +15558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F550" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G550" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="551" spans="1:7">
@@ -15566,22 +15569,22 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C551" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D551" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E551" s="1">
-        <x:v>817066</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F551" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>0</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -15589,22 +15592,22 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B552" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C552" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D552" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E552" s="1">
-        <x:v>0</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="F552" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G552" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="553" spans="1:7">
@@ -15612,7 +15615,7 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B553" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C553" s="1">
         <x:v>50</x:v>
@@ -15635,22 +15638,22 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C554" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D554" s="1">
-        <x:v>88256</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E554" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F554" s="1">
-        <x:v>14866</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G554" s="1">
-        <x:v>117122</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="555" spans="1:7">
@@ -15658,22 +15661,22 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B555" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C555" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D555" s="1">
-        <x:v>0</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="E555" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F555" s="1">
-        <x:v>0</x:v>
+        <x:v>14866</x:v>
       </x:c>
       <x:c r="G555" s="1">
-        <x:v>50</x:v>
+        <x:v>117122</x:v>
       </x:c>
     </x:row>
     <x:row r="556" spans="1:7">
@@ -15681,7 +15684,7 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C556" s="1">
         <x:v>50</x:v>
@@ -15704,7 +15707,7 @@
         <x:v>614</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>615</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C557" s="1">
         <x:v>50</x:v>
@@ -15724,10 +15727,10 @@
     </x:row>
     <x:row r="558" spans="1:7">
       <x:c r="A558" s="1" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B558" s="1" t="s">
         <x:v>616</x:v>
-      </x:c>
-      <x:c r="B558" s="1" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="C558" s="1">
         <x:v>50</x:v>
@@ -15750,10 +15753,10 @@
         <x:v>617</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C559" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D559" s="1">
         <x:v>0</x:v>
@@ -15762,10 +15765,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F559" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G559" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:7">
@@ -15773,7 +15776,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B560" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C560" s="1">
         <x:v>0</x:v>
@@ -15785,10 +15788,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F560" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G560" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="561" spans="1:7">
@@ -15799,19 +15802,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C561" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D561" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E561" s="1">
-        <x:v>10041119</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F561" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G561" s="1">
-        <x:v>50</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="562" spans="1:7">
@@ -15819,7 +15822,7 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B562" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C562" s="1">
         <x:v>50</x:v>
@@ -15828,13 +15831,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E562" s="1">
-        <x:v>0</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="F562" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G562" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="563" spans="1:7">
@@ -15842,7 +15845,7 @@
         <x:v>621</x:v>
       </x:c>
       <x:c r="B563" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C563" s="1">
         <x:v>50</x:v>
@@ -15854,10 +15857,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F563" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G563" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="564" spans="1:7">
@@ -15865,10 +15868,10 @@
         <x:v>622</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C564" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D564" s="1">
         <x:v>0</x:v>
@@ -15877,10 +15880,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F564" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G564" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="565" spans="1:7">
@@ -15888,10 +15891,10 @@
         <x:v>623</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C565" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D565" s="1">
         <x:v>0</x:v>
@@ -15900,10 +15903,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -15911,7 +15914,7 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>50</x:v>
@@ -15934,7 +15937,7 @@
         <x:v>625</x:v>
       </x:c>
       <x:c r="B567" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C567" s="1">
         <x:v>50</x:v>
@@ -15957,10 +15960,10 @@
         <x:v>626</x:v>
       </x:c>
       <x:c r="B568" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C568" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D568" s="1">
         <x:v>0</x:v>
@@ -15969,10 +15972,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F568" s="1">
-        <x:v>-19405</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G568" s="1">
-        <x:v>-19405</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="569" spans="1:7">
@@ -15980,22 +15983,22 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C569" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D569" s="1">
-        <x:v>1491280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E569" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F569" s="1">
-        <x:v>0</x:v>
+        <x:v>-19405</x:v>
       </x:c>
       <x:c r="G569" s="1">
-        <x:v>1491280</x:v>
+        <x:v>-19405</x:v>
       </x:c>
     </x:row>
     <x:row r="570" spans="1:7">
@@ -16003,22 +16006,22 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D570" s="1">
-        <x:v>0</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="E570" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F570" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G570" s="1">
-        <x:v>500</x:v>
+        <x:v>1491280</x:v>
       </x:c>
     </x:row>
     <x:row r="571" spans="1:7">
@@ -16026,10 +16029,10 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B571" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C571" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D571" s="1">
         <x:v>0</x:v>
@@ -16038,10 +16041,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F571" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G571" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="572" spans="1:7">
@@ -16049,7 +16052,7 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="B572" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C572" s="1">
         <x:v>50</x:v>
@@ -16061,10 +16064,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F572" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -16072,7 +16075,7 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C573" s="1">
         <x:v>50</x:v>
@@ -16084,10 +16087,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F573" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G573" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="574" spans="1:7">
@@ -16095,7 +16098,7 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C574" s="1">
         <x:v>50</x:v>
@@ -16107,10 +16110,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F574" s="1">
-        <x:v>1287</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G574" s="1">
-        <x:v>1337</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="575" spans="1:7">
@@ -16118,10 +16121,10 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="B575" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C575" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D575" s="1">
         <x:v>0</x:v>
@@ -16130,10 +16133,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F575" s="1">
-        <x:v>6697</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G575" s="1">
-        <x:v>6697</x:v>
+        <x:v>1337</x:v>
       </x:c>
     </x:row>
     <x:row r="576" spans="1:7">
@@ -16141,10 +16144,10 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="B576" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C576" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D576" s="1">
         <x:v>0</x:v>
@@ -16153,10 +16156,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F576" s="1">
-        <x:v>0</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="G576" s="1">
-        <x:v>50</x:v>
+        <x:v>6697</x:v>
       </x:c>
     </x:row>
     <x:row r="577" spans="1:7">
@@ -16164,10 +16167,10 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B577" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C577" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D577" s="1">
         <x:v>0</x:v>
@@ -16176,10 +16179,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F577" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G577" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="578" spans="1:7">
@@ -16187,7 +16190,7 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="B578" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C578" s="1">
         <x:v>0</x:v>
@@ -16199,10 +16202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F578" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="G578" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="579" spans="1:7">
@@ -16210,10 +16213,10 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B579" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C579" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D579" s="1">
         <x:v>0</x:v>
@@ -16222,10 +16225,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F579" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G579" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="580" spans="1:7">
@@ -16233,7 +16236,7 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C580" s="1">
         <x:v>50</x:v>
@@ -16256,7 +16259,7 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B581" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C581" s="1">
         <x:v>50</x:v>
@@ -16279,22 +16282,22 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C582" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D582" s="1">
-        <x:v>1400000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E582" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F582" s="1">
-        <x:v>7000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G582" s="1">
-        <x:v>1409500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="583" spans="1:7">
@@ -16302,22 +16305,22 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="B583" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C583" s="1">
-        <x:v>50</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D583" s="1">
-        <x:v>0</x:v>
+        <x:v>1400000</x:v>
       </x:c>
       <x:c r="E583" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F583" s="1">
-        <x:v>0</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G583" s="1">
-        <x:v>50</x:v>
+        <x:v>1414500</x:v>
       </x:c>
     </x:row>
     <x:row r="584" spans="1:7">
@@ -16325,10 +16328,10 @@
         <x:v>642</x:v>
       </x:c>
       <x:c r="B584" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C584" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D584" s="1">
         <x:v>0</x:v>
@@ -16337,10 +16340,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F584" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G584" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:7">
@@ -16348,10 +16351,10 @@
         <x:v>643</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -16363,7 +16366,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>1550</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -16371,7 +16374,7 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C586" s="1">
         <x:v>50</x:v>
@@ -16383,10 +16386,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -16394,7 +16397,7 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C587" s="1">
         <x:v>50</x:v>
@@ -16417,7 +16420,7 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C588" s="1">
         <x:v>50</x:v>
@@ -16440,7 +16443,7 @@
         <x:v>647</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C589" s="1">
         <x:v>50</x:v>
@@ -16463,7 +16466,7 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C590" s="1">
         <x:v>50</x:v>
@@ -16486,13 +16489,13 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C591" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D591" s="1">
-        <x:v>275541</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E591" s="1">
         <x:v>0</x:v>
@@ -16501,7 +16504,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G591" s="1">
-        <x:v>275541</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="592" spans="1:7">
@@ -16509,22 +16512,22 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C592" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D592" s="1">
-        <x:v>0</x:v>
+        <x:v>275541</x:v>
       </x:c>
       <x:c r="E592" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F592" s="1">
-        <x:v>81050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G592" s="1">
-        <x:v>81050</x:v>
+        <x:v>275541</x:v>
       </x:c>
     </x:row>
     <x:row r="593" spans="1:7">
@@ -16532,10 +16535,10 @@
         <x:v>651</x:v>
       </x:c>
       <x:c r="B593" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C593" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D593" s="1">
         <x:v>0</x:v>
@@ -16544,10 +16547,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F593" s="1">
-        <x:v>0</x:v>
+        <x:v>81050</x:v>
       </x:c>
       <x:c r="G593" s="1">
-        <x:v>50</x:v>
+        <x:v>81050</x:v>
       </x:c>
     </x:row>
     <x:row r="594" spans="1:7">
@@ -16555,7 +16558,7 @@
         <x:v>652</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C594" s="1">
         <x:v>50</x:v>
@@ -16578,10 +16581,10 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C595" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D595" s="1">
         <x:v>0</x:v>
@@ -16593,7 +16596,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G595" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="596" spans="1:7">
@@ -16601,10 +16604,10 @@
         <x:v>654</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C596" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D596" s="1">
         <x:v>0</x:v>
@@ -16616,7 +16619,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G596" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
     </x:row>
     <x:row r="597" spans="1:7">
@@ -16624,7 +16627,7 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B597" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C597" s="1">
         <x:v>50</x:v>
@@ -16636,10 +16639,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F597" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G597" s="1">
-        <x:v>14050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="598" spans="1:7">
@@ -16647,10 +16650,10 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C598" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D598" s="1">
         <x:v>0</x:v>
@@ -16659,10 +16662,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F598" s="1">
-        <x:v>2700</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G598" s="1">
-        <x:v>2700</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="599" spans="1:7">
@@ -16670,7 +16673,7 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C599" s="1">
         <x:v>0</x:v>
@@ -16682,10 +16685,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F599" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G599" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="600" spans="1:7">
@@ -16693,30 +16696,30 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C600" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D600" s="1">
-        <x:v>14446984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E600" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F600" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G600" s="1">
-        <x:v>14446984</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="601" spans="1:7">
       <x:c r="A601" s="1" t="s">
-        <x:v>658</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C601" s="1">
         <x:v>0</x:v>
@@ -16739,13 +16742,13 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C602" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D602" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E602" s="1">
         <x:v>0</x:v>
@@ -16754,7 +16757,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
@@ -16762,22 +16765,22 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C603" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D603" s="1">
-        <x:v>2470488</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E603" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F603" s="1">
-        <x:v>11834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G603" s="1">
-        <x:v>2494372</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="604" spans="1:7">
@@ -16785,22 +16788,22 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C604" s="1">
-        <x:v>100</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="D604" s="1">
-        <x:v>0</x:v>
+        <x:v>2470488</x:v>
       </x:c>
       <x:c r="E604" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F604" s="1">
-        <x:v>0</x:v>
+        <x:v>11834</x:v>
       </x:c>
       <x:c r="G604" s="1">
-        <x:v>100</x:v>
+        <x:v>2494372</x:v>
       </x:c>
     </x:row>
     <x:row r="605" spans="1:7">
@@ -16808,10 +16811,10 @@
         <x:v>662</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D605" s="1">
         <x:v>0</x:v>
@@ -16823,7 +16826,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16831,7 +16834,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>50</x:v>
@@ -16857,7 +16860,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C607" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D607" s="1">
         <x:v>0</x:v>
@@ -16866,10 +16869,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F607" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G607" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="608" spans="1:7">
@@ -16877,10 +16880,10 @@
         <x:v>665</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C608" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D608" s="1">
         <x:v>0</x:v>
@@ -16889,10 +16892,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F608" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G608" s="1">
-        <x:v>2550</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="609" spans="1:7">
@@ -16900,7 +16903,7 @@
         <x:v>666</x:v>
       </x:c>
       <x:c r="B609" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C609" s="1">
         <x:v>50</x:v>
@@ -16912,10 +16915,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F609" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G609" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="610" spans="1:7">
@@ -16923,7 +16926,7 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C610" s="1">
         <x:v>50</x:v>
@@ -16946,7 +16949,7 @@
         <x:v>668</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C611" s="1">
         <x:v>50</x:v>
@@ -16969,7 +16972,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>50</x:v>
@@ -16992,22 +16995,22 @@
         <x:v>670</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C613" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D613" s="1">
-        <x:v>3975320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E613" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F613" s="1">
-        <x:v>6634</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G613" s="1">
-        <x:v>3982954</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:7">
@@ -17015,22 +17018,22 @@
         <x:v>671</x:v>
       </x:c>
       <x:c r="B614" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C614" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D614" s="1">
-        <x:v>0</x:v>
+        <x:v>3975320</x:v>
       </x:c>
       <x:c r="E614" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F614" s="1">
-        <x:v>22000</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G614" s="1">
-        <x:v>22000</x:v>
+        <x:v>3982954</x:v>
       </x:c>
     </x:row>
     <x:row r="615" spans="1:7">
@@ -17038,10 +17041,10 @@
         <x:v>672</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -17050,10 +17053,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>5800</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>5850</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -17061,7 +17064,7 @@
         <x:v>673</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>674</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C616" s="1">
         <x:v>50</x:v>
@@ -17073,21 +17076,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
       <x:c r="A617" s="1" t="s">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="B617" s="1" t="s">
         <x:v>675</x:v>
       </x:c>
-      <x:c r="B617" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C617" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D617" s="1">
         <x:v>0</x:v>
@@ -17096,10 +17099,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F617" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G617" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="618" spans="1:7">
@@ -17107,10 +17110,10 @@
         <x:v>676</x:v>
       </x:c>
       <x:c r="B618" s="1" t="s">
-        <x:v>677</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C618" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D618" s="1">
         <x:v>0</x:v>
@@ -17119,18 +17122,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F618" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G618" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="619" spans="1:7">
       <x:c r="A619" s="1" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="B619" s="1" t="s">
         <x:v>678</x:v>
-      </x:c>
-      <x:c r="B619" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C619" s="1">
         <x:v>50</x:v>
@@ -17153,7 +17156,7 @@
         <x:v>679</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C620" s="1">
         <x:v>50</x:v>
@@ -17173,13 +17176,13 @@
     </x:row>
     <x:row r="621" spans="1:7">
       <x:c r="A621" s="1" t="s">
-        <x:v>679</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="B621" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C621" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D621" s="1">
         <x:v>0</x:v>
@@ -17188,10 +17191,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F621" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G621" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="622" spans="1:7">
@@ -17199,10 +17202,10 @@
         <x:v>680</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C622" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D622" s="1">
         <x:v>0</x:v>
@@ -17211,10 +17214,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F622" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G622" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="623" spans="1:7">
@@ -17222,7 +17225,7 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C623" s="1">
         <x:v>50</x:v>
@@ -17245,10 +17248,10 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C624" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D624" s="1">
         <x:v>0</x:v>
@@ -17257,10 +17260,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F624" s="1">
-        <x:v>68600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G624" s="1">
-        <x:v>71150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="625" spans="1:7">
@@ -17268,10 +17271,10 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D625" s="1">
         <x:v>0</x:v>
@@ -17280,10 +17283,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>0</x:v>
+        <x:v>68600</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>50</x:v>
+        <x:v>71150</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17291,7 +17294,7 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C626" s="1">
         <x:v>50</x:v>
@@ -17314,10 +17317,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17326,10 +17329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -17337,10 +17340,10 @@
         <x:v>686</x:v>
       </x:c>
       <x:c r="B628" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C628" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D628" s="1">
         <x:v>0</x:v>
@@ -17349,10 +17352,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F628" s="1">
-        <x:v>58000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G628" s="1">
-        <x:v>58050</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:7">
@@ -17360,10 +17363,10 @@
         <x:v>687</x:v>
       </x:c>
       <x:c r="B629" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C629" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D629" s="1">
         <x:v>0</x:v>
@@ -17372,10 +17375,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F629" s="1">
-        <x:v>1666</x:v>
+        <x:v>58000</x:v>
       </x:c>
       <x:c r="G629" s="1">
-        <x:v>3716</x:v>
+        <x:v>58050</x:v>
       </x:c>
     </x:row>
     <x:row r="630" spans="1:7">
@@ -17383,10 +17386,10 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C630" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D630" s="1">
         <x:v>0</x:v>
@@ -17395,10 +17398,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F630" s="1">
-        <x:v>1668</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="G630" s="1">
-        <x:v>1668</x:v>
+        <x:v>3716</x:v>
       </x:c>
     </x:row>
     <x:row r="631" spans="1:7">
@@ -17406,10 +17409,10 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D631" s="1">
         <x:v>0</x:v>
@@ -17418,10 +17421,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>0</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>50</x:v>
+        <x:v>1668</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -17429,13 +17432,13 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C632" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D632" s="1">
-        <x:v>105040</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E632" s="1">
         <x:v>0</x:v>
@@ -17444,7 +17447,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>105090</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17452,22 +17455,22 @@
         <x:v>691</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C633" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D633" s="1">
-        <x:v>0</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="E633" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F633" s="1">
-        <x:v>30600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G633" s="1">
-        <x:v>33550</x:v>
+        <x:v>105090</x:v>
       </x:c>
     </x:row>
     <x:row r="634" spans="1:7">
@@ -17475,10 +17478,10 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C634" s="1">
-        <x:v>2550</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D634" s="1">
         <x:v>0</x:v>
@@ -17487,10 +17490,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F634" s="1">
-        <x:v>0</x:v>
+        <x:v>30600</x:v>
       </x:c>
       <x:c r="G634" s="1">
-        <x:v>2550</x:v>
+        <x:v>33550</x:v>
       </x:c>
     </x:row>
     <x:row r="635" spans="1:7">
@@ -17498,22 +17501,22 @@
         <x:v>693</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C635" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D635" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E635" s="1">
-        <x:v>56045</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F635" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G635" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:7">
@@ -17530,7 +17533,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E636" s="1">
-        <x:v>0</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="F636" s="1">
         <x:v>0</x:v>
@@ -17544,10 +17547,10 @@
         <x:v>695</x:v>
       </x:c>
       <x:c r="B637" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C637" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D637" s="1">
         <x:v>0</x:v>
@@ -17559,7 +17562,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G637" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="638" spans="1:7">
@@ -17567,10 +17570,10 @@
         <x:v>696</x:v>
       </x:c>
       <x:c r="B638" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C638" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D638" s="1">
         <x:v>0</x:v>
@@ -17582,7 +17585,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G638" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="639" spans="1:7">
@@ -17590,10 +17593,10 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C639" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D639" s="1">
         <x:v>0</x:v>
@@ -17602,33 +17605,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F639" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
       <x:c r="A640" s="1" t="s">
-        <x:v>697</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C640" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D640" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E640" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F640" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G640" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:7">
@@ -17642,7 +17645,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D641" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E641" s="1">
         <x:v>0</x:v>
@@ -17651,7 +17654,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G641" s="1">
-        <x:v>852561</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="642" spans="1:7">
@@ -17659,13 +17662,13 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C642" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D642" s="1">
-        <x:v>0</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="E642" s="1">
         <x:v>0</x:v>
@@ -17674,7 +17677,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G642" s="1">
-        <x:v>50</x:v>
+        <x:v>852561</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:7">
@@ -17682,7 +17685,7 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="B643" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C643" s="1">
         <x:v>50</x:v>
@@ -17705,13 +17708,13 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>2200000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
@@ -17720,7 +17723,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>2200000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17728,13 +17731,13 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>0</x:v>
+        <x:v>2200000</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
@@ -17743,7 +17746,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>50</x:v>
+        <x:v>2200000</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -17751,7 +17754,7 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C646" s="1">
         <x:v>50</x:v>
@@ -17774,7 +17777,7 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="B647" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C647" s="1">
         <x:v>50</x:v>
@@ -17797,10 +17800,10 @@
         <x:v>705</x:v>
       </x:c>
       <x:c r="B648" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C648" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D648" s="1">
         <x:v>0</x:v>
@@ -17812,7 +17815,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G648" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="649" spans="1:7">
@@ -17820,10 +17823,10 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B649" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C649" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D649" s="1">
         <x:v>0</x:v>
@@ -17835,7 +17838,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G649" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:7">
@@ -17843,10 +17846,10 @@
         <x:v>707</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C650" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D650" s="1">
         <x:v>0</x:v>
@@ -17858,7 +17861,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G650" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:7">
@@ -17866,10 +17869,10 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C651" s="1">
-        <x:v>1050</x:v>
+        <x:v>10050</x:v>
       </x:c>
       <x:c r="D651" s="1">
         <x:v>0</x:v>
@@ -17878,10 +17881,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F651" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G651" s="1">
-        <x:v>2717</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:7">
@@ -17889,10 +17892,10 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C652" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D652" s="1">
         <x:v>0</x:v>
@@ -17901,10 +17904,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F652" s="1">
-        <x:v>0</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>50</x:v>
+        <x:v>2717</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -17912,22 +17915,22 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D653" s="1">
-        <x:v>111599</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E653" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F653" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>114899</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
@@ -17935,22 +17938,22 @@
         <x:v>711</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C654" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D654" s="1">
-        <x:v>0</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="E654" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F654" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G654" s="1">
-        <x:v>50</x:v>
+        <x:v>114899</x:v>
       </x:c>
     </x:row>
     <x:row r="655" spans="1:7">
@@ -17958,7 +17961,7 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C655" s="1">
         <x:v>50</x:v>
@@ -17978,16 +17981,16 @@
     </x:row>
     <x:row r="656" spans="1:7">
       <x:c r="A656" s="1" t="s">
-        <x:v>712</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C656" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
@@ -17996,7 +17999,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -18004,13 +18007,13 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C657" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D657" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E657" s="1">
         <x:v>0</x:v>
@@ -18019,7 +18022,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G657" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:7">
@@ -18027,22 +18030,22 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B658" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C658" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D658" s="1">
-        <x:v>10046680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E658" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F658" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G658" s="1">
-        <x:v>10048730</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:7">
@@ -18050,22 +18053,22 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C659" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D659" s="1">
-        <x:v>2263800</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E659" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F659" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G659" s="1">
-        <x:v>2263850</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:7">
@@ -18073,13 +18076,13 @@
         <x:v>716</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C660" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D660" s="1">
-        <x:v>0</x:v>
+        <x:v>2263800</x:v>
       </x:c>
       <x:c r="E660" s="1">
         <x:v>0</x:v>
@@ -18088,7 +18091,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>50</x:v>
+        <x:v>2263850</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18096,7 +18099,7 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C661" s="1">
         <x:v>50</x:v>
@@ -18108,10 +18111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F661" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18119,10 +18122,10 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C662" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D662" s="1">
         <x:v>0</x:v>
@@ -18131,10 +18134,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F662" s="1">
-        <x:v>52333</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>58383</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -18142,10 +18145,10 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C663" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D663" s="1">
         <x:v>0</x:v>
@@ -18154,10 +18157,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F663" s="1">
-        <x:v>0</x:v>
+        <x:v>52333</x:v>
       </x:c>
       <x:c r="G663" s="1">
-        <x:v>50</x:v>
+        <x:v>58383</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:7">
@@ -18165,7 +18168,7 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="B664" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C664" s="1">
         <x:v>50</x:v>
@@ -18188,10 +18191,10 @@
         <x:v>721</x:v>
       </x:c>
       <x:c r="B665" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C665" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D665" s="1">
         <x:v>0</x:v>
@@ -18200,10 +18203,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F665" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G665" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:7">
@@ -18211,22 +18214,22 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C666" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D666" s="1">
-        <x:v>367531</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E666" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F666" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G666" s="1">
-        <x:v>367531</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:7">
@@ -18234,22 +18237,22 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C667" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D667" s="1">
-        <x:v>817169</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="E667" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F667" s="1">
-        <x:v>1668</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G667" s="1">
-        <x:v>820837</x:v>
+        <x:v>367531</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:7">
@@ -18257,22 +18260,22 @@
         <x:v>724</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C668" s="1">
-        <x:v>11050</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D668" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E668" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F668" s="1">
-        <x:v>6242</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>17292</x:v>
+        <x:v>820837</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -18280,10 +18283,10 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C669" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D669" s="1">
         <x:v>0</x:v>
@@ -18292,10 +18295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F669" s="1">
-        <x:v>0</x:v>
+        <x:v>6242</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>50</x:v>
+        <x:v>17292</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
@@ -18303,7 +18306,7 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C670" s="1">
         <x:v>50</x:v>
@@ -18326,10 +18329,10 @@
         <x:v>727</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C671" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D671" s="1">
         <x:v>0</x:v>
@@ -18338,10 +18341,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F671" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">
@@ -18349,10 +18352,10 @@
         <x:v>728</x:v>
       </x:c>
       <x:c r="B672" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C672" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D672" s="1">
         <x:v>0</x:v>
@@ -18361,10 +18364,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F672" s="1">
-        <x:v>25000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G672" s="1">
-        <x:v>25050</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="673" spans="1:7">
@@ -18372,7 +18375,7 @@
         <x:v>729</x:v>
       </x:c>
       <x:c r="B673" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C673" s="1">
         <x:v>50</x:v>
@@ -18384,10 +18387,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F673" s="1">
-        <x:v>0</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G673" s="1">
-        <x:v>50</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="674" spans="1:7">
@@ -18395,22 +18398,22 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C674" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D674" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E674" s="1">
-        <x:v>1531015</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F674" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G674" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="675" spans="1:7">
@@ -18418,22 +18421,22 @@
         <x:v>731</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C675" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D675" s="1">
-        <x:v>157560</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E675" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F675" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G675" s="1">
-        <x:v>157610</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:7">
@@ -18441,13 +18444,13 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B676" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C676" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D676" s="1">
-        <x:v>0</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="E676" s="1">
         <x:v>0</x:v>
@@ -18456,7 +18459,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G676" s="1">
-        <x:v>50</x:v>
+        <x:v>157610</x:v>
       </x:c>
     </x:row>
     <x:row r="677" spans="1:7">
@@ -18464,13 +18467,13 @@
         <x:v>733</x:v>
       </x:c>
       <x:c r="B677" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C677" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D677" s="1">
-        <x:v>5583432</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E677" s="1">
         <x:v>0</x:v>
@@ -18479,7 +18482,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>5584432</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
@@ -18487,13 +18490,13 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B678" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C678" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D678" s="1">
-        <x:v>0</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E678" s="1">
         <x:v>0</x:v>
@@ -18502,7 +18505,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G678" s="1">
-        <x:v>50</x:v>
+        <x:v>5584432</x:v>
       </x:c>
     </x:row>
     <x:row r="679" spans="1:7">
@@ -18510,22 +18513,22 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C679" s="1">
-        <x:v>24050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D679" s="1">
-        <x:v>764206</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E679" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F679" s="1">
-        <x:v>20501</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>808757</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
@@ -18533,22 +18536,22 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>0</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="D680" s="1">
-        <x:v>0</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="E680" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F680" s="1">
-        <x:v>2700</x:v>
+        <x:v>20501</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>2700</x:v>
+        <x:v>810257</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -18556,22 +18559,22 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C681" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D681" s="1">
-        <x:v>1543316</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E681" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -18579,22 +18582,22 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D682" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E682" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>14500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>14550</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -18602,7 +18605,7 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C683" s="1">
         <x:v>50</x:v>
@@ -18614,10 +18617,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>50</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -18625,7 +18628,7 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C684" s="1">
         <x:v>50</x:v>
@@ -18648,13 +18651,13 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C685" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D685" s="1">
-        <x:v>619349</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E685" s="1">
         <x:v>0</x:v>
@@ -18663,7 +18666,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>619399</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -18671,22 +18674,22 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C686" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D686" s="1">
-        <x:v>0</x:v>
+        <x:v>619349</x:v>
       </x:c>
       <x:c r="E686" s="1">
-        <x:v>10135449</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F686" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G686" s="1">
-        <x:v>0</x:v>
+        <x:v>619399</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:7">
@@ -18694,22 +18697,22 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D687" s="1">
-        <x:v>103020</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E687" s="1">
-        <x:v>0</x:v>
+        <x:v>10135449</x:v>
       </x:c>
       <x:c r="F687" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>106354</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
@@ -18717,22 +18720,22 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C688" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D688" s="1">
-        <x:v>0</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="E688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F688" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>2500</x:v>
+        <x:v>106354</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
@@ -18740,13 +18743,13 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C689" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D689" s="1">
-        <x:v>106947</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E689" s="1">
         <x:v>0</x:v>
@@ -18755,7 +18758,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G689" s="1">
-        <x:v>106947</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="690" spans="1:7">
@@ -18763,22 +18766,22 @@
         <x:v>746</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D690" s="1">
-        <x:v>0</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="E690" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>25050</x:v>
+        <x:v>106947</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -18786,22 +18789,22 @@
         <x:v>747</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>1050</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D691" s="1">
-        <x:v>902176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E691" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>7000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>910226</x:v>
+        <x:v>27050</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -18809,22 +18812,22 @@
         <x:v>748</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D692" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E692" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>25500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>25550</x:v>
+        <x:v>910226</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -18844,10 +18847,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F693" s="1">
-        <x:v>0</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>50</x:v>
+        <x:v>25550</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
@@ -18855,10 +18858,10 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C694" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D694" s="1">
         <x:v>0</x:v>
@@ -18867,10 +18870,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F694" s="1">
-        <x:v>10500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>10500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
@@ -18878,7 +18881,7 @@
         <x:v>751</x:v>
       </x:c>
       <x:c r="B695" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C695" s="1">
         <x:v>0</x:v>
@@ -18890,10 +18893,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F695" s="1">
-        <x:v>6200</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>6200</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
@@ -18901,10 +18904,10 @@
         <x:v>752</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D696" s="1">
         <x:v>0</x:v>
@@ -18913,10 +18916,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>50</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -18924,10 +18927,10 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C697" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D697" s="1">
         <x:v>0</x:v>
@@ -18939,7 +18942,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">
@@ -18947,10 +18950,10 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C698" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D698" s="1">
         <x:v>0</x:v>
@@ -18959,10 +18962,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F698" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>6650</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
@@ -18970,22 +18973,22 @@
         <x:v>755</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C699" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D699" s="1">
-        <x:v>1888055</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E699" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F699" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G699" s="1">
-        <x:v>1888055</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:7">
@@ -18993,22 +18996,22 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C700" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D700" s="1">
-        <x:v>0</x:v>
+        <x:v>1888055</x:v>
       </x:c>
       <x:c r="E700" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F700" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>5000</x:v>
+        <x:v>1888055</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
@@ -19016,10 +19019,10 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C701" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D701" s="1">
         <x:v>0</x:v>
@@ -19028,10 +19031,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
@@ -19039,10 +19042,10 @@
         <x:v>758</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C702" s="1">
-        <x:v>6550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D702" s="1">
         <x:v>0</x:v>
@@ -19051,10 +19054,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F702" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>9850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
@@ -19062,10 +19065,10 @@
         <x:v>759</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C703" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D703" s="1">
         <x:v>0</x:v>
@@ -19074,10 +19077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F703" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>50</x:v>
+        <x:v>9850</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
@@ -19085,7 +19088,7 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C704" s="1">
         <x:v>50</x:v>
@@ -19108,10 +19111,10 @@
         <x:v>761</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D705" s="1">
         <x:v>0</x:v>
@@ -19120,10 +19123,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>9550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19131,10 +19134,10 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C706" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D706" s="1">
         <x:v>0</x:v>
@@ -19143,10 +19146,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F706" s="1">
-        <x:v>2700</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G706" s="1">
-        <x:v>2700</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:7">
@@ -19154,10 +19157,10 @@
         <x:v>763</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D707" s="1">
         <x:v>0</x:v>
@@ -19166,10 +19169,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
@@ -19177,10 +19180,10 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D708" s="1">
         <x:v>0</x:v>
@@ -19189,33 +19192,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>9350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
       <x:c r="A709" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D709" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E709" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -19223,22 +19226,22 @@
         <x:v>765</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C710" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D710" s="1">
-        <x:v>2572233</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E710" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>5500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>2577783</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
@@ -19246,22 +19249,22 @@
         <x:v>766</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C711" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D711" s="1">
-        <x:v>0</x:v>
+        <x:v>2572233</x:v>
       </x:c>
       <x:c r="E711" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F711" s="1">
-        <x:v>0</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>50</x:v>
+        <x:v>2577783</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
@@ -19269,7 +19272,7 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C712" s="1">
         <x:v>50</x:v>
@@ -19281,10 +19284,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19292,7 +19295,7 @@
         <x:v>768</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C713" s="1">
         <x:v>50</x:v>
@@ -19304,10 +19307,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19315,10 +19318,10 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D714" s="1">
         <x:v>0</x:v>
@@ -19327,10 +19330,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>3300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19341,7 +19344,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C715" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D715" s="1">
         <x:v>0</x:v>
@@ -19350,10 +19353,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>50</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
@@ -19361,7 +19364,7 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C716" s="1">
         <x:v>50</x:v>
@@ -19373,10 +19376,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>5700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19384,7 +19387,7 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="B717" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C717" s="1">
         <x:v>50</x:v>
@@ -19396,10 +19399,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>0</x:v>
+        <x:v>5700</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
@@ -19407,7 +19410,7 @@
         <x:v>773</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C718" s="1">
         <x:v>50</x:v>
@@ -19430,22 +19433,22 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C719" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D719" s="1">
-        <x:v>1892270</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E719" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F719" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G719" s="1">
-        <x:v>1909770</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="720" spans="1:7">
@@ -19453,13 +19456,13 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C720" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D720" s="1">
-        <x:v>0</x:v>
+        <x:v>1892270</x:v>
       </x:c>
       <x:c r="E720" s="1">
         <x:v>0</x:v>
@@ -19468,7 +19471,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G720" s="1">
-        <x:v>1000</x:v>
+        <x:v>1909770</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:7">
@@ -19476,10 +19479,10 @@
         <x:v>776</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C721" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D721" s="1">
         <x:v>0</x:v>
@@ -19488,10 +19491,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F721" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
@@ -19499,10 +19502,10 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C722" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D722" s="1">
         <x:v>0</x:v>
@@ -19511,10 +19514,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F722" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
@@ -19522,10 +19525,10 @@
         <x:v>778</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D723" s="1">
         <x:v>0</x:v>
@@ -19534,10 +19537,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F723" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
@@ -19545,13 +19548,13 @@
         <x:v>779</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C724" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D724" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E724" s="1">
         <x:v>0</x:v>
@@ -19560,7 +19563,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>40000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
@@ -19568,13 +19571,13 @@
         <x:v>780</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D725" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E725" s="1">
         <x:v>0</x:v>
@@ -19583,7 +19586,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>1000</x:v>
+        <x:v>40000</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
@@ -19591,10 +19594,10 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C726" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D726" s="1">
         <x:v>0</x:v>
@@ -19606,7 +19609,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
@@ -19614,10 +19617,10 @@
         <x:v>782</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D727" s="1">
         <x:v>0</x:v>
@@ -19626,10 +19629,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F727" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>5200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
@@ -19637,10 +19640,10 @@
         <x:v>783</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C728" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D728" s="1">
         <x:v>0</x:v>
@@ -19649,10 +19652,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F728" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
@@ -19660,7 +19663,7 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C729" s="1">
         <x:v>50</x:v>
@@ -19683,7 +19686,7 @@
         <x:v>785</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C730" s="1">
         <x:v>50</x:v>
@@ -19695,10 +19698,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F730" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
@@ -19706,22 +19709,22 @@
         <x:v>786</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C731" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D731" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E731" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F731" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G731" s="1">
-        <x:v>3920589</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:7">
@@ -19729,13 +19732,13 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C732" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D732" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E732" s="1">
         <x:v>0</x:v>
@@ -19744,7 +19747,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>50</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
@@ -19752,10 +19755,10 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C733" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D733" s="1">
         <x:v>0</x:v>
@@ -19767,7 +19770,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G733" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:7">
@@ -19775,10 +19778,10 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C734" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D734" s="1">
         <x:v>0</x:v>
@@ -19790,7 +19793,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G734" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:7">
@@ -19798,7 +19801,7 @@
         <x:v>790</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C735" s="1">
         <x:v>50</x:v>
@@ -19821,10 +19824,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>4500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19833,10 +19836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F736" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>9334</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
@@ -19844,10 +19847,10 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C737" s="1">
-        <x:v>1050</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D737" s="1">
         <x:v>0</x:v>
@@ -19856,10 +19859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F737" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G737" s="1">
-        <x:v>1050</x:v>
+        <x:v>9334</x:v>
       </x:c>
     </x:row>
     <x:row r="738" spans="1:7">
@@ -19870,7 +19873,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C738" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D738" s="1">
         <x:v>0</x:v>
@@ -19882,7 +19885,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
@@ -19890,7 +19893,7 @@
         <x:v>794</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C739" s="1">
         <x:v>50</x:v>
@@ -19913,13 +19916,13 @@
         <x:v>795</x:v>
       </x:c>
       <x:c r="B740" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D740" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E740" s="1">
         <x:v>0</x:v>
@@ -19928,7 +19931,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
@@ -19936,13 +19939,13 @@
         <x:v>796</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C741" s="1">
-        <x:v>50</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D741" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E741" s="1">
         <x:v>0</x:v>
@@ -19951,7 +19954,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G741" s="1">
-        <x:v>50</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:7">
@@ -19959,10 +19962,10 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C742" s="1">
-        <x:v>19600</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D742" s="1">
         <x:v>0</x:v>
@@ -19971,10 +19974,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F742" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>36600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
@@ -19982,10 +19985,10 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C743" s="1">
-        <x:v>50</x:v>
+        <x:v>19600</x:v>
       </x:c>
       <x:c r="D743" s="1">
         <x:v>0</x:v>
@@ -19994,10 +19997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F743" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G743" s="1">
-        <x:v>50</x:v>
+        <x:v>36600</x:v>
       </x:c>
     </x:row>
     <x:row r="744" spans="1:7">
@@ -20005,7 +20008,7 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C744" s="1">
         <x:v>50</x:v>
@@ -20028,7 +20031,7 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C745" s="1">
         <x:v>50</x:v>
@@ -20051,13 +20054,13 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C746" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D746" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E746" s="1">
         <x:v>0</x:v>
@@ -20066,7 +20069,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G746" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:7">
@@ -20074,13 +20077,13 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C747" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D747" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E747" s="1">
         <x:v>0</x:v>
@@ -20089,7 +20092,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G747" s="1">
-        <x:v>50</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:7">
@@ -20097,10 +20100,10 @@
         <x:v>803</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D748" s="1">
         <x:v>0</x:v>
@@ -20109,10 +20112,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F748" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>30000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
@@ -20120,10 +20123,10 @@
         <x:v>804</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C749" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D749" s="1">
         <x:v>0</x:v>
@@ -20132,10 +20135,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F749" s="1">
-        <x:v>0</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G749" s="1">
-        <x:v>50</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:7">
@@ -20143,10 +20146,10 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>19050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20155,10 +20158,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F750" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>21550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
@@ -20166,10 +20169,10 @@
         <x:v>806</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>3500</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20178,10 +20181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F751" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>3500</x:v>
+        <x:v>21550</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
@@ -20189,10 +20192,10 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D752" s="1">
         <x:v>0</x:v>
@@ -20204,12 +20207,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
       <x:c r="A753" s="1" t="s">
-        <x:v>807</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
         <x:v>97</x:v>
@@ -20235,7 +20238,7 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C754" s="1">
         <x:v>50</x:v>
@@ -20258,10 +20261,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -20273,7 +20276,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
@@ -20281,10 +20284,10 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C756" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D756" s="1">
         <x:v>0</x:v>
@@ -20296,7 +20299,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">
@@ -20304,10 +20307,10 @@
         <x:v>811</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20316,10 +20319,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20327,10 +20330,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20339,10 +20342,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>5000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>5050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
@@ -20350,7 +20353,7 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C759" s="1">
         <x:v>50</x:v>
@@ -20362,10 +20365,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F759" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
@@ -20373,10 +20376,10 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C760" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D760" s="1">
         <x:v>0</x:v>
@@ -20385,10 +20388,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F760" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
@@ -20396,10 +20399,10 @@
         <x:v>815</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>459</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C761" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D761" s="1">
         <x:v>0</x:v>
@@ -20408,10 +20411,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F761" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">
@@ -20419,7 +20422,7 @@
         <x:v>816</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C762" s="1">
         <x:v>50</x:v>
@@ -20442,13 +20445,13 @@
         <x:v>817</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C763" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D763" s="1">
-        <x:v>943006</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E763" s="1">
         <x:v>0</x:v>
@@ -20457,7 +20460,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G763" s="1">
-        <x:v>943056</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="764" spans="1:7">
@@ -20465,13 +20468,13 @@
         <x:v>818</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C764" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D764" s="1">
-        <x:v>0</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="E764" s="1">
         <x:v>0</x:v>
@@ -20480,7 +20483,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G764" s="1">
-        <x:v>50</x:v>
+        <x:v>943056</x:v>
       </x:c>
     </x:row>
     <x:row r="765" spans="1:7">
@@ -20488,7 +20491,7 @@
         <x:v>819</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C765" s="1">
         <x:v>50</x:v>
@@ -20511,22 +20514,22 @@
         <x:v>820</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C766" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D766" s="1">
-        <x:v>476254</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E766" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F766" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>478754</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
@@ -20534,22 +20537,22 @@
         <x:v>821</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C767" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D767" s="1">
-        <x:v>0</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="E767" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F767" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G767" s="1">
-        <x:v>50</x:v>
+        <x:v>478754</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:7">
@@ -20557,7 +20560,7 @@
         <x:v>822</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C768" s="1">
         <x:v>50</x:v>
@@ -20569,10 +20572,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>4999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>5049</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
@@ -20580,10 +20583,10 @@
         <x:v>823</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C769" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D769" s="1">
         <x:v>0</x:v>
@@ -20592,10 +20595,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F769" s="1">
-        <x:v>16500</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G769" s="1">
-        <x:v>16500</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:7">
@@ -20603,10 +20606,10 @@
         <x:v>824</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C770" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D770" s="1">
         <x:v>0</x:v>
@@ -20615,10 +20618,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F770" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G770" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="771" spans="1:7">
@@ -20626,7 +20629,7 @@
         <x:v>825</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C771" s="1">
         <x:v>50</x:v>
@@ -20649,7 +20652,7 @@
         <x:v>826</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C772" s="1">
         <x:v>50</x:v>
@@ -20672,7 +20675,7 @@
         <x:v>827</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C773" s="1">
         <x:v>50</x:v>
@@ -20695,7 +20698,7 @@
         <x:v>828</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C774" s="1">
         <x:v>50</x:v>
@@ -20707,10 +20710,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F774" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G774" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:7">
@@ -20718,7 +20721,7 @@
         <x:v>829</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C775" s="1">
         <x:v>50</x:v>
@@ -20730,10 +20733,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F775" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G775" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:7">
@@ -20741,10 +20744,10 @@
         <x:v>830</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C776" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D776" s="1">
         <x:v>0</x:v>
@@ -20753,10 +20756,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>37300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>48150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
@@ -20764,10 +20767,10 @@
         <x:v>831</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C777" s="1">
-        <x:v>0</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D777" s="1">
         <x:v>0</x:v>
@@ -20776,10 +20779,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F777" s="1">
-        <x:v>83</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G777" s="1">
-        <x:v>83</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="778" spans="1:7">
@@ -20787,10 +20790,10 @@
         <x:v>832</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C778" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D778" s="1">
         <x:v>0</x:v>
@@ -20799,10 +20802,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F778" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
@@ -20810,7 +20813,7 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C779" s="1">
         <x:v>50</x:v>
@@ -20833,7 +20836,7 @@
         <x:v>834</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C780" s="1">
         <x:v>50</x:v>
@@ -20856,10 +20859,10 @@
         <x:v>835</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C781" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D781" s="1">
         <x:v>0</x:v>
@@ -20868,10 +20871,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F781" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G781" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:7">
@@ -20879,21 +20882,44 @@
         <x:v>836</x:v>
       </x:c>
       <x:c r="B782" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C782" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D782" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E782" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F782" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G782" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="783" spans="1:7">
+      <x:c r="A783" s="1" t="s">
+        <x:v>837</x:v>
+      </x:c>
+      <x:c r="B783" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C782" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D782" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E782" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F782" s="1">
+      <x:c r="C783" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D783" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E783" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F783" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G782" s="1">
+      <x:c r="G783" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -20175,7 +20175,7 @@
         <x:v>19050</x:v>
       </x:c>
       <x:c r="D751" s="1">
-        <x:v>0</x:v>
+        <x:v>1350000</x:v>
       </x:c>
       <x:c r="E751" s="1">
         <x:v>0</x:v>
@@ -20184,7 +20184,7 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>21550</x:v>
+        <x:v>1371550</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
@@ -20215,10 +20215,10 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D753" s="1">
         <x:v>0</x:v>
@@ -20227,10 +20227,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
@@ -20238,10 +20238,10 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C754" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D754" s="1">
         <x:v>0</x:v>
@@ -20250,10 +20250,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F754" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16719,7 +16719,7 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C601" s="1">
         <x:v>0</x:v>
@@ -16742,7 +16742,7 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C602" s="1">
         <x:v>0</x:v>
@@ -17984,13 +17984,13 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C656" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
@@ -17999,7 +17999,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -18007,13 +18007,13 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C657" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D657" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E657" s="1">
         <x:v>0</x:v>
@@ -18022,7 +18022,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G657" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -13557,7 +13557,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E463" s="1">
-        <x:v>215160</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="F463" s="1">
         <x:v>0</x:v>
@@ -17205,10 +17205,10 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C622" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D622" s="1">
         <x:v>0</x:v>
@@ -17217,10 +17217,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F622" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G622" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="623" spans="1:7">
@@ -17228,10 +17228,10 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C623" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D623" s="1">
         <x:v>0</x:v>
@@ -17240,10 +17240,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F623" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G623" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="624" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16745,7 +16745,7 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C602" s="1">
         <x:v>0</x:v>
@@ -16768,7 +16768,7 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C603" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -20241,10 +20241,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C754" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D754" s="1">
         <x:v>0</x:v>
@@ -20253,10 +20253,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F754" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
@@ -20264,10 +20264,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -20276,10 +20276,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F755" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -6407,10 +6407,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F152" s="1">
-        <x:v>10000</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G152" s="1">
-        <x:v>16000</x:v>
+        <x:v>21500</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:7">
@@ -6752,10 +6752,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F167" s="1">
-        <x:v>29250</x:v>
+        <x:v>36250</x:v>
       </x:c>
       <x:c r="G167" s="1">
-        <x:v>44300</x:v>
+        <x:v>51300</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:7">
@@ -10478,10 +10478,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F329" s="1">
-        <x:v>21000</x:v>
+        <x:v>21500</x:v>
       </x:c>
       <x:c r="G329" s="1">
-        <x:v>25500</x:v>
+        <x:v>26000</x:v>
       </x:c>
     </x:row>
     <x:row r="330" spans="1:7">
@@ -12663,10 +12663,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F424" s="1">
-        <x:v>33100</x:v>
+        <x:v>33600</x:v>
       </x:c>
       <x:c r="G424" s="1">
-        <x:v>33150</x:v>
+        <x:v>33650</x:v>
       </x:c>
     </x:row>
     <x:row r="425" spans="1:7">
@@ -16343,10 +16343,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F584" s="1">
-        <x:v>7000</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G584" s="1">
-        <x:v>1414500</x:v>
+        <x:v>1418000</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:7">
@@ -20241,10 +20241,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C754" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D754" s="1">
         <x:v>0</x:v>
@@ -20253,10 +20253,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F754" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
@@ -20264,10 +20264,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -20276,10 +20276,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F755" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -307,10 +307,10 @@
     <x:t>BOOKER, CORY A.</x:t>
   </x:si>
   <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
     <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
   </x:si>
   <x:si>
     <x:t>BOOZMAN, SEN. JOHN</x:t>
@@ -4236,7 +4236,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C58" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>0</x:v>
@@ -4245,10 +4245,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>2800</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G58" s="1">
-        <x:v>2800</x:v>
+        <x:v>18250</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
@@ -4259,7 +4259,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C59" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>0</x:v>
@@ -4268,10 +4268,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>18200</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G59" s="1">
-        <x:v>18250</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
@@ -4923,7 +4923,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C88" s="1">
         <x:v>0</x:v>
@@ -5866,7 +5866,7 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C129" s="1">
         <x:v>0</x:v>
@@ -5981,7 +5981,7 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C134" s="1">
         <x:v>50</x:v>
@@ -7154,7 +7154,7 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="B185" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C185" s="1">
         <x:v>0</x:v>
@@ -8994,7 +8994,7 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="B265" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C265" s="1">
         <x:v>4550</x:v>
@@ -9500,7 +9500,7 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="B287" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C287" s="1">
         <x:v>0</x:v>
@@ -9638,7 +9638,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="B293" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C293" s="1">
         <x:v>0</x:v>
@@ -10420,7 +10420,7 @@
         <x:v>381</x:v>
       </x:c>
       <x:c r="B327" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C327" s="1">
         <x:v>0</x:v>
@@ -11110,7 +11110,7 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B357" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C357" s="1">
         <x:v>0</x:v>
@@ -11156,7 +11156,7 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C359" s="1">
         <x:v>0</x:v>
@@ -11363,7 +11363,7 @@
         <x:v>423</x:v>
       </x:c>
       <x:c r="B368" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C368" s="1">
         <x:v>0</x:v>
@@ -11409,7 +11409,7 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B370" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C370" s="1">
         <x:v>0</x:v>
@@ -11501,7 +11501,7 @@
         <x:v>429</x:v>
       </x:c>
       <x:c r="B374" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C374" s="1">
         <x:v>50</x:v>
@@ -12789,7 +12789,7 @@
         <x:v>486</x:v>
       </x:c>
       <x:c r="B430" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C430" s="1">
         <x:v>50</x:v>
@@ -13157,7 +13157,7 @@
         <x:v>502</x:v>
       </x:c>
       <x:c r="B446" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C446" s="1">
         <x:v>0</x:v>
@@ -13732,7 +13732,7 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C471" s="1">
         <x:v>1550</x:v>
@@ -14813,7 +14813,7 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C518" s="1">
         <x:v>50</x:v>
@@ -14974,7 +14974,7 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C525" s="1">
         <x:v>0</x:v>
@@ -15043,7 +15043,7 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="B528" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C528" s="1">
         <x:v>0</x:v>
@@ -15227,7 +15227,7 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C536" s="1">
         <x:v>50</x:v>
@@ -15296,7 +15296,7 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C539" s="1">
         <x:v>50</x:v>
@@ -15388,7 +15388,7 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C543" s="1">
         <x:v>50</x:v>
@@ -15549,7 +15549,7 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C550" s="1">
         <x:v>0</x:v>
@@ -15917,7 +15917,7 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>1000</x:v>
@@ -16009,7 +16009,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>0</x:v>
@@ -16561,7 +16561,7 @@
         <x:v>652</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C594" s="1">
         <x:v>0</x:v>
@@ -16745,7 +16745,7 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C602" s="1">
         <x:v>0</x:v>
@@ -16768,7 +16768,7 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C603" s="1">
         <x:v>0</x:v>
@@ -17228,7 +17228,7 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C623" s="1">
         <x:v>0</x:v>
@@ -17918,7 +17918,7 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C653" s="1">
         <x:v>1050</x:v>
@@ -18056,7 +18056,7 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C659" s="1">
         <x:v>50</x:v>
@@ -18125,7 +18125,7 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C662" s="1">
         <x:v>50</x:v>
@@ -18585,7 +18585,7 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C682" s="1">
         <x:v>0</x:v>
@@ -19505,7 +19505,7 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C722" s="1">
         <x:v>0</x:v>
@@ -19597,7 +19597,7 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C726" s="1">
         <x:v>0</x:v>
@@ -19781,7 +19781,7 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C734" s="1">
         <x:v>50</x:v>
@@ -20264,7 +20264,7 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C755" s="1">
         <x:v>0</x:v>
@@ -20816,7 +20816,7 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C779" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -307,10 +307,10 @@
     <x:t>BOOKER, CORY A.</x:t>
   </x:si>
   <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
     <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
   </x:si>
   <x:si>
     <x:t>BOOZMAN, SEN. JOHN</x:t>
@@ -4236,7 +4236,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C58" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>0</x:v>
@@ -4245,10 +4245,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>18200</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G58" s="1">
-        <x:v>18250</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
@@ -4259,7 +4259,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="C59" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>0</x:v>
@@ -4268,10 +4268,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>2800</x:v>
+        <x:v>18200</x:v>
       </x:c>
       <x:c r="G59" s="1">
-        <x:v>2800</x:v>
+        <x:v>18250</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
@@ -4923,7 +4923,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C88" s="1">
         <x:v>0</x:v>
@@ -5866,7 +5866,7 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B129" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C129" s="1">
         <x:v>0</x:v>
@@ -5981,7 +5981,7 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B134" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C134" s="1">
         <x:v>50</x:v>
@@ -7154,7 +7154,7 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="B185" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C185" s="1">
         <x:v>0</x:v>
@@ -8994,7 +8994,7 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="B265" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C265" s="1">
         <x:v>4550</x:v>
@@ -9500,7 +9500,7 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="B287" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C287" s="1">
         <x:v>0</x:v>
@@ -9638,7 +9638,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="B293" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C293" s="1">
         <x:v>0</x:v>
@@ -10420,7 +10420,7 @@
         <x:v>381</x:v>
       </x:c>
       <x:c r="B327" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C327" s="1">
         <x:v>0</x:v>
@@ -11110,7 +11110,7 @@
         <x:v>412</x:v>
       </x:c>
       <x:c r="B357" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C357" s="1">
         <x:v>0</x:v>
@@ -11156,7 +11156,7 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C359" s="1">
         <x:v>0</x:v>
@@ -11363,7 +11363,7 @@
         <x:v>423</x:v>
       </x:c>
       <x:c r="B368" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C368" s="1">
         <x:v>0</x:v>
@@ -11409,7 +11409,7 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="B370" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C370" s="1">
         <x:v>0</x:v>
@@ -11501,7 +11501,7 @@
         <x:v>429</x:v>
       </x:c>
       <x:c r="B374" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C374" s="1">
         <x:v>50</x:v>
@@ -12789,7 +12789,7 @@
         <x:v>486</x:v>
       </x:c>
       <x:c r="B430" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C430" s="1">
         <x:v>50</x:v>
@@ -13157,7 +13157,7 @@
         <x:v>502</x:v>
       </x:c>
       <x:c r="B446" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C446" s="1">
         <x:v>0</x:v>
@@ -13732,7 +13732,7 @@
         <x:v>527</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C471" s="1">
         <x:v>1550</x:v>
@@ -14813,7 +14813,7 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C518" s="1">
         <x:v>50</x:v>
@@ -14974,7 +14974,7 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C525" s="1">
         <x:v>0</x:v>
@@ -15043,7 +15043,7 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="B528" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C528" s="1">
         <x:v>0</x:v>
@@ -15227,7 +15227,7 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C536" s="1">
         <x:v>50</x:v>
@@ -15296,7 +15296,7 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C539" s="1">
         <x:v>50</x:v>
@@ -15388,7 +15388,7 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C543" s="1">
         <x:v>50</x:v>
@@ -15549,7 +15549,7 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C550" s="1">
         <x:v>0</x:v>
@@ -15917,7 +15917,7 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>1000</x:v>
@@ -16009,7 +16009,7 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C570" s="1">
         <x:v>0</x:v>
@@ -16561,7 +16561,7 @@
         <x:v>652</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C594" s="1">
         <x:v>0</x:v>
@@ -17205,10 +17205,10 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C622" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D622" s="1">
         <x:v>0</x:v>
@@ -17217,10 +17217,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F622" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G622" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="623" spans="1:7">
@@ -17228,10 +17228,10 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C623" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D623" s="1">
         <x:v>0</x:v>
@@ -17240,10 +17240,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F623" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G623" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="624" spans="1:7">
@@ -17918,7 +17918,7 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C653" s="1">
         <x:v>1050</x:v>
@@ -18056,7 +18056,7 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C659" s="1">
         <x:v>50</x:v>
@@ -18125,7 +18125,7 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C662" s="1">
         <x:v>50</x:v>
@@ -18585,7 +18585,7 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C682" s="1">
         <x:v>0</x:v>
@@ -19505,7 +19505,7 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C722" s="1">
         <x:v>0</x:v>
@@ -19597,7 +19597,7 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C726" s="1">
         <x:v>0</x:v>
@@ -19781,7 +19781,7 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C734" s="1">
         <x:v>50</x:v>
@@ -20264,7 +20264,7 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C755" s="1">
         <x:v>0</x:v>
@@ -20816,7 +20816,7 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C779" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -1700,6 +1700,9 @@
   </x:si>
   <x:si>
     <x:t>MURPHY, GREGORY FRANCIS DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MURPHY, PATRICK E</x:t>
   </x:si>
   <x:si>
     <x:t>MURPHY, SCOTT M</x:t>
@@ -2601,8 +2604,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G784" totalsRowShown="0">
-  <x:autoFilter ref="A1:G784"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G785" totalsRowShown="0">
+  <x:autoFilter ref="A1:G785"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_state" dataDxfId="0"/>
@@ -2904,7 +2907,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G784"/>
+  <x:dimension ref="A1:G785"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -8218,7 +8221,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D231" s="1">
-        <x:v>0</x:v>
+        <x:v>50571</x:v>
       </x:c>
       <x:c r="E231" s="1">
         <x:v>0</x:v>
@@ -8227,7 +8230,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G231" s="1">
-        <x:v>50</x:v>
+        <x:v>50621</x:v>
       </x:c>
     </x:row>
     <x:row r="232" spans="1:7">
@@ -14537,22 +14540,22 @@
         <x:v>562</x:v>
       </x:c>
       <x:c r="B506" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C506" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D506" s="1">
-        <x:v>0</x:v>
+        <x:v>50571</x:v>
       </x:c>
       <x:c r="E506" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F506" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G506" s="1">
-        <x:v>250</x:v>
+        <x:v>50571</x:v>
       </x:c>
     </x:row>
     <x:row r="507" spans="1:7">
@@ -14560,10 +14563,10 @@
         <x:v>563</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C507" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D507" s="1">
         <x:v>0</x:v>
@@ -14572,10 +14575,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F507" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G507" s="1">
-        <x:v>50</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="508" spans="1:7">
@@ -14583,7 +14586,7 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="B508" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C508" s="1">
         <x:v>50</x:v>
@@ -14595,10 +14598,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F508" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G508" s="1">
-        <x:v>2750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="509" spans="1:7">
@@ -14606,10 +14609,10 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C509" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D509" s="1">
         <x:v>0</x:v>
@@ -14618,10 +14621,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F509" s="1">
-        <x:v>4600</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G509" s="1">
-        <x:v>4600</x:v>
+        <x:v>2750</x:v>
       </x:c>
     </x:row>
     <x:row r="510" spans="1:7">
@@ -14629,10 +14632,10 @@
         <x:v>566</x:v>
       </x:c>
       <x:c r="B510" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C510" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D510" s="1">
         <x:v>0</x:v>
@@ -14641,10 +14644,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F510" s="1">
-        <x:v>0</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G510" s="1">
-        <x:v>50</x:v>
+        <x:v>4600</x:v>
       </x:c>
     </x:row>
     <x:row r="511" spans="1:7">
@@ -14652,7 +14655,7 @@
         <x:v>567</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C511" s="1">
         <x:v>50</x:v>
@@ -14675,7 +14678,7 @@
         <x:v>568</x:v>
       </x:c>
       <x:c r="B512" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C512" s="1">
         <x:v>50</x:v>
@@ -14698,7 +14701,7 @@
         <x:v>569</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C513" s="1">
         <x:v>50</x:v>
@@ -14721,13 +14724,13 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="B514" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C514" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D514" s="1">
-        <x:v>282526</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E514" s="1">
         <x:v>0</x:v>
@@ -14736,7 +14739,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G514" s="1">
-        <x:v>282526</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="515" spans="1:7">
@@ -14744,22 +14747,22 @@
         <x:v>571</x:v>
       </x:c>
       <x:c r="B515" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C515" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D515" s="1">
-        <x:v>0</x:v>
+        <x:v>282526</x:v>
       </x:c>
       <x:c r="E515" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F515" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G515" s="1">
-        <x:v>1000</x:v>
+        <x:v>282526</x:v>
       </x:c>
     </x:row>
     <x:row r="516" spans="1:7">
@@ -14767,10 +14770,10 @@
         <x:v>572</x:v>
       </x:c>
       <x:c r="B516" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C516" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D516" s="1">
         <x:v>0</x:v>
@@ -14779,10 +14782,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F516" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G516" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="517" spans="1:7">
@@ -14790,22 +14793,22 @@
         <x:v>573</x:v>
       </x:c>
       <x:c r="B517" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C517" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D517" s="1">
-        <x:v>116161</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E517" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F517" s="1">
-        <x:v>4500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G517" s="1">
-        <x:v>124661</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="518" spans="1:7">
@@ -14813,22 +14816,22 @@
         <x:v>574</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C518" s="1">
-        <x:v>50</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D518" s="1">
-        <x:v>0</x:v>
+        <x:v>116161</x:v>
       </x:c>
       <x:c r="E518" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F518" s="1">
-        <x:v>0</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G518" s="1">
-        <x:v>50</x:v>
+        <x:v>124661</x:v>
       </x:c>
     </x:row>
     <x:row r="519" spans="1:7">
@@ -14836,7 +14839,7 @@
         <x:v>575</x:v>
       </x:c>
       <x:c r="B519" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C519" s="1">
         <x:v>50</x:v>
@@ -14859,7 +14862,7 @@
         <x:v>576</x:v>
       </x:c>
       <x:c r="B520" s="1" t="s">
-        <x:v>577</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C520" s="1">
         <x:v>50</x:v>
@@ -14879,10 +14882,10 @@
     </x:row>
     <x:row r="521" spans="1:7">
       <x:c r="A521" s="1" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="B521" s="1" t="s">
         <x:v>578</x:v>
-      </x:c>
-      <x:c r="B521" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C521" s="1">
         <x:v>50</x:v>
@@ -14905,22 +14908,22 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C522" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D522" s="1">
-        <x:v>2997852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E522" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F522" s="1">
-        <x:v>6800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G522" s="1">
-        <x:v>3007652</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="523" spans="1:7">
@@ -14928,22 +14931,22 @@
         <x:v>580</x:v>
       </x:c>
       <x:c r="B523" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C523" s="1">
-        <x:v>0</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D523" s="1">
-        <x:v>14446984</x:v>
+        <x:v>2997852</x:v>
       </x:c>
       <x:c r="E523" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F523" s="1">
-        <x:v>0</x:v>
+        <x:v>6800</x:v>
       </x:c>
       <x:c r="G523" s="1">
-        <x:v>14446984</x:v>
+        <x:v>3007652</x:v>
       </x:c>
     </x:row>
     <x:row r="524" spans="1:7">
@@ -14951,13 +14954,13 @@
         <x:v>581</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C524" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D524" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E524" s="1">
         <x:v>0</x:v>
@@ -14966,7 +14969,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G524" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="525" spans="1:7">
@@ -14974,10 +14977,10 @@
         <x:v>582</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C525" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D525" s="1">
         <x:v>0</x:v>
@@ -14986,10 +14989,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F525" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G525" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="526" spans="1:7">
@@ -14997,7 +15000,7 @@
         <x:v>583</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C526" s="1">
         <x:v>0</x:v>
@@ -15009,10 +15012,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F526" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="G526" s="1">
-        <x:v>22334</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="527" spans="1:7">
@@ -15020,10 +15023,10 @@
         <x:v>584</x:v>
       </x:c>
       <x:c r="B527" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C527" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D527" s="1">
         <x:v>0</x:v>
@@ -15032,10 +15035,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F527" s="1">
-        <x:v>0</x:v>
+        <x:v>22334</x:v>
       </x:c>
       <x:c r="G527" s="1">
-        <x:v>50</x:v>
+        <x:v>22334</x:v>
       </x:c>
     </x:row>
     <x:row r="528" spans="1:7">
@@ -15043,10 +15046,10 @@
         <x:v>585</x:v>
       </x:c>
       <x:c r="B528" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C528" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D528" s="1">
         <x:v>0</x:v>
@@ -15055,10 +15058,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F528" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G528" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="529" spans="1:7">
@@ -15066,10 +15069,10 @@
         <x:v>586</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C529" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D529" s="1">
         <x:v>0</x:v>
@@ -15078,10 +15081,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F529" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G529" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="530" spans="1:7">
@@ -15089,13 +15092,13 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="B530" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C530" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D530" s="1">
-        <x:v>209387</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E530" s="1">
         <x:v>0</x:v>
@@ -15104,7 +15107,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G530" s="1">
-        <x:v>209387</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="531" spans="1:7">
@@ -15112,13 +15115,13 @@
         <x:v>588</x:v>
       </x:c>
       <x:c r="B531" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C531" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D531" s="1">
-        <x:v>0</x:v>
+        <x:v>209387</x:v>
       </x:c>
       <x:c r="E531" s="1">
         <x:v>0</x:v>
@@ -15127,7 +15130,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G531" s="1">
-        <x:v>50</x:v>
+        <x:v>209387</x:v>
       </x:c>
     </x:row>
     <x:row r="532" spans="1:7">
@@ -15135,13 +15138,13 @@
         <x:v>589</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C532" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D532" s="1">
-        <x:v>257695</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E532" s="1">
         <x:v>0</x:v>
@@ -15150,7 +15153,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G532" s="1">
-        <x:v>257695</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="533" spans="1:7">
@@ -15158,22 +15161,22 @@
         <x:v>590</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C533" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D533" s="1">
-        <x:v>0</x:v>
+        <x:v>257695</x:v>
       </x:c>
       <x:c r="E533" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F533" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G533" s="1">
-        <x:v>3300</x:v>
+        <x:v>257695</x:v>
       </x:c>
     </x:row>
     <x:row r="534" spans="1:7">
@@ -15181,10 +15184,10 @@
         <x:v>591</x:v>
       </x:c>
       <x:c r="B534" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C534" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D534" s="1">
         <x:v>0</x:v>
@@ -15193,10 +15196,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F534" s="1">
-        <x:v>29800</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G534" s="1">
-        <x:v>34800</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="535" spans="1:7">
@@ -15204,10 +15207,10 @@
         <x:v>592</x:v>
       </x:c>
       <x:c r="B535" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C535" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D535" s="1">
         <x:v>0</x:v>
@@ -15216,10 +15219,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F535" s="1">
-        <x:v>0</x:v>
+        <x:v>29800</x:v>
       </x:c>
       <x:c r="G535" s="1">
-        <x:v>50</x:v>
+        <x:v>34800</x:v>
       </x:c>
     </x:row>
     <x:row r="536" spans="1:7">
@@ -15227,7 +15230,7 @@
         <x:v>593</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C536" s="1">
         <x:v>50</x:v>
@@ -15239,10 +15242,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F536" s="1">
-        <x:v>5600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G536" s="1">
-        <x:v>5650</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="537" spans="1:7">
@@ -15250,10 +15253,10 @@
         <x:v>594</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C537" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D537" s="1">
         <x:v>0</x:v>
@@ -15262,10 +15265,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F537" s="1">
-        <x:v>0</x:v>
+        <x:v>5600</x:v>
       </x:c>
       <x:c r="G537" s="1">
-        <x:v>2050</x:v>
+        <x:v>5650</x:v>
       </x:c>
     </x:row>
     <x:row r="538" spans="1:7">
@@ -15273,10 +15276,10 @@
         <x:v>595</x:v>
       </x:c>
       <x:c r="B538" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C538" s="1">
-        <x:v>50</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D538" s="1">
         <x:v>0</x:v>
@@ -15285,10 +15288,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F538" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G538" s="1">
-        <x:v>3384</x:v>
+        <x:v>2050</x:v>
       </x:c>
     </x:row>
     <x:row r="539" spans="1:7">
@@ -15296,7 +15299,7 @@
         <x:v>596</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C539" s="1">
         <x:v>50</x:v>
@@ -15308,10 +15311,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F539" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G539" s="1">
-        <x:v>50</x:v>
+        <x:v>3384</x:v>
       </x:c>
     </x:row>
     <x:row r="540" spans="1:7">
@@ -15319,22 +15322,22 @@
         <x:v>597</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C540" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D540" s="1">
-        <x:v>558813</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E540" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F540" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G540" s="1">
-        <x:v>559813</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:7">
@@ -15342,22 +15345,22 @@
         <x:v>598</x:v>
       </x:c>
       <x:c r="B541" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C541" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D541" s="1">
-        <x:v>0</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="E541" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F541" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G541" s="1">
-        <x:v>6650</x:v>
+        <x:v>559813</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:7">
@@ -15365,22 +15368,22 @@
         <x:v>599</x:v>
       </x:c>
       <x:c r="B542" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C542" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D542" s="1">
-        <x:v>8250000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E542" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F542" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G542" s="1">
-        <x:v>8250000</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="543" spans="1:7">
@@ -15388,13 +15391,13 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="B543" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C543" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D543" s="1">
-        <x:v>0</x:v>
+        <x:v>8250000</x:v>
       </x:c>
       <x:c r="E543" s="1">
         <x:v>0</x:v>
@@ -15403,7 +15406,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G543" s="1">
-        <x:v>50</x:v>
+        <x:v>8250000</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:7">
@@ -15411,22 +15414,22 @@
         <x:v>601</x:v>
       </x:c>
       <x:c r="B544" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C544" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D544" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E544" s="1">
-        <x:v>20483</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F544" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G544" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:7">
@@ -15434,22 +15437,22 @@
         <x:v>602</x:v>
       </x:c>
       <x:c r="B545" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C545" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D545" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E545" s="1">
-        <x:v>0</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="F545" s="1">
-        <x:v>1089100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G545" s="1">
-        <x:v>1089150</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="546" spans="1:7">
@@ -15457,22 +15460,22 @@
         <x:v>603</x:v>
       </x:c>
       <x:c r="B546" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C546" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D546" s="1">
-        <x:v>1927706</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E546" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F546" s="1">
-        <x:v>0</x:v>
+        <x:v>1089100</x:v>
       </x:c>
       <x:c r="G546" s="1">
-        <x:v>1927706</x:v>
+        <x:v>1089150</x:v>
       </x:c>
     </x:row>
     <x:row r="547" spans="1:7">
@@ -15480,13 +15483,13 @@
         <x:v>604</x:v>
       </x:c>
       <x:c r="B547" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C547" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D547" s="1">
-        <x:v>0</x:v>
+        <x:v>1927706</x:v>
       </x:c>
       <x:c r="E547" s="1">
         <x:v>0</x:v>
@@ -15495,7 +15498,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G547" s="1">
-        <x:v>50</x:v>
+        <x:v>1927706</x:v>
       </x:c>
     </x:row>
     <x:row r="548" spans="1:7">
@@ -15503,7 +15506,7 @@
         <x:v>605</x:v>
       </x:c>
       <x:c r="B548" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C548" s="1">
         <x:v>50</x:v>
@@ -15515,10 +15518,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F548" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G548" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="549" spans="1:7">
@@ -15526,7 +15529,7 @@
         <x:v>606</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C549" s="1">
         <x:v>50</x:v>
@@ -15538,10 +15541,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F549" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G549" s="1">
-        <x:v>50</x:v>
+        <x:v>3550</x:v>
       </x:c>
     </x:row>
     <x:row r="550" spans="1:7">
@@ -15549,10 +15552,10 @@
         <x:v>607</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C550" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D550" s="1">
         <x:v>0</x:v>
@@ -15561,10 +15564,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F550" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G550" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="551" spans="1:7">
@@ -15572,10 +15575,10 @@
         <x:v>608</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C551" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D551" s="1">
         <x:v>0</x:v>
@@ -15584,10 +15587,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F551" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -15595,7 +15598,7 @@
         <x:v>609</x:v>
       </x:c>
       <x:c r="B552" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C552" s="1">
         <x:v>50</x:v>
@@ -15607,10 +15610,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F552" s="1">
-        <x:v>10000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G552" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="553" spans="1:7">
@@ -15618,22 +15621,22 @@
         <x:v>610</x:v>
       </x:c>
       <x:c r="B553" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C553" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D553" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E553" s="1">
-        <x:v>817066</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F553" s="1">
-        <x:v>0</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G553" s="1">
-        <x:v>0</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="554" spans="1:7">
@@ -15641,22 +15644,22 @@
         <x:v>611</x:v>
       </x:c>
       <x:c r="B554" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C554" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D554" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E554" s="1">
-        <x:v>0</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="F554" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G554" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="555" spans="1:7">
@@ -15664,7 +15667,7 @@
         <x:v>612</x:v>
       </x:c>
       <x:c r="B555" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C555" s="1">
         <x:v>50</x:v>
@@ -15687,22 +15690,22 @@
         <x:v>613</x:v>
       </x:c>
       <x:c r="B556" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C556" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D556" s="1">
-        <x:v>88256</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E556" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F556" s="1">
-        <x:v>14866</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G556" s="1">
-        <x:v>117122</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:7">
@@ -15710,22 +15713,22 @@
         <x:v>614</x:v>
       </x:c>
       <x:c r="B557" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C557" s="1">
-        <x:v>50</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D557" s="1">
-        <x:v>0</x:v>
+        <x:v>88256</x:v>
       </x:c>
       <x:c r="E557" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F557" s="1">
-        <x:v>0</x:v>
+        <x:v>14866</x:v>
       </x:c>
       <x:c r="G557" s="1">
-        <x:v>50</x:v>
+        <x:v>117122</x:v>
       </x:c>
     </x:row>
     <x:row r="558" spans="1:7">
@@ -15733,7 +15736,7 @@
         <x:v>615</x:v>
       </x:c>
       <x:c r="B558" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C558" s="1">
         <x:v>50</x:v>
@@ -15756,7 +15759,7 @@
         <x:v>616</x:v>
       </x:c>
       <x:c r="B559" s="1" t="s">
-        <x:v>617</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C559" s="1">
         <x:v>50</x:v>
@@ -15776,10 +15779,10 @@
     </x:row>
     <x:row r="560" spans="1:7">
       <x:c r="A560" s="1" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="B560" s="1" t="s">
         <x:v>618</x:v>
-      </x:c>
-      <x:c r="B560" s="1" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="C560" s="1">
         <x:v>50</x:v>
@@ -15802,10 +15805,10 @@
         <x:v>619</x:v>
       </x:c>
       <x:c r="B561" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C561" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D561" s="1">
         <x:v>0</x:v>
@@ -15814,10 +15817,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F561" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G561" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="562" spans="1:7">
@@ -15825,7 +15828,7 @@
         <x:v>620</x:v>
       </x:c>
       <x:c r="B562" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C562" s="1">
         <x:v>0</x:v>
@@ -15837,10 +15840,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F562" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G562" s="1">
-        <x:v>6000</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="563" spans="1:7">
@@ -15851,19 +15854,19 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C563" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D563" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E563" s="1">
-        <x:v>10041119</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F563" s="1">
-        <x:v>0</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G563" s="1">
-        <x:v>50</x:v>
+        <x:v>6000</x:v>
       </x:c>
     </x:row>
     <x:row r="564" spans="1:7">
@@ -15871,7 +15874,7 @@
         <x:v>622</x:v>
       </x:c>
       <x:c r="B564" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C564" s="1">
         <x:v>50</x:v>
@@ -15880,13 +15883,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E564" s="1">
-        <x:v>0</x:v>
+        <x:v>10041119</x:v>
       </x:c>
       <x:c r="F564" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G564" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="565" spans="1:7">
@@ -15894,7 +15897,7 @@
         <x:v>623</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>50</x:v>
@@ -15906,10 +15909,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -15917,10 +15920,10 @@
         <x:v>624</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C566" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D566" s="1">
         <x:v>0</x:v>
@@ -15929,10 +15932,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F566" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>2500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -15940,10 +15943,10 @@
         <x:v>625</x:v>
       </x:c>
       <x:c r="B567" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C567" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D567" s="1">
         <x:v>0</x:v>
@@ -15952,10 +15955,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F567" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G567" s="1">
-        <x:v>50</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="568" spans="1:7">
@@ -15963,7 +15966,7 @@
         <x:v>626</x:v>
       </x:c>
       <x:c r="B568" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C568" s="1">
         <x:v>50</x:v>
@@ -15986,7 +15989,7 @@
         <x:v>627</x:v>
       </x:c>
       <x:c r="B569" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C569" s="1">
         <x:v>50</x:v>
@@ -16009,10 +16012,10 @@
         <x:v>628</x:v>
       </x:c>
       <x:c r="B570" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C570" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D570" s="1">
         <x:v>0</x:v>
@@ -16021,10 +16024,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F570" s="1">
-        <x:v>-19405</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G570" s="1">
-        <x:v>-19405</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="571" spans="1:7">
@@ -16032,22 +16035,22 @@
         <x:v>629</x:v>
       </x:c>
       <x:c r="B571" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C571" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D571" s="1">
-        <x:v>1491280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E571" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F571" s="1">
-        <x:v>0</x:v>
+        <x:v>-19405</x:v>
       </x:c>
       <x:c r="G571" s="1">
-        <x:v>1491280</x:v>
+        <x:v>-19405</x:v>
       </x:c>
     </x:row>
     <x:row r="572" spans="1:7">
@@ -16055,22 +16058,22 @@
         <x:v>630</x:v>
       </x:c>
       <x:c r="B572" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C572" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D572" s="1">
-        <x:v>0</x:v>
+        <x:v>1491280</x:v>
       </x:c>
       <x:c r="E572" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F572" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>500</x:v>
+        <x:v>1491280</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -16078,10 +16081,10 @@
         <x:v>631</x:v>
       </x:c>
       <x:c r="B573" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C573" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D573" s="1">
         <x:v>0</x:v>
@@ -16090,10 +16093,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F573" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G573" s="1">
-        <x:v>50</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="574" spans="1:7">
@@ -16101,7 +16104,7 @@
         <x:v>632</x:v>
       </x:c>
       <x:c r="B574" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C574" s="1">
         <x:v>50</x:v>
@@ -16113,10 +16116,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F574" s="1">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G574" s="1">
-        <x:v>300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="575" spans="1:7">
@@ -16124,7 +16127,7 @@
         <x:v>633</x:v>
       </x:c>
       <x:c r="B575" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C575" s="1">
         <x:v>50</x:v>
@@ -16136,10 +16139,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F575" s="1">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="G575" s="1">
-        <x:v>50</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="576" spans="1:7">
@@ -16147,7 +16150,7 @@
         <x:v>634</x:v>
       </x:c>
       <x:c r="B576" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C576" s="1">
         <x:v>50</x:v>
@@ -16159,10 +16162,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F576" s="1">
-        <x:v>1287</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G576" s="1">
-        <x:v>1337</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="577" spans="1:7">
@@ -16170,10 +16173,10 @@
         <x:v>635</x:v>
       </x:c>
       <x:c r="B577" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C577" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D577" s="1">
         <x:v>0</x:v>
@@ -16182,10 +16185,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F577" s="1">
-        <x:v>6697</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G577" s="1">
-        <x:v>6697</x:v>
+        <x:v>1337</x:v>
       </x:c>
     </x:row>
     <x:row r="578" spans="1:7">
@@ -16193,10 +16196,10 @@
         <x:v>636</x:v>
       </x:c>
       <x:c r="B578" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C578" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D578" s="1">
         <x:v>0</x:v>
@@ -16205,10 +16208,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F578" s="1">
-        <x:v>0</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="G578" s="1">
-        <x:v>50</x:v>
+        <x:v>6697</x:v>
       </x:c>
     </x:row>
     <x:row r="579" spans="1:7">
@@ -16216,10 +16219,10 @@
         <x:v>637</x:v>
       </x:c>
       <x:c r="B579" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C579" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D579" s="1">
         <x:v>0</x:v>
@@ -16228,10 +16231,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F579" s="1">
-        <x:v>4000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G579" s="1">
-        <x:v>4000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="580" spans="1:7">
@@ -16239,7 +16242,7 @@
         <x:v>638</x:v>
       </x:c>
       <x:c r="B580" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C580" s="1">
         <x:v>0</x:v>
@@ -16251,10 +16254,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F580" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="G580" s="1">
-        <x:v>6500</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="581" spans="1:7">
@@ -16262,10 +16265,10 @@
         <x:v>639</x:v>
       </x:c>
       <x:c r="B581" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C581" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D581" s="1">
         <x:v>0</x:v>
@@ -16274,10 +16277,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F581" s="1">
-        <x:v>0</x:v>
+        <x:v>6500</x:v>
       </x:c>
       <x:c r="G581" s="1">
-        <x:v>50</x:v>
+        <x:v>6500</x:v>
       </x:c>
     </x:row>
     <x:row r="582" spans="1:7">
@@ -16285,7 +16288,7 @@
         <x:v>640</x:v>
       </x:c>
       <x:c r="B582" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C582" s="1">
         <x:v>50</x:v>
@@ -16308,7 +16311,7 @@
         <x:v>641</x:v>
       </x:c>
       <x:c r="B583" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C583" s="1">
         <x:v>50</x:v>
@@ -16331,22 +16334,22 @@
         <x:v>642</x:v>
       </x:c>
       <x:c r="B584" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C584" s="1">
-        <x:v>7500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D584" s="1">
-        <x:v>1400000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E584" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F584" s="1">
-        <x:v>10500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G584" s="1">
-        <x:v>1418000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:7">
@@ -16354,22 +16357,22 @@
         <x:v>643</x:v>
       </x:c>
       <x:c r="B585" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>50</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D585" s="1">
-        <x:v>0</x:v>
+        <x:v>1400000</x:v>
       </x:c>
       <x:c r="E585" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F585" s="1">
-        <x:v>0</x:v>
+        <x:v>10500</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>50</x:v>
+        <x:v>1418000</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -16377,10 +16380,10 @@
         <x:v>644</x:v>
       </x:c>
       <x:c r="B586" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C586" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D586" s="1">
         <x:v>0</x:v>
@@ -16389,10 +16392,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F586" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G586" s="1">
-        <x:v>1500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:7">
@@ -16400,10 +16403,10 @@
         <x:v>645</x:v>
       </x:c>
       <x:c r="B587" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C587" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D587" s="1">
         <x:v>0</x:v>
@@ -16415,7 +16418,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G587" s="1">
-        <x:v>1550</x:v>
+        <x:v>1500</x:v>
       </x:c>
     </x:row>
     <x:row r="588" spans="1:7">
@@ -16423,7 +16426,7 @@
         <x:v>646</x:v>
       </x:c>
       <x:c r="B588" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C588" s="1">
         <x:v>50</x:v>
@@ -16435,10 +16438,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F588" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G588" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:7">
@@ -16446,7 +16449,7 @@
         <x:v>647</x:v>
       </x:c>
       <x:c r="B589" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C589" s="1">
         <x:v>50</x:v>
@@ -16469,7 +16472,7 @@
         <x:v>648</x:v>
       </x:c>
       <x:c r="B590" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C590" s="1">
         <x:v>50</x:v>
@@ -16492,7 +16495,7 @@
         <x:v>649</x:v>
       </x:c>
       <x:c r="B591" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C591" s="1">
         <x:v>50</x:v>
@@ -16515,7 +16518,7 @@
         <x:v>650</x:v>
       </x:c>
       <x:c r="B592" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C592" s="1">
         <x:v>50</x:v>
@@ -16538,13 +16541,13 @@
         <x:v>651</x:v>
       </x:c>
       <x:c r="B593" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C593" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D593" s="1">
-        <x:v>275541</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E593" s="1">
         <x:v>0</x:v>
@@ -16553,7 +16556,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G593" s="1">
-        <x:v>275541</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="594" spans="1:7">
@@ -16561,22 +16564,22 @@
         <x:v>652</x:v>
       </x:c>
       <x:c r="B594" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C594" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D594" s="1">
-        <x:v>0</x:v>
+        <x:v>275541</x:v>
       </x:c>
       <x:c r="E594" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F594" s="1">
-        <x:v>81050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G594" s="1">
-        <x:v>81050</x:v>
+        <x:v>275541</x:v>
       </x:c>
     </x:row>
     <x:row r="595" spans="1:7">
@@ -16584,10 +16587,10 @@
         <x:v>653</x:v>
       </x:c>
       <x:c r="B595" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C595" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D595" s="1">
         <x:v>0</x:v>
@@ -16596,10 +16599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F595" s="1">
-        <x:v>0</x:v>
+        <x:v>81050</x:v>
       </x:c>
       <x:c r="G595" s="1">
-        <x:v>50</x:v>
+        <x:v>81050</x:v>
       </x:c>
     </x:row>
     <x:row r="596" spans="1:7">
@@ -16607,7 +16610,7 @@
         <x:v>654</x:v>
       </x:c>
       <x:c r="B596" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C596" s="1">
         <x:v>50</x:v>
@@ -16630,10 +16633,10 @@
         <x:v>655</x:v>
       </x:c>
       <x:c r="B597" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C597" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D597" s="1">
         <x:v>0</x:v>
@@ -16645,7 +16648,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G597" s="1">
-        <x:v>2850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="598" spans="1:7">
@@ -16653,10 +16656,10 @@
         <x:v>656</x:v>
       </x:c>
       <x:c r="B598" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C598" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
       <x:c r="D598" s="1">
         <x:v>0</x:v>
@@ -16668,7 +16671,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G598" s="1">
-        <x:v>50</x:v>
+        <x:v>2850</x:v>
       </x:c>
     </x:row>
     <x:row r="599" spans="1:7">
@@ -16676,7 +16679,7 @@
         <x:v>657</x:v>
       </x:c>
       <x:c r="B599" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C599" s="1">
         <x:v>50</x:v>
@@ -16688,10 +16691,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F599" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G599" s="1">
-        <x:v>14050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="600" spans="1:7">
@@ -16699,10 +16702,10 @@
         <x:v>658</x:v>
       </x:c>
       <x:c r="B600" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C600" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D600" s="1">
         <x:v>0</x:v>
@@ -16711,10 +16714,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F600" s="1">
-        <x:v>2700</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G600" s="1">
-        <x:v>2700</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="601" spans="1:7">
@@ -16722,7 +16725,7 @@
         <x:v>659</x:v>
       </x:c>
       <x:c r="B601" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C601" s="1">
         <x:v>0</x:v>
@@ -16734,10 +16737,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F601" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G601" s="1">
-        <x:v>1000</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:7">
@@ -16745,27 +16748,27 @@
         <x:v>660</x:v>
       </x:c>
       <x:c r="B602" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C602" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D602" s="1">
-        <x:v>14446984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E602" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F602" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G602" s="1">
-        <x:v>14446984</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:7">
       <x:c r="A603" s="1" t="s">
-        <x:v>660</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
         <x:v>50</x:v>
@@ -16791,13 +16794,13 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C604" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D604" s="1">
-        <x:v>0</x:v>
+        <x:v>14446984</x:v>
       </x:c>
       <x:c r="E604" s="1">
         <x:v>0</x:v>
@@ -16806,7 +16809,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G604" s="1">
-        <x:v>50</x:v>
+        <x:v>14446984</x:v>
       </x:c>
     </x:row>
     <x:row r="605" spans="1:7">
@@ -16814,22 +16817,22 @@
         <x:v>662</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C605" s="1">
-        <x:v>12050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D605" s="1">
-        <x:v>2470488</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E605" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F605" s="1">
-        <x:v>11834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G605" s="1">
-        <x:v>2494372</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:7">
@@ -16837,22 +16840,22 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="C606" s="1">
-        <x:v>100</x:v>
+        <x:v>12050</x:v>
       </x:c>
       <x:c r="D606" s="1">
-        <x:v>0</x:v>
+        <x:v>2470488</x:v>
       </x:c>
       <x:c r="E606" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F606" s="1">
-        <x:v>0</x:v>
+        <x:v>11834</x:v>
       </x:c>
       <x:c r="G606" s="1">
-        <x:v>100</x:v>
+        <x:v>2494372</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:7">
@@ -16860,10 +16863,10 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C607" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D607" s="1">
         <x:v>0</x:v>
@@ -16875,7 +16878,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G607" s="1">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="608" spans="1:7">
@@ -16883,7 +16886,7 @@
         <x:v>665</x:v>
       </x:c>
       <x:c r="B608" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C608" s="1">
         <x:v>50</x:v>
@@ -16909,7 +16912,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C609" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D609" s="1">
         <x:v>0</x:v>
@@ -16918,10 +16921,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F609" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G609" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="610" spans="1:7">
@@ -16929,10 +16932,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B610" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C610" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D610" s="1">
         <x:v>0</x:v>
@@ -16941,10 +16944,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F610" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G610" s="1">
-        <x:v>2550</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="611" spans="1:7">
@@ -16952,7 +16955,7 @@
         <x:v>668</x:v>
       </x:c>
       <x:c r="B611" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C611" s="1">
         <x:v>50</x:v>
@@ -16964,10 +16967,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F611" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G611" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="612" spans="1:7">
@@ -16975,7 +16978,7 @@
         <x:v>669</x:v>
       </x:c>
       <x:c r="B612" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C612" s="1">
         <x:v>50</x:v>
@@ -16998,7 +17001,7 @@
         <x:v>670</x:v>
       </x:c>
       <x:c r="B613" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C613" s="1">
         <x:v>50</x:v>
@@ -17021,7 +17024,7 @@
         <x:v>671</x:v>
       </x:c>
       <x:c r="B614" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C614" s="1">
         <x:v>50</x:v>
@@ -17044,22 +17047,22 @@
         <x:v>672</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D615" s="1">
-        <x:v>3975320</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E615" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>6634</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>3982954</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -17067,22 +17070,22 @@
         <x:v>673</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D616" s="1">
-        <x:v>0</x:v>
+        <x:v>3975320</x:v>
       </x:c>
       <x:c r="E616" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>22000</x:v>
+        <x:v>6634</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>22000</x:v>
+        <x:v>3982954</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -17090,10 +17093,10 @@
         <x:v>674</x:v>
       </x:c>
       <x:c r="B617" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C617" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D617" s="1">
         <x:v>0</x:v>
@@ -17102,10 +17105,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F617" s="1">
-        <x:v>5800</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G617" s="1">
-        <x:v>5850</x:v>
+        <x:v>22000</x:v>
       </x:c>
     </x:row>
     <x:row r="618" spans="1:7">
@@ -17113,7 +17116,7 @@
         <x:v>675</x:v>
       </x:c>
       <x:c r="B618" s="1" t="s">
-        <x:v>676</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C618" s="1">
         <x:v>50</x:v>
@@ -17125,21 +17128,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F618" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G618" s="1">
-        <x:v>50</x:v>
+        <x:v>5850</x:v>
       </x:c>
     </x:row>
     <x:row r="619" spans="1:7">
       <x:c r="A619" s="1" t="s">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c r="B619" s="1" t="s">
         <x:v>677</x:v>
       </x:c>
-      <x:c r="B619" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C619" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D619" s="1">
         <x:v>0</x:v>
@@ -17148,10 +17151,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F619" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G619" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="620" spans="1:7">
@@ -17159,10 +17162,10 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="B620" s="1" t="s">
-        <x:v>679</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C620" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D620" s="1">
         <x:v>0</x:v>
@@ -17171,18 +17174,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F620" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G620" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="621" spans="1:7">
       <x:c r="A621" s="1" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="B621" s="1" t="s">
         <x:v>680</x:v>
-      </x:c>
-      <x:c r="B621" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
       <x:c r="C621" s="1">
         <x:v>50</x:v>
@@ -17205,10 +17208,10 @@
         <x:v>681</x:v>
       </x:c>
       <x:c r="B622" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C622" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D622" s="1">
         <x:v>0</x:v>
@@ -17217,15 +17220,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F622" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G622" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="623" spans="1:7">
       <x:c r="A623" s="1" t="s">
-        <x:v>681</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
         <x:v>460</x:v>
@@ -17251,10 +17254,10 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C624" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D624" s="1">
         <x:v>0</x:v>
@@ -17263,10 +17266,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F624" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G624" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="625" spans="1:7">
@@ -17274,7 +17277,7 @@
         <x:v>683</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C625" s="1">
         <x:v>50</x:v>
@@ -17297,10 +17300,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17309,10 +17312,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>68600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>71150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17320,10 +17323,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17332,10 +17335,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>0</x:v>
+        <x:v>68600</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>50</x:v>
+        <x:v>71150</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
@@ -17343,7 +17346,7 @@
         <x:v>686</x:v>
       </x:c>
       <x:c r="B628" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C628" s="1">
         <x:v>50</x:v>
@@ -17366,10 +17369,10 @@
         <x:v>687</x:v>
       </x:c>
       <x:c r="B629" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C629" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D629" s="1">
         <x:v>0</x:v>
@@ -17378,10 +17381,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F629" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G629" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="630" spans="1:7">
@@ -17389,10 +17392,10 @@
         <x:v>688</x:v>
       </x:c>
       <x:c r="B630" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C630" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="D630" s="1">
         <x:v>0</x:v>
@@ -17401,10 +17404,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F630" s="1">
-        <x:v>58000</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="G630" s="1">
-        <x:v>58050</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="631" spans="1:7">
@@ -17412,10 +17415,10 @@
         <x:v>689</x:v>
       </x:c>
       <x:c r="B631" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C631" s="1">
-        <x:v>2050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D631" s="1">
         <x:v>0</x:v>
@@ -17424,10 +17427,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F631" s="1">
-        <x:v>1666</x:v>
+        <x:v>58000</x:v>
       </x:c>
       <x:c r="G631" s="1">
-        <x:v>3716</x:v>
+        <x:v>58050</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:7">
@@ -17435,10 +17438,10 @@
         <x:v>690</x:v>
       </x:c>
       <x:c r="B632" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C632" s="1">
-        <x:v>0</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D632" s="1">
         <x:v>0</x:v>
@@ -17447,10 +17450,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F632" s="1">
-        <x:v>1668</x:v>
+        <x:v>1666</x:v>
       </x:c>
       <x:c r="G632" s="1">
-        <x:v>1668</x:v>
+        <x:v>3716</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:7">
@@ -17458,10 +17461,10 @@
         <x:v>691</x:v>
       </x:c>
       <x:c r="B633" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C633" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D633" s="1">
         <x:v>0</x:v>
@@ -17470,10 +17473,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F633" s="1">
-        <x:v>0</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G633" s="1">
-        <x:v>50</x:v>
+        <x:v>1668</x:v>
       </x:c>
     </x:row>
     <x:row r="634" spans="1:7">
@@ -17481,13 +17484,13 @@
         <x:v>692</x:v>
       </x:c>
       <x:c r="B634" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C634" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D634" s="1">
-        <x:v>105040</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E634" s="1">
         <x:v>0</x:v>
@@ -17496,7 +17499,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G634" s="1">
-        <x:v>105090</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="635" spans="1:7">
@@ -17504,22 +17507,22 @@
         <x:v>693</x:v>
       </x:c>
       <x:c r="B635" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C635" s="1">
-        <x:v>2950</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D635" s="1">
-        <x:v>0</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="E635" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F635" s="1">
-        <x:v>30600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G635" s="1">
-        <x:v>33550</x:v>
+        <x:v>105090</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:7">
@@ -17527,10 +17530,10 @@
         <x:v>694</x:v>
       </x:c>
       <x:c r="B636" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C636" s="1">
-        <x:v>2550</x:v>
+        <x:v>2950</x:v>
       </x:c>
       <x:c r="D636" s="1">
         <x:v>0</x:v>
@@ -17539,10 +17542,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F636" s="1">
-        <x:v>0</x:v>
+        <x:v>30600</x:v>
       </x:c>
       <x:c r="G636" s="1">
-        <x:v>2550</x:v>
+        <x:v>33550</x:v>
       </x:c>
     </x:row>
     <x:row r="637" spans="1:7">
@@ -17550,22 +17553,22 @@
         <x:v>695</x:v>
       </x:c>
       <x:c r="B637" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C637" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D637" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E637" s="1">
-        <x:v>56045</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F637" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G637" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="638" spans="1:7">
@@ -17582,7 +17585,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E638" s="1">
-        <x:v>0</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="F638" s="1">
         <x:v>0</x:v>
@@ -17596,10 +17599,10 @@
         <x:v>697</x:v>
       </x:c>
       <x:c r="B639" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C639" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D639" s="1">
         <x:v>0</x:v>
@@ -17611,7 +17614,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G639" s="1">
-        <x:v>2550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:7">
@@ -17619,10 +17622,10 @@
         <x:v>698</x:v>
       </x:c>
       <x:c r="B640" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C640" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
       <x:c r="D640" s="1">
         <x:v>0</x:v>
@@ -17634,7 +17637,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G640" s="1">
-        <x:v>50</x:v>
+        <x:v>2550</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:7">
@@ -17642,10 +17645,10 @@
         <x:v>699</x:v>
       </x:c>
       <x:c r="B641" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C641" s="1">
-        <x:v>4550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D641" s="1">
         <x:v>0</x:v>
@@ -17654,15 +17657,15 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F641" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G641" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="642" spans="1:7">
       <x:c r="A642" s="1" t="s">
-        <x:v>699</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
         <x:v>19</x:v>
@@ -17688,22 +17691,22 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="B643" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C643" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D643" s="1">
-        <x:v>852561</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E643" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F643" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G643" s="1">
-        <x:v>852561</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="644" spans="1:7">
@@ -17711,13 +17714,13 @@
         <x:v>701</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>0</x:v>
+        <x:v>852561</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
@@ -17726,7 +17729,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>50</x:v>
+        <x:v>852561</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17734,7 +17737,7 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C645" s="1">
         <x:v>50</x:v>
@@ -17757,13 +17760,13 @@
         <x:v>703</x:v>
       </x:c>
       <x:c r="B646" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C646" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D646" s="1">
-        <x:v>2200000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E646" s="1">
         <x:v>0</x:v>
@@ -17772,7 +17775,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G646" s="1">
-        <x:v>2200000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:7">
@@ -17780,13 +17783,13 @@
         <x:v>704</x:v>
       </x:c>
       <x:c r="B647" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C647" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D647" s="1">
-        <x:v>0</x:v>
+        <x:v>2200000</x:v>
       </x:c>
       <x:c r="E647" s="1">
         <x:v>0</x:v>
@@ -17795,7 +17798,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G647" s="1">
-        <x:v>50</x:v>
+        <x:v>2200000</x:v>
       </x:c>
     </x:row>
     <x:row r="648" spans="1:7">
@@ -17803,7 +17806,7 @@
         <x:v>705</x:v>
       </x:c>
       <x:c r="B648" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C648" s="1">
         <x:v>50</x:v>
@@ -17826,7 +17829,7 @@
         <x:v>706</x:v>
       </x:c>
       <x:c r="B649" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C649" s="1">
         <x:v>50</x:v>
@@ -17849,10 +17852,10 @@
         <x:v>707</x:v>
       </x:c>
       <x:c r="B650" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C650" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D650" s="1">
         <x:v>0</x:v>
@@ -17864,7 +17867,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G650" s="1">
-        <x:v>5000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:7">
@@ -17872,10 +17875,10 @@
         <x:v>708</x:v>
       </x:c>
       <x:c r="B651" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C651" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D651" s="1">
         <x:v>0</x:v>
@@ -17887,7 +17890,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G651" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:7">
@@ -17895,10 +17898,10 @@
         <x:v>709</x:v>
       </x:c>
       <x:c r="B652" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C652" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D652" s="1">
         <x:v>0</x:v>
@@ -17910,7 +17913,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G652" s="1">
-        <x:v>10050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:7">
@@ -17918,10 +17921,10 @@
         <x:v>710</x:v>
       </x:c>
       <x:c r="B653" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C653" s="1">
-        <x:v>1050</x:v>
+        <x:v>10050</x:v>
       </x:c>
       <x:c r="D653" s="1">
         <x:v>0</x:v>
@@ -17930,10 +17933,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F653" s="1">
-        <x:v>1667</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G653" s="1">
-        <x:v>2717</x:v>
+        <x:v>10050</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:7">
@@ -17941,10 +17944,10 @@
         <x:v>711</x:v>
       </x:c>
       <x:c r="B654" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C654" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D654" s="1">
         <x:v>0</x:v>
@@ -17953,10 +17956,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F654" s="1">
-        <x:v>0</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G654" s="1">
-        <x:v>50</x:v>
+        <x:v>2717</x:v>
       </x:c>
     </x:row>
     <x:row r="655" spans="1:7">
@@ -17964,22 +17967,22 @@
         <x:v>712</x:v>
       </x:c>
       <x:c r="B655" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C655" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D655" s="1">
-        <x:v>111599</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E655" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F655" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G655" s="1">
-        <x:v>114899</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="656" spans="1:7">
@@ -17987,22 +17990,22 @@
         <x:v>713</x:v>
       </x:c>
       <x:c r="B656" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C656" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D656" s="1">
-        <x:v>0</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="E656" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F656" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G656" s="1">
-        <x:v>50</x:v>
+        <x:v>114899</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:7">
@@ -18010,7 +18013,7 @@
         <x:v>714</x:v>
       </x:c>
       <x:c r="B657" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C657" s="1">
         <x:v>50</x:v>
@@ -18030,16 +18033,16 @@
     </x:row>
     <x:row r="658" spans="1:7">
       <x:c r="A658" s="1" t="s">
-        <x:v>714</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B658" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C658" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D658" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E658" s="1">
         <x:v>0</x:v>
@@ -18048,7 +18051,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G658" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:7">
@@ -18056,13 +18059,13 @@
         <x:v>715</x:v>
       </x:c>
       <x:c r="B659" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C659" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D659" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E659" s="1">
         <x:v>0</x:v>
@@ -18071,7 +18074,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G659" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:7">
@@ -18079,22 +18082,22 @@
         <x:v>716</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C660" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D660" s="1">
-        <x:v>10046680</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E660" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F660" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>10048730</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18102,22 +18105,22 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C661" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>2263800</x:v>
+        <x:v>10046680</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F661" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>2263850</x:v>
+        <x:v>10048730</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18125,13 +18128,13 @@
         <x:v>718</x:v>
       </x:c>
       <x:c r="B662" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C662" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D662" s="1">
-        <x:v>0</x:v>
+        <x:v>2263800</x:v>
       </x:c>
       <x:c r="E662" s="1">
         <x:v>0</x:v>
@@ -18140,7 +18143,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G662" s="1">
-        <x:v>50</x:v>
+        <x:v>2263850</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:7">
@@ -18148,7 +18151,7 @@
         <x:v>719</x:v>
       </x:c>
       <x:c r="B663" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C663" s="1">
         <x:v>50</x:v>
@@ -18160,10 +18163,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F663" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G663" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:7">
@@ -18171,10 +18174,10 @@
         <x:v>720</x:v>
       </x:c>
       <x:c r="B664" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C664" s="1">
-        <x:v>6050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D664" s="1">
         <x:v>0</x:v>
@@ -18183,10 +18186,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F664" s="1">
-        <x:v>52333</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G664" s="1">
-        <x:v>58383</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:7">
@@ -18194,10 +18197,10 @@
         <x:v>721</x:v>
       </x:c>
       <x:c r="B665" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C665" s="1">
-        <x:v>50</x:v>
+        <x:v>6050</x:v>
       </x:c>
       <x:c r="D665" s="1">
         <x:v>0</x:v>
@@ -18206,10 +18209,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F665" s="1">
-        <x:v>0</x:v>
+        <x:v>52333</x:v>
       </x:c>
       <x:c r="G665" s="1">
-        <x:v>50</x:v>
+        <x:v>58383</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:7">
@@ -18217,7 +18220,7 @@
         <x:v>722</x:v>
       </x:c>
       <x:c r="B666" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C666" s="1">
         <x:v>50</x:v>
@@ -18240,10 +18243,10 @@
         <x:v>723</x:v>
       </x:c>
       <x:c r="B667" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C667" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D667" s="1">
         <x:v>0</x:v>
@@ -18252,10 +18255,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F667" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G667" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:7">
@@ -18263,22 +18266,22 @@
         <x:v>724</x:v>
       </x:c>
       <x:c r="B668" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C668" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D668" s="1">
-        <x:v>367531</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E668" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F668" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G668" s="1">
-        <x:v>367531</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:7">
@@ -18286,22 +18289,22 @@
         <x:v>725</x:v>
       </x:c>
       <x:c r="B669" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C669" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D669" s="1">
-        <x:v>817169</x:v>
+        <x:v>367531</x:v>
       </x:c>
       <x:c r="E669" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F669" s="1">
-        <x:v>1668</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G669" s="1">
-        <x:v>820837</x:v>
+        <x:v>367531</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:7">
@@ -18309,22 +18312,22 @@
         <x:v>726</x:v>
       </x:c>
       <x:c r="B670" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C670" s="1">
-        <x:v>11050</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D670" s="1">
-        <x:v>0</x:v>
+        <x:v>817169</x:v>
       </x:c>
       <x:c r="E670" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F670" s="1">
-        <x:v>6242</x:v>
+        <x:v>1668</x:v>
       </x:c>
       <x:c r="G670" s="1">
-        <x:v>17292</x:v>
+        <x:v>820837</x:v>
       </x:c>
     </x:row>
     <x:row r="671" spans="1:7">
@@ -18332,10 +18335,10 @@
         <x:v>727</x:v>
       </x:c>
       <x:c r="B671" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C671" s="1">
-        <x:v>50</x:v>
+        <x:v>11050</x:v>
       </x:c>
       <x:c r="D671" s="1">
         <x:v>0</x:v>
@@ -18344,10 +18347,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F671" s="1">
-        <x:v>0</x:v>
+        <x:v>6242</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>50</x:v>
+        <x:v>17292</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">
@@ -18355,7 +18358,7 @@
         <x:v>728</x:v>
       </x:c>
       <x:c r="B672" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C672" s="1">
         <x:v>50</x:v>
@@ -18378,10 +18381,10 @@
         <x:v>729</x:v>
       </x:c>
       <x:c r="B673" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C673" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D673" s="1">
         <x:v>0</x:v>
@@ -18390,10 +18393,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F673" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G673" s="1">
-        <x:v>500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="674" spans="1:7">
@@ -18401,10 +18404,10 @@
         <x:v>730</x:v>
       </x:c>
       <x:c r="B674" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C674" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D674" s="1">
         <x:v>0</x:v>
@@ -18413,10 +18416,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F674" s="1">
-        <x:v>25000</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G674" s="1">
-        <x:v>25050</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="675" spans="1:7">
@@ -18424,7 +18427,7 @@
         <x:v>731</x:v>
       </x:c>
       <x:c r="B675" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C675" s="1">
         <x:v>50</x:v>
@@ -18436,10 +18439,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F675" s="1">
-        <x:v>0</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G675" s="1">
-        <x:v>50</x:v>
+        <x:v>25050</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:7">
@@ -18447,22 +18450,22 @@
         <x:v>732</x:v>
       </x:c>
       <x:c r="B676" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C676" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D676" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E676" s="1">
-        <x:v>1531015</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F676" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G676" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="677" spans="1:7">
@@ -18470,22 +18473,22 @@
         <x:v>733</x:v>
       </x:c>
       <x:c r="B677" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C677" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D677" s="1">
-        <x:v>157560</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E677" s="1">
-        <x:v>0</x:v>
+        <x:v>1531015</x:v>
       </x:c>
       <x:c r="F677" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>157610</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
@@ -18493,13 +18496,13 @@
         <x:v>734</x:v>
       </x:c>
       <x:c r="B678" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C678" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D678" s="1">
-        <x:v>0</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="E678" s="1">
         <x:v>0</x:v>
@@ -18508,7 +18511,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G678" s="1">
-        <x:v>50</x:v>
+        <x:v>157610</x:v>
       </x:c>
     </x:row>
     <x:row r="679" spans="1:7">
@@ -18516,13 +18519,13 @@
         <x:v>735</x:v>
       </x:c>
       <x:c r="B679" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C679" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D679" s="1">
-        <x:v>5583432</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E679" s="1">
         <x:v>0</x:v>
@@ -18531,7 +18534,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G679" s="1">
-        <x:v>5584432</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:7">
@@ -18539,13 +18542,13 @@
         <x:v>736</x:v>
       </x:c>
       <x:c r="B680" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C680" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D680" s="1">
-        <x:v>0</x:v>
+        <x:v>5583432</x:v>
       </x:c>
       <x:c r="E680" s="1">
         <x:v>0</x:v>
@@ -18554,7 +18557,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G680" s="1">
-        <x:v>50</x:v>
+        <x:v>5584432</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:7">
@@ -18562,22 +18565,22 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="B681" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C681" s="1">
-        <x:v>25550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D681" s="1">
-        <x:v>764206</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E681" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F681" s="1">
-        <x:v>20501</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G681" s="1">
-        <x:v>810257</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:7">
@@ -18585,22 +18588,22 @@
         <x:v>738</x:v>
       </x:c>
       <x:c r="B682" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C682" s="1">
-        <x:v>0</x:v>
+        <x:v>25550</x:v>
       </x:c>
       <x:c r="D682" s="1">
-        <x:v>0</x:v>
+        <x:v>764206</x:v>
       </x:c>
       <x:c r="E682" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F682" s="1">
-        <x:v>2700</x:v>
+        <x:v>20501</x:v>
       </x:c>
       <x:c r="G682" s="1">
-        <x:v>2700</x:v>
+        <x:v>810257</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:7">
@@ -18608,22 +18611,22 @@
         <x:v>739</x:v>
       </x:c>
       <x:c r="B683" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C683" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D683" s="1">
-        <x:v>1543316</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E683" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F683" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G683" s="1">
-        <x:v>1543316</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:7">
@@ -18631,22 +18634,22 @@
         <x:v>740</x:v>
       </x:c>
       <x:c r="B684" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C684" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D684" s="1">
-        <x:v>0</x:v>
+        <x:v>1543316</x:v>
       </x:c>
       <x:c r="E684" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F684" s="1">
-        <x:v>14500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G684" s="1">
-        <x:v>14550</x:v>
+        <x:v>1543316</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:7">
@@ -18654,7 +18657,7 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B685" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C685" s="1">
         <x:v>50</x:v>
@@ -18666,10 +18669,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F685" s="1">
-        <x:v>0</x:v>
+        <x:v>14500</x:v>
       </x:c>
       <x:c r="G685" s="1">
-        <x:v>50</x:v>
+        <x:v>14550</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:7">
@@ -18677,7 +18680,7 @@
         <x:v>742</x:v>
       </x:c>
       <x:c r="B686" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C686" s="1">
         <x:v>50</x:v>
@@ -18700,13 +18703,13 @@
         <x:v>743</x:v>
       </x:c>
       <x:c r="B687" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C687" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D687" s="1">
-        <x:v>619349</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E687" s="1">
         <x:v>0</x:v>
@@ -18715,7 +18718,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G687" s="1">
-        <x:v>619399</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:7">
@@ -18723,22 +18726,22 @@
         <x:v>744</x:v>
       </x:c>
       <x:c r="B688" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C688" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D688" s="1">
-        <x:v>0</x:v>
+        <x:v>619349</x:v>
       </x:c>
       <x:c r="E688" s="1">
-        <x:v>10135449</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F688" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G688" s="1">
-        <x:v>0</x:v>
+        <x:v>619399</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:7">
@@ -18746,22 +18749,22 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="B689" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C689" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D689" s="1">
-        <x:v>103020</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E689" s="1">
-        <x:v>0</x:v>
+        <x:v>10135449</x:v>
       </x:c>
       <x:c r="F689" s="1">
-        <x:v>3334</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G689" s="1">
-        <x:v>106354</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="690" spans="1:7">
@@ -18769,22 +18772,22 @@
         <x:v>746</x:v>
       </x:c>
       <x:c r="B690" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C690" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D690" s="1">
-        <x:v>0</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="E690" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F690" s="1">
-        <x:v>0</x:v>
+        <x:v>3334</x:v>
       </x:c>
       <x:c r="G690" s="1">
-        <x:v>2500</x:v>
+        <x:v>106354</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:7">
@@ -18792,13 +18795,13 @@
         <x:v>747</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D691" s="1">
-        <x:v>106947</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E691" s="1">
         <x:v>0</x:v>
@@ -18807,7 +18810,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>106947</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -18815,22 +18818,22 @@
         <x:v>748</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>2050</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D692" s="1">
-        <x:v>0</x:v>
+        <x:v>106947</x:v>
       </x:c>
       <x:c r="E692" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>25000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>27050</x:v>
+        <x:v>106947</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -18838,22 +18841,22 @@
         <x:v>749</x:v>
       </x:c>
       <x:c r="B693" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C693" s="1">
-        <x:v>1050</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="D693" s="1">
-        <x:v>902176</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E693" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F693" s="1">
-        <x:v>7000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="G693" s="1">
-        <x:v>910226</x:v>
+        <x:v>27050</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:7">
@@ -18861,22 +18864,22 @@
         <x:v>750</x:v>
       </x:c>
       <x:c r="B694" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C694" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D694" s="1">
-        <x:v>0</x:v>
+        <x:v>902176</x:v>
       </x:c>
       <x:c r="E694" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F694" s="1">
-        <x:v>25500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="G694" s="1">
-        <x:v>25550</x:v>
+        <x:v>910226</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:7">
@@ -18896,10 +18899,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F695" s="1">
-        <x:v>0</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="G695" s="1">
-        <x:v>50</x:v>
+        <x:v>25550</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:7">
@@ -18907,10 +18910,10 @@
         <x:v>752</x:v>
       </x:c>
       <x:c r="B696" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C696" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D696" s="1">
         <x:v>0</x:v>
@@ -18919,10 +18922,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F696" s="1">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G696" s="1">
-        <x:v>14000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:7">
@@ -18930,7 +18933,7 @@
         <x:v>753</x:v>
       </x:c>
       <x:c r="B697" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C697" s="1">
         <x:v>0</x:v>
@@ -18942,10 +18945,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F697" s="1">
-        <x:v>6200</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G697" s="1">
-        <x:v>6200</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:7">
@@ -18953,10 +18956,10 @@
         <x:v>754</x:v>
       </x:c>
       <x:c r="B698" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C698" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D698" s="1">
         <x:v>0</x:v>
@@ -18965,10 +18968,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F698" s="1">
-        <x:v>0</x:v>
+        <x:v>6200</x:v>
       </x:c>
       <x:c r="G698" s="1">
-        <x:v>50</x:v>
+        <x:v>6200</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:7">
@@ -18976,10 +18979,10 @@
         <x:v>755</x:v>
       </x:c>
       <x:c r="B699" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C699" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D699" s="1">
         <x:v>0</x:v>
@@ -18991,7 +18994,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G699" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:7">
@@ -18999,10 +19002,10 @@
         <x:v>756</x:v>
       </x:c>
       <x:c r="B700" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C700" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D700" s="1">
         <x:v>0</x:v>
@@ -19011,10 +19014,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F700" s="1">
-        <x:v>6600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>6650</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
@@ -19022,22 +19025,22 @@
         <x:v>757</x:v>
       </x:c>
       <x:c r="B701" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C701" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D701" s="1">
-        <x:v>2772295</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E701" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F701" s="1">
-        <x:v>0</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G701" s="1">
-        <x:v>2772295</x:v>
+        <x:v>6650</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:7">
@@ -19045,22 +19048,22 @@
         <x:v>758</x:v>
       </x:c>
       <x:c r="B702" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C702" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D702" s="1">
-        <x:v>0</x:v>
+        <x:v>2772295</x:v>
       </x:c>
       <x:c r="E702" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F702" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G702" s="1">
-        <x:v>5000</x:v>
+        <x:v>2772295</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:7">
@@ -19068,10 +19071,10 @@
         <x:v>759</x:v>
       </x:c>
       <x:c r="B703" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C703" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D703" s="1">
         <x:v>0</x:v>
@@ -19080,10 +19083,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F703" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G703" s="1">
-        <x:v>50</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:7">
@@ -19091,10 +19094,10 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="B704" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C704" s="1">
-        <x:v>6550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D704" s="1">
         <x:v>0</x:v>
@@ -19103,10 +19106,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F704" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G704" s="1">
-        <x:v>9850</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:7">
@@ -19114,10 +19117,10 @@
         <x:v>761</x:v>
       </x:c>
       <x:c r="B705" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C705" s="1">
-        <x:v>50</x:v>
+        <x:v>6550</x:v>
       </x:c>
       <x:c r="D705" s="1">
         <x:v>0</x:v>
@@ -19126,10 +19129,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F705" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G705" s="1">
-        <x:v>50</x:v>
+        <x:v>9850</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:7">
@@ -19137,7 +19140,7 @@
         <x:v>762</x:v>
       </x:c>
       <x:c r="B706" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C706" s="1">
         <x:v>50</x:v>
@@ -19160,10 +19163,10 @@
         <x:v>763</x:v>
       </x:c>
       <x:c r="B707" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C707" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D707" s="1">
         <x:v>0</x:v>
@@ -19172,10 +19175,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F707" s="1">
-        <x:v>6000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G707" s="1">
-        <x:v>9550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:7">
@@ -19183,10 +19186,10 @@
         <x:v>764</x:v>
       </x:c>
       <x:c r="B708" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="C708" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D708" s="1">
         <x:v>0</x:v>
@@ -19195,10 +19198,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F708" s="1">
-        <x:v>2700</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="G708" s="1">
-        <x:v>2700</x:v>
+        <x:v>9550</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:7">
@@ -19206,10 +19209,10 @@
         <x:v>765</x:v>
       </x:c>
       <x:c r="B709" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C709" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D709" s="1">
         <x:v>0</x:v>
@@ -19218,10 +19221,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F709" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G709" s="1">
-        <x:v>50</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:7">
@@ -19229,10 +19232,10 @@
         <x:v>766</x:v>
       </x:c>
       <x:c r="B710" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C710" s="1">
-        <x:v>3550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D710" s="1">
         <x:v>0</x:v>
@@ -19241,33 +19244,33 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F710" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G710" s="1">
-        <x:v>9350</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:7">
       <x:c r="A711" s="1" t="s">
-        <x:v>766</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="B711" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C711" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D711" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E711" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F711" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G711" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="712" spans="1:7">
@@ -19275,22 +19278,22 @@
         <x:v>767</x:v>
       </x:c>
       <x:c r="B712" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C712" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D712" s="1">
-        <x:v>2572233</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E712" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F712" s="1">
-        <x:v>5500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G712" s="1">
-        <x:v>2577783</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:7">
@@ -19298,22 +19301,22 @@
         <x:v>768</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C713" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D713" s="1">
-        <x:v>0</x:v>
+        <x:v>2572233</x:v>
       </x:c>
       <x:c r="E713" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>0</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>50</x:v>
+        <x:v>2577783</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19321,7 +19324,7 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C714" s="1">
         <x:v>50</x:v>
@@ -19333,10 +19336,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>5750</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>5800</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">
@@ -19344,7 +19347,7 @@
         <x:v>770</x:v>
       </x:c>
       <x:c r="B715" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C715" s="1">
         <x:v>50</x:v>
@@ -19356,10 +19359,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F715" s="1">
-        <x:v>0</x:v>
+        <x:v>5750</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>50</x:v>
+        <x:v>5800</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
@@ -19367,10 +19370,10 @@
         <x:v>771</x:v>
       </x:c>
       <x:c r="B716" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C716" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D716" s="1">
         <x:v>0</x:v>
@@ -19379,10 +19382,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F716" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G716" s="1">
-        <x:v>3300</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:7">
@@ -19393,7 +19396,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C717" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D717" s="1">
         <x:v>0</x:v>
@@ -19402,10 +19405,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F717" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G717" s="1">
-        <x:v>50</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:7">
@@ -19413,7 +19416,7 @@
         <x:v>773</x:v>
       </x:c>
       <x:c r="B718" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C718" s="1">
         <x:v>50</x:v>
@@ -19425,10 +19428,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F718" s="1">
-        <x:v>5700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G718" s="1">
-        <x:v>5750</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:7">
@@ -19436,7 +19439,7 @@
         <x:v>774</x:v>
       </x:c>
       <x:c r="B719" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C719" s="1">
         <x:v>50</x:v>
@@ -19448,10 +19451,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F719" s="1">
-        <x:v>0</x:v>
+        <x:v>5700</x:v>
       </x:c>
       <x:c r="G719" s="1">
-        <x:v>50</x:v>
+        <x:v>5750</x:v>
       </x:c>
     </x:row>
     <x:row r="720" spans="1:7">
@@ -19459,7 +19462,7 @@
         <x:v>775</x:v>
       </x:c>
       <x:c r="B720" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C720" s="1">
         <x:v>50</x:v>
@@ -19482,22 +19485,22 @@
         <x:v>776</x:v>
       </x:c>
       <x:c r="B721" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C721" s="1">
-        <x:v>16500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D721" s="1">
-        <x:v>1892270</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E721" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F721" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G721" s="1">
-        <x:v>1909770</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:7">
@@ -19505,13 +19508,13 @@
         <x:v>777</x:v>
       </x:c>
       <x:c r="B722" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C722" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="D722" s="1">
-        <x:v>0</x:v>
+        <x:v>1892270</x:v>
       </x:c>
       <x:c r="E722" s="1">
         <x:v>0</x:v>
@@ -19520,7 +19523,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G722" s="1">
-        <x:v>1000</x:v>
+        <x:v>1909770</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:7">
@@ -19528,10 +19531,10 @@
         <x:v>778</x:v>
       </x:c>
       <x:c r="B723" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C723" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D723" s="1">
         <x:v>0</x:v>
@@ -19540,10 +19543,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F723" s="1">
-        <x:v>0</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G723" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:7">
@@ -19551,10 +19554,10 @@
         <x:v>779</x:v>
       </x:c>
       <x:c r="B724" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C724" s="1">
-        <x:v>2000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D724" s="1">
         <x:v>0</x:v>
@@ -19563,10 +19566,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F724" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>3500</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
@@ -19574,10 +19577,10 @@
         <x:v>780</x:v>
       </x:c>
       <x:c r="B725" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C725" s="1">
-        <x:v>50</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D725" s="1">
         <x:v>0</x:v>
@@ -19586,10 +19589,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F725" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G725" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:7">
@@ -19597,13 +19600,13 @@
         <x:v>781</x:v>
       </x:c>
       <x:c r="B726" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C726" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D726" s="1">
-        <x:v>40000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E726" s="1">
         <x:v>0</x:v>
@@ -19612,7 +19615,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G726" s="1">
-        <x:v>40000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:7">
@@ -19620,13 +19623,13 @@
         <x:v>782</x:v>
       </x:c>
       <x:c r="B727" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C727" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D727" s="1">
-        <x:v>0</x:v>
+        <x:v>40000</x:v>
       </x:c>
       <x:c r="E727" s="1">
         <x:v>0</x:v>
@@ -19635,7 +19638,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G727" s="1">
-        <x:v>1000</x:v>
+        <x:v>40000</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:7">
@@ -19643,10 +19646,10 @@
         <x:v>783</x:v>
       </x:c>
       <x:c r="B728" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C728" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D728" s="1">
         <x:v>0</x:v>
@@ -19658,7 +19661,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G728" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:7">
@@ -19666,10 +19669,10 @@
         <x:v>784</x:v>
       </x:c>
       <x:c r="B729" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C729" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D729" s="1">
         <x:v>0</x:v>
@@ -19678,10 +19681,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F729" s="1">
-        <x:v>5200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G729" s="1">
-        <x:v>5200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:7">
@@ -19689,10 +19692,10 @@
         <x:v>785</x:v>
       </x:c>
       <x:c r="B730" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C730" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D730" s="1">
         <x:v>0</x:v>
@@ -19701,10 +19704,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F730" s="1">
-        <x:v>0</x:v>
+        <x:v>5200</x:v>
       </x:c>
       <x:c r="G730" s="1">
-        <x:v>50</x:v>
+        <x:v>5200</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:7">
@@ -19712,7 +19715,7 @@
         <x:v>786</x:v>
       </x:c>
       <x:c r="B731" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C731" s="1">
         <x:v>50</x:v>
@@ -19735,7 +19738,7 @@
         <x:v>787</x:v>
       </x:c>
       <x:c r="B732" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C732" s="1">
         <x:v>50</x:v>
@@ -19747,10 +19750,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F732" s="1">
-        <x:v>5000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G732" s="1">
-        <x:v>5050</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:7">
@@ -19758,22 +19761,22 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="B733" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C733" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D733" s="1">
-        <x:v>3920589</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E733" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F733" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G733" s="1">
-        <x:v>3920589</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:7">
@@ -19781,13 +19784,13 @@
         <x:v>789</x:v>
       </x:c>
       <x:c r="B734" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C734" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D734" s="1">
-        <x:v>0</x:v>
+        <x:v>3920589</x:v>
       </x:c>
       <x:c r="E734" s="1">
         <x:v>0</x:v>
@@ -19796,7 +19799,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G734" s="1">
-        <x:v>50</x:v>
+        <x:v>3920589</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:7">
@@ -19804,10 +19807,10 @@
         <x:v>790</x:v>
       </x:c>
       <x:c r="B735" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C735" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D735" s="1">
         <x:v>0</x:v>
@@ -19819,7 +19822,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G735" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:7">
@@ -19827,10 +19830,10 @@
         <x:v>791</x:v>
       </x:c>
       <x:c r="B736" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C736" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D736" s="1">
         <x:v>0</x:v>
@@ -19842,7 +19845,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G736" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:7">
@@ -19850,7 +19853,7 @@
         <x:v>792</x:v>
       </x:c>
       <x:c r="B737" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C737" s="1">
         <x:v>50</x:v>
@@ -19873,10 +19876,10 @@
         <x:v>793</x:v>
       </x:c>
       <x:c r="B738" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C738" s="1">
-        <x:v>4500</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D738" s="1">
         <x:v>0</x:v>
@@ -19885,10 +19888,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F738" s="1">
-        <x:v>4834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G738" s="1">
-        <x:v>9334</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:7">
@@ -19896,10 +19899,10 @@
         <x:v>794</x:v>
       </x:c>
       <x:c r="B739" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C739" s="1">
-        <x:v>1050</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="D739" s="1">
         <x:v>0</x:v>
@@ -19908,10 +19911,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F739" s="1">
-        <x:v>0</x:v>
+        <x:v>4834</x:v>
       </x:c>
       <x:c r="G739" s="1">
-        <x:v>1050</x:v>
+        <x:v>9334</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:7">
@@ -19922,7 +19925,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="C740" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="D740" s="1">
         <x:v>0</x:v>
@@ -19934,7 +19937,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G740" s="1">
-        <x:v>50</x:v>
+        <x:v>1050</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:7">
@@ -19942,7 +19945,7 @@
         <x:v>796</x:v>
       </x:c>
       <x:c r="B741" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C741" s="1">
         <x:v>50</x:v>
@@ -19965,13 +19968,13 @@
         <x:v>797</x:v>
       </x:c>
       <x:c r="B742" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C742" s="1">
-        <x:v>3000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D742" s="1">
-        <x:v>889852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E742" s="1">
         <x:v>0</x:v>
@@ -19980,7 +19983,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G742" s="1">
-        <x:v>892852</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:7">
@@ -19988,13 +19991,13 @@
         <x:v>798</x:v>
       </x:c>
       <x:c r="B743" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C743" s="1">
-        <x:v>50</x:v>
+        <x:v>3000</x:v>
       </x:c>
       <x:c r="D743" s="1">
-        <x:v>0</x:v>
+        <x:v>889852</x:v>
       </x:c>
       <x:c r="E743" s="1">
         <x:v>0</x:v>
@@ -20003,7 +20006,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G743" s="1">
-        <x:v>50</x:v>
+        <x:v>892852</x:v>
       </x:c>
     </x:row>
     <x:row r="744" spans="1:7">
@@ -20011,10 +20014,10 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="B744" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C744" s="1">
-        <x:v>19600</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D744" s="1">
         <x:v>0</x:v>
@@ -20023,10 +20026,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F744" s="1">
-        <x:v>17000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G744" s="1">
-        <x:v>36600</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:7">
@@ -20034,10 +20037,10 @@
         <x:v>800</x:v>
       </x:c>
       <x:c r="B745" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C745" s="1">
-        <x:v>50</x:v>
+        <x:v>19600</x:v>
       </x:c>
       <x:c r="D745" s="1">
         <x:v>0</x:v>
@@ -20046,10 +20049,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F745" s="1">
-        <x:v>0</x:v>
+        <x:v>17000</x:v>
       </x:c>
       <x:c r="G745" s="1">
-        <x:v>50</x:v>
+        <x:v>36600</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:7">
@@ -20057,7 +20060,7 @@
         <x:v>801</x:v>
       </x:c>
       <x:c r="B746" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C746" s="1">
         <x:v>50</x:v>
@@ -20080,7 +20083,7 @@
         <x:v>802</x:v>
       </x:c>
       <x:c r="B747" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C747" s="1">
         <x:v>50</x:v>
@@ -20103,13 +20106,13 @@
         <x:v>803</x:v>
       </x:c>
       <x:c r="B748" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C748" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D748" s="1">
-        <x:v>1012792</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E748" s="1">
         <x:v>0</x:v>
@@ -20118,7 +20121,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G748" s="1">
-        <x:v>1012792</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:7">
@@ -20126,13 +20129,13 @@
         <x:v>804</x:v>
       </x:c>
       <x:c r="B749" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C749" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D749" s="1">
-        <x:v>0</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="E749" s="1">
         <x:v>0</x:v>
@@ -20141,7 +20144,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G749" s="1">
-        <x:v>50</x:v>
+        <x:v>1012792</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:7">
@@ -20149,10 +20152,10 @@
         <x:v>805</x:v>
       </x:c>
       <x:c r="B750" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C750" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D750" s="1">
         <x:v>0</x:v>
@@ -20161,10 +20164,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F750" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G750" s="1">
-        <x:v>30000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:7">
@@ -20172,10 +20175,10 @@
         <x:v>806</x:v>
       </x:c>
       <x:c r="B751" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C751" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D751" s="1">
         <x:v>0</x:v>
@@ -20184,10 +20187,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F751" s="1">
-        <x:v>0</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G751" s="1">
-        <x:v>50</x:v>
+        <x:v>30000</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:7">
@@ -20195,22 +20198,22 @@
         <x:v>807</x:v>
       </x:c>
       <x:c r="B752" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C752" s="1">
-        <x:v>19050</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D752" s="1">
-        <x:v>1350000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E752" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F752" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G752" s="1">
-        <x:v>1371550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:7">
@@ -20218,22 +20221,22 @@
         <x:v>808</x:v>
       </x:c>
       <x:c r="B753" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C753" s="1">
-        <x:v>3500</x:v>
+        <x:v>19050</x:v>
       </x:c>
       <x:c r="D753" s="1">
-        <x:v>0</x:v>
+        <x:v>1350000</x:v>
       </x:c>
       <x:c r="E753" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F753" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="G753" s="1">
-        <x:v>3500</x:v>
+        <x:v>1371550</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:7">
@@ -20241,10 +20244,10 @@
         <x:v>809</x:v>
       </x:c>
       <x:c r="B754" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C754" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D754" s="1">
         <x:v>0</x:v>
@@ -20256,18 +20259,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G754" s="1">
-        <x:v>50</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:7">
       <x:c r="A755" s="1" t="s">
-        <x:v>809</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="B755" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C755" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D755" s="1">
         <x:v>0</x:v>
@@ -20276,10 +20279,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F755" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G755" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:7">
@@ -20287,10 +20290,10 @@
         <x:v>810</x:v>
       </x:c>
       <x:c r="B756" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C756" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D756" s="1">
         <x:v>0</x:v>
@@ -20299,10 +20302,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F756" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G756" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:7">
@@ -20310,10 +20313,10 @@
         <x:v>811</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20325,7 +20328,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>6450</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20333,10 +20336,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20348,7 +20351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>50</x:v>
+        <x:v>6450</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">
@@ -20356,10 +20359,10 @@
         <x:v>813</x:v>
       </x:c>
       <x:c r="B759" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C759" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D759" s="1">
         <x:v>0</x:v>
@@ -20368,10 +20371,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F759" s="1">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G759" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:7">
@@ -20379,10 +20382,10 @@
         <x:v>814</x:v>
       </x:c>
       <x:c r="B760" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C760" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D760" s="1">
         <x:v>0</x:v>
@@ -20391,10 +20394,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F760" s="1">
-        <x:v>5000</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G760" s="1">
-        <x:v>5050</x:v>
+        <x:v>1000</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:7">
@@ -20402,7 +20405,7 @@
         <x:v>815</x:v>
       </x:c>
       <x:c r="B761" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C761" s="1">
         <x:v>50</x:v>
@@ -20414,10 +20417,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F761" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G761" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:7">
@@ -20425,10 +20428,10 @@
         <x:v>816</x:v>
       </x:c>
       <x:c r="B762" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C762" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D762" s="1">
         <x:v>0</x:v>
@@ -20437,10 +20440,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F762" s="1">
-        <x:v>13200</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G762" s="1">
-        <x:v>13200</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:7">
@@ -20448,10 +20451,10 @@
         <x:v>817</x:v>
       </x:c>
       <x:c r="B763" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C763" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D763" s="1">
         <x:v>0</x:v>
@@ -20460,10 +20463,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F763" s="1">
-        <x:v>0</x:v>
+        <x:v>13200</x:v>
       </x:c>
       <x:c r="G763" s="1">
-        <x:v>50</x:v>
+        <x:v>13200</x:v>
       </x:c>
     </x:row>
     <x:row r="764" spans="1:7">
@@ -20471,7 +20474,7 @@
         <x:v>818</x:v>
       </x:c>
       <x:c r="B764" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C764" s="1">
         <x:v>50</x:v>
@@ -20494,13 +20497,13 @@
         <x:v>819</x:v>
       </x:c>
       <x:c r="B765" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C765" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D765" s="1">
-        <x:v>943006</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E765" s="1">
         <x:v>0</x:v>
@@ -20509,7 +20512,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G765" s="1">
-        <x:v>943056</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="766" spans="1:7">
@@ -20517,13 +20520,13 @@
         <x:v>820</x:v>
       </x:c>
       <x:c r="B766" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C766" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="D766" s="1">
-        <x:v>0</x:v>
+        <x:v>943006</x:v>
       </x:c>
       <x:c r="E766" s="1">
         <x:v>0</x:v>
@@ -20532,7 +20535,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G766" s="1">
-        <x:v>50</x:v>
+        <x:v>943056</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:7">
@@ -20540,7 +20543,7 @@
         <x:v>821</x:v>
       </x:c>
       <x:c r="B767" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C767" s="1">
         <x:v>50</x:v>
@@ -20563,22 +20566,22 @@
         <x:v>822</x:v>
       </x:c>
       <x:c r="B768" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C768" s="1">
-        <x:v>1000</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D768" s="1">
-        <x:v>476254</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E768" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F768" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G768" s="1">
-        <x:v>478754</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:7">
@@ -20586,22 +20589,22 @@
         <x:v>823</x:v>
       </x:c>
       <x:c r="B769" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C769" s="1">
-        <x:v>50</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="D769" s="1">
-        <x:v>0</x:v>
+        <x:v>476254</x:v>
       </x:c>
       <x:c r="E769" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F769" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G769" s="1">
-        <x:v>50</x:v>
+        <x:v>478754</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:7">
@@ -20609,7 +20612,7 @@
         <x:v>824</x:v>
       </x:c>
       <x:c r="B770" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C770" s="1">
         <x:v>50</x:v>
@@ -20621,10 +20624,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F770" s="1">
-        <x:v>4999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G770" s="1">
-        <x:v>5049</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="771" spans="1:7">
@@ -20632,10 +20635,10 @@
         <x:v>825</x:v>
       </x:c>
       <x:c r="B771" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C771" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D771" s="1">
         <x:v>0</x:v>
@@ -20644,10 +20647,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F771" s="1">
-        <x:v>16500</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="G771" s="1">
-        <x:v>16500</x:v>
+        <x:v>5049</x:v>
       </x:c>
     </x:row>
     <x:row r="772" spans="1:7">
@@ -20655,10 +20658,10 @@
         <x:v>826</x:v>
       </x:c>
       <x:c r="B772" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C772" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D772" s="1">
         <x:v>0</x:v>
@@ -20667,10 +20670,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F772" s="1">
-        <x:v>0</x:v>
+        <x:v>16500</x:v>
       </x:c>
       <x:c r="G772" s="1">
-        <x:v>50</x:v>
+        <x:v>16500</x:v>
       </x:c>
     </x:row>
     <x:row r="773" spans="1:7">
@@ -20678,7 +20681,7 @@
         <x:v>827</x:v>
       </x:c>
       <x:c r="B773" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C773" s="1">
         <x:v>50</x:v>
@@ -20701,7 +20704,7 @@
         <x:v>828</x:v>
       </x:c>
       <x:c r="B774" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C774" s="1">
         <x:v>50</x:v>
@@ -20724,7 +20727,7 @@
         <x:v>829</x:v>
       </x:c>
       <x:c r="B775" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C775" s="1">
         <x:v>50</x:v>
@@ -20747,7 +20750,7 @@
         <x:v>830</x:v>
       </x:c>
       <x:c r="B776" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C776" s="1">
         <x:v>50</x:v>
@@ -20759,10 +20762,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F776" s="1">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G776" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:7">
@@ -20770,7 +20773,7 @@
         <x:v>831</x:v>
       </x:c>
       <x:c r="B777" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C777" s="1">
         <x:v>50</x:v>
@@ -20782,10 +20785,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F777" s="1">
-        <x:v>0</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G777" s="1">
-        <x:v>50</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="778" spans="1:7">
@@ -20793,10 +20796,10 @@
         <x:v>832</x:v>
       </x:c>
       <x:c r="B778" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C778" s="1">
-        <x:v>10850</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D778" s="1">
         <x:v>0</x:v>
@@ -20805,10 +20808,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F778" s="1">
-        <x:v>37300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G778" s="1">
-        <x:v>48150</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:7">
@@ -20816,10 +20819,10 @@
         <x:v>833</x:v>
       </x:c>
       <x:c r="B779" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C779" s="1">
-        <x:v>0</x:v>
+        <x:v>10850</x:v>
       </x:c>
       <x:c r="D779" s="1">
         <x:v>0</x:v>
@@ -20828,10 +20831,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F779" s="1">
-        <x:v>83</x:v>
+        <x:v>37300</x:v>
       </x:c>
       <x:c r="G779" s="1">
-        <x:v>83</x:v>
+        <x:v>48150</x:v>
       </x:c>
     </x:row>
     <x:row r="780" spans="1:7">
@@ -20839,10 +20842,10 @@
         <x:v>834</x:v>
       </x:c>
       <x:c r="B780" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C780" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D780" s="1">
         <x:v>0</x:v>
@@ -20851,10 +20854,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F780" s="1">
-        <x:v>0</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G780" s="1">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="781" spans="1:7">
@@ -20862,7 +20865,7 @@
         <x:v>835</x:v>
       </x:c>
       <x:c r="B781" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C781" s="1">
         <x:v>50</x:v>
@@ -20885,7 +20888,7 @@
         <x:v>836</x:v>
       </x:c>
       <x:c r="B782" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C782" s="1">
         <x:v>50</x:v>
@@ -20908,10 +20911,10 @@
         <x:v>837</x:v>
       </x:c>
       <x:c r="B783" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C783" s="1">
-        <x:v>1550</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D783" s="1">
         <x:v>0</x:v>
@@ -20920,10 +20923,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F783" s="1">
-        <x:v>30000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G783" s="1">
-        <x:v>31550</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="784" spans="1:7">
@@ -20931,21 +20934,44 @@
         <x:v>838</x:v>
       </x:c>
       <x:c r="B784" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C784" s="1">
+        <x:v>1550</x:v>
+      </x:c>
+      <x:c r="D784" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E784" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F784" s="1">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="G784" s="1">
+        <x:v>31550</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="785" spans="1:7">
+      <x:c r="A785" s="1" t="s">
+        <x:v>839</x:v>
+      </x:c>
+      <x:c r="B785" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C784" s="1">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D784" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E784" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F784" s="1">
+      <x:c r="C785" s="1">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D785" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E785" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F785" s="1">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="G784" s="1">
+      <x:c r="G785" s="1">
         <x:v>328</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3782,7 +3782,7 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>0</x:v>
+        <x:v>1016284</x:v>
       </x:c>
       <x:c r="E38" s="1">
         <x:v>0</x:v>
@@ -3791,7 +3791,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G38" s="1">
-        <x:v>2500</x:v>
+        <x:v>1018784</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -5208,7 +5208,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D100" s="1">
-        <x:v>511942</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="E100" s="1">
         <x:v>0</x:v>
@@ -5217,7 +5217,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G100" s="1">
-        <x:v>511942</x:v>
+        <x:v>547042</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
@@ -16771,7 +16771,7 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C603" s="1">
         <x:v>0</x:v>
@@ -16794,7 +16794,7 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C604" s="1">
         <x:v>0</x:v>
@@ -17231,10 +17231,10 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C623" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D623" s="1">
         <x:v>0</x:v>
@@ -17243,10 +17243,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F623" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G623" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="624" spans="1:7">
@@ -17254,10 +17254,10 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C624" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D624" s="1">
         <x:v>0</x:v>
@@ -17266,10 +17266,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F624" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G624" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="625" spans="1:7">
@@ -17668,22 +17668,22 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="B642" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C642" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D642" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E642" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F642" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G642" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:7">
@@ -17691,22 +17691,22 @@
         <x:v>700</x:v>
       </x:c>
       <x:c r="B643" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C643" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D643" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E643" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F643" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G643" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="644" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16771,7 +16771,7 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C603" s="1">
         <x:v>0</x:v>
@@ -16794,7 +16794,7 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C604" s="1">
         <x:v>0</x:v>
@@ -17231,10 +17231,10 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B623" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C623" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D623" s="1">
         <x:v>0</x:v>
@@ -17243,10 +17243,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F623" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G623" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="624" spans="1:7">
@@ -17254,10 +17254,10 @@
         <x:v>682</x:v>
       </x:c>
       <x:c r="B624" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C624" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D624" s="1">
         <x:v>0</x:v>
@@ -17266,10 +17266,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F624" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G624" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="625" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -8221,7 +8221,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D231" s="1">
-        <x:v>50571</x:v>
+        <x:v>101142</x:v>
       </x:c>
       <x:c r="E231" s="1">
         <x:v>0</x:v>
@@ -8230,7 +8230,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G231" s="1">
-        <x:v>50621</x:v>
+        <x:v>101192</x:v>
       </x:c>
     </x:row>
     <x:row r="232" spans="1:7">
@@ -14546,7 +14546,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D506" s="1">
-        <x:v>50571</x:v>
+        <x:v>101142</x:v>
       </x:c>
       <x:c r="E506" s="1">
         <x:v>0</x:v>
@@ -14555,7 +14555,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G506" s="1">
-        <x:v>50571</x:v>
+        <x:v>101142</x:v>
       </x:c>
     </x:row>
     <x:row r="507" spans="1:7">
@@ -16771,7 +16771,7 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B603" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C603" s="1">
         <x:v>0</x:v>
@@ -16794,7 +16794,7 @@
         <x:v>661</x:v>
       </x:c>
       <x:c r="B604" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C604" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17283,10 +17283,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D625" s="1">
         <x:v>0</x:v>
@@ -17295,10 +17295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17306,10 +17306,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17318,10 +17318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17720,22 +17720,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F644" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17743,22 +17743,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16823,7 +16823,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>0</x:v>
@@ -16846,7 +16846,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -17283,10 +17283,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D625" s="1">
         <x:v>0</x:v>
@@ -17295,10 +17295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17306,10 +17306,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17318,10 +17318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17720,22 +17720,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F644" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17743,22 +17743,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17283,10 +17283,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D625" s="1">
         <x:v>0</x:v>
@@ -17295,10 +17295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17306,10 +17306,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17318,10 +17318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -20319,10 +20319,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20331,10 +20331,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20342,10 +20342,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20354,10 +20354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -8250,7 +8250,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D232" s="1">
-        <x:v>101142</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="E232" s="1">
         <x:v>0</x:v>
@@ -8259,7 +8259,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G232" s="1">
-        <x:v>101192</x:v>
+        <x:v>151763</x:v>
       </x:c>
     </x:row>
     <x:row r="233" spans="1:7">
@@ -14598,7 +14598,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D508" s="1">
-        <x:v>101142</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="E508" s="1">
         <x:v>0</x:v>
@@ -14607,7 +14607,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G508" s="1">
-        <x:v>101142</x:v>
+        <x:v>151713</x:v>
       </x:c>
     </x:row>
     <x:row r="509" spans="1:7">
@@ -20319,10 +20319,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20331,10 +20331,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20342,10 +20342,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20354,10 +20354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3351,7 +3351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>0</x:v>
+        <x:v>94764</x:v>
       </x:c>
       <x:c r="E19" s="1">
         <x:v>0</x:v>
@@ -3360,7 +3360,7 @@
         <x:v>14100</x:v>
       </x:c>
       <x:c r="G19" s="1">
-        <x:v>14100</x:v>
+        <x:v>108864</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
@@ -19307,22 +19307,22 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D713" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E713" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>9350</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19330,22 +19330,22 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D714" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E714" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16823,7 +16823,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>0</x:v>
@@ -16846,7 +16846,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -19307,22 +19307,22 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B713" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C713" s="1">
-        <x:v>0</x:v>
+        <x:v>3550</x:v>
       </x:c>
       <x:c r="D713" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E713" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F713" s="1">
-        <x:v>0</x:v>
+        <x:v>5800</x:v>
       </x:c>
       <x:c r="G713" s="1">
-        <x:v>1100000</x:v>
+        <x:v>9350</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:7">
@@ -19330,22 +19330,22 @@
         <x:v>769</x:v>
       </x:c>
       <x:c r="B714" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C714" s="1">
-        <x:v>3550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D714" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E714" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F714" s="1">
-        <x:v>5800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G714" s="1">
-        <x:v>9350</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3558,16 +3558,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>0</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="E28" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F28" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G28" s="1">
         <x:v>98455</x:v>
-      </x:c>
-      <x:c r="F28" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G28" s="1">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
@@ -3932,10 +3932,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>0</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="G44" s="1">
-        <x:v>50</x:v>
+        <x:v>15050</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
@@ -4156,7 +4156,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D54" s="1">
-        <x:v>5259859</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="E54" s="1">
         <x:v>0</x:v>
@@ -4165,7 +4165,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G54" s="1">
-        <x:v>5259859</x:v>
+        <x:v>5259858</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
@@ -5082,10 +5082,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G94" s="1">
-        <x:v>50</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
@@ -7514,16 +7514,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D200" s="1">
-        <x:v>0</x:v>
+        <x:v>344592</x:v>
       </x:c>
       <x:c r="E200" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F200" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G200" s="1">
         <x:v>344592</x:v>
-      </x:c>
-      <x:c r="F200" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G200" s="1">
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:7">
@@ -8072,10 +8072,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F224" s="1">
-        <x:v>18500</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G224" s="1">
-        <x:v>162240</x:v>
+        <x:v>165740</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:7">
@@ -9314,10 +9314,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F278" s="1">
-        <x:v>0</x:v>
+        <x:v>15000</x:v>
       </x:c>
       <x:c r="G278" s="1">
-        <x:v>50</x:v>
+        <x:v>15050</x:v>
       </x:c>
     </x:row>
     <x:row r="279" spans="1:7">
@@ -9952,7 +9952,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D306" s="1">
-        <x:v>1335613</x:v>
+        <x:v>2071226</x:v>
       </x:c>
       <x:c r="E306" s="1">
         <x:v>0</x:v>
@@ -9961,7 +9961,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G306" s="1">
-        <x:v>1335663</x:v>
+        <x:v>2071276</x:v>
       </x:c>
     </x:row>
     <x:row r="307" spans="1:7">
@@ -10573,7 +10573,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D333" s="1">
-        <x:v>366028</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="E333" s="1">
         <x:v>0</x:v>
@@ -10582,7 +10582,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G333" s="1">
-        <x:v>366028</x:v>
+        <x:v>377124</x:v>
       </x:c>
     </x:row>
     <x:row r="334" spans="1:7">
@@ -13385,10 +13385,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F455" s="1">
-        <x:v>16550</x:v>
+        <x:v>20050</x:v>
       </x:c>
       <x:c r="G455" s="1">
-        <x:v>129760</x:v>
+        <x:v>133260</x:v>
       </x:c>
     </x:row>
     <x:row r="456" spans="1:7">
@@ -13517,7 +13517,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D461" s="1">
-        <x:v>372060</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="E461" s="1">
         <x:v>0</x:v>
@@ -13526,7 +13526,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G461" s="1">
-        <x:v>372060</x:v>
+        <x:v>382680</x:v>
       </x:c>
     </x:row>
     <x:row r="462" spans="1:7">
@@ -14161,7 +14161,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="D489" s="1">
-        <x:v>400022</x:v>
+        <x:v>800044</x:v>
       </x:c>
       <x:c r="E489" s="1">
         <x:v>0</x:v>
@@ -14170,7 +14170,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G489" s="1">
-        <x:v>401022</x:v>
+        <x:v>801044</x:v>
       </x:c>
     </x:row>
     <x:row r="490" spans="1:7">
@@ -14184,7 +14184,7 @@
         <x:v>3500</x:v>
       </x:c>
       <x:c r="D490" s="1">
-        <x:v>44693946</x:v>
+        <x:v>50315254</x:v>
       </x:c>
       <x:c r="E490" s="1">
         <x:v>0</x:v>
@@ -14193,7 +14193,7 @@
         <x:v>8000</x:v>
       </x:c>
       <x:c r="G490" s="1">
-        <x:v>44705446</x:v>
+        <x:v>50326754</x:v>
       </x:c>
     </x:row>
     <x:row r="491" spans="1:7">
@@ -15363,10 +15363,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F541" s="1">
-        <x:v>3334</x:v>
+        <x:v>6834</x:v>
       </x:c>
       <x:c r="G541" s="1">
-        <x:v>3384</x:v>
+        <x:v>6884</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:7">
@@ -18347,7 +18347,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D671" s="1">
-        <x:v>367531</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="E671" s="1">
         <x:v>0</x:v>
@@ -18356,7 +18356,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G671" s="1">
-        <x:v>367531</x:v>
+        <x:v>380377</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:7">
@@ -19359,7 +19359,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="D715" s="1">
-        <x:v>2572233</x:v>
+        <x:v>2835078</x:v>
       </x:c>
       <x:c r="E715" s="1">
         <x:v>0</x:v>
@@ -19368,7 +19368,7 @@
         <x:v>5500</x:v>
       </x:c>
       <x:c r="G715" s="1">
-        <x:v>2577783</x:v>
+        <x:v>2840628</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:7">
@@ -19566,7 +19566,7 @@
         <x:v>16500</x:v>
       </x:c>
       <x:c r="D724" s="1">
-        <x:v>1892270</x:v>
+        <x:v>2192272</x:v>
       </x:c>
       <x:c r="E724" s="1">
         <x:v>0</x:v>
@@ -19575,7 +19575,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G724" s="1">
-        <x:v>1909770</x:v>
+        <x:v>2209772</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:7">
@@ -20647,7 +20647,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="D771" s="1">
-        <x:v>476254</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="E771" s="1">
         <x:v>0</x:v>
@@ -20656,7 +20656,7 @@
         <x:v>8500</x:v>
       </x:c>
       <x:c r="G771" s="1">
-        <x:v>485754</x:v>
+        <x:v>496674</x:v>
       </x:c>
     </x:row>
     <x:row r="772" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16823,7 +16823,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>0</x:v>
@@ -16846,7 +16846,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -17720,22 +17720,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F644" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17743,22 +17743,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16823,7 +16823,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>0</x:v>
@@ -16846,7 +16846,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -17720,22 +17720,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F644" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17743,22 +17743,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -20319,10 +20319,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20331,10 +20331,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20342,10 +20342,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20354,10 +20354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3351,7 +3351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>94764</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="E19" s="1">
         <x:v>0</x:v>
@@ -3360,7 +3360,7 @@
         <x:v>14100</x:v>
       </x:c>
       <x:c r="G19" s="1">
-        <x:v>108864</x:v>
+        <x:v>203628</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
@@ -18088,13 +18088,13 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D660" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E660" s="1">
         <x:v>0</x:v>
@@ -18103,7 +18103,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18111,13 +18111,13 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18126,7 +18126,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -20319,10 +20319,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20331,10 +20331,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20342,10 +20342,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20354,10 +20354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -9049,13 +9049,13 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B267" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C267" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D267" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E267" s="1">
         <x:v>0</x:v>
@@ -9064,7 +9064,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G267" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="268" spans="1:7">
@@ -9072,13 +9072,13 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B268" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C268" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D268" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E268" s="1">
         <x:v>0</x:v>
@@ -9087,7 +9087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="269" spans="1:7">
@@ -16823,7 +16823,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>0</x:v>
@@ -16846,7 +16846,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -18088,13 +18088,13 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D660" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E660" s="1">
         <x:v>0</x:v>
@@ -18103,7 +18103,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18111,13 +18111,13 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18126,7 +18126,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -20319,10 +20319,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20331,10 +20331,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20342,10 +20342,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20354,10 +20354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -9049,13 +9049,13 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B267" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C267" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D267" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E267" s="1">
         <x:v>0</x:v>
@@ -9064,7 +9064,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G267" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="268" spans="1:7">
@@ -9072,13 +9072,13 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B268" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C268" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D268" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E268" s="1">
         <x:v>0</x:v>
@@ -9087,7 +9087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="269" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3351,7 +3351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>189528</x:v>
+        <x:v>284292</x:v>
       </x:c>
       <x:c r="E19" s="1">
         <x:v>0</x:v>
@@ -3360,7 +3360,7 @@
         <x:v>14100</x:v>
       </x:c>
       <x:c r="G19" s="1">
-        <x:v>203628</x:v>
+        <x:v>298392</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
@@ -20319,10 +20319,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20331,10 +20331,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20342,10 +20342,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20354,10 +20354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17283,10 +17283,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D625" s="1">
         <x:v>0</x:v>
@@ -17295,10 +17295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17306,10 +17306,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17318,10 +17318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -18088,13 +18088,13 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D660" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E660" s="1">
         <x:v>0</x:v>
@@ -18103,7 +18103,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18111,13 +18111,13 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18126,7 +18126,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">
@@ -18238,10 +18238,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F666" s="1">
-        <x:v>5000</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="G666" s="1">
-        <x:v>5050</x:v>
+        <x:v>19550</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16823,7 +16823,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>0</x:v>
@@ -16846,7 +16846,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -17283,10 +17283,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B625" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="C625" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D625" s="1">
         <x:v>0</x:v>
@@ -17295,10 +17295,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F625" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G625" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:7">
@@ -17306,10 +17306,10 @@
         <x:v>684</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17318,10 +17318,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17720,22 +17720,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F644" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17743,22 +17743,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17720,22 +17720,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B644" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C644" s="1">
-        <x:v>0</x:v>
+        <x:v>4550</x:v>
       </x:c>
       <x:c r="D644" s="1">
-        <x:v>1100000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E644" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F644" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G644" s="1">
-        <x:v>1100000</x:v>
+        <x:v>5050</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:7">
@@ -17743,22 +17743,22 @@
         <x:v>702</x:v>
       </x:c>
       <x:c r="B645" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C645" s="1">
-        <x:v>4550</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D645" s="1">
-        <x:v>0</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E645" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F645" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G645" s="1">
-        <x:v>5050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:7">
@@ -18088,13 +18088,13 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B660" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C660" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D660" s="1">
-        <x:v>226240</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E660" s="1">
         <x:v>0</x:v>
@@ -18103,7 +18103,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G660" s="1">
-        <x:v>226240</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:7">
@@ -18111,13 +18111,13 @@
         <x:v>717</x:v>
       </x:c>
       <x:c r="B661" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C661" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D661" s="1">
-        <x:v>0</x:v>
+        <x:v>226240</x:v>
       </x:c>
       <x:c r="E661" s="1">
         <x:v>0</x:v>
@@ -18126,7 +18126,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G661" s="1">
-        <x:v>50</x:v>
+        <x:v>226240</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -9049,13 +9049,13 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B267" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C267" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D267" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E267" s="1">
         <x:v>0</x:v>
@@ -9064,7 +9064,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G267" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="268" spans="1:7">
@@ -9072,13 +9072,13 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B268" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C268" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D268" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E268" s="1">
         <x:v>0</x:v>
@@ -9087,7 +9087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="269" spans="1:7">
@@ -20319,10 +20319,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20331,10 +20331,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20342,10 +20342,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20354,10 +20354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -3351,7 +3351,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>284292</x:v>
+        <x:v>379056</x:v>
       </x:c>
       <x:c r="E19" s="1">
         <x:v>0</x:v>
@@ -3360,7 +3360,7 @@
         <x:v>14100</x:v>
       </x:c>
       <x:c r="G19" s="1">
-        <x:v>298392</x:v>
+        <x:v>393156</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
@@ -9049,13 +9049,13 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B267" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C267" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D267" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700000</x:v>
       </x:c>
       <x:c r="E267" s="1">
         <x:v>0</x:v>
@@ -9064,7 +9064,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G267" s="1">
-        <x:v>1100000</x:v>
+        <x:v>7700050</x:v>
       </x:c>
     </x:row>
     <x:row r="268" spans="1:7">
@@ -9072,13 +9072,13 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B268" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C268" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D268" s="1">
-        <x:v>7700000</x:v>
+        <x:v>1100000</x:v>
       </x:c>
       <x:c r="E268" s="1">
         <x:v>0</x:v>
@@ -9087,7 +9087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G268" s="1">
-        <x:v>7700050</x:v>
+        <x:v>1100000</x:v>
       </x:c>
     </x:row>
     <x:row r="269" spans="1:7">
@@ -16823,7 +16823,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>0</x:v>
@@ -16846,7 +16846,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -20319,10 +20319,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B757" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C757" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D757" s="1">
         <x:v>0</x:v>
@@ -20331,10 +20331,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F757" s="1">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G757" s="1">
-        <x:v>35</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:7">
@@ -20342,10 +20342,10 @@
         <x:v>812</x:v>
       </x:c>
       <x:c r="B758" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C758" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D758" s="1">
         <x:v>0</x:v>
@@ -20354,10 +20354,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F758" s="1">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G758" s="1">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16823,7 +16823,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>0</x:v>
@@ -16846,7 +16846,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -14420,10 +14420,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F500" s="1">
-        <x:v>0</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="G500" s="1">
-        <x:v>50</x:v>
+        <x:v>14050</x:v>
       </x:c>
     </x:row>
     <x:row r="501" spans="1:7">
@@ -16823,7 +16823,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B605" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C605" s="1">
         <x:v>0</x:v>
@@ -16846,7 +16846,7 @@
         <x:v>663</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17309,10 +17309,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17321,10 +17321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17332,10 +17332,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17344,10 +17344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -16849,7 +16849,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B606" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C606" s="1">
         <x:v>0</x:v>
@@ -16872,7 +16872,7 @@
         <x:v>664</x:v>
       </x:c>
       <x:c r="B607" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C607" s="1">
         <x:v>0</x:v>
@@ -17309,10 +17309,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17321,10 +17321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17332,10 +17332,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17344,10 +17344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">

--- a/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-crypto/pro-crypto-candidate-lobby-lifetime-report.xlsx
@@ -17309,10 +17309,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B626" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C626" s="1">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D626" s="1">
         <x:v>0</x:v>
@@ -17321,10 +17321,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F626" s="1">
-        <x:v>249</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G626" s="1">
-        <x:v>249</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:7">
@@ -17332,10 +17332,10 @@
         <x:v>685</x:v>
       </x:c>
       <x:c r="B627" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C627" s="1">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D627" s="1">
         <x:v>0</x:v>
@@ -17344,10 +17344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F627" s="1">
-        <x:v>0</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G627" s="1">
-        <x:v>50</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:7">
